--- a/data/danish_artwork_review.xlsx
+++ b/data/danish_artwork_review.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EPGoal\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2A5422C-5881-4321-BE44-844B562D4C1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77998F98-2650-4853-BFDA-D803C775E18C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3267" uniqueCount="1640">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3287" uniqueCount="1650">
   <si>
     <t>Nøgle (intern)</t>
   </si>
@@ -2369,6 +2369,12 @@
     <t>Jagerpilotens sidste mission</t>
   </si>
   <si>
+    <t>jagten på danmarkshistorien</t>
+  </si>
+  <si>
+    <t>Jagten på Danmarkshistorien</t>
+  </si>
+  <si>
     <t>jagten på regnbuens magi</t>
   </si>
   <si>
@@ -2435,6 +2441,12 @@
     <t>Kald mig far</t>
   </si>
   <si>
+    <t>kamæleonen</t>
+  </si>
+  <si>
+    <t>Kamæleonen</t>
+  </si>
+  <si>
     <t>kaptajn sabeltand og den magiske diamant</t>
   </si>
   <si>
@@ -3029,6 +3041,12 @@
     <t>Min enestående mor</t>
   </si>
   <si>
+    <t>min fars krig</t>
+  </si>
+  <si>
+    <t>Min fars krig</t>
+  </si>
+  <si>
     <t>min kones ferie</t>
   </si>
   <si>
@@ -4841,6 +4859,12 @@
     <t>Vores planet</t>
   </si>
   <si>
+    <t>vores spektakulære solsystem</t>
+  </si>
+  <si>
+    <t>Vores spektakulære solsystem</t>
+  </si>
+  <si>
     <t>værkstedet</t>
   </si>
   <si>
@@ -4869,6 +4893,12 @@
   </si>
   <si>
     <t>Winnerbäck Et Slags Liv</t>
+  </si>
+  <si>
+    <t>wisting</t>
+  </si>
+  <si>
+    <t>Wisting</t>
   </si>
   <si>
     <t>wizards beyond waverly place</t>
@@ -5318,7 +5348,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F813"/>
+  <dimension ref="A1:F818"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -5358,7 +5388,7 @@
       <c r="C2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D2" t="s">
         <v>8</v>
       </c>
     </row>
@@ -5742,10 +5772,10 @@
     </row>
     <row r="30" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="B30" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>7</v>
@@ -5756,10 +5786,10 @@
     </row>
     <row r="31" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="B31" t="s">
-        <v>850</v>
+        <v>854</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>7</v>
@@ -5770,10 +5800,10 @@
     </row>
     <row r="32" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="B32" t="s">
-        <v>890</v>
+        <v>894</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>7</v>
@@ -5784,10 +5814,10 @@
     </row>
     <row r="33" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>903</v>
+        <v>907</v>
       </c>
       <c r="B33" t="s">
-        <v>904</v>
+        <v>908</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>7</v>
@@ -5798,10 +5828,10 @@
     </row>
     <row r="34" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
       <c r="B34" t="s">
-        <v>928</v>
+        <v>932</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>7</v>
@@ -5812,10 +5842,10 @@
     </row>
     <row r="35" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>943</v>
+        <v>947</v>
       </c>
       <c r="B35" t="s">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>7</v>
@@ -5826,10 +5856,10 @@
     </row>
     <row r="36" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>1031</v>
+        <v>1037</v>
       </c>
       <c r="B36" t="s">
-        <v>1032</v>
+        <v>1038</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>7</v>
@@ -5840,10 +5870,10 @@
     </row>
     <row r="37" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>1087</v>
+        <v>1093</v>
       </c>
       <c r="B37" t="s">
-        <v>1088</v>
+        <v>1094</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>7</v>
@@ -5854,10 +5884,10 @@
     </row>
     <row r="38" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>1231</v>
+        <v>1237</v>
       </c>
       <c r="B38" t="s">
-        <v>1232</v>
+        <v>1238</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>7</v>
@@ -5868,10 +5898,10 @@
     </row>
     <row r="39" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>1259</v>
+        <v>1265</v>
       </c>
       <c r="B39" t="s">
-        <v>1260</v>
+        <v>1266</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>7</v>
@@ -5882,10 +5912,10 @@
     </row>
     <row r="40" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>1287</v>
+        <v>1293</v>
       </c>
       <c r="B40" t="s">
-        <v>1288</v>
+        <v>1294</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>7</v>
@@ -5896,10 +5926,10 @@
     </row>
     <row r="41" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>1297</v>
+        <v>1303</v>
       </c>
       <c r="B41" t="s">
-        <v>1298</v>
+        <v>1304</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>7</v>
@@ -5910,10 +5940,10 @@
     </row>
     <row r="42" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>1303</v>
+        <v>1309</v>
       </c>
       <c r="B42" t="s">
-        <v>1304</v>
+        <v>1310</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>7</v>
@@ -5924,10 +5954,10 @@
     </row>
     <row r="43" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>1317</v>
+        <v>1323</v>
       </c>
       <c r="B43" t="s">
-        <v>1318</v>
+        <v>1324</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>7</v>
@@ -5938,10 +5968,10 @@
     </row>
     <row r="44" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>1321</v>
+        <v>1327</v>
       </c>
       <c r="B44" t="s">
-        <v>1322</v>
+        <v>1328</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>7</v>
@@ -5952,10 +5982,10 @@
     </row>
     <row r="45" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>1399</v>
+        <v>1405</v>
       </c>
       <c r="B45" t="s">
-        <v>1400</v>
+        <v>1406</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>7</v>
@@ -5966,10 +5996,10 @@
     </row>
     <row r="46" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>1445</v>
+        <v>1451</v>
       </c>
       <c r="B46" t="s">
-        <v>1446</v>
+        <v>1452</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>7</v>
@@ -5980,10 +6010,10 @@
     </row>
     <row r="47" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>1447</v>
+        <v>1453</v>
       </c>
       <c r="B47" t="s">
-        <v>1448</v>
+        <v>1454</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>7</v>
@@ -5994,10 +6024,10 @@
     </row>
     <row r="48" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>1459</v>
+        <v>1465</v>
       </c>
       <c r="B48" t="s">
-        <v>1460</v>
+        <v>1466</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>7</v>
@@ -6008,10 +6038,10 @@
     </row>
     <row r="49" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>1461</v>
+        <v>1467</v>
       </c>
       <c r="B49" t="s">
-        <v>1462</v>
+        <v>1468</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>7</v>
@@ -6022,10 +6052,10 @@
     </row>
     <row r="50" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>1479</v>
+        <v>1485</v>
       </c>
       <c r="B50" t="s">
-        <v>1480</v>
+        <v>1486</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>7</v>
@@ -6036,10 +6066,10 @@
     </row>
     <row r="51" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>1499</v>
+        <v>1505</v>
       </c>
       <c r="B51" t="s">
-        <v>1500</v>
+        <v>1506</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>7</v>
@@ -6050,10 +6080,10 @@
     </row>
     <row r="52" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>1523</v>
+        <v>1529</v>
       </c>
       <c r="B52" t="s">
-        <v>1524</v>
+        <v>1530</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>7</v>
@@ -6064,10 +6094,10 @@
     </row>
     <row r="53" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>1563</v>
+        <v>1569</v>
       </c>
       <c r="B53" t="s">
-        <v>1564</v>
+        <v>1570</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>7</v>
@@ -6078,10 +6108,10 @@
     </row>
     <row r="54" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>1575</v>
+        <v>1581</v>
       </c>
       <c r="B54" t="s">
-        <v>1576</v>
+        <v>1582</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>7</v>
@@ -6092,10 +6122,10 @@
     </row>
     <row r="55" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>1605</v>
+        <v>1613</v>
       </c>
       <c r="B55" t="s">
-        <v>1606</v>
+        <v>1614</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>7</v>
@@ -7338,10 +7368,10 @@
     </row>
     <row r="144" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B144" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>7</v>
@@ -7352,10 +7382,10 @@
     </row>
     <row r="145" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B145" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>7</v>
@@ -7366,10 +7396,10 @@
     </row>
     <row r="146" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B146" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>7</v>
@@ -7380,10 +7410,10 @@
     </row>
     <row r="147" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B147" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>7</v>
@@ -7394,10 +7424,10 @@
     </row>
     <row r="148" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B148" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>7</v>
@@ -7408,10 +7438,10 @@
     </row>
     <row r="149" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B149" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>7</v>
@@ -7422,10 +7452,10 @@
     </row>
     <row r="150" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B150" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>7</v>
@@ -7436,10 +7466,10 @@
     </row>
     <row r="151" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B151" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>7</v>
@@ -7450,10 +7480,10 @@
     </row>
     <row r="152" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B152" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>7</v>
@@ -7464,10 +7494,10 @@
     </row>
     <row r="153" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B153" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>7</v>
@@ -7478,10 +7508,10 @@
     </row>
     <row r="154" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B154" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>7</v>
@@ -7492,10 +7522,10 @@
     </row>
     <row r="155" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B155" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>7</v>
@@ -7506,10 +7536,10 @@
     </row>
     <row r="156" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B156" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>7</v>
@@ -7520,10 +7550,10 @@
     </row>
     <row r="157" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B157" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>7</v>
@@ -7534,10 +7564,10 @@
     </row>
     <row r="158" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B158" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>7</v>
@@ -7548,10 +7578,10 @@
     </row>
     <row r="159" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B159" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>7</v>
@@ -7562,10 +7592,10 @@
     </row>
     <row r="160" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B160" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>7</v>
@@ -7576,10 +7606,10 @@
     </row>
     <row r="161" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B161" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>7</v>
@@ -7590,10 +7620,10 @@
     </row>
     <row r="162" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B162" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>7</v>
@@ -7604,10 +7634,10 @@
     </row>
     <row r="163" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B163" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>7</v>
@@ -7618,10 +7648,10 @@
     </row>
     <row r="164" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B164" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>7</v>
@@ -7632,10 +7662,10 @@
     </row>
     <row r="165" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B165" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>7</v>
@@ -7646,10 +7676,10 @@
     </row>
     <row r="166" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B166" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>7</v>
@@ -7660,10 +7690,10 @@
     </row>
     <row r="167" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B167" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>7</v>
@@ -7674,10 +7704,10 @@
     </row>
     <row r="168" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B168" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C168" s="2" t="s">
         <v>7</v>
@@ -7688,10 +7718,10 @@
     </row>
     <row r="169" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B169" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C169" s="2" t="s">
         <v>7</v>
@@ -7702,10 +7732,10 @@
     </row>
     <row r="170" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B170" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C170" s="2" t="s">
         <v>7</v>
@@ -7716,10 +7746,10 @@
     </row>
     <row r="171" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B171" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C171" s="2" t="s">
         <v>7</v>
@@ -7730,10 +7760,10 @@
     </row>
     <row r="172" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B172" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>7</v>
@@ -7744,10 +7774,10 @@
     </row>
     <row r="173" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B173" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C173" s="2" t="s">
         <v>7</v>
@@ -7758,10 +7788,10 @@
     </row>
     <row r="174" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="B174" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>7</v>
@@ -7772,10 +7802,10 @@
     </row>
     <row r="175" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B175" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>7</v>
@@ -7786,10 +7816,10 @@
     </row>
     <row r="176" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B176" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C176" s="2" t="s">
         <v>7</v>
@@ -7800,10 +7830,10 @@
     </row>
     <row r="177" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="B177" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="C177" s="2" t="s">
         <v>7</v>
@@ -7814,10 +7844,10 @@
     </row>
     <row r="178" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="B178" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="C178" s="2" t="s">
         <v>7</v>
@@ -7828,10 +7858,10 @@
     </row>
     <row r="179" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B179" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>7</v>
@@ -7842,10 +7872,10 @@
     </row>
     <row r="180" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B180" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C180" s="2" t="s">
         <v>7</v>
@@ -7856,10 +7886,10 @@
     </row>
     <row r="181" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="B181" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C181" s="2" t="s">
         <v>7</v>
@@ -7870,10 +7900,10 @@
     </row>
     <row r="182" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B182" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C182" s="2" t="s">
         <v>7</v>
@@ -7884,10 +7914,10 @@
     </row>
     <row r="183" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B183" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C183" s="2" t="s">
         <v>7</v>
@@ -7898,10 +7928,10 @@
     </row>
     <row r="184" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B184" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C184" s="2" t="s">
         <v>7</v>
@@ -7912,10 +7942,10 @@
     </row>
     <row r="185" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B185" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C185" s="2" t="s">
         <v>7</v>
@@ -7926,10 +7956,10 @@
     </row>
     <row r="186" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B186" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C186" s="2" t="s">
         <v>7</v>
@@ -7940,10 +7970,10 @@
     </row>
     <row r="187" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B187" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C187" s="2" t="s">
         <v>7</v>
@@ -7954,10 +7984,10 @@
     </row>
     <row r="188" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B188" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C188" s="2" t="s">
         <v>7</v>
@@ -7968,10 +7998,10 @@
     </row>
     <row r="189" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B189" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>7</v>
@@ -7982,10 +8012,10 @@
     </row>
     <row r="190" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B190" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>7</v>
@@ -7996,10 +8026,10 @@
     </row>
     <row r="191" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="B191" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="C191" s="2" t="s">
         <v>7</v>
@@ -8010,10 +8040,10 @@
     </row>
     <row r="192" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B192" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C192" s="2" t="s">
         <v>7</v>
@@ -8024,10 +8054,10 @@
     </row>
     <row r="193" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B193" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C193" s="2" t="s">
         <v>7</v>
@@ -8038,10 +8068,10 @@
     </row>
     <row r="194" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B194" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C194" s="2" t="s">
         <v>7</v>
@@ -8052,10 +8082,10 @@
     </row>
     <row r="195" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B195" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C195" s="2" t="s">
         <v>7</v>
@@ -8066,10 +8096,10 @@
     </row>
     <row r="196" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B196" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C196" s="2" t="s">
         <v>7</v>
@@ -8080,10 +8110,10 @@
     </row>
     <row r="197" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B197" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C197" s="2" t="s">
         <v>7</v>
@@ -8094,10 +8124,10 @@
     </row>
     <row r="198" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B198" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C198" s="2" t="s">
         <v>7</v>
@@ -8108,10 +8138,10 @@
     </row>
     <row r="199" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B199" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C199" s="2" t="s">
         <v>7</v>
@@ -8122,10 +8152,10 @@
     </row>
     <row r="200" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B200" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C200" s="2" t="s">
         <v>7</v>
@@ -8136,10 +8166,10 @@
     </row>
     <row r="201" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B201" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C201" s="2" t="s">
         <v>7</v>
@@ -8150,10 +8180,10 @@
     </row>
     <row r="202" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B202" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C202" s="2" t="s">
         <v>7</v>
@@ -8164,10 +8194,10 @@
     </row>
     <row r="203" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B203" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C203" s="2" t="s">
         <v>7</v>
@@ -8178,10 +8208,10 @@
     </row>
     <row r="204" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B204" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C204" s="2" t="s">
         <v>7</v>
@@ -8192,10 +8222,10 @@
     </row>
     <row r="205" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B205" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C205" s="2" t="s">
         <v>7</v>
@@ -8206,10 +8236,10 @@
     </row>
     <row r="206" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B206" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C206" s="2" t="s">
         <v>7</v>
@@ -8220,10 +8250,10 @@
     </row>
     <row r="207" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="B207" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="C207" s="2" t="s">
         <v>7</v>
@@ -8234,10 +8264,10 @@
     </row>
     <row r="208" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B208" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C208" s="2" t="s">
         <v>7</v>
@@ -8248,10 +8278,10 @@
     </row>
     <row r="209" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B209" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C209" s="2" t="s">
         <v>7</v>
@@ -8262,10 +8292,10 @@
     </row>
     <row r="210" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B210" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C210" s="2" t="s">
         <v>7</v>
@@ -8276,10 +8306,10 @@
     </row>
     <row r="211" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B211" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C211" s="2" t="s">
         <v>7</v>
@@ -8290,10 +8320,10 @@
     </row>
     <row r="212" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B212" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C212" s="2" t="s">
         <v>7</v>
@@ -8304,10 +8334,10 @@
     </row>
     <row r="213" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B213" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C213" s="2" t="s">
         <v>7</v>
@@ -8318,10 +8348,10 @@
     </row>
     <row r="214" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B214" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C214" s="2" t="s">
         <v>7</v>
@@ -8332,10 +8362,10 @@
     </row>
     <row r="215" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B215" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C215" s="2" t="s">
         <v>7</v>
@@ -8346,10 +8376,10 @@
     </row>
     <row r="216" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B216" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C216" s="2" t="s">
         <v>7</v>
@@ -8360,10 +8390,10 @@
     </row>
     <row r="217" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B217" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C217" s="2" t="s">
         <v>7</v>
@@ -8374,10 +8404,10 @@
     </row>
     <row r="218" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B218" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C218" s="2" t="s">
         <v>7</v>
@@ -8388,10 +8418,10 @@
     </row>
     <row r="219" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B219" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C219" s="2" t="s">
         <v>7</v>
@@ -8402,10 +8432,10 @@
     </row>
     <row r="220" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B220" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C220" s="2" t="s">
         <v>7</v>
@@ -8416,10 +8446,10 @@
     </row>
     <row r="221" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B221" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C221" s="2" t="s">
         <v>7</v>
@@ -8430,10 +8460,10 @@
     </row>
     <row r="222" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B222" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C222" s="2" t="s">
         <v>7</v>
@@ -8444,10 +8474,10 @@
     </row>
     <row r="223" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B223" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C223" s="2" t="s">
         <v>7</v>
@@ -8458,10 +8488,10 @@
     </row>
     <row r="224" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B224" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C224" s="2" t="s">
         <v>7</v>
@@ -8472,10 +8502,10 @@
     </row>
     <row r="225" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="B225" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="C225" s="2" t="s">
         <v>7</v>
@@ -8486,10 +8516,10 @@
     </row>
     <row r="226" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B226" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C226" s="2" t="s">
         <v>7</v>
@@ -8500,10 +8530,10 @@
     </row>
     <row r="227" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B227" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C227" s="2" t="s">
         <v>7</v>
@@ -8514,10 +8544,10 @@
     </row>
     <row r="228" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="B228" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="C228" s="2" t="s">
         <v>7</v>
@@ -8528,10 +8558,10 @@
     </row>
     <row r="229" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B229" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C229" s="2" t="s">
         <v>7</v>
@@ -8542,10 +8572,10 @@
     </row>
     <row r="230" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B230" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C230" s="2" t="s">
         <v>7</v>
@@ -8556,10 +8586,10 @@
     </row>
     <row r="231" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B231" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C231" s="2" t="s">
         <v>7</v>
@@ -8570,10 +8600,10 @@
     </row>
     <row r="232" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B232" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C232" s="2" t="s">
         <v>7</v>
@@ -8584,10 +8614,10 @@
     </row>
     <row r="233" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B233" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C233" s="2" t="s">
         <v>7</v>
@@ -8598,10 +8628,10 @@
     </row>
     <row r="234" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="B234" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="C234" s="2" t="s">
         <v>7</v>
@@ -8612,10 +8642,10 @@
     </row>
     <row r="235" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B235" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C235" s="2" t="s">
         <v>7</v>
@@ -8626,10 +8656,10 @@
     </row>
     <row r="236" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B236" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C236" s="2" t="s">
         <v>7</v>
@@ -8640,10 +8670,10 @@
     </row>
     <row r="237" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B237" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C237" s="2" t="s">
         <v>7</v>
@@ -8654,10 +8684,10 @@
     </row>
     <row r="238" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B238" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C238" s="2" t="s">
         <v>7</v>
@@ -8668,10 +8698,10 @@
     </row>
     <row r="239" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B239" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C239" s="2" t="s">
         <v>7</v>
@@ -8682,10 +8712,10 @@
     </row>
     <row r="240" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B240" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C240" s="2" t="s">
         <v>7</v>
@@ -8696,10 +8726,10 @@
     </row>
     <row r="241" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B241" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C241" s="2" t="s">
         <v>7</v>
@@ -8710,10 +8740,10 @@
     </row>
     <row r="242" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B242" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C242" s="2" t="s">
         <v>7</v>
@@ -8724,10 +8754,10 @@
     </row>
     <row r="243" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B243" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C243" s="2" t="s">
         <v>7</v>
@@ -8738,10 +8768,10 @@
     </row>
     <row r="244" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B244" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C244" s="2" t="s">
         <v>7</v>
@@ -8752,10 +8782,10 @@
     </row>
     <row r="245" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B245" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C245" s="2" t="s">
         <v>7</v>
@@ -8766,10 +8796,10 @@
     </row>
     <row r="246" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B246" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C246" s="2" t="s">
         <v>7</v>
@@ -8780,10 +8810,10 @@
     </row>
     <row r="247" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B247" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C247" s="2" t="s">
         <v>7</v>
@@ -8794,10 +8824,10 @@
     </row>
     <row r="248" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B248" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C248" s="2" t="s">
         <v>7</v>
@@ -8808,10 +8838,10 @@
     </row>
     <row r="249" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B249" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C249" s="2" t="s">
         <v>7</v>
@@ -8822,10 +8852,10 @@
     </row>
     <row r="250" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B250" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C250" s="2" t="s">
         <v>7</v>
@@ -8836,10 +8866,10 @@
     </row>
     <row r="251" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B251" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C251" s="2" t="s">
         <v>7</v>
@@ -8850,10 +8880,10 @@
     </row>
     <row r="252" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="B252" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="C252" s="2" t="s">
         <v>7</v>
@@ -8864,10 +8894,10 @@
     </row>
     <row r="253" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B253" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C253" s="2" t="s">
         <v>7</v>
@@ -8878,10 +8908,10 @@
     </row>
     <row r="254" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B254" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C254" s="2" t="s">
         <v>7</v>
@@ -8892,10 +8922,10 @@
     </row>
     <row r="255" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B255" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C255" s="2" t="s">
         <v>7</v>
@@ -8906,10 +8936,10 @@
     </row>
     <row r="256" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B256" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C256" s="2" t="s">
         <v>7</v>
@@ -8920,10 +8950,10 @@
     </row>
     <row r="257" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B257" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C257" s="2" t="s">
         <v>7</v>
@@ -8934,10 +8964,10 @@
     </row>
     <row r="258" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B258" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C258" s="2" t="s">
         <v>7</v>
@@ -8948,10 +8978,10 @@
     </row>
     <row r="259" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B259" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C259" s="2" t="s">
         <v>7</v>
@@ -8962,10 +8992,10 @@
     </row>
     <row r="260" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B260" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C260" s="2" t="s">
         <v>7</v>
@@ -8976,10 +9006,10 @@
     </row>
     <row r="261" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B261" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C261" s="2" t="s">
         <v>7</v>
@@ -8990,10 +9020,10 @@
     </row>
     <row r="262" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B262" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C262" s="2" t="s">
         <v>7</v>
@@ -9004,10 +9034,10 @@
     </row>
     <row r="263" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B263" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C263" s="2" t="s">
         <v>7</v>
@@ -9018,10 +9048,10 @@
     </row>
     <row r="264" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B264" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C264" s="2" t="s">
         <v>7</v>
@@ -9032,10 +9062,10 @@
     </row>
     <row r="265" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B265" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C265" s="2" t="s">
         <v>7</v>
@@ -9046,10 +9076,10 @@
     </row>
     <row r="266" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B266" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C266" s="2" t="s">
         <v>7</v>
@@ -9060,10 +9090,10 @@
     </row>
     <row r="267" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B267" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C267" s="2" t="s">
         <v>7</v>
@@ -9074,10 +9104,10 @@
     </row>
     <row r="268" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B268" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C268" s="2" t="s">
         <v>7</v>
@@ -9088,10 +9118,10 @@
     </row>
     <row r="269" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B269" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C269" s="2" t="s">
         <v>7</v>
@@ -9102,10 +9132,10 @@
     </row>
     <row r="270" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B270" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C270" s="2" t="s">
         <v>7</v>
@@ -9116,10 +9146,10 @@
     </row>
     <row r="271" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B271" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C271" s="2" t="s">
         <v>7</v>
@@ -9130,10 +9160,10 @@
     </row>
     <row r="272" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B272" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C272" s="2" t="s">
         <v>7</v>
@@ -9144,10 +9174,10 @@
     </row>
     <row r="273" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B273" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C273" s="2" t="s">
         <v>7</v>
@@ -9158,10 +9188,10 @@
     </row>
     <row r="274" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B274" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C274" s="2" t="s">
         <v>7</v>
@@ -9172,10 +9202,10 @@
     </row>
     <row r="275" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B275" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C275" s="2" t="s">
         <v>7</v>
@@ -9186,10 +9216,10 @@
     </row>
     <row r="276" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B276" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C276" s="2" t="s">
         <v>7</v>
@@ -9200,10 +9230,10 @@
     </row>
     <row r="277" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B277" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C277" s="2" t="s">
         <v>7</v>
@@ -9214,10 +9244,10 @@
     </row>
     <row r="278" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="B278" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C278" s="2" t="s">
         <v>7</v>
@@ -9228,10 +9258,10 @@
     </row>
     <row r="279" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B279" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C279" s="2" t="s">
         <v>7</v>
@@ -9242,10 +9272,10 @@
     </row>
     <row r="280" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="B280" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="C280" s="2" t="s">
         <v>7</v>
@@ -9256,10 +9286,10 @@
     </row>
     <row r="281" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B281" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C281" s="2" t="s">
         <v>7</v>
@@ -9270,10 +9300,10 @@
     </row>
     <row r="282" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B282" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C282" s="2" t="s">
         <v>7</v>
@@ -9284,10 +9314,10 @@
     </row>
     <row r="283" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B283" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C283" s="2" t="s">
         <v>7</v>
@@ -9298,10 +9328,10 @@
     </row>
     <row r="284" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="B284" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="C284" s="2" t="s">
         <v>7</v>
@@ -9312,10 +9342,10 @@
     </row>
     <row r="285" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B285" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C285" s="2" t="s">
         <v>7</v>
@@ -9326,10 +9356,10 @@
     </row>
     <row r="286" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B286" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C286" s="2" t="s">
         <v>7</v>
@@ -9340,10 +9370,10 @@
     </row>
     <row r="287" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B287" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C287" s="2" t="s">
         <v>7</v>
@@ -9354,10 +9384,10 @@
     </row>
     <row r="288" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B288" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="C288" s="2" t="s">
         <v>7</v>
@@ -9368,10 +9398,10 @@
     </row>
     <row r="289" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B289" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C289" s="2" t="s">
         <v>7</v>
@@ -9382,10 +9412,10 @@
     </row>
     <row r="290" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B290" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C290" s="2" t="s">
         <v>7</v>
@@ -9396,10 +9426,10 @@
     </row>
     <row r="291" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B291" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="C291" s="2" t="s">
         <v>7</v>
@@ -9410,10 +9440,10 @@
     </row>
     <row r="292" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B292" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C292" s="2" t="s">
         <v>7</v>
@@ -9424,10 +9454,10 @@
     </row>
     <row r="293" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="B293" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="C293" s="2" t="s">
         <v>7</v>
@@ -9438,10 +9468,10 @@
     </row>
     <row r="294" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B294" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C294" s="2" t="s">
         <v>7</v>
@@ -9452,10 +9482,10 @@
     </row>
     <row r="295" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B295" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C295" s="2" t="s">
         <v>7</v>
@@ -9466,10 +9496,10 @@
     </row>
     <row r="296" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="B296" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C296" s="2" t="s">
         <v>7</v>
@@ -9480,10 +9510,10 @@
     </row>
     <row r="297" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B297" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C297" s="2" t="s">
         <v>7</v>
@@ -9494,10 +9524,10 @@
     </row>
     <row r="298" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B298" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="C298" s="2" t="s">
         <v>7</v>
@@ -9508,10 +9538,10 @@
     </row>
     <row r="299" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B299" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="C299" s="2" t="s">
         <v>7</v>
@@ -9522,10 +9552,10 @@
     </row>
     <row r="300" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B300" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C300" s="2" t="s">
         <v>7</v>
@@ -9536,10 +9566,10 @@
     </row>
     <row r="301" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B301" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="C301" s="2" t="s">
         <v>7</v>
@@ -9550,10 +9580,10 @@
     </row>
     <row r="302" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B302" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="C302" s="2" t="s">
         <v>7</v>
@@ -9564,10 +9594,10 @@
     </row>
     <row r="303" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B303" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C303" s="2" t="s">
         <v>7</v>
@@ -9578,10 +9608,10 @@
     </row>
     <row r="304" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B304" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C304" s="2" t="s">
         <v>7</v>
@@ -9592,10 +9622,10 @@
     </row>
     <row r="305" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B305" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C305" s="2" t="s">
         <v>7</v>
@@ -9606,10 +9636,10 @@
     </row>
     <row r="306" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B306" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="C306" s="2" t="s">
         <v>7</v>
@@ -9620,10 +9650,10 @@
     </row>
     <row r="307" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B307" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C307" s="2" t="s">
         <v>7</v>
@@ -9634,10 +9664,10 @@
     </row>
     <row r="308" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="B308" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="C308" s="2" t="s">
         <v>7</v>
@@ -9648,10 +9678,10 @@
     </row>
     <row r="309" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B309" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="C309" s="2" t="s">
         <v>7</v>
@@ -9662,10 +9692,10 @@
     </row>
     <row r="310" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B310" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C310" s="2" t="s">
         <v>7</v>
@@ -9676,10 +9706,10 @@
     </row>
     <row r="311" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B311" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="C311" s="2" t="s">
         <v>7</v>
@@ -9690,10 +9720,10 @@
     </row>
     <row r="312" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="B312" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="C312" s="2" t="s">
         <v>7</v>
@@ -9704,10 +9734,10 @@
     </row>
     <row r="313" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B313" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="C313" s="2" t="s">
         <v>7</v>
@@ -9718,10 +9748,10 @@
     </row>
     <row r="314" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="B314" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C314" s="2" t="s">
         <v>7</v>
@@ -9732,10 +9762,10 @@
     </row>
     <row r="315" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B315" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C315" s="2" t="s">
         <v>7</v>
@@ -9746,10 +9776,10 @@
     </row>
     <row r="316" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="B316" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C316" s="2" t="s">
         <v>7</v>
@@ -9760,10 +9790,10 @@
     </row>
     <row r="317" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B317" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C317" s="2" t="s">
         <v>7</v>
@@ -9774,10 +9804,10 @@
     </row>
     <row r="318" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B318" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="C318" s="2" t="s">
         <v>7</v>
@@ -9788,10 +9818,10 @@
     </row>
     <row r="319" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="B319" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="C319" s="2" t="s">
         <v>7</v>
@@ -9802,10 +9832,10 @@
     </row>
     <row r="320" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B320" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="C320" s="2" t="s">
         <v>7</v>
@@ -9816,10 +9846,10 @@
     </row>
     <row r="321" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="B321" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="C321" s="2" t="s">
         <v>7</v>
@@ -9830,10 +9860,10 @@
     </row>
     <row r="322" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B322" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C322" s="2" t="s">
         <v>7</v>
@@ -9844,10 +9874,10 @@
     </row>
     <row r="323" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="B323" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C323" s="2" t="s">
         <v>7</v>
@@ -9858,10 +9888,10 @@
     </row>
     <row r="324" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="B324" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="C324" s="2" t="s">
         <v>7</v>
@@ -9872,10 +9902,10 @@
     </row>
     <row r="325" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B325" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="C325" s="2" t="s">
         <v>7</v>
@@ -9886,10 +9916,10 @@
     </row>
     <row r="326" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="B326" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="C326" s="2" t="s">
         <v>7</v>
@@ -9900,10 +9930,10 @@
     </row>
     <row r="327" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B327" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="C327" s="2" t="s">
         <v>7</v>
@@ -9914,10 +9944,10 @@
     </row>
     <row r="328" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="B328" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="C328" s="2" t="s">
         <v>7</v>
@@ -9928,10 +9958,10 @@
     </row>
     <row r="329" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B329" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="C329" s="2" t="s">
         <v>7</v>
@@ -9942,10 +9972,10 @@
     </row>
     <row r="330" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="B330" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="C330" s="2" t="s">
         <v>7</v>
@@ -9956,10 +9986,10 @@
     </row>
     <row r="331" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="B331" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C331" s="2" t="s">
         <v>7</v>
@@ -9970,10 +10000,10 @@
     </row>
     <row r="332" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B332" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="C332" s="2" t="s">
         <v>7</v>
@@ -9984,10 +10014,10 @@
     </row>
     <row r="333" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="B333" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="C333" s="2" t="s">
         <v>7</v>
@@ -9998,10 +10028,10 @@
     </row>
     <row r="334" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="B334" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="C334" s="2" t="s">
         <v>7</v>
@@ -10012,10 +10042,10 @@
     </row>
     <row r="335" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="B335" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="C335" s="2" t="s">
         <v>7</v>
@@ -10026,10 +10056,10 @@
     </row>
     <row r="336" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B336" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="C336" s="2" t="s">
         <v>7</v>
@@ -10040,10 +10070,10 @@
     </row>
     <row r="337" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="B337" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="C337" s="2" t="s">
         <v>7</v>
@@ -10054,10 +10084,10 @@
     </row>
     <row r="338" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="B338" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="C338" s="2" t="s">
         <v>7</v>
@@ -10068,10 +10098,10 @@
     </row>
     <row r="339" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="B339" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="C339" s="2" t="s">
         <v>7</v>
@@ -10082,10 +10112,10 @@
     </row>
     <row r="340" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="B340" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="C340" s="2" t="s">
         <v>7</v>
@@ -10096,10 +10126,10 @@
     </row>
     <row r="341" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="B341" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="C341" s="2" t="s">
         <v>7</v>
@@ -10110,10 +10140,10 @@
     </row>
     <row r="342" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="B342" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="C342" s="2" t="s">
         <v>7</v>
@@ -10124,10 +10154,10 @@
     </row>
     <row r="343" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="B343" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C343" s="2" t="s">
         <v>7</v>
@@ -10138,10 +10168,10 @@
     </row>
     <row r="344" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B344" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C344" s="2" t="s">
         <v>7</v>
@@ -10152,10 +10182,10 @@
     </row>
     <row r="345" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B345" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="C345" s="2" t="s">
         <v>7</v>
@@ -10166,10 +10196,10 @@
     </row>
     <row r="346" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="B346" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="C346" s="2" t="s">
         <v>7</v>
@@ -10180,10 +10210,10 @@
     </row>
     <row r="347" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="B347" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="C347" s="2" t="s">
         <v>7</v>
@@ -10194,10 +10224,10 @@
     </row>
     <row r="348" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B348" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="C348" s="2" t="s">
         <v>7</v>
@@ -10208,10 +10238,10 @@
     </row>
     <row r="349" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="B349" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="C349" s="2" t="s">
         <v>7</v>
@@ -10222,10 +10252,10 @@
     </row>
     <row r="350" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="B350" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C350" s="2" t="s">
         <v>7</v>
@@ -10236,10 +10266,10 @@
     </row>
     <row r="351" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="B351" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="C351" s="2" t="s">
         <v>7</v>
@@ -10250,10 +10280,10 @@
     </row>
     <row r="352" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="B352" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="C352" s="2" t="s">
         <v>7</v>
@@ -10264,10 +10294,10 @@
     </row>
     <row r="353" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>659</v>
+        <v>653</v>
       </c>
       <c r="B353" t="s">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="C353" s="2" t="s">
         <v>7</v>
@@ -10278,10 +10308,10 @@
     </row>
     <row r="354" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>661</v>
+        <v>655</v>
       </c>
       <c r="B354" t="s">
-        <v>662</v>
+        <v>656</v>
       </c>
       <c r="C354" s="2" t="s">
         <v>7</v>
@@ -10292,10 +10322,10 @@
     </row>
     <row r="355" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="B355" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="C355" s="2" t="s">
         <v>7</v>
@@ -10306,10 +10336,10 @@
     </row>
     <row r="356" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="B356" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="C356" s="2" t="s">
         <v>7</v>
@@ -10320,10 +10350,10 @@
     </row>
     <row r="357" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="B357" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="C357" s="2" t="s">
         <v>7</v>
@@ -10334,10 +10364,10 @@
     </row>
     <row r="358" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="B358" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="C358" s="2" t="s">
         <v>7</v>
@@ -10348,10 +10378,10 @@
     </row>
     <row r="359" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="B359" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="C359" s="2" t="s">
         <v>7</v>
@@ -10362,10 +10392,10 @@
     </row>
     <row r="360" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="B360" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="C360" s="2" t="s">
         <v>7</v>
@@ -10376,10 +10406,10 @@
     </row>
     <row r="361" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B361" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="C361" s="2" t="s">
         <v>7</v>
@@ -10390,10 +10420,10 @@
     </row>
     <row r="362" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="B362" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="C362" s="2" t="s">
         <v>7</v>
@@ -10404,10 +10434,10 @@
     </row>
     <row r="363" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="B363" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="C363" s="2" t="s">
         <v>7</v>
@@ -10418,10 +10448,10 @@
     </row>
     <row r="364" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="B364" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="C364" s="2" t="s">
         <v>7</v>
@@ -10432,10 +10462,10 @@
     </row>
     <row r="365" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="B365" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="C365" s="2" t="s">
         <v>7</v>
@@ -10446,10 +10476,10 @@
     </row>
     <row r="366" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="B366" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="C366" s="2" t="s">
         <v>7</v>
@@ -10460,10 +10490,10 @@
     </row>
     <row r="367" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="B367" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="C367" s="2" t="s">
         <v>7</v>
@@ -10474,10 +10504,10 @@
     </row>
     <row r="368" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="B368" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="C368" s="2" t="s">
         <v>7</v>
@@ -10488,10 +10518,10 @@
     </row>
     <row r="369" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="B369" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="C369" s="2" t="s">
         <v>7</v>
@@ -10502,10 +10532,10 @@
     </row>
     <row r="370" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>695</v>
+        <v>689</v>
       </c>
       <c r="B370" t="s">
-        <v>696</v>
+        <v>690</v>
       </c>
       <c r="C370" s="2" t="s">
         <v>7</v>
@@ -10516,10 +10546,10 @@
     </row>
     <row r="371" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="B371" t="s">
-        <v>698</v>
+        <v>692</v>
       </c>
       <c r="C371" s="2" t="s">
         <v>7</v>
@@ -10530,10 +10560,10 @@
     </row>
     <row r="372" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="B372" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="C372" s="2" t="s">
         <v>7</v>
@@ -10544,10 +10574,10 @@
     </row>
     <row r="373" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="B373" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="C373" s="2" t="s">
         <v>7</v>
@@ -10558,10 +10588,10 @@
     </row>
     <row r="374" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>703</v>
+        <v>697</v>
       </c>
       <c r="B374" t="s">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="C374" s="2" t="s">
         <v>7</v>
@@ -10572,10 +10602,10 @@
     </row>
     <row r="375" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="B375" t="s">
-        <v>706</v>
+        <v>700</v>
       </c>
       <c r="C375" s="2" t="s">
         <v>7</v>
@@ -10586,10 +10616,10 @@
     </row>
     <row r="376" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>707</v>
+        <v>701</v>
       </c>
       <c r="B376" t="s">
-        <v>708</v>
+        <v>702</v>
       </c>
       <c r="C376" s="2" t="s">
         <v>7</v>
@@ -10600,10 +10630,10 @@
     </row>
     <row r="377" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>709</v>
+        <v>703</v>
       </c>
       <c r="B377" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="C377" s="2" t="s">
         <v>7</v>
@@ -10614,10 +10644,10 @@
     </row>
     <row r="378" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="B378" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="C378" s="2" t="s">
         <v>7</v>
@@ -10628,10 +10658,10 @@
     </row>
     <row r="379" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="B379" t="s">
-        <v>714</v>
+        <v>708</v>
       </c>
       <c r="C379" s="2" t="s">
         <v>7</v>
@@ -10642,10 +10672,10 @@
     </row>
     <row r="380" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>715</v>
+        <v>709</v>
       </c>
       <c r="B380" t="s">
-        <v>716</v>
+        <v>710</v>
       </c>
       <c r="C380" s="2" t="s">
         <v>7</v>
@@ -10656,10 +10686,10 @@
     </row>
     <row r="381" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>717</v>
+        <v>711</v>
       </c>
       <c r="B381" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="C381" s="2" t="s">
         <v>7</v>
@@ -10670,10 +10700,10 @@
     </row>
     <row r="382" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>719</v>
+        <v>713</v>
       </c>
       <c r="B382" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="C382" s="2" t="s">
         <v>7</v>
@@ -10684,10 +10714,10 @@
     </row>
     <row r="383" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="B383" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="C383" s="2" t="s">
         <v>7</v>
@@ -10698,10 +10728,10 @@
     </row>
     <row r="384" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
       <c r="B384" t="s">
-        <v>724</v>
+        <v>718</v>
       </c>
       <c r="C384" s="2" t="s">
         <v>7</v>
@@ -10712,10 +10742,10 @@
     </row>
     <row r="385" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="B385" t="s">
-        <v>726</v>
+        <v>720</v>
       </c>
       <c r="C385" s="2" t="s">
         <v>7</v>
@@ -10726,10 +10756,10 @@
     </row>
     <row r="386" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="B386" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="C386" s="2" t="s">
         <v>7</v>
@@ -10740,10 +10770,10 @@
     </row>
     <row r="387" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>729</v>
+        <v>723</v>
       </c>
       <c r="B387" t="s">
-        <v>730</v>
+        <v>724</v>
       </c>
       <c r="C387" s="2" t="s">
         <v>7</v>
@@ -10754,10 +10784,10 @@
     </row>
     <row r="388" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="B388" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="C388" s="2" t="s">
         <v>7</v>
@@ -10768,10 +10798,10 @@
     </row>
     <row r="389" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>733</v>
+        <v>727</v>
       </c>
       <c r="B389" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="C389" s="2" t="s">
         <v>7</v>
@@ -10782,10 +10812,10 @@
     </row>
     <row r="390" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>735</v>
+        <v>729</v>
       </c>
       <c r="B390" t="s">
-        <v>736</v>
+        <v>730</v>
       </c>
       <c r="C390" s="2" t="s">
         <v>7</v>
@@ -10796,10 +10826,10 @@
     </row>
     <row r="391" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="B391" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="C391" s="2" t="s">
         <v>7</v>
@@ -10810,10 +10840,10 @@
     </row>
     <row r="392" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="B392" t="s">
-        <v>740</v>
+        <v>734</v>
       </c>
       <c r="C392" s="2" t="s">
         <v>7</v>
@@ -10824,10 +10854,10 @@
     </row>
     <row r="393" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
       <c r="B393" t="s">
-        <v>742</v>
+        <v>736</v>
       </c>
       <c r="C393" s="2" t="s">
         <v>7</v>
@@ -10838,10 +10868,10 @@
     </row>
     <row r="394" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="B394" t="s">
-        <v>744</v>
+        <v>738</v>
       </c>
       <c r="C394" s="2" t="s">
         <v>7</v>
@@ -10852,10 +10882,10 @@
     </row>
     <row r="395" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>745</v>
+        <v>739</v>
       </c>
       <c r="B395" t="s">
-        <v>746</v>
+        <v>740</v>
       </c>
       <c r="C395" s="2" t="s">
         <v>7</v>
@@ -10866,10 +10896,10 @@
     </row>
     <row r="396" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>747</v>
+        <v>741</v>
       </c>
       <c r="B396" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="C396" s="2" t="s">
         <v>7</v>
@@ -10880,10 +10910,10 @@
     </row>
     <row r="397" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>749</v>
+        <v>743</v>
       </c>
       <c r="B397" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="C397" s="2" t="s">
         <v>7</v>
@@ -10894,10 +10924,10 @@
     </row>
     <row r="398" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>751</v>
+        <v>745</v>
       </c>
       <c r="B398" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="C398" s="2" t="s">
         <v>7</v>
@@ -10908,10 +10938,10 @@
     </row>
     <row r="399" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>753</v>
+        <v>747</v>
       </c>
       <c r="B399" t="s">
-        <v>754</v>
+        <v>748</v>
       </c>
       <c r="C399" s="2" t="s">
         <v>7</v>
@@ -10922,10 +10952,10 @@
     </row>
     <row r="400" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>755</v>
+        <v>749</v>
       </c>
       <c r="B400" t="s">
-        <v>756</v>
+        <v>750</v>
       </c>
       <c r="C400" s="2" t="s">
         <v>7</v>
@@ -10936,10 +10966,10 @@
     </row>
     <row r="401" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>757</v>
+        <v>751</v>
       </c>
       <c r="B401" t="s">
-        <v>758</v>
+        <v>752</v>
       </c>
       <c r="C401" s="2" t="s">
         <v>7</v>
@@ -10950,10 +10980,10 @@
     </row>
     <row r="402" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>759</v>
+        <v>753</v>
       </c>
       <c r="B402" t="s">
-        <v>760</v>
+        <v>754</v>
       </c>
       <c r="C402" s="2" t="s">
         <v>7</v>
@@ -10964,10 +10994,10 @@
     </row>
     <row r="403" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>761</v>
+        <v>755</v>
       </c>
       <c r="B403" t="s">
-        <v>762</v>
+        <v>756</v>
       </c>
       <c r="C403" s="2" t="s">
         <v>7</v>
@@ -10978,10 +11008,10 @@
     </row>
     <row r="404" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>763</v>
+        <v>757</v>
       </c>
       <c r="B404" t="s">
-        <v>764</v>
+        <v>758</v>
       </c>
       <c r="C404" s="2" t="s">
         <v>7</v>
@@ -10992,10 +11022,10 @@
     </row>
     <row r="405" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>765</v>
+        <v>759</v>
       </c>
       <c r="B405" t="s">
-        <v>766</v>
+        <v>760</v>
       </c>
       <c r="C405" s="2" t="s">
         <v>7</v>
@@ -11006,10 +11036,10 @@
     </row>
     <row r="406" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>767</v>
+        <v>761</v>
       </c>
       <c r="B406" t="s">
-        <v>768</v>
+        <v>762</v>
       </c>
       <c r="C406" s="2" t="s">
         <v>7</v>
@@ -11020,10 +11050,10 @@
     </row>
     <row r="407" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>769</v>
+        <v>763</v>
       </c>
       <c r="B407" t="s">
-        <v>770</v>
+        <v>764</v>
       </c>
       <c r="C407" s="2" t="s">
         <v>7</v>
@@ -11034,10 +11064,10 @@
     </row>
     <row r="408" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>771</v>
+        <v>765</v>
       </c>
       <c r="B408" t="s">
-        <v>772</v>
+        <v>766</v>
       </c>
       <c r="C408" s="2" t="s">
         <v>7</v>
@@ -11048,10 +11078,10 @@
     </row>
     <row r="409" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>773</v>
+        <v>767</v>
       </c>
       <c r="B409" t="s">
-        <v>774</v>
+        <v>768</v>
       </c>
       <c r="C409" s="2" t="s">
         <v>7</v>
@@ -11062,10 +11092,10 @@
     </row>
     <row r="410" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>775</v>
+        <v>769</v>
       </c>
       <c r="B410" t="s">
-        <v>776</v>
+        <v>770</v>
       </c>
       <c r="C410" s="2" t="s">
         <v>7</v>
@@ -11076,10 +11106,10 @@
     </row>
     <row r="411" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>777</v>
+        <v>771</v>
       </c>
       <c r="B411" t="s">
-        <v>778</v>
+        <v>772</v>
       </c>
       <c r="C411" s="2" t="s">
         <v>7</v>
@@ -11090,10 +11120,10 @@
     </row>
     <row r="412" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>779</v>
+        <v>773</v>
       </c>
       <c r="B412" t="s">
-        <v>780</v>
+        <v>774</v>
       </c>
       <c r="C412" s="2" t="s">
         <v>7</v>
@@ -11104,10 +11134,10 @@
     </row>
     <row r="413" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>781</v>
+        <v>775</v>
       </c>
       <c r="B413" t="s">
-        <v>782</v>
+        <v>776</v>
       </c>
       <c r="C413" s="2" t="s">
         <v>7</v>
@@ -11118,10 +11148,10 @@
     </row>
     <row r="414" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>783</v>
+        <v>777</v>
       </c>
       <c r="B414" t="s">
-        <v>784</v>
+        <v>778</v>
       </c>
       <c r="C414" s="2" t="s">
         <v>7</v>
@@ -11132,10 +11162,10 @@
     </row>
     <row r="415" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>785</v>
+        <v>779</v>
       </c>
       <c r="B415" t="s">
-        <v>786</v>
+        <v>780</v>
       </c>
       <c r="C415" s="2" t="s">
         <v>7</v>
@@ -11146,10 +11176,10 @@
     </row>
     <row r="416" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="B416" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="C416" s="2" t="s">
         <v>7</v>
@@ -11160,10 +11190,10 @@
     </row>
     <row r="417" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="B417" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
       <c r="C417" s="2" t="s">
         <v>7</v>
@@ -11174,10 +11204,10 @@
     </row>
     <row r="418" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
       <c r="B418" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
       <c r="C418" s="2" t="s">
         <v>7</v>
@@ -11188,10 +11218,10 @@
     </row>
     <row r="419" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
       <c r="B419" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
       <c r="C419" s="2" t="s">
         <v>7</v>
@@ -11202,10 +11232,10 @@
     </row>
     <row r="420" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
       <c r="B420" t="s">
-        <v>796</v>
+        <v>792</v>
       </c>
       <c r="C420" s="2" t="s">
         <v>7</v>
@@ -11216,10 +11246,10 @@
     </row>
     <row r="421" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
       <c r="B421" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
       <c r="C421" s="2" t="s">
         <v>7</v>
@@ -11230,10 +11260,10 @@
     </row>
     <row r="422" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="B422" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="C422" s="2" t="s">
         <v>7</v>
@@ -11244,10 +11274,10 @@
     </row>
     <row r="423" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="B423" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="C423" s="2" t="s">
         <v>7</v>
@@ -11258,10 +11288,10 @@
     </row>
     <row r="424" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="B424" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="C424" s="2" t="s">
         <v>7</v>
@@ -11272,10 +11302,10 @@
     </row>
     <row r="425" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="B425" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="C425" s="2" t="s">
         <v>7</v>
@@ -11286,10 +11316,10 @@
     </row>
     <row r="426" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="B426" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="C426" s="2" t="s">
         <v>7</v>
@@ -11300,10 +11330,10 @@
     </row>
     <row r="427" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="B427" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="C427" s="2" t="s">
         <v>7</v>
@@ -11314,10 +11344,10 @@
     </row>
     <row r="428" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="B428" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="C428" s="2" t="s">
         <v>7</v>
@@ -11328,10 +11358,10 @@
     </row>
     <row r="429" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="B429" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="C429" s="2" t="s">
         <v>7</v>
@@ -11342,10 +11372,10 @@
     </row>
     <row r="430" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="B430" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C430" s="2" t="s">
         <v>7</v>
@@ -11356,10 +11386,10 @@
     </row>
     <row r="431" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="B431" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="C431" s="2" t="s">
         <v>7</v>
@@ -11370,10 +11400,10 @@
     </row>
     <row r="432" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="B432" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="C432" s="2" t="s">
         <v>7</v>
@@ -11384,10 +11414,10 @@
     </row>
     <row r="433" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="B433" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="C433" s="2" t="s">
         <v>7</v>
@@ -11398,10 +11428,10 @@
     </row>
     <row r="434" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="B434" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="C434" s="2" t="s">
         <v>7</v>
@@ -11412,10 +11442,10 @@
     </row>
     <row r="435" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="B435" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="C435" s="2" t="s">
         <v>7</v>
@@ -11426,10 +11456,10 @@
     </row>
     <row r="436" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="B436" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="C436" s="2" t="s">
         <v>7</v>
@@ -11440,10 +11470,10 @@
     </row>
     <row r="437" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="B437" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="C437" s="2" t="s">
         <v>7</v>
@@ -11454,10 +11484,10 @@
     </row>
     <row r="438" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B438" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="C438" s="2" t="s">
         <v>7</v>
@@ -11468,10 +11498,10 @@
     </row>
     <row r="439" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="B439" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="C439" s="2" t="s">
         <v>7</v>
@@ -11482,10 +11512,10 @@
     </row>
     <row r="440" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="B440" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="C440" s="2" t="s">
         <v>7</v>
@@ -11496,10 +11526,10 @@
     </row>
     <row r="441" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="B441" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="C441" s="2" t="s">
         <v>7</v>
@@ -11510,10 +11540,10 @@
     </row>
     <row r="442" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
       <c r="B442" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="C442" s="2" t="s">
         <v>7</v>
@@ -11524,10 +11554,10 @@
     </row>
     <row r="443" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="B443" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="C443" s="2" t="s">
         <v>7</v>
@@ -11538,10 +11568,10 @@
     </row>
     <row r="444" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="B444" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="C444" s="2" t="s">
         <v>7</v>
@@ -11552,10 +11582,10 @@
     </row>
     <row r="445" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="B445" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="C445" s="2" t="s">
         <v>7</v>
@@ -11566,10 +11596,10 @@
     </row>
     <row r="446" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="B446" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="C446" s="2" t="s">
         <v>7</v>
@@ -11580,10 +11610,10 @@
     </row>
     <row r="447" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
       <c r="B447" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
       <c r="C447" s="2" t="s">
         <v>7</v>
@@ -11594,10 +11624,10 @@
     </row>
     <row r="448" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="B448" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
       <c r="C448" s="2" t="s">
         <v>7</v>
@@ -11608,10 +11638,10 @@
     </row>
     <row r="449" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="B449" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="C449" s="2" t="s">
         <v>7</v>
@@ -11622,10 +11652,10 @@
     </row>
     <row r="450" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="B450" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="C450" s="2" t="s">
         <v>7</v>
@@ -11636,10 +11666,10 @@
     </row>
     <row r="451" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="B451" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="C451" s="2" t="s">
         <v>7</v>
@@ -11650,10 +11680,10 @@
     </row>
     <row r="452" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="B452" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="C452" s="2" t="s">
         <v>7</v>
@@ -11664,10 +11694,10 @@
     </row>
     <row r="453" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="B453" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="C453" s="2" t="s">
         <v>7</v>
@@ -11678,10 +11708,10 @@
     </row>
     <row r="454" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="B454" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="C454" s="2" t="s">
         <v>7</v>
@@ -11692,10 +11722,10 @@
     </row>
     <row r="455" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="B455" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="C455" s="2" t="s">
         <v>7</v>
@@ -11706,10 +11736,10 @@
     </row>
     <row r="456" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="B456" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="C456" s="2" t="s">
         <v>7</v>
@@ -11720,10 +11750,10 @@
     </row>
     <row r="457" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="B457" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="C457" s="2" t="s">
         <v>7</v>
@@ -11734,10 +11764,10 @@
     </row>
     <row r="458" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="B458" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="C458" s="2" t="s">
         <v>7</v>
@@ -11748,10 +11778,10 @@
     </row>
     <row r="459" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="B459" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="C459" s="2" t="s">
         <v>7</v>
@@ -11762,10 +11792,10 @@
     </row>
     <row r="460" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="B460" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="C460" s="2" t="s">
         <v>7</v>
@@ -11776,10 +11806,10 @@
     </row>
     <row r="461" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="B461" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="C461" s="2" t="s">
         <v>7</v>
@@ -11790,10 +11820,10 @@
     </row>
     <row r="462" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="B462" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="C462" s="2" t="s">
         <v>7</v>
@@ -11804,10 +11834,10 @@
     </row>
     <row r="463" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="B463" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="C463" s="2" t="s">
         <v>7</v>
@@ -11818,10 +11848,10 @@
     </row>
     <row r="464" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="B464" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="C464" s="2" t="s">
         <v>7</v>
@@ -11832,10 +11862,10 @@
     </row>
     <row r="465" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="B465" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="C465" s="2" t="s">
         <v>7</v>
@@ -11846,10 +11876,10 @@
     </row>
     <row r="466" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="B466" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="C466" s="2" t="s">
         <v>7</v>
@@ -11860,10 +11890,10 @@
     </row>
     <row r="467" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="B467" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="C467" s="2" t="s">
         <v>7</v>
@@ -11874,10 +11904,10 @@
     </row>
     <row r="468" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="B468" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="C468" s="2" t="s">
         <v>7</v>
@@ -11888,10 +11918,10 @@
     </row>
     <row r="469" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="B469" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="C469" s="2" t="s">
         <v>7</v>
@@ -11902,10 +11932,10 @@
     </row>
     <row r="470" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="B470" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="C470" s="2" t="s">
         <v>7</v>
@@ -11916,10 +11946,10 @@
     </row>
     <row r="471" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="B471" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
       <c r="C471" s="2" t="s">
         <v>7</v>
@@ -11930,10 +11960,10 @@
     </row>
     <row r="472" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="B472" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
       <c r="C472" s="2" t="s">
         <v>7</v>
@@ -11944,10 +11974,10 @@
     </row>
     <row r="473" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="B473" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="C473" s="2" t="s">
         <v>7</v>
@@ -11958,10 +11988,10 @@
     </row>
     <row r="474" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="B474" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="C474" s="2" t="s">
         <v>7</v>
@@ -11972,10 +12002,10 @@
     </row>
     <row r="475" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="B475" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="C475" s="2" t="s">
         <v>7</v>
@@ -11986,10 +12016,10 @@
     </row>
     <row r="476" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="B476" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="C476" s="2" t="s">
         <v>7</v>
@@ -12000,10 +12030,10 @@
     </row>
     <row r="477" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="B477" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="C477" s="2" t="s">
         <v>7</v>
@@ -12014,10 +12044,10 @@
     </row>
     <row r="478" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="B478" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="C478" s="2" t="s">
         <v>7</v>
@@ -12028,10 +12058,10 @@
     </row>
     <row r="479" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="B479" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="C479" s="2" t="s">
         <v>7</v>
@@ -12042,10 +12072,10 @@
     </row>
     <row r="480" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="B480" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="C480" s="2" t="s">
         <v>7</v>
@@ -12056,10 +12086,10 @@
     </row>
     <row r="481" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="B481" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="C481" s="2" t="s">
         <v>7</v>
@@ -12070,10 +12100,10 @@
     </row>
     <row r="482" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="B482" t="s">
-        <v>930</v>
+        <v>926</v>
       </c>
       <c r="C482" s="2" t="s">
         <v>7</v>
@@ -12084,10 +12114,10 @@
     </row>
     <row r="483" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
-        <v>931</v>
+        <v>927</v>
       </c>
       <c r="B483" t="s">
-        <v>932</v>
+        <v>928</v>
       </c>
       <c r="C483" s="2" t="s">
         <v>7</v>
@@ -12098,10 +12128,10 @@
     </row>
     <row r="484" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="B484" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C484" s="2" t="s">
         <v>7</v>
@@ -12112,10 +12142,10 @@
     </row>
     <row r="485" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="B485" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="C485" s="2" t="s">
         <v>7</v>
@@ -12126,10 +12156,10 @@
     </row>
     <row r="486" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="B486" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="C486" s="2" t="s">
         <v>7</v>
@@ -12140,10 +12170,10 @@
     </row>
     <row r="487" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="B487" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="C487" s="2" t="s">
         <v>7</v>
@@ -12154,10 +12184,10 @@
     </row>
     <row r="488" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="B488" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="C488" s="2" t="s">
         <v>7</v>
@@ -12168,10 +12198,10 @@
     </row>
     <row r="489" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
-        <v>945</v>
+        <v>941</v>
       </c>
       <c r="B489" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
       <c r="C489" s="2" t="s">
         <v>7</v>
@@ -12182,10 +12212,10 @@
     </row>
     <row r="490" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
-        <v>947</v>
+        <v>943</v>
       </c>
       <c r="B490" t="s">
-        <v>948</v>
+        <v>944</v>
       </c>
       <c r="C490" s="2" t="s">
         <v>7</v>
@@ -12196,10 +12226,10 @@
     </row>
     <row r="491" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>949</v>
+        <v>945</v>
       </c>
       <c r="B491" t="s">
-        <v>950</v>
+        <v>946</v>
       </c>
       <c r="C491" s="2" t="s">
         <v>7</v>
@@ -12210,10 +12240,10 @@
     </row>
     <row r="492" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="B492" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="C492" s="2" t="s">
         <v>7</v>
@@ -12224,10 +12254,10 @@
     </row>
     <row r="493" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="B493" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="C493" s="2" t="s">
         <v>7</v>
@@ -12238,10 +12268,10 @@
     </row>
     <row r="494" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="B494" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="C494" s="2" t="s">
         <v>7</v>
@@ -12252,10 +12282,10 @@
     </row>
     <row r="495" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="B495" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="C495" s="2" t="s">
         <v>7</v>
@@ -12266,10 +12296,10 @@
     </row>
     <row r="496" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="B496" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="C496" s="2" t="s">
         <v>7</v>
@@ -12280,10 +12310,10 @@
     </row>
     <row r="497" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="B497" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="C497" s="2" t="s">
         <v>7</v>
@@ -12294,10 +12324,10 @@
     </row>
     <row r="498" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="B498" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="C498" s="2" t="s">
         <v>7</v>
@@ -12308,10 +12338,10 @@
     </row>
     <row r="499" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="B499" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="C499" s="2" t="s">
         <v>7</v>
@@ -12322,10 +12352,10 @@
     </row>
     <row r="500" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="B500" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="C500" s="2" t="s">
         <v>7</v>
@@ -12336,10 +12366,10 @@
     </row>
     <row r="501" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="B501" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="C501" s="2" t="s">
         <v>7</v>
@@ -12350,10 +12380,10 @@
     </row>
     <row r="502" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="B502" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="C502" s="2" t="s">
         <v>7</v>
@@ -12364,10 +12394,10 @@
     </row>
     <row r="503" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="B503" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="C503" s="2" t="s">
         <v>7</v>
@@ -12378,10 +12408,10 @@
     </row>
     <row r="504" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="B504" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="C504" s="2" t="s">
         <v>7</v>
@@ -12392,10 +12422,10 @@
     </row>
     <row r="505" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="B505" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="C505" s="2" t="s">
         <v>7</v>
@@ -12406,10 +12436,10 @@
     </row>
     <row r="506" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="B506" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="C506" s="2" t="s">
         <v>7</v>
@@ -12420,10 +12450,10 @@
     </row>
     <row r="507" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="B507" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="C507" s="2" t="s">
         <v>7</v>
@@ -12434,10 +12464,10 @@
     </row>
     <row r="508" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="B508" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="C508" s="2" t="s">
         <v>7</v>
@@ -12448,10 +12478,10 @@
     </row>
     <row r="509" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="B509" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="C509" s="2" t="s">
         <v>7</v>
@@ -12462,10 +12492,10 @@
     </row>
     <row r="510" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="B510" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="C510" s="2" t="s">
         <v>7</v>
@@ -12476,10 +12506,10 @@
     </row>
     <row r="511" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="B511" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="C511" s="2" t="s">
         <v>7</v>
@@ -12490,10 +12520,10 @@
     </row>
     <row r="512" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="B512" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="C512" s="2" t="s">
         <v>7</v>
@@ -12504,10 +12534,10 @@
     </row>
     <row r="513" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="B513" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="C513" s="2" t="s">
         <v>7</v>
@@ -12518,10 +12548,10 @@
     </row>
     <row r="514" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="B514" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="C514" s="2" t="s">
         <v>7</v>
@@ -12532,10 +12562,10 @@
     </row>
     <row r="515" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="B515" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="C515" s="2" t="s">
         <v>7</v>
@@ -12546,10 +12576,10 @@
     </row>
     <row r="516" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="B516" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="C516" s="2" t="s">
         <v>7</v>
@@ -12560,10 +12590,10 @@
     </row>
     <row r="517" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="B517" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="C517" s="2" t="s">
         <v>7</v>
@@ -12574,10 +12604,10 @@
     </row>
     <row r="518" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="B518" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="C518" s="2" t="s">
         <v>7</v>
@@ -12588,10 +12618,10 @@
     </row>
     <row r="519" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="B519" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="C519" s="2" t="s">
         <v>7</v>
@@ -12770,10 +12800,10 @@
     </row>
     <row r="532" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="B532" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="C532" s="2" t="s">
         <v>7</v>
@@ -12784,10 +12814,10 @@
     </row>
     <row r="533" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="B533" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="C533" s="2" t="s">
         <v>7</v>
@@ -12798,10 +12828,10 @@
     </row>
     <row r="534" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="B534" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="C534" s="2" t="s">
         <v>7</v>
@@ -13148,10 +13178,10 @@
     </row>
     <row r="559" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="B559" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="C559" s="2" t="s">
         <v>7</v>
@@ -13162,10 +13192,10 @@
     </row>
     <row r="560" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="B560" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="C560" s="2" t="s">
         <v>7</v>
@@ -13176,10 +13206,10 @@
     </row>
     <row r="561" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="B561" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="C561" s="2" t="s">
         <v>7</v>
@@ -13414,10 +13444,10 @@
     </row>
     <row r="578" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="B578" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="C578" s="2" t="s">
         <v>7</v>
@@ -13428,10 +13458,10 @@
     </row>
     <row r="579" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="B579" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="C579" s="2" t="s">
         <v>7</v>
@@ -13442,10 +13472,10 @@
     </row>
     <row r="580" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="B580" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="C580" s="2" t="s">
         <v>7</v>
@@ -13456,10 +13486,10 @@
     </row>
     <row r="581" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="B581" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="C581" s="2" t="s">
         <v>7</v>
@@ -13470,10 +13500,10 @@
     </row>
     <row r="582" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="B582" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
       <c r="C582" s="2" t="s">
         <v>7</v>
@@ -13484,10 +13514,10 @@
     </row>
     <row r="583" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="B583" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="C583" s="2" t="s">
         <v>7</v>
@@ -13498,10 +13528,10 @@
     </row>
     <row r="584" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="B584" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="C584" s="2" t="s">
         <v>7</v>
@@ -13512,10 +13542,10 @@
     </row>
     <row r="585" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="B585" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="C585" s="2" t="s">
         <v>7</v>
@@ -13526,10 +13556,10 @@
     </row>
     <row r="586" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="B586" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="C586" s="2" t="s">
         <v>7</v>
@@ -13540,10 +13570,10 @@
     </row>
     <row r="587" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="B587" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="C587" s="2" t="s">
         <v>7</v>
@@ -13554,10 +13584,10 @@
     </row>
     <row r="588" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
       <c r="B588" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="C588" s="2" t="s">
         <v>7</v>
@@ -13568,10 +13598,10 @@
     </row>
     <row r="589" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="B589" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="C589" s="2" t="s">
         <v>7</v>
@@ -13582,10 +13612,10 @@
     </row>
     <row r="590" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="B590" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="C590" s="2" t="s">
         <v>7</v>
@@ -13596,10 +13626,10 @@
     </row>
     <row r="591" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="B591" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="C591" s="2" t="s">
         <v>7</v>
@@ -13610,10 +13640,10 @@
     </row>
     <row r="592" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="B592" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="C592" s="2" t="s">
         <v>7</v>
@@ -13624,10 +13654,10 @@
     </row>
     <row r="593" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="B593" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="C593" s="2" t="s">
         <v>7</v>
@@ -13638,10 +13668,10 @@
     </row>
     <row r="594" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="B594" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
       <c r="C594" s="2" t="s">
         <v>7</v>
@@ -13652,10 +13682,10 @@
     </row>
     <row r="595" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="B595" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="C595" s="2" t="s">
         <v>7</v>
@@ -13666,10 +13696,10 @@
     </row>
     <row r="596" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="B596" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
       <c r="C596" s="2" t="s">
         <v>7</v>
@@ -13680,10 +13710,10 @@
     </row>
     <row r="597" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="B597" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="C597" s="2" t="s">
         <v>7</v>
@@ -13694,10 +13724,10 @@
     </row>
     <row r="598" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="B598" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="C598" s="2" t="s">
         <v>7</v>
@@ -13708,10 +13738,10 @@
     </row>
     <row r="599" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="B599" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
       <c r="C599" s="2" t="s">
         <v>7</v>
@@ -13722,10 +13752,10 @@
     </row>
     <row r="600" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="B600" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
       <c r="C600" s="2" t="s">
         <v>7</v>
@@ -13736,10 +13766,10 @@
     </row>
     <row r="601" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="B601" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="C601" s="2" t="s">
         <v>7</v>
@@ -13750,10 +13780,10 @@
     </row>
     <row r="602" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="B602" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
       <c r="C602" s="2" t="s">
         <v>7</v>
@@ -13764,10 +13794,10 @@
     </row>
     <row r="603" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="B603" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="C603" s="2" t="s">
         <v>7</v>
@@ -13778,10 +13808,10 @@
     </row>
     <row r="604" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="B604" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="C604" s="2" t="s">
         <v>7</v>
@@ -13792,10 +13822,10 @@
     </row>
     <row r="605" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
-        <v>1185</v>
+        <v>1181</v>
       </c>
       <c r="B605" t="s">
-        <v>1186</v>
+        <v>1182</v>
       </c>
       <c r="C605" s="2" t="s">
         <v>7</v>
@@ -13806,10 +13836,10 @@
     </row>
     <row r="606" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
-        <v>1187</v>
+        <v>1183</v>
       </c>
       <c r="B606" t="s">
-        <v>1188</v>
+        <v>1184</v>
       </c>
       <c r="C606" s="2" t="s">
         <v>7</v>
@@ -13820,10 +13850,10 @@
     </row>
     <row r="607" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
-        <v>1189</v>
+        <v>1185</v>
       </c>
       <c r="B607" t="s">
-        <v>1190</v>
+        <v>1186</v>
       </c>
       <c r="C607" s="2" t="s">
         <v>7</v>
@@ -13834,10 +13864,10 @@
     </row>
     <row r="608" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
-        <v>1193</v>
+        <v>1187</v>
       </c>
       <c r="B608" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
       <c r="C608" s="2" t="s">
         <v>7</v>
@@ -13848,10 +13878,10 @@
     </row>
     <row r="609" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
-        <v>1195</v>
+        <v>1189</v>
       </c>
       <c r="B609" t="s">
-        <v>1196</v>
+        <v>1190</v>
       </c>
       <c r="C609" s="2" t="s">
         <v>7</v>
@@ -13862,10 +13892,10 @@
     </row>
     <row r="610" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
-        <v>1197</v>
+        <v>1191</v>
       </c>
       <c r="B610" t="s">
-        <v>1198</v>
+        <v>1192</v>
       </c>
       <c r="C610" s="2" t="s">
         <v>7</v>
@@ -13876,10 +13906,10 @@
     </row>
     <row r="611" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
-        <v>1199</v>
+        <v>1193</v>
       </c>
       <c r="B611" t="s">
-        <v>1200</v>
+        <v>1194</v>
       </c>
       <c r="C611" s="2" t="s">
         <v>7</v>
@@ -13890,10 +13920,10 @@
     </row>
     <row r="612" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
-        <v>1201</v>
+        <v>1195</v>
       </c>
       <c r="B612" t="s">
-        <v>1202</v>
+        <v>1196</v>
       </c>
       <c r="C612" s="2" t="s">
         <v>7</v>
@@ -13904,10 +13934,10 @@
     </row>
     <row r="613" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
-        <v>1203</v>
+        <v>1197</v>
       </c>
       <c r="B613" t="s">
-        <v>1204</v>
+        <v>1198</v>
       </c>
       <c r="C613" s="2" t="s">
         <v>7</v>
@@ -13918,10 +13948,10 @@
     </row>
     <row r="614" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
-        <v>1205</v>
+        <v>1199</v>
       </c>
       <c r="B614" t="s">
-        <v>1206</v>
+        <v>1200</v>
       </c>
       <c r="C614" s="2" t="s">
         <v>7</v>
@@ -13932,10 +13962,10 @@
     </row>
     <row r="615" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
-        <v>1207</v>
+        <v>1201</v>
       </c>
       <c r="B615" t="s">
-        <v>1208</v>
+        <v>1202</v>
       </c>
       <c r="C615" s="2" t="s">
         <v>7</v>
@@ -13946,10 +13976,10 @@
     </row>
     <row r="616" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
-        <v>1209</v>
+        <v>1203</v>
       </c>
       <c r="B616" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="C616" s="2" t="s">
         <v>7</v>
@@ -13960,10 +13990,10 @@
     </row>
     <row r="617" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
-        <v>1211</v>
+        <v>1205</v>
       </c>
       <c r="B617" t="s">
-        <v>1212</v>
+        <v>1206</v>
       </c>
       <c r="C617" s="2" t="s">
         <v>7</v>
@@ -13974,10 +14004,10 @@
     </row>
     <row r="618" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
-        <v>1213</v>
+        <v>1207</v>
       </c>
       <c r="B618" t="s">
-        <v>1214</v>
+        <v>1208</v>
       </c>
       <c r="C618" s="2" t="s">
         <v>7</v>
@@ -13988,10 +14018,10 @@
     </row>
     <row r="619" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
-        <v>1215</v>
+        <v>1209</v>
       </c>
       <c r="B619" t="s">
-        <v>1216</v>
+        <v>1210</v>
       </c>
       <c r="C619" s="2" t="s">
         <v>7</v>
@@ -14002,10 +14032,10 @@
     </row>
     <row r="620" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
-        <v>1217</v>
+        <v>1211</v>
       </c>
       <c r="B620" t="s">
-        <v>1218</v>
+        <v>1212</v>
       </c>
       <c r="C620" s="2" t="s">
         <v>7</v>
@@ -14016,10 +14046,10 @@
     </row>
     <row r="621" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
-        <v>1219</v>
+        <v>1213</v>
       </c>
       <c r="B621" t="s">
-        <v>1220</v>
+        <v>1214</v>
       </c>
       <c r="C621" s="2" t="s">
         <v>7</v>
@@ -14030,10 +14060,10 @@
     </row>
     <row r="622" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
-        <v>1221</v>
+        <v>1215</v>
       </c>
       <c r="B622" t="s">
-        <v>1222</v>
+        <v>1216</v>
       </c>
       <c r="C622" s="2" t="s">
         <v>7</v>
@@ -14044,10 +14074,10 @@
     </row>
     <row r="623" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
-        <v>1223</v>
+        <v>1217</v>
       </c>
       <c r="B623" t="s">
-        <v>1224</v>
+        <v>1218</v>
       </c>
       <c r="C623" s="2" t="s">
         <v>7</v>
@@ -14058,10 +14088,10 @@
     </row>
     <row r="624" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
-        <v>1225</v>
+        <v>1219</v>
       </c>
       <c r="B624" t="s">
-        <v>1226</v>
+        <v>1220</v>
       </c>
       <c r="C624" s="2" t="s">
         <v>7</v>
@@ -14072,10 +14102,10 @@
     </row>
     <row r="625" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
-        <v>1227</v>
+        <v>1221</v>
       </c>
       <c r="B625" t="s">
-        <v>1228</v>
+        <v>1222</v>
       </c>
       <c r="C625" s="2" t="s">
         <v>7</v>
@@ -14086,10 +14116,10 @@
     </row>
     <row r="626" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
-        <v>1229</v>
+        <v>1223</v>
       </c>
       <c r="B626" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="C626" s="2" t="s">
         <v>7</v>
@@ -14100,10 +14130,10 @@
     </row>
     <row r="627" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
-        <v>1233</v>
+        <v>1225</v>
       </c>
       <c r="B627" t="s">
-        <v>1234</v>
+        <v>1226</v>
       </c>
       <c r="C627" s="2" t="s">
         <v>7</v>
@@ -14114,10 +14144,10 @@
     </row>
     <row r="628" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
-        <v>1235</v>
+        <v>1227</v>
       </c>
       <c r="B628" t="s">
-        <v>1236</v>
+        <v>1228</v>
       </c>
       <c r="C628" s="2" t="s">
         <v>7</v>
@@ -14128,10 +14158,10 @@
     </row>
     <row r="629" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
-        <v>1237</v>
+        <v>1229</v>
       </c>
       <c r="B629" t="s">
-        <v>1238</v>
+        <v>1230</v>
       </c>
       <c r="C629" s="2" t="s">
         <v>7</v>
@@ -14142,10 +14172,10 @@
     </row>
     <row r="630" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
-        <v>1239</v>
+        <v>1231</v>
       </c>
       <c r="B630" t="s">
-        <v>1240</v>
+        <v>1232</v>
       </c>
       <c r="C630" s="2" t="s">
         <v>7</v>
@@ -14156,10 +14186,10 @@
     </row>
     <row r="631" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
-        <v>1241</v>
+        <v>1233</v>
       </c>
       <c r="B631" t="s">
-        <v>1242</v>
+        <v>1234</v>
       </c>
       <c r="C631" s="2" t="s">
         <v>7</v>
@@ -14170,10 +14200,10 @@
     </row>
     <row r="632" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
-        <v>1243</v>
+        <v>1235</v>
       </c>
       <c r="B632" t="s">
-        <v>1244</v>
+        <v>1236</v>
       </c>
       <c r="C632" s="2" t="s">
         <v>7</v>
@@ -14184,10 +14214,10 @@
     </row>
     <row r="633" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
-        <v>1245</v>
+        <v>1239</v>
       </c>
       <c r="B633" t="s">
-        <v>1246</v>
+        <v>1240</v>
       </c>
       <c r="C633" s="2" t="s">
         <v>7</v>
@@ -14198,10 +14228,10 @@
     </row>
     <row r="634" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
-        <v>1247</v>
+        <v>1241</v>
       </c>
       <c r="B634" t="s">
-        <v>1248</v>
+        <v>1242</v>
       </c>
       <c r="C634" s="2" t="s">
         <v>7</v>
@@ -14212,10 +14242,10 @@
     </row>
     <row r="635" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
-        <v>1249</v>
+        <v>1243</v>
       </c>
       <c r="B635" t="s">
-        <v>1250</v>
+        <v>1244</v>
       </c>
       <c r="C635" s="2" t="s">
         <v>7</v>
@@ -14226,10 +14256,10 @@
     </row>
     <row r="636" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
-        <v>1251</v>
+        <v>1245</v>
       </c>
       <c r="B636" t="s">
-        <v>1252</v>
+        <v>1246</v>
       </c>
       <c r="C636" s="2" t="s">
         <v>7</v>
@@ -14240,10 +14270,10 @@
     </row>
     <row r="637" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
-        <v>1253</v>
+        <v>1247</v>
       </c>
       <c r="B637" t="s">
-        <v>1254</v>
+        <v>1248</v>
       </c>
       <c r="C637" s="2" t="s">
         <v>7</v>
@@ -14254,10 +14284,10 @@
     </row>
     <row r="638" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
-        <v>1255</v>
+        <v>1249</v>
       </c>
       <c r="B638" t="s">
-        <v>1256</v>
+        <v>1250</v>
       </c>
       <c r="C638" s="2" t="s">
         <v>7</v>
@@ -14268,10 +14298,10 @@
     </row>
     <row r="639" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
-        <v>1257</v>
+        <v>1251</v>
       </c>
       <c r="B639" t="s">
-        <v>1258</v>
+        <v>1252</v>
       </c>
       <c r="C639" s="2" t="s">
         <v>7</v>
@@ -14282,10 +14312,10 @@
     </row>
     <row r="640" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
-        <v>1261</v>
+        <v>1253</v>
       </c>
       <c r="B640" t="s">
-        <v>1262</v>
+        <v>1254</v>
       </c>
       <c r="C640" s="2" t="s">
         <v>7</v>
@@ -14296,10 +14326,10 @@
     </row>
     <row r="641" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
-        <v>1263</v>
+        <v>1255</v>
       </c>
       <c r="B641" t="s">
-        <v>1264</v>
+        <v>1256</v>
       </c>
       <c r="C641" s="2" t="s">
         <v>7</v>
@@ -14310,10 +14340,10 @@
     </row>
     <row r="642" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
-        <v>1265</v>
+        <v>1257</v>
       </c>
       <c r="B642" t="s">
-        <v>1266</v>
+        <v>1258</v>
       </c>
       <c r="C642" s="2" t="s">
         <v>7</v>
@@ -14324,10 +14354,10 @@
     </row>
     <row r="643" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
-        <v>1267</v>
+        <v>1259</v>
       </c>
       <c r="B643" t="s">
-        <v>1268</v>
+        <v>1260</v>
       </c>
       <c r="C643" s="2" t="s">
         <v>7</v>
@@ -14338,10 +14368,10 @@
     </row>
     <row r="644" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
-        <v>1269</v>
+        <v>1261</v>
       </c>
       <c r="B644" t="s">
-        <v>1270</v>
+        <v>1262</v>
       </c>
       <c r="C644" s="2" t="s">
         <v>7</v>
@@ -14352,10 +14382,10 @@
     </row>
     <row r="645" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
-        <v>1271</v>
+        <v>1263</v>
       </c>
       <c r="B645" t="s">
-        <v>1272</v>
+        <v>1264</v>
       </c>
       <c r="C645" s="2" t="s">
         <v>7</v>
@@ -14366,10 +14396,10 @@
     </row>
     <row r="646" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
-        <v>1273</v>
+        <v>1267</v>
       </c>
       <c r="B646" t="s">
-        <v>1274</v>
+        <v>1268</v>
       </c>
       <c r="C646" s="2" t="s">
         <v>7</v>
@@ -14380,10 +14410,10 @@
     </row>
     <row r="647" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
-        <v>1275</v>
+        <v>1269</v>
       </c>
       <c r="B647" t="s">
-        <v>1276</v>
+        <v>1270</v>
       </c>
       <c r="C647" s="2" t="s">
         <v>7</v>
@@ -14394,10 +14424,10 @@
     </row>
     <row r="648" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
-        <v>1277</v>
+        <v>1271</v>
       </c>
       <c r="B648" t="s">
-        <v>1278</v>
+        <v>1272</v>
       </c>
       <c r="C648" s="2" t="s">
         <v>7</v>
@@ -14408,10 +14438,10 @@
     </row>
     <row r="649" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
-        <v>1279</v>
+        <v>1273</v>
       </c>
       <c r="B649" t="s">
-        <v>1280</v>
+        <v>1274</v>
       </c>
       <c r="C649" s="2" t="s">
         <v>7</v>
@@ -14422,10 +14452,10 @@
     </row>
     <row r="650" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
-        <v>1281</v>
+        <v>1275</v>
       </c>
       <c r="B650" t="s">
-        <v>1282</v>
+        <v>1276</v>
       </c>
       <c r="C650" s="2" t="s">
         <v>7</v>
@@ -14436,10 +14466,10 @@
     </row>
     <row r="651" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
-        <v>1283</v>
+        <v>1277</v>
       </c>
       <c r="B651" t="s">
-        <v>1284</v>
+        <v>1278</v>
       </c>
       <c r="C651" s="2" t="s">
         <v>7</v>
@@ -14450,10 +14480,10 @@
     </row>
     <row r="652" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
-        <v>1285</v>
+        <v>1279</v>
       </c>
       <c r="B652" t="s">
-        <v>1286</v>
+        <v>1280</v>
       </c>
       <c r="C652" s="2" t="s">
         <v>7</v>
@@ -14464,10 +14494,10 @@
     </row>
     <row r="653" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
-        <v>1289</v>
+        <v>1281</v>
       </c>
       <c r="B653" t="s">
-        <v>1290</v>
+        <v>1282</v>
       </c>
       <c r="C653" s="2" t="s">
         <v>7</v>
@@ -14478,10 +14508,10 @@
     </row>
     <row r="654" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
-        <v>1291</v>
+        <v>1283</v>
       </c>
       <c r="B654" t="s">
-        <v>1292</v>
+        <v>1284</v>
       </c>
       <c r="C654" s="2" t="s">
         <v>7</v>
@@ -14492,10 +14522,10 @@
     </row>
     <row r="655" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
-        <v>1293</v>
+        <v>1285</v>
       </c>
       <c r="B655" t="s">
-        <v>1294</v>
+        <v>1286</v>
       </c>
       <c r="C655" s="2" t="s">
         <v>7</v>
@@ -14506,10 +14536,10 @@
     </row>
     <row r="656" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
-        <v>1295</v>
+        <v>1287</v>
       </c>
       <c r="B656" t="s">
-        <v>1296</v>
+        <v>1288</v>
       </c>
       <c r="C656" s="2" t="s">
         <v>7</v>
@@ -14520,10 +14550,10 @@
     </row>
     <row r="657" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
-        <v>1299</v>
+        <v>1289</v>
       </c>
       <c r="B657" t="s">
-        <v>1300</v>
+        <v>1290</v>
       </c>
       <c r="C657" s="2" t="s">
         <v>7</v>
@@ -14534,10 +14564,10 @@
     </row>
     <row r="658" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
-        <v>1301</v>
+        <v>1291</v>
       </c>
       <c r="B658" t="s">
-        <v>1302</v>
+        <v>1292</v>
       </c>
       <c r="C658" s="2" t="s">
         <v>7</v>
@@ -14548,10 +14578,10 @@
     </row>
     <row r="659" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
-        <v>1305</v>
+        <v>1295</v>
       </c>
       <c r="B659" t="s">
-        <v>1306</v>
+        <v>1296</v>
       </c>
       <c r="C659" s="2" t="s">
         <v>7</v>
@@ -14562,10 +14592,10 @@
     </row>
     <row r="660" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
-        <v>1307</v>
+        <v>1297</v>
       </c>
       <c r="B660" t="s">
-        <v>1308</v>
+        <v>1298</v>
       </c>
       <c r="C660" s="2" t="s">
         <v>7</v>
@@ -14576,10 +14606,10 @@
     </row>
     <row r="661" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
-        <v>1309</v>
+        <v>1299</v>
       </c>
       <c r="B661" t="s">
-        <v>1310</v>
+        <v>1300</v>
       </c>
       <c r="C661" s="2" t="s">
         <v>7</v>
@@ -14590,10 +14620,10 @@
     </row>
     <row r="662" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
-        <v>1311</v>
+        <v>1301</v>
       </c>
       <c r="B662" t="s">
-        <v>1312</v>
+        <v>1302</v>
       </c>
       <c r="C662" s="2" t="s">
         <v>7</v>
@@ -14604,10 +14634,10 @@
     </row>
     <row r="663" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
-        <v>1313</v>
+        <v>1305</v>
       </c>
       <c r="B663" t="s">
-        <v>1314</v>
+        <v>1306</v>
       </c>
       <c r="C663" s="2" t="s">
         <v>7</v>
@@ -14618,10 +14648,10 @@
     </row>
     <row r="664" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
-        <v>1315</v>
+        <v>1307</v>
       </c>
       <c r="B664" t="s">
-        <v>1316</v>
+        <v>1308</v>
       </c>
       <c r="C664" s="2" t="s">
         <v>7</v>
@@ -14632,10 +14662,10 @@
     </row>
     <row r="665" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
-        <v>1319</v>
+        <v>1311</v>
       </c>
       <c r="B665" t="s">
-        <v>1320</v>
+        <v>1312</v>
       </c>
       <c r="C665" s="2" t="s">
         <v>7</v>
@@ -14646,10 +14676,10 @@
     </row>
     <row r="666" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
-        <v>1323</v>
+        <v>1313</v>
       </c>
       <c r="B666" t="s">
-        <v>1324</v>
+        <v>1314</v>
       </c>
       <c r="C666" s="2" t="s">
         <v>7</v>
@@ -14660,10 +14690,10 @@
     </row>
     <row r="667" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
-        <v>1325</v>
+        <v>1315</v>
       </c>
       <c r="B667" t="s">
-        <v>1326</v>
+        <v>1316</v>
       </c>
       <c r="C667" s="2" t="s">
         <v>7</v>
@@ -14674,10 +14704,10 @@
     </row>
     <row r="668" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
-        <v>1327</v>
+        <v>1317</v>
       </c>
       <c r="B668" t="s">
-        <v>1328</v>
+        <v>1318</v>
       </c>
       <c r="C668" s="2" t="s">
         <v>7</v>
@@ -14688,10 +14718,10 @@
     </row>
     <row r="669" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
-        <v>1329</v>
+        <v>1319</v>
       </c>
       <c r="B669" t="s">
-        <v>1330</v>
+        <v>1320</v>
       </c>
       <c r="C669" s="2" t="s">
         <v>7</v>
@@ -14702,10 +14732,10 @@
     </row>
     <row r="670" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
-        <v>1331</v>
+        <v>1321</v>
       </c>
       <c r="B670" t="s">
-        <v>1332</v>
+        <v>1322</v>
       </c>
       <c r="C670" s="2" t="s">
         <v>7</v>
@@ -14716,10 +14746,10 @@
     </row>
     <row r="671" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
-        <v>1333</v>
+        <v>1325</v>
       </c>
       <c r="B671" t="s">
-        <v>1334</v>
+        <v>1326</v>
       </c>
       <c r="C671" s="2" t="s">
         <v>7</v>
@@ -14730,10 +14760,10 @@
     </row>
     <row r="672" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
-        <v>1335</v>
+        <v>1329</v>
       </c>
       <c r="B672" t="s">
-        <v>1336</v>
+        <v>1330</v>
       </c>
       <c r="C672" s="2" t="s">
         <v>7</v>
@@ -14744,10 +14774,10 @@
     </row>
     <row r="673" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
-        <v>1337</v>
+        <v>1331</v>
       </c>
       <c r="B673" t="s">
-        <v>1338</v>
+        <v>1332</v>
       </c>
       <c r="C673" s="2" t="s">
         <v>7</v>
@@ -14758,10 +14788,10 @@
     </row>
     <row r="674" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
-        <v>1339</v>
+        <v>1333</v>
       </c>
       <c r="B674" t="s">
-        <v>1340</v>
+        <v>1334</v>
       </c>
       <c r="C674" s="2" t="s">
         <v>7</v>
@@ -14772,10 +14802,10 @@
     </row>
     <row r="675" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
-        <v>1341</v>
+        <v>1335</v>
       </c>
       <c r="B675" t="s">
-        <v>1342</v>
+        <v>1336</v>
       </c>
       <c r="C675" s="2" t="s">
         <v>7</v>
@@ -14786,10 +14816,10 @@
     </row>
     <row r="676" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="B676" t="s">
-        <v>1344</v>
+        <v>1338</v>
       </c>
       <c r="C676" s="2" t="s">
         <v>7</v>
@@ -14800,10 +14830,10 @@
     </row>
     <row r="677" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
-        <v>1345</v>
+        <v>1339</v>
       </c>
       <c r="B677" t="s">
-        <v>1346</v>
+        <v>1340</v>
       </c>
       <c r="C677" s="2" t="s">
         <v>7</v>
@@ -14814,10 +14844,10 @@
     </row>
     <row r="678" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
-        <v>1347</v>
+        <v>1341</v>
       </c>
       <c r="B678" t="s">
-        <v>1348</v>
+        <v>1342</v>
       </c>
       <c r="C678" s="2" t="s">
         <v>7</v>
@@ -14828,10 +14858,10 @@
     </row>
     <row r="679" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
-        <v>1349</v>
+        <v>1343</v>
       </c>
       <c r="B679" t="s">
-        <v>1350</v>
+        <v>1344</v>
       </c>
       <c r="C679" s="2" t="s">
         <v>7</v>
@@ -14842,10 +14872,10 @@
     </row>
     <row r="680" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
-        <v>1351</v>
+        <v>1345</v>
       </c>
       <c r="B680" t="s">
-        <v>1352</v>
+        <v>1346</v>
       </c>
       <c r="C680" s="2" t="s">
         <v>7</v>
@@ -14856,10 +14886,10 @@
     </row>
     <row r="681" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
-        <v>1353</v>
+        <v>1347</v>
       </c>
       <c r="B681" t="s">
-        <v>1354</v>
+        <v>1348</v>
       </c>
       <c r="C681" s="2" t="s">
         <v>7</v>
@@ -14870,10 +14900,10 @@
     </row>
     <row r="682" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
-        <v>1355</v>
+        <v>1349</v>
       </c>
       <c r="B682" t="s">
-        <v>1356</v>
+        <v>1350</v>
       </c>
       <c r="C682" s="2" t="s">
         <v>7</v>
@@ -14884,10 +14914,10 @@
     </row>
     <row r="683" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
-        <v>1357</v>
+        <v>1351</v>
       </c>
       <c r="B683" t="s">
-        <v>1358</v>
+        <v>1352</v>
       </c>
       <c r="C683" s="2" t="s">
         <v>7</v>
@@ -14898,10 +14928,10 @@
     </row>
     <row r="684" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
-        <v>1359</v>
+        <v>1353</v>
       </c>
       <c r="B684" t="s">
-        <v>1360</v>
+        <v>1354</v>
       </c>
       <c r="C684" s="2" t="s">
         <v>7</v>
@@ -14912,10 +14942,10 @@
     </row>
     <row r="685" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
-        <v>1361</v>
+        <v>1355</v>
       </c>
       <c r="B685" t="s">
-        <v>1362</v>
+        <v>1356</v>
       </c>
       <c r="C685" s="2" t="s">
         <v>7</v>
@@ -14926,10 +14956,10 @@
     </row>
     <row r="686" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
-        <v>1363</v>
+        <v>1357</v>
       </c>
       <c r="B686" t="s">
-        <v>1364</v>
+        <v>1358</v>
       </c>
       <c r="C686" s="2" t="s">
         <v>7</v>
@@ -14940,10 +14970,10 @@
     </row>
     <row r="687" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
-        <v>1365</v>
+        <v>1359</v>
       </c>
       <c r="B687" t="s">
-        <v>1366</v>
+        <v>1360</v>
       </c>
       <c r="C687" s="2" t="s">
         <v>7</v>
@@ -14954,10 +14984,10 @@
     </row>
     <row r="688" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
-        <v>1367</v>
+        <v>1361</v>
       </c>
       <c r="B688" t="s">
-        <v>1368</v>
+        <v>1362</v>
       </c>
       <c r="C688" s="2" t="s">
         <v>7</v>
@@ -14968,10 +14998,10 @@
     </row>
     <row r="689" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
-        <v>1369</v>
+        <v>1363</v>
       </c>
       <c r="B689" t="s">
-        <v>1370</v>
+        <v>1364</v>
       </c>
       <c r="C689" s="2" t="s">
         <v>7</v>
@@ -14982,10 +15012,10 @@
     </row>
     <row r="690" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
-        <v>1371</v>
+        <v>1365</v>
       </c>
       <c r="B690" t="s">
-        <v>1372</v>
+        <v>1366</v>
       </c>
       <c r="C690" s="2" t="s">
         <v>7</v>
@@ -14996,10 +15026,10 @@
     </row>
     <row r="691" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
-        <v>1373</v>
+        <v>1367</v>
       </c>
       <c r="B691" t="s">
-        <v>1374</v>
+        <v>1368</v>
       </c>
       <c r="C691" s="2" t="s">
         <v>7</v>
@@ -15010,10 +15040,10 @@
     </row>
     <row r="692" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
-        <v>1375</v>
+        <v>1369</v>
       </c>
       <c r="B692" t="s">
-        <v>1376</v>
+        <v>1370</v>
       </c>
       <c r="C692" s="2" t="s">
         <v>7</v>
@@ -15024,10 +15054,10 @@
     </row>
     <row r="693" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
-        <v>1377</v>
+        <v>1371</v>
       </c>
       <c r="B693" t="s">
-        <v>1378</v>
+        <v>1372</v>
       </c>
       <c r="C693" s="2" t="s">
         <v>7</v>
@@ -15038,10 +15068,10 @@
     </row>
     <row r="694" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
-        <v>1379</v>
+        <v>1373</v>
       </c>
       <c r="B694" t="s">
-        <v>1380</v>
+        <v>1374</v>
       </c>
       <c r="C694" s="2" t="s">
         <v>7</v>
@@ -15052,10 +15082,10 @@
     </row>
     <row r="695" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
-        <v>1381</v>
+        <v>1375</v>
       </c>
       <c r="B695" t="s">
-        <v>1382</v>
+        <v>1376</v>
       </c>
       <c r="C695" s="2" t="s">
         <v>7</v>
@@ -15066,10 +15096,10 @@
     </row>
     <row r="696" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
-        <v>1383</v>
+        <v>1377</v>
       </c>
       <c r="B696" t="s">
-        <v>1384</v>
+        <v>1378</v>
       </c>
       <c r="C696" s="2" t="s">
         <v>7</v>
@@ -15080,10 +15110,10 @@
     </row>
     <row r="697" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
-        <v>1385</v>
+        <v>1379</v>
       </c>
       <c r="B697" t="s">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="C697" s="2" t="s">
         <v>7</v>
@@ -15094,10 +15124,10 @@
     </row>
     <row r="698" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
-        <v>1387</v>
+        <v>1381</v>
       </c>
       <c r="B698" t="s">
-        <v>1388</v>
+        <v>1382</v>
       </c>
       <c r="C698" s="2" t="s">
         <v>7</v>
@@ -15108,10 +15138,10 @@
     </row>
     <row r="699" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
-        <v>1389</v>
+        <v>1383</v>
       </c>
       <c r="B699" t="s">
-        <v>1390</v>
+        <v>1384</v>
       </c>
       <c r="C699" s="2" t="s">
         <v>7</v>
@@ -15122,10 +15152,10 @@
     </row>
     <row r="700" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
-        <v>1391</v>
+        <v>1385</v>
       </c>
       <c r="B700" t="s">
-        <v>1392</v>
+        <v>1386</v>
       </c>
       <c r="C700" s="2" t="s">
         <v>7</v>
@@ -15136,10 +15166,10 @@
     </row>
     <row r="701" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
-        <v>1393</v>
+        <v>1387</v>
       </c>
       <c r="B701" t="s">
-        <v>1394</v>
+        <v>1388</v>
       </c>
       <c r="C701" s="2" t="s">
         <v>7</v>
@@ -15150,10 +15180,10 @@
     </row>
     <row r="702" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
-        <v>1395</v>
+        <v>1389</v>
       </c>
       <c r="B702" t="s">
-        <v>1396</v>
+        <v>1390</v>
       </c>
       <c r="C702" s="2" t="s">
         <v>7</v>
@@ -15164,10 +15194,10 @@
     </row>
     <row r="703" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
-        <v>1397</v>
+        <v>1391</v>
       </c>
       <c r="B703" t="s">
-        <v>1398</v>
+        <v>1392</v>
       </c>
       <c r="C703" s="2" t="s">
         <v>7</v>
@@ -15178,10 +15208,10 @@
     </row>
     <row r="704" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
-        <v>1401</v>
+        <v>1393</v>
       </c>
       <c r="B704" t="s">
-        <v>1402</v>
+        <v>1394</v>
       </c>
       <c r="C704" s="2" t="s">
         <v>7</v>
@@ -15192,10 +15222,10 @@
     </row>
     <row r="705" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
-        <v>1403</v>
+        <v>1395</v>
       </c>
       <c r="B705" t="s">
-        <v>1404</v>
+        <v>1396</v>
       </c>
       <c r="C705" s="2" t="s">
         <v>7</v>
@@ -15206,10 +15236,10 @@
     </row>
     <row r="706" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
-        <v>1405</v>
+        <v>1397</v>
       </c>
       <c r="B706" t="s">
-        <v>1406</v>
+        <v>1398</v>
       </c>
       <c r="C706" s="2" t="s">
         <v>7</v>
@@ -15220,10 +15250,10 @@
     </row>
     <row r="707" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
-        <v>1407</v>
+        <v>1399</v>
       </c>
       <c r="B707" t="s">
-        <v>1408</v>
+        <v>1400</v>
       </c>
       <c r="C707" s="2" t="s">
         <v>7</v>
@@ -15234,10 +15264,10 @@
     </row>
     <row r="708" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
-        <v>1409</v>
+        <v>1401</v>
       </c>
       <c r="B708" t="s">
-        <v>1410</v>
+        <v>1402</v>
       </c>
       <c r="C708" s="2" t="s">
         <v>7</v>
@@ -15248,10 +15278,10 @@
     </row>
     <row r="709" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
       <c r="B709" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
       <c r="C709" s="2" t="s">
         <v>7</v>
@@ -15262,10 +15292,10 @@
     </row>
     <row r="710" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
-        <v>1413</v>
+        <v>1407</v>
       </c>
       <c r="B710" t="s">
-        <v>1414</v>
+        <v>1408</v>
       </c>
       <c r="C710" s="2" t="s">
         <v>7</v>
@@ -15276,10 +15306,10 @@
     </row>
     <row r="711" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
-        <v>1415</v>
+        <v>1409</v>
       </c>
       <c r="B711" t="s">
-        <v>1416</v>
+        <v>1410</v>
       </c>
       <c r="C711" s="2" t="s">
         <v>7</v>
@@ -15290,10 +15320,10 @@
     </row>
     <row r="712" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
-        <v>1417</v>
+        <v>1411</v>
       </c>
       <c r="B712" t="s">
-        <v>1418</v>
+        <v>1412</v>
       </c>
       <c r="C712" s="2" t="s">
         <v>7</v>
@@ -15304,10 +15334,10 @@
     </row>
     <row r="713" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A713" t="s">
-        <v>1419</v>
+        <v>1413</v>
       </c>
       <c r="B713" t="s">
-        <v>1420</v>
+        <v>1414</v>
       </c>
       <c r="C713" s="2" t="s">
         <v>7</v>
@@ -15318,10 +15348,10 @@
     </row>
     <row r="714" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A714" t="s">
-        <v>1421</v>
+        <v>1415</v>
       </c>
       <c r="B714" t="s">
-        <v>1422</v>
+        <v>1416</v>
       </c>
       <c r="C714" s="2" t="s">
         <v>7</v>
@@ -15332,10 +15362,10 @@
     </row>
     <row r="715" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
-        <v>1423</v>
+        <v>1417</v>
       </c>
       <c r="B715" t="s">
-        <v>1424</v>
+        <v>1418</v>
       </c>
       <c r="C715" s="2" t="s">
         <v>7</v>
@@ -15346,10 +15376,10 @@
     </row>
     <row r="716" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
-        <v>1425</v>
+        <v>1419</v>
       </c>
       <c r="B716" t="s">
-        <v>1426</v>
+        <v>1420</v>
       </c>
       <c r="C716" s="2" t="s">
         <v>7</v>
@@ -15360,10 +15390,10 @@
     </row>
     <row r="717" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A717" t="s">
-        <v>1427</v>
+        <v>1421</v>
       </c>
       <c r="B717" t="s">
-        <v>1428</v>
+        <v>1422</v>
       </c>
       <c r="C717" s="2" t="s">
         <v>7</v>
@@ -15374,10 +15404,10 @@
     </row>
     <row r="718" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
-        <v>1429</v>
+        <v>1423</v>
       </c>
       <c r="B718" t="s">
-        <v>1430</v>
+        <v>1424</v>
       </c>
       <c r="C718" s="2" t="s">
         <v>7</v>
@@ -15388,10 +15418,10 @@
     </row>
     <row r="719" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
-        <v>1431</v>
+        <v>1425</v>
       </c>
       <c r="B719" t="s">
-        <v>1432</v>
+        <v>1426</v>
       </c>
       <c r="C719" s="2" t="s">
         <v>7</v>
@@ -15402,10 +15432,10 @@
     </row>
     <row r="720" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A720" t="s">
-        <v>1433</v>
+        <v>1427</v>
       </c>
       <c r="B720" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="C720" s="2" t="s">
         <v>7</v>
@@ -15416,10 +15446,10 @@
     </row>
     <row r="721" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
-        <v>1435</v>
+        <v>1429</v>
       </c>
       <c r="B721" t="s">
-        <v>1436</v>
+        <v>1430</v>
       </c>
       <c r="C721" s="2" t="s">
         <v>7</v>
@@ -15430,10 +15460,10 @@
     </row>
     <row r="722" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
-        <v>1437</v>
+        <v>1431</v>
       </c>
       <c r="B722" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="C722" s="2" t="s">
         <v>7</v>
@@ -15444,10 +15474,10 @@
     </row>
     <row r="723" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
-        <v>1439</v>
+        <v>1433</v>
       </c>
       <c r="B723" t="s">
-        <v>1440</v>
+        <v>1434</v>
       </c>
       <c r="C723" s="2" t="s">
         <v>7</v>
@@ -15458,10 +15488,10 @@
     </row>
     <row r="724" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A724" t="s">
-        <v>1441</v>
+        <v>1435</v>
       </c>
       <c r="B724" t="s">
-        <v>1442</v>
+        <v>1436</v>
       </c>
       <c r="C724" s="2" t="s">
         <v>7</v>
@@ -15472,10 +15502,10 @@
     </row>
     <row r="725" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A725" t="s">
-        <v>1443</v>
+        <v>1437</v>
       </c>
       <c r="B725" t="s">
-        <v>1444</v>
+        <v>1438</v>
       </c>
       <c r="C725" s="2" t="s">
         <v>7</v>
@@ -15486,10 +15516,10 @@
     </row>
     <row r="726" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A726" t="s">
-        <v>1449</v>
+        <v>1439</v>
       </c>
       <c r="B726" t="s">
-        <v>1450</v>
+        <v>1440</v>
       </c>
       <c r="C726" s="2" t="s">
         <v>7</v>
@@ -15500,10 +15530,10 @@
     </row>
     <row r="727" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A727" t="s">
-        <v>1451</v>
+        <v>1441</v>
       </c>
       <c r="B727" t="s">
-        <v>1452</v>
+        <v>1442</v>
       </c>
       <c r="C727" s="2" t="s">
         <v>7</v>
@@ -15514,10 +15544,10 @@
     </row>
     <row r="728" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A728" t="s">
-        <v>1453</v>
+        <v>1443</v>
       </c>
       <c r="B728" t="s">
-        <v>1454</v>
+        <v>1444</v>
       </c>
       <c r="C728" s="2" t="s">
         <v>7</v>
@@ -15528,10 +15558,10 @@
     </row>
     <row r="729" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A729" t="s">
-        <v>1455</v>
+        <v>1445</v>
       </c>
       <c r="B729" t="s">
-        <v>1456</v>
+        <v>1446</v>
       </c>
       <c r="C729" s="2" t="s">
         <v>7</v>
@@ -15542,10 +15572,10 @@
     </row>
     <row r="730" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A730" t="s">
-        <v>1457</v>
+        <v>1447</v>
       </c>
       <c r="B730" t="s">
-        <v>1458</v>
+        <v>1448</v>
       </c>
       <c r="C730" s="2" t="s">
         <v>7</v>
@@ -15556,10 +15586,10 @@
     </row>
     <row r="731" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A731" t="s">
-        <v>1463</v>
+        <v>1449</v>
       </c>
       <c r="B731" t="s">
-        <v>1464</v>
+        <v>1450</v>
       </c>
       <c r="C731" s="2" t="s">
         <v>7</v>
@@ -15570,10 +15600,10 @@
     </row>
     <row r="732" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A732" t="s">
-        <v>1465</v>
+        <v>1455</v>
       </c>
       <c r="B732" t="s">
-        <v>1466</v>
+        <v>1456</v>
       </c>
       <c r="C732" s="2" t="s">
         <v>7</v>
@@ -15584,10 +15614,10 @@
     </row>
     <row r="733" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A733" t="s">
-        <v>1467</v>
+        <v>1457</v>
       </c>
       <c r="B733" t="s">
-        <v>1468</v>
+        <v>1458</v>
       </c>
       <c r="C733" s="2" t="s">
         <v>7</v>
@@ -15598,10 +15628,10 @@
     </row>
     <row r="734" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A734" t="s">
-        <v>1469</v>
+        <v>1459</v>
       </c>
       <c r="B734" t="s">
-        <v>1470</v>
+        <v>1460</v>
       </c>
       <c r="C734" s="2" t="s">
         <v>7</v>
@@ -15612,10 +15642,10 @@
     </row>
     <row r="735" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A735" t="s">
-        <v>1471</v>
+        <v>1461</v>
       </c>
       <c r="B735" t="s">
-        <v>1472</v>
+        <v>1462</v>
       </c>
       <c r="C735" s="2" t="s">
         <v>7</v>
@@ -15626,10 +15656,10 @@
     </row>
     <row r="736" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A736" t="s">
-        <v>1473</v>
+        <v>1463</v>
       </c>
       <c r="B736" t="s">
-        <v>1474</v>
+        <v>1464</v>
       </c>
       <c r="C736" s="2" t="s">
         <v>7</v>
@@ -15640,10 +15670,10 @@
     </row>
     <row r="737" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A737" t="s">
-        <v>1475</v>
+        <v>1469</v>
       </c>
       <c r="B737" t="s">
-        <v>1476</v>
+        <v>1470</v>
       </c>
       <c r="C737" s="2" t="s">
         <v>7</v>
@@ -15654,10 +15684,10 @@
     </row>
     <row r="738" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A738" t="s">
-        <v>1477</v>
+        <v>1471</v>
       </c>
       <c r="B738" t="s">
-        <v>1478</v>
+        <v>1472</v>
       </c>
       <c r="C738" s="2" t="s">
         <v>7</v>
@@ -15668,10 +15698,10 @@
     </row>
     <row r="739" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A739" t="s">
-        <v>1481</v>
+        <v>1473</v>
       </c>
       <c r="B739" t="s">
-        <v>1482</v>
+        <v>1474</v>
       </c>
       <c r="C739" s="2" t="s">
         <v>7</v>
@@ -15682,10 +15712,10 @@
     </row>
     <row r="740" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A740" t="s">
-        <v>1483</v>
+        <v>1475</v>
       </c>
       <c r="B740" t="s">
-        <v>1484</v>
+        <v>1476</v>
       </c>
       <c r="C740" s="2" t="s">
         <v>7</v>
@@ -15696,10 +15726,10 @@
     </row>
     <row r="741" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A741" t="s">
-        <v>1485</v>
+        <v>1477</v>
       </c>
       <c r="B741" t="s">
-        <v>1486</v>
+        <v>1478</v>
       </c>
       <c r="C741" s="2" t="s">
         <v>7</v>
@@ -15710,10 +15740,10 @@
     </row>
     <row r="742" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A742" t="s">
-        <v>1487</v>
+        <v>1479</v>
       </c>
       <c r="B742" t="s">
-        <v>1488</v>
+        <v>1480</v>
       </c>
       <c r="C742" s="2" t="s">
         <v>7</v>
@@ -15724,10 +15754,10 @@
     </row>
     <row r="743" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A743" t="s">
-        <v>1489</v>
+        <v>1481</v>
       </c>
       <c r="B743" t="s">
-        <v>1490</v>
+        <v>1482</v>
       </c>
       <c r="C743" s="2" t="s">
         <v>7</v>
@@ -15738,10 +15768,10 @@
     </row>
     <row r="744" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A744" t="s">
-        <v>1491</v>
+        <v>1483</v>
       </c>
       <c r="B744" t="s">
-        <v>1492</v>
+        <v>1484</v>
       </c>
       <c r="C744" s="2" t="s">
         <v>7</v>
@@ -15752,10 +15782,10 @@
     </row>
     <row r="745" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A745" t="s">
-        <v>1493</v>
+        <v>1487</v>
       </c>
       <c r="B745" t="s">
-        <v>1494</v>
+        <v>1488</v>
       </c>
       <c r="C745" s="2" t="s">
         <v>7</v>
@@ -15766,10 +15796,10 @@
     </row>
     <row r="746" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A746" t="s">
-        <v>1495</v>
+        <v>1489</v>
       </c>
       <c r="B746" t="s">
-        <v>1496</v>
+        <v>1490</v>
       </c>
       <c r="C746" s="2" t="s">
         <v>7</v>
@@ -15780,10 +15810,10 @@
     </row>
     <row r="747" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A747" t="s">
-        <v>1497</v>
+        <v>1491</v>
       </c>
       <c r="B747" t="s">
-        <v>1498</v>
+        <v>1492</v>
       </c>
       <c r="C747" s="2" t="s">
         <v>7</v>
@@ -15794,10 +15824,10 @@
     </row>
     <row r="748" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A748" t="s">
-        <v>1501</v>
+        <v>1493</v>
       </c>
       <c r="B748" t="s">
-        <v>1502</v>
+        <v>1494</v>
       </c>
       <c r="C748" s="2" t="s">
         <v>7</v>
@@ -15808,10 +15838,10 @@
     </row>
     <row r="749" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A749" t="s">
-        <v>1503</v>
+        <v>1495</v>
       </c>
       <c r="B749" t="s">
-        <v>1504</v>
+        <v>1496</v>
       </c>
       <c r="C749" s="2" t="s">
         <v>7</v>
@@ -15822,10 +15852,10 @@
     </row>
     <row r="750" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A750" t="s">
-        <v>1505</v>
+        <v>1497</v>
       </c>
       <c r="B750" t="s">
-        <v>1506</v>
+        <v>1498</v>
       </c>
       <c r="C750" s="2" t="s">
         <v>7</v>
@@ -15836,10 +15866,10 @@
     </row>
     <row r="751" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A751" t="s">
-        <v>1507</v>
+        <v>1499</v>
       </c>
       <c r="B751" t="s">
-        <v>1508</v>
+        <v>1500</v>
       </c>
       <c r="C751" s="2" t="s">
         <v>7</v>
@@ -15850,10 +15880,10 @@
     </row>
     <row r="752" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A752" t="s">
-        <v>1509</v>
+        <v>1501</v>
       </c>
       <c r="B752" t="s">
-        <v>1510</v>
+        <v>1502</v>
       </c>
       <c r="C752" s="2" t="s">
         <v>7</v>
@@ -15864,10 +15894,10 @@
     </row>
     <row r="753" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A753" t="s">
-        <v>1511</v>
+        <v>1503</v>
       </c>
       <c r="B753" t="s">
-        <v>1512</v>
+        <v>1504</v>
       </c>
       <c r="C753" s="2" t="s">
         <v>7</v>
@@ -15878,10 +15908,10 @@
     </row>
     <row r="754" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A754" t="s">
-        <v>1513</v>
+        <v>1507</v>
       </c>
       <c r="B754" t="s">
-        <v>1514</v>
+        <v>1508</v>
       </c>
       <c r="C754" s="2" t="s">
         <v>7</v>
@@ -15892,10 +15922,10 @@
     </row>
     <row r="755" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A755" t="s">
-        <v>1515</v>
+        <v>1509</v>
       </c>
       <c r="B755" t="s">
-        <v>1516</v>
+        <v>1510</v>
       </c>
       <c r="C755" s="2" t="s">
         <v>7</v>
@@ -15906,10 +15936,10 @@
     </row>
     <row r="756" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A756" t="s">
-        <v>1517</v>
+        <v>1511</v>
       </c>
       <c r="B756" t="s">
-        <v>1518</v>
+        <v>1512</v>
       </c>
       <c r="C756" s="2" t="s">
         <v>7</v>
@@ -15920,10 +15950,10 @@
     </row>
     <row r="757" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A757" t="s">
-        <v>1519</v>
+        <v>1513</v>
       </c>
       <c r="B757" t="s">
-        <v>1520</v>
+        <v>1514</v>
       </c>
       <c r="C757" s="2" t="s">
         <v>7</v>
@@ -15934,10 +15964,10 @@
     </row>
     <row r="758" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A758" t="s">
-        <v>1521</v>
+        <v>1515</v>
       </c>
       <c r="B758" t="s">
-        <v>1522</v>
+        <v>1516</v>
       </c>
       <c r="C758" s="2" t="s">
         <v>7</v>
@@ -15948,10 +15978,10 @@
     </row>
     <row r="759" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A759" t="s">
-        <v>1525</v>
+        <v>1517</v>
       </c>
       <c r="B759" t="s">
-        <v>1526</v>
+        <v>1518</v>
       </c>
       <c r="C759" s="2" t="s">
         <v>7</v>
@@ -15962,10 +15992,10 @@
     </row>
     <row r="760" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A760" t="s">
-        <v>1527</v>
+        <v>1519</v>
       </c>
       <c r="B760" t="s">
-        <v>1528</v>
+        <v>1520</v>
       </c>
       <c r="C760" s="2" t="s">
         <v>7</v>
@@ -15976,10 +16006,10 @@
     </row>
     <row r="761" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A761" t="s">
-        <v>1529</v>
+        <v>1521</v>
       </c>
       <c r="B761" t="s">
-        <v>1530</v>
+        <v>1522</v>
       </c>
       <c r="C761" s="2" t="s">
         <v>7</v>
@@ -15990,10 +16020,10 @@
     </row>
     <row r="762" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A762" t="s">
-        <v>1531</v>
+        <v>1523</v>
       </c>
       <c r="B762" t="s">
-        <v>1532</v>
+        <v>1524</v>
       </c>
       <c r="C762" s="2" t="s">
         <v>7</v>
@@ -16004,10 +16034,10 @@
     </row>
     <row r="763" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A763" t="s">
-        <v>1533</v>
+        <v>1525</v>
       </c>
       <c r="B763" t="s">
-        <v>1534</v>
+        <v>1526</v>
       </c>
       <c r="C763" s="2" t="s">
         <v>7</v>
@@ -16018,10 +16048,10 @@
     </row>
     <row r="764" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A764" t="s">
-        <v>1535</v>
+        <v>1527</v>
       </c>
       <c r="B764" t="s">
-        <v>1536</v>
+        <v>1528</v>
       </c>
       <c r="C764" s="2" t="s">
         <v>7</v>
@@ -16032,10 +16062,10 @@
     </row>
     <row r="765" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A765" t="s">
-        <v>1537</v>
+        <v>1531</v>
       </c>
       <c r="B765" t="s">
-        <v>1538</v>
+        <v>1532</v>
       </c>
       <c r="C765" s="2" t="s">
         <v>7</v>
@@ -16046,10 +16076,10 @@
     </row>
     <row r="766" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A766" t="s">
-        <v>1539</v>
+        <v>1533</v>
       </c>
       <c r="B766" t="s">
-        <v>1540</v>
+        <v>1534</v>
       </c>
       <c r="C766" s="2" t="s">
         <v>7</v>
@@ -16060,10 +16090,10 @@
     </row>
     <row r="767" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A767" t="s">
-        <v>1541</v>
+        <v>1535</v>
       </c>
       <c r="B767" t="s">
-        <v>1542</v>
+        <v>1536</v>
       </c>
       <c r="C767" s="2" t="s">
         <v>7</v>
@@ -16074,10 +16104,10 @@
     </row>
     <row r="768" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A768" t="s">
-        <v>1543</v>
+        <v>1537</v>
       </c>
       <c r="B768" t="s">
-        <v>1544</v>
+        <v>1538</v>
       </c>
       <c r="C768" s="2" t="s">
         <v>7</v>
@@ -16088,10 +16118,10 @@
     </row>
     <row r="769" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A769" t="s">
-        <v>1545</v>
+        <v>1539</v>
       </c>
       <c r="B769" t="s">
-        <v>1546</v>
+        <v>1540</v>
       </c>
       <c r="C769" s="2" t="s">
         <v>7</v>
@@ -16102,10 +16132,10 @@
     </row>
     <row r="770" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A770" t="s">
-        <v>1547</v>
+        <v>1541</v>
       </c>
       <c r="B770" t="s">
-        <v>1548</v>
+        <v>1542</v>
       </c>
       <c r="C770" s="2" t="s">
         <v>7</v>
@@ -16116,10 +16146,10 @@
     </row>
     <row r="771" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A771" t="s">
-        <v>1549</v>
+        <v>1543</v>
       </c>
       <c r="B771" t="s">
-        <v>1550</v>
+        <v>1544</v>
       </c>
       <c r="C771" s="2" t="s">
         <v>7</v>
@@ -16130,10 +16160,10 @@
     </row>
     <row r="772" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A772" t="s">
-        <v>1551</v>
+        <v>1545</v>
       </c>
       <c r="B772" t="s">
-        <v>1552</v>
+        <v>1546</v>
       </c>
       <c r="C772" s="2" t="s">
         <v>7</v>
@@ -16144,10 +16174,10 @@
     </row>
     <row r="773" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A773" t="s">
-        <v>1553</v>
+        <v>1547</v>
       </c>
       <c r="B773" t="s">
-        <v>1554</v>
+        <v>1548</v>
       </c>
       <c r="C773" s="2" t="s">
         <v>7</v>
@@ -16158,10 +16188,10 @@
     </row>
     <row r="774" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A774" t="s">
-        <v>1555</v>
+        <v>1549</v>
       </c>
       <c r="B774" t="s">
-        <v>1556</v>
+        <v>1550</v>
       </c>
       <c r="C774" s="2" t="s">
         <v>7</v>
@@ -16172,10 +16202,10 @@
     </row>
     <row r="775" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A775" t="s">
-        <v>1557</v>
+        <v>1551</v>
       </c>
       <c r="B775" t="s">
-        <v>1558</v>
+        <v>1552</v>
       </c>
       <c r="C775" s="2" t="s">
         <v>7</v>
@@ -16186,10 +16216,10 @@
     </row>
     <row r="776" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A776" t="s">
-        <v>1559</v>
+        <v>1553</v>
       </c>
       <c r="B776" t="s">
-        <v>1560</v>
+        <v>1554</v>
       </c>
       <c r="C776" s="2" t="s">
         <v>7</v>
@@ -16200,10 +16230,10 @@
     </row>
     <row r="777" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A777" t="s">
-        <v>1561</v>
+        <v>1555</v>
       </c>
       <c r="B777" t="s">
-        <v>1562</v>
+        <v>1556</v>
       </c>
       <c r="C777" s="2" t="s">
         <v>7</v>
@@ -16214,10 +16244,10 @@
     </row>
     <row r="778" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A778" t="s">
-        <v>1565</v>
+        <v>1557</v>
       </c>
       <c r="B778" t="s">
-        <v>1566</v>
+        <v>1558</v>
       </c>
       <c r="C778" s="2" t="s">
         <v>7</v>
@@ -16228,10 +16258,10 @@
     </row>
     <row r="779" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A779" t="s">
-        <v>1567</v>
+        <v>1559</v>
       </c>
       <c r="B779" t="s">
-        <v>1568</v>
+        <v>1560</v>
       </c>
       <c r="C779" s="2" t="s">
         <v>7</v>
@@ -16242,10 +16272,10 @@
     </row>
     <row r="780" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A780" t="s">
-        <v>1569</v>
+        <v>1561</v>
       </c>
       <c r="B780" t="s">
-        <v>1570</v>
+        <v>1562</v>
       </c>
       <c r="C780" s="2" t="s">
         <v>7</v>
@@ -16256,10 +16286,10 @@
     </row>
     <row r="781" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A781" t="s">
-        <v>1571</v>
+        <v>1563</v>
       </c>
       <c r="B781" t="s">
-        <v>1572</v>
+        <v>1564</v>
       </c>
       <c r="C781" s="2" t="s">
         <v>7</v>
@@ -16270,10 +16300,10 @@
     </row>
     <row r="782" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A782" t="s">
-        <v>1573</v>
+        <v>1565</v>
       </c>
       <c r="B782" t="s">
-        <v>1574</v>
+        <v>1566</v>
       </c>
       <c r="C782" s="2" t="s">
         <v>7</v>
@@ -16284,10 +16314,10 @@
     </row>
     <row r="783" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A783" t="s">
-        <v>1577</v>
+        <v>1567</v>
       </c>
       <c r="B783" t="s">
-        <v>1578</v>
+        <v>1568</v>
       </c>
       <c r="C783" s="2" t="s">
         <v>7</v>
@@ -16298,10 +16328,10 @@
     </row>
     <row r="784" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A784" t="s">
-        <v>1579</v>
+        <v>1571</v>
       </c>
       <c r="B784" t="s">
-        <v>1580</v>
+        <v>1572</v>
       </c>
       <c r="C784" s="2" t="s">
         <v>7</v>
@@ -16312,10 +16342,10 @@
     </row>
     <row r="785" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A785" t="s">
-        <v>1581</v>
+        <v>1573</v>
       </c>
       <c r="B785" t="s">
-        <v>1582</v>
+        <v>1574</v>
       </c>
       <c r="C785" s="2" t="s">
         <v>7</v>
@@ -16326,10 +16356,10 @@
     </row>
     <row r="786" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A786" t="s">
-        <v>1583</v>
+        <v>1575</v>
       </c>
       <c r="B786" t="s">
-        <v>1584</v>
+        <v>1576</v>
       </c>
       <c r="C786" s="2" t="s">
         <v>7</v>
@@ -16340,10 +16370,10 @@
     </row>
     <row r="787" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A787" t="s">
-        <v>1585</v>
+        <v>1577</v>
       </c>
       <c r="B787" t="s">
-        <v>1586</v>
+        <v>1578</v>
       </c>
       <c r="C787" s="2" t="s">
         <v>7</v>
@@ -16354,10 +16384,10 @@
     </row>
     <row r="788" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A788" t="s">
-        <v>1587</v>
+        <v>1579</v>
       </c>
       <c r="B788" t="s">
-        <v>1588</v>
+        <v>1580</v>
       </c>
       <c r="C788" s="2" t="s">
         <v>7</v>
@@ -16368,10 +16398,10 @@
     </row>
     <row r="789" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A789" t="s">
-        <v>1589</v>
+        <v>1583</v>
       </c>
       <c r="B789" t="s">
-        <v>1590</v>
+        <v>1584</v>
       </c>
       <c r="C789" s="2" t="s">
         <v>7</v>
@@ -16382,10 +16412,10 @@
     </row>
     <row r="790" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A790" t="s">
-        <v>1591</v>
+        <v>1585</v>
       </c>
       <c r="B790" t="s">
-        <v>1592</v>
+        <v>1586</v>
       </c>
       <c r="C790" s="2" t="s">
         <v>7</v>
@@ -16396,10 +16426,10 @@
     </row>
     <row r="791" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A791" t="s">
-        <v>1593</v>
+        <v>1587</v>
       </c>
       <c r="B791" t="s">
-        <v>1594</v>
+        <v>1588</v>
       </c>
       <c r="C791" s="2" t="s">
         <v>7</v>
@@ -16410,10 +16440,10 @@
     </row>
     <row r="792" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A792" t="s">
-        <v>1595</v>
+        <v>1589</v>
       </c>
       <c r="B792" t="s">
-        <v>1596</v>
+        <v>1590</v>
       </c>
       <c r="C792" s="2" t="s">
         <v>7</v>
@@ -16424,10 +16454,10 @@
     </row>
     <row r="793" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A793" t="s">
-        <v>1597</v>
+        <v>1591</v>
       </c>
       <c r="B793" t="s">
-        <v>1598</v>
+        <v>1592</v>
       </c>
       <c r="C793" s="2" t="s">
         <v>7</v>
@@ -16438,10 +16468,10 @@
     </row>
     <row r="794" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A794" t="s">
-        <v>1599</v>
+        <v>1593</v>
       </c>
       <c r="B794" t="s">
-        <v>1600</v>
+        <v>1594</v>
       </c>
       <c r="C794" s="2" t="s">
         <v>7</v>
@@ -16452,10 +16482,10 @@
     </row>
     <row r="795" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A795" t="s">
-        <v>1601</v>
+        <v>1595</v>
       </c>
       <c r="B795" t="s">
-        <v>1602</v>
+        <v>1596</v>
       </c>
       <c r="C795" s="2" t="s">
         <v>7</v>
@@ -16466,10 +16496,10 @@
     </row>
     <row r="796" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A796" t="s">
-        <v>1603</v>
+        <v>1597</v>
       </c>
       <c r="B796" t="s">
-        <v>1604</v>
+        <v>1598</v>
       </c>
       <c r="C796" s="2" t="s">
         <v>7</v>
@@ -16480,10 +16510,10 @@
     </row>
     <row r="797" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A797" t="s">
-        <v>1607</v>
+        <v>1599</v>
       </c>
       <c r="B797" t="s">
-        <v>1608</v>
+        <v>1600</v>
       </c>
       <c r="C797" s="2" t="s">
         <v>7</v>
@@ -16494,10 +16524,10 @@
     </row>
     <row r="798" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A798" t="s">
-        <v>1609</v>
+        <v>1601</v>
       </c>
       <c r="B798" t="s">
-        <v>1610</v>
+        <v>1602</v>
       </c>
       <c r="C798" s="2" t="s">
         <v>7</v>
@@ -16508,10 +16538,10 @@
     </row>
     <row r="799" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A799" t="s">
-        <v>1611</v>
+        <v>1603</v>
       </c>
       <c r="B799" t="s">
-        <v>1612</v>
+        <v>1604</v>
       </c>
       <c r="C799" s="2" t="s">
         <v>7</v>
@@ -16522,10 +16552,10 @@
     </row>
     <row r="800" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A800" t="s">
-        <v>1613</v>
+        <v>1605</v>
       </c>
       <c r="B800" t="s">
-        <v>1614</v>
+        <v>1606</v>
       </c>
       <c r="C800" s="2" t="s">
         <v>7</v>
@@ -16536,10 +16566,10 @@
     </row>
     <row r="801" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A801" t="s">
-        <v>1615</v>
+        <v>1607</v>
       </c>
       <c r="B801" t="s">
-        <v>1616</v>
+        <v>1608</v>
       </c>
       <c r="C801" s="2" t="s">
         <v>7</v>
@@ -16550,10 +16580,10 @@
     </row>
     <row r="802" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A802" t="s">
-        <v>1617</v>
+        <v>1609</v>
       </c>
       <c r="B802" t="s">
-        <v>1618</v>
+        <v>1610</v>
       </c>
       <c r="C802" s="2" t="s">
         <v>7</v>
@@ -16564,10 +16594,10 @@
     </row>
     <row r="803" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A803" t="s">
-        <v>1619</v>
+        <v>1615</v>
       </c>
       <c r="B803" t="s">
-        <v>1620</v>
+        <v>1616</v>
       </c>
       <c r="C803" s="2" t="s">
         <v>7</v>
@@ -16578,10 +16608,10 @@
     </row>
     <row r="804" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A804" t="s">
-        <v>1621</v>
+        <v>1617</v>
       </c>
       <c r="B804" t="s">
-        <v>1622</v>
+        <v>1618</v>
       </c>
       <c r="C804" s="2" t="s">
         <v>7</v>
@@ -16592,10 +16622,10 @@
     </row>
     <row r="805" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A805" t="s">
-        <v>1623</v>
+        <v>1619</v>
       </c>
       <c r="B805" t="s">
-        <v>1624</v>
+        <v>1620</v>
       </c>
       <c r="C805" s="2" t="s">
         <v>7</v>
@@ -16606,10 +16636,10 @@
     </row>
     <row r="806" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A806" t="s">
-        <v>1625</v>
+        <v>1621</v>
       </c>
       <c r="B806" t="s">
-        <v>1626</v>
+        <v>1622</v>
       </c>
       <c r="C806" s="2" t="s">
         <v>7</v>
@@ -16620,10 +16650,10 @@
     </row>
     <row r="807" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A807" t="s">
-        <v>1627</v>
+        <v>1625</v>
       </c>
       <c r="B807" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="C807" s="2" t="s">
         <v>7</v>
@@ -16634,10 +16664,10 @@
     </row>
     <row r="808" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A808" t="s">
-        <v>201</v>
+        <v>1627</v>
       </c>
       <c r="B808" t="s">
-        <v>202</v>
+        <v>1628</v>
       </c>
       <c r="C808" s="2" t="s">
         <v>7</v>
@@ -16648,10 +16678,10 @@
     </row>
     <row r="809" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A809" t="s">
-        <v>651</v>
+        <v>1629</v>
       </c>
       <c r="B809" t="s">
-        <v>652</v>
+        <v>1630</v>
       </c>
       <c r="C809" s="2" t="s">
         <v>7</v>
@@ -16662,10 +16692,10 @@
     </row>
     <row r="810" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A810" t="s">
-        <v>693</v>
+        <v>1631</v>
       </c>
       <c r="B810" t="s">
-        <v>694</v>
+        <v>1632</v>
       </c>
       <c r="C810" s="2" t="s">
         <v>7</v>
@@ -16676,10 +16706,10 @@
     </row>
     <row r="811" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A811" t="s">
-        <v>1127</v>
+        <v>1633</v>
       </c>
       <c r="B811" t="s">
-        <v>1128</v>
+        <v>1634</v>
       </c>
       <c r="C811" s="2" t="s">
         <v>7</v>
@@ -16690,10 +16720,10 @@
     </row>
     <row r="812" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A812" t="s">
-        <v>1183</v>
+        <v>1635</v>
       </c>
       <c r="B812" t="s">
-        <v>1184</v>
+        <v>1636</v>
       </c>
       <c r="C812" s="2" t="s">
         <v>7</v>
@@ -16704,26 +16734,96 @@
     </row>
     <row r="813" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A813" t="s">
-        <v>1191</v>
+        <v>1637</v>
       </c>
       <c r="B813" t="s">
-        <v>1192</v>
+        <v>1638</v>
       </c>
       <c r="C813" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D813" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="814" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A814" t="s">
+        <v>781</v>
+      </c>
+      <c r="B814" t="s">
+        <v>782</v>
+      </c>
+      <c r="C814" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D814" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="815" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A815" t="s">
+        <v>805</v>
+      </c>
+      <c r="B815" t="s">
+        <v>806</v>
+      </c>
+      <c r="C815" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D815" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="816" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A816" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B816" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C816" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D816" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="817" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A817" t="s">
+        <v>1611</v>
+      </c>
+      <c r="B817" t="s">
+        <v>1612</v>
+      </c>
+      <c r="C817" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D817" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="818" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A818" t="s">
+        <v>1623</v>
+      </c>
+      <c r="B818" t="s">
+        <v>1624</v>
+      </c>
+      <c r="C818" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D818" t="s">
         <v>8</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F813">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F818">
       <sortCondition ref="E1"/>
     </sortState>
   </autoFilter>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="D2:E813" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D2:E818" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"X"</formula1>
     </dataValidation>
   </dataValidations>
@@ -16826,409 +16926,409 @@
     <hyperlink ref="C141" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
     <hyperlink ref="C142" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
     <hyperlink ref="C143" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
-    <hyperlink ref="C808" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
-    <hyperlink ref="C144" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
-    <hyperlink ref="C145" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
-    <hyperlink ref="C146" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
-    <hyperlink ref="C147" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
-    <hyperlink ref="C148" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
-    <hyperlink ref="C149" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
-    <hyperlink ref="C150" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
-    <hyperlink ref="C151" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
-    <hyperlink ref="C152" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
-    <hyperlink ref="C153" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
-    <hyperlink ref="C154" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
-    <hyperlink ref="C155" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
-    <hyperlink ref="C156" r:id="rId112" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
-    <hyperlink ref="C157" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
-    <hyperlink ref="C158" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
-    <hyperlink ref="C159" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
-    <hyperlink ref="C160" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
-    <hyperlink ref="C161" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
-    <hyperlink ref="C162" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
-    <hyperlink ref="C163" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
-    <hyperlink ref="C164" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
-    <hyperlink ref="C165" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
-    <hyperlink ref="C166" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
-    <hyperlink ref="C167" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
-    <hyperlink ref="C168" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
-    <hyperlink ref="C169" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
-    <hyperlink ref="C170" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
-    <hyperlink ref="C171" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
-    <hyperlink ref="C172" r:id="rId128" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
-    <hyperlink ref="C173" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
+    <hyperlink ref="C144" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="C145" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="C146" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="C147" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="C148" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="C149" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="C150" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="C151" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="C152" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="C153" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="C154" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="C155" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="C156" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="C157" r:id="rId112" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
+    <hyperlink ref="C158" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
+    <hyperlink ref="C159" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="C160" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="C161" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="C162" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
+    <hyperlink ref="C163" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
+    <hyperlink ref="C164" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
+    <hyperlink ref="C165" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
+    <hyperlink ref="C166" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
+    <hyperlink ref="C167" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
+    <hyperlink ref="C168" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
+    <hyperlink ref="C169" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
+    <hyperlink ref="C170" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
+    <hyperlink ref="C171" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
+    <hyperlink ref="C172" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
+    <hyperlink ref="C173" r:id="rId128" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
+    <hyperlink ref="C174" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
     <hyperlink ref="C12" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
-    <hyperlink ref="C174" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
-    <hyperlink ref="C175" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
-    <hyperlink ref="C176" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
+    <hyperlink ref="C175" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
+    <hyperlink ref="C176" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
+    <hyperlink ref="C177" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
     <hyperlink ref="C13" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
-    <hyperlink ref="C177" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
+    <hyperlink ref="C178" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
     <hyperlink ref="C14" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
-    <hyperlink ref="C178" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
-    <hyperlink ref="C179" r:id="rId138" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
-    <hyperlink ref="C180" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
+    <hyperlink ref="C179" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
+    <hyperlink ref="C180" r:id="rId138" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
+    <hyperlink ref="C181" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
     <hyperlink ref="C15" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
-    <hyperlink ref="C181" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
-    <hyperlink ref="C182" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
-    <hyperlink ref="C183" r:id="rId143" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
-    <hyperlink ref="C184" r:id="rId144" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
-    <hyperlink ref="C185" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
-    <hyperlink ref="C186" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
-    <hyperlink ref="C187" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
-    <hyperlink ref="C188" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
-    <hyperlink ref="C189" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
-    <hyperlink ref="C190" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
+    <hyperlink ref="C182" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
+    <hyperlink ref="C183" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
+    <hyperlink ref="C184" r:id="rId143" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
+    <hyperlink ref="C185" r:id="rId144" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
+    <hyperlink ref="C186" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
+    <hyperlink ref="C187" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
+    <hyperlink ref="C188" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
+    <hyperlink ref="C189" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
+    <hyperlink ref="C190" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
+    <hyperlink ref="C191" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
     <hyperlink ref="C16" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
-    <hyperlink ref="C191" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
-    <hyperlink ref="C192" r:id="rId153" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
-    <hyperlink ref="C193" r:id="rId154" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
-    <hyperlink ref="C194" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
-    <hyperlink ref="C195" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
-    <hyperlink ref="C196" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
-    <hyperlink ref="C197" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
-    <hyperlink ref="C198" r:id="rId159" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
-    <hyperlink ref="C199" r:id="rId160" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
-    <hyperlink ref="C200" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
-    <hyperlink ref="C201" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
-    <hyperlink ref="C202" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
-    <hyperlink ref="C203" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
-    <hyperlink ref="C204" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
-    <hyperlink ref="C205" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
-    <hyperlink ref="C206" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
+    <hyperlink ref="C192" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
+    <hyperlink ref="C193" r:id="rId153" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
+    <hyperlink ref="C194" r:id="rId154" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
+    <hyperlink ref="C195" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
+    <hyperlink ref="C196" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
+    <hyperlink ref="C197" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
+    <hyperlink ref="C198" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
+    <hyperlink ref="C199" r:id="rId159" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
+    <hyperlink ref="C200" r:id="rId160" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
+    <hyperlink ref="C201" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
+    <hyperlink ref="C202" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
+    <hyperlink ref="C203" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
+    <hyperlink ref="C204" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
+    <hyperlink ref="C205" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
+    <hyperlink ref="C206" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
+    <hyperlink ref="C207" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
     <hyperlink ref="C17" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
-    <hyperlink ref="C207" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
-    <hyperlink ref="C208" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
-    <hyperlink ref="C209" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
-    <hyperlink ref="C210" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
-    <hyperlink ref="C211" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
-    <hyperlink ref="C212" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
-    <hyperlink ref="C213" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
-    <hyperlink ref="C214" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
-    <hyperlink ref="C215" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
-    <hyperlink ref="C216" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
-    <hyperlink ref="C217" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
-    <hyperlink ref="C218" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
-    <hyperlink ref="C219" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
-    <hyperlink ref="C220" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
-    <hyperlink ref="C221" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
-    <hyperlink ref="C222" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
-    <hyperlink ref="C223" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
-    <hyperlink ref="C224" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
+    <hyperlink ref="C208" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
+    <hyperlink ref="C209" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
+    <hyperlink ref="C210" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
+    <hyperlink ref="C211" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
+    <hyperlink ref="C212" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
+    <hyperlink ref="C213" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
+    <hyperlink ref="C214" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
+    <hyperlink ref="C215" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
+    <hyperlink ref="C216" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
+    <hyperlink ref="C217" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
+    <hyperlink ref="C218" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
+    <hyperlink ref="C219" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
+    <hyperlink ref="C220" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
+    <hyperlink ref="C221" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
+    <hyperlink ref="C222" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
+    <hyperlink ref="C223" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
+    <hyperlink ref="C224" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
+    <hyperlink ref="C225" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
     <hyperlink ref="C18" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
-    <hyperlink ref="C225" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
-    <hyperlink ref="C226" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
-    <hyperlink ref="C227" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
+    <hyperlink ref="C226" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
+    <hyperlink ref="C227" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
+    <hyperlink ref="C228" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
     <hyperlink ref="C19" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
-    <hyperlink ref="C228" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
-    <hyperlink ref="C229" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
-    <hyperlink ref="C230" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
-    <hyperlink ref="C231" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
-    <hyperlink ref="C232" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
-    <hyperlink ref="C233" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
+    <hyperlink ref="C229" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
+    <hyperlink ref="C230" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
+    <hyperlink ref="C231" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
+    <hyperlink ref="C232" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
+    <hyperlink ref="C233" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
+    <hyperlink ref="C234" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
     <hyperlink ref="C20" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
-    <hyperlink ref="C234" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
-    <hyperlink ref="C235" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
-    <hyperlink ref="C236" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
-    <hyperlink ref="C237" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
-    <hyperlink ref="C238" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
-    <hyperlink ref="C239" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
-    <hyperlink ref="C240" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
-    <hyperlink ref="C241" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
-    <hyperlink ref="C242" r:id="rId207" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
-    <hyperlink ref="C243" r:id="rId208" xr:uid="{00000000-0004-0000-0000-0000CF000000}"/>
-    <hyperlink ref="C244" r:id="rId209" xr:uid="{00000000-0004-0000-0000-0000D0000000}"/>
-    <hyperlink ref="C245" r:id="rId210" xr:uid="{00000000-0004-0000-0000-0000D1000000}"/>
-    <hyperlink ref="C246" r:id="rId211" xr:uid="{00000000-0004-0000-0000-0000D2000000}"/>
-    <hyperlink ref="C247" r:id="rId212" xr:uid="{00000000-0004-0000-0000-0000D3000000}"/>
-    <hyperlink ref="C248" r:id="rId213" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
-    <hyperlink ref="C249" r:id="rId214" xr:uid="{00000000-0004-0000-0000-0000D5000000}"/>
-    <hyperlink ref="C250" r:id="rId215" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
-    <hyperlink ref="C251" r:id="rId216" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
+    <hyperlink ref="C235" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
+    <hyperlink ref="C236" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
+    <hyperlink ref="C237" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
+    <hyperlink ref="C238" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
+    <hyperlink ref="C239" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
+    <hyperlink ref="C240" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
+    <hyperlink ref="C241" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
+    <hyperlink ref="C242" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
+    <hyperlink ref="C243" r:id="rId207" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
+    <hyperlink ref="C244" r:id="rId208" xr:uid="{00000000-0004-0000-0000-0000CF000000}"/>
+    <hyperlink ref="C245" r:id="rId209" xr:uid="{00000000-0004-0000-0000-0000D0000000}"/>
+    <hyperlink ref="C246" r:id="rId210" xr:uid="{00000000-0004-0000-0000-0000D1000000}"/>
+    <hyperlink ref="C247" r:id="rId211" xr:uid="{00000000-0004-0000-0000-0000D2000000}"/>
+    <hyperlink ref="C248" r:id="rId212" xr:uid="{00000000-0004-0000-0000-0000D3000000}"/>
+    <hyperlink ref="C249" r:id="rId213" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
+    <hyperlink ref="C250" r:id="rId214" xr:uid="{00000000-0004-0000-0000-0000D5000000}"/>
+    <hyperlink ref="C251" r:id="rId215" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
+    <hyperlink ref="C252" r:id="rId216" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
     <hyperlink ref="C21" r:id="rId217" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
-    <hyperlink ref="C252" r:id="rId218" xr:uid="{00000000-0004-0000-0000-0000D9000000}"/>
-    <hyperlink ref="C253" r:id="rId219" xr:uid="{00000000-0004-0000-0000-0000DA000000}"/>
-    <hyperlink ref="C254" r:id="rId220" xr:uid="{00000000-0004-0000-0000-0000DB000000}"/>
-    <hyperlink ref="C255" r:id="rId221" xr:uid="{00000000-0004-0000-0000-0000DC000000}"/>
-    <hyperlink ref="C256" r:id="rId222" xr:uid="{00000000-0004-0000-0000-0000DD000000}"/>
-    <hyperlink ref="C257" r:id="rId223" xr:uid="{00000000-0004-0000-0000-0000DE000000}"/>
-    <hyperlink ref="C258" r:id="rId224" xr:uid="{00000000-0004-0000-0000-0000DF000000}"/>
-    <hyperlink ref="C259" r:id="rId225" xr:uid="{00000000-0004-0000-0000-0000E0000000}"/>
-    <hyperlink ref="C260" r:id="rId226" xr:uid="{00000000-0004-0000-0000-0000E1000000}"/>
-    <hyperlink ref="C261" r:id="rId227" xr:uid="{00000000-0004-0000-0000-0000E2000000}"/>
-    <hyperlink ref="C262" r:id="rId228" xr:uid="{00000000-0004-0000-0000-0000E3000000}"/>
-    <hyperlink ref="C263" r:id="rId229" xr:uid="{00000000-0004-0000-0000-0000E4000000}"/>
-    <hyperlink ref="C264" r:id="rId230" xr:uid="{00000000-0004-0000-0000-0000E5000000}"/>
-    <hyperlink ref="C265" r:id="rId231" xr:uid="{00000000-0004-0000-0000-0000E6000000}"/>
-    <hyperlink ref="C266" r:id="rId232" xr:uid="{00000000-0004-0000-0000-0000E7000000}"/>
-    <hyperlink ref="C267" r:id="rId233" xr:uid="{00000000-0004-0000-0000-0000E8000000}"/>
-    <hyperlink ref="C268" r:id="rId234" xr:uid="{00000000-0004-0000-0000-0000E9000000}"/>
-    <hyperlink ref="C269" r:id="rId235" xr:uid="{00000000-0004-0000-0000-0000EA000000}"/>
-    <hyperlink ref="C270" r:id="rId236" xr:uid="{00000000-0004-0000-0000-0000EB000000}"/>
-    <hyperlink ref="C271" r:id="rId237" xr:uid="{00000000-0004-0000-0000-0000EC000000}"/>
-    <hyperlink ref="C272" r:id="rId238" xr:uid="{00000000-0004-0000-0000-0000ED000000}"/>
-    <hyperlink ref="C273" r:id="rId239" xr:uid="{00000000-0004-0000-0000-0000EE000000}"/>
-    <hyperlink ref="C274" r:id="rId240" xr:uid="{00000000-0004-0000-0000-0000EF000000}"/>
-    <hyperlink ref="C275" r:id="rId241" xr:uid="{00000000-0004-0000-0000-0000F0000000}"/>
-    <hyperlink ref="C276" r:id="rId242" xr:uid="{00000000-0004-0000-0000-0000F1000000}"/>
-    <hyperlink ref="C277" r:id="rId243" xr:uid="{00000000-0004-0000-0000-0000F2000000}"/>
-    <hyperlink ref="C278" r:id="rId244" xr:uid="{00000000-0004-0000-0000-0000F3000000}"/>
-    <hyperlink ref="C279" r:id="rId245" xr:uid="{00000000-0004-0000-0000-0000F4000000}"/>
+    <hyperlink ref="C253" r:id="rId218" xr:uid="{00000000-0004-0000-0000-0000D9000000}"/>
+    <hyperlink ref="C254" r:id="rId219" xr:uid="{00000000-0004-0000-0000-0000DA000000}"/>
+    <hyperlink ref="C255" r:id="rId220" xr:uid="{00000000-0004-0000-0000-0000DB000000}"/>
+    <hyperlink ref="C256" r:id="rId221" xr:uid="{00000000-0004-0000-0000-0000DC000000}"/>
+    <hyperlink ref="C257" r:id="rId222" xr:uid="{00000000-0004-0000-0000-0000DD000000}"/>
+    <hyperlink ref="C258" r:id="rId223" xr:uid="{00000000-0004-0000-0000-0000DE000000}"/>
+    <hyperlink ref="C259" r:id="rId224" xr:uid="{00000000-0004-0000-0000-0000DF000000}"/>
+    <hyperlink ref="C260" r:id="rId225" xr:uid="{00000000-0004-0000-0000-0000E0000000}"/>
+    <hyperlink ref="C261" r:id="rId226" xr:uid="{00000000-0004-0000-0000-0000E1000000}"/>
+    <hyperlink ref="C262" r:id="rId227" xr:uid="{00000000-0004-0000-0000-0000E2000000}"/>
+    <hyperlink ref="C263" r:id="rId228" xr:uid="{00000000-0004-0000-0000-0000E3000000}"/>
+    <hyperlink ref="C264" r:id="rId229" xr:uid="{00000000-0004-0000-0000-0000E4000000}"/>
+    <hyperlink ref="C265" r:id="rId230" xr:uid="{00000000-0004-0000-0000-0000E5000000}"/>
+    <hyperlink ref="C266" r:id="rId231" xr:uid="{00000000-0004-0000-0000-0000E6000000}"/>
+    <hyperlink ref="C267" r:id="rId232" xr:uid="{00000000-0004-0000-0000-0000E7000000}"/>
+    <hyperlink ref="C268" r:id="rId233" xr:uid="{00000000-0004-0000-0000-0000E8000000}"/>
+    <hyperlink ref="C269" r:id="rId234" xr:uid="{00000000-0004-0000-0000-0000E9000000}"/>
+    <hyperlink ref="C270" r:id="rId235" xr:uid="{00000000-0004-0000-0000-0000EA000000}"/>
+    <hyperlink ref="C271" r:id="rId236" xr:uid="{00000000-0004-0000-0000-0000EB000000}"/>
+    <hyperlink ref="C272" r:id="rId237" xr:uid="{00000000-0004-0000-0000-0000EC000000}"/>
+    <hyperlink ref="C273" r:id="rId238" xr:uid="{00000000-0004-0000-0000-0000ED000000}"/>
+    <hyperlink ref="C274" r:id="rId239" xr:uid="{00000000-0004-0000-0000-0000EE000000}"/>
+    <hyperlink ref="C275" r:id="rId240" xr:uid="{00000000-0004-0000-0000-0000EF000000}"/>
+    <hyperlink ref="C276" r:id="rId241" xr:uid="{00000000-0004-0000-0000-0000F0000000}"/>
+    <hyperlink ref="C277" r:id="rId242" xr:uid="{00000000-0004-0000-0000-0000F1000000}"/>
+    <hyperlink ref="C278" r:id="rId243" xr:uid="{00000000-0004-0000-0000-0000F2000000}"/>
+    <hyperlink ref="C279" r:id="rId244" xr:uid="{00000000-0004-0000-0000-0000F3000000}"/>
+    <hyperlink ref="C280" r:id="rId245" xr:uid="{00000000-0004-0000-0000-0000F4000000}"/>
     <hyperlink ref="C22" r:id="rId246" xr:uid="{00000000-0004-0000-0000-0000F5000000}"/>
-    <hyperlink ref="C280" r:id="rId247" xr:uid="{00000000-0004-0000-0000-0000F6000000}"/>
-    <hyperlink ref="C281" r:id="rId248" xr:uid="{00000000-0004-0000-0000-0000F7000000}"/>
-    <hyperlink ref="C282" r:id="rId249" xr:uid="{00000000-0004-0000-0000-0000F8000000}"/>
-    <hyperlink ref="C283" r:id="rId250" xr:uid="{00000000-0004-0000-0000-0000F9000000}"/>
+    <hyperlink ref="C281" r:id="rId247" xr:uid="{00000000-0004-0000-0000-0000F6000000}"/>
+    <hyperlink ref="C282" r:id="rId248" xr:uid="{00000000-0004-0000-0000-0000F7000000}"/>
+    <hyperlink ref="C283" r:id="rId249" xr:uid="{00000000-0004-0000-0000-0000F8000000}"/>
+    <hyperlink ref="C284" r:id="rId250" xr:uid="{00000000-0004-0000-0000-0000F9000000}"/>
     <hyperlink ref="C23" r:id="rId251" xr:uid="{00000000-0004-0000-0000-0000FA000000}"/>
-    <hyperlink ref="C284" r:id="rId252" xr:uid="{00000000-0004-0000-0000-0000FB000000}"/>
-    <hyperlink ref="C285" r:id="rId253" xr:uid="{00000000-0004-0000-0000-0000FC000000}"/>
-    <hyperlink ref="C286" r:id="rId254" xr:uid="{00000000-0004-0000-0000-0000FD000000}"/>
-    <hyperlink ref="C287" r:id="rId255" xr:uid="{00000000-0004-0000-0000-0000FE000000}"/>
-    <hyperlink ref="C288" r:id="rId256" xr:uid="{00000000-0004-0000-0000-0000FF000000}"/>
-    <hyperlink ref="C289" r:id="rId257" xr:uid="{00000000-0004-0000-0000-000000010000}"/>
-    <hyperlink ref="C290" r:id="rId258" xr:uid="{00000000-0004-0000-0000-000001010000}"/>
-    <hyperlink ref="C291" r:id="rId259" xr:uid="{00000000-0004-0000-0000-000002010000}"/>
-    <hyperlink ref="C292" r:id="rId260" xr:uid="{00000000-0004-0000-0000-000003010000}"/>
+    <hyperlink ref="C285" r:id="rId252" xr:uid="{00000000-0004-0000-0000-0000FB000000}"/>
+    <hyperlink ref="C286" r:id="rId253" xr:uid="{00000000-0004-0000-0000-0000FC000000}"/>
+    <hyperlink ref="C287" r:id="rId254" xr:uid="{00000000-0004-0000-0000-0000FD000000}"/>
+    <hyperlink ref="C288" r:id="rId255" xr:uid="{00000000-0004-0000-0000-0000FE000000}"/>
+    <hyperlink ref="C289" r:id="rId256" xr:uid="{00000000-0004-0000-0000-0000FF000000}"/>
+    <hyperlink ref="C290" r:id="rId257" xr:uid="{00000000-0004-0000-0000-000000010000}"/>
+    <hyperlink ref="C291" r:id="rId258" xr:uid="{00000000-0004-0000-0000-000001010000}"/>
+    <hyperlink ref="C292" r:id="rId259" xr:uid="{00000000-0004-0000-0000-000002010000}"/>
+    <hyperlink ref="C293" r:id="rId260" xr:uid="{00000000-0004-0000-0000-000003010000}"/>
     <hyperlink ref="C24" r:id="rId261" xr:uid="{00000000-0004-0000-0000-000004010000}"/>
-    <hyperlink ref="C293" r:id="rId262" xr:uid="{00000000-0004-0000-0000-000005010000}"/>
-    <hyperlink ref="C294" r:id="rId263" xr:uid="{00000000-0004-0000-0000-000006010000}"/>
-    <hyperlink ref="C295" r:id="rId264" xr:uid="{00000000-0004-0000-0000-000007010000}"/>
-    <hyperlink ref="C296" r:id="rId265" xr:uid="{00000000-0004-0000-0000-000008010000}"/>
-    <hyperlink ref="C297" r:id="rId266" xr:uid="{00000000-0004-0000-0000-000009010000}"/>
-    <hyperlink ref="C298" r:id="rId267" xr:uid="{00000000-0004-0000-0000-00000A010000}"/>
-    <hyperlink ref="C299" r:id="rId268" xr:uid="{00000000-0004-0000-0000-00000B010000}"/>
-    <hyperlink ref="C300" r:id="rId269" xr:uid="{00000000-0004-0000-0000-00000C010000}"/>
-    <hyperlink ref="C301" r:id="rId270" xr:uid="{00000000-0004-0000-0000-00000D010000}"/>
-    <hyperlink ref="C302" r:id="rId271" xr:uid="{00000000-0004-0000-0000-00000E010000}"/>
-    <hyperlink ref="C303" r:id="rId272" xr:uid="{00000000-0004-0000-0000-00000F010000}"/>
-    <hyperlink ref="C304" r:id="rId273" xr:uid="{00000000-0004-0000-0000-000010010000}"/>
-    <hyperlink ref="C305" r:id="rId274" xr:uid="{00000000-0004-0000-0000-000011010000}"/>
-    <hyperlink ref="C306" r:id="rId275" xr:uid="{00000000-0004-0000-0000-000012010000}"/>
-    <hyperlink ref="C307" r:id="rId276" xr:uid="{00000000-0004-0000-0000-000013010000}"/>
-    <hyperlink ref="C308" r:id="rId277" xr:uid="{00000000-0004-0000-0000-000014010000}"/>
-    <hyperlink ref="C309" r:id="rId278" xr:uid="{00000000-0004-0000-0000-000015010000}"/>
-    <hyperlink ref="C310" r:id="rId279" xr:uid="{00000000-0004-0000-0000-000016010000}"/>
-    <hyperlink ref="C311" r:id="rId280" xr:uid="{00000000-0004-0000-0000-000017010000}"/>
+    <hyperlink ref="C294" r:id="rId262" xr:uid="{00000000-0004-0000-0000-000005010000}"/>
+    <hyperlink ref="C295" r:id="rId263" xr:uid="{00000000-0004-0000-0000-000006010000}"/>
+    <hyperlink ref="C296" r:id="rId264" xr:uid="{00000000-0004-0000-0000-000007010000}"/>
+    <hyperlink ref="C297" r:id="rId265" xr:uid="{00000000-0004-0000-0000-000008010000}"/>
+    <hyperlink ref="C298" r:id="rId266" xr:uid="{00000000-0004-0000-0000-000009010000}"/>
+    <hyperlink ref="C299" r:id="rId267" xr:uid="{00000000-0004-0000-0000-00000A010000}"/>
+    <hyperlink ref="C300" r:id="rId268" xr:uid="{00000000-0004-0000-0000-00000B010000}"/>
+    <hyperlink ref="C301" r:id="rId269" xr:uid="{00000000-0004-0000-0000-00000C010000}"/>
+    <hyperlink ref="C302" r:id="rId270" xr:uid="{00000000-0004-0000-0000-00000D010000}"/>
+    <hyperlink ref="C303" r:id="rId271" xr:uid="{00000000-0004-0000-0000-00000E010000}"/>
+    <hyperlink ref="C304" r:id="rId272" xr:uid="{00000000-0004-0000-0000-00000F010000}"/>
+    <hyperlink ref="C305" r:id="rId273" xr:uid="{00000000-0004-0000-0000-000010010000}"/>
+    <hyperlink ref="C306" r:id="rId274" xr:uid="{00000000-0004-0000-0000-000011010000}"/>
+    <hyperlink ref="C307" r:id="rId275" xr:uid="{00000000-0004-0000-0000-000012010000}"/>
+    <hyperlink ref="C308" r:id="rId276" xr:uid="{00000000-0004-0000-0000-000013010000}"/>
+    <hyperlink ref="C309" r:id="rId277" xr:uid="{00000000-0004-0000-0000-000014010000}"/>
+    <hyperlink ref="C310" r:id="rId278" xr:uid="{00000000-0004-0000-0000-000015010000}"/>
+    <hyperlink ref="C311" r:id="rId279" xr:uid="{00000000-0004-0000-0000-000016010000}"/>
+    <hyperlink ref="C312" r:id="rId280" xr:uid="{00000000-0004-0000-0000-000017010000}"/>
     <hyperlink ref="C25" r:id="rId281" xr:uid="{00000000-0004-0000-0000-000018010000}"/>
-    <hyperlink ref="C312" r:id="rId282" xr:uid="{00000000-0004-0000-0000-000019010000}"/>
-    <hyperlink ref="C313" r:id="rId283" xr:uid="{00000000-0004-0000-0000-00001A010000}"/>
-    <hyperlink ref="C314" r:id="rId284" xr:uid="{00000000-0004-0000-0000-00001B010000}"/>
-    <hyperlink ref="C315" r:id="rId285" xr:uid="{00000000-0004-0000-0000-00001C010000}"/>
-    <hyperlink ref="C316" r:id="rId286" xr:uid="{00000000-0004-0000-0000-00001D010000}"/>
-    <hyperlink ref="C317" r:id="rId287" xr:uid="{00000000-0004-0000-0000-00001E010000}"/>
-    <hyperlink ref="C318" r:id="rId288" xr:uid="{00000000-0004-0000-0000-00001F010000}"/>
-    <hyperlink ref="C319" r:id="rId289" xr:uid="{00000000-0004-0000-0000-000020010000}"/>
-    <hyperlink ref="C320" r:id="rId290" xr:uid="{00000000-0004-0000-0000-000021010000}"/>
+    <hyperlink ref="C313" r:id="rId282" xr:uid="{00000000-0004-0000-0000-000019010000}"/>
+    <hyperlink ref="C314" r:id="rId283" xr:uid="{00000000-0004-0000-0000-00001A010000}"/>
+    <hyperlink ref="C315" r:id="rId284" xr:uid="{00000000-0004-0000-0000-00001B010000}"/>
+    <hyperlink ref="C316" r:id="rId285" xr:uid="{00000000-0004-0000-0000-00001C010000}"/>
+    <hyperlink ref="C317" r:id="rId286" xr:uid="{00000000-0004-0000-0000-00001D010000}"/>
+    <hyperlink ref="C318" r:id="rId287" xr:uid="{00000000-0004-0000-0000-00001E010000}"/>
+    <hyperlink ref="C319" r:id="rId288" xr:uid="{00000000-0004-0000-0000-00001F010000}"/>
+    <hyperlink ref="C320" r:id="rId289" xr:uid="{00000000-0004-0000-0000-000020010000}"/>
+    <hyperlink ref="C321" r:id="rId290" xr:uid="{00000000-0004-0000-0000-000021010000}"/>
     <hyperlink ref="C26" r:id="rId291" xr:uid="{00000000-0004-0000-0000-000022010000}"/>
-    <hyperlink ref="C321" r:id="rId292" xr:uid="{00000000-0004-0000-0000-000023010000}"/>
-    <hyperlink ref="C322" r:id="rId293" xr:uid="{00000000-0004-0000-0000-000024010000}"/>
-    <hyperlink ref="C323" r:id="rId294" xr:uid="{00000000-0004-0000-0000-000025010000}"/>
-    <hyperlink ref="C324" r:id="rId295" xr:uid="{00000000-0004-0000-0000-000026010000}"/>
-    <hyperlink ref="C325" r:id="rId296" xr:uid="{00000000-0004-0000-0000-000027010000}"/>
-    <hyperlink ref="C326" r:id="rId297" xr:uid="{00000000-0004-0000-0000-000028010000}"/>
-    <hyperlink ref="C327" r:id="rId298" xr:uid="{00000000-0004-0000-0000-000029010000}"/>
-    <hyperlink ref="C328" r:id="rId299" xr:uid="{00000000-0004-0000-0000-00002A010000}"/>
-    <hyperlink ref="C329" r:id="rId300" xr:uid="{00000000-0004-0000-0000-00002B010000}"/>
-    <hyperlink ref="C330" r:id="rId301" xr:uid="{00000000-0004-0000-0000-00002C010000}"/>
-    <hyperlink ref="C331" r:id="rId302" xr:uid="{00000000-0004-0000-0000-00002D010000}"/>
-    <hyperlink ref="C332" r:id="rId303" xr:uid="{00000000-0004-0000-0000-00002E010000}"/>
-    <hyperlink ref="C333" r:id="rId304" xr:uid="{00000000-0004-0000-0000-00002F010000}"/>
-    <hyperlink ref="C334" r:id="rId305" xr:uid="{00000000-0004-0000-0000-000030010000}"/>
-    <hyperlink ref="C335" r:id="rId306" xr:uid="{00000000-0004-0000-0000-000031010000}"/>
-    <hyperlink ref="C336" r:id="rId307" xr:uid="{00000000-0004-0000-0000-000032010000}"/>
-    <hyperlink ref="C337" r:id="rId308" xr:uid="{00000000-0004-0000-0000-000033010000}"/>
-    <hyperlink ref="C338" r:id="rId309" xr:uid="{00000000-0004-0000-0000-000034010000}"/>
-    <hyperlink ref="C339" r:id="rId310" xr:uid="{00000000-0004-0000-0000-000035010000}"/>
-    <hyperlink ref="C340" r:id="rId311" xr:uid="{00000000-0004-0000-0000-000036010000}"/>
-    <hyperlink ref="C341" r:id="rId312" xr:uid="{00000000-0004-0000-0000-000037010000}"/>
-    <hyperlink ref="C342" r:id="rId313" xr:uid="{00000000-0004-0000-0000-000038010000}"/>
-    <hyperlink ref="C343" r:id="rId314" xr:uid="{00000000-0004-0000-0000-000039010000}"/>
-    <hyperlink ref="C344" r:id="rId315" xr:uid="{00000000-0004-0000-0000-00003A010000}"/>
-    <hyperlink ref="C345" r:id="rId316" xr:uid="{00000000-0004-0000-0000-00003B010000}"/>
-    <hyperlink ref="C346" r:id="rId317" xr:uid="{00000000-0004-0000-0000-00003C010000}"/>
-    <hyperlink ref="C347" r:id="rId318" xr:uid="{00000000-0004-0000-0000-00003D010000}"/>
-    <hyperlink ref="C348" r:id="rId319" xr:uid="{00000000-0004-0000-0000-00003E010000}"/>
+    <hyperlink ref="C322" r:id="rId292" xr:uid="{00000000-0004-0000-0000-000023010000}"/>
+    <hyperlink ref="C323" r:id="rId293" xr:uid="{00000000-0004-0000-0000-000024010000}"/>
+    <hyperlink ref="C324" r:id="rId294" xr:uid="{00000000-0004-0000-0000-000025010000}"/>
+    <hyperlink ref="C325" r:id="rId295" xr:uid="{00000000-0004-0000-0000-000026010000}"/>
+    <hyperlink ref="C326" r:id="rId296" xr:uid="{00000000-0004-0000-0000-000027010000}"/>
+    <hyperlink ref="C327" r:id="rId297" xr:uid="{00000000-0004-0000-0000-000028010000}"/>
+    <hyperlink ref="C328" r:id="rId298" xr:uid="{00000000-0004-0000-0000-000029010000}"/>
+    <hyperlink ref="C329" r:id="rId299" xr:uid="{00000000-0004-0000-0000-00002A010000}"/>
+    <hyperlink ref="C330" r:id="rId300" xr:uid="{00000000-0004-0000-0000-00002B010000}"/>
+    <hyperlink ref="C331" r:id="rId301" xr:uid="{00000000-0004-0000-0000-00002C010000}"/>
+    <hyperlink ref="C332" r:id="rId302" xr:uid="{00000000-0004-0000-0000-00002D010000}"/>
+    <hyperlink ref="C333" r:id="rId303" xr:uid="{00000000-0004-0000-0000-00002E010000}"/>
+    <hyperlink ref="C334" r:id="rId304" xr:uid="{00000000-0004-0000-0000-00002F010000}"/>
+    <hyperlink ref="C335" r:id="rId305" xr:uid="{00000000-0004-0000-0000-000030010000}"/>
+    <hyperlink ref="C336" r:id="rId306" xr:uid="{00000000-0004-0000-0000-000031010000}"/>
+    <hyperlink ref="C337" r:id="rId307" xr:uid="{00000000-0004-0000-0000-000032010000}"/>
+    <hyperlink ref="C338" r:id="rId308" xr:uid="{00000000-0004-0000-0000-000033010000}"/>
+    <hyperlink ref="C339" r:id="rId309" xr:uid="{00000000-0004-0000-0000-000034010000}"/>
+    <hyperlink ref="C340" r:id="rId310" xr:uid="{00000000-0004-0000-0000-000035010000}"/>
+    <hyperlink ref="C341" r:id="rId311" xr:uid="{00000000-0004-0000-0000-000036010000}"/>
+    <hyperlink ref="C342" r:id="rId312" xr:uid="{00000000-0004-0000-0000-000037010000}"/>
+    <hyperlink ref="C343" r:id="rId313" xr:uid="{00000000-0004-0000-0000-000038010000}"/>
+    <hyperlink ref="C344" r:id="rId314" xr:uid="{00000000-0004-0000-0000-000039010000}"/>
+    <hyperlink ref="C345" r:id="rId315" xr:uid="{00000000-0004-0000-0000-00003A010000}"/>
+    <hyperlink ref="C346" r:id="rId316" xr:uid="{00000000-0004-0000-0000-00003B010000}"/>
+    <hyperlink ref="C347" r:id="rId317" xr:uid="{00000000-0004-0000-0000-00003C010000}"/>
+    <hyperlink ref="C348" r:id="rId318" xr:uid="{00000000-0004-0000-0000-00003D010000}"/>
+    <hyperlink ref="C349" r:id="rId319" xr:uid="{00000000-0004-0000-0000-00003E010000}"/>
     <hyperlink ref="C27" r:id="rId320" xr:uid="{00000000-0004-0000-0000-00003F010000}"/>
     <hyperlink ref="C28" r:id="rId321" xr:uid="{00000000-0004-0000-0000-000040010000}"/>
-    <hyperlink ref="C349" r:id="rId322" xr:uid="{00000000-0004-0000-0000-000041010000}"/>
-    <hyperlink ref="C350" r:id="rId323" xr:uid="{00000000-0004-0000-0000-000042010000}"/>
-    <hyperlink ref="C809" r:id="rId324" xr:uid="{00000000-0004-0000-0000-000043010000}"/>
-    <hyperlink ref="C351" r:id="rId325" xr:uid="{00000000-0004-0000-0000-000044010000}"/>
-    <hyperlink ref="C352" r:id="rId326" xr:uid="{00000000-0004-0000-0000-000045010000}"/>
+    <hyperlink ref="C350" r:id="rId322" xr:uid="{00000000-0004-0000-0000-000041010000}"/>
+    <hyperlink ref="C351" r:id="rId323" xr:uid="{00000000-0004-0000-0000-000042010000}"/>
+    <hyperlink ref="C352" r:id="rId324" xr:uid="{00000000-0004-0000-0000-000043010000}"/>
+    <hyperlink ref="C353" r:id="rId325" xr:uid="{00000000-0004-0000-0000-000044010000}"/>
+    <hyperlink ref="C354" r:id="rId326" xr:uid="{00000000-0004-0000-0000-000045010000}"/>
     <hyperlink ref="C29" r:id="rId327" xr:uid="{00000000-0004-0000-0000-000046010000}"/>
-    <hyperlink ref="C353" r:id="rId328" xr:uid="{00000000-0004-0000-0000-000047010000}"/>
-    <hyperlink ref="C354" r:id="rId329" xr:uid="{00000000-0004-0000-0000-000048010000}"/>
-    <hyperlink ref="C355" r:id="rId330" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
-    <hyperlink ref="C356" r:id="rId331" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
-    <hyperlink ref="C357" r:id="rId332" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
-    <hyperlink ref="C358" r:id="rId333" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
-    <hyperlink ref="C359" r:id="rId334" xr:uid="{00000000-0004-0000-0000-00004D010000}"/>
-    <hyperlink ref="C360" r:id="rId335" xr:uid="{00000000-0004-0000-0000-00004E010000}"/>
-    <hyperlink ref="C361" r:id="rId336" xr:uid="{00000000-0004-0000-0000-00004F010000}"/>
-    <hyperlink ref="C362" r:id="rId337" xr:uid="{00000000-0004-0000-0000-000050010000}"/>
-    <hyperlink ref="C363" r:id="rId338" xr:uid="{00000000-0004-0000-0000-000051010000}"/>
-    <hyperlink ref="C364" r:id="rId339" xr:uid="{00000000-0004-0000-0000-000052010000}"/>
-    <hyperlink ref="C365" r:id="rId340" xr:uid="{00000000-0004-0000-0000-000053010000}"/>
-    <hyperlink ref="C366" r:id="rId341" xr:uid="{00000000-0004-0000-0000-000054010000}"/>
-    <hyperlink ref="C367" r:id="rId342" xr:uid="{00000000-0004-0000-0000-000055010000}"/>
-    <hyperlink ref="C368" r:id="rId343" xr:uid="{00000000-0004-0000-0000-000056010000}"/>
-    <hyperlink ref="C369" r:id="rId344" xr:uid="{00000000-0004-0000-0000-000057010000}"/>
-    <hyperlink ref="C810" r:id="rId345" xr:uid="{00000000-0004-0000-0000-000058010000}"/>
-    <hyperlink ref="C370" r:id="rId346" xr:uid="{00000000-0004-0000-0000-000059010000}"/>
-    <hyperlink ref="C371" r:id="rId347" xr:uid="{00000000-0004-0000-0000-00005A010000}"/>
-    <hyperlink ref="C372" r:id="rId348" xr:uid="{00000000-0004-0000-0000-00005B010000}"/>
-    <hyperlink ref="C373" r:id="rId349" xr:uid="{00000000-0004-0000-0000-00005C010000}"/>
-    <hyperlink ref="C374" r:id="rId350" xr:uid="{00000000-0004-0000-0000-00005D010000}"/>
-    <hyperlink ref="C375" r:id="rId351" xr:uid="{00000000-0004-0000-0000-00005E010000}"/>
-    <hyperlink ref="C376" r:id="rId352" xr:uid="{00000000-0004-0000-0000-00005F010000}"/>
-    <hyperlink ref="C377" r:id="rId353" xr:uid="{00000000-0004-0000-0000-000060010000}"/>
-    <hyperlink ref="C378" r:id="rId354" xr:uid="{00000000-0004-0000-0000-000061010000}"/>
-    <hyperlink ref="C379" r:id="rId355" xr:uid="{00000000-0004-0000-0000-000062010000}"/>
-    <hyperlink ref="C380" r:id="rId356" xr:uid="{00000000-0004-0000-0000-000063010000}"/>
-    <hyperlink ref="C381" r:id="rId357" xr:uid="{00000000-0004-0000-0000-000064010000}"/>
-    <hyperlink ref="C382" r:id="rId358" xr:uid="{00000000-0004-0000-0000-000065010000}"/>
-    <hyperlink ref="C383" r:id="rId359" xr:uid="{00000000-0004-0000-0000-000066010000}"/>
-    <hyperlink ref="C384" r:id="rId360" xr:uid="{00000000-0004-0000-0000-000067010000}"/>
-    <hyperlink ref="C385" r:id="rId361" xr:uid="{00000000-0004-0000-0000-000068010000}"/>
-    <hyperlink ref="C386" r:id="rId362" xr:uid="{00000000-0004-0000-0000-000069010000}"/>
-    <hyperlink ref="C387" r:id="rId363" xr:uid="{00000000-0004-0000-0000-00006A010000}"/>
-    <hyperlink ref="C388" r:id="rId364" xr:uid="{00000000-0004-0000-0000-00006B010000}"/>
-    <hyperlink ref="C389" r:id="rId365" xr:uid="{00000000-0004-0000-0000-00006C010000}"/>
-    <hyperlink ref="C390" r:id="rId366" xr:uid="{00000000-0004-0000-0000-00006D010000}"/>
-    <hyperlink ref="C391" r:id="rId367" xr:uid="{00000000-0004-0000-0000-00006E010000}"/>
-    <hyperlink ref="C392" r:id="rId368" xr:uid="{00000000-0004-0000-0000-00006F010000}"/>
-    <hyperlink ref="C393" r:id="rId369" xr:uid="{00000000-0004-0000-0000-000070010000}"/>
-    <hyperlink ref="C394" r:id="rId370" xr:uid="{00000000-0004-0000-0000-000071010000}"/>
-    <hyperlink ref="C395" r:id="rId371" xr:uid="{00000000-0004-0000-0000-000072010000}"/>
-    <hyperlink ref="C396" r:id="rId372" xr:uid="{00000000-0004-0000-0000-000073010000}"/>
-    <hyperlink ref="C397" r:id="rId373" xr:uid="{00000000-0004-0000-0000-000074010000}"/>
-    <hyperlink ref="C398" r:id="rId374" xr:uid="{00000000-0004-0000-0000-000075010000}"/>
-    <hyperlink ref="C399" r:id="rId375" xr:uid="{00000000-0004-0000-0000-000076010000}"/>
-    <hyperlink ref="C400" r:id="rId376" xr:uid="{00000000-0004-0000-0000-000077010000}"/>
-    <hyperlink ref="C401" r:id="rId377" xr:uid="{00000000-0004-0000-0000-000078010000}"/>
-    <hyperlink ref="C402" r:id="rId378" xr:uid="{00000000-0004-0000-0000-000079010000}"/>
-    <hyperlink ref="C403" r:id="rId379" xr:uid="{00000000-0004-0000-0000-00007A010000}"/>
-    <hyperlink ref="C404" r:id="rId380" xr:uid="{00000000-0004-0000-0000-00007B010000}"/>
-    <hyperlink ref="C405" r:id="rId381" xr:uid="{00000000-0004-0000-0000-00007C010000}"/>
-    <hyperlink ref="C406" r:id="rId382" xr:uid="{00000000-0004-0000-0000-00007D010000}"/>
-    <hyperlink ref="C407" r:id="rId383" xr:uid="{00000000-0004-0000-0000-00007E010000}"/>
-    <hyperlink ref="C408" r:id="rId384" xr:uid="{00000000-0004-0000-0000-00007F010000}"/>
-    <hyperlink ref="C409" r:id="rId385" xr:uid="{00000000-0004-0000-0000-000080010000}"/>
-    <hyperlink ref="C410" r:id="rId386" xr:uid="{00000000-0004-0000-0000-000081010000}"/>
-    <hyperlink ref="C411" r:id="rId387" xr:uid="{00000000-0004-0000-0000-000082010000}"/>
-    <hyperlink ref="C412" r:id="rId388" xr:uid="{00000000-0004-0000-0000-000083010000}"/>
-    <hyperlink ref="C413" r:id="rId389" xr:uid="{00000000-0004-0000-0000-000084010000}"/>
-    <hyperlink ref="C414" r:id="rId390" xr:uid="{00000000-0004-0000-0000-000085010000}"/>
-    <hyperlink ref="C415" r:id="rId391" xr:uid="{00000000-0004-0000-0000-000086010000}"/>
-    <hyperlink ref="C416" r:id="rId392" xr:uid="{00000000-0004-0000-0000-000087010000}"/>
-    <hyperlink ref="C417" r:id="rId393" xr:uid="{00000000-0004-0000-0000-000088010000}"/>
-    <hyperlink ref="C418" r:id="rId394" xr:uid="{00000000-0004-0000-0000-000089010000}"/>
-    <hyperlink ref="C419" r:id="rId395" xr:uid="{00000000-0004-0000-0000-00008A010000}"/>
-    <hyperlink ref="C420" r:id="rId396" xr:uid="{00000000-0004-0000-0000-00008B010000}"/>
-    <hyperlink ref="C421" r:id="rId397" xr:uid="{00000000-0004-0000-0000-00008C010000}"/>
-    <hyperlink ref="C422" r:id="rId398" xr:uid="{00000000-0004-0000-0000-00008D010000}"/>
-    <hyperlink ref="C423" r:id="rId399" xr:uid="{00000000-0004-0000-0000-00008E010000}"/>
-    <hyperlink ref="C424" r:id="rId400" xr:uid="{00000000-0004-0000-0000-00008F010000}"/>
-    <hyperlink ref="C425" r:id="rId401" xr:uid="{00000000-0004-0000-0000-000090010000}"/>
-    <hyperlink ref="C426" r:id="rId402" xr:uid="{00000000-0004-0000-0000-000091010000}"/>
-    <hyperlink ref="C427" r:id="rId403" xr:uid="{00000000-0004-0000-0000-000092010000}"/>
-    <hyperlink ref="C428" r:id="rId404" xr:uid="{00000000-0004-0000-0000-000093010000}"/>
-    <hyperlink ref="C429" r:id="rId405" xr:uid="{00000000-0004-0000-0000-000094010000}"/>
-    <hyperlink ref="C430" r:id="rId406" xr:uid="{00000000-0004-0000-0000-000095010000}"/>
-    <hyperlink ref="C431" r:id="rId407" xr:uid="{00000000-0004-0000-0000-000096010000}"/>
-    <hyperlink ref="C432" r:id="rId408" xr:uid="{00000000-0004-0000-0000-000097010000}"/>
-    <hyperlink ref="C433" r:id="rId409" xr:uid="{00000000-0004-0000-0000-000098010000}"/>
-    <hyperlink ref="C434" r:id="rId410" xr:uid="{00000000-0004-0000-0000-000099010000}"/>
-    <hyperlink ref="C435" r:id="rId411" xr:uid="{00000000-0004-0000-0000-00009A010000}"/>
-    <hyperlink ref="C436" r:id="rId412" xr:uid="{00000000-0004-0000-0000-00009B010000}"/>
-    <hyperlink ref="C437" r:id="rId413" xr:uid="{00000000-0004-0000-0000-00009C010000}"/>
-    <hyperlink ref="C438" r:id="rId414" xr:uid="{00000000-0004-0000-0000-00009D010000}"/>
-    <hyperlink ref="C439" r:id="rId415" xr:uid="{00000000-0004-0000-0000-00009E010000}"/>
-    <hyperlink ref="C30" r:id="rId416" xr:uid="{00000000-0004-0000-0000-00009F010000}"/>
-    <hyperlink ref="C440" r:id="rId417" xr:uid="{00000000-0004-0000-0000-0000A0010000}"/>
-    <hyperlink ref="C441" r:id="rId418" xr:uid="{00000000-0004-0000-0000-0000A1010000}"/>
-    <hyperlink ref="C442" r:id="rId419" xr:uid="{00000000-0004-0000-0000-0000A2010000}"/>
-    <hyperlink ref="C443" r:id="rId420" xr:uid="{00000000-0004-0000-0000-0000A3010000}"/>
-    <hyperlink ref="C444" r:id="rId421" xr:uid="{00000000-0004-0000-0000-0000A4010000}"/>
-    <hyperlink ref="C445" r:id="rId422" xr:uid="{00000000-0004-0000-0000-0000A5010000}"/>
-    <hyperlink ref="C31" r:id="rId423" xr:uid="{00000000-0004-0000-0000-0000A6010000}"/>
-    <hyperlink ref="C446" r:id="rId424" xr:uid="{00000000-0004-0000-0000-0000A7010000}"/>
-    <hyperlink ref="C447" r:id="rId425" xr:uid="{00000000-0004-0000-0000-0000A8010000}"/>
-    <hyperlink ref="C448" r:id="rId426" xr:uid="{00000000-0004-0000-0000-0000A9010000}"/>
-    <hyperlink ref="C449" r:id="rId427" xr:uid="{00000000-0004-0000-0000-0000AA010000}"/>
-    <hyperlink ref="C450" r:id="rId428" xr:uid="{00000000-0004-0000-0000-0000AB010000}"/>
-    <hyperlink ref="C451" r:id="rId429" xr:uid="{00000000-0004-0000-0000-0000AC010000}"/>
-    <hyperlink ref="C452" r:id="rId430" xr:uid="{00000000-0004-0000-0000-0000AD010000}"/>
-    <hyperlink ref="C453" r:id="rId431" xr:uid="{00000000-0004-0000-0000-0000AE010000}"/>
-    <hyperlink ref="C454" r:id="rId432" xr:uid="{00000000-0004-0000-0000-0000AF010000}"/>
-    <hyperlink ref="C455" r:id="rId433" xr:uid="{00000000-0004-0000-0000-0000B0010000}"/>
-    <hyperlink ref="C456" r:id="rId434" xr:uid="{00000000-0004-0000-0000-0000B1010000}"/>
-    <hyperlink ref="C457" r:id="rId435" xr:uid="{00000000-0004-0000-0000-0000B2010000}"/>
-    <hyperlink ref="C458" r:id="rId436" xr:uid="{00000000-0004-0000-0000-0000B3010000}"/>
-    <hyperlink ref="C459" r:id="rId437" xr:uid="{00000000-0004-0000-0000-0000B4010000}"/>
-    <hyperlink ref="C460" r:id="rId438" xr:uid="{00000000-0004-0000-0000-0000B5010000}"/>
-    <hyperlink ref="C461" r:id="rId439" xr:uid="{00000000-0004-0000-0000-0000B6010000}"/>
-    <hyperlink ref="C462" r:id="rId440" xr:uid="{00000000-0004-0000-0000-0000B7010000}"/>
-    <hyperlink ref="C463" r:id="rId441" xr:uid="{00000000-0004-0000-0000-0000B8010000}"/>
-    <hyperlink ref="C464" r:id="rId442" xr:uid="{00000000-0004-0000-0000-0000B9010000}"/>
-    <hyperlink ref="C32" r:id="rId443" xr:uid="{00000000-0004-0000-0000-0000BA010000}"/>
-    <hyperlink ref="C465" r:id="rId444" xr:uid="{00000000-0004-0000-0000-0000BB010000}"/>
-    <hyperlink ref="C466" r:id="rId445" xr:uid="{00000000-0004-0000-0000-0000BC010000}"/>
-    <hyperlink ref="C467" r:id="rId446" xr:uid="{00000000-0004-0000-0000-0000BD010000}"/>
-    <hyperlink ref="C468" r:id="rId447" xr:uid="{00000000-0004-0000-0000-0000BE010000}"/>
-    <hyperlink ref="C469" r:id="rId448" xr:uid="{00000000-0004-0000-0000-0000BF010000}"/>
-    <hyperlink ref="C470" r:id="rId449" xr:uid="{00000000-0004-0000-0000-0000C0010000}"/>
-    <hyperlink ref="C33" r:id="rId450" xr:uid="{00000000-0004-0000-0000-0000C1010000}"/>
-    <hyperlink ref="C471" r:id="rId451" xr:uid="{00000000-0004-0000-0000-0000C2010000}"/>
-    <hyperlink ref="C472" r:id="rId452" xr:uid="{00000000-0004-0000-0000-0000C3010000}"/>
-    <hyperlink ref="C473" r:id="rId453" xr:uid="{00000000-0004-0000-0000-0000C4010000}"/>
-    <hyperlink ref="C474" r:id="rId454" xr:uid="{00000000-0004-0000-0000-0000C5010000}"/>
-    <hyperlink ref="C475" r:id="rId455" xr:uid="{00000000-0004-0000-0000-0000C6010000}"/>
-    <hyperlink ref="C476" r:id="rId456" xr:uid="{00000000-0004-0000-0000-0000C7010000}"/>
-    <hyperlink ref="C477" r:id="rId457" xr:uid="{00000000-0004-0000-0000-0000C8010000}"/>
-    <hyperlink ref="C478" r:id="rId458" xr:uid="{00000000-0004-0000-0000-0000C9010000}"/>
-    <hyperlink ref="C479" r:id="rId459" xr:uid="{00000000-0004-0000-0000-0000CA010000}"/>
-    <hyperlink ref="C480" r:id="rId460" xr:uid="{00000000-0004-0000-0000-0000CB010000}"/>
-    <hyperlink ref="C481" r:id="rId461" xr:uid="{00000000-0004-0000-0000-0000CC010000}"/>
-    <hyperlink ref="C34" r:id="rId462" xr:uid="{00000000-0004-0000-0000-0000CD010000}"/>
-    <hyperlink ref="C482" r:id="rId463" xr:uid="{00000000-0004-0000-0000-0000CE010000}"/>
-    <hyperlink ref="C483" r:id="rId464" xr:uid="{00000000-0004-0000-0000-0000CF010000}"/>
-    <hyperlink ref="C484" r:id="rId465" xr:uid="{00000000-0004-0000-0000-0000D0010000}"/>
-    <hyperlink ref="C485" r:id="rId466" xr:uid="{00000000-0004-0000-0000-0000D1010000}"/>
-    <hyperlink ref="C486" r:id="rId467" xr:uid="{00000000-0004-0000-0000-0000D2010000}"/>
-    <hyperlink ref="C487" r:id="rId468" xr:uid="{00000000-0004-0000-0000-0000D3010000}"/>
-    <hyperlink ref="C488" r:id="rId469" xr:uid="{00000000-0004-0000-0000-0000D4010000}"/>
-    <hyperlink ref="C35" r:id="rId470" xr:uid="{00000000-0004-0000-0000-0000D5010000}"/>
-    <hyperlink ref="C489" r:id="rId471" xr:uid="{00000000-0004-0000-0000-0000D6010000}"/>
-    <hyperlink ref="C490" r:id="rId472" xr:uid="{00000000-0004-0000-0000-0000D7010000}"/>
-    <hyperlink ref="C491" r:id="rId473" xr:uid="{00000000-0004-0000-0000-0000D8010000}"/>
-    <hyperlink ref="C492" r:id="rId474" xr:uid="{00000000-0004-0000-0000-0000D9010000}"/>
-    <hyperlink ref="C493" r:id="rId475" xr:uid="{00000000-0004-0000-0000-0000DA010000}"/>
-    <hyperlink ref="C494" r:id="rId476" xr:uid="{00000000-0004-0000-0000-0000DB010000}"/>
-    <hyperlink ref="C495" r:id="rId477" xr:uid="{00000000-0004-0000-0000-0000DC010000}"/>
-    <hyperlink ref="C496" r:id="rId478" xr:uid="{00000000-0004-0000-0000-0000DD010000}"/>
-    <hyperlink ref="C497" r:id="rId479" xr:uid="{00000000-0004-0000-0000-0000DE010000}"/>
-    <hyperlink ref="C498" r:id="rId480" xr:uid="{00000000-0004-0000-0000-0000DF010000}"/>
-    <hyperlink ref="C499" r:id="rId481" xr:uid="{00000000-0004-0000-0000-0000E0010000}"/>
-    <hyperlink ref="C500" r:id="rId482" xr:uid="{00000000-0004-0000-0000-0000E1010000}"/>
-    <hyperlink ref="C501" r:id="rId483" xr:uid="{00000000-0004-0000-0000-0000E2010000}"/>
-    <hyperlink ref="C502" r:id="rId484" xr:uid="{00000000-0004-0000-0000-0000E3010000}"/>
-    <hyperlink ref="C503" r:id="rId485" xr:uid="{00000000-0004-0000-0000-0000E4010000}"/>
-    <hyperlink ref="C504" r:id="rId486" xr:uid="{00000000-0004-0000-0000-0000E5010000}"/>
-    <hyperlink ref="C505" r:id="rId487" xr:uid="{00000000-0004-0000-0000-0000E6010000}"/>
-    <hyperlink ref="C506" r:id="rId488" xr:uid="{00000000-0004-0000-0000-0000E7010000}"/>
-    <hyperlink ref="C507" r:id="rId489" xr:uid="{00000000-0004-0000-0000-0000E8010000}"/>
-    <hyperlink ref="C508" r:id="rId490" xr:uid="{00000000-0004-0000-0000-0000E9010000}"/>
-    <hyperlink ref="C509" r:id="rId491" xr:uid="{00000000-0004-0000-0000-0000EA010000}"/>
-    <hyperlink ref="C510" r:id="rId492" xr:uid="{00000000-0004-0000-0000-0000EB010000}"/>
-    <hyperlink ref="C511" r:id="rId493" xr:uid="{00000000-0004-0000-0000-0000EC010000}"/>
-    <hyperlink ref="C512" r:id="rId494" xr:uid="{00000000-0004-0000-0000-0000ED010000}"/>
-    <hyperlink ref="C513" r:id="rId495" xr:uid="{00000000-0004-0000-0000-0000EE010000}"/>
-    <hyperlink ref="C514" r:id="rId496" xr:uid="{00000000-0004-0000-0000-0000EF010000}"/>
-    <hyperlink ref="C515" r:id="rId497" xr:uid="{00000000-0004-0000-0000-0000F0010000}"/>
-    <hyperlink ref="C516" r:id="rId498" xr:uid="{00000000-0004-0000-0000-0000F1010000}"/>
-    <hyperlink ref="C517" r:id="rId499" xr:uid="{00000000-0004-0000-0000-0000F2010000}"/>
-    <hyperlink ref="C518" r:id="rId500" xr:uid="{00000000-0004-0000-0000-0000F3010000}"/>
-    <hyperlink ref="C519" r:id="rId501" xr:uid="{00000000-0004-0000-0000-0000F4010000}"/>
+    <hyperlink ref="C355" r:id="rId328" xr:uid="{00000000-0004-0000-0000-000047010000}"/>
+    <hyperlink ref="C356" r:id="rId329" xr:uid="{00000000-0004-0000-0000-000048010000}"/>
+    <hyperlink ref="C357" r:id="rId330" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
+    <hyperlink ref="C358" r:id="rId331" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
+    <hyperlink ref="C359" r:id="rId332" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
+    <hyperlink ref="C360" r:id="rId333" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
+    <hyperlink ref="C361" r:id="rId334" xr:uid="{00000000-0004-0000-0000-00004D010000}"/>
+    <hyperlink ref="C362" r:id="rId335" xr:uid="{00000000-0004-0000-0000-00004E010000}"/>
+    <hyperlink ref="C363" r:id="rId336" xr:uid="{00000000-0004-0000-0000-00004F010000}"/>
+    <hyperlink ref="C364" r:id="rId337" xr:uid="{00000000-0004-0000-0000-000050010000}"/>
+    <hyperlink ref="C365" r:id="rId338" xr:uid="{00000000-0004-0000-0000-000051010000}"/>
+    <hyperlink ref="C366" r:id="rId339" xr:uid="{00000000-0004-0000-0000-000052010000}"/>
+    <hyperlink ref="C367" r:id="rId340" xr:uid="{00000000-0004-0000-0000-000053010000}"/>
+    <hyperlink ref="C368" r:id="rId341" xr:uid="{00000000-0004-0000-0000-000054010000}"/>
+    <hyperlink ref="C369" r:id="rId342" xr:uid="{00000000-0004-0000-0000-000055010000}"/>
+    <hyperlink ref="C370" r:id="rId343" xr:uid="{00000000-0004-0000-0000-000056010000}"/>
+    <hyperlink ref="C371" r:id="rId344" xr:uid="{00000000-0004-0000-0000-000057010000}"/>
+    <hyperlink ref="C372" r:id="rId345" xr:uid="{00000000-0004-0000-0000-000058010000}"/>
+    <hyperlink ref="C373" r:id="rId346" xr:uid="{00000000-0004-0000-0000-000059010000}"/>
+    <hyperlink ref="C374" r:id="rId347" xr:uid="{00000000-0004-0000-0000-00005A010000}"/>
+    <hyperlink ref="C375" r:id="rId348" xr:uid="{00000000-0004-0000-0000-00005B010000}"/>
+    <hyperlink ref="C376" r:id="rId349" xr:uid="{00000000-0004-0000-0000-00005C010000}"/>
+    <hyperlink ref="C377" r:id="rId350" xr:uid="{00000000-0004-0000-0000-00005D010000}"/>
+    <hyperlink ref="C378" r:id="rId351" xr:uid="{00000000-0004-0000-0000-00005E010000}"/>
+    <hyperlink ref="C379" r:id="rId352" xr:uid="{00000000-0004-0000-0000-00005F010000}"/>
+    <hyperlink ref="C380" r:id="rId353" xr:uid="{00000000-0004-0000-0000-000060010000}"/>
+    <hyperlink ref="C381" r:id="rId354" xr:uid="{00000000-0004-0000-0000-000061010000}"/>
+    <hyperlink ref="C382" r:id="rId355" xr:uid="{00000000-0004-0000-0000-000062010000}"/>
+    <hyperlink ref="C383" r:id="rId356" xr:uid="{00000000-0004-0000-0000-000063010000}"/>
+    <hyperlink ref="C384" r:id="rId357" xr:uid="{00000000-0004-0000-0000-000064010000}"/>
+    <hyperlink ref="C385" r:id="rId358" xr:uid="{00000000-0004-0000-0000-000065010000}"/>
+    <hyperlink ref="C386" r:id="rId359" xr:uid="{00000000-0004-0000-0000-000066010000}"/>
+    <hyperlink ref="C387" r:id="rId360" xr:uid="{00000000-0004-0000-0000-000067010000}"/>
+    <hyperlink ref="C388" r:id="rId361" xr:uid="{00000000-0004-0000-0000-000068010000}"/>
+    <hyperlink ref="C389" r:id="rId362" xr:uid="{00000000-0004-0000-0000-000069010000}"/>
+    <hyperlink ref="C390" r:id="rId363" xr:uid="{00000000-0004-0000-0000-00006A010000}"/>
+    <hyperlink ref="C391" r:id="rId364" xr:uid="{00000000-0004-0000-0000-00006B010000}"/>
+    <hyperlink ref="C392" r:id="rId365" xr:uid="{00000000-0004-0000-0000-00006C010000}"/>
+    <hyperlink ref="C393" r:id="rId366" xr:uid="{00000000-0004-0000-0000-00006D010000}"/>
+    <hyperlink ref="C394" r:id="rId367" xr:uid="{00000000-0004-0000-0000-00006E010000}"/>
+    <hyperlink ref="C395" r:id="rId368" xr:uid="{00000000-0004-0000-0000-00006F010000}"/>
+    <hyperlink ref="C396" r:id="rId369" xr:uid="{00000000-0004-0000-0000-000070010000}"/>
+    <hyperlink ref="C397" r:id="rId370" xr:uid="{00000000-0004-0000-0000-000071010000}"/>
+    <hyperlink ref="C398" r:id="rId371" xr:uid="{00000000-0004-0000-0000-000072010000}"/>
+    <hyperlink ref="C399" r:id="rId372" xr:uid="{00000000-0004-0000-0000-000073010000}"/>
+    <hyperlink ref="C400" r:id="rId373" xr:uid="{00000000-0004-0000-0000-000074010000}"/>
+    <hyperlink ref="C401" r:id="rId374" xr:uid="{00000000-0004-0000-0000-000075010000}"/>
+    <hyperlink ref="C402" r:id="rId375" xr:uid="{00000000-0004-0000-0000-000076010000}"/>
+    <hyperlink ref="C403" r:id="rId376" xr:uid="{00000000-0004-0000-0000-000077010000}"/>
+    <hyperlink ref="C404" r:id="rId377" xr:uid="{00000000-0004-0000-0000-000078010000}"/>
+    <hyperlink ref="C405" r:id="rId378" xr:uid="{00000000-0004-0000-0000-000079010000}"/>
+    <hyperlink ref="C406" r:id="rId379" xr:uid="{00000000-0004-0000-0000-00007A010000}"/>
+    <hyperlink ref="C407" r:id="rId380" xr:uid="{00000000-0004-0000-0000-00007B010000}"/>
+    <hyperlink ref="C408" r:id="rId381" xr:uid="{00000000-0004-0000-0000-00007C010000}"/>
+    <hyperlink ref="C409" r:id="rId382" xr:uid="{00000000-0004-0000-0000-00007D010000}"/>
+    <hyperlink ref="C410" r:id="rId383" xr:uid="{00000000-0004-0000-0000-00007E010000}"/>
+    <hyperlink ref="C411" r:id="rId384" xr:uid="{00000000-0004-0000-0000-00007F010000}"/>
+    <hyperlink ref="C412" r:id="rId385" xr:uid="{00000000-0004-0000-0000-000080010000}"/>
+    <hyperlink ref="C413" r:id="rId386" xr:uid="{00000000-0004-0000-0000-000081010000}"/>
+    <hyperlink ref="C414" r:id="rId387" xr:uid="{00000000-0004-0000-0000-000082010000}"/>
+    <hyperlink ref="C415" r:id="rId388" xr:uid="{00000000-0004-0000-0000-000083010000}"/>
+    <hyperlink ref="C814" r:id="rId389" xr:uid="{00000000-0004-0000-0000-000084010000}"/>
+    <hyperlink ref="C416" r:id="rId390" xr:uid="{00000000-0004-0000-0000-000085010000}"/>
+    <hyperlink ref="C417" r:id="rId391" xr:uid="{00000000-0004-0000-0000-000086010000}"/>
+    <hyperlink ref="C418" r:id="rId392" xr:uid="{00000000-0004-0000-0000-000087010000}"/>
+    <hyperlink ref="C419" r:id="rId393" xr:uid="{00000000-0004-0000-0000-000088010000}"/>
+    <hyperlink ref="C420" r:id="rId394" xr:uid="{00000000-0004-0000-0000-000089010000}"/>
+    <hyperlink ref="C421" r:id="rId395" xr:uid="{00000000-0004-0000-0000-00008A010000}"/>
+    <hyperlink ref="C422" r:id="rId396" xr:uid="{00000000-0004-0000-0000-00008B010000}"/>
+    <hyperlink ref="C423" r:id="rId397" xr:uid="{00000000-0004-0000-0000-00008C010000}"/>
+    <hyperlink ref="C424" r:id="rId398" xr:uid="{00000000-0004-0000-0000-00008D010000}"/>
+    <hyperlink ref="C425" r:id="rId399" xr:uid="{00000000-0004-0000-0000-00008E010000}"/>
+    <hyperlink ref="C426" r:id="rId400" xr:uid="{00000000-0004-0000-0000-00008F010000}"/>
+    <hyperlink ref="C815" r:id="rId401" xr:uid="{00000000-0004-0000-0000-000090010000}"/>
+    <hyperlink ref="C427" r:id="rId402" xr:uid="{00000000-0004-0000-0000-000091010000}"/>
+    <hyperlink ref="C428" r:id="rId403" xr:uid="{00000000-0004-0000-0000-000092010000}"/>
+    <hyperlink ref="C429" r:id="rId404" xr:uid="{00000000-0004-0000-0000-000093010000}"/>
+    <hyperlink ref="C430" r:id="rId405" xr:uid="{00000000-0004-0000-0000-000094010000}"/>
+    <hyperlink ref="C431" r:id="rId406" xr:uid="{00000000-0004-0000-0000-000095010000}"/>
+    <hyperlink ref="C432" r:id="rId407" xr:uid="{00000000-0004-0000-0000-000096010000}"/>
+    <hyperlink ref="C433" r:id="rId408" xr:uid="{00000000-0004-0000-0000-000097010000}"/>
+    <hyperlink ref="C434" r:id="rId409" xr:uid="{00000000-0004-0000-0000-000098010000}"/>
+    <hyperlink ref="C435" r:id="rId410" xr:uid="{00000000-0004-0000-0000-000099010000}"/>
+    <hyperlink ref="C436" r:id="rId411" xr:uid="{00000000-0004-0000-0000-00009A010000}"/>
+    <hyperlink ref="C437" r:id="rId412" xr:uid="{00000000-0004-0000-0000-00009B010000}"/>
+    <hyperlink ref="C438" r:id="rId413" xr:uid="{00000000-0004-0000-0000-00009C010000}"/>
+    <hyperlink ref="C439" r:id="rId414" xr:uid="{00000000-0004-0000-0000-00009D010000}"/>
+    <hyperlink ref="C440" r:id="rId415" xr:uid="{00000000-0004-0000-0000-00009E010000}"/>
+    <hyperlink ref="C441" r:id="rId416" xr:uid="{00000000-0004-0000-0000-00009F010000}"/>
+    <hyperlink ref="C442" r:id="rId417" xr:uid="{00000000-0004-0000-0000-0000A0010000}"/>
+    <hyperlink ref="C30" r:id="rId418" xr:uid="{00000000-0004-0000-0000-0000A1010000}"/>
+    <hyperlink ref="C443" r:id="rId419" xr:uid="{00000000-0004-0000-0000-0000A2010000}"/>
+    <hyperlink ref="C444" r:id="rId420" xr:uid="{00000000-0004-0000-0000-0000A3010000}"/>
+    <hyperlink ref="C445" r:id="rId421" xr:uid="{00000000-0004-0000-0000-0000A4010000}"/>
+    <hyperlink ref="C446" r:id="rId422" xr:uid="{00000000-0004-0000-0000-0000A5010000}"/>
+    <hyperlink ref="C447" r:id="rId423" xr:uid="{00000000-0004-0000-0000-0000A6010000}"/>
+    <hyperlink ref="C448" r:id="rId424" xr:uid="{00000000-0004-0000-0000-0000A7010000}"/>
+    <hyperlink ref="C31" r:id="rId425" xr:uid="{00000000-0004-0000-0000-0000A8010000}"/>
+    <hyperlink ref="C449" r:id="rId426" xr:uid="{00000000-0004-0000-0000-0000A9010000}"/>
+    <hyperlink ref="C450" r:id="rId427" xr:uid="{00000000-0004-0000-0000-0000AA010000}"/>
+    <hyperlink ref="C451" r:id="rId428" xr:uid="{00000000-0004-0000-0000-0000AB010000}"/>
+    <hyperlink ref="C452" r:id="rId429" xr:uid="{00000000-0004-0000-0000-0000AC010000}"/>
+    <hyperlink ref="C453" r:id="rId430" xr:uid="{00000000-0004-0000-0000-0000AD010000}"/>
+    <hyperlink ref="C454" r:id="rId431" xr:uid="{00000000-0004-0000-0000-0000AE010000}"/>
+    <hyperlink ref="C455" r:id="rId432" xr:uid="{00000000-0004-0000-0000-0000AF010000}"/>
+    <hyperlink ref="C456" r:id="rId433" xr:uid="{00000000-0004-0000-0000-0000B0010000}"/>
+    <hyperlink ref="C457" r:id="rId434" xr:uid="{00000000-0004-0000-0000-0000B1010000}"/>
+    <hyperlink ref="C458" r:id="rId435" xr:uid="{00000000-0004-0000-0000-0000B2010000}"/>
+    <hyperlink ref="C459" r:id="rId436" xr:uid="{00000000-0004-0000-0000-0000B3010000}"/>
+    <hyperlink ref="C460" r:id="rId437" xr:uid="{00000000-0004-0000-0000-0000B4010000}"/>
+    <hyperlink ref="C461" r:id="rId438" xr:uid="{00000000-0004-0000-0000-0000B5010000}"/>
+    <hyperlink ref="C462" r:id="rId439" xr:uid="{00000000-0004-0000-0000-0000B6010000}"/>
+    <hyperlink ref="C463" r:id="rId440" xr:uid="{00000000-0004-0000-0000-0000B7010000}"/>
+    <hyperlink ref="C464" r:id="rId441" xr:uid="{00000000-0004-0000-0000-0000B8010000}"/>
+    <hyperlink ref="C465" r:id="rId442" xr:uid="{00000000-0004-0000-0000-0000B9010000}"/>
+    <hyperlink ref="C466" r:id="rId443" xr:uid="{00000000-0004-0000-0000-0000BA010000}"/>
+    <hyperlink ref="C467" r:id="rId444" xr:uid="{00000000-0004-0000-0000-0000BB010000}"/>
+    <hyperlink ref="C32" r:id="rId445" xr:uid="{00000000-0004-0000-0000-0000BC010000}"/>
+    <hyperlink ref="C468" r:id="rId446" xr:uid="{00000000-0004-0000-0000-0000BD010000}"/>
+    <hyperlink ref="C469" r:id="rId447" xr:uid="{00000000-0004-0000-0000-0000BE010000}"/>
+    <hyperlink ref="C470" r:id="rId448" xr:uid="{00000000-0004-0000-0000-0000BF010000}"/>
+    <hyperlink ref="C471" r:id="rId449" xr:uid="{00000000-0004-0000-0000-0000C0010000}"/>
+    <hyperlink ref="C472" r:id="rId450" xr:uid="{00000000-0004-0000-0000-0000C1010000}"/>
+    <hyperlink ref="C473" r:id="rId451" xr:uid="{00000000-0004-0000-0000-0000C2010000}"/>
+    <hyperlink ref="C33" r:id="rId452" xr:uid="{00000000-0004-0000-0000-0000C3010000}"/>
+    <hyperlink ref="C474" r:id="rId453" xr:uid="{00000000-0004-0000-0000-0000C4010000}"/>
+    <hyperlink ref="C475" r:id="rId454" xr:uid="{00000000-0004-0000-0000-0000C5010000}"/>
+    <hyperlink ref="C476" r:id="rId455" xr:uid="{00000000-0004-0000-0000-0000C6010000}"/>
+    <hyperlink ref="C477" r:id="rId456" xr:uid="{00000000-0004-0000-0000-0000C7010000}"/>
+    <hyperlink ref="C478" r:id="rId457" xr:uid="{00000000-0004-0000-0000-0000C8010000}"/>
+    <hyperlink ref="C479" r:id="rId458" xr:uid="{00000000-0004-0000-0000-0000C9010000}"/>
+    <hyperlink ref="C480" r:id="rId459" xr:uid="{00000000-0004-0000-0000-0000CA010000}"/>
+    <hyperlink ref="C481" r:id="rId460" xr:uid="{00000000-0004-0000-0000-0000CB010000}"/>
+    <hyperlink ref="C482" r:id="rId461" xr:uid="{00000000-0004-0000-0000-0000CC010000}"/>
+    <hyperlink ref="C483" r:id="rId462" xr:uid="{00000000-0004-0000-0000-0000CD010000}"/>
+    <hyperlink ref="C484" r:id="rId463" xr:uid="{00000000-0004-0000-0000-0000CE010000}"/>
+    <hyperlink ref="C34" r:id="rId464" xr:uid="{00000000-0004-0000-0000-0000CF010000}"/>
+    <hyperlink ref="C485" r:id="rId465" xr:uid="{00000000-0004-0000-0000-0000D0010000}"/>
+    <hyperlink ref="C486" r:id="rId466" xr:uid="{00000000-0004-0000-0000-0000D1010000}"/>
+    <hyperlink ref="C487" r:id="rId467" xr:uid="{00000000-0004-0000-0000-0000D2010000}"/>
+    <hyperlink ref="C488" r:id="rId468" xr:uid="{00000000-0004-0000-0000-0000D3010000}"/>
+    <hyperlink ref="C489" r:id="rId469" xr:uid="{00000000-0004-0000-0000-0000D4010000}"/>
+    <hyperlink ref="C490" r:id="rId470" xr:uid="{00000000-0004-0000-0000-0000D5010000}"/>
+    <hyperlink ref="C491" r:id="rId471" xr:uid="{00000000-0004-0000-0000-0000D6010000}"/>
+    <hyperlink ref="C35" r:id="rId472" xr:uid="{00000000-0004-0000-0000-0000D7010000}"/>
+    <hyperlink ref="C492" r:id="rId473" xr:uid="{00000000-0004-0000-0000-0000D8010000}"/>
+    <hyperlink ref="C493" r:id="rId474" xr:uid="{00000000-0004-0000-0000-0000D9010000}"/>
+    <hyperlink ref="C494" r:id="rId475" xr:uid="{00000000-0004-0000-0000-0000DA010000}"/>
+    <hyperlink ref="C495" r:id="rId476" xr:uid="{00000000-0004-0000-0000-0000DB010000}"/>
+    <hyperlink ref="C496" r:id="rId477" xr:uid="{00000000-0004-0000-0000-0000DC010000}"/>
+    <hyperlink ref="C497" r:id="rId478" xr:uid="{00000000-0004-0000-0000-0000DD010000}"/>
+    <hyperlink ref="C498" r:id="rId479" xr:uid="{00000000-0004-0000-0000-0000DE010000}"/>
+    <hyperlink ref="C499" r:id="rId480" xr:uid="{00000000-0004-0000-0000-0000DF010000}"/>
+    <hyperlink ref="C500" r:id="rId481" xr:uid="{00000000-0004-0000-0000-0000E0010000}"/>
+    <hyperlink ref="C501" r:id="rId482" xr:uid="{00000000-0004-0000-0000-0000E1010000}"/>
+    <hyperlink ref="C502" r:id="rId483" xr:uid="{00000000-0004-0000-0000-0000E2010000}"/>
+    <hyperlink ref="C503" r:id="rId484" xr:uid="{00000000-0004-0000-0000-0000E3010000}"/>
+    <hyperlink ref="C504" r:id="rId485" xr:uid="{00000000-0004-0000-0000-0000E4010000}"/>
+    <hyperlink ref="C505" r:id="rId486" xr:uid="{00000000-0004-0000-0000-0000E5010000}"/>
+    <hyperlink ref="C506" r:id="rId487" xr:uid="{00000000-0004-0000-0000-0000E6010000}"/>
+    <hyperlink ref="C507" r:id="rId488" xr:uid="{00000000-0004-0000-0000-0000E7010000}"/>
+    <hyperlink ref="C508" r:id="rId489" xr:uid="{00000000-0004-0000-0000-0000E8010000}"/>
+    <hyperlink ref="C509" r:id="rId490" xr:uid="{00000000-0004-0000-0000-0000E9010000}"/>
+    <hyperlink ref="C510" r:id="rId491" xr:uid="{00000000-0004-0000-0000-0000EA010000}"/>
+    <hyperlink ref="C511" r:id="rId492" xr:uid="{00000000-0004-0000-0000-0000EB010000}"/>
+    <hyperlink ref="C512" r:id="rId493" xr:uid="{00000000-0004-0000-0000-0000EC010000}"/>
+    <hyperlink ref="C513" r:id="rId494" xr:uid="{00000000-0004-0000-0000-0000ED010000}"/>
+    <hyperlink ref="C514" r:id="rId495" xr:uid="{00000000-0004-0000-0000-0000EE010000}"/>
+    <hyperlink ref="C515" r:id="rId496" xr:uid="{00000000-0004-0000-0000-0000EF010000}"/>
+    <hyperlink ref="C516" r:id="rId497" xr:uid="{00000000-0004-0000-0000-0000F0010000}"/>
+    <hyperlink ref="C517" r:id="rId498" xr:uid="{00000000-0004-0000-0000-0000F1010000}"/>
+    <hyperlink ref="C518" r:id="rId499" xr:uid="{00000000-0004-0000-0000-0000F2010000}"/>
+    <hyperlink ref="C519" r:id="rId500" xr:uid="{00000000-0004-0000-0000-0000F3010000}"/>
+    <hyperlink ref="C816" r:id="rId501" xr:uid="{00000000-0004-0000-0000-0000F4010000}"/>
     <hyperlink ref="C520" r:id="rId502" xr:uid="{00000000-0004-0000-0000-0000F5010000}"/>
     <hyperlink ref="C521" r:id="rId503" xr:uid="{00000000-0004-0000-0000-0000F6010000}"/>
     <hyperlink ref="C522" r:id="rId504" xr:uid="{00000000-0004-0000-0000-0000F7010000}"/>
@@ -17241,10 +17341,10 @@
     <hyperlink ref="C529" r:id="rId511" xr:uid="{00000000-0004-0000-0000-0000FE010000}"/>
     <hyperlink ref="C530" r:id="rId512" xr:uid="{00000000-0004-0000-0000-0000FF010000}"/>
     <hyperlink ref="C531" r:id="rId513" xr:uid="{00000000-0004-0000-0000-000000020000}"/>
-    <hyperlink ref="C36" r:id="rId514" xr:uid="{00000000-0004-0000-0000-000001020000}"/>
-    <hyperlink ref="C532" r:id="rId515" xr:uid="{00000000-0004-0000-0000-000002020000}"/>
-    <hyperlink ref="C533" r:id="rId516" xr:uid="{00000000-0004-0000-0000-000003020000}"/>
-    <hyperlink ref="C534" r:id="rId517" xr:uid="{00000000-0004-0000-0000-000004020000}"/>
+    <hyperlink ref="C532" r:id="rId514" xr:uid="{00000000-0004-0000-0000-000001020000}"/>
+    <hyperlink ref="C533" r:id="rId515" xr:uid="{00000000-0004-0000-0000-000002020000}"/>
+    <hyperlink ref="C534" r:id="rId516" xr:uid="{00000000-0004-0000-0000-000003020000}"/>
+    <hyperlink ref="C36" r:id="rId517" xr:uid="{00000000-0004-0000-0000-000004020000}"/>
     <hyperlink ref="C535" r:id="rId518" xr:uid="{00000000-0004-0000-0000-000005020000}"/>
     <hyperlink ref="C536" r:id="rId519" xr:uid="{00000000-0004-0000-0000-000006020000}"/>
     <hyperlink ref="C537" r:id="rId520" xr:uid="{00000000-0004-0000-0000-000007020000}"/>
@@ -17269,10 +17369,10 @@
     <hyperlink ref="C556" r:id="rId539" xr:uid="{00000000-0004-0000-0000-00001A020000}"/>
     <hyperlink ref="C557" r:id="rId540" xr:uid="{00000000-0004-0000-0000-00001B020000}"/>
     <hyperlink ref="C558" r:id="rId541" xr:uid="{00000000-0004-0000-0000-00001C020000}"/>
-    <hyperlink ref="C37" r:id="rId542" xr:uid="{00000000-0004-0000-0000-00001D020000}"/>
-    <hyperlink ref="C559" r:id="rId543" xr:uid="{00000000-0004-0000-0000-00001E020000}"/>
-    <hyperlink ref="C560" r:id="rId544" xr:uid="{00000000-0004-0000-0000-00001F020000}"/>
-    <hyperlink ref="C561" r:id="rId545" xr:uid="{00000000-0004-0000-0000-000020020000}"/>
+    <hyperlink ref="C559" r:id="rId542" xr:uid="{00000000-0004-0000-0000-00001D020000}"/>
+    <hyperlink ref="C560" r:id="rId543" xr:uid="{00000000-0004-0000-0000-00001E020000}"/>
+    <hyperlink ref="C561" r:id="rId544" xr:uid="{00000000-0004-0000-0000-00001F020000}"/>
+    <hyperlink ref="C37" r:id="rId545" xr:uid="{00000000-0004-0000-0000-000020020000}"/>
     <hyperlink ref="C562" r:id="rId546" xr:uid="{00000000-0004-0000-0000-000021020000}"/>
     <hyperlink ref="C563" r:id="rId547" xr:uid="{00000000-0004-0000-0000-000022020000}"/>
     <hyperlink ref="C564" r:id="rId548" xr:uid="{00000000-0004-0000-0000-000023020000}"/>
@@ -17289,257 +17389,262 @@
     <hyperlink ref="C575" r:id="rId559" xr:uid="{00000000-0004-0000-0000-00002E020000}"/>
     <hyperlink ref="C576" r:id="rId560" xr:uid="{00000000-0004-0000-0000-00002F020000}"/>
     <hyperlink ref="C577" r:id="rId561" xr:uid="{00000000-0004-0000-0000-000030020000}"/>
-    <hyperlink ref="C811" r:id="rId562" xr:uid="{00000000-0004-0000-0000-000031020000}"/>
-    <hyperlink ref="C578" r:id="rId563" xr:uid="{00000000-0004-0000-0000-000032020000}"/>
-    <hyperlink ref="C579" r:id="rId564" xr:uid="{00000000-0004-0000-0000-000033020000}"/>
-    <hyperlink ref="C580" r:id="rId565" xr:uid="{00000000-0004-0000-0000-000034020000}"/>
-    <hyperlink ref="C581" r:id="rId566" xr:uid="{00000000-0004-0000-0000-000035020000}"/>
-    <hyperlink ref="C582" r:id="rId567" xr:uid="{00000000-0004-0000-0000-000036020000}"/>
-    <hyperlink ref="C583" r:id="rId568" xr:uid="{00000000-0004-0000-0000-000037020000}"/>
-    <hyperlink ref="C584" r:id="rId569" xr:uid="{00000000-0004-0000-0000-000038020000}"/>
-    <hyperlink ref="C585" r:id="rId570" xr:uid="{00000000-0004-0000-0000-000039020000}"/>
-    <hyperlink ref="C586" r:id="rId571" xr:uid="{00000000-0004-0000-0000-00003A020000}"/>
-    <hyperlink ref="C587" r:id="rId572" xr:uid="{00000000-0004-0000-0000-00003B020000}"/>
-    <hyperlink ref="C588" r:id="rId573" xr:uid="{00000000-0004-0000-0000-00003C020000}"/>
-    <hyperlink ref="C589" r:id="rId574" xr:uid="{00000000-0004-0000-0000-00003D020000}"/>
-    <hyperlink ref="C590" r:id="rId575" xr:uid="{00000000-0004-0000-0000-00003E020000}"/>
-    <hyperlink ref="C591" r:id="rId576" xr:uid="{00000000-0004-0000-0000-00003F020000}"/>
-    <hyperlink ref="C592" r:id="rId577" xr:uid="{00000000-0004-0000-0000-000040020000}"/>
-    <hyperlink ref="C593" r:id="rId578" xr:uid="{00000000-0004-0000-0000-000041020000}"/>
-    <hyperlink ref="C594" r:id="rId579" xr:uid="{00000000-0004-0000-0000-000042020000}"/>
-    <hyperlink ref="C595" r:id="rId580" xr:uid="{00000000-0004-0000-0000-000043020000}"/>
-    <hyperlink ref="C596" r:id="rId581" xr:uid="{00000000-0004-0000-0000-000044020000}"/>
-    <hyperlink ref="C597" r:id="rId582" xr:uid="{00000000-0004-0000-0000-000045020000}"/>
-    <hyperlink ref="C598" r:id="rId583" xr:uid="{00000000-0004-0000-0000-000046020000}"/>
-    <hyperlink ref="C599" r:id="rId584" xr:uid="{00000000-0004-0000-0000-000047020000}"/>
-    <hyperlink ref="C600" r:id="rId585" xr:uid="{00000000-0004-0000-0000-000048020000}"/>
-    <hyperlink ref="C601" r:id="rId586" xr:uid="{00000000-0004-0000-0000-000049020000}"/>
-    <hyperlink ref="C602" r:id="rId587" xr:uid="{00000000-0004-0000-0000-00004A020000}"/>
-    <hyperlink ref="C603" r:id="rId588" xr:uid="{00000000-0004-0000-0000-00004B020000}"/>
-    <hyperlink ref="C604" r:id="rId589" xr:uid="{00000000-0004-0000-0000-00004C020000}"/>
-    <hyperlink ref="C812" r:id="rId590" xr:uid="{00000000-0004-0000-0000-00004D020000}"/>
-    <hyperlink ref="C605" r:id="rId591" xr:uid="{00000000-0004-0000-0000-00004E020000}"/>
-    <hyperlink ref="C606" r:id="rId592" xr:uid="{00000000-0004-0000-0000-00004F020000}"/>
-    <hyperlink ref="C607" r:id="rId593" xr:uid="{00000000-0004-0000-0000-000050020000}"/>
-    <hyperlink ref="C813" r:id="rId594" xr:uid="{00000000-0004-0000-0000-000051020000}"/>
-    <hyperlink ref="C608" r:id="rId595" xr:uid="{00000000-0004-0000-0000-000052020000}"/>
-    <hyperlink ref="C609" r:id="rId596" xr:uid="{00000000-0004-0000-0000-000053020000}"/>
-    <hyperlink ref="C610" r:id="rId597" xr:uid="{00000000-0004-0000-0000-000054020000}"/>
-    <hyperlink ref="C611" r:id="rId598" xr:uid="{00000000-0004-0000-0000-000055020000}"/>
-    <hyperlink ref="C612" r:id="rId599" xr:uid="{00000000-0004-0000-0000-000056020000}"/>
-    <hyperlink ref="C613" r:id="rId600" xr:uid="{00000000-0004-0000-0000-000057020000}"/>
-    <hyperlink ref="C614" r:id="rId601" xr:uid="{00000000-0004-0000-0000-000058020000}"/>
-    <hyperlink ref="C615" r:id="rId602" xr:uid="{00000000-0004-0000-0000-000059020000}"/>
-    <hyperlink ref="C616" r:id="rId603" xr:uid="{00000000-0004-0000-0000-00005A020000}"/>
-    <hyperlink ref="C617" r:id="rId604" xr:uid="{00000000-0004-0000-0000-00005B020000}"/>
-    <hyperlink ref="C618" r:id="rId605" xr:uid="{00000000-0004-0000-0000-00005C020000}"/>
-    <hyperlink ref="C619" r:id="rId606" xr:uid="{00000000-0004-0000-0000-00005D020000}"/>
-    <hyperlink ref="C620" r:id="rId607" xr:uid="{00000000-0004-0000-0000-00005E020000}"/>
-    <hyperlink ref="C621" r:id="rId608" xr:uid="{00000000-0004-0000-0000-00005F020000}"/>
-    <hyperlink ref="C622" r:id="rId609" xr:uid="{00000000-0004-0000-0000-000060020000}"/>
-    <hyperlink ref="C623" r:id="rId610" xr:uid="{00000000-0004-0000-0000-000061020000}"/>
-    <hyperlink ref="C624" r:id="rId611" xr:uid="{00000000-0004-0000-0000-000062020000}"/>
-    <hyperlink ref="C625" r:id="rId612" xr:uid="{00000000-0004-0000-0000-000063020000}"/>
-    <hyperlink ref="C626" r:id="rId613" xr:uid="{00000000-0004-0000-0000-000064020000}"/>
-    <hyperlink ref="C38" r:id="rId614" xr:uid="{00000000-0004-0000-0000-000065020000}"/>
-    <hyperlink ref="C627" r:id="rId615" xr:uid="{00000000-0004-0000-0000-000066020000}"/>
-    <hyperlink ref="C628" r:id="rId616" xr:uid="{00000000-0004-0000-0000-000067020000}"/>
-    <hyperlink ref="C629" r:id="rId617" xr:uid="{00000000-0004-0000-0000-000068020000}"/>
-    <hyperlink ref="C630" r:id="rId618" xr:uid="{00000000-0004-0000-0000-000069020000}"/>
-    <hyperlink ref="C631" r:id="rId619" xr:uid="{00000000-0004-0000-0000-00006A020000}"/>
-    <hyperlink ref="C632" r:id="rId620" xr:uid="{00000000-0004-0000-0000-00006B020000}"/>
-    <hyperlink ref="C633" r:id="rId621" xr:uid="{00000000-0004-0000-0000-00006C020000}"/>
-    <hyperlink ref="C634" r:id="rId622" xr:uid="{00000000-0004-0000-0000-00006D020000}"/>
-    <hyperlink ref="C635" r:id="rId623" xr:uid="{00000000-0004-0000-0000-00006E020000}"/>
-    <hyperlink ref="C636" r:id="rId624" xr:uid="{00000000-0004-0000-0000-00006F020000}"/>
-    <hyperlink ref="C637" r:id="rId625" xr:uid="{00000000-0004-0000-0000-000070020000}"/>
-    <hyperlink ref="C638" r:id="rId626" xr:uid="{00000000-0004-0000-0000-000071020000}"/>
-    <hyperlink ref="C639" r:id="rId627" xr:uid="{00000000-0004-0000-0000-000072020000}"/>
-    <hyperlink ref="C39" r:id="rId628" xr:uid="{00000000-0004-0000-0000-000073020000}"/>
-    <hyperlink ref="C640" r:id="rId629" xr:uid="{00000000-0004-0000-0000-000074020000}"/>
-    <hyperlink ref="C641" r:id="rId630" xr:uid="{00000000-0004-0000-0000-000075020000}"/>
-    <hyperlink ref="C642" r:id="rId631" xr:uid="{00000000-0004-0000-0000-000076020000}"/>
-    <hyperlink ref="C643" r:id="rId632" xr:uid="{00000000-0004-0000-0000-000077020000}"/>
-    <hyperlink ref="C644" r:id="rId633" xr:uid="{00000000-0004-0000-0000-000078020000}"/>
-    <hyperlink ref="C645" r:id="rId634" xr:uid="{00000000-0004-0000-0000-000079020000}"/>
-    <hyperlink ref="C646" r:id="rId635" xr:uid="{00000000-0004-0000-0000-00007A020000}"/>
-    <hyperlink ref="C647" r:id="rId636" xr:uid="{00000000-0004-0000-0000-00007B020000}"/>
-    <hyperlink ref="C648" r:id="rId637" xr:uid="{00000000-0004-0000-0000-00007C020000}"/>
-    <hyperlink ref="C649" r:id="rId638" xr:uid="{00000000-0004-0000-0000-00007D020000}"/>
-    <hyperlink ref="C650" r:id="rId639" xr:uid="{00000000-0004-0000-0000-00007E020000}"/>
-    <hyperlink ref="C651" r:id="rId640" xr:uid="{00000000-0004-0000-0000-00007F020000}"/>
-    <hyperlink ref="C652" r:id="rId641" xr:uid="{00000000-0004-0000-0000-000080020000}"/>
-    <hyperlink ref="C40" r:id="rId642" xr:uid="{00000000-0004-0000-0000-000081020000}"/>
-    <hyperlink ref="C653" r:id="rId643" xr:uid="{00000000-0004-0000-0000-000082020000}"/>
-    <hyperlink ref="C654" r:id="rId644" xr:uid="{00000000-0004-0000-0000-000083020000}"/>
-    <hyperlink ref="C655" r:id="rId645" xr:uid="{00000000-0004-0000-0000-000084020000}"/>
-    <hyperlink ref="C656" r:id="rId646" xr:uid="{00000000-0004-0000-0000-000085020000}"/>
-    <hyperlink ref="C41" r:id="rId647" xr:uid="{00000000-0004-0000-0000-000086020000}"/>
-    <hyperlink ref="C657" r:id="rId648" xr:uid="{00000000-0004-0000-0000-000087020000}"/>
-    <hyperlink ref="C658" r:id="rId649" xr:uid="{00000000-0004-0000-0000-000088020000}"/>
-    <hyperlink ref="C42" r:id="rId650" xr:uid="{00000000-0004-0000-0000-000089020000}"/>
-    <hyperlink ref="C659" r:id="rId651" xr:uid="{00000000-0004-0000-0000-00008A020000}"/>
-    <hyperlink ref="C660" r:id="rId652" xr:uid="{00000000-0004-0000-0000-00008B020000}"/>
-    <hyperlink ref="C661" r:id="rId653" xr:uid="{00000000-0004-0000-0000-00008C020000}"/>
-    <hyperlink ref="C662" r:id="rId654" xr:uid="{00000000-0004-0000-0000-00008D020000}"/>
-    <hyperlink ref="C663" r:id="rId655" xr:uid="{00000000-0004-0000-0000-00008E020000}"/>
-    <hyperlink ref="C664" r:id="rId656" xr:uid="{00000000-0004-0000-0000-00008F020000}"/>
-    <hyperlink ref="C43" r:id="rId657" xr:uid="{00000000-0004-0000-0000-000090020000}"/>
-    <hyperlink ref="C665" r:id="rId658" xr:uid="{00000000-0004-0000-0000-000091020000}"/>
-    <hyperlink ref="C44" r:id="rId659" xr:uid="{00000000-0004-0000-0000-000092020000}"/>
-    <hyperlink ref="C666" r:id="rId660" xr:uid="{00000000-0004-0000-0000-000093020000}"/>
-    <hyperlink ref="C667" r:id="rId661" xr:uid="{00000000-0004-0000-0000-000094020000}"/>
-    <hyperlink ref="C668" r:id="rId662" xr:uid="{00000000-0004-0000-0000-000095020000}"/>
-    <hyperlink ref="C669" r:id="rId663" xr:uid="{00000000-0004-0000-0000-000096020000}"/>
-    <hyperlink ref="C670" r:id="rId664" xr:uid="{00000000-0004-0000-0000-000097020000}"/>
-    <hyperlink ref="C671" r:id="rId665" xr:uid="{00000000-0004-0000-0000-000098020000}"/>
-    <hyperlink ref="C672" r:id="rId666" xr:uid="{00000000-0004-0000-0000-000099020000}"/>
-    <hyperlink ref="C673" r:id="rId667" xr:uid="{00000000-0004-0000-0000-00009A020000}"/>
-    <hyperlink ref="C674" r:id="rId668" xr:uid="{00000000-0004-0000-0000-00009B020000}"/>
-    <hyperlink ref="C675" r:id="rId669" xr:uid="{00000000-0004-0000-0000-00009C020000}"/>
-    <hyperlink ref="C676" r:id="rId670" xr:uid="{00000000-0004-0000-0000-00009D020000}"/>
-    <hyperlink ref="C677" r:id="rId671" xr:uid="{00000000-0004-0000-0000-00009E020000}"/>
-    <hyperlink ref="C678" r:id="rId672" xr:uid="{00000000-0004-0000-0000-00009F020000}"/>
-    <hyperlink ref="C679" r:id="rId673" xr:uid="{00000000-0004-0000-0000-0000A0020000}"/>
-    <hyperlink ref="C680" r:id="rId674" xr:uid="{00000000-0004-0000-0000-0000A1020000}"/>
-    <hyperlink ref="C681" r:id="rId675" xr:uid="{00000000-0004-0000-0000-0000A2020000}"/>
-    <hyperlink ref="C682" r:id="rId676" xr:uid="{00000000-0004-0000-0000-0000A3020000}"/>
-    <hyperlink ref="C683" r:id="rId677" xr:uid="{00000000-0004-0000-0000-0000A4020000}"/>
-    <hyperlink ref="C684" r:id="rId678" xr:uid="{00000000-0004-0000-0000-0000A5020000}"/>
-    <hyperlink ref="C685" r:id="rId679" xr:uid="{00000000-0004-0000-0000-0000A6020000}"/>
-    <hyperlink ref="C686" r:id="rId680" xr:uid="{00000000-0004-0000-0000-0000A7020000}"/>
-    <hyperlink ref="C687" r:id="rId681" xr:uid="{00000000-0004-0000-0000-0000A8020000}"/>
-    <hyperlink ref="C688" r:id="rId682" xr:uid="{00000000-0004-0000-0000-0000A9020000}"/>
-    <hyperlink ref="C689" r:id="rId683" xr:uid="{00000000-0004-0000-0000-0000AA020000}"/>
-    <hyperlink ref="C690" r:id="rId684" xr:uid="{00000000-0004-0000-0000-0000AB020000}"/>
-    <hyperlink ref="C691" r:id="rId685" xr:uid="{00000000-0004-0000-0000-0000AC020000}"/>
-    <hyperlink ref="C692" r:id="rId686" xr:uid="{00000000-0004-0000-0000-0000AD020000}"/>
-    <hyperlink ref="C693" r:id="rId687" xr:uid="{00000000-0004-0000-0000-0000AE020000}"/>
-    <hyperlink ref="C694" r:id="rId688" xr:uid="{00000000-0004-0000-0000-0000AF020000}"/>
-    <hyperlink ref="C695" r:id="rId689" xr:uid="{00000000-0004-0000-0000-0000B0020000}"/>
-    <hyperlink ref="C696" r:id="rId690" xr:uid="{00000000-0004-0000-0000-0000B1020000}"/>
-    <hyperlink ref="C697" r:id="rId691" xr:uid="{00000000-0004-0000-0000-0000B2020000}"/>
-    <hyperlink ref="C698" r:id="rId692" xr:uid="{00000000-0004-0000-0000-0000B3020000}"/>
-    <hyperlink ref="C699" r:id="rId693" xr:uid="{00000000-0004-0000-0000-0000B4020000}"/>
-    <hyperlink ref="C700" r:id="rId694" xr:uid="{00000000-0004-0000-0000-0000B5020000}"/>
-    <hyperlink ref="C701" r:id="rId695" xr:uid="{00000000-0004-0000-0000-0000B6020000}"/>
-    <hyperlink ref="C702" r:id="rId696" xr:uid="{00000000-0004-0000-0000-0000B7020000}"/>
-    <hyperlink ref="C703" r:id="rId697" xr:uid="{00000000-0004-0000-0000-0000B8020000}"/>
-    <hyperlink ref="C45" r:id="rId698" xr:uid="{00000000-0004-0000-0000-0000B9020000}"/>
-    <hyperlink ref="C704" r:id="rId699" xr:uid="{00000000-0004-0000-0000-0000BA020000}"/>
-    <hyperlink ref="C705" r:id="rId700" xr:uid="{00000000-0004-0000-0000-0000BB020000}"/>
-    <hyperlink ref="C706" r:id="rId701" xr:uid="{00000000-0004-0000-0000-0000BC020000}"/>
-    <hyperlink ref="C707" r:id="rId702" xr:uid="{00000000-0004-0000-0000-0000BD020000}"/>
-    <hyperlink ref="C708" r:id="rId703" xr:uid="{00000000-0004-0000-0000-0000BE020000}"/>
-    <hyperlink ref="C709" r:id="rId704" xr:uid="{00000000-0004-0000-0000-0000BF020000}"/>
-    <hyperlink ref="C710" r:id="rId705" xr:uid="{00000000-0004-0000-0000-0000C0020000}"/>
-    <hyperlink ref="C711" r:id="rId706" xr:uid="{00000000-0004-0000-0000-0000C1020000}"/>
-    <hyperlink ref="C712" r:id="rId707" xr:uid="{00000000-0004-0000-0000-0000C2020000}"/>
-    <hyperlink ref="C713" r:id="rId708" xr:uid="{00000000-0004-0000-0000-0000C3020000}"/>
-    <hyperlink ref="C714" r:id="rId709" xr:uid="{00000000-0004-0000-0000-0000C4020000}"/>
-    <hyperlink ref="C715" r:id="rId710" xr:uid="{00000000-0004-0000-0000-0000C5020000}"/>
-    <hyperlink ref="C716" r:id="rId711" xr:uid="{00000000-0004-0000-0000-0000C6020000}"/>
-    <hyperlink ref="C717" r:id="rId712" xr:uid="{00000000-0004-0000-0000-0000C7020000}"/>
-    <hyperlink ref="C718" r:id="rId713" xr:uid="{00000000-0004-0000-0000-0000C8020000}"/>
-    <hyperlink ref="C719" r:id="rId714" xr:uid="{00000000-0004-0000-0000-0000C9020000}"/>
-    <hyperlink ref="C720" r:id="rId715" xr:uid="{00000000-0004-0000-0000-0000CA020000}"/>
-    <hyperlink ref="C721" r:id="rId716" xr:uid="{00000000-0004-0000-0000-0000CB020000}"/>
-    <hyperlink ref="C722" r:id="rId717" xr:uid="{00000000-0004-0000-0000-0000CC020000}"/>
-    <hyperlink ref="C723" r:id="rId718" xr:uid="{00000000-0004-0000-0000-0000CD020000}"/>
-    <hyperlink ref="C724" r:id="rId719" xr:uid="{00000000-0004-0000-0000-0000CE020000}"/>
-    <hyperlink ref="C725" r:id="rId720" xr:uid="{00000000-0004-0000-0000-0000CF020000}"/>
-    <hyperlink ref="C46" r:id="rId721" xr:uid="{00000000-0004-0000-0000-0000D0020000}"/>
-    <hyperlink ref="C47" r:id="rId722" xr:uid="{00000000-0004-0000-0000-0000D1020000}"/>
-    <hyperlink ref="C726" r:id="rId723" xr:uid="{00000000-0004-0000-0000-0000D2020000}"/>
-    <hyperlink ref="C727" r:id="rId724" xr:uid="{00000000-0004-0000-0000-0000D3020000}"/>
-    <hyperlink ref="C728" r:id="rId725" xr:uid="{00000000-0004-0000-0000-0000D4020000}"/>
-    <hyperlink ref="C729" r:id="rId726" xr:uid="{00000000-0004-0000-0000-0000D5020000}"/>
-    <hyperlink ref="C730" r:id="rId727" xr:uid="{00000000-0004-0000-0000-0000D6020000}"/>
-    <hyperlink ref="C48" r:id="rId728" xr:uid="{00000000-0004-0000-0000-0000D7020000}"/>
-    <hyperlink ref="C49" r:id="rId729" xr:uid="{00000000-0004-0000-0000-0000D8020000}"/>
-    <hyperlink ref="C731" r:id="rId730" xr:uid="{00000000-0004-0000-0000-0000D9020000}"/>
-    <hyperlink ref="C732" r:id="rId731" xr:uid="{00000000-0004-0000-0000-0000DA020000}"/>
-    <hyperlink ref="C733" r:id="rId732" xr:uid="{00000000-0004-0000-0000-0000DB020000}"/>
-    <hyperlink ref="C734" r:id="rId733" xr:uid="{00000000-0004-0000-0000-0000DC020000}"/>
-    <hyperlink ref="C735" r:id="rId734" xr:uid="{00000000-0004-0000-0000-0000DD020000}"/>
-    <hyperlink ref="C736" r:id="rId735" xr:uid="{00000000-0004-0000-0000-0000DE020000}"/>
-    <hyperlink ref="C737" r:id="rId736" xr:uid="{00000000-0004-0000-0000-0000DF020000}"/>
-    <hyperlink ref="C738" r:id="rId737" xr:uid="{00000000-0004-0000-0000-0000E0020000}"/>
-    <hyperlink ref="C50" r:id="rId738" xr:uid="{00000000-0004-0000-0000-0000E1020000}"/>
-    <hyperlink ref="C739" r:id="rId739" xr:uid="{00000000-0004-0000-0000-0000E2020000}"/>
-    <hyperlink ref="C740" r:id="rId740" xr:uid="{00000000-0004-0000-0000-0000E3020000}"/>
-    <hyperlink ref="C741" r:id="rId741" xr:uid="{00000000-0004-0000-0000-0000E4020000}"/>
-    <hyperlink ref="C742" r:id="rId742" xr:uid="{00000000-0004-0000-0000-0000E5020000}"/>
-    <hyperlink ref="C743" r:id="rId743" xr:uid="{00000000-0004-0000-0000-0000E6020000}"/>
-    <hyperlink ref="C744" r:id="rId744" xr:uid="{00000000-0004-0000-0000-0000E7020000}"/>
-    <hyperlink ref="C745" r:id="rId745" xr:uid="{00000000-0004-0000-0000-0000E8020000}"/>
-    <hyperlink ref="C746" r:id="rId746" xr:uid="{00000000-0004-0000-0000-0000E9020000}"/>
-    <hyperlink ref="C747" r:id="rId747" xr:uid="{00000000-0004-0000-0000-0000EA020000}"/>
-    <hyperlink ref="C51" r:id="rId748" xr:uid="{00000000-0004-0000-0000-0000EB020000}"/>
-    <hyperlink ref="C748" r:id="rId749" xr:uid="{00000000-0004-0000-0000-0000EC020000}"/>
-    <hyperlink ref="C749" r:id="rId750" xr:uid="{00000000-0004-0000-0000-0000ED020000}"/>
-    <hyperlink ref="C750" r:id="rId751" xr:uid="{00000000-0004-0000-0000-0000EE020000}"/>
-    <hyperlink ref="C751" r:id="rId752" xr:uid="{00000000-0004-0000-0000-0000EF020000}"/>
-    <hyperlink ref="C752" r:id="rId753" xr:uid="{00000000-0004-0000-0000-0000F0020000}"/>
-    <hyperlink ref="C753" r:id="rId754" xr:uid="{00000000-0004-0000-0000-0000F1020000}"/>
-    <hyperlink ref="C754" r:id="rId755" xr:uid="{00000000-0004-0000-0000-0000F2020000}"/>
-    <hyperlink ref="C755" r:id="rId756" xr:uid="{00000000-0004-0000-0000-0000F3020000}"/>
-    <hyperlink ref="C756" r:id="rId757" xr:uid="{00000000-0004-0000-0000-0000F4020000}"/>
-    <hyperlink ref="C757" r:id="rId758" xr:uid="{00000000-0004-0000-0000-0000F5020000}"/>
-    <hyperlink ref="C758" r:id="rId759" xr:uid="{00000000-0004-0000-0000-0000F6020000}"/>
-    <hyperlink ref="C52" r:id="rId760" xr:uid="{00000000-0004-0000-0000-0000F7020000}"/>
-    <hyperlink ref="C759" r:id="rId761" xr:uid="{00000000-0004-0000-0000-0000F8020000}"/>
-    <hyperlink ref="C760" r:id="rId762" xr:uid="{00000000-0004-0000-0000-0000F9020000}"/>
-    <hyperlink ref="C761" r:id="rId763" xr:uid="{00000000-0004-0000-0000-0000FA020000}"/>
-    <hyperlink ref="C762" r:id="rId764" xr:uid="{00000000-0004-0000-0000-0000FB020000}"/>
-    <hyperlink ref="C763" r:id="rId765" xr:uid="{00000000-0004-0000-0000-0000FC020000}"/>
-    <hyperlink ref="C764" r:id="rId766" xr:uid="{00000000-0004-0000-0000-0000FD020000}"/>
-    <hyperlink ref="C765" r:id="rId767" xr:uid="{00000000-0004-0000-0000-0000FE020000}"/>
-    <hyperlink ref="C766" r:id="rId768" xr:uid="{00000000-0004-0000-0000-0000FF020000}"/>
-    <hyperlink ref="C767" r:id="rId769" xr:uid="{00000000-0004-0000-0000-000000030000}"/>
-    <hyperlink ref="C768" r:id="rId770" xr:uid="{00000000-0004-0000-0000-000001030000}"/>
-    <hyperlink ref="C769" r:id="rId771" xr:uid="{00000000-0004-0000-0000-000002030000}"/>
-    <hyperlink ref="C770" r:id="rId772" xr:uid="{00000000-0004-0000-0000-000003030000}"/>
-    <hyperlink ref="C771" r:id="rId773" xr:uid="{00000000-0004-0000-0000-000004030000}"/>
-    <hyperlink ref="C772" r:id="rId774" xr:uid="{00000000-0004-0000-0000-000005030000}"/>
-    <hyperlink ref="C773" r:id="rId775" xr:uid="{00000000-0004-0000-0000-000006030000}"/>
-    <hyperlink ref="C774" r:id="rId776" xr:uid="{00000000-0004-0000-0000-000007030000}"/>
-    <hyperlink ref="C775" r:id="rId777" xr:uid="{00000000-0004-0000-0000-000008030000}"/>
-    <hyperlink ref="C776" r:id="rId778" xr:uid="{00000000-0004-0000-0000-000009030000}"/>
-    <hyperlink ref="C777" r:id="rId779" xr:uid="{00000000-0004-0000-0000-00000A030000}"/>
-    <hyperlink ref="C53" r:id="rId780" xr:uid="{00000000-0004-0000-0000-00000B030000}"/>
-    <hyperlink ref="C778" r:id="rId781" xr:uid="{00000000-0004-0000-0000-00000C030000}"/>
-    <hyperlink ref="C779" r:id="rId782" xr:uid="{00000000-0004-0000-0000-00000D030000}"/>
-    <hyperlink ref="C780" r:id="rId783" xr:uid="{00000000-0004-0000-0000-00000E030000}"/>
-    <hyperlink ref="C781" r:id="rId784" xr:uid="{00000000-0004-0000-0000-00000F030000}"/>
-    <hyperlink ref="C782" r:id="rId785" xr:uid="{00000000-0004-0000-0000-000010030000}"/>
-    <hyperlink ref="C54" r:id="rId786" xr:uid="{00000000-0004-0000-0000-000011030000}"/>
-    <hyperlink ref="C783" r:id="rId787" xr:uid="{00000000-0004-0000-0000-000012030000}"/>
-    <hyperlink ref="C784" r:id="rId788" xr:uid="{00000000-0004-0000-0000-000013030000}"/>
-    <hyperlink ref="C785" r:id="rId789" xr:uid="{00000000-0004-0000-0000-000014030000}"/>
-    <hyperlink ref="C786" r:id="rId790" xr:uid="{00000000-0004-0000-0000-000015030000}"/>
-    <hyperlink ref="C787" r:id="rId791" xr:uid="{00000000-0004-0000-0000-000016030000}"/>
-    <hyperlink ref="C788" r:id="rId792" xr:uid="{00000000-0004-0000-0000-000017030000}"/>
-    <hyperlink ref="C789" r:id="rId793" xr:uid="{00000000-0004-0000-0000-000018030000}"/>
-    <hyperlink ref="C790" r:id="rId794" xr:uid="{00000000-0004-0000-0000-000019030000}"/>
-    <hyperlink ref="C791" r:id="rId795" xr:uid="{00000000-0004-0000-0000-00001A030000}"/>
-    <hyperlink ref="C792" r:id="rId796" xr:uid="{00000000-0004-0000-0000-00001B030000}"/>
-    <hyperlink ref="C793" r:id="rId797" xr:uid="{00000000-0004-0000-0000-00001C030000}"/>
-    <hyperlink ref="C794" r:id="rId798" xr:uid="{00000000-0004-0000-0000-00001D030000}"/>
-    <hyperlink ref="C795" r:id="rId799" xr:uid="{00000000-0004-0000-0000-00001E030000}"/>
-    <hyperlink ref="C796" r:id="rId800" xr:uid="{00000000-0004-0000-0000-00001F030000}"/>
-    <hyperlink ref="C55" r:id="rId801" xr:uid="{00000000-0004-0000-0000-000020030000}"/>
-    <hyperlink ref="C797" r:id="rId802" xr:uid="{00000000-0004-0000-0000-000021030000}"/>
-    <hyperlink ref="C798" r:id="rId803" xr:uid="{00000000-0004-0000-0000-000022030000}"/>
-    <hyperlink ref="C799" r:id="rId804" xr:uid="{00000000-0004-0000-0000-000023030000}"/>
-    <hyperlink ref="C800" r:id="rId805" xr:uid="{00000000-0004-0000-0000-000024030000}"/>
-    <hyperlink ref="C801" r:id="rId806" xr:uid="{00000000-0004-0000-0000-000025030000}"/>
-    <hyperlink ref="C802" r:id="rId807" xr:uid="{00000000-0004-0000-0000-000026030000}"/>
-    <hyperlink ref="C803" r:id="rId808" xr:uid="{00000000-0004-0000-0000-000027030000}"/>
-    <hyperlink ref="C804" r:id="rId809" xr:uid="{00000000-0004-0000-0000-000028030000}"/>
-    <hyperlink ref="C805" r:id="rId810" xr:uid="{00000000-0004-0000-0000-000029030000}"/>
-    <hyperlink ref="C806" r:id="rId811" xr:uid="{00000000-0004-0000-0000-00002A030000}"/>
-    <hyperlink ref="C807" r:id="rId812" xr:uid="{00000000-0004-0000-0000-00002B030000}"/>
+    <hyperlink ref="C578" r:id="rId562" xr:uid="{00000000-0004-0000-0000-000031020000}"/>
+    <hyperlink ref="C579" r:id="rId563" xr:uid="{00000000-0004-0000-0000-000032020000}"/>
+    <hyperlink ref="C580" r:id="rId564" xr:uid="{00000000-0004-0000-0000-000033020000}"/>
+    <hyperlink ref="C581" r:id="rId565" xr:uid="{00000000-0004-0000-0000-000034020000}"/>
+    <hyperlink ref="C582" r:id="rId566" xr:uid="{00000000-0004-0000-0000-000035020000}"/>
+    <hyperlink ref="C583" r:id="rId567" xr:uid="{00000000-0004-0000-0000-000036020000}"/>
+    <hyperlink ref="C584" r:id="rId568" xr:uid="{00000000-0004-0000-0000-000037020000}"/>
+    <hyperlink ref="C585" r:id="rId569" xr:uid="{00000000-0004-0000-0000-000038020000}"/>
+    <hyperlink ref="C586" r:id="rId570" xr:uid="{00000000-0004-0000-0000-000039020000}"/>
+    <hyperlink ref="C587" r:id="rId571" xr:uid="{00000000-0004-0000-0000-00003A020000}"/>
+    <hyperlink ref="C588" r:id="rId572" xr:uid="{00000000-0004-0000-0000-00003B020000}"/>
+    <hyperlink ref="C589" r:id="rId573" xr:uid="{00000000-0004-0000-0000-00003C020000}"/>
+    <hyperlink ref="C590" r:id="rId574" xr:uid="{00000000-0004-0000-0000-00003D020000}"/>
+    <hyperlink ref="C591" r:id="rId575" xr:uid="{00000000-0004-0000-0000-00003E020000}"/>
+    <hyperlink ref="C592" r:id="rId576" xr:uid="{00000000-0004-0000-0000-00003F020000}"/>
+    <hyperlink ref="C593" r:id="rId577" xr:uid="{00000000-0004-0000-0000-000040020000}"/>
+    <hyperlink ref="C594" r:id="rId578" xr:uid="{00000000-0004-0000-0000-000041020000}"/>
+    <hyperlink ref="C595" r:id="rId579" xr:uid="{00000000-0004-0000-0000-000042020000}"/>
+    <hyperlink ref="C596" r:id="rId580" xr:uid="{00000000-0004-0000-0000-000043020000}"/>
+    <hyperlink ref="C597" r:id="rId581" xr:uid="{00000000-0004-0000-0000-000044020000}"/>
+    <hyperlink ref="C598" r:id="rId582" xr:uid="{00000000-0004-0000-0000-000045020000}"/>
+    <hyperlink ref="C599" r:id="rId583" xr:uid="{00000000-0004-0000-0000-000046020000}"/>
+    <hyperlink ref="C600" r:id="rId584" xr:uid="{00000000-0004-0000-0000-000047020000}"/>
+    <hyperlink ref="C601" r:id="rId585" xr:uid="{00000000-0004-0000-0000-000048020000}"/>
+    <hyperlink ref="C602" r:id="rId586" xr:uid="{00000000-0004-0000-0000-000049020000}"/>
+    <hyperlink ref="C603" r:id="rId587" xr:uid="{00000000-0004-0000-0000-00004A020000}"/>
+    <hyperlink ref="C604" r:id="rId588" xr:uid="{00000000-0004-0000-0000-00004B020000}"/>
+    <hyperlink ref="C605" r:id="rId589" xr:uid="{00000000-0004-0000-0000-00004C020000}"/>
+    <hyperlink ref="C606" r:id="rId590" xr:uid="{00000000-0004-0000-0000-00004D020000}"/>
+    <hyperlink ref="C607" r:id="rId591" xr:uid="{00000000-0004-0000-0000-00004E020000}"/>
+    <hyperlink ref="C608" r:id="rId592" xr:uid="{00000000-0004-0000-0000-00004F020000}"/>
+    <hyperlink ref="C609" r:id="rId593" xr:uid="{00000000-0004-0000-0000-000050020000}"/>
+    <hyperlink ref="C610" r:id="rId594" xr:uid="{00000000-0004-0000-0000-000051020000}"/>
+    <hyperlink ref="C611" r:id="rId595" xr:uid="{00000000-0004-0000-0000-000052020000}"/>
+    <hyperlink ref="C612" r:id="rId596" xr:uid="{00000000-0004-0000-0000-000053020000}"/>
+    <hyperlink ref="C613" r:id="rId597" xr:uid="{00000000-0004-0000-0000-000054020000}"/>
+    <hyperlink ref="C614" r:id="rId598" xr:uid="{00000000-0004-0000-0000-000055020000}"/>
+    <hyperlink ref="C615" r:id="rId599" xr:uid="{00000000-0004-0000-0000-000056020000}"/>
+    <hyperlink ref="C616" r:id="rId600" xr:uid="{00000000-0004-0000-0000-000057020000}"/>
+    <hyperlink ref="C617" r:id="rId601" xr:uid="{00000000-0004-0000-0000-000058020000}"/>
+    <hyperlink ref="C618" r:id="rId602" xr:uid="{00000000-0004-0000-0000-000059020000}"/>
+    <hyperlink ref="C619" r:id="rId603" xr:uid="{00000000-0004-0000-0000-00005A020000}"/>
+    <hyperlink ref="C620" r:id="rId604" xr:uid="{00000000-0004-0000-0000-00005B020000}"/>
+    <hyperlink ref="C621" r:id="rId605" xr:uid="{00000000-0004-0000-0000-00005C020000}"/>
+    <hyperlink ref="C622" r:id="rId606" xr:uid="{00000000-0004-0000-0000-00005D020000}"/>
+    <hyperlink ref="C623" r:id="rId607" xr:uid="{00000000-0004-0000-0000-00005E020000}"/>
+    <hyperlink ref="C624" r:id="rId608" xr:uid="{00000000-0004-0000-0000-00005F020000}"/>
+    <hyperlink ref="C625" r:id="rId609" xr:uid="{00000000-0004-0000-0000-000060020000}"/>
+    <hyperlink ref="C626" r:id="rId610" xr:uid="{00000000-0004-0000-0000-000061020000}"/>
+    <hyperlink ref="C627" r:id="rId611" xr:uid="{00000000-0004-0000-0000-000062020000}"/>
+    <hyperlink ref="C628" r:id="rId612" xr:uid="{00000000-0004-0000-0000-000063020000}"/>
+    <hyperlink ref="C629" r:id="rId613" xr:uid="{00000000-0004-0000-0000-000064020000}"/>
+    <hyperlink ref="C630" r:id="rId614" xr:uid="{00000000-0004-0000-0000-000065020000}"/>
+    <hyperlink ref="C631" r:id="rId615" xr:uid="{00000000-0004-0000-0000-000066020000}"/>
+    <hyperlink ref="C632" r:id="rId616" xr:uid="{00000000-0004-0000-0000-000067020000}"/>
+    <hyperlink ref="C38" r:id="rId617" xr:uid="{00000000-0004-0000-0000-000068020000}"/>
+    <hyperlink ref="C633" r:id="rId618" xr:uid="{00000000-0004-0000-0000-000069020000}"/>
+    <hyperlink ref="C634" r:id="rId619" xr:uid="{00000000-0004-0000-0000-00006A020000}"/>
+    <hyperlink ref="C635" r:id="rId620" xr:uid="{00000000-0004-0000-0000-00006B020000}"/>
+    <hyperlink ref="C636" r:id="rId621" xr:uid="{00000000-0004-0000-0000-00006C020000}"/>
+    <hyperlink ref="C637" r:id="rId622" xr:uid="{00000000-0004-0000-0000-00006D020000}"/>
+    <hyperlink ref="C638" r:id="rId623" xr:uid="{00000000-0004-0000-0000-00006E020000}"/>
+    <hyperlink ref="C639" r:id="rId624" xr:uid="{00000000-0004-0000-0000-00006F020000}"/>
+    <hyperlink ref="C640" r:id="rId625" xr:uid="{00000000-0004-0000-0000-000070020000}"/>
+    <hyperlink ref="C641" r:id="rId626" xr:uid="{00000000-0004-0000-0000-000071020000}"/>
+    <hyperlink ref="C642" r:id="rId627" xr:uid="{00000000-0004-0000-0000-000072020000}"/>
+    <hyperlink ref="C643" r:id="rId628" xr:uid="{00000000-0004-0000-0000-000073020000}"/>
+    <hyperlink ref="C644" r:id="rId629" xr:uid="{00000000-0004-0000-0000-000074020000}"/>
+    <hyperlink ref="C645" r:id="rId630" xr:uid="{00000000-0004-0000-0000-000075020000}"/>
+    <hyperlink ref="C39" r:id="rId631" xr:uid="{00000000-0004-0000-0000-000076020000}"/>
+    <hyperlink ref="C646" r:id="rId632" xr:uid="{00000000-0004-0000-0000-000077020000}"/>
+    <hyperlink ref="C647" r:id="rId633" xr:uid="{00000000-0004-0000-0000-000078020000}"/>
+    <hyperlink ref="C648" r:id="rId634" xr:uid="{00000000-0004-0000-0000-000079020000}"/>
+    <hyperlink ref="C649" r:id="rId635" xr:uid="{00000000-0004-0000-0000-00007A020000}"/>
+    <hyperlink ref="C650" r:id="rId636" xr:uid="{00000000-0004-0000-0000-00007B020000}"/>
+    <hyperlink ref="C651" r:id="rId637" xr:uid="{00000000-0004-0000-0000-00007C020000}"/>
+    <hyperlink ref="C652" r:id="rId638" xr:uid="{00000000-0004-0000-0000-00007D020000}"/>
+    <hyperlink ref="C653" r:id="rId639" xr:uid="{00000000-0004-0000-0000-00007E020000}"/>
+    <hyperlink ref="C654" r:id="rId640" xr:uid="{00000000-0004-0000-0000-00007F020000}"/>
+    <hyperlink ref="C655" r:id="rId641" xr:uid="{00000000-0004-0000-0000-000080020000}"/>
+    <hyperlink ref="C656" r:id="rId642" xr:uid="{00000000-0004-0000-0000-000081020000}"/>
+    <hyperlink ref="C657" r:id="rId643" xr:uid="{00000000-0004-0000-0000-000082020000}"/>
+    <hyperlink ref="C658" r:id="rId644" xr:uid="{00000000-0004-0000-0000-000083020000}"/>
+    <hyperlink ref="C40" r:id="rId645" xr:uid="{00000000-0004-0000-0000-000084020000}"/>
+    <hyperlink ref="C659" r:id="rId646" xr:uid="{00000000-0004-0000-0000-000085020000}"/>
+    <hyperlink ref="C660" r:id="rId647" xr:uid="{00000000-0004-0000-0000-000086020000}"/>
+    <hyperlink ref="C661" r:id="rId648" xr:uid="{00000000-0004-0000-0000-000087020000}"/>
+    <hyperlink ref="C662" r:id="rId649" xr:uid="{00000000-0004-0000-0000-000088020000}"/>
+    <hyperlink ref="C41" r:id="rId650" xr:uid="{00000000-0004-0000-0000-000089020000}"/>
+    <hyperlink ref="C663" r:id="rId651" xr:uid="{00000000-0004-0000-0000-00008A020000}"/>
+    <hyperlink ref="C664" r:id="rId652" xr:uid="{00000000-0004-0000-0000-00008B020000}"/>
+    <hyperlink ref="C42" r:id="rId653" xr:uid="{00000000-0004-0000-0000-00008C020000}"/>
+    <hyperlink ref="C665" r:id="rId654" xr:uid="{00000000-0004-0000-0000-00008D020000}"/>
+    <hyperlink ref="C666" r:id="rId655" xr:uid="{00000000-0004-0000-0000-00008E020000}"/>
+    <hyperlink ref="C667" r:id="rId656" xr:uid="{00000000-0004-0000-0000-00008F020000}"/>
+    <hyperlink ref="C668" r:id="rId657" xr:uid="{00000000-0004-0000-0000-000090020000}"/>
+    <hyperlink ref="C669" r:id="rId658" xr:uid="{00000000-0004-0000-0000-000091020000}"/>
+    <hyperlink ref="C670" r:id="rId659" xr:uid="{00000000-0004-0000-0000-000092020000}"/>
+    <hyperlink ref="C43" r:id="rId660" xr:uid="{00000000-0004-0000-0000-000093020000}"/>
+    <hyperlink ref="C671" r:id="rId661" xr:uid="{00000000-0004-0000-0000-000094020000}"/>
+    <hyperlink ref="C44" r:id="rId662" xr:uid="{00000000-0004-0000-0000-000095020000}"/>
+    <hyperlink ref="C672" r:id="rId663" xr:uid="{00000000-0004-0000-0000-000096020000}"/>
+    <hyperlink ref="C673" r:id="rId664" xr:uid="{00000000-0004-0000-0000-000097020000}"/>
+    <hyperlink ref="C674" r:id="rId665" xr:uid="{00000000-0004-0000-0000-000098020000}"/>
+    <hyperlink ref="C675" r:id="rId666" xr:uid="{00000000-0004-0000-0000-000099020000}"/>
+    <hyperlink ref="C676" r:id="rId667" xr:uid="{00000000-0004-0000-0000-00009A020000}"/>
+    <hyperlink ref="C677" r:id="rId668" xr:uid="{00000000-0004-0000-0000-00009B020000}"/>
+    <hyperlink ref="C678" r:id="rId669" xr:uid="{00000000-0004-0000-0000-00009C020000}"/>
+    <hyperlink ref="C679" r:id="rId670" xr:uid="{00000000-0004-0000-0000-00009D020000}"/>
+    <hyperlink ref="C680" r:id="rId671" xr:uid="{00000000-0004-0000-0000-00009E020000}"/>
+    <hyperlink ref="C681" r:id="rId672" xr:uid="{00000000-0004-0000-0000-00009F020000}"/>
+    <hyperlink ref="C682" r:id="rId673" xr:uid="{00000000-0004-0000-0000-0000A0020000}"/>
+    <hyperlink ref="C683" r:id="rId674" xr:uid="{00000000-0004-0000-0000-0000A1020000}"/>
+    <hyperlink ref="C684" r:id="rId675" xr:uid="{00000000-0004-0000-0000-0000A2020000}"/>
+    <hyperlink ref="C685" r:id="rId676" xr:uid="{00000000-0004-0000-0000-0000A3020000}"/>
+    <hyperlink ref="C686" r:id="rId677" xr:uid="{00000000-0004-0000-0000-0000A4020000}"/>
+    <hyperlink ref="C687" r:id="rId678" xr:uid="{00000000-0004-0000-0000-0000A5020000}"/>
+    <hyperlink ref="C688" r:id="rId679" xr:uid="{00000000-0004-0000-0000-0000A6020000}"/>
+    <hyperlink ref="C689" r:id="rId680" xr:uid="{00000000-0004-0000-0000-0000A7020000}"/>
+    <hyperlink ref="C690" r:id="rId681" xr:uid="{00000000-0004-0000-0000-0000A8020000}"/>
+    <hyperlink ref="C691" r:id="rId682" xr:uid="{00000000-0004-0000-0000-0000A9020000}"/>
+    <hyperlink ref="C692" r:id="rId683" xr:uid="{00000000-0004-0000-0000-0000AA020000}"/>
+    <hyperlink ref="C693" r:id="rId684" xr:uid="{00000000-0004-0000-0000-0000AB020000}"/>
+    <hyperlink ref="C694" r:id="rId685" xr:uid="{00000000-0004-0000-0000-0000AC020000}"/>
+    <hyperlink ref="C695" r:id="rId686" xr:uid="{00000000-0004-0000-0000-0000AD020000}"/>
+    <hyperlink ref="C696" r:id="rId687" xr:uid="{00000000-0004-0000-0000-0000AE020000}"/>
+    <hyperlink ref="C697" r:id="rId688" xr:uid="{00000000-0004-0000-0000-0000AF020000}"/>
+    <hyperlink ref="C698" r:id="rId689" xr:uid="{00000000-0004-0000-0000-0000B0020000}"/>
+    <hyperlink ref="C699" r:id="rId690" xr:uid="{00000000-0004-0000-0000-0000B1020000}"/>
+    <hyperlink ref="C700" r:id="rId691" xr:uid="{00000000-0004-0000-0000-0000B2020000}"/>
+    <hyperlink ref="C701" r:id="rId692" xr:uid="{00000000-0004-0000-0000-0000B3020000}"/>
+    <hyperlink ref="C702" r:id="rId693" xr:uid="{00000000-0004-0000-0000-0000B4020000}"/>
+    <hyperlink ref="C703" r:id="rId694" xr:uid="{00000000-0004-0000-0000-0000B5020000}"/>
+    <hyperlink ref="C704" r:id="rId695" xr:uid="{00000000-0004-0000-0000-0000B6020000}"/>
+    <hyperlink ref="C705" r:id="rId696" xr:uid="{00000000-0004-0000-0000-0000B7020000}"/>
+    <hyperlink ref="C706" r:id="rId697" xr:uid="{00000000-0004-0000-0000-0000B8020000}"/>
+    <hyperlink ref="C707" r:id="rId698" xr:uid="{00000000-0004-0000-0000-0000B9020000}"/>
+    <hyperlink ref="C708" r:id="rId699" xr:uid="{00000000-0004-0000-0000-0000BA020000}"/>
+    <hyperlink ref="C709" r:id="rId700" xr:uid="{00000000-0004-0000-0000-0000BB020000}"/>
+    <hyperlink ref="C45" r:id="rId701" xr:uid="{00000000-0004-0000-0000-0000BC020000}"/>
+    <hyperlink ref="C710" r:id="rId702" xr:uid="{00000000-0004-0000-0000-0000BD020000}"/>
+    <hyperlink ref="C711" r:id="rId703" xr:uid="{00000000-0004-0000-0000-0000BE020000}"/>
+    <hyperlink ref="C712" r:id="rId704" xr:uid="{00000000-0004-0000-0000-0000BF020000}"/>
+    <hyperlink ref="C713" r:id="rId705" xr:uid="{00000000-0004-0000-0000-0000C0020000}"/>
+    <hyperlink ref="C714" r:id="rId706" xr:uid="{00000000-0004-0000-0000-0000C1020000}"/>
+    <hyperlink ref="C715" r:id="rId707" xr:uid="{00000000-0004-0000-0000-0000C2020000}"/>
+    <hyperlink ref="C716" r:id="rId708" xr:uid="{00000000-0004-0000-0000-0000C3020000}"/>
+    <hyperlink ref="C717" r:id="rId709" xr:uid="{00000000-0004-0000-0000-0000C4020000}"/>
+    <hyperlink ref="C718" r:id="rId710" xr:uid="{00000000-0004-0000-0000-0000C5020000}"/>
+    <hyperlink ref="C719" r:id="rId711" xr:uid="{00000000-0004-0000-0000-0000C6020000}"/>
+    <hyperlink ref="C720" r:id="rId712" xr:uid="{00000000-0004-0000-0000-0000C7020000}"/>
+    <hyperlink ref="C721" r:id="rId713" xr:uid="{00000000-0004-0000-0000-0000C8020000}"/>
+    <hyperlink ref="C722" r:id="rId714" xr:uid="{00000000-0004-0000-0000-0000C9020000}"/>
+    <hyperlink ref="C723" r:id="rId715" xr:uid="{00000000-0004-0000-0000-0000CA020000}"/>
+    <hyperlink ref="C724" r:id="rId716" xr:uid="{00000000-0004-0000-0000-0000CB020000}"/>
+    <hyperlink ref="C725" r:id="rId717" xr:uid="{00000000-0004-0000-0000-0000CC020000}"/>
+    <hyperlink ref="C726" r:id="rId718" xr:uid="{00000000-0004-0000-0000-0000CD020000}"/>
+    <hyperlink ref="C727" r:id="rId719" xr:uid="{00000000-0004-0000-0000-0000CE020000}"/>
+    <hyperlink ref="C728" r:id="rId720" xr:uid="{00000000-0004-0000-0000-0000CF020000}"/>
+    <hyperlink ref="C729" r:id="rId721" xr:uid="{00000000-0004-0000-0000-0000D0020000}"/>
+    <hyperlink ref="C730" r:id="rId722" xr:uid="{00000000-0004-0000-0000-0000D1020000}"/>
+    <hyperlink ref="C731" r:id="rId723" xr:uid="{00000000-0004-0000-0000-0000D2020000}"/>
+    <hyperlink ref="C46" r:id="rId724" xr:uid="{00000000-0004-0000-0000-0000D3020000}"/>
+    <hyperlink ref="C47" r:id="rId725" xr:uid="{00000000-0004-0000-0000-0000D4020000}"/>
+    <hyperlink ref="C732" r:id="rId726" xr:uid="{00000000-0004-0000-0000-0000D5020000}"/>
+    <hyperlink ref="C733" r:id="rId727" xr:uid="{00000000-0004-0000-0000-0000D6020000}"/>
+    <hyperlink ref="C734" r:id="rId728" xr:uid="{00000000-0004-0000-0000-0000D7020000}"/>
+    <hyperlink ref="C735" r:id="rId729" xr:uid="{00000000-0004-0000-0000-0000D8020000}"/>
+    <hyperlink ref="C736" r:id="rId730" xr:uid="{00000000-0004-0000-0000-0000D9020000}"/>
+    <hyperlink ref="C48" r:id="rId731" xr:uid="{00000000-0004-0000-0000-0000DA020000}"/>
+    <hyperlink ref="C49" r:id="rId732" xr:uid="{00000000-0004-0000-0000-0000DB020000}"/>
+    <hyperlink ref="C737" r:id="rId733" xr:uid="{00000000-0004-0000-0000-0000DC020000}"/>
+    <hyperlink ref="C738" r:id="rId734" xr:uid="{00000000-0004-0000-0000-0000DD020000}"/>
+    <hyperlink ref="C739" r:id="rId735" xr:uid="{00000000-0004-0000-0000-0000DE020000}"/>
+    <hyperlink ref="C740" r:id="rId736" xr:uid="{00000000-0004-0000-0000-0000DF020000}"/>
+    <hyperlink ref="C741" r:id="rId737" xr:uid="{00000000-0004-0000-0000-0000E0020000}"/>
+    <hyperlink ref="C742" r:id="rId738" xr:uid="{00000000-0004-0000-0000-0000E1020000}"/>
+    <hyperlink ref="C743" r:id="rId739" xr:uid="{00000000-0004-0000-0000-0000E2020000}"/>
+    <hyperlink ref="C744" r:id="rId740" xr:uid="{00000000-0004-0000-0000-0000E3020000}"/>
+    <hyperlink ref="C50" r:id="rId741" xr:uid="{00000000-0004-0000-0000-0000E4020000}"/>
+    <hyperlink ref="C745" r:id="rId742" xr:uid="{00000000-0004-0000-0000-0000E5020000}"/>
+    <hyperlink ref="C746" r:id="rId743" xr:uid="{00000000-0004-0000-0000-0000E6020000}"/>
+    <hyperlink ref="C747" r:id="rId744" xr:uid="{00000000-0004-0000-0000-0000E7020000}"/>
+    <hyperlink ref="C748" r:id="rId745" xr:uid="{00000000-0004-0000-0000-0000E8020000}"/>
+    <hyperlink ref="C749" r:id="rId746" xr:uid="{00000000-0004-0000-0000-0000E9020000}"/>
+    <hyperlink ref="C750" r:id="rId747" xr:uid="{00000000-0004-0000-0000-0000EA020000}"/>
+    <hyperlink ref="C751" r:id="rId748" xr:uid="{00000000-0004-0000-0000-0000EB020000}"/>
+    <hyperlink ref="C752" r:id="rId749" xr:uid="{00000000-0004-0000-0000-0000EC020000}"/>
+    <hyperlink ref="C753" r:id="rId750" xr:uid="{00000000-0004-0000-0000-0000ED020000}"/>
+    <hyperlink ref="C51" r:id="rId751" xr:uid="{00000000-0004-0000-0000-0000EE020000}"/>
+    <hyperlink ref="C754" r:id="rId752" xr:uid="{00000000-0004-0000-0000-0000EF020000}"/>
+    <hyperlink ref="C755" r:id="rId753" xr:uid="{00000000-0004-0000-0000-0000F0020000}"/>
+    <hyperlink ref="C756" r:id="rId754" xr:uid="{00000000-0004-0000-0000-0000F1020000}"/>
+    <hyperlink ref="C757" r:id="rId755" xr:uid="{00000000-0004-0000-0000-0000F2020000}"/>
+    <hyperlink ref="C758" r:id="rId756" xr:uid="{00000000-0004-0000-0000-0000F3020000}"/>
+    <hyperlink ref="C759" r:id="rId757" xr:uid="{00000000-0004-0000-0000-0000F4020000}"/>
+    <hyperlink ref="C760" r:id="rId758" xr:uid="{00000000-0004-0000-0000-0000F5020000}"/>
+    <hyperlink ref="C761" r:id="rId759" xr:uid="{00000000-0004-0000-0000-0000F6020000}"/>
+    <hyperlink ref="C762" r:id="rId760" xr:uid="{00000000-0004-0000-0000-0000F7020000}"/>
+    <hyperlink ref="C763" r:id="rId761" xr:uid="{00000000-0004-0000-0000-0000F8020000}"/>
+    <hyperlink ref="C764" r:id="rId762" xr:uid="{00000000-0004-0000-0000-0000F9020000}"/>
+    <hyperlink ref="C52" r:id="rId763" xr:uid="{00000000-0004-0000-0000-0000FA020000}"/>
+    <hyperlink ref="C765" r:id="rId764" xr:uid="{00000000-0004-0000-0000-0000FB020000}"/>
+    <hyperlink ref="C766" r:id="rId765" xr:uid="{00000000-0004-0000-0000-0000FC020000}"/>
+    <hyperlink ref="C767" r:id="rId766" xr:uid="{00000000-0004-0000-0000-0000FD020000}"/>
+    <hyperlink ref="C768" r:id="rId767" xr:uid="{00000000-0004-0000-0000-0000FE020000}"/>
+    <hyperlink ref="C769" r:id="rId768" xr:uid="{00000000-0004-0000-0000-0000FF020000}"/>
+    <hyperlink ref="C770" r:id="rId769" xr:uid="{00000000-0004-0000-0000-000000030000}"/>
+    <hyperlink ref="C771" r:id="rId770" xr:uid="{00000000-0004-0000-0000-000001030000}"/>
+    <hyperlink ref="C772" r:id="rId771" xr:uid="{00000000-0004-0000-0000-000002030000}"/>
+    <hyperlink ref="C773" r:id="rId772" xr:uid="{00000000-0004-0000-0000-000003030000}"/>
+    <hyperlink ref="C774" r:id="rId773" xr:uid="{00000000-0004-0000-0000-000004030000}"/>
+    <hyperlink ref="C775" r:id="rId774" xr:uid="{00000000-0004-0000-0000-000005030000}"/>
+    <hyperlink ref="C776" r:id="rId775" xr:uid="{00000000-0004-0000-0000-000006030000}"/>
+    <hyperlink ref="C777" r:id="rId776" xr:uid="{00000000-0004-0000-0000-000007030000}"/>
+    <hyperlink ref="C778" r:id="rId777" xr:uid="{00000000-0004-0000-0000-000008030000}"/>
+    <hyperlink ref="C779" r:id="rId778" xr:uid="{00000000-0004-0000-0000-000009030000}"/>
+    <hyperlink ref="C780" r:id="rId779" xr:uid="{00000000-0004-0000-0000-00000A030000}"/>
+    <hyperlink ref="C781" r:id="rId780" xr:uid="{00000000-0004-0000-0000-00000B030000}"/>
+    <hyperlink ref="C782" r:id="rId781" xr:uid="{00000000-0004-0000-0000-00000C030000}"/>
+    <hyperlink ref="C783" r:id="rId782" xr:uid="{00000000-0004-0000-0000-00000D030000}"/>
+    <hyperlink ref="C53" r:id="rId783" xr:uid="{00000000-0004-0000-0000-00000E030000}"/>
+    <hyperlink ref="C784" r:id="rId784" xr:uid="{00000000-0004-0000-0000-00000F030000}"/>
+    <hyperlink ref="C785" r:id="rId785" xr:uid="{00000000-0004-0000-0000-000010030000}"/>
+    <hyperlink ref="C786" r:id="rId786" xr:uid="{00000000-0004-0000-0000-000011030000}"/>
+    <hyperlink ref="C787" r:id="rId787" xr:uid="{00000000-0004-0000-0000-000012030000}"/>
+    <hyperlink ref="C788" r:id="rId788" xr:uid="{00000000-0004-0000-0000-000013030000}"/>
+    <hyperlink ref="C54" r:id="rId789" xr:uid="{00000000-0004-0000-0000-000014030000}"/>
+    <hyperlink ref="C789" r:id="rId790" xr:uid="{00000000-0004-0000-0000-000015030000}"/>
+    <hyperlink ref="C790" r:id="rId791" xr:uid="{00000000-0004-0000-0000-000016030000}"/>
+    <hyperlink ref="C791" r:id="rId792" xr:uid="{00000000-0004-0000-0000-000017030000}"/>
+    <hyperlink ref="C792" r:id="rId793" xr:uid="{00000000-0004-0000-0000-000018030000}"/>
+    <hyperlink ref="C793" r:id="rId794" xr:uid="{00000000-0004-0000-0000-000019030000}"/>
+    <hyperlink ref="C794" r:id="rId795" xr:uid="{00000000-0004-0000-0000-00001A030000}"/>
+    <hyperlink ref="C795" r:id="rId796" xr:uid="{00000000-0004-0000-0000-00001B030000}"/>
+    <hyperlink ref="C796" r:id="rId797" xr:uid="{00000000-0004-0000-0000-00001C030000}"/>
+    <hyperlink ref="C797" r:id="rId798" xr:uid="{00000000-0004-0000-0000-00001D030000}"/>
+    <hyperlink ref="C798" r:id="rId799" xr:uid="{00000000-0004-0000-0000-00001E030000}"/>
+    <hyperlink ref="C799" r:id="rId800" xr:uid="{00000000-0004-0000-0000-00001F030000}"/>
+    <hyperlink ref="C800" r:id="rId801" xr:uid="{00000000-0004-0000-0000-000020030000}"/>
+    <hyperlink ref="C801" r:id="rId802" xr:uid="{00000000-0004-0000-0000-000021030000}"/>
+    <hyperlink ref="C802" r:id="rId803" xr:uid="{00000000-0004-0000-0000-000022030000}"/>
+    <hyperlink ref="C817" r:id="rId804" xr:uid="{00000000-0004-0000-0000-000023030000}"/>
+    <hyperlink ref="C55" r:id="rId805" xr:uid="{00000000-0004-0000-0000-000024030000}"/>
+    <hyperlink ref="C803" r:id="rId806" xr:uid="{00000000-0004-0000-0000-000025030000}"/>
+    <hyperlink ref="C804" r:id="rId807" xr:uid="{00000000-0004-0000-0000-000026030000}"/>
+    <hyperlink ref="C805" r:id="rId808" xr:uid="{00000000-0004-0000-0000-000027030000}"/>
+    <hyperlink ref="C806" r:id="rId809" xr:uid="{00000000-0004-0000-0000-000028030000}"/>
+    <hyperlink ref="C818" r:id="rId810" xr:uid="{00000000-0004-0000-0000-000029030000}"/>
+    <hyperlink ref="C807" r:id="rId811" xr:uid="{00000000-0004-0000-0000-00002A030000}"/>
+    <hyperlink ref="C808" r:id="rId812" xr:uid="{00000000-0004-0000-0000-00002B030000}"/>
+    <hyperlink ref="C809" r:id="rId813" xr:uid="{00000000-0004-0000-0000-00002C030000}"/>
+    <hyperlink ref="C810" r:id="rId814" xr:uid="{00000000-0004-0000-0000-00002D030000}"/>
+    <hyperlink ref="C811" r:id="rId815" xr:uid="{00000000-0004-0000-0000-00002E030000}"/>
+    <hyperlink ref="C812" r:id="rId816" xr:uid="{00000000-0004-0000-0000-00002F030000}"/>
+    <hyperlink ref="C813" r:id="rId817" xr:uid="{00000000-0004-0000-0000-000030030000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17556,7 +17661,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>1629</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -17564,26 +17669,26 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>1630</v>
+        <v>1640</v>
       </c>
       <c r="B3" t="s">
-        <v>1631</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>1632</v>
+        <v>1642</v>
       </c>
       <c r="B4" t="s">
-        <v>1633</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>1634</v>
+        <v>1644</v>
       </c>
       <c r="B5" t="s">
-        <v>1635</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -17591,26 +17696,26 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>1636</v>
+        <v>1646</v>
       </c>
       <c r="B7" t="s">
-        <v>1637</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>1636</v>
+        <v>1646</v>
       </c>
       <c r="B8" t="s">
-        <v>1638</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>1636</v>
+        <v>1646</v>
       </c>
       <c r="B9" t="s">
-        <v>1639</v>
+        <v>1649</v>
       </c>
     </row>
   </sheetData>

--- a/data/danish_artwork_review.xlsx
+++ b/data/danish_artwork_review.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EPGoal\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77998F98-2650-4853-BFDA-D803C775E18C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F14445D1-29E5-478C-88EB-440F04A3BF1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5380,24 +5380,24 @@
     </row>
     <row r="2" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>7</v>
@@ -5408,10 +5408,10 @@
     </row>
     <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>67</v>
+        <v>105</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>106</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>7</v>
@@ -5422,10 +5422,10 @@
     </row>
     <row r="5" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>7</v>
@@ -5436,10 +5436,10 @@
     </row>
     <row r="6" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>107</v>
+        <v>147</v>
       </c>
       <c r="B6" t="s">
-        <v>108</v>
+        <v>148</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>7</v>
@@ -5450,10 +5450,10 @@
     </row>
     <row r="7" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B7" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>7</v>
@@ -5464,10 +5464,10 @@
     </row>
     <row r="8" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B8" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>7</v>
@@ -5478,10 +5478,10 @@
     </row>
     <row r="9" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>151</v>
+        <v>177</v>
       </c>
       <c r="B9" t="s">
-        <v>152</v>
+        <v>178</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>7</v>
@@ -5492,10 +5492,10 @@
     </row>
     <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="B10" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>7</v>
@@ -5506,10 +5506,10 @@
     </row>
     <row r="11" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>183</v>
+        <v>263</v>
       </c>
       <c r="B11" t="s">
-        <v>184</v>
+        <v>264</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>7</v>
@@ -5520,10 +5520,10 @@
     </row>
     <row r="12" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B12" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>7</v>
@@ -5534,10 +5534,10 @@
     </row>
     <row r="13" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B13" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>7</v>
@@ -5548,10 +5548,10 @@
     </row>
     <row r="14" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="B14" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>7</v>
@@ -5562,10 +5562,10 @@
     </row>
     <row r="15" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>283</v>
+        <v>305</v>
       </c>
       <c r="B15" t="s">
-        <v>284</v>
+        <v>306</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>7</v>
@@ -5576,10 +5576,10 @@
     </row>
     <row r="16" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>305</v>
+        <v>339</v>
       </c>
       <c r="B16" t="s">
-        <v>306</v>
+        <v>340</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>7</v>
@@ -5590,10 +5590,10 @@
     </row>
     <row r="17" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>339</v>
+        <v>377</v>
       </c>
       <c r="B17" t="s">
-        <v>340</v>
+        <v>378</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>7</v>
@@ -5604,10 +5604,10 @@
     </row>
     <row r="18" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="B18" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>7</v>
@@ -5618,10 +5618,10 @@
     </row>
     <row r="19" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="B19" t="s">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>7</v>
@@ -5632,10 +5632,10 @@
     </row>
     <row r="20" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>399</v>
+        <v>437</v>
       </c>
       <c r="B20" t="s">
-        <v>400</v>
+        <v>438</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>7</v>
@@ -5646,10 +5646,10 @@
     </row>
     <row r="21" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>437</v>
+        <v>495</v>
       </c>
       <c r="B21" t="s">
-        <v>438</v>
+        <v>496</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>7</v>
@@ -5660,10 +5660,10 @@
     </row>
     <row r="22" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>495</v>
+        <v>505</v>
       </c>
       <c r="B22" t="s">
-        <v>496</v>
+        <v>506</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>7</v>
@@ -5674,10 +5674,10 @@
     </row>
     <row r="23" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>505</v>
+        <v>525</v>
       </c>
       <c r="B23" t="s">
-        <v>506</v>
+        <v>526</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>7</v>
@@ -5688,10 +5688,10 @@
     </row>
     <row r="24" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>525</v>
+        <v>565</v>
       </c>
       <c r="B24" t="s">
-        <v>526</v>
+        <v>566</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>7</v>
@@ -5702,10 +5702,10 @@
     </row>
     <row r="25" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>565</v>
+        <v>585</v>
       </c>
       <c r="B25" t="s">
-        <v>566</v>
+        <v>586</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>7</v>
@@ -5716,10 +5716,10 @@
     </row>
     <row r="26" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>585</v>
+        <v>643</v>
       </c>
       <c r="B26" t="s">
-        <v>586</v>
+        <v>644</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>7</v>
@@ -5730,10 +5730,10 @@
     </row>
     <row r="27" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="B27" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>7</v>
@@ -5744,10 +5744,10 @@
     </row>
     <row r="28" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>645</v>
+        <v>657</v>
       </c>
       <c r="B28" t="s">
-        <v>646</v>
+        <v>658</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>7</v>
@@ -5758,10 +5758,10 @@
     </row>
     <row r="29" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>657</v>
+        <v>839</v>
       </c>
       <c r="B29" t="s">
-        <v>658</v>
+        <v>840</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>7</v>
@@ -5772,10 +5772,10 @@
     </row>
     <row r="30" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>839</v>
+        <v>853</v>
       </c>
       <c r="B30" t="s">
-        <v>840</v>
+        <v>854</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>7</v>
@@ -5786,10 +5786,10 @@
     </row>
     <row r="31" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>853</v>
+        <v>893</v>
       </c>
       <c r="B31" t="s">
-        <v>854</v>
+        <v>894</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>7</v>
@@ -5800,10 +5800,10 @@
     </row>
     <row r="32" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>893</v>
+        <v>907</v>
       </c>
       <c r="B32" t="s">
-        <v>894</v>
+        <v>908</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>7</v>
@@ -5814,10 +5814,10 @@
     </row>
     <row r="33" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>907</v>
+        <v>931</v>
       </c>
       <c r="B33" t="s">
-        <v>908</v>
+        <v>932</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>7</v>
@@ -5828,10 +5828,10 @@
     </row>
     <row r="34" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>931</v>
+        <v>947</v>
       </c>
       <c r="B34" t="s">
-        <v>932</v>
+        <v>948</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>7</v>
@@ -5842,10 +5842,10 @@
     </row>
     <row r="35" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>947</v>
+        <v>1037</v>
       </c>
       <c r="B35" t="s">
-        <v>948</v>
+        <v>1038</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>7</v>
@@ -5856,10 +5856,10 @@
     </row>
     <row r="36" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>1037</v>
+        <v>1093</v>
       </c>
       <c r="B36" t="s">
-        <v>1038</v>
+        <v>1094</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>7</v>
@@ -5870,10 +5870,10 @@
     </row>
     <row r="37" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>1093</v>
+        <v>1237</v>
       </c>
       <c r="B37" t="s">
-        <v>1094</v>
+        <v>1238</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>7</v>
@@ -5884,10 +5884,10 @@
     </row>
     <row r="38" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>1237</v>
+        <v>1265</v>
       </c>
       <c r="B38" t="s">
-        <v>1238</v>
+        <v>1266</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>7</v>
@@ -5898,10 +5898,10 @@
     </row>
     <row r="39" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>1265</v>
+        <v>1293</v>
       </c>
       <c r="B39" t="s">
-        <v>1266</v>
+        <v>1294</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>7</v>
@@ -5912,10 +5912,10 @@
     </row>
     <row r="40" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>1293</v>
+        <v>1303</v>
       </c>
       <c r="B40" t="s">
-        <v>1294</v>
+        <v>1304</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>7</v>
@@ -5926,10 +5926,10 @@
     </row>
     <row r="41" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>1303</v>
+        <v>1309</v>
       </c>
       <c r="B41" t="s">
-        <v>1304</v>
+        <v>1310</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>7</v>
@@ -5940,10 +5940,10 @@
     </row>
     <row r="42" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>1309</v>
+        <v>1323</v>
       </c>
       <c r="B42" t="s">
-        <v>1310</v>
+        <v>1324</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>7</v>
@@ -5954,10 +5954,10 @@
     </row>
     <row r="43" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>1323</v>
+        <v>1327</v>
       </c>
       <c r="B43" t="s">
-        <v>1324</v>
+        <v>1328</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>7</v>
@@ -5968,10 +5968,10 @@
     </row>
     <row r="44" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>1327</v>
+        <v>1405</v>
       </c>
       <c r="B44" t="s">
-        <v>1328</v>
+        <v>1406</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>7</v>
@@ -5982,10 +5982,10 @@
     </row>
     <row r="45" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>1405</v>
+        <v>1451</v>
       </c>
       <c r="B45" t="s">
-        <v>1406</v>
+        <v>1452</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>7</v>
@@ -5996,10 +5996,10 @@
     </row>
     <row r="46" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="B46" t="s">
-        <v>1452</v>
+        <v>1454</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>7</v>
@@ -6010,10 +6010,10 @@
     </row>
     <row r="47" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>1453</v>
+        <v>1465</v>
       </c>
       <c r="B47" t="s">
-        <v>1454</v>
+        <v>1466</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>7</v>
@@ -6024,10 +6024,10 @@
     </row>
     <row r="48" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="B48" t="s">
-        <v>1466</v>
+        <v>1468</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>7</v>
@@ -6038,10 +6038,10 @@
     </row>
     <row r="49" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>1467</v>
+        <v>1485</v>
       </c>
       <c r="B49" t="s">
-        <v>1468</v>
+        <v>1486</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>7</v>
@@ -6052,10 +6052,10 @@
     </row>
     <row r="50" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>1485</v>
+        <v>1505</v>
       </c>
       <c r="B50" t="s">
-        <v>1486</v>
+        <v>1506</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>7</v>
@@ -6066,10 +6066,10 @@
     </row>
     <row r="51" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>1505</v>
+        <v>1529</v>
       </c>
       <c r="B51" t="s">
-        <v>1506</v>
+        <v>1530</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>7</v>
@@ -6080,10 +6080,10 @@
     </row>
     <row r="52" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>1529</v>
+        <v>1569</v>
       </c>
       <c r="B52" t="s">
-        <v>1530</v>
+        <v>1570</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>7</v>
@@ -6094,10 +6094,10 @@
     </row>
     <row r="53" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>1569</v>
+        <v>1581</v>
       </c>
       <c r="B53" t="s">
-        <v>1570</v>
+        <v>1582</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>7</v>
@@ -6108,10 +6108,10 @@
     </row>
     <row r="54" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>1581</v>
+        <v>1613</v>
       </c>
       <c r="B54" t="s">
-        <v>1582</v>
+        <v>1614</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>7</v>
@@ -6122,15 +6122,15 @@
     </row>
     <row r="55" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>1613</v>
+        <v>6</v>
       </c>
       <c r="B55" t="s">
-        <v>1614</v>
+        <v>6</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E55" t="s">
+      <c r="D55" t="s">
         <v>8</v>
       </c>
     </row>
@@ -11176,10 +11176,10 @@
     </row>
     <row r="416" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B416" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C416" s="2" t="s">
         <v>7</v>
@@ -11190,10 +11190,10 @@
     </row>
     <row r="417" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="B417" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="C417" s="2" t="s">
         <v>7</v>
@@ -11204,10 +11204,10 @@
     </row>
     <row r="418" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="B418" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="C418" s="2" t="s">
         <v>7</v>
@@ -11218,10 +11218,10 @@
     </row>
     <row r="419" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="B419" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="C419" s="2" t="s">
         <v>7</v>
@@ -11232,10 +11232,10 @@
     </row>
     <row r="420" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="B420" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="C420" s="2" t="s">
         <v>7</v>
@@ -11246,10 +11246,10 @@
     </row>
     <row r="421" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="B421" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="C421" s="2" t="s">
         <v>7</v>
@@ -11260,10 +11260,10 @@
     </row>
     <row r="422" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="B422" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="C422" s="2" t="s">
         <v>7</v>
@@ -11274,10 +11274,10 @@
     </row>
     <row r="423" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B423" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="C423" s="2" t="s">
         <v>7</v>
@@ -11288,10 +11288,10 @@
     </row>
     <row r="424" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="B424" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="C424" s="2" t="s">
         <v>7</v>
@@ -11302,10 +11302,10 @@
     </row>
     <row r="425" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="B425" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="C425" s="2" t="s">
         <v>7</v>
@@ -11316,10 +11316,10 @@
     </row>
     <row r="426" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="B426" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="C426" s="2" t="s">
         <v>7</v>
@@ -11330,10 +11330,10 @@
     </row>
     <row r="427" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="B427" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="C427" s="2" t="s">
         <v>7</v>
@@ -11344,10 +11344,10 @@
     </row>
     <row r="428" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="B428" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="C428" s="2" t="s">
         <v>7</v>
@@ -11358,10 +11358,10 @@
     </row>
     <row r="429" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="B429" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="C429" s="2" t="s">
         <v>7</v>
@@ -11372,10 +11372,10 @@
     </row>
     <row r="430" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="B430" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="C430" s="2" t="s">
         <v>7</v>
@@ -11386,10 +11386,10 @@
     </row>
     <row r="431" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
       <c r="B431" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="C431" s="2" t="s">
         <v>7</v>
@@ -11400,10 +11400,10 @@
     </row>
     <row r="432" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
       <c r="B432" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
       <c r="C432" s="2" t="s">
         <v>7</v>
@@ -11414,10 +11414,10 @@
     </row>
     <row r="433" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
       <c r="B433" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
       <c r="C433" s="2" t="s">
         <v>7</v>
@@ -11428,10 +11428,10 @@
     </row>
     <row r="434" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
       <c r="B434" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="C434" s="2" t="s">
         <v>7</v>
@@ -11442,10 +11442,10 @@
     </row>
     <row r="435" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="B435" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
       <c r="C435" s="2" t="s">
         <v>7</v>
@@ -11456,10 +11456,10 @@
     </row>
     <row r="436" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="B436" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="C436" s="2" t="s">
         <v>7</v>
@@ -11470,10 +11470,10 @@
     </row>
     <row r="437" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="B437" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="C437" s="2" t="s">
         <v>7</v>
@@ -11484,10 +11484,10 @@
     </row>
     <row r="438" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="B438" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="C438" s="2" t="s">
         <v>7</v>
@@ -11498,10 +11498,10 @@
     </row>
     <row r="439" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="B439" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="C439" s="2" t="s">
         <v>7</v>
@@ -11512,10 +11512,10 @@
     </row>
     <row r="440" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="B440" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="C440" s="2" t="s">
         <v>7</v>
@@ -11526,10 +11526,10 @@
     </row>
     <row r="441" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="B441" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="C441" s="2" t="s">
         <v>7</v>
@@ -11540,10 +11540,10 @@
     </row>
     <row r="442" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="B442" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="C442" s="2" t="s">
         <v>7</v>
@@ -11554,10 +11554,10 @@
     </row>
     <row r="443" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
-        <v>841</v>
+        <v>835</v>
       </c>
       <c r="B443" t="s">
-        <v>842</v>
+        <v>836</v>
       </c>
       <c r="C443" s="2" t="s">
         <v>7</v>
@@ -11568,10 +11568,10 @@
     </row>
     <row r="444" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
-        <v>843</v>
+        <v>837</v>
       </c>
       <c r="B444" t="s">
-        <v>844</v>
+        <v>838</v>
       </c>
       <c r="C444" s="2" t="s">
         <v>7</v>
@@ -11582,10 +11582,10 @@
     </row>
     <row r="445" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
-        <v>845</v>
+        <v>841</v>
       </c>
       <c r="B445" t="s">
-        <v>846</v>
+        <v>842</v>
       </c>
       <c r="C445" s="2" t="s">
         <v>7</v>
@@ -11596,10 +11596,10 @@
     </row>
     <row r="446" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="B446" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="C446" s="2" t="s">
         <v>7</v>
@@ -11610,10 +11610,10 @@
     </row>
     <row r="447" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="B447" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="C447" s="2" t="s">
         <v>7</v>
@@ -11624,10 +11624,10 @@
     </row>
     <row r="448" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="B448" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="C448" s="2" t="s">
         <v>7</v>
@@ -11638,10 +11638,10 @@
     </row>
     <row r="449" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>855</v>
+        <v>849</v>
       </c>
       <c r="B449" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
       <c r="C449" s="2" t="s">
         <v>7</v>
@@ -11652,10 +11652,10 @@
     </row>
     <row r="450" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
-        <v>857</v>
+        <v>851</v>
       </c>
       <c r="B450" t="s">
-        <v>858</v>
+        <v>852</v>
       </c>
       <c r="C450" s="2" t="s">
         <v>7</v>
@@ -11666,10 +11666,10 @@
     </row>
     <row r="451" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="B451" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="C451" s="2" t="s">
         <v>7</v>
@@ -11680,10 +11680,10 @@
     </row>
     <row r="452" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
       <c r="B452" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="C452" s="2" t="s">
         <v>7</v>
@@ -11694,10 +11694,10 @@
     </row>
     <row r="453" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
       <c r="B453" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="C453" s="2" t="s">
         <v>7</v>
@@ -11708,10 +11708,10 @@
     </row>
     <row r="454" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="B454" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="C454" s="2" t="s">
         <v>7</v>
@@ -11722,10 +11722,10 @@
     </row>
     <row r="455" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="B455" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="C455" s="2" t="s">
         <v>7</v>
@@ -11736,10 +11736,10 @@
     </row>
     <row r="456" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
       <c r="B456" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
       <c r="C456" s="2" t="s">
         <v>7</v>
@@ -11750,10 +11750,10 @@
     </row>
     <row r="457" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
       <c r="B457" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="C457" s="2" t="s">
         <v>7</v>
@@ -11764,10 +11764,10 @@
     </row>
     <row r="458" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
       <c r="B458" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="C458" s="2" t="s">
         <v>7</v>
@@ -11778,10 +11778,10 @@
     </row>
     <row r="459" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="B459" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="C459" s="2" t="s">
         <v>7</v>
@@ -11792,10 +11792,10 @@
     </row>
     <row r="460" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="B460" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
       <c r="C460" s="2" t="s">
         <v>7</v>
@@ -11806,10 +11806,10 @@
     </row>
     <row r="461" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
-        <v>879</v>
+        <v>875</v>
       </c>
       <c r="B461" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="C461" s="2" t="s">
         <v>7</v>
@@ -11820,10 +11820,10 @@
     </row>
     <row r="462" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
       <c r="B462" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
       <c r="C462" s="2" t="s">
         <v>7</v>
@@ -11834,10 +11834,10 @@
     </row>
     <row r="463" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
       <c r="B463" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
       <c r="C463" s="2" t="s">
         <v>7</v>
@@ -11848,10 +11848,10 @@
     </row>
     <row r="464" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="B464" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="C464" s="2" t="s">
         <v>7</v>
@@ -11862,10 +11862,10 @@
     </row>
     <row r="465" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="B465" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
       <c r="C465" s="2" t="s">
         <v>7</v>
@@ -11876,10 +11876,10 @@
     </row>
     <row r="466" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
       <c r="B466" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="C466" s="2" t="s">
         <v>7</v>
@@ -11890,10 +11890,10 @@
     </row>
     <row r="467" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="B467" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="C467" s="2" t="s">
         <v>7</v>
@@ -11904,10 +11904,10 @@
     </row>
     <row r="468" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>895</v>
+        <v>889</v>
       </c>
       <c r="B468" t="s">
-        <v>896</v>
+        <v>890</v>
       </c>
       <c r="C468" s="2" t="s">
         <v>7</v>
@@ -11918,10 +11918,10 @@
     </row>
     <row r="469" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>897</v>
+        <v>891</v>
       </c>
       <c r="B469" t="s">
-        <v>898</v>
+        <v>892</v>
       </c>
       <c r="C469" s="2" t="s">
         <v>7</v>
@@ -11932,10 +11932,10 @@
     </row>
     <row r="470" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>899</v>
+        <v>895</v>
       </c>
       <c r="B470" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
       <c r="C470" s="2" t="s">
         <v>7</v>
@@ -11946,10 +11946,10 @@
     </row>
     <row r="471" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
       <c r="B471" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
       <c r="C471" s="2" t="s">
         <v>7</v>
@@ -11960,10 +11960,10 @@
     </row>
     <row r="472" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
       <c r="B472" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
       <c r="C472" s="2" t="s">
         <v>7</v>
@@ -11974,10 +11974,10 @@
     </row>
     <row r="473" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="B473" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
       <c r="C473" s="2" t="s">
         <v>7</v>
@@ -11988,10 +11988,10 @@
     </row>
     <row r="474" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
-        <v>909</v>
+        <v>903</v>
       </c>
       <c r="B474" t="s">
-        <v>910</v>
+        <v>904</v>
       </c>
       <c r="C474" s="2" t="s">
         <v>7</v>
@@ -12002,10 +12002,10 @@
     </row>
     <row r="475" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
-        <v>911</v>
+        <v>905</v>
       </c>
       <c r="B475" t="s">
-        <v>912</v>
+        <v>906</v>
       </c>
       <c r="C475" s="2" t="s">
         <v>7</v>
@@ -12016,10 +12016,10 @@
     </row>
     <row r="476" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="B476" t="s">
-        <v>914</v>
+        <v>910</v>
       </c>
       <c r="C476" s="2" t="s">
         <v>7</v>
@@ -12030,10 +12030,10 @@
     </row>
     <row r="477" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
       <c r="B477" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
       <c r="C477" s="2" t="s">
         <v>7</v>
@@ -12044,10 +12044,10 @@
     </row>
     <row r="478" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
       <c r="B478" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="C478" s="2" t="s">
         <v>7</v>
@@ -12058,10 +12058,10 @@
     </row>
     <row r="479" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
       <c r="B479" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="C479" s="2" t="s">
         <v>7</v>
@@ -12072,10 +12072,10 @@
     </row>
     <row r="480" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="B480" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="C480" s="2" t="s">
         <v>7</v>
@@ -12086,10 +12086,10 @@
     </row>
     <row r="481" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
       <c r="B481" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="C481" s="2" t="s">
         <v>7</v>
@@ -12100,10 +12100,10 @@
     </row>
     <row r="482" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="B482" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
       <c r="C482" s="2" t="s">
         <v>7</v>
@@ -12114,10 +12114,10 @@
     </row>
     <row r="483" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="B483" t="s">
-        <v>928</v>
+        <v>924</v>
       </c>
       <c r="C483" s="2" t="s">
         <v>7</v>
@@ -12128,10 +12128,10 @@
     </row>
     <row r="484" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="B484" t="s">
-        <v>930</v>
+        <v>926</v>
       </c>
       <c r="C484" s="2" t="s">
         <v>7</v>
@@ -12142,10 +12142,10 @@
     </row>
     <row r="485" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>933</v>
+        <v>927</v>
       </c>
       <c r="B485" t="s">
-        <v>934</v>
+        <v>928</v>
       </c>
       <c r="C485" s="2" t="s">
         <v>7</v>
@@ -12156,10 +12156,10 @@
     </row>
     <row r="486" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>935</v>
+        <v>929</v>
       </c>
       <c r="B486" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="C486" s="2" t="s">
         <v>7</v>
@@ -12170,10 +12170,10 @@
     </row>
     <row r="487" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
-        <v>937</v>
+        <v>933</v>
       </c>
       <c r="B487" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
       <c r="C487" s="2" t="s">
         <v>7</v>
@@ -12184,10 +12184,10 @@
     </row>
     <row r="488" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
-        <v>939</v>
+        <v>935</v>
       </c>
       <c r="B488" t="s">
-        <v>940</v>
+        <v>936</v>
       </c>
       <c r="C488" s="2" t="s">
         <v>7</v>
@@ -12198,10 +12198,10 @@
     </row>
     <row r="489" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
-        <v>941</v>
+        <v>937</v>
       </c>
       <c r="B489" t="s">
-        <v>942</v>
+        <v>938</v>
       </c>
       <c r="C489" s="2" t="s">
         <v>7</v>
@@ -12212,10 +12212,10 @@
     </row>
     <row r="490" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
       <c r="B490" t="s">
-        <v>944</v>
+        <v>940</v>
       </c>
       <c r="C490" s="2" t="s">
         <v>7</v>
@@ -12226,10 +12226,10 @@
     </row>
     <row r="491" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>945</v>
+        <v>941</v>
       </c>
       <c r="B491" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
       <c r="C491" s="2" t="s">
         <v>7</v>
@@ -12240,10 +12240,10 @@
     </row>
     <row r="492" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
-        <v>949</v>
+        <v>943</v>
       </c>
       <c r="B492" t="s">
-        <v>950</v>
+        <v>944</v>
       </c>
       <c r="C492" s="2" t="s">
         <v>7</v>
@@ -12254,10 +12254,10 @@
     </row>
     <row r="493" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>951</v>
+        <v>945</v>
       </c>
       <c r="B493" t="s">
-        <v>952</v>
+        <v>946</v>
       </c>
       <c r="C493" s="2" t="s">
         <v>7</v>
@@ -12268,10 +12268,10 @@
     </row>
     <row r="494" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
-        <v>953</v>
+        <v>949</v>
       </c>
       <c r="B494" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
       <c r="C494" s="2" t="s">
         <v>7</v>
@@ -12282,10 +12282,10 @@
     </row>
     <row r="495" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
-        <v>955</v>
+        <v>951</v>
       </c>
       <c r="B495" t="s">
-        <v>956</v>
+        <v>952</v>
       </c>
       <c r="C495" s="2" t="s">
         <v>7</v>
@@ -12296,10 +12296,10 @@
     </row>
     <row r="496" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
-        <v>957</v>
+        <v>953</v>
       </c>
       <c r="B496" t="s">
-        <v>958</v>
+        <v>954</v>
       </c>
       <c r="C496" s="2" t="s">
         <v>7</v>
@@ -12310,10 +12310,10 @@
     </row>
     <row r="497" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
-        <v>959</v>
+        <v>955</v>
       </c>
       <c r="B497" t="s">
-        <v>960</v>
+        <v>956</v>
       </c>
       <c r="C497" s="2" t="s">
         <v>7</v>
@@ -12324,10 +12324,10 @@
     </row>
     <row r="498" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
       <c r="B498" t="s">
-        <v>962</v>
+        <v>958</v>
       </c>
       <c r="C498" s="2" t="s">
         <v>7</v>
@@ -12338,10 +12338,10 @@
     </row>
     <row r="499" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="B499" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="C499" s="2" t="s">
         <v>7</v>
@@ -12352,10 +12352,10 @@
     </row>
     <row r="500" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="B500" t="s">
-        <v>966</v>
+        <v>962</v>
       </c>
       <c r="C500" s="2" t="s">
         <v>7</v>
@@ -12366,10 +12366,10 @@
     </row>
     <row r="501" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
-        <v>967</v>
+        <v>963</v>
       </c>
       <c r="B501" t="s">
-        <v>968</v>
+        <v>964</v>
       </c>
       <c r="C501" s="2" t="s">
         <v>7</v>
@@ -12380,10 +12380,10 @@
     </row>
     <row r="502" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
-        <v>969</v>
+        <v>965</v>
       </c>
       <c r="B502" t="s">
-        <v>970</v>
+        <v>966</v>
       </c>
       <c r="C502" s="2" t="s">
         <v>7</v>
@@ -12394,10 +12394,10 @@
     </row>
     <row r="503" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="B503" t="s">
-        <v>972</v>
+        <v>968</v>
       </c>
       <c r="C503" s="2" t="s">
         <v>7</v>
@@ -12408,10 +12408,10 @@
     </row>
     <row r="504" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
-        <v>973</v>
+        <v>969</v>
       </c>
       <c r="B504" t="s">
-        <v>974</v>
+        <v>970</v>
       </c>
       <c r="C504" s="2" t="s">
         <v>7</v>
@@ -12422,10 +12422,10 @@
     </row>
     <row r="505" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
-        <v>975</v>
+        <v>971</v>
       </c>
       <c r="B505" t="s">
-        <v>976</v>
+        <v>972</v>
       </c>
       <c r="C505" s="2" t="s">
         <v>7</v>
@@ -12436,10 +12436,10 @@
     </row>
     <row r="506" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
-        <v>977</v>
+        <v>973</v>
       </c>
       <c r="B506" t="s">
-        <v>978</v>
+        <v>974</v>
       </c>
       <c r="C506" s="2" t="s">
         <v>7</v>
@@ -12450,10 +12450,10 @@
     </row>
     <row r="507" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="B507" t="s">
-        <v>980</v>
+        <v>976</v>
       </c>
       <c r="C507" s="2" t="s">
         <v>7</v>
@@ -12464,10 +12464,10 @@
     </row>
     <row r="508" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
-        <v>981</v>
+        <v>977</v>
       </c>
       <c r="B508" t="s">
-        <v>982</v>
+        <v>978</v>
       </c>
       <c r="C508" s="2" t="s">
         <v>7</v>
@@ -12478,10 +12478,10 @@
     </row>
     <row r="509" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="B509" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
       <c r="C509" s="2" t="s">
         <v>7</v>
@@ -12492,10 +12492,10 @@
     </row>
     <row r="510" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
-        <v>985</v>
+        <v>981</v>
       </c>
       <c r="B510" t="s">
-        <v>986</v>
+        <v>982</v>
       </c>
       <c r="C510" s="2" t="s">
         <v>7</v>
@@ -12506,10 +12506,10 @@
     </row>
     <row r="511" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
-        <v>987</v>
+        <v>983</v>
       </c>
       <c r="B511" t="s">
-        <v>988</v>
+        <v>984</v>
       </c>
       <c r="C511" s="2" t="s">
         <v>7</v>
@@ -12520,10 +12520,10 @@
     </row>
     <row r="512" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
-        <v>989</v>
+        <v>985</v>
       </c>
       <c r="B512" t="s">
-        <v>990</v>
+        <v>986</v>
       </c>
       <c r="C512" s="2" t="s">
         <v>7</v>
@@ -12534,10 +12534,10 @@
     </row>
     <row r="513" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
-        <v>991</v>
+        <v>987</v>
       </c>
       <c r="B513" t="s">
-        <v>992</v>
+        <v>988</v>
       </c>
       <c r="C513" s="2" t="s">
         <v>7</v>
@@ -12548,10 +12548,10 @@
     </row>
     <row r="514" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
-        <v>993</v>
+        <v>989</v>
       </c>
       <c r="B514" t="s">
-        <v>994</v>
+        <v>990</v>
       </c>
       <c r="C514" s="2" t="s">
         <v>7</v>
@@ -12562,10 +12562,10 @@
     </row>
     <row r="515" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
-        <v>995</v>
+        <v>991</v>
       </c>
       <c r="B515" t="s">
-        <v>996</v>
+        <v>992</v>
       </c>
       <c r="C515" s="2" t="s">
         <v>7</v>
@@ -12576,10 +12576,10 @@
     </row>
     <row r="516" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
-        <v>997</v>
+        <v>993</v>
       </c>
       <c r="B516" t="s">
-        <v>998</v>
+        <v>994</v>
       </c>
       <c r="C516" s="2" t="s">
         <v>7</v>
@@ -12590,10 +12590,10 @@
     </row>
     <row r="517" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
-        <v>999</v>
+        <v>995</v>
       </c>
       <c r="B517" t="s">
-        <v>1000</v>
+        <v>996</v>
       </c>
       <c r="C517" s="2" t="s">
         <v>7</v>
@@ -12604,10 +12604,10 @@
     </row>
     <row r="518" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
-        <v>1001</v>
+        <v>997</v>
       </c>
       <c r="B518" t="s">
-        <v>1002</v>
+        <v>998</v>
       </c>
       <c r="C518" s="2" t="s">
         <v>7</v>
@@ -12618,10 +12618,10 @@
     </row>
     <row r="519" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
-        <v>1003</v>
+        <v>999</v>
       </c>
       <c r="B519" t="s">
-        <v>1004</v>
+        <v>1000</v>
       </c>
       <c r="C519" s="2" t="s">
         <v>7</v>
@@ -12632,10 +12632,10 @@
     </row>
     <row r="520" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
-        <v>1007</v>
+        <v>1001</v>
       </c>
       <c r="B520" t="s">
-        <v>1008</v>
+        <v>1002</v>
       </c>
       <c r="C520" s="2" t="s">
         <v>7</v>
@@ -12646,10 +12646,10 @@
     </row>
     <row r="521" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
-        <v>1009</v>
+        <v>1003</v>
       </c>
       <c r="B521" t="s">
-        <v>1010</v>
+        <v>1004</v>
       </c>
       <c r="C521" s="2" t="s">
         <v>7</v>
@@ -12660,10 +12660,10 @@
     </row>
     <row r="522" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
-        <v>1011</v>
+        <v>1005</v>
       </c>
       <c r="B522" t="s">
-        <v>1012</v>
+        <v>1006</v>
       </c>
       <c r="C522" s="2" t="s">
         <v>7</v>
@@ -12674,10 +12674,10 @@
     </row>
     <row r="523" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
-        <v>1013</v>
+        <v>1007</v>
       </c>
       <c r="B523" t="s">
-        <v>1014</v>
+        <v>1008</v>
       </c>
       <c r="C523" s="2" t="s">
         <v>7</v>
@@ -12688,10 +12688,10 @@
     </row>
     <row r="524" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
-        <v>1015</v>
+        <v>1009</v>
       </c>
       <c r="B524" t="s">
-        <v>1016</v>
+        <v>1010</v>
       </c>
       <c r="C524" s="2" t="s">
         <v>7</v>
@@ -12702,10 +12702,10 @@
     </row>
     <row r="525" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
-        <v>1017</v>
+        <v>1011</v>
       </c>
       <c r="B525" t="s">
-        <v>1018</v>
+        <v>1012</v>
       </c>
       <c r="C525" s="2" t="s">
         <v>7</v>
@@ -12716,10 +12716,10 @@
     </row>
     <row r="526" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
-        <v>1019</v>
+        <v>1013</v>
       </c>
       <c r="B526" t="s">
-        <v>1020</v>
+        <v>1014</v>
       </c>
       <c r="C526" s="2" t="s">
         <v>7</v>
@@ -12730,10 +12730,10 @@
     </row>
     <row r="527" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
-        <v>1021</v>
+        <v>1015</v>
       </c>
       <c r="B527" t="s">
-        <v>1022</v>
+        <v>1016</v>
       </c>
       <c r="C527" s="2" t="s">
         <v>7</v>
@@ -12744,10 +12744,10 @@
     </row>
     <row r="528" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
-        <v>1023</v>
+        <v>1017</v>
       </c>
       <c r="B528" t="s">
-        <v>1024</v>
+        <v>1018</v>
       </c>
       <c r="C528" s="2" t="s">
         <v>7</v>
@@ -12758,10 +12758,10 @@
     </row>
     <row r="529" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
-        <v>1025</v>
+        <v>1019</v>
       </c>
       <c r="B529" t="s">
-        <v>1026</v>
+        <v>1020</v>
       </c>
       <c r="C529" s="2" t="s">
         <v>7</v>
@@ -12772,10 +12772,10 @@
     </row>
     <row r="530" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
-        <v>1027</v>
+        <v>1021</v>
       </c>
       <c r="B530" t="s">
-        <v>1028</v>
+        <v>1022</v>
       </c>
       <c r="C530" s="2" t="s">
         <v>7</v>
@@ -12786,10 +12786,10 @@
     </row>
     <row r="531" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
-        <v>1029</v>
+        <v>1023</v>
       </c>
       <c r="B531" t="s">
-        <v>1030</v>
+        <v>1024</v>
       </c>
       <c r="C531" s="2" t="s">
         <v>7</v>
@@ -12800,10 +12800,10 @@
     </row>
     <row r="532" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
-        <v>1031</v>
+        <v>1025</v>
       </c>
       <c r="B532" t="s">
-        <v>1032</v>
+        <v>1026</v>
       </c>
       <c r="C532" s="2" t="s">
         <v>7</v>
@@ -12814,10 +12814,10 @@
     </row>
     <row r="533" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
-        <v>1033</v>
+        <v>1027</v>
       </c>
       <c r="B533" t="s">
-        <v>1034</v>
+        <v>1028</v>
       </c>
       <c r="C533" s="2" t="s">
         <v>7</v>
@@ -12828,10 +12828,10 @@
     </row>
     <row r="534" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
-        <v>1035</v>
+        <v>1029</v>
       </c>
       <c r="B534" t="s">
-        <v>1036</v>
+        <v>1030</v>
       </c>
       <c r="C534" s="2" t="s">
         <v>7</v>
@@ -12842,10 +12842,10 @@
     </row>
     <row r="535" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
-        <v>1039</v>
+        <v>1031</v>
       </c>
       <c r="B535" t="s">
-        <v>1040</v>
+        <v>1032</v>
       </c>
       <c r="C535" s="2" t="s">
         <v>7</v>
@@ -12856,10 +12856,10 @@
     </row>
     <row r="536" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
-        <v>1041</v>
+        <v>1033</v>
       </c>
       <c r="B536" t="s">
-        <v>1042</v>
+        <v>1034</v>
       </c>
       <c r="C536" s="2" t="s">
         <v>7</v>
@@ -12870,10 +12870,10 @@
     </row>
     <row r="537" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
-        <v>1043</v>
+        <v>1035</v>
       </c>
       <c r="B537" t="s">
-        <v>1044</v>
+        <v>1036</v>
       </c>
       <c r="C537" s="2" t="s">
         <v>7</v>
@@ -12884,10 +12884,10 @@
     </row>
     <row r="538" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
-        <v>1045</v>
+        <v>1039</v>
       </c>
       <c r="B538" t="s">
-        <v>1046</v>
+        <v>1040</v>
       </c>
       <c r="C538" s="2" t="s">
         <v>7</v>
@@ -12898,10 +12898,10 @@
     </row>
     <row r="539" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
-        <v>1047</v>
+        <v>1041</v>
       </c>
       <c r="B539" t="s">
-        <v>1048</v>
+        <v>1042</v>
       </c>
       <c r="C539" s="2" t="s">
         <v>7</v>
@@ -12912,10 +12912,10 @@
     </row>
     <row r="540" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
-        <v>1049</v>
+        <v>1043</v>
       </c>
       <c r="B540" t="s">
-        <v>1050</v>
+        <v>1044</v>
       </c>
       <c r="C540" s="2" t="s">
         <v>7</v>
@@ -12926,10 +12926,10 @@
     </row>
     <row r="541" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
-        <v>1051</v>
+        <v>1045</v>
       </c>
       <c r="B541" t="s">
-        <v>1052</v>
+        <v>1046</v>
       </c>
       <c r="C541" s="2" t="s">
         <v>7</v>
@@ -12940,10 +12940,10 @@
     </row>
     <row r="542" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
-        <v>1053</v>
+        <v>1047</v>
       </c>
       <c r="B542" t="s">
-        <v>1054</v>
+        <v>1048</v>
       </c>
       <c r="C542" s="2" t="s">
         <v>7</v>
@@ -12954,10 +12954,10 @@
     </row>
     <row r="543" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
-        <v>1055</v>
+        <v>1049</v>
       </c>
       <c r="B543" t="s">
-        <v>1056</v>
+        <v>1050</v>
       </c>
       <c r="C543" s="2" t="s">
         <v>7</v>
@@ -12968,10 +12968,10 @@
     </row>
     <row r="544" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="B544" t="s">
-        <v>1058</v>
+        <v>1052</v>
       </c>
       <c r="C544" s="2" t="s">
         <v>7</v>
@@ -12982,10 +12982,10 @@
     </row>
     <row r="545" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
-        <v>1059</v>
+        <v>1053</v>
       </c>
       <c r="B545" t="s">
-        <v>1060</v>
+        <v>1054</v>
       </c>
       <c r="C545" s="2" t="s">
         <v>7</v>
@@ -12996,10 +12996,10 @@
     </row>
     <row r="546" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
-        <v>1061</v>
+        <v>1055</v>
       </c>
       <c r="B546" t="s">
-        <v>1062</v>
+        <v>1056</v>
       </c>
       <c r="C546" s="2" t="s">
         <v>7</v>
@@ -13010,10 +13010,10 @@
     </row>
     <row r="547" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
-        <v>1063</v>
+        <v>1057</v>
       </c>
       <c r="B547" t="s">
-        <v>1064</v>
+        <v>1058</v>
       </c>
       <c r="C547" s="2" t="s">
         <v>7</v>
@@ -13024,10 +13024,10 @@
     </row>
     <row r="548" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
-        <v>1065</v>
+        <v>1059</v>
       </c>
       <c r="B548" t="s">
-        <v>1066</v>
+        <v>1060</v>
       </c>
       <c r="C548" s="2" t="s">
         <v>7</v>
@@ -13038,10 +13038,10 @@
     </row>
     <row r="549" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
-        <v>1067</v>
+        <v>1061</v>
       </c>
       <c r="B549" t="s">
-        <v>1068</v>
+        <v>1062</v>
       </c>
       <c r="C549" s="2" t="s">
         <v>7</v>
@@ -13052,10 +13052,10 @@
     </row>
     <row r="550" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
-        <v>1069</v>
+        <v>1063</v>
       </c>
       <c r="B550" t="s">
-        <v>1070</v>
+        <v>1064</v>
       </c>
       <c r="C550" s="2" t="s">
         <v>7</v>
@@ -13066,10 +13066,10 @@
     </row>
     <row r="551" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
-        <v>1071</v>
+        <v>1065</v>
       </c>
       <c r="B551" t="s">
-        <v>1072</v>
+        <v>1066</v>
       </c>
       <c r="C551" s="2" t="s">
         <v>7</v>
@@ -13080,10 +13080,10 @@
     </row>
     <row r="552" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
-        <v>1073</v>
+        <v>1067</v>
       </c>
       <c r="B552" t="s">
-        <v>1074</v>
+        <v>1068</v>
       </c>
       <c r="C552" s="2" t="s">
         <v>7</v>
@@ -13094,10 +13094,10 @@
     </row>
     <row r="553" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
-        <v>1075</v>
+        <v>1069</v>
       </c>
       <c r="B553" t="s">
-        <v>1076</v>
+        <v>1070</v>
       </c>
       <c r="C553" s="2" t="s">
         <v>7</v>
@@ -13108,10 +13108,10 @@
     </row>
     <row r="554" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
-        <v>1077</v>
+        <v>1071</v>
       </c>
       <c r="B554" t="s">
-        <v>1078</v>
+        <v>1072</v>
       </c>
       <c r="C554" s="2" t="s">
         <v>7</v>
@@ -13122,10 +13122,10 @@
     </row>
     <row r="555" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
-        <v>1079</v>
+        <v>1073</v>
       </c>
       <c r="B555" t="s">
-        <v>1080</v>
+        <v>1074</v>
       </c>
       <c r="C555" s="2" t="s">
         <v>7</v>
@@ -13136,10 +13136,10 @@
     </row>
     <row r="556" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
-        <v>1081</v>
+        <v>1075</v>
       </c>
       <c r="B556" t="s">
-        <v>1082</v>
+        <v>1076</v>
       </c>
       <c r="C556" s="2" t="s">
         <v>7</v>
@@ -13150,10 +13150,10 @@
     </row>
     <row r="557" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
-        <v>1083</v>
+        <v>1077</v>
       </c>
       <c r="B557" t="s">
-        <v>1084</v>
+        <v>1078</v>
       </c>
       <c r="C557" s="2" t="s">
         <v>7</v>
@@ -13164,10 +13164,10 @@
     </row>
     <row r="558" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
-        <v>1085</v>
+        <v>1079</v>
       </c>
       <c r="B558" t="s">
-        <v>1086</v>
+        <v>1080</v>
       </c>
       <c r="C558" s="2" t="s">
         <v>7</v>
@@ -13178,10 +13178,10 @@
     </row>
     <row r="559" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
-        <v>1087</v>
+        <v>1081</v>
       </c>
       <c r="B559" t="s">
-        <v>1088</v>
+        <v>1082</v>
       </c>
       <c r="C559" s="2" t="s">
         <v>7</v>
@@ -13192,10 +13192,10 @@
     </row>
     <row r="560" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
-        <v>1089</v>
+        <v>1083</v>
       </c>
       <c r="B560" t="s">
-        <v>1090</v>
+        <v>1084</v>
       </c>
       <c r="C560" s="2" t="s">
         <v>7</v>
@@ -13206,10 +13206,10 @@
     </row>
     <row r="561" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
-        <v>1091</v>
+        <v>1085</v>
       </c>
       <c r="B561" t="s">
-        <v>1092</v>
+        <v>1086</v>
       </c>
       <c r="C561" s="2" t="s">
         <v>7</v>
@@ -13220,10 +13220,10 @@
     </row>
     <row r="562" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
-        <v>1095</v>
+        <v>1087</v>
       </c>
       <c r="B562" t="s">
-        <v>1096</v>
+        <v>1088</v>
       </c>
       <c r="C562" s="2" t="s">
         <v>7</v>
@@ -13234,10 +13234,10 @@
     </row>
     <row r="563" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
-        <v>1097</v>
+        <v>1089</v>
       </c>
       <c r="B563" t="s">
-        <v>1098</v>
+        <v>1090</v>
       </c>
       <c r="C563" s="2" t="s">
         <v>7</v>
@@ -13248,10 +13248,10 @@
     </row>
     <row r="564" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
-        <v>1099</v>
+        <v>1091</v>
       </c>
       <c r="B564" t="s">
-        <v>1100</v>
+        <v>1092</v>
       </c>
       <c r="C564" s="2" t="s">
         <v>7</v>
@@ -13262,10 +13262,10 @@
     </row>
     <row r="565" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
-        <v>1101</v>
+        <v>1095</v>
       </c>
       <c r="B565" t="s">
-        <v>1102</v>
+        <v>1096</v>
       </c>
       <c r="C565" s="2" t="s">
         <v>7</v>
@@ -13276,10 +13276,10 @@
     </row>
     <row r="566" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
-        <v>1103</v>
+        <v>1097</v>
       </c>
       <c r="B566" t="s">
-        <v>1104</v>
+        <v>1098</v>
       </c>
       <c r="C566" s="2" t="s">
         <v>7</v>
@@ -13290,10 +13290,10 @@
     </row>
     <row r="567" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
-        <v>1105</v>
+        <v>1099</v>
       </c>
       <c r="B567" t="s">
-        <v>1106</v>
+        <v>1100</v>
       </c>
       <c r="C567" s="2" t="s">
         <v>7</v>
@@ -13304,10 +13304,10 @@
     </row>
     <row r="568" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
-        <v>1107</v>
+        <v>1101</v>
       </c>
       <c r="B568" t="s">
-        <v>1108</v>
+        <v>1102</v>
       </c>
       <c r="C568" s="2" t="s">
         <v>7</v>
@@ -13318,10 +13318,10 @@
     </row>
     <row r="569" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
-        <v>1109</v>
+        <v>1103</v>
       </c>
       <c r="B569" t="s">
-        <v>1110</v>
+        <v>1104</v>
       </c>
       <c r="C569" s="2" t="s">
         <v>7</v>
@@ -13332,10 +13332,10 @@
     </row>
     <row r="570" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
-        <v>1111</v>
+        <v>1105</v>
       </c>
       <c r="B570" t="s">
-        <v>1112</v>
+        <v>1106</v>
       </c>
       <c r="C570" s="2" t="s">
         <v>7</v>
@@ -13346,10 +13346,10 @@
     </row>
     <row r="571" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
-        <v>1113</v>
+        <v>1107</v>
       </c>
       <c r="B571" t="s">
-        <v>1114</v>
+        <v>1108</v>
       </c>
       <c r="C571" s="2" t="s">
         <v>7</v>
@@ -13360,10 +13360,10 @@
     </row>
     <row r="572" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
-        <v>1115</v>
+        <v>1109</v>
       </c>
       <c r="B572" t="s">
-        <v>1116</v>
+        <v>1110</v>
       </c>
       <c r="C572" s="2" t="s">
         <v>7</v>
@@ -13374,10 +13374,10 @@
     </row>
     <row r="573" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
-        <v>1117</v>
+        <v>1111</v>
       </c>
       <c r="B573" t="s">
-        <v>1118</v>
+        <v>1112</v>
       </c>
       <c r="C573" s="2" t="s">
         <v>7</v>
@@ -13388,10 +13388,10 @@
     </row>
     <row r="574" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
-        <v>1119</v>
+        <v>1113</v>
       </c>
       <c r="B574" t="s">
-        <v>1120</v>
+        <v>1114</v>
       </c>
       <c r="C574" s="2" t="s">
         <v>7</v>
@@ -13402,10 +13402,10 @@
     </row>
     <row r="575" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
-        <v>1121</v>
+        <v>1115</v>
       </c>
       <c r="B575" t="s">
-        <v>1122</v>
+        <v>1116</v>
       </c>
       <c r="C575" s="2" t="s">
         <v>7</v>
@@ -13416,10 +13416,10 @@
     </row>
     <row r="576" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
-        <v>1123</v>
+        <v>1117</v>
       </c>
       <c r="B576" t="s">
-        <v>1124</v>
+        <v>1118</v>
       </c>
       <c r="C576" s="2" t="s">
         <v>7</v>
@@ -13430,10 +13430,10 @@
     </row>
     <row r="577" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
-        <v>1125</v>
+        <v>1119</v>
       </c>
       <c r="B577" t="s">
-        <v>1126</v>
+        <v>1120</v>
       </c>
       <c r="C577" s="2" t="s">
         <v>7</v>
@@ -13444,10 +13444,10 @@
     </row>
     <row r="578" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
-        <v>1127</v>
+        <v>1121</v>
       </c>
       <c r="B578" t="s">
-        <v>1128</v>
+        <v>1122</v>
       </c>
       <c r="C578" s="2" t="s">
         <v>7</v>
@@ -13458,10 +13458,10 @@
     </row>
     <row r="579" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
-        <v>1129</v>
+        <v>1123</v>
       </c>
       <c r="B579" t="s">
-        <v>1130</v>
+        <v>1124</v>
       </c>
       <c r="C579" s="2" t="s">
         <v>7</v>
@@ -13472,10 +13472,10 @@
     </row>
     <row r="580" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
-        <v>1131</v>
+        <v>1125</v>
       </c>
       <c r="B580" t="s">
-        <v>1132</v>
+        <v>1126</v>
       </c>
       <c r="C580" s="2" t="s">
         <v>7</v>
@@ -13486,10 +13486,10 @@
     </row>
     <row r="581" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
-        <v>1133</v>
+        <v>1127</v>
       </c>
       <c r="B581" t="s">
-        <v>1134</v>
+        <v>1128</v>
       </c>
       <c r="C581" s="2" t="s">
         <v>7</v>
@@ -13500,10 +13500,10 @@
     </row>
     <row r="582" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
-        <v>1135</v>
+        <v>1129</v>
       </c>
       <c r="B582" t="s">
-        <v>1136</v>
+        <v>1130</v>
       </c>
       <c r="C582" s="2" t="s">
         <v>7</v>
@@ -13514,10 +13514,10 @@
     </row>
     <row r="583" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
-        <v>1137</v>
+        <v>1131</v>
       </c>
       <c r="B583" t="s">
-        <v>1138</v>
+        <v>1132</v>
       </c>
       <c r="C583" s="2" t="s">
         <v>7</v>
@@ -13528,10 +13528,10 @@
     </row>
     <row r="584" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
-        <v>1139</v>
+        <v>1133</v>
       </c>
       <c r="B584" t="s">
-        <v>1140</v>
+        <v>1134</v>
       </c>
       <c r="C584" s="2" t="s">
         <v>7</v>
@@ -13542,10 +13542,10 @@
     </row>
     <row r="585" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
-        <v>1141</v>
+        <v>1135</v>
       </c>
       <c r="B585" t="s">
-        <v>1142</v>
+        <v>1136</v>
       </c>
       <c r="C585" s="2" t="s">
         <v>7</v>
@@ -13556,10 +13556,10 @@
     </row>
     <row r="586" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
-        <v>1143</v>
+        <v>1137</v>
       </c>
       <c r="B586" t="s">
-        <v>1144</v>
+        <v>1138</v>
       </c>
       <c r="C586" s="2" t="s">
         <v>7</v>
@@ -13570,10 +13570,10 @@
     </row>
     <row r="587" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
-        <v>1145</v>
+        <v>1139</v>
       </c>
       <c r="B587" t="s">
-        <v>1146</v>
+        <v>1140</v>
       </c>
       <c r="C587" s="2" t="s">
         <v>7</v>
@@ -13584,10 +13584,10 @@
     </row>
     <row r="588" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
-        <v>1147</v>
+        <v>1141</v>
       </c>
       <c r="B588" t="s">
-        <v>1148</v>
+        <v>1142</v>
       </c>
       <c r="C588" s="2" t="s">
         <v>7</v>
@@ -13598,10 +13598,10 @@
     </row>
     <row r="589" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
-        <v>1149</v>
+        <v>1143</v>
       </c>
       <c r="B589" t="s">
-        <v>1150</v>
+        <v>1144</v>
       </c>
       <c r="C589" s="2" t="s">
         <v>7</v>
@@ -13612,10 +13612,10 @@
     </row>
     <row r="590" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
-        <v>1151</v>
+        <v>1145</v>
       </c>
       <c r="B590" t="s">
-        <v>1152</v>
+        <v>1146</v>
       </c>
       <c r="C590" s="2" t="s">
         <v>7</v>
@@ -13626,10 +13626,10 @@
     </row>
     <row r="591" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
-        <v>1153</v>
+        <v>1147</v>
       </c>
       <c r="B591" t="s">
-        <v>1154</v>
+        <v>1148</v>
       </c>
       <c r="C591" s="2" t="s">
         <v>7</v>
@@ -13640,10 +13640,10 @@
     </row>
     <row r="592" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
-        <v>1155</v>
+        <v>1149</v>
       </c>
       <c r="B592" t="s">
-        <v>1156</v>
+        <v>1150</v>
       </c>
       <c r="C592" s="2" t="s">
         <v>7</v>
@@ -13654,10 +13654,10 @@
     </row>
     <row r="593" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
-        <v>1157</v>
+        <v>1151</v>
       </c>
       <c r="B593" t="s">
-        <v>1158</v>
+        <v>1152</v>
       </c>
       <c r="C593" s="2" t="s">
         <v>7</v>
@@ -13668,10 +13668,10 @@
     </row>
     <row r="594" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
-        <v>1159</v>
+        <v>1153</v>
       </c>
       <c r="B594" t="s">
-        <v>1160</v>
+        <v>1154</v>
       </c>
       <c r="C594" s="2" t="s">
         <v>7</v>
@@ -13682,10 +13682,10 @@
     </row>
     <row r="595" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
-        <v>1161</v>
+        <v>1155</v>
       </c>
       <c r="B595" t="s">
-        <v>1162</v>
+        <v>1156</v>
       </c>
       <c r="C595" s="2" t="s">
         <v>7</v>
@@ -13696,10 +13696,10 @@
     </row>
     <row r="596" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
-        <v>1163</v>
+        <v>1157</v>
       </c>
       <c r="B596" t="s">
-        <v>1164</v>
+        <v>1158</v>
       </c>
       <c r="C596" s="2" t="s">
         <v>7</v>
@@ -13710,10 +13710,10 @@
     </row>
     <row r="597" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
-        <v>1165</v>
+        <v>1159</v>
       </c>
       <c r="B597" t="s">
-        <v>1166</v>
+        <v>1160</v>
       </c>
       <c r="C597" s="2" t="s">
         <v>7</v>
@@ -13724,10 +13724,10 @@
     </row>
     <row r="598" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
-        <v>1167</v>
+        <v>1161</v>
       </c>
       <c r="B598" t="s">
-        <v>1168</v>
+        <v>1162</v>
       </c>
       <c r="C598" s="2" t="s">
         <v>7</v>
@@ -13738,10 +13738,10 @@
     </row>
     <row r="599" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
-        <v>1169</v>
+        <v>1163</v>
       </c>
       <c r="B599" t="s">
-        <v>1170</v>
+        <v>1164</v>
       </c>
       <c r="C599" s="2" t="s">
         <v>7</v>
@@ -13752,10 +13752,10 @@
     </row>
     <row r="600" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
-        <v>1171</v>
+        <v>1165</v>
       </c>
       <c r="B600" t="s">
-        <v>1172</v>
+        <v>1166</v>
       </c>
       <c r="C600" s="2" t="s">
         <v>7</v>
@@ -13766,10 +13766,10 @@
     </row>
     <row r="601" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
-        <v>1173</v>
+        <v>1167</v>
       </c>
       <c r="B601" t="s">
-        <v>1174</v>
+        <v>1168</v>
       </c>
       <c r="C601" s="2" t="s">
         <v>7</v>
@@ -13780,10 +13780,10 @@
     </row>
     <row r="602" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
-        <v>1175</v>
+        <v>1169</v>
       </c>
       <c r="B602" t="s">
-        <v>1176</v>
+        <v>1170</v>
       </c>
       <c r="C602" s="2" t="s">
         <v>7</v>
@@ -13794,10 +13794,10 @@
     </row>
     <row r="603" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
-        <v>1177</v>
+        <v>1171</v>
       </c>
       <c r="B603" t="s">
-        <v>1178</v>
+        <v>1172</v>
       </c>
       <c r="C603" s="2" t="s">
         <v>7</v>
@@ -13808,10 +13808,10 @@
     </row>
     <row r="604" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
-        <v>1179</v>
+        <v>1173</v>
       </c>
       <c r="B604" t="s">
-        <v>1180</v>
+        <v>1174</v>
       </c>
       <c r="C604" s="2" t="s">
         <v>7</v>
@@ -13822,10 +13822,10 @@
     </row>
     <row r="605" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
-        <v>1181</v>
+        <v>1175</v>
       </c>
       <c r="B605" t="s">
-        <v>1182</v>
+        <v>1176</v>
       </c>
       <c r="C605" s="2" t="s">
         <v>7</v>
@@ -13836,10 +13836,10 @@
     </row>
     <row r="606" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
-        <v>1183</v>
+        <v>1177</v>
       </c>
       <c r="B606" t="s">
-        <v>1184</v>
+        <v>1178</v>
       </c>
       <c r="C606" s="2" t="s">
         <v>7</v>
@@ -13850,10 +13850,10 @@
     </row>
     <row r="607" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
-        <v>1185</v>
+        <v>1179</v>
       </c>
       <c r="B607" t="s">
-        <v>1186</v>
+        <v>1180</v>
       </c>
       <c r="C607" s="2" t="s">
         <v>7</v>
@@ -13864,10 +13864,10 @@
     </row>
     <row r="608" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
-        <v>1187</v>
+        <v>1181</v>
       </c>
       <c r="B608" t="s">
-        <v>1188</v>
+        <v>1182</v>
       </c>
       <c r="C608" s="2" t="s">
         <v>7</v>
@@ -13878,10 +13878,10 @@
     </row>
     <row r="609" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
-        <v>1189</v>
+        <v>1183</v>
       </c>
       <c r="B609" t="s">
-        <v>1190</v>
+        <v>1184</v>
       </c>
       <c r="C609" s="2" t="s">
         <v>7</v>
@@ -13892,10 +13892,10 @@
     </row>
     <row r="610" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
-        <v>1191</v>
+        <v>1185</v>
       </c>
       <c r="B610" t="s">
-        <v>1192</v>
+        <v>1186</v>
       </c>
       <c r="C610" s="2" t="s">
         <v>7</v>
@@ -13906,10 +13906,10 @@
     </row>
     <row r="611" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
-        <v>1193</v>
+        <v>1187</v>
       </c>
       <c r="B611" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
       <c r="C611" s="2" t="s">
         <v>7</v>
@@ -13920,10 +13920,10 @@
     </row>
     <row r="612" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
-        <v>1195</v>
+        <v>1189</v>
       </c>
       <c r="B612" t="s">
-        <v>1196</v>
+        <v>1190</v>
       </c>
       <c r="C612" s="2" t="s">
         <v>7</v>
@@ -13934,10 +13934,10 @@
     </row>
     <row r="613" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
-        <v>1197</v>
+        <v>1191</v>
       </c>
       <c r="B613" t="s">
-        <v>1198</v>
+        <v>1192</v>
       </c>
       <c r="C613" s="2" t="s">
         <v>7</v>
@@ -13948,10 +13948,10 @@
     </row>
     <row r="614" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
-        <v>1199</v>
+        <v>1193</v>
       </c>
       <c r="B614" t="s">
-        <v>1200</v>
+        <v>1194</v>
       </c>
       <c r="C614" s="2" t="s">
         <v>7</v>
@@ -13962,10 +13962,10 @@
     </row>
     <row r="615" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
-        <v>1201</v>
+        <v>1195</v>
       </c>
       <c r="B615" t="s">
-        <v>1202</v>
+        <v>1196</v>
       </c>
       <c r="C615" s="2" t="s">
         <v>7</v>
@@ -13976,10 +13976,10 @@
     </row>
     <row r="616" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
-        <v>1203</v>
+        <v>1197</v>
       </c>
       <c r="B616" t="s">
-        <v>1204</v>
+        <v>1198</v>
       </c>
       <c r="C616" s="2" t="s">
         <v>7</v>
@@ -13990,10 +13990,10 @@
     </row>
     <row r="617" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
-        <v>1205</v>
+        <v>1199</v>
       </c>
       <c r="B617" t="s">
-        <v>1206</v>
+        <v>1200</v>
       </c>
       <c r="C617" s="2" t="s">
         <v>7</v>
@@ -14004,10 +14004,10 @@
     </row>
     <row r="618" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
-        <v>1207</v>
+        <v>1201</v>
       </c>
       <c r="B618" t="s">
-        <v>1208</v>
+        <v>1202</v>
       </c>
       <c r="C618" s="2" t="s">
         <v>7</v>
@@ -14018,10 +14018,10 @@
     </row>
     <row r="619" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
-        <v>1209</v>
+        <v>1203</v>
       </c>
       <c r="B619" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="C619" s="2" t="s">
         <v>7</v>
@@ -14032,10 +14032,10 @@
     </row>
     <row r="620" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
-        <v>1211</v>
+        <v>1205</v>
       </c>
       <c r="B620" t="s">
-        <v>1212</v>
+        <v>1206</v>
       </c>
       <c r="C620" s="2" t="s">
         <v>7</v>
@@ -14046,10 +14046,10 @@
     </row>
     <row r="621" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
-        <v>1213</v>
+        <v>1207</v>
       </c>
       <c r="B621" t="s">
-        <v>1214</v>
+        <v>1208</v>
       </c>
       <c r="C621" s="2" t="s">
         <v>7</v>
@@ -14060,10 +14060,10 @@
     </row>
     <row r="622" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
-        <v>1215</v>
+        <v>1209</v>
       </c>
       <c r="B622" t="s">
-        <v>1216</v>
+        <v>1210</v>
       </c>
       <c r="C622" s="2" t="s">
         <v>7</v>
@@ -14074,10 +14074,10 @@
     </row>
     <row r="623" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
-        <v>1217</v>
+        <v>1211</v>
       </c>
       <c r="B623" t="s">
-        <v>1218</v>
+        <v>1212</v>
       </c>
       <c r="C623" s="2" t="s">
         <v>7</v>
@@ -14088,10 +14088,10 @@
     </row>
     <row r="624" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
-        <v>1219</v>
+        <v>1213</v>
       </c>
       <c r="B624" t="s">
-        <v>1220</v>
+        <v>1214</v>
       </c>
       <c r="C624" s="2" t="s">
         <v>7</v>
@@ -14102,10 +14102,10 @@
     </row>
     <row r="625" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
-        <v>1221</v>
+        <v>1215</v>
       </c>
       <c r="B625" t="s">
-        <v>1222</v>
+        <v>1216</v>
       </c>
       <c r="C625" s="2" t="s">
         <v>7</v>
@@ -14116,10 +14116,10 @@
     </row>
     <row r="626" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
-        <v>1223</v>
+        <v>1217</v>
       </c>
       <c r="B626" t="s">
-        <v>1224</v>
+        <v>1218</v>
       </c>
       <c r="C626" s="2" t="s">
         <v>7</v>
@@ -14130,10 +14130,10 @@
     </row>
     <row r="627" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
-        <v>1225</v>
+        <v>1219</v>
       </c>
       <c r="B627" t="s">
-        <v>1226</v>
+        <v>1220</v>
       </c>
       <c r="C627" s="2" t="s">
         <v>7</v>
@@ -14144,10 +14144,10 @@
     </row>
     <row r="628" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
-        <v>1227</v>
+        <v>1221</v>
       </c>
       <c r="B628" t="s">
-        <v>1228</v>
+        <v>1222</v>
       </c>
       <c r="C628" s="2" t="s">
         <v>7</v>
@@ -14158,10 +14158,10 @@
     </row>
     <row r="629" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
-        <v>1229</v>
+        <v>1223</v>
       </c>
       <c r="B629" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="C629" s="2" t="s">
         <v>7</v>
@@ -14172,10 +14172,10 @@
     </row>
     <row r="630" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
       <c r="B630" t="s">
-        <v>1232</v>
+        <v>1226</v>
       </c>
       <c r="C630" s="2" t="s">
         <v>7</v>
@@ -14186,10 +14186,10 @@
     </row>
     <row r="631" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
-        <v>1233</v>
+        <v>1227</v>
       </c>
       <c r="B631" t="s">
-        <v>1234</v>
+        <v>1228</v>
       </c>
       <c r="C631" s="2" t="s">
         <v>7</v>
@@ -14200,10 +14200,10 @@
     </row>
     <row r="632" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
-        <v>1235</v>
+        <v>1229</v>
       </c>
       <c r="B632" t="s">
-        <v>1236</v>
+        <v>1230</v>
       </c>
       <c r="C632" s="2" t="s">
         <v>7</v>
@@ -14214,10 +14214,10 @@
     </row>
     <row r="633" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
-        <v>1239</v>
+        <v>1231</v>
       </c>
       <c r="B633" t="s">
-        <v>1240</v>
+        <v>1232</v>
       </c>
       <c r="C633" s="2" t="s">
         <v>7</v>
@@ -14228,10 +14228,10 @@
     </row>
     <row r="634" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
-        <v>1241</v>
+        <v>1233</v>
       </c>
       <c r="B634" t="s">
-        <v>1242</v>
+        <v>1234</v>
       </c>
       <c r="C634" s="2" t="s">
         <v>7</v>
@@ -14242,10 +14242,10 @@
     </row>
     <row r="635" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
-        <v>1243</v>
+        <v>1235</v>
       </c>
       <c r="B635" t="s">
-        <v>1244</v>
+        <v>1236</v>
       </c>
       <c r="C635" s="2" t="s">
         <v>7</v>
@@ -14256,10 +14256,10 @@
     </row>
     <row r="636" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
-        <v>1245</v>
+        <v>1239</v>
       </c>
       <c r="B636" t="s">
-        <v>1246</v>
+        <v>1240</v>
       </c>
       <c r="C636" s="2" t="s">
         <v>7</v>
@@ -14270,10 +14270,10 @@
     </row>
     <row r="637" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
-        <v>1247</v>
+        <v>1241</v>
       </c>
       <c r="B637" t="s">
-        <v>1248</v>
+        <v>1242</v>
       </c>
       <c r="C637" s="2" t="s">
         <v>7</v>
@@ -14284,10 +14284,10 @@
     </row>
     <row r="638" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
-        <v>1249</v>
+        <v>1243</v>
       </c>
       <c r="B638" t="s">
-        <v>1250</v>
+        <v>1244</v>
       </c>
       <c r="C638" s="2" t="s">
         <v>7</v>
@@ -14298,10 +14298,10 @@
     </row>
     <row r="639" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
-        <v>1251</v>
+        <v>1245</v>
       </c>
       <c r="B639" t="s">
-        <v>1252</v>
+        <v>1246</v>
       </c>
       <c r="C639" s="2" t="s">
         <v>7</v>
@@ -14312,10 +14312,10 @@
     </row>
     <row r="640" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
-        <v>1253</v>
+        <v>1247</v>
       </c>
       <c r="B640" t="s">
-        <v>1254</v>
+        <v>1248</v>
       </c>
       <c r="C640" s="2" t="s">
         <v>7</v>
@@ -14326,10 +14326,10 @@
     </row>
     <row r="641" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
-        <v>1255</v>
+        <v>1249</v>
       </c>
       <c r="B641" t="s">
-        <v>1256</v>
+        <v>1250</v>
       </c>
       <c r="C641" s="2" t="s">
         <v>7</v>
@@ -14340,10 +14340,10 @@
     </row>
     <row r="642" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
-        <v>1257</v>
+        <v>1251</v>
       </c>
       <c r="B642" t="s">
-        <v>1258</v>
+        <v>1252</v>
       </c>
       <c r="C642" s="2" t="s">
         <v>7</v>
@@ -14354,10 +14354,10 @@
     </row>
     <row r="643" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
-        <v>1259</v>
+        <v>1253</v>
       </c>
       <c r="B643" t="s">
-        <v>1260</v>
+        <v>1254</v>
       </c>
       <c r="C643" s="2" t="s">
         <v>7</v>
@@ -14368,10 +14368,10 @@
     </row>
     <row r="644" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
-        <v>1261</v>
+        <v>1255</v>
       </c>
       <c r="B644" t="s">
-        <v>1262</v>
+        <v>1256</v>
       </c>
       <c r="C644" s="2" t="s">
         <v>7</v>
@@ -14382,10 +14382,10 @@
     </row>
     <row r="645" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
-        <v>1263</v>
+        <v>1257</v>
       </c>
       <c r="B645" t="s">
-        <v>1264</v>
+        <v>1258</v>
       </c>
       <c r="C645" s="2" t="s">
         <v>7</v>
@@ -14396,10 +14396,10 @@
     </row>
     <row r="646" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
-        <v>1267</v>
+        <v>1259</v>
       </c>
       <c r="B646" t="s">
-        <v>1268</v>
+        <v>1260</v>
       </c>
       <c r="C646" s="2" t="s">
         <v>7</v>
@@ -14410,10 +14410,10 @@
     </row>
     <row r="647" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
-        <v>1269</v>
+        <v>1261</v>
       </c>
       <c r="B647" t="s">
-        <v>1270</v>
+        <v>1262</v>
       </c>
       <c r="C647" s="2" t="s">
         <v>7</v>
@@ -14424,10 +14424,10 @@
     </row>
     <row r="648" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
-        <v>1271</v>
+        <v>1263</v>
       </c>
       <c r="B648" t="s">
-        <v>1272</v>
+        <v>1264</v>
       </c>
       <c r="C648" s="2" t="s">
         <v>7</v>
@@ -14438,10 +14438,10 @@
     </row>
     <row r="649" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
-        <v>1273</v>
+        <v>1267</v>
       </c>
       <c r="B649" t="s">
-        <v>1274</v>
+        <v>1268</v>
       </c>
       <c r="C649" s="2" t="s">
         <v>7</v>
@@ -14452,10 +14452,10 @@
     </row>
     <row r="650" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
-        <v>1275</v>
+        <v>1269</v>
       </c>
       <c r="B650" t="s">
-        <v>1276</v>
+        <v>1270</v>
       </c>
       <c r="C650" s="2" t="s">
         <v>7</v>
@@ -14466,10 +14466,10 @@
     </row>
     <row r="651" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
-        <v>1277</v>
+        <v>1271</v>
       </c>
       <c r="B651" t="s">
-        <v>1278</v>
+        <v>1272</v>
       </c>
       <c r="C651" s="2" t="s">
         <v>7</v>
@@ -14480,10 +14480,10 @@
     </row>
     <row r="652" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
-        <v>1279</v>
+        <v>1273</v>
       </c>
       <c r="B652" t="s">
-        <v>1280</v>
+        <v>1274</v>
       </c>
       <c r="C652" s="2" t="s">
         <v>7</v>
@@ -14494,10 +14494,10 @@
     </row>
     <row r="653" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
-        <v>1281</v>
+        <v>1275</v>
       </c>
       <c r="B653" t="s">
-        <v>1282</v>
+        <v>1276</v>
       </c>
       <c r="C653" s="2" t="s">
         <v>7</v>
@@ -14508,10 +14508,10 @@
     </row>
     <row r="654" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
-        <v>1283</v>
+        <v>1277</v>
       </c>
       <c r="B654" t="s">
-        <v>1284</v>
+        <v>1278</v>
       </c>
       <c r="C654" s="2" t="s">
         <v>7</v>
@@ -14522,10 +14522,10 @@
     </row>
     <row r="655" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
-        <v>1285</v>
+        <v>1279</v>
       </c>
       <c r="B655" t="s">
-        <v>1286</v>
+        <v>1280</v>
       </c>
       <c r="C655" s="2" t="s">
         <v>7</v>
@@ -14536,10 +14536,10 @@
     </row>
     <row r="656" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
-        <v>1287</v>
+        <v>1281</v>
       </c>
       <c r="B656" t="s">
-        <v>1288</v>
+        <v>1282</v>
       </c>
       <c r="C656" s="2" t="s">
         <v>7</v>
@@ -14550,10 +14550,10 @@
     </row>
     <row r="657" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
-        <v>1289</v>
+        <v>1283</v>
       </c>
       <c r="B657" t="s">
-        <v>1290</v>
+        <v>1284</v>
       </c>
       <c r="C657" s="2" t="s">
         <v>7</v>
@@ -14564,10 +14564,10 @@
     </row>
     <row r="658" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
-        <v>1291</v>
+        <v>1285</v>
       </c>
       <c r="B658" t="s">
-        <v>1292</v>
+        <v>1286</v>
       </c>
       <c r="C658" s="2" t="s">
         <v>7</v>
@@ -14578,10 +14578,10 @@
     </row>
     <row r="659" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
-        <v>1295</v>
+        <v>1287</v>
       </c>
       <c r="B659" t="s">
-        <v>1296</v>
+        <v>1288</v>
       </c>
       <c r="C659" s="2" t="s">
         <v>7</v>
@@ -14592,10 +14592,10 @@
     </row>
     <row r="660" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
-        <v>1297</v>
+        <v>1289</v>
       </c>
       <c r="B660" t="s">
-        <v>1298</v>
+        <v>1290</v>
       </c>
       <c r="C660" s="2" t="s">
         <v>7</v>
@@ -14606,10 +14606,10 @@
     </row>
     <row r="661" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
-        <v>1299</v>
+        <v>1291</v>
       </c>
       <c r="B661" t="s">
-        <v>1300</v>
+        <v>1292</v>
       </c>
       <c r="C661" s="2" t="s">
         <v>7</v>
@@ -14620,10 +14620,10 @@
     </row>
     <row r="662" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
-        <v>1301</v>
+        <v>1295</v>
       </c>
       <c r="B662" t="s">
-        <v>1302</v>
+        <v>1296</v>
       </c>
       <c r="C662" s="2" t="s">
         <v>7</v>
@@ -14634,10 +14634,10 @@
     </row>
     <row r="663" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
-        <v>1305</v>
+        <v>1297</v>
       </c>
       <c r="B663" t="s">
-        <v>1306</v>
+        <v>1298</v>
       </c>
       <c r="C663" s="2" t="s">
         <v>7</v>
@@ -14648,10 +14648,10 @@
     </row>
     <row r="664" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
-        <v>1307</v>
+        <v>1299</v>
       </c>
       <c r="B664" t="s">
-        <v>1308</v>
+        <v>1300</v>
       </c>
       <c r="C664" s="2" t="s">
         <v>7</v>
@@ -14662,10 +14662,10 @@
     </row>
     <row r="665" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
-        <v>1311</v>
+        <v>1301</v>
       </c>
       <c r="B665" t="s">
-        <v>1312</v>
+        <v>1302</v>
       </c>
       <c r="C665" s="2" t="s">
         <v>7</v>
@@ -14676,10 +14676,10 @@
     </row>
     <row r="666" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
-        <v>1313</v>
+        <v>1305</v>
       </c>
       <c r="B666" t="s">
-        <v>1314</v>
+        <v>1306</v>
       </c>
       <c r="C666" s="2" t="s">
         <v>7</v>
@@ -14690,10 +14690,10 @@
     </row>
     <row r="667" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
-        <v>1315</v>
+        <v>1307</v>
       </c>
       <c r="B667" t="s">
-        <v>1316</v>
+        <v>1308</v>
       </c>
       <c r="C667" s="2" t="s">
         <v>7</v>
@@ -14704,10 +14704,10 @@
     </row>
     <row r="668" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
-        <v>1317</v>
+        <v>1311</v>
       </c>
       <c r="B668" t="s">
-        <v>1318</v>
+        <v>1312</v>
       </c>
       <c r="C668" s="2" t="s">
         <v>7</v>
@@ -14718,10 +14718,10 @@
     </row>
     <row r="669" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
-        <v>1319</v>
+        <v>1313</v>
       </c>
       <c r="B669" t="s">
-        <v>1320</v>
+        <v>1314</v>
       </c>
       <c r="C669" s="2" t="s">
         <v>7</v>
@@ -14732,10 +14732,10 @@
     </row>
     <row r="670" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
-        <v>1321</v>
+        <v>1315</v>
       </c>
       <c r="B670" t="s">
-        <v>1322</v>
+        <v>1316</v>
       </c>
       <c r="C670" s="2" t="s">
         <v>7</v>
@@ -14746,10 +14746,10 @@
     </row>
     <row r="671" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
-        <v>1325</v>
+        <v>1317</v>
       </c>
       <c r="B671" t="s">
-        <v>1326</v>
+        <v>1318</v>
       </c>
       <c r="C671" s="2" t="s">
         <v>7</v>
@@ -14760,10 +14760,10 @@
     </row>
     <row r="672" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
-        <v>1329</v>
+        <v>1319</v>
       </c>
       <c r="B672" t="s">
-        <v>1330</v>
+        <v>1320</v>
       </c>
       <c r="C672" s="2" t="s">
         <v>7</v>
@@ -14774,10 +14774,10 @@
     </row>
     <row r="673" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
-        <v>1331</v>
+        <v>1321</v>
       </c>
       <c r="B673" t="s">
-        <v>1332</v>
+        <v>1322</v>
       </c>
       <c r="C673" s="2" t="s">
         <v>7</v>
@@ -14788,10 +14788,10 @@
     </row>
     <row r="674" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
-        <v>1333</v>
+        <v>1325</v>
       </c>
       <c r="B674" t="s">
-        <v>1334</v>
+        <v>1326</v>
       </c>
       <c r="C674" s="2" t="s">
         <v>7</v>
@@ -14802,10 +14802,10 @@
     </row>
     <row r="675" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
-        <v>1335</v>
+        <v>1329</v>
       </c>
       <c r="B675" t="s">
-        <v>1336</v>
+        <v>1330</v>
       </c>
       <c r="C675" s="2" t="s">
         <v>7</v>
@@ -14816,10 +14816,10 @@
     </row>
     <row r="676" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
-        <v>1337</v>
+        <v>1331</v>
       </c>
       <c r="B676" t="s">
-        <v>1338</v>
+        <v>1332</v>
       </c>
       <c r="C676" s="2" t="s">
         <v>7</v>
@@ -14830,10 +14830,10 @@
     </row>
     <row r="677" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
-        <v>1339</v>
+        <v>1333</v>
       </c>
       <c r="B677" t="s">
-        <v>1340</v>
+        <v>1334</v>
       </c>
       <c r="C677" s="2" t="s">
         <v>7</v>
@@ -14844,10 +14844,10 @@
     </row>
     <row r="678" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
-        <v>1341</v>
+        <v>1335</v>
       </c>
       <c r="B678" t="s">
-        <v>1342</v>
+        <v>1336</v>
       </c>
       <c r="C678" s="2" t="s">
         <v>7</v>
@@ -14858,10 +14858,10 @@
     </row>
     <row r="679" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="B679" t="s">
-        <v>1344</v>
+        <v>1338</v>
       </c>
       <c r="C679" s="2" t="s">
         <v>7</v>
@@ -14872,10 +14872,10 @@
     </row>
     <row r="680" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
-        <v>1345</v>
+        <v>1339</v>
       </c>
       <c r="B680" t="s">
-        <v>1346</v>
+        <v>1340</v>
       </c>
       <c r="C680" s="2" t="s">
         <v>7</v>
@@ -14886,10 +14886,10 @@
     </row>
     <row r="681" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
-        <v>1347</v>
+        <v>1341</v>
       </c>
       <c r="B681" t="s">
-        <v>1348</v>
+        <v>1342</v>
       </c>
       <c r="C681" s="2" t="s">
         <v>7</v>
@@ -14900,10 +14900,10 @@
     </row>
     <row r="682" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
-        <v>1349</v>
+        <v>1343</v>
       </c>
       <c r="B682" t="s">
-        <v>1350</v>
+        <v>1344</v>
       </c>
       <c r="C682" s="2" t="s">
         <v>7</v>
@@ -14914,10 +14914,10 @@
     </row>
     <row r="683" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
-        <v>1351</v>
+        <v>1345</v>
       </c>
       <c r="B683" t="s">
-        <v>1352</v>
+        <v>1346</v>
       </c>
       <c r="C683" s="2" t="s">
         <v>7</v>
@@ -14928,10 +14928,10 @@
     </row>
     <row r="684" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
-        <v>1353</v>
+        <v>1347</v>
       </c>
       <c r="B684" t="s">
-        <v>1354</v>
+        <v>1348</v>
       </c>
       <c r="C684" s="2" t="s">
         <v>7</v>
@@ -14942,10 +14942,10 @@
     </row>
     <row r="685" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
-        <v>1355</v>
+        <v>1349</v>
       </c>
       <c r="B685" t="s">
-        <v>1356</v>
+        <v>1350</v>
       </c>
       <c r="C685" s="2" t="s">
         <v>7</v>
@@ -14956,10 +14956,10 @@
     </row>
     <row r="686" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
-        <v>1357</v>
+        <v>1351</v>
       </c>
       <c r="B686" t="s">
-        <v>1358</v>
+        <v>1352</v>
       </c>
       <c r="C686" s="2" t="s">
         <v>7</v>
@@ -14970,10 +14970,10 @@
     </row>
     <row r="687" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
-        <v>1359</v>
+        <v>1353</v>
       </c>
       <c r="B687" t="s">
-        <v>1360</v>
+        <v>1354</v>
       </c>
       <c r="C687" s="2" t="s">
         <v>7</v>
@@ -14984,10 +14984,10 @@
     </row>
     <row r="688" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
-        <v>1361</v>
+        <v>1355</v>
       </c>
       <c r="B688" t="s">
-        <v>1362</v>
+        <v>1356</v>
       </c>
       <c r="C688" s="2" t="s">
         <v>7</v>
@@ -14998,10 +14998,10 @@
     </row>
     <row r="689" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
-        <v>1363</v>
+        <v>1357</v>
       </c>
       <c r="B689" t="s">
-        <v>1364</v>
+        <v>1358</v>
       </c>
       <c r="C689" s="2" t="s">
         <v>7</v>
@@ -15012,10 +15012,10 @@
     </row>
     <row r="690" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
-        <v>1365</v>
+        <v>1359</v>
       </c>
       <c r="B690" t="s">
-        <v>1366</v>
+        <v>1360</v>
       </c>
       <c r="C690" s="2" t="s">
         <v>7</v>
@@ -15026,10 +15026,10 @@
     </row>
     <row r="691" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
-        <v>1367</v>
+        <v>1361</v>
       </c>
       <c r="B691" t="s">
-        <v>1368</v>
+        <v>1362</v>
       </c>
       <c r="C691" s="2" t="s">
         <v>7</v>
@@ -15040,10 +15040,10 @@
     </row>
     <row r="692" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
-        <v>1369</v>
+        <v>1363</v>
       </c>
       <c r="B692" t="s">
-        <v>1370</v>
+        <v>1364</v>
       </c>
       <c r="C692" s="2" t="s">
         <v>7</v>
@@ -15054,10 +15054,10 @@
     </row>
     <row r="693" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
-        <v>1371</v>
+        <v>1365</v>
       </c>
       <c r="B693" t="s">
-        <v>1372</v>
+        <v>1366</v>
       </c>
       <c r="C693" s="2" t="s">
         <v>7</v>
@@ -15068,10 +15068,10 @@
     </row>
     <row r="694" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
-        <v>1373</v>
+        <v>1367</v>
       </c>
       <c r="B694" t="s">
-        <v>1374</v>
+        <v>1368</v>
       </c>
       <c r="C694" s="2" t="s">
         <v>7</v>
@@ -15082,10 +15082,10 @@
     </row>
     <row r="695" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
-        <v>1375</v>
+        <v>1369</v>
       </c>
       <c r="B695" t="s">
-        <v>1376</v>
+        <v>1370</v>
       </c>
       <c r="C695" s="2" t="s">
         <v>7</v>
@@ -15096,10 +15096,10 @@
     </row>
     <row r="696" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
-        <v>1377</v>
+        <v>1371</v>
       </c>
       <c r="B696" t="s">
-        <v>1378</v>
+        <v>1372</v>
       </c>
       <c r="C696" s="2" t="s">
         <v>7</v>
@@ -15110,10 +15110,10 @@
     </row>
     <row r="697" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
-        <v>1379</v>
+        <v>1373</v>
       </c>
       <c r="B697" t="s">
-        <v>1380</v>
+        <v>1374</v>
       </c>
       <c r="C697" s="2" t="s">
         <v>7</v>
@@ -15124,10 +15124,10 @@
     </row>
     <row r="698" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
-        <v>1381</v>
+        <v>1375</v>
       </c>
       <c r="B698" t="s">
-        <v>1382</v>
+        <v>1376</v>
       </c>
       <c r="C698" s="2" t="s">
         <v>7</v>
@@ -15138,10 +15138,10 @@
     </row>
     <row r="699" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
-        <v>1383</v>
+        <v>1377</v>
       </c>
       <c r="B699" t="s">
-        <v>1384</v>
+        <v>1378</v>
       </c>
       <c r="C699" s="2" t="s">
         <v>7</v>
@@ -15152,10 +15152,10 @@
     </row>
     <row r="700" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
-        <v>1385</v>
+        <v>1379</v>
       </c>
       <c r="B700" t="s">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="C700" s="2" t="s">
         <v>7</v>
@@ -15166,10 +15166,10 @@
     </row>
     <row r="701" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
-        <v>1387</v>
+        <v>1381</v>
       </c>
       <c r="B701" t="s">
-        <v>1388</v>
+        <v>1382</v>
       </c>
       <c r="C701" s="2" t="s">
         <v>7</v>
@@ -15180,10 +15180,10 @@
     </row>
     <row r="702" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
-        <v>1389</v>
+        <v>1383</v>
       </c>
       <c r="B702" t="s">
-        <v>1390</v>
+        <v>1384</v>
       </c>
       <c r="C702" s="2" t="s">
         <v>7</v>
@@ -15194,10 +15194,10 @@
     </row>
     <row r="703" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
-        <v>1391</v>
+        <v>1385</v>
       </c>
       <c r="B703" t="s">
-        <v>1392</v>
+        <v>1386</v>
       </c>
       <c r="C703" s="2" t="s">
         <v>7</v>
@@ -15208,10 +15208,10 @@
     </row>
     <row r="704" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
-        <v>1393</v>
+        <v>1387</v>
       </c>
       <c r="B704" t="s">
-        <v>1394</v>
+        <v>1388</v>
       </c>
       <c r="C704" s="2" t="s">
         <v>7</v>
@@ -15222,10 +15222,10 @@
     </row>
     <row r="705" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
-        <v>1395</v>
+        <v>1389</v>
       </c>
       <c r="B705" t="s">
-        <v>1396</v>
+        <v>1390</v>
       </c>
       <c r="C705" s="2" t="s">
         <v>7</v>
@@ -15236,10 +15236,10 @@
     </row>
     <row r="706" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
-        <v>1397</v>
+        <v>1391</v>
       </c>
       <c r="B706" t="s">
-        <v>1398</v>
+        <v>1392</v>
       </c>
       <c r="C706" s="2" t="s">
         <v>7</v>
@@ -15250,10 +15250,10 @@
     </row>
     <row r="707" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
-        <v>1399</v>
+        <v>1393</v>
       </c>
       <c r="B707" t="s">
-        <v>1400</v>
+        <v>1394</v>
       </c>
       <c r="C707" s="2" t="s">
         <v>7</v>
@@ -15264,10 +15264,10 @@
     </row>
     <row r="708" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
-        <v>1401</v>
+        <v>1395</v>
       </c>
       <c r="B708" t="s">
-        <v>1402</v>
+        <v>1396</v>
       </c>
       <c r="C708" s="2" t="s">
         <v>7</v>
@@ -15278,10 +15278,10 @@
     </row>
     <row r="709" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
-        <v>1403</v>
+        <v>1397</v>
       </c>
       <c r="B709" t="s">
-        <v>1404</v>
+        <v>1398</v>
       </c>
       <c r="C709" s="2" t="s">
         <v>7</v>
@@ -15292,10 +15292,10 @@
     </row>
     <row r="710" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
-        <v>1407</v>
+        <v>1399</v>
       </c>
       <c r="B710" t="s">
-        <v>1408</v>
+        <v>1400</v>
       </c>
       <c r="C710" s="2" t="s">
         <v>7</v>
@@ -15306,10 +15306,10 @@
     </row>
     <row r="711" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
-        <v>1409</v>
+        <v>1401</v>
       </c>
       <c r="B711" t="s">
-        <v>1410</v>
+        <v>1402</v>
       </c>
       <c r="C711" s="2" t="s">
         <v>7</v>
@@ -15320,10 +15320,10 @@
     </row>
     <row r="712" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
       <c r="B712" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
       <c r="C712" s="2" t="s">
         <v>7</v>
@@ -15334,10 +15334,10 @@
     </row>
     <row r="713" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A713" t="s">
-        <v>1413</v>
+        <v>1407</v>
       </c>
       <c r="B713" t="s">
-        <v>1414</v>
+        <v>1408</v>
       </c>
       <c r="C713" s="2" t="s">
         <v>7</v>
@@ -15348,10 +15348,10 @@
     </row>
     <row r="714" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A714" t="s">
-        <v>1415</v>
+        <v>1409</v>
       </c>
       <c r="B714" t="s">
-        <v>1416</v>
+        <v>1410</v>
       </c>
       <c r="C714" s="2" t="s">
         <v>7</v>
@@ -15362,10 +15362,10 @@
     </row>
     <row r="715" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
-        <v>1417</v>
+        <v>1411</v>
       </c>
       <c r="B715" t="s">
-        <v>1418</v>
+        <v>1412</v>
       </c>
       <c r="C715" s="2" t="s">
         <v>7</v>
@@ -15376,10 +15376,10 @@
     </row>
     <row r="716" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
-        <v>1419</v>
+        <v>1413</v>
       </c>
       <c r="B716" t="s">
-        <v>1420</v>
+        <v>1414</v>
       </c>
       <c r="C716" s="2" t="s">
         <v>7</v>
@@ -15390,10 +15390,10 @@
     </row>
     <row r="717" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A717" t="s">
-        <v>1421</v>
+        <v>1415</v>
       </c>
       <c r="B717" t="s">
-        <v>1422</v>
+        <v>1416</v>
       </c>
       <c r="C717" s="2" t="s">
         <v>7</v>
@@ -15404,10 +15404,10 @@
     </row>
     <row r="718" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
-        <v>1423</v>
+        <v>1417</v>
       </c>
       <c r="B718" t="s">
-        <v>1424</v>
+        <v>1418</v>
       </c>
       <c r="C718" s="2" t="s">
         <v>7</v>
@@ -15418,10 +15418,10 @@
     </row>
     <row r="719" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
-        <v>1425</v>
+        <v>1419</v>
       </c>
       <c r="B719" t="s">
-        <v>1426</v>
+        <v>1420</v>
       </c>
       <c r="C719" s="2" t="s">
         <v>7</v>
@@ -15432,10 +15432,10 @@
     </row>
     <row r="720" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A720" t="s">
-        <v>1427</v>
+        <v>1421</v>
       </c>
       <c r="B720" t="s">
-        <v>1428</v>
+        <v>1422</v>
       </c>
       <c r="C720" s="2" t="s">
         <v>7</v>
@@ -15446,10 +15446,10 @@
     </row>
     <row r="721" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
-        <v>1429</v>
+        <v>1423</v>
       </c>
       <c r="B721" t="s">
-        <v>1430</v>
+        <v>1424</v>
       </c>
       <c r="C721" s="2" t="s">
         <v>7</v>
@@ -15460,10 +15460,10 @@
     </row>
     <row r="722" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
-        <v>1431</v>
+        <v>1425</v>
       </c>
       <c r="B722" t="s">
-        <v>1432</v>
+        <v>1426</v>
       </c>
       <c r="C722" s="2" t="s">
         <v>7</v>
@@ -15474,10 +15474,10 @@
     </row>
     <row r="723" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
-        <v>1433</v>
+        <v>1427</v>
       </c>
       <c r="B723" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="C723" s="2" t="s">
         <v>7</v>
@@ -15488,10 +15488,10 @@
     </row>
     <row r="724" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A724" t="s">
-        <v>1435</v>
+        <v>1429</v>
       </c>
       <c r="B724" t="s">
-        <v>1436</v>
+        <v>1430</v>
       </c>
       <c r="C724" s="2" t="s">
         <v>7</v>
@@ -15502,10 +15502,10 @@
     </row>
     <row r="725" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A725" t="s">
-        <v>1437</v>
+        <v>1431</v>
       </c>
       <c r="B725" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="C725" s="2" t="s">
         <v>7</v>
@@ -15516,10 +15516,10 @@
     </row>
     <row r="726" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A726" t="s">
-        <v>1439</v>
+        <v>1433</v>
       </c>
       <c r="B726" t="s">
-        <v>1440</v>
+        <v>1434</v>
       </c>
       <c r="C726" s="2" t="s">
         <v>7</v>
@@ -15530,10 +15530,10 @@
     </row>
     <row r="727" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A727" t="s">
-        <v>1441</v>
+        <v>1435</v>
       </c>
       <c r="B727" t="s">
-        <v>1442</v>
+        <v>1436</v>
       </c>
       <c r="C727" s="2" t="s">
         <v>7</v>
@@ -15544,10 +15544,10 @@
     </row>
     <row r="728" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A728" t="s">
-        <v>1443</v>
+        <v>1437</v>
       </c>
       <c r="B728" t="s">
-        <v>1444</v>
+        <v>1438</v>
       </c>
       <c r="C728" s="2" t="s">
         <v>7</v>
@@ -15558,10 +15558,10 @@
     </row>
     <row r="729" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A729" t="s">
-        <v>1445</v>
+        <v>1439</v>
       </c>
       <c r="B729" t="s">
-        <v>1446</v>
+        <v>1440</v>
       </c>
       <c r="C729" s="2" t="s">
         <v>7</v>
@@ -15572,10 +15572,10 @@
     </row>
     <row r="730" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A730" t="s">
-        <v>1447</v>
+        <v>1441</v>
       </c>
       <c r="B730" t="s">
-        <v>1448</v>
+        <v>1442</v>
       </c>
       <c r="C730" s="2" t="s">
         <v>7</v>
@@ -15586,10 +15586,10 @@
     </row>
     <row r="731" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A731" t="s">
-        <v>1449</v>
+        <v>1443</v>
       </c>
       <c r="B731" t="s">
-        <v>1450</v>
+        <v>1444</v>
       </c>
       <c r="C731" s="2" t="s">
         <v>7</v>
@@ -15600,10 +15600,10 @@
     </row>
     <row r="732" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A732" t="s">
-        <v>1455</v>
+        <v>1445</v>
       </c>
       <c r="B732" t="s">
-        <v>1456</v>
+        <v>1446</v>
       </c>
       <c r="C732" s="2" t="s">
         <v>7</v>
@@ -15614,10 +15614,10 @@
     </row>
     <row r="733" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A733" t="s">
-        <v>1457</v>
+        <v>1447</v>
       </c>
       <c r="B733" t="s">
-        <v>1458</v>
+        <v>1448</v>
       </c>
       <c r="C733" s="2" t="s">
         <v>7</v>
@@ -15628,10 +15628,10 @@
     </row>
     <row r="734" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A734" t="s">
-        <v>1459</v>
+        <v>1449</v>
       </c>
       <c r="B734" t="s">
-        <v>1460</v>
+        <v>1450</v>
       </c>
       <c r="C734" s="2" t="s">
         <v>7</v>
@@ -15642,10 +15642,10 @@
     </row>
     <row r="735" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A735" t="s">
-        <v>1461</v>
+        <v>1455</v>
       </c>
       <c r="B735" t="s">
-        <v>1462</v>
+        <v>1456</v>
       </c>
       <c r="C735" s="2" t="s">
         <v>7</v>
@@ -15656,10 +15656,10 @@
     </row>
     <row r="736" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A736" t="s">
-        <v>1463</v>
+        <v>1457</v>
       </c>
       <c r="B736" t="s">
-        <v>1464</v>
+        <v>1458</v>
       </c>
       <c r="C736" s="2" t="s">
         <v>7</v>
@@ -15670,10 +15670,10 @@
     </row>
     <row r="737" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A737" t="s">
-        <v>1469</v>
+        <v>1459</v>
       </c>
       <c r="B737" t="s">
-        <v>1470</v>
+        <v>1460</v>
       </c>
       <c r="C737" s="2" t="s">
         <v>7</v>
@@ -15684,10 +15684,10 @@
     </row>
     <row r="738" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A738" t="s">
-        <v>1471</v>
+        <v>1461</v>
       </c>
       <c r="B738" t="s">
-        <v>1472</v>
+        <v>1462</v>
       </c>
       <c r="C738" s="2" t="s">
         <v>7</v>
@@ -15698,10 +15698,10 @@
     </row>
     <row r="739" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A739" t="s">
-        <v>1473</v>
+        <v>1463</v>
       </c>
       <c r="B739" t="s">
-        <v>1474</v>
+        <v>1464</v>
       </c>
       <c r="C739" s="2" t="s">
         <v>7</v>
@@ -15712,10 +15712,10 @@
     </row>
     <row r="740" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A740" t="s">
-        <v>1475</v>
+        <v>1469</v>
       </c>
       <c r="B740" t="s">
-        <v>1476</v>
+        <v>1470</v>
       </c>
       <c r="C740" s="2" t="s">
         <v>7</v>
@@ -15726,10 +15726,10 @@
     </row>
     <row r="741" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A741" t="s">
-        <v>1477</v>
+        <v>1471</v>
       </c>
       <c r="B741" t="s">
-        <v>1478</v>
+        <v>1472</v>
       </c>
       <c r="C741" s="2" t="s">
         <v>7</v>
@@ -15740,10 +15740,10 @@
     </row>
     <row r="742" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A742" t="s">
-        <v>1479</v>
+        <v>1473</v>
       </c>
       <c r="B742" t="s">
-        <v>1480</v>
+        <v>1474</v>
       </c>
       <c r="C742" s="2" t="s">
         <v>7</v>
@@ -15754,10 +15754,10 @@
     </row>
     <row r="743" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A743" t="s">
-        <v>1481</v>
+        <v>1475</v>
       </c>
       <c r="B743" t="s">
-        <v>1482</v>
+        <v>1476</v>
       </c>
       <c r="C743" s="2" t="s">
         <v>7</v>
@@ -15768,10 +15768,10 @@
     </row>
     <row r="744" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A744" t="s">
-        <v>1483</v>
+        <v>1477</v>
       </c>
       <c r="B744" t="s">
-        <v>1484</v>
+        <v>1478</v>
       </c>
       <c r="C744" s="2" t="s">
         <v>7</v>
@@ -15782,10 +15782,10 @@
     </row>
     <row r="745" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A745" t="s">
-        <v>1487</v>
+        <v>1479</v>
       </c>
       <c r="B745" t="s">
-        <v>1488</v>
+        <v>1480</v>
       </c>
       <c r="C745" s="2" t="s">
         <v>7</v>
@@ -15796,10 +15796,10 @@
     </row>
     <row r="746" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A746" t="s">
-        <v>1489</v>
+        <v>1481</v>
       </c>
       <c r="B746" t="s">
-        <v>1490</v>
+        <v>1482</v>
       </c>
       <c r="C746" s="2" t="s">
         <v>7</v>
@@ -15810,10 +15810,10 @@
     </row>
     <row r="747" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A747" t="s">
-        <v>1491</v>
+        <v>1483</v>
       </c>
       <c r="B747" t="s">
-        <v>1492</v>
+        <v>1484</v>
       </c>
       <c r="C747" s="2" t="s">
         <v>7</v>
@@ -15824,10 +15824,10 @@
     </row>
     <row r="748" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A748" t="s">
-        <v>1493</v>
+        <v>1487</v>
       </c>
       <c r="B748" t="s">
-        <v>1494</v>
+        <v>1488</v>
       </c>
       <c r="C748" s="2" t="s">
         <v>7</v>
@@ -15838,10 +15838,10 @@
     </row>
     <row r="749" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A749" t="s">
-        <v>1495</v>
+        <v>1489</v>
       </c>
       <c r="B749" t="s">
-        <v>1496</v>
+        <v>1490</v>
       </c>
       <c r="C749" s="2" t="s">
         <v>7</v>
@@ -15852,10 +15852,10 @@
     </row>
     <row r="750" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A750" t="s">
-        <v>1497</v>
+        <v>1491</v>
       </c>
       <c r="B750" t="s">
-        <v>1498</v>
+        <v>1492</v>
       </c>
       <c r="C750" s="2" t="s">
         <v>7</v>
@@ -15866,10 +15866,10 @@
     </row>
     <row r="751" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A751" t="s">
-        <v>1499</v>
+        <v>1493</v>
       </c>
       <c r="B751" t="s">
-        <v>1500</v>
+        <v>1494</v>
       </c>
       <c r="C751" s="2" t="s">
         <v>7</v>
@@ -15880,10 +15880,10 @@
     </row>
     <row r="752" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A752" t="s">
-        <v>1501</v>
+        <v>1495</v>
       </c>
       <c r="B752" t="s">
-        <v>1502</v>
+        <v>1496</v>
       </c>
       <c r="C752" s="2" t="s">
         <v>7</v>
@@ -15894,10 +15894,10 @@
     </row>
     <row r="753" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A753" t="s">
-        <v>1503</v>
+        <v>1497</v>
       </c>
       <c r="B753" t="s">
-        <v>1504</v>
+        <v>1498</v>
       </c>
       <c r="C753" s="2" t="s">
         <v>7</v>
@@ -15908,10 +15908,10 @@
     </row>
     <row r="754" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A754" t="s">
-        <v>1507</v>
+        <v>1499</v>
       </c>
       <c r="B754" t="s">
-        <v>1508</v>
+        <v>1500</v>
       </c>
       <c r="C754" s="2" t="s">
         <v>7</v>
@@ -15922,10 +15922,10 @@
     </row>
     <row r="755" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A755" t="s">
-        <v>1509</v>
+        <v>1501</v>
       </c>
       <c r="B755" t="s">
-        <v>1510</v>
+        <v>1502</v>
       </c>
       <c r="C755" s="2" t="s">
         <v>7</v>
@@ -15936,10 +15936,10 @@
     </row>
     <row r="756" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A756" t="s">
-        <v>1511</v>
+        <v>1503</v>
       </c>
       <c r="B756" t="s">
-        <v>1512</v>
+        <v>1504</v>
       </c>
       <c r="C756" s="2" t="s">
         <v>7</v>
@@ -15950,10 +15950,10 @@
     </row>
     <row r="757" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A757" t="s">
-        <v>1513</v>
+        <v>1507</v>
       </c>
       <c r="B757" t="s">
-        <v>1514</v>
+        <v>1508</v>
       </c>
       <c r="C757" s="2" t="s">
         <v>7</v>
@@ -15964,10 +15964,10 @@
     </row>
     <row r="758" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A758" t="s">
-        <v>1515</v>
+        <v>1509</v>
       </c>
       <c r="B758" t="s">
-        <v>1516</v>
+        <v>1510</v>
       </c>
       <c r="C758" s="2" t="s">
         <v>7</v>
@@ -15978,10 +15978,10 @@
     </row>
     <row r="759" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A759" t="s">
-        <v>1517</v>
+        <v>1511</v>
       </c>
       <c r="B759" t="s">
-        <v>1518</v>
+        <v>1512</v>
       </c>
       <c r="C759" s="2" t="s">
         <v>7</v>
@@ -15992,10 +15992,10 @@
     </row>
     <row r="760" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A760" t="s">
-        <v>1519</v>
+        <v>1513</v>
       </c>
       <c r="B760" t="s">
-        <v>1520</v>
+        <v>1514</v>
       </c>
       <c r="C760" s="2" t="s">
         <v>7</v>
@@ -16006,10 +16006,10 @@
     </row>
     <row r="761" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A761" t="s">
-        <v>1521</v>
+        <v>1515</v>
       </c>
       <c r="B761" t="s">
-        <v>1522</v>
+        <v>1516</v>
       </c>
       <c r="C761" s="2" t="s">
         <v>7</v>
@@ -16020,10 +16020,10 @@
     </row>
     <row r="762" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A762" t="s">
-        <v>1523</v>
+        <v>1517</v>
       </c>
       <c r="B762" t="s">
-        <v>1524</v>
+        <v>1518</v>
       </c>
       <c r="C762" s="2" t="s">
         <v>7</v>
@@ -16034,10 +16034,10 @@
     </row>
     <row r="763" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A763" t="s">
-        <v>1525</v>
+        <v>1519</v>
       </c>
       <c r="B763" t="s">
-        <v>1526</v>
+        <v>1520</v>
       </c>
       <c r="C763" s="2" t="s">
         <v>7</v>
@@ -16048,10 +16048,10 @@
     </row>
     <row r="764" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A764" t="s">
-        <v>1527</v>
+        <v>1521</v>
       </c>
       <c r="B764" t="s">
-        <v>1528</v>
+        <v>1522</v>
       </c>
       <c r="C764" s="2" t="s">
         <v>7</v>
@@ -16062,10 +16062,10 @@
     </row>
     <row r="765" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A765" t="s">
-        <v>1531</v>
+        <v>1523</v>
       </c>
       <c r="B765" t="s">
-        <v>1532</v>
+        <v>1524</v>
       </c>
       <c r="C765" s="2" t="s">
         <v>7</v>
@@ -16076,10 +16076,10 @@
     </row>
     <row r="766" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A766" t="s">
-        <v>1533</v>
+        <v>1525</v>
       </c>
       <c r="B766" t="s">
-        <v>1534</v>
+        <v>1526</v>
       </c>
       <c r="C766" s="2" t="s">
         <v>7</v>
@@ -16090,10 +16090,10 @@
     </row>
     <row r="767" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A767" t="s">
-        <v>1535</v>
+        <v>1527</v>
       </c>
       <c r="B767" t="s">
-        <v>1536</v>
+        <v>1528</v>
       </c>
       <c r="C767" s="2" t="s">
         <v>7</v>
@@ -16104,10 +16104,10 @@
     </row>
     <row r="768" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A768" t="s">
-        <v>1537</v>
+        <v>1531</v>
       </c>
       <c r="B768" t="s">
-        <v>1538</v>
+        <v>1532</v>
       </c>
       <c r="C768" s="2" t="s">
         <v>7</v>
@@ -16118,10 +16118,10 @@
     </row>
     <row r="769" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A769" t="s">
-        <v>1539</v>
+        <v>1533</v>
       </c>
       <c r="B769" t="s">
-        <v>1540</v>
+        <v>1534</v>
       </c>
       <c r="C769" s="2" t="s">
         <v>7</v>
@@ -16132,10 +16132,10 @@
     </row>
     <row r="770" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A770" t="s">
-        <v>1541</v>
+        <v>1535</v>
       </c>
       <c r="B770" t="s">
-        <v>1542</v>
+        <v>1536</v>
       </c>
       <c r="C770" s="2" t="s">
         <v>7</v>
@@ -16146,10 +16146,10 @@
     </row>
     <row r="771" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A771" t="s">
-        <v>1543</v>
+        <v>1537</v>
       </c>
       <c r="B771" t="s">
-        <v>1544</v>
+        <v>1538</v>
       </c>
       <c r="C771" s="2" t="s">
         <v>7</v>
@@ -16160,10 +16160,10 @@
     </row>
     <row r="772" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A772" t="s">
-        <v>1545</v>
+        <v>1539</v>
       </c>
       <c r="B772" t="s">
-        <v>1546</v>
+        <v>1540</v>
       </c>
       <c r="C772" s="2" t="s">
         <v>7</v>
@@ -16174,10 +16174,10 @@
     </row>
     <row r="773" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A773" t="s">
-        <v>1547</v>
+        <v>1541</v>
       </c>
       <c r="B773" t="s">
-        <v>1548</v>
+        <v>1542</v>
       </c>
       <c r="C773" s="2" t="s">
         <v>7</v>
@@ -16188,10 +16188,10 @@
     </row>
     <row r="774" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A774" t="s">
-        <v>1549</v>
+        <v>1543</v>
       </c>
       <c r="B774" t="s">
-        <v>1550</v>
+        <v>1544</v>
       </c>
       <c r="C774" s="2" t="s">
         <v>7</v>
@@ -16202,10 +16202,10 @@
     </row>
     <row r="775" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A775" t="s">
-        <v>1551</v>
+        <v>1545</v>
       </c>
       <c r="B775" t="s">
-        <v>1552</v>
+        <v>1546</v>
       </c>
       <c r="C775" s="2" t="s">
         <v>7</v>
@@ -16216,10 +16216,10 @@
     </row>
     <row r="776" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A776" t="s">
-        <v>1553</v>
+        <v>1547</v>
       </c>
       <c r="B776" t="s">
-        <v>1554</v>
+        <v>1548</v>
       </c>
       <c r="C776" s="2" t="s">
         <v>7</v>
@@ -16230,10 +16230,10 @@
     </row>
     <row r="777" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A777" t="s">
-        <v>1555</v>
+        <v>1549</v>
       </c>
       <c r="B777" t="s">
-        <v>1556</v>
+        <v>1550</v>
       </c>
       <c r="C777" s="2" t="s">
         <v>7</v>
@@ -16244,10 +16244,10 @@
     </row>
     <row r="778" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A778" t="s">
-        <v>1557</v>
+        <v>1551</v>
       </c>
       <c r="B778" t="s">
-        <v>1558</v>
+        <v>1552</v>
       </c>
       <c r="C778" s="2" t="s">
         <v>7</v>
@@ -16258,10 +16258,10 @@
     </row>
     <row r="779" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A779" t="s">
-        <v>1559</v>
+        <v>1553</v>
       </c>
       <c r="B779" t="s">
-        <v>1560</v>
+        <v>1554</v>
       </c>
       <c r="C779" s="2" t="s">
         <v>7</v>
@@ -16272,10 +16272,10 @@
     </row>
     <row r="780" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A780" t="s">
-        <v>1561</v>
+        <v>1555</v>
       </c>
       <c r="B780" t="s">
-        <v>1562</v>
+        <v>1556</v>
       </c>
       <c r="C780" s="2" t="s">
         <v>7</v>
@@ -16286,10 +16286,10 @@
     </row>
     <row r="781" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A781" t="s">
-        <v>1563</v>
+        <v>1557</v>
       </c>
       <c r="B781" t="s">
-        <v>1564</v>
+        <v>1558</v>
       </c>
       <c r="C781" s="2" t="s">
         <v>7</v>
@@ -16300,10 +16300,10 @@
     </row>
     <row r="782" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A782" t="s">
-        <v>1565</v>
+        <v>1559</v>
       </c>
       <c r="B782" t="s">
-        <v>1566</v>
+        <v>1560</v>
       </c>
       <c r="C782" s="2" t="s">
         <v>7</v>
@@ -16314,10 +16314,10 @@
     </row>
     <row r="783" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A783" t="s">
-        <v>1567</v>
+        <v>1561</v>
       </c>
       <c r="B783" t="s">
-        <v>1568</v>
+        <v>1562</v>
       </c>
       <c r="C783" s="2" t="s">
         <v>7</v>
@@ -16328,10 +16328,10 @@
     </row>
     <row r="784" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A784" t="s">
-        <v>1571</v>
+        <v>1563</v>
       </c>
       <c r="B784" t="s">
-        <v>1572</v>
+        <v>1564</v>
       </c>
       <c r="C784" s="2" t="s">
         <v>7</v>
@@ -16342,10 +16342,10 @@
     </row>
     <row r="785" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A785" t="s">
-        <v>1573</v>
+        <v>1565</v>
       </c>
       <c r="B785" t="s">
-        <v>1574</v>
+        <v>1566</v>
       </c>
       <c r="C785" s="2" t="s">
         <v>7</v>
@@ -16356,10 +16356,10 @@
     </row>
     <row r="786" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A786" t="s">
-        <v>1575</v>
+        <v>1567</v>
       </c>
       <c r="B786" t="s">
-        <v>1576</v>
+        <v>1568</v>
       </c>
       <c r="C786" s="2" t="s">
         <v>7</v>
@@ -16370,10 +16370,10 @@
     </row>
     <row r="787" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A787" t="s">
-        <v>1577</v>
+        <v>1571</v>
       </c>
       <c r="B787" t="s">
-        <v>1578</v>
+        <v>1572</v>
       </c>
       <c r="C787" s="2" t="s">
         <v>7</v>
@@ -16384,10 +16384,10 @@
     </row>
     <row r="788" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A788" t="s">
-        <v>1579</v>
+        <v>1573</v>
       </c>
       <c r="B788" t="s">
-        <v>1580</v>
+        <v>1574</v>
       </c>
       <c r="C788" s="2" t="s">
         <v>7</v>
@@ -16398,10 +16398,10 @@
     </row>
     <row r="789" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A789" t="s">
-        <v>1583</v>
+        <v>1575</v>
       </c>
       <c r="B789" t="s">
-        <v>1584</v>
+        <v>1576</v>
       </c>
       <c r="C789" s="2" t="s">
         <v>7</v>
@@ -16412,10 +16412,10 @@
     </row>
     <row r="790" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A790" t="s">
-        <v>1585</v>
+        <v>1577</v>
       </c>
       <c r="B790" t="s">
-        <v>1586</v>
+        <v>1578</v>
       </c>
       <c r="C790" s="2" t="s">
         <v>7</v>
@@ -16426,10 +16426,10 @@
     </row>
     <row r="791" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A791" t="s">
-        <v>1587</v>
+        <v>1579</v>
       </c>
       <c r="B791" t="s">
-        <v>1588</v>
+        <v>1580</v>
       </c>
       <c r="C791" s="2" t="s">
         <v>7</v>
@@ -16440,10 +16440,10 @@
     </row>
     <row r="792" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A792" t="s">
-        <v>1589</v>
+        <v>1583</v>
       </c>
       <c r="B792" t="s">
-        <v>1590</v>
+        <v>1584</v>
       </c>
       <c r="C792" s="2" t="s">
         <v>7</v>
@@ -16454,10 +16454,10 @@
     </row>
     <row r="793" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A793" t="s">
-        <v>1591</v>
+        <v>1585</v>
       </c>
       <c r="B793" t="s">
-        <v>1592</v>
+        <v>1586</v>
       </c>
       <c r="C793" s="2" t="s">
         <v>7</v>
@@ -16468,10 +16468,10 @@
     </row>
     <row r="794" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A794" t="s">
-        <v>1593</v>
+        <v>1587</v>
       </c>
       <c r="B794" t="s">
-        <v>1594</v>
+        <v>1588</v>
       </c>
       <c r="C794" s="2" t="s">
         <v>7</v>
@@ -16482,10 +16482,10 @@
     </row>
     <row r="795" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A795" t="s">
-        <v>1595</v>
+        <v>1589</v>
       </c>
       <c r="B795" t="s">
-        <v>1596</v>
+        <v>1590</v>
       </c>
       <c r="C795" s="2" t="s">
         <v>7</v>
@@ -16496,10 +16496,10 @@
     </row>
     <row r="796" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A796" t="s">
-        <v>1597</v>
+        <v>1591</v>
       </c>
       <c r="B796" t="s">
-        <v>1598</v>
+        <v>1592</v>
       </c>
       <c r="C796" s="2" t="s">
         <v>7</v>
@@ -16510,10 +16510,10 @@
     </row>
     <row r="797" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A797" t="s">
-        <v>1599</v>
+        <v>1593</v>
       </c>
       <c r="B797" t="s">
-        <v>1600</v>
+        <v>1594</v>
       </c>
       <c r="C797" s="2" t="s">
         <v>7</v>
@@ -16524,10 +16524,10 @@
     </row>
     <row r="798" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A798" t="s">
-        <v>1601</v>
+        <v>1595</v>
       </c>
       <c r="B798" t="s">
-        <v>1602</v>
+        <v>1596</v>
       </c>
       <c r="C798" s="2" t="s">
         <v>7</v>
@@ -16538,10 +16538,10 @@
     </row>
     <row r="799" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A799" t="s">
-        <v>1603</v>
+        <v>1597</v>
       </c>
       <c r="B799" t="s">
-        <v>1604</v>
+        <v>1598</v>
       </c>
       <c r="C799" s="2" t="s">
         <v>7</v>
@@ -16552,10 +16552,10 @@
     </row>
     <row r="800" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A800" t="s">
-        <v>1605</v>
+        <v>1599</v>
       </c>
       <c r="B800" t="s">
-        <v>1606</v>
+        <v>1600</v>
       </c>
       <c r="C800" s="2" t="s">
         <v>7</v>
@@ -16566,10 +16566,10 @@
     </row>
     <row r="801" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A801" t="s">
-        <v>1607</v>
+        <v>1601</v>
       </c>
       <c r="B801" t="s">
-        <v>1608</v>
+        <v>1602</v>
       </c>
       <c r="C801" s="2" t="s">
         <v>7</v>
@@ -16580,10 +16580,10 @@
     </row>
     <row r="802" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A802" t="s">
-        <v>1609</v>
+        <v>1603</v>
       </c>
       <c r="B802" t="s">
-        <v>1610</v>
+        <v>1604</v>
       </c>
       <c r="C802" s="2" t="s">
         <v>7</v>
@@ -16594,10 +16594,10 @@
     </row>
     <row r="803" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A803" t="s">
-        <v>1615</v>
+        <v>1605</v>
       </c>
       <c r="B803" t="s">
-        <v>1616</v>
+        <v>1606</v>
       </c>
       <c r="C803" s="2" t="s">
         <v>7</v>
@@ -16608,10 +16608,10 @@
     </row>
     <row r="804" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A804" t="s">
-        <v>1617</v>
+        <v>1607</v>
       </c>
       <c r="B804" t="s">
-        <v>1618</v>
+        <v>1608</v>
       </c>
       <c r="C804" s="2" t="s">
         <v>7</v>
@@ -16622,10 +16622,10 @@
     </row>
     <row r="805" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A805" t="s">
-        <v>1619</v>
+        <v>1609</v>
       </c>
       <c r="B805" t="s">
-        <v>1620</v>
+        <v>1610</v>
       </c>
       <c r="C805" s="2" t="s">
         <v>7</v>
@@ -16636,10 +16636,10 @@
     </row>
     <row r="806" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A806" t="s">
-        <v>1621</v>
+        <v>1611</v>
       </c>
       <c r="B806" t="s">
-        <v>1622</v>
+        <v>1612</v>
       </c>
       <c r="C806" s="2" t="s">
         <v>7</v>
@@ -16650,10 +16650,10 @@
     </row>
     <row r="807" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A807" t="s">
-        <v>1625</v>
+        <v>1615</v>
       </c>
       <c r="B807" t="s">
-        <v>1626</v>
+        <v>1616</v>
       </c>
       <c r="C807" s="2" t="s">
         <v>7</v>
@@ -16664,10 +16664,10 @@
     </row>
     <row r="808" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A808" t="s">
-        <v>1627</v>
+        <v>1617</v>
       </c>
       <c r="B808" t="s">
-        <v>1628</v>
+        <v>1618</v>
       </c>
       <c r="C808" s="2" t="s">
         <v>7</v>
@@ -16678,10 +16678,10 @@
     </row>
     <row r="809" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A809" t="s">
-        <v>1629</v>
+        <v>1619</v>
       </c>
       <c r="B809" t="s">
-        <v>1630</v>
+        <v>1620</v>
       </c>
       <c r="C809" s="2" t="s">
         <v>7</v>
@@ -16692,10 +16692,10 @@
     </row>
     <row r="810" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A810" t="s">
-        <v>1631</v>
+        <v>1621</v>
       </c>
       <c r="B810" t="s">
-        <v>1632</v>
+        <v>1622</v>
       </c>
       <c r="C810" s="2" t="s">
         <v>7</v>
@@ -16706,10 +16706,10 @@
     </row>
     <row r="811" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A811" t="s">
-        <v>1633</v>
+        <v>1623</v>
       </c>
       <c r="B811" t="s">
-        <v>1634</v>
+        <v>1624</v>
       </c>
       <c r="C811" s="2" t="s">
         <v>7</v>
@@ -16720,10 +16720,10 @@
     </row>
     <row r="812" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A812" t="s">
-        <v>1635</v>
+        <v>1625</v>
       </c>
       <c r="B812" t="s">
-        <v>1636</v>
+        <v>1626</v>
       </c>
       <c r="C812" s="2" t="s">
         <v>7</v>
@@ -16734,10 +16734,10 @@
     </row>
     <row r="813" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A813" t="s">
-        <v>1637</v>
+        <v>1627</v>
       </c>
       <c r="B813" t="s">
-        <v>1638</v>
+        <v>1628</v>
       </c>
       <c r="C813" s="2" t="s">
         <v>7</v>
@@ -16748,10 +16748,10 @@
     </row>
     <row r="814" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A814" t="s">
-        <v>781</v>
+        <v>1629</v>
       </c>
       <c r="B814" t="s">
-        <v>782</v>
+        <v>1630</v>
       </c>
       <c r="C814" s="2" t="s">
         <v>7</v>
@@ -16762,10 +16762,10 @@
     </row>
     <row r="815" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A815" t="s">
-        <v>805</v>
+        <v>1631</v>
       </c>
       <c r="B815" t="s">
-        <v>806</v>
+        <v>1632</v>
       </c>
       <c r="C815" s="2" t="s">
         <v>7</v>
@@ -16776,10 +16776,10 @@
     </row>
     <row r="816" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A816" t="s">
-        <v>1005</v>
+        <v>1633</v>
       </c>
       <c r="B816" t="s">
-        <v>1006</v>
+        <v>1634</v>
       </c>
       <c r="C816" s="2" t="s">
         <v>7</v>
@@ -16790,10 +16790,10 @@
     </row>
     <row r="817" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A817" t="s">
-        <v>1611</v>
+        <v>1635</v>
       </c>
       <c r="B817" t="s">
-        <v>1612</v>
+        <v>1636</v>
       </c>
       <c r="C817" s="2" t="s">
         <v>7</v>
@@ -16804,10 +16804,10 @@
     </row>
     <row r="818" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A818" t="s">
-        <v>1623</v>
+        <v>1637</v>
       </c>
       <c r="B818" t="s">
-        <v>1624</v>
+        <v>1638</v>
       </c>
       <c r="C818" s="2" t="s">
         <v>7</v>
@@ -16828,7 +16828,7 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="C55" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="C56" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
     <hyperlink ref="C57" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
     <hyperlink ref="C58" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
@@ -16851,7 +16851,7 @@
     <hyperlink ref="C75" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
     <hyperlink ref="C76" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
     <hyperlink ref="C77" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="C3" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="C2" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
     <hyperlink ref="C78" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
     <hyperlink ref="C79" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
     <hyperlink ref="C80" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
@@ -16859,7 +16859,7 @@
     <hyperlink ref="C82" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
     <hyperlink ref="C83" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
     <hyperlink ref="C84" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="C4" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="C3" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
     <hyperlink ref="C85" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
     <hyperlink ref="C86" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
     <hyperlink ref="C87" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
@@ -16878,8 +16878,8 @@
     <hyperlink ref="C100" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
     <hyperlink ref="C101" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
     <hyperlink ref="C102" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="C5" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="C6" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="C4" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="C5" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
     <hyperlink ref="C103" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
     <hyperlink ref="C104" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
     <hyperlink ref="C105" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
@@ -16899,9 +16899,9 @@
     <hyperlink ref="C119" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
     <hyperlink ref="C120" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
     <hyperlink ref="C121" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="C7" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
-    <hyperlink ref="C8" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="C9" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="C6" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="C7" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="C8" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
     <hyperlink ref="C122" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
     <hyperlink ref="C123" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
     <hyperlink ref="C124" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
@@ -16914,10 +16914,10 @@
     <hyperlink ref="C131" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
     <hyperlink ref="C132" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
     <hyperlink ref="C133" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="C10" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="C9" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
     <hyperlink ref="C134" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
     <hyperlink ref="C135" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="C11" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="C10" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
     <hyperlink ref="C136" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
     <hyperlink ref="C137" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
     <hyperlink ref="C138" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
@@ -16957,17 +16957,17 @@
     <hyperlink ref="C172" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
     <hyperlink ref="C173" r:id="rId128" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
     <hyperlink ref="C174" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
-    <hyperlink ref="C12" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
+    <hyperlink ref="C11" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
     <hyperlink ref="C175" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
     <hyperlink ref="C176" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
     <hyperlink ref="C177" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
-    <hyperlink ref="C13" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
+    <hyperlink ref="C12" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
     <hyperlink ref="C178" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
-    <hyperlink ref="C14" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
+    <hyperlink ref="C13" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
     <hyperlink ref="C179" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
     <hyperlink ref="C180" r:id="rId138" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
     <hyperlink ref="C181" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
-    <hyperlink ref="C15" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
+    <hyperlink ref="C14" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
     <hyperlink ref="C182" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
     <hyperlink ref="C183" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
     <hyperlink ref="C184" r:id="rId143" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
@@ -16978,7 +16978,7 @@
     <hyperlink ref="C189" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
     <hyperlink ref="C190" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
     <hyperlink ref="C191" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
-    <hyperlink ref="C16" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
+    <hyperlink ref="C15" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
     <hyperlink ref="C192" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
     <hyperlink ref="C193" r:id="rId153" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
     <hyperlink ref="C194" r:id="rId154" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
@@ -16995,7 +16995,7 @@
     <hyperlink ref="C205" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
     <hyperlink ref="C206" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
     <hyperlink ref="C207" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
-    <hyperlink ref="C17" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
+    <hyperlink ref="C16" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
     <hyperlink ref="C208" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
     <hyperlink ref="C209" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
     <hyperlink ref="C210" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
@@ -17014,18 +17014,18 @@
     <hyperlink ref="C223" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
     <hyperlink ref="C224" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
     <hyperlink ref="C225" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
-    <hyperlink ref="C18" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
+    <hyperlink ref="C17" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
     <hyperlink ref="C226" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
     <hyperlink ref="C227" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
     <hyperlink ref="C228" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
-    <hyperlink ref="C19" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
+    <hyperlink ref="C18" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
     <hyperlink ref="C229" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
     <hyperlink ref="C230" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
     <hyperlink ref="C231" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
     <hyperlink ref="C232" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
     <hyperlink ref="C233" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
     <hyperlink ref="C234" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
-    <hyperlink ref="C20" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
+    <hyperlink ref="C19" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
     <hyperlink ref="C235" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
     <hyperlink ref="C236" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
     <hyperlink ref="C237" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
@@ -17044,7 +17044,7 @@
     <hyperlink ref="C250" r:id="rId214" xr:uid="{00000000-0004-0000-0000-0000D5000000}"/>
     <hyperlink ref="C251" r:id="rId215" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
     <hyperlink ref="C252" r:id="rId216" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
-    <hyperlink ref="C21" r:id="rId217" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
+    <hyperlink ref="C20" r:id="rId217" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
     <hyperlink ref="C253" r:id="rId218" xr:uid="{00000000-0004-0000-0000-0000D9000000}"/>
     <hyperlink ref="C254" r:id="rId219" xr:uid="{00000000-0004-0000-0000-0000DA000000}"/>
     <hyperlink ref="C255" r:id="rId220" xr:uid="{00000000-0004-0000-0000-0000DB000000}"/>
@@ -17073,12 +17073,12 @@
     <hyperlink ref="C278" r:id="rId243" xr:uid="{00000000-0004-0000-0000-0000F2000000}"/>
     <hyperlink ref="C279" r:id="rId244" xr:uid="{00000000-0004-0000-0000-0000F3000000}"/>
     <hyperlink ref="C280" r:id="rId245" xr:uid="{00000000-0004-0000-0000-0000F4000000}"/>
-    <hyperlink ref="C22" r:id="rId246" xr:uid="{00000000-0004-0000-0000-0000F5000000}"/>
+    <hyperlink ref="C21" r:id="rId246" xr:uid="{00000000-0004-0000-0000-0000F5000000}"/>
     <hyperlink ref="C281" r:id="rId247" xr:uid="{00000000-0004-0000-0000-0000F6000000}"/>
     <hyperlink ref="C282" r:id="rId248" xr:uid="{00000000-0004-0000-0000-0000F7000000}"/>
     <hyperlink ref="C283" r:id="rId249" xr:uid="{00000000-0004-0000-0000-0000F8000000}"/>
     <hyperlink ref="C284" r:id="rId250" xr:uid="{00000000-0004-0000-0000-0000F9000000}"/>
-    <hyperlink ref="C23" r:id="rId251" xr:uid="{00000000-0004-0000-0000-0000FA000000}"/>
+    <hyperlink ref="C22" r:id="rId251" xr:uid="{00000000-0004-0000-0000-0000FA000000}"/>
     <hyperlink ref="C285" r:id="rId252" xr:uid="{00000000-0004-0000-0000-0000FB000000}"/>
     <hyperlink ref="C286" r:id="rId253" xr:uid="{00000000-0004-0000-0000-0000FC000000}"/>
     <hyperlink ref="C287" r:id="rId254" xr:uid="{00000000-0004-0000-0000-0000FD000000}"/>
@@ -17088,7 +17088,7 @@
     <hyperlink ref="C291" r:id="rId258" xr:uid="{00000000-0004-0000-0000-000001010000}"/>
     <hyperlink ref="C292" r:id="rId259" xr:uid="{00000000-0004-0000-0000-000002010000}"/>
     <hyperlink ref="C293" r:id="rId260" xr:uid="{00000000-0004-0000-0000-000003010000}"/>
-    <hyperlink ref="C24" r:id="rId261" xr:uid="{00000000-0004-0000-0000-000004010000}"/>
+    <hyperlink ref="C23" r:id="rId261" xr:uid="{00000000-0004-0000-0000-000004010000}"/>
     <hyperlink ref="C294" r:id="rId262" xr:uid="{00000000-0004-0000-0000-000005010000}"/>
     <hyperlink ref="C295" r:id="rId263" xr:uid="{00000000-0004-0000-0000-000006010000}"/>
     <hyperlink ref="C296" r:id="rId264" xr:uid="{00000000-0004-0000-0000-000007010000}"/>
@@ -17108,7 +17108,7 @@
     <hyperlink ref="C310" r:id="rId278" xr:uid="{00000000-0004-0000-0000-000015010000}"/>
     <hyperlink ref="C311" r:id="rId279" xr:uid="{00000000-0004-0000-0000-000016010000}"/>
     <hyperlink ref="C312" r:id="rId280" xr:uid="{00000000-0004-0000-0000-000017010000}"/>
-    <hyperlink ref="C25" r:id="rId281" xr:uid="{00000000-0004-0000-0000-000018010000}"/>
+    <hyperlink ref="C24" r:id="rId281" xr:uid="{00000000-0004-0000-0000-000018010000}"/>
     <hyperlink ref="C313" r:id="rId282" xr:uid="{00000000-0004-0000-0000-000019010000}"/>
     <hyperlink ref="C314" r:id="rId283" xr:uid="{00000000-0004-0000-0000-00001A010000}"/>
     <hyperlink ref="C315" r:id="rId284" xr:uid="{00000000-0004-0000-0000-00001B010000}"/>
@@ -17118,7 +17118,7 @@
     <hyperlink ref="C319" r:id="rId288" xr:uid="{00000000-0004-0000-0000-00001F010000}"/>
     <hyperlink ref="C320" r:id="rId289" xr:uid="{00000000-0004-0000-0000-000020010000}"/>
     <hyperlink ref="C321" r:id="rId290" xr:uid="{00000000-0004-0000-0000-000021010000}"/>
-    <hyperlink ref="C26" r:id="rId291" xr:uid="{00000000-0004-0000-0000-000022010000}"/>
+    <hyperlink ref="C25" r:id="rId291" xr:uid="{00000000-0004-0000-0000-000022010000}"/>
     <hyperlink ref="C322" r:id="rId292" xr:uid="{00000000-0004-0000-0000-000023010000}"/>
     <hyperlink ref="C323" r:id="rId293" xr:uid="{00000000-0004-0000-0000-000024010000}"/>
     <hyperlink ref="C324" r:id="rId294" xr:uid="{00000000-0004-0000-0000-000025010000}"/>
@@ -17147,14 +17147,14 @@
     <hyperlink ref="C347" r:id="rId317" xr:uid="{00000000-0004-0000-0000-00003C010000}"/>
     <hyperlink ref="C348" r:id="rId318" xr:uid="{00000000-0004-0000-0000-00003D010000}"/>
     <hyperlink ref="C349" r:id="rId319" xr:uid="{00000000-0004-0000-0000-00003E010000}"/>
-    <hyperlink ref="C27" r:id="rId320" xr:uid="{00000000-0004-0000-0000-00003F010000}"/>
-    <hyperlink ref="C28" r:id="rId321" xr:uid="{00000000-0004-0000-0000-000040010000}"/>
+    <hyperlink ref="C26" r:id="rId320" xr:uid="{00000000-0004-0000-0000-00003F010000}"/>
+    <hyperlink ref="C27" r:id="rId321" xr:uid="{00000000-0004-0000-0000-000040010000}"/>
     <hyperlink ref="C350" r:id="rId322" xr:uid="{00000000-0004-0000-0000-000041010000}"/>
     <hyperlink ref="C351" r:id="rId323" xr:uid="{00000000-0004-0000-0000-000042010000}"/>
     <hyperlink ref="C352" r:id="rId324" xr:uid="{00000000-0004-0000-0000-000043010000}"/>
     <hyperlink ref="C353" r:id="rId325" xr:uid="{00000000-0004-0000-0000-000044010000}"/>
     <hyperlink ref="C354" r:id="rId326" xr:uid="{00000000-0004-0000-0000-000045010000}"/>
-    <hyperlink ref="C29" r:id="rId327" xr:uid="{00000000-0004-0000-0000-000046010000}"/>
+    <hyperlink ref="C28" r:id="rId327" xr:uid="{00000000-0004-0000-0000-000046010000}"/>
     <hyperlink ref="C355" r:id="rId328" xr:uid="{00000000-0004-0000-0000-000047010000}"/>
     <hyperlink ref="C356" r:id="rId329" xr:uid="{00000000-0004-0000-0000-000048010000}"/>
     <hyperlink ref="C357" r:id="rId330" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
@@ -17216,435 +17216,435 @@
     <hyperlink ref="C413" r:id="rId386" xr:uid="{00000000-0004-0000-0000-000081010000}"/>
     <hyperlink ref="C414" r:id="rId387" xr:uid="{00000000-0004-0000-0000-000082010000}"/>
     <hyperlink ref="C415" r:id="rId388" xr:uid="{00000000-0004-0000-0000-000083010000}"/>
-    <hyperlink ref="C814" r:id="rId389" xr:uid="{00000000-0004-0000-0000-000084010000}"/>
-    <hyperlink ref="C416" r:id="rId390" xr:uid="{00000000-0004-0000-0000-000085010000}"/>
-    <hyperlink ref="C417" r:id="rId391" xr:uid="{00000000-0004-0000-0000-000086010000}"/>
-    <hyperlink ref="C418" r:id="rId392" xr:uid="{00000000-0004-0000-0000-000087010000}"/>
-    <hyperlink ref="C419" r:id="rId393" xr:uid="{00000000-0004-0000-0000-000088010000}"/>
-    <hyperlink ref="C420" r:id="rId394" xr:uid="{00000000-0004-0000-0000-000089010000}"/>
-    <hyperlink ref="C421" r:id="rId395" xr:uid="{00000000-0004-0000-0000-00008A010000}"/>
-    <hyperlink ref="C422" r:id="rId396" xr:uid="{00000000-0004-0000-0000-00008B010000}"/>
-    <hyperlink ref="C423" r:id="rId397" xr:uid="{00000000-0004-0000-0000-00008C010000}"/>
-    <hyperlink ref="C424" r:id="rId398" xr:uid="{00000000-0004-0000-0000-00008D010000}"/>
-    <hyperlink ref="C425" r:id="rId399" xr:uid="{00000000-0004-0000-0000-00008E010000}"/>
-    <hyperlink ref="C426" r:id="rId400" xr:uid="{00000000-0004-0000-0000-00008F010000}"/>
-    <hyperlink ref="C815" r:id="rId401" xr:uid="{00000000-0004-0000-0000-000090010000}"/>
-    <hyperlink ref="C427" r:id="rId402" xr:uid="{00000000-0004-0000-0000-000091010000}"/>
-    <hyperlink ref="C428" r:id="rId403" xr:uid="{00000000-0004-0000-0000-000092010000}"/>
-    <hyperlink ref="C429" r:id="rId404" xr:uid="{00000000-0004-0000-0000-000093010000}"/>
-    <hyperlink ref="C430" r:id="rId405" xr:uid="{00000000-0004-0000-0000-000094010000}"/>
-    <hyperlink ref="C431" r:id="rId406" xr:uid="{00000000-0004-0000-0000-000095010000}"/>
-    <hyperlink ref="C432" r:id="rId407" xr:uid="{00000000-0004-0000-0000-000096010000}"/>
-    <hyperlink ref="C433" r:id="rId408" xr:uid="{00000000-0004-0000-0000-000097010000}"/>
-    <hyperlink ref="C434" r:id="rId409" xr:uid="{00000000-0004-0000-0000-000098010000}"/>
-    <hyperlink ref="C435" r:id="rId410" xr:uid="{00000000-0004-0000-0000-000099010000}"/>
-    <hyperlink ref="C436" r:id="rId411" xr:uid="{00000000-0004-0000-0000-00009A010000}"/>
-    <hyperlink ref="C437" r:id="rId412" xr:uid="{00000000-0004-0000-0000-00009B010000}"/>
-    <hyperlink ref="C438" r:id="rId413" xr:uid="{00000000-0004-0000-0000-00009C010000}"/>
-    <hyperlink ref="C439" r:id="rId414" xr:uid="{00000000-0004-0000-0000-00009D010000}"/>
-    <hyperlink ref="C440" r:id="rId415" xr:uid="{00000000-0004-0000-0000-00009E010000}"/>
-    <hyperlink ref="C441" r:id="rId416" xr:uid="{00000000-0004-0000-0000-00009F010000}"/>
-    <hyperlink ref="C442" r:id="rId417" xr:uid="{00000000-0004-0000-0000-0000A0010000}"/>
-    <hyperlink ref="C30" r:id="rId418" xr:uid="{00000000-0004-0000-0000-0000A1010000}"/>
-    <hyperlink ref="C443" r:id="rId419" xr:uid="{00000000-0004-0000-0000-0000A2010000}"/>
-    <hyperlink ref="C444" r:id="rId420" xr:uid="{00000000-0004-0000-0000-0000A3010000}"/>
-    <hyperlink ref="C445" r:id="rId421" xr:uid="{00000000-0004-0000-0000-0000A4010000}"/>
-    <hyperlink ref="C446" r:id="rId422" xr:uid="{00000000-0004-0000-0000-0000A5010000}"/>
-    <hyperlink ref="C447" r:id="rId423" xr:uid="{00000000-0004-0000-0000-0000A6010000}"/>
-    <hyperlink ref="C448" r:id="rId424" xr:uid="{00000000-0004-0000-0000-0000A7010000}"/>
-    <hyperlink ref="C31" r:id="rId425" xr:uid="{00000000-0004-0000-0000-0000A8010000}"/>
-    <hyperlink ref="C449" r:id="rId426" xr:uid="{00000000-0004-0000-0000-0000A9010000}"/>
-    <hyperlink ref="C450" r:id="rId427" xr:uid="{00000000-0004-0000-0000-0000AA010000}"/>
-    <hyperlink ref="C451" r:id="rId428" xr:uid="{00000000-0004-0000-0000-0000AB010000}"/>
-    <hyperlink ref="C452" r:id="rId429" xr:uid="{00000000-0004-0000-0000-0000AC010000}"/>
-    <hyperlink ref="C453" r:id="rId430" xr:uid="{00000000-0004-0000-0000-0000AD010000}"/>
-    <hyperlink ref="C454" r:id="rId431" xr:uid="{00000000-0004-0000-0000-0000AE010000}"/>
-    <hyperlink ref="C455" r:id="rId432" xr:uid="{00000000-0004-0000-0000-0000AF010000}"/>
-    <hyperlink ref="C456" r:id="rId433" xr:uid="{00000000-0004-0000-0000-0000B0010000}"/>
-    <hyperlink ref="C457" r:id="rId434" xr:uid="{00000000-0004-0000-0000-0000B1010000}"/>
-    <hyperlink ref="C458" r:id="rId435" xr:uid="{00000000-0004-0000-0000-0000B2010000}"/>
-    <hyperlink ref="C459" r:id="rId436" xr:uid="{00000000-0004-0000-0000-0000B3010000}"/>
-    <hyperlink ref="C460" r:id="rId437" xr:uid="{00000000-0004-0000-0000-0000B4010000}"/>
-    <hyperlink ref="C461" r:id="rId438" xr:uid="{00000000-0004-0000-0000-0000B5010000}"/>
-    <hyperlink ref="C462" r:id="rId439" xr:uid="{00000000-0004-0000-0000-0000B6010000}"/>
-    <hyperlink ref="C463" r:id="rId440" xr:uid="{00000000-0004-0000-0000-0000B7010000}"/>
-    <hyperlink ref="C464" r:id="rId441" xr:uid="{00000000-0004-0000-0000-0000B8010000}"/>
-    <hyperlink ref="C465" r:id="rId442" xr:uid="{00000000-0004-0000-0000-0000B9010000}"/>
-    <hyperlink ref="C466" r:id="rId443" xr:uid="{00000000-0004-0000-0000-0000BA010000}"/>
-    <hyperlink ref="C467" r:id="rId444" xr:uid="{00000000-0004-0000-0000-0000BB010000}"/>
-    <hyperlink ref="C32" r:id="rId445" xr:uid="{00000000-0004-0000-0000-0000BC010000}"/>
-    <hyperlink ref="C468" r:id="rId446" xr:uid="{00000000-0004-0000-0000-0000BD010000}"/>
-    <hyperlink ref="C469" r:id="rId447" xr:uid="{00000000-0004-0000-0000-0000BE010000}"/>
-    <hyperlink ref="C470" r:id="rId448" xr:uid="{00000000-0004-0000-0000-0000BF010000}"/>
-    <hyperlink ref="C471" r:id="rId449" xr:uid="{00000000-0004-0000-0000-0000C0010000}"/>
-    <hyperlink ref="C472" r:id="rId450" xr:uid="{00000000-0004-0000-0000-0000C1010000}"/>
-    <hyperlink ref="C473" r:id="rId451" xr:uid="{00000000-0004-0000-0000-0000C2010000}"/>
-    <hyperlink ref="C33" r:id="rId452" xr:uid="{00000000-0004-0000-0000-0000C3010000}"/>
-    <hyperlink ref="C474" r:id="rId453" xr:uid="{00000000-0004-0000-0000-0000C4010000}"/>
-    <hyperlink ref="C475" r:id="rId454" xr:uid="{00000000-0004-0000-0000-0000C5010000}"/>
-    <hyperlink ref="C476" r:id="rId455" xr:uid="{00000000-0004-0000-0000-0000C6010000}"/>
-    <hyperlink ref="C477" r:id="rId456" xr:uid="{00000000-0004-0000-0000-0000C7010000}"/>
-    <hyperlink ref="C478" r:id="rId457" xr:uid="{00000000-0004-0000-0000-0000C8010000}"/>
-    <hyperlink ref="C479" r:id="rId458" xr:uid="{00000000-0004-0000-0000-0000C9010000}"/>
-    <hyperlink ref="C480" r:id="rId459" xr:uid="{00000000-0004-0000-0000-0000CA010000}"/>
-    <hyperlink ref="C481" r:id="rId460" xr:uid="{00000000-0004-0000-0000-0000CB010000}"/>
-    <hyperlink ref="C482" r:id="rId461" xr:uid="{00000000-0004-0000-0000-0000CC010000}"/>
-    <hyperlink ref="C483" r:id="rId462" xr:uid="{00000000-0004-0000-0000-0000CD010000}"/>
-    <hyperlink ref="C484" r:id="rId463" xr:uid="{00000000-0004-0000-0000-0000CE010000}"/>
-    <hyperlink ref="C34" r:id="rId464" xr:uid="{00000000-0004-0000-0000-0000CF010000}"/>
-    <hyperlink ref="C485" r:id="rId465" xr:uid="{00000000-0004-0000-0000-0000D0010000}"/>
-    <hyperlink ref="C486" r:id="rId466" xr:uid="{00000000-0004-0000-0000-0000D1010000}"/>
-    <hyperlink ref="C487" r:id="rId467" xr:uid="{00000000-0004-0000-0000-0000D2010000}"/>
-    <hyperlink ref="C488" r:id="rId468" xr:uid="{00000000-0004-0000-0000-0000D3010000}"/>
-    <hyperlink ref="C489" r:id="rId469" xr:uid="{00000000-0004-0000-0000-0000D4010000}"/>
-    <hyperlink ref="C490" r:id="rId470" xr:uid="{00000000-0004-0000-0000-0000D5010000}"/>
-    <hyperlink ref="C491" r:id="rId471" xr:uid="{00000000-0004-0000-0000-0000D6010000}"/>
-    <hyperlink ref="C35" r:id="rId472" xr:uid="{00000000-0004-0000-0000-0000D7010000}"/>
-    <hyperlink ref="C492" r:id="rId473" xr:uid="{00000000-0004-0000-0000-0000D8010000}"/>
-    <hyperlink ref="C493" r:id="rId474" xr:uid="{00000000-0004-0000-0000-0000D9010000}"/>
-    <hyperlink ref="C494" r:id="rId475" xr:uid="{00000000-0004-0000-0000-0000DA010000}"/>
-    <hyperlink ref="C495" r:id="rId476" xr:uid="{00000000-0004-0000-0000-0000DB010000}"/>
-    <hyperlink ref="C496" r:id="rId477" xr:uid="{00000000-0004-0000-0000-0000DC010000}"/>
-    <hyperlink ref="C497" r:id="rId478" xr:uid="{00000000-0004-0000-0000-0000DD010000}"/>
-    <hyperlink ref="C498" r:id="rId479" xr:uid="{00000000-0004-0000-0000-0000DE010000}"/>
-    <hyperlink ref="C499" r:id="rId480" xr:uid="{00000000-0004-0000-0000-0000DF010000}"/>
-    <hyperlink ref="C500" r:id="rId481" xr:uid="{00000000-0004-0000-0000-0000E0010000}"/>
-    <hyperlink ref="C501" r:id="rId482" xr:uid="{00000000-0004-0000-0000-0000E1010000}"/>
-    <hyperlink ref="C502" r:id="rId483" xr:uid="{00000000-0004-0000-0000-0000E2010000}"/>
-    <hyperlink ref="C503" r:id="rId484" xr:uid="{00000000-0004-0000-0000-0000E3010000}"/>
-    <hyperlink ref="C504" r:id="rId485" xr:uid="{00000000-0004-0000-0000-0000E4010000}"/>
-    <hyperlink ref="C505" r:id="rId486" xr:uid="{00000000-0004-0000-0000-0000E5010000}"/>
-    <hyperlink ref="C506" r:id="rId487" xr:uid="{00000000-0004-0000-0000-0000E6010000}"/>
-    <hyperlink ref="C507" r:id="rId488" xr:uid="{00000000-0004-0000-0000-0000E7010000}"/>
-    <hyperlink ref="C508" r:id="rId489" xr:uid="{00000000-0004-0000-0000-0000E8010000}"/>
-    <hyperlink ref="C509" r:id="rId490" xr:uid="{00000000-0004-0000-0000-0000E9010000}"/>
-    <hyperlink ref="C510" r:id="rId491" xr:uid="{00000000-0004-0000-0000-0000EA010000}"/>
-    <hyperlink ref="C511" r:id="rId492" xr:uid="{00000000-0004-0000-0000-0000EB010000}"/>
-    <hyperlink ref="C512" r:id="rId493" xr:uid="{00000000-0004-0000-0000-0000EC010000}"/>
-    <hyperlink ref="C513" r:id="rId494" xr:uid="{00000000-0004-0000-0000-0000ED010000}"/>
-    <hyperlink ref="C514" r:id="rId495" xr:uid="{00000000-0004-0000-0000-0000EE010000}"/>
-    <hyperlink ref="C515" r:id="rId496" xr:uid="{00000000-0004-0000-0000-0000EF010000}"/>
-    <hyperlink ref="C516" r:id="rId497" xr:uid="{00000000-0004-0000-0000-0000F0010000}"/>
-    <hyperlink ref="C517" r:id="rId498" xr:uid="{00000000-0004-0000-0000-0000F1010000}"/>
-    <hyperlink ref="C518" r:id="rId499" xr:uid="{00000000-0004-0000-0000-0000F2010000}"/>
-    <hyperlink ref="C519" r:id="rId500" xr:uid="{00000000-0004-0000-0000-0000F3010000}"/>
-    <hyperlink ref="C816" r:id="rId501" xr:uid="{00000000-0004-0000-0000-0000F4010000}"/>
-    <hyperlink ref="C520" r:id="rId502" xr:uid="{00000000-0004-0000-0000-0000F5010000}"/>
-    <hyperlink ref="C521" r:id="rId503" xr:uid="{00000000-0004-0000-0000-0000F6010000}"/>
-    <hyperlink ref="C522" r:id="rId504" xr:uid="{00000000-0004-0000-0000-0000F7010000}"/>
-    <hyperlink ref="C523" r:id="rId505" xr:uid="{00000000-0004-0000-0000-0000F8010000}"/>
-    <hyperlink ref="C524" r:id="rId506" xr:uid="{00000000-0004-0000-0000-0000F9010000}"/>
-    <hyperlink ref="C525" r:id="rId507" xr:uid="{00000000-0004-0000-0000-0000FA010000}"/>
-    <hyperlink ref="C526" r:id="rId508" xr:uid="{00000000-0004-0000-0000-0000FB010000}"/>
-    <hyperlink ref="C527" r:id="rId509" xr:uid="{00000000-0004-0000-0000-0000FC010000}"/>
-    <hyperlink ref="C528" r:id="rId510" xr:uid="{00000000-0004-0000-0000-0000FD010000}"/>
-    <hyperlink ref="C529" r:id="rId511" xr:uid="{00000000-0004-0000-0000-0000FE010000}"/>
-    <hyperlink ref="C530" r:id="rId512" xr:uid="{00000000-0004-0000-0000-0000FF010000}"/>
-    <hyperlink ref="C531" r:id="rId513" xr:uid="{00000000-0004-0000-0000-000000020000}"/>
-    <hyperlink ref="C532" r:id="rId514" xr:uid="{00000000-0004-0000-0000-000001020000}"/>
-    <hyperlink ref="C533" r:id="rId515" xr:uid="{00000000-0004-0000-0000-000002020000}"/>
-    <hyperlink ref="C534" r:id="rId516" xr:uid="{00000000-0004-0000-0000-000003020000}"/>
-    <hyperlink ref="C36" r:id="rId517" xr:uid="{00000000-0004-0000-0000-000004020000}"/>
-    <hyperlink ref="C535" r:id="rId518" xr:uid="{00000000-0004-0000-0000-000005020000}"/>
-    <hyperlink ref="C536" r:id="rId519" xr:uid="{00000000-0004-0000-0000-000006020000}"/>
-    <hyperlink ref="C537" r:id="rId520" xr:uid="{00000000-0004-0000-0000-000007020000}"/>
-    <hyperlink ref="C538" r:id="rId521" xr:uid="{00000000-0004-0000-0000-000008020000}"/>
-    <hyperlink ref="C539" r:id="rId522" xr:uid="{00000000-0004-0000-0000-000009020000}"/>
-    <hyperlink ref="C540" r:id="rId523" xr:uid="{00000000-0004-0000-0000-00000A020000}"/>
-    <hyperlink ref="C541" r:id="rId524" xr:uid="{00000000-0004-0000-0000-00000B020000}"/>
-    <hyperlink ref="C542" r:id="rId525" xr:uid="{00000000-0004-0000-0000-00000C020000}"/>
-    <hyperlink ref="C543" r:id="rId526" xr:uid="{00000000-0004-0000-0000-00000D020000}"/>
-    <hyperlink ref="C544" r:id="rId527" xr:uid="{00000000-0004-0000-0000-00000E020000}"/>
-    <hyperlink ref="C545" r:id="rId528" xr:uid="{00000000-0004-0000-0000-00000F020000}"/>
-    <hyperlink ref="C546" r:id="rId529" xr:uid="{00000000-0004-0000-0000-000010020000}"/>
-    <hyperlink ref="C547" r:id="rId530" xr:uid="{00000000-0004-0000-0000-000011020000}"/>
-    <hyperlink ref="C548" r:id="rId531" xr:uid="{00000000-0004-0000-0000-000012020000}"/>
-    <hyperlink ref="C549" r:id="rId532" xr:uid="{00000000-0004-0000-0000-000013020000}"/>
-    <hyperlink ref="C550" r:id="rId533" xr:uid="{00000000-0004-0000-0000-000014020000}"/>
-    <hyperlink ref="C551" r:id="rId534" xr:uid="{00000000-0004-0000-0000-000015020000}"/>
-    <hyperlink ref="C552" r:id="rId535" xr:uid="{00000000-0004-0000-0000-000016020000}"/>
-    <hyperlink ref="C553" r:id="rId536" xr:uid="{00000000-0004-0000-0000-000017020000}"/>
-    <hyperlink ref="C554" r:id="rId537" xr:uid="{00000000-0004-0000-0000-000018020000}"/>
-    <hyperlink ref="C555" r:id="rId538" xr:uid="{00000000-0004-0000-0000-000019020000}"/>
-    <hyperlink ref="C556" r:id="rId539" xr:uid="{00000000-0004-0000-0000-00001A020000}"/>
-    <hyperlink ref="C557" r:id="rId540" xr:uid="{00000000-0004-0000-0000-00001B020000}"/>
-    <hyperlink ref="C558" r:id="rId541" xr:uid="{00000000-0004-0000-0000-00001C020000}"/>
-    <hyperlink ref="C559" r:id="rId542" xr:uid="{00000000-0004-0000-0000-00001D020000}"/>
-    <hyperlink ref="C560" r:id="rId543" xr:uid="{00000000-0004-0000-0000-00001E020000}"/>
-    <hyperlink ref="C561" r:id="rId544" xr:uid="{00000000-0004-0000-0000-00001F020000}"/>
-    <hyperlink ref="C37" r:id="rId545" xr:uid="{00000000-0004-0000-0000-000020020000}"/>
-    <hyperlink ref="C562" r:id="rId546" xr:uid="{00000000-0004-0000-0000-000021020000}"/>
-    <hyperlink ref="C563" r:id="rId547" xr:uid="{00000000-0004-0000-0000-000022020000}"/>
-    <hyperlink ref="C564" r:id="rId548" xr:uid="{00000000-0004-0000-0000-000023020000}"/>
-    <hyperlink ref="C565" r:id="rId549" xr:uid="{00000000-0004-0000-0000-000024020000}"/>
-    <hyperlink ref="C566" r:id="rId550" xr:uid="{00000000-0004-0000-0000-000025020000}"/>
-    <hyperlink ref="C567" r:id="rId551" xr:uid="{00000000-0004-0000-0000-000026020000}"/>
-    <hyperlink ref="C568" r:id="rId552" xr:uid="{00000000-0004-0000-0000-000027020000}"/>
-    <hyperlink ref="C569" r:id="rId553" xr:uid="{00000000-0004-0000-0000-000028020000}"/>
-    <hyperlink ref="C570" r:id="rId554" xr:uid="{00000000-0004-0000-0000-000029020000}"/>
-    <hyperlink ref="C571" r:id="rId555" xr:uid="{00000000-0004-0000-0000-00002A020000}"/>
-    <hyperlink ref="C572" r:id="rId556" xr:uid="{00000000-0004-0000-0000-00002B020000}"/>
-    <hyperlink ref="C573" r:id="rId557" xr:uid="{00000000-0004-0000-0000-00002C020000}"/>
-    <hyperlink ref="C574" r:id="rId558" xr:uid="{00000000-0004-0000-0000-00002D020000}"/>
-    <hyperlink ref="C575" r:id="rId559" xr:uid="{00000000-0004-0000-0000-00002E020000}"/>
-    <hyperlink ref="C576" r:id="rId560" xr:uid="{00000000-0004-0000-0000-00002F020000}"/>
-    <hyperlink ref="C577" r:id="rId561" xr:uid="{00000000-0004-0000-0000-000030020000}"/>
-    <hyperlink ref="C578" r:id="rId562" xr:uid="{00000000-0004-0000-0000-000031020000}"/>
-    <hyperlink ref="C579" r:id="rId563" xr:uid="{00000000-0004-0000-0000-000032020000}"/>
-    <hyperlink ref="C580" r:id="rId564" xr:uid="{00000000-0004-0000-0000-000033020000}"/>
-    <hyperlink ref="C581" r:id="rId565" xr:uid="{00000000-0004-0000-0000-000034020000}"/>
-    <hyperlink ref="C582" r:id="rId566" xr:uid="{00000000-0004-0000-0000-000035020000}"/>
-    <hyperlink ref="C583" r:id="rId567" xr:uid="{00000000-0004-0000-0000-000036020000}"/>
-    <hyperlink ref="C584" r:id="rId568" xr:uid="{00000000-0004-0000-0000-000037020000}"/>
-    <hyperlink ref="C585" r:id="rId569" xr:uid="{00000000-0004-0000-0000-000038020000}"/>
-    <hyperlink ref="C586" r:id="rId570" xr:uid="{00000000-0004-0000-0000-000039020000}"/>
-    <hyperlink ref="C587" r:id="rId571" xr:uid="{00000000-0004-0000-0000-00003A020000}"/>
-    <hyperlink ref="C588" r:id="rId572" xr:uid="{00000000-0004-0000-0000-00003B020000}"/>
-    <hyperlink ref="C589" r:id="rId573" xr:uid="{00000000-0004-0000-0000-00003C020000}"/>
-    <hyperlink ref="C590" r:id="rId574" xr:uid="{00000000-0004-0000-0000-00003D020000}"/>
-    <hyperlink ref="C591" r:id="rId575" xr:uid="{00000000-0004-0000-0000-00003E020000}"/>
-    <hyperlink ref="C592" r:id="rId576" xr:uid="{00000000-0004-0000-0000-00003F020000}"/>
-    <hyperlink ref="C593" r:id="rId577" xr:uid="{00000000-0004-0000-0000-000040020000}"/>
-    <hyperlink ref="C594" r:id="rId578" xr:uid="{00000000-0004-0000-0000-000041020000}"/>
-    <hyperlink ref="C595" r:id="rId579" xr:uid="{00000000-0004-0000-0000-000042020000}"/>
-    <hyperlink ref="C596" r:id="rId580" xr:uid="{00000000-0004-0000-0000-000043020000}"/>
-    <hyperlink ref="C597" r:id="rId581" xr:uid="{00000000-0004-0000-0000-000044020000}"/>
-    <hyperlink ref="C598" r:id="rId582" xr:uid="{00000000-0004-0000-0000-000045020000}"/>
-    <hyperlink ref="C599" r:id="rId583" xr:uid="{00000000-0004-0000-0000-000046020000}"/>
-    <hyperlink ref="C600" r:id="rId584" xr:uid="{00000000-0004-0000-0000-000047020000}"/>
-    <hyperlink ref="C601" r:id="rId585" xr:uid="{00000000-0004-0000-0000-000048020000}"/>
-    <hyperlink ref="C602" r:id="rId586" xr:uid="{00000000-0004-0000-0000-000049020000}"/>
-    <hyperlink ref="C603" r:id="rId587" xr:uid="{00000000-0004-0000-0000-00004A020000}"/>
-    <hyperlink ref="C604" r:id="rId588" xr:uid="{00000000-0004-0000-0000-00004B020000}"/>
-    <hyperlink ref="C605" r:id="rId589" xr:uid="{00000000-0004-0000-0000-00004C020000}"/>
-    <hyperlink ref="C606" r:id="rId590" xr:uid="{00000000-0004-0000-0000-00004D020000}"/>
-    <hyperlink ref="C607" r:id="rId591" xr:uid="{00000000-0004-0000-0000-00004E020000}"/>
-    <hyperlink ref="C608" r:id="rId592" xr:uid="{00000000-0004-0000-0000-00004F020000}"/>
-    <hyperlink ref="C609" r:id="rId593" xr:uid="{00000000-0004-0000-0000-000050020000}"/>
-    <hyperlink ref="C610" r:id="rId594" xr:uid="{00000000-0004-0000-0000-000051020000}"/>
-    <hyperlink ref="C611" r:id="rId595" xr:uid="{00000000-0004-0000-0000-000052020000}"/>
-    <hyperlink ref="C612" r:id="rId596" xr:uid="{00000000-0004-0000-0000-000053020000}"/>
-    <hyperlink ref="C613" r:id="rId597" xr:uid="{00000000-0004-0000-0000-000054020000}"/>
-    <hyperlink ref="C614" r:id="rId598" xr:uid="{00000000-0004-0000-0000-000055020000}"/>
-    <hyperlink ref="C615" r:id="rId599" xr:uid="{00000000-0004-0000-0000-000056020000}"/>
-    <hyperlink ref="C616" r:id="rId600" xr:uid="{00000000-0004-0000-0000-000057020000}"/>
-    <hyperlink ref="C617" r:id="rId601" xr:uid="{00000000-0004-0000-0000-000058020000}"/>
-    <hyperlink ref="C618" r:id="rId602" xr:uid="{00000000-0004-0000-0000-000059020000}"/>
-    <hyperlink ref="C619" r:id="rId603" xr:uid="{00000000-0004-0000-0000-00005A020000}"/>
-    <hyperlink ref="C620" r:id="rId604" xr:uid="{00000000-0004-0000-0000-00005B020000}"/>
-    <hyperlink ref="C621" r:id="rId605" xr:uid="{00000000-0004-0000-0000-00005C020000}"/>
-    <hyperlink ref="C622" r:id="rId606" xr:uid="{00000000-0004-0000-0000-00005D020000}"/>
-    <hyperlink ref="C623" r:id="rId607" xr:uid="{00000000-0004-0000-0000-00005E020000}"/>
-    <hyperlink ref="C624" r:id="rId608" xr:uid="{00000000-0004-0000-0000-00005F020000}"/>
-    <hyperlink ref="C625" r:id="rId609" xr:uid="{00000000-0004-0000-0000-000060020000}"/>
-    <hyperlink ref="C626" r:id="rId610" xr:uid="{00000000-0004-0000-0000-000061020000}"/>
-    <hyperlink ref="C627" r:id="rId611" xr:uid="{00000000-0004-0000-0000-000062020000}"/>
-    <hyperlink ref="C628" r:id="rId612" xr:uid="{00000000-0004-0000-0000-000063020000}"/>
-    <hyperlink ref="C629" r:id="rId613" xr:uid="{00000000-0004-0000-0000-000064020000}"/>
-    <hyperlink ref="C630" r:id="rId614" xr:uid="{00000000-0004-0000-0000-000065020000}"/>
-    <hyperlink ref="C631" r:id="rId615" xr:uid="{00000000-0004-0000-0000-000066020000}"/>
-    <hyperlink ref="C632" r:id="rId616" xr:uid="{00000000-0004-0000-0000-000067020000}"/>
-    <hyperlink ref="C38" r:id="rId617" xr:uid="{00000000-0004-0000-0000-000068020000}"/>
-    <hyperlink ref="C633" r:id="rId618" xr:uid="{00000000-0004-0000-0000-000069020000}"/>
-    <hyperlink ref="C634" r:id="rId619" xr:uid="{00000000-0004-0000-0000-00006A020000}"/>
-    <hyperlink ref="C635" r:id="rId620" xr:uid="{00000000-0004-0000-0000-00006B020000}"/>
-    <hyperlink ref="C636" r:id="rId621" xr:uid="{00000000-0004-0000-0000-00006C020000}"/>
-    <hyperlink ref="C637" r:id="rId622" xr:uid="{00000000-0004-0000-0000-00006D020000}"/>
-    <hyperlink ref="C638" r:id="rId623" xr:uid="{00000000-0004-0000-0000-00006E020000}"/>
-    <hyperlink ref="C639" r:id="rId624" xr:uid="{00000000-0004-0000-0000-00006F020000}"/>
-    <hyperlink ref="C640" r:id="rId625" xr:uid="{00000000-0004-0000-0000-000070020000}"/>
-    <hyperlink ref="C641" r:id="rId626" xr:uid="{00000000-0004-0000-0000-000071020000}"/>
-    <hyperlink ref="C642" r:id="rId627" xr:uid="{00000000-0004-0000-0000-000072020000}"/>
-    <hyperlink ref="C643" r:id="rId628" xr:uid="{00000000-0004-0000-0000-000073020000}"/>
-    <hyperlink ref="C644" r:id="rId629" xr:uid="{00000000-0004-0000-0000-000074020000}"/>
-    <hyperlink ref="C645" r:id="rId630" xr:uid="{00000000-0004-0000-0000-000075020000}"/>
-    <hyperlink ref="C39" r:id="rId631" xr:uid="{00000000-0004-0000-0000-000076020000}"/>
-    <hyperlink ref="C646" r:id="rId632" xr:uid="{00000000-0004-0000-0000-000077020000}"/>
-    <hyperlink ref="C647" r:id="rId633" xr:uid="{00000000-0004-0000-0000-000078020000}"/>
-    <hyperlink ref="C648" r:id="rId634" xr:uid="{00000000-0004-0000-0000-000079020000}"/>
-    <hyperlink ref="C649" r:id="rId635" xr:uid="{00000000-0004-0000-0000-00007A020000}"/>
-    <hyperlink ref="C650" r:id="rId636" xr:uid="{00000000-0004-0000-0000-00007B020000}"/>
-    <hyperlink ref="C651" r:id="rId637" xr:uid="{00000000-0004-0000-0000-00007C020000}"/>
-    <hyperlink ref="C652" r:id="rId638" xr:uid="{00000000-0004-0000-0000-00007D020000}"/>
-    <hyperlink ref="C653" r:id="rId639" xr:uid="{00000000-0004-0000-0000-00007E020000}"/>
-    <hyperlink ref="C654" r:id="rId640" xr:uid="{00000000-0004-0000-0000-00007F020000}"/>
-    <hyperlink ref="C655" r:id="rId641" xr:uid="{00000000-0004-0000-0000-000080020000}"/>
-    <hyperlink ref="C656" r:id="rId642" xr:uid="{00000000-0004-0000-0000-000081020000}"/>
-    <hyperlink ref="C657" r:id="rId643" xr:uid="{00000000-0004-0000-0000-000082020000}"/>
-    <hyperlink ref="C658" r:id="rId644" xr:uid="{00000000-0004-0000-0000-000083020000}"/>
-    <hyperlink ref="C40" r:id="rId645" xr:uid="{00000000-0004-0000-0000-000084020000}"/>
-    <hyperlink ref="C659" r:id="rId646" xr:uid="{00000000-0004-0000-0000-000085020000}"/>
-    <hyperlink ref="C660" r:id="rId647" xr:uid="{00000000-0004-0000-0000-000086020000}"/>
-    <hyperlink ref="C661" r:id="rId648" xr:uid="{00000000-0004-0000-0000-000087020000}"/>
-    <hyperlink ref="C662" r:id="rId649" xr:uid="{00000000-0004-0000-0000-000088020000}"/>
-    <hyperlink ref="C41" r:id="rId650" xr:uid="{00000000-0004-0000-0000-000089020000}"/>
-    <hyperlink ref="C663" r:id="rId651" xr:uid="{00000000-0004-0000-0000-00008A020000}"/>
-    <hyperlink ref="C664" r:id="rId652" xr:uid="{00000000-0004-0000-0000-00008B020000}"/>
-    <hyperlink ref="C42" r:id="rId653" xr:uid="{00000000-0004-0000-0000-00008C020000}"/>
-    <hyperlink ref="C665" r:id="rId654" xr:uid="{00000000-0004-0000-0000-00008D020000}"/>
-    <hyperlink ref="C666" r:id="rId655" xr:uid="{00000000-0004-0000-0000-00008E020000}"/>
-    <hyperlink ref="C667" r:id="rId656" xr:uid="{00000000-0004-0000-0000-00008F020000}"/>
-    <hyperlink ref="C668" r:id="rId657" xr:uid="{00000000-0004-0000-0000-000090020000}"/>
-    <hyperlink ref="C669" r:id="rId658" xr:uid="{00000000-0004-0000-0000-000091020000}"/>
-    <hyperlink ref="C670" r:id="rId659" xr:uid="{00000000-0004-0000-0000-000092020000}"/>
-    <hyperlink ref="C43" r:id="rId660" xr:uid="{00000000-0004-0000-0000-000093020000}"/>
-    <hyperlink ref="C671" r:id="rId661" xr:uid="{00000000-0004-0000-0000-000094020000}"/>
-    <hyperlink ref="C44" r:id="rId662" xr:uid="{00000000-0004-0000-0000-000095020000}"/>
-    <hyperlink ref="C672" r:id="rId663" xr:uid="{00000000-0004-0000-0000-000096020000}"/>
-    <hyperlink ref="C673" r:id="rId664" xr:uid="{00000000-0004-0000-0000-000097020000}"/>
-    <hyperlink ref="C674" r:id="rId665" xr:uid="{00000000-0004-0000-0000-000098020000}"/>
-    <hyperlink ref="C675" r:id="rId666" xr:uid="{00000000-0004-0000-0000-000099020000}"/>
-    <hyperlink ref="C676" r:id="rId667" xr:uid="{00000000-0004-0000-0000-00009A020000}"/>
-    <hyperlink ref="C677" r:id="rId668" xr:uid="{00000000-0004-0000-0000-00009B020000}"/>
-    <hyperlink ref="C678" r:id="rId669" xr:uid="{00000000-0004-0000-0000-00009C020000}"/>
-    <hyperlink ref="C679" r:id="rId670" xr:uid="{00000000-0004-0000-0000-00009D020000}"/>
-    <hyperlink ref="C680" r:id="rId671" xr:uid="{00000000-0004-0000-0000-00009E020000}"/>
-    <hyperlink ref="C681" r:id="rId672" xr:uid="{00000000-0004-0000-0000-00009F020000}"/>
-    <hyperlink ref="C682" r:id="rId673" xr:uid="{00000000-0004-0000-0000-0000A0020000}"/>
-    <hyperlink ref="C683" r:id="rId674" xr:uid="{00000000-0004-0000-0000-0000A1020000}"/>
-    <hyperlink ref="C684" r:id="rId675" xr:uid="{00000000-0004-0000-0000-0000A2020000}"/>
-    <hyperlink ref="C685" r:id="rId676" xr:uid="{00000000-0004-0000-0000-0000A3020000}"/>
-    <hyperlink ref="C686" r:id="rId677" xr:uid="{00000000-0004-0000-0000-0000A4020000}"/>
-    <hyperlink ref="C687" r:id="rId678" xr:uid="{00000000-0004-0000-0000-0000A5020000}"/>
-    <hyperlink ref="C688" r:id="rId679" xr:uid="{00000000-0004-0000-0000-0000A6020000}"/>
-    <hyperlink ref="C689" r:id="rId680" xr:uid="{00000000-0004-0000-0000-0000A7020000}"/>
-    <hyperlink ref="C690" r:id="rId681" xr:uid="{00000000-0004-0000-0000-0000A8020000}"/>
-    <hyperlink ref="C691" r:id="rId682" xr:uid="{00000000-0004-0000-0000-0000A9020000}"/>
-    <hyperlink ref="C692" r:id="rId683" xr:uid="{00000000-0004-0000-0000-0000AA020000}"/>
-    <hyperlink ref="C693" r:id="rId684" xr:uid="{00000000-0004-0000-0000-0000AB020000}"/>
-    <hyperlink ref="C694" r:id="rId685" xr:uid="{00000000-0004-0000-0000-0000AC020000}"/>
-    <hyperlink ref="C695" r:id="rId686" xr:uid="{00000000-0004-0000-0000-0000AD020000}"/>
-    <hyperlink ref="C696" r:id="rId687" xr:uid="{00000000-0004-0000-0000-0000AE020000}"/>
-    <hyperlink ref="C697" r:id="rId688" xr:uid="{00000000-0004-0000-0000-0000AF020000}"/>
-    <hyperlink ref="C698" r:id="rId689" xr:uid="{00000000-0004-0000-0000-0000B0020000}"/>
-    <hyperlink ref="C699" r:id="rId690" xr:uid="{00000000-0004-0000-0000-0000B1020000}"/>
-    <hyperlink ref="C700" r:id="rId691" xr:uid="{00000000-0004-0000-0000-0000B2020000}"/>
-    <hyperlink ref="C701" r:id="rId692" xr:uid="{00000000-0004-0000-0000-0000B3020000}"/>
-    <hyperlink ref="C702" r:id="rId693" xr:uid="{00000000-0004-0000-0000-0000B4020000}"/>
-    <hyperlink ref="C703" r:id="rId694" xr:uid="{00000000-0004-0000-0000-0000B5020000}"/>
-    <hyperlink ref="C704" r:id="rId695" xr:uid="{00000000-0004-0000-0000-0000B6020000}"/>
-    <hyperlink ref="C705" r:id="rId696" xr:uid="{00000000-0004-0000-0000-0000B7020000}"/>
-    <hyperlink ref="C706" r:id="rId697" xr:uid="{00000000-0004-0000-0000-0000B8020000}"/>
-    <hyperlink ref="C707" r:id="rId698" xr:uid="{00000000-0004-0000-0000-0000B9020000}"/>
-    <hyperlink ref="C708" r:id="rId699" xr:uid="{00000000-0004-0000-0000-0000BA020000}"/>
-    <hyperlink ref="C709" r:id="rId700" xr:uid="{00000000-0004-0000-0000-0000BB020000}"/>
-    <hyperlink ref="C45" r:id="rId701" xr:uid="{00000000-0004-0000-0000-0000BC020000}"/>
-    <hyperlink ref="C710" r:id="rId702" xr:uid="{00000000-0004-0000-0000-0000BD020000}"/>
-    <hyperlink ref="C711" r:id="rId703" xr:uid="{00000000-0004-0000-0000-0000BE020000}"/>
-    <hyperlink ref="C712" r:id="rId704" xr:uid="{00000000-0004-0000-0000-0000BF020000}"/>
-    <hyperlink ref="C713" r:id="rId705" xr:uid="{00000000-0004-0000-0000-0000C0020000}"/>
-    <hyperlink ref="C714" r:id="rId706" xr:uid="{00000000-0004-0000-0000-0000C1020000}"/>
-    <hyperlink ref="C715" r:id="rId707" xr:uid="{00000000-0004-0000-0000-0000C2020000}"/>
-    <hyperlink ref="C716" r:id="rId708" xr:uid="{00000000-0004-0000-0000-0000C3020000}"/>
-    <hyperlink ref="C717" r:id="rId709" xr:uid="{00000000-0004-0000-0000-0000C4020000}"/>
-    <hyperlink ref="C718" r:id="rId710" xr:uid="{00000000-0004-0000-0000-0000C5020000}"/>
-    <hyperlink ref="C719" r:id="rId711" xr:uid="{00000000-0004-0000-0000-0000C6020000}"/>
-    <hyperlink ref="C720" r:id="rId712" xr:uid="{00000000-0004-0000-0000-0000C7020000}"/>
-    <hyperlink ref="C721" r:id="rId713" xr:uid="{00000000-0004-0000-0000-0000C8020000}"/>
-    <hyperlink ref="C722" r:id="rId714" xr:uid="{00000000-0004-0000-0000-0000C9020000}"/>
-    <hyperlink ref="C723" r:id="rId715" xr:uid="{00000000-0004-0000-0000-0000CA020000}"/>
-    <hyperlink ref="C724" r:id="rId716" xr:uid="{00000000-0004-0000-0000-0000CB020000}"/>
-    <hyperlink ref="C725" r:id="rId717" xr:uid="{00000000-0004-0000-0000-0000CC020000}"/>
-    <hyperlink ref="C726" r:id="rId718" xr:uid="{00000000-0004-0000-0000-0000CD020000}"/>
-    <hyperlink ref="C727" r:id="rId719" xr:uid="{00000000-0004-0000-0000-0000CE020000}"/>
-    <hyperlink ref="C728" r:id="rId720" xr:uid="{00000000-0004-0000-0000-0000CF020000}"/>
-    <hyperlink ref="C729" r:id="rId721" xr:uid="{00000000-0004-0000-0000-0000D0020000}"/>
-    <hyperlink ref="C730" r:id="rId722" xr:uid="{00000000-0004-0000-0000-0000D1020000}"/>
-    <hyperlink ref="C731" r:id="rId723" xr:uid="{00000000-0004-0000-0000-0000D2020000}"/>
-    <hyperlink ref="C46" r:id="rId724" xr:uid="{00000000-0004-0000-0000-0000D3020000}"/>
-    <hyperlink ref="C47" r:id="rId725" xr:uid="{00000000-0004-0000-0000-0000D4020000}"/>
-    <hyperlink ref="C732" r:id="rId726" xr:uid="{00000000-0004-0000-0000-0000D5020000}"/>
-    <hyperlink ref="C733" r:id="rId727" xr:uid="{00000000-0004-0000-0000-0000D6020000}"/>
-    <hyperlink ref="C734" r:id="rId728" xr:uid="{00000000-0004-0000-0000-0000D7020000}"/>
-    <hyperlink ref="C735" r:id="rId729" xr:uid="{00000000-0004-0000-0000-0000D8020000}"/>
-    <hyperlink ref="C736" r:id="rId730" xr:uid="{00000000-0004-0000-0000-0000D9020000}"/>
-    <hyperlink ref="C48" r:id="rId731" xr:uid="{00000000-0004-0000-0000-0000DA020000}"/>
-    <hyperlink ref="C49" r:id="rId732" xr:uid="{00000000-0004-0000-0000-0000DB020000}"/>
-    <hyperlink ref="C737" r:id="rId733" xr:uid="{00000000-0004-0000-0000-0000DC020000}"/>
-    <hyperlink ref="C738" r:id="rId734" xr:uid="{00000000-0004-0000-0000-0000DD020000}"/>
-    <hyperlink ref="C739" r:id="rId735" xr:uid="{00000000-0004-0000-0000-0000DE020000}"/>
-    <hyperlink ref="C740" r:id="rId736" xr:uid="{00000000-0004-0000-0000-0000DF020000}"/>
-    <hyperlink ref="C741" r:id="rId737" xr:uid="{00000000-0004-0000-0000-0000E0020000}"/>
-    <hyperlink ref="C742" r:id="rId738" xr:uid="{00000000-0004-0000-0000-0000E1020000}"/>
-    <hyperlink ref="C743" r:id="rId739" xr:uid="{00000000-0004-0000-0000-0000E2020000}"/>
-    <hyperlink ref="C744" r:id="rId740" xr:uid="{00000000-0004-0000-0000-0000E3020000}"/>
-    <hyperlink ref="C50" r:id="rId741" xr:uid="{00000000-0004-0000-0000-0000E4020000}"/>
-    <hyperlink ref="C745" r:id="rId742" xr:uid="{00000000-0004-0000-0000-0000E5020000}"/>
-    <hyperlink ref="C746" r:id="rId743" xr:uid="{00000000-0004-0000-0000-0000E6020000}"/>
-    <hyperlink ref="C747" r:id="rId744" xr:uid="{00000000-0004-0000-0000-0000E7020000}"/>
-    <hyperlink ref="C748" r:id="rId745" xr:uid="{00000000-0004-0000-0000-0000E8020000}"/>
-    <hyperlink ref="C749" r:id="rId746" xr:uid="{00000000-0004-0000-0000-0000E9020000}"/>
-    <hyperlink ref="C750" r:id="rId747" xr:uid="{00000000-0004-0000-0000-0000EA020000}"/>
-    <hyperlink ref="C751" r:id="rId748" xr:uid="{00000000-0004-0000-0000-0000EB020000}"/>
-    <hyperlink ref="C752" r:id="rId749" xr:uid="{00000000-0004-0000-0000-0000EC020000}"/>
-    <hyperlink ref="C753" r:id="rId750" xr:uid="{00000000-0004-0000-0000-0000ED020000}"/>
-    <hyperlink ref="C51" r:id="rId751" xr:uid="{00000000-0004-0000-0000-0000EE020000}"/>
-    <hyperlink ref="C754" r:id="rId752" xr:uid="{00000000-0004-0000-0000-0000EF020000}"/>
-    <hyperlink ref="C755" r:id="rId753" xr:uid="{00000000-0004-0000-0000-0000F0020000}"/>
-    <hyperlink ref="C756" r:id="rId754" xr:uid="{00000000-0004-0000-0000-0000F1020000}"/>
-    <hyperlink ref="C757" r:id="rId755" xr:uid="{00000000-0004-0000-0000-0000F2020000}"/>
-    <hyperlink ref="C758" r:id="rId756" xr:uid="{00000000-0004-0000-0000-0000F3020000}"/>
-    <hyperlink ref="C759" r:id="rId757" xr:uid="{00000000-0004-0000-0000-0000F4020000}"/>
-    <hyperlink ref="C760" r:id="rId758" xr:uid="{00000000-0004-0000-0000-0000F5020000}"/>
-    <hyperlink ref="C761" r:id="rId759" xr:uid="{00000000-0004-0000-0000-0000F6020000}"/>
-    <hyperlink ref="C762" r:id="rId760" xr:uid="{00000000-0004-0000-0000-0000F7020000}"/>
-    <hyperlink ref="C763" r:id="rId761" xr:uid="{00000000-0004-0000-0000-0000F8020000}"/>
-    <hyperlink ref="C764" r:id="rId762" xr:uid="{00000000-0004-0000-0000-0000F9020000}"/>
-    <hyperlink ref="C52" r:id="rId763" xr:uid="{00000000-0004-0000-0000-0000FA020000}"/>
-    <hyperlink ref="C765" r:id="rId764" xr:uid="{00000000-0004-0000-0000-0000FB020000}"/>
-    <hyperlink ref="C766" r:id="rId765" xr:uid="{00000000-0004-0000-0000-0000FC020000}"/>
-    <hyperlink ref="C767" r:id="rId766" xr:uid="{00000000-0004-0000-0000-0000FD020000}"/>
-    <hyperlink ref="C768" r:id="rId767" xr:uid="{00000000-0004-0000-0000-0000FE020000}"/>
-    <hyperlink ref="C769" r:id="rId768" xr:uid="{00000000-0004-0000-0000-0000FF020000}"/>
-    <hyperlink ref="C770" r:id="rId769" xr:uid="{00000000-0004-0000-0000-000000030000}"/>
-    <hyperlink ref="C771" r:id="rId770" xr:uid="{00000000-0004-0000-0000-000001030000}"/>
-    <hyperlink ref="C772" r:id="rId771" xr:uid="{00000000-0004-0000-0000-000002030000}"/>
-    <hyperlink ref="C773" r:id="rId772" xr:uid="{00000000-0004-0000-0000-000003030000}"/>
-    <hyperlink ref="C774" r:id="rId773" xr:uid="{00000000-0004-0000-0000-000004030000}"/>
-    <hyperlink ref="C775" r:id="rId774" xr:uid="{00000000-0004-0000-0000-000005030000}"/>
-    <hyperlink ref="C776" r:id="rId775" xr:uid="{00000000-0004-0000-0000-000006030000}"/>
-    <hyperlink ref="C777" r:id="rId776" xr:uid="{00000000-0004-0000-0000-000007030000}"/>
-    <hyperlink ref="C778" r:id="rId777" xr:uid="{00000000-0004-0000-0000-000008030000}"/>
-    <hyperlink ref="C779" r:id="rId778" xr:uid="{00000000-0004-0000-0000-000009030000}"/>
-    <hyperlink ref="C780" r:id="rId779" xr:uid="{00000000-0004-0000-0000-00000A030000}"/>
-    <hyperlink ref="C781" r:id="rId780" xr:uid="{00000000-0004-0000-0000-00000B030000}"/>
-    <hyperlink ref="C782" r:id="rId781" xr:uid="{00000000-0004-0000-0000-00000C030000}"/>
-    <hyperlink ref="C783" r:id="rId782" xr:uid="{00000000-0004-0000-0000-00000D030000}"/>
-    <hyperlink ref="C53" r:id="rId783" xr:uid="{00000000-0004-0000-0000-00000E030000}"/>
-    <hyperlink ref="C784" r:id="rId784" xr:uid="{00000000-0004-0000-0000-00000F030000}"/>
-    <hyperlink ref="C785" r:id="rId785" xr:uid="{00000000-0004-0000-0000-000010030000}"/>
-    <hyperlink ref="C786" r:id="rId786" xr:uid="{00000000-0004-0000-0000-000011030000}"/>
-    <hyperlink ref="C787" r:id="rId787" xr:uid="{00000000-0004-0000-0000-000012030000}"/>
-    <hyperlink ref="C788" r:id="rId788" xr:uid="{00000000-0004-0000-0000-000013030000}"/>
-    <hyperlink ref="C54" r:id="rId789" xr:uid="{00000000-0004-0000-0000-000014030000}"/>
-    <hyperlink ref="C789" r:id="rId790" xr:uid="{00000000-0004-0000-0000-000015030000}"/>
-    <hyperlink ref="C790" r:id="rId791" xr:uid="{00000000-0004-0000-0000-000016030000}"/>
-    <hyperlink ref="C791" r:id="rId792" xr:uid="{00000000-0004-0000-0000-000017030000}"/>
-    <hyperlink ref="C792" r:id="rId793" xr:uid="{00000000-0004-0000-0000-000018030000}"/>
-    <hyperlink ref="C793" r:id="rId794" xr:uid="{00000000-0004-0000-0000-000019030000}"/>
-    <hyperlink ref="C794" r:id="rId795" xr:uid="{00000000-0004-0000-0000-00001A030000}"/>
-    <hyperlink ref="C795" r:id="rId796" xr:uid="{00000000-0004-0000-0000-00001B030000}"/>
-    <hyperlink ref="C796" r:id="rId797" xr:uid="{00000000-0004-0000-0000-00001C030000}"/>
-    <hyperlink ref="C797" r:id="rId798" xr:uid="{00000000-0004-0000-0000-00001D030000}"/>
-    <hyperlink ref="C798" r:id="rId799" xr:uid="{00000000-0004-0000-0000-00001E030000}"/>
-    <hyperlink ref="C799" r:id="rId800" xr:uid="{00000000-0004-0000-0000-00001F030000}"/>
-    <hyperlink ref="C800" r:id="rId801" xr:uid="{00000000-0004-0000-0000-000020030000}"/>
-    <hyperlink ref="C801" r:id="rId802" xr:uid="{00000000-0004-0000-0000-000021030000}"/>
-    <hyperlink ref="C802" r:id="rId803" xr:uid="{00000000-0004-0000-0000-000022030000}"/>
-    <hyperlink ref="C817" r:id="rId804" xr:uid="{00000000-0004-0000-0000-000023030000}"/>
-    <hyperlink ref="C55" r:id="rId805" xr:uid="{00000000-0004-0000-0000-000024030000}"/>
-    <hyperlink ref="C803" r:id="rId806" xr:uid="{00000000-0004-0000-0000-000025030000}"/>
-    <hyperlink ref="C804" r:id="rId807" xr:uid="{00000000-0004-0000-0000-000026030000}"/>
-    <hyperlink ref="C805" r:id="rId808" xr:uid="{00000000-0004-0000-0000-000027030000}"/>
-    <hyperlink ref="C806" r:id="rId809" xr:uid="{00000000-0004-0000-0000-000028030000}"/>
-    <hyperlink ref="C818" r:id="rId810" xr:uid="{00000000-0004-0000-0000-000029030000}"/>
-    <hyperlink ref="C807" r:id="rId811" xr:uid="{00000000-0004-0000-0000-00002A030000}"/>
-    <hyperlink ref="C808" r:id="rId812" xr:uid="{00000000-0004-0000-0000-00002B030000}"/>
-    <hyperlink ref="C809" r:id="rId813" xr:uid="{00000000-0004-0000-0000-00002C030000}"/>
-    <hyperlink ref="C810" r:id="rId814" xr:uid="{00000000-0004-0000-0000-00002D030000}"/>
-    <hyperlink ref="C811" r:id="rId815" xr:uid="{00000000-0004-0000-0000-00002E030000}"/>
-    <hyperlink ref="C812" r:id="rId816" xr:uid="{00000000-0004-0000-0000-00002F030000}"/>
-    <hyperlink ref="C813" r:id="rId817" xr:uid="{00000000-0004-0000-0000-000030030000}"/>
+    <hyperlink ref="C416" r:id="rId389" xr:uid="{00000000-0004-0000-0000-000084010000}"/>
+    <hyperlink ref="C417" r:id="rId390" xr:uid="{00000000-0004-0000-0000-000085010000}"/>
+    <hyperlink ref="C418" r:id="rId391" xr:uid="{00000000-0004-0000-0000-000086010000}"/>
+    <hyperlink ref="C419" r:id="rId392" xr:uid="{00000000-0004-0000-0000-000087010000}"/>
+    <hyperlink ref="C420" r:id="rId393" xr:uid="{00000000-0004-0000-0000-000088010000}"/>
+    <hyperlink ref="C421" r:id="rId394" xr:uid="{00000000-0004-0000-0000-000089010000}"/>
+    <hyperlink ref="C422" r:id="rId395" xr:uid="{00000000-0004-0000-0000-00008A010000}"/>
+    <hyperlink ref="C423" r:id="rId396" xr:uid="{00000000-0004-0000-0000-00008B010000}"/>
+    <hyperlink ref="C424" r:id="rId397" xr:uid="{00000000-0004-0000-0000-00008C010000}"/>
+    <hyperlink ref="C425" r:id="rId398" xr:uid="{00000000-0004-0000-0000-00008D010000}"/>
+    <hyperlink ref="C426" r:id="rId399" xr:uid="{00000000-0004-0000-0000-00008E010000}"/>
+    <hyperlink ref="C427" r:id="rId400" xr:uid="{00000000-0004-0000-0000-00008F010000}"/>
+    <hyperlink ref="C428" r:id="rId401" xr:uid="{00000000-0004-0000-0000-000090010000}"/>
+    <hyperlink ref="C429" r:id="rId402" xr:uid="{00000000-0004-0000-0000-000091010000}"/>
+    <hyperlink ref="C430" r:id="rId403" xr:uid="{00000000-0004-0000-0000-000092010000}"/>
+    <hyperlink ref="C431" r:id="rId404" xr:uid="{00000000-0004-0000-0000-000093010000}"/>
+    <hyperlink ref="C432" r:id="rId405" xr:uid="{00000000-0004-0000-0000-000094010000}"/>
+    <hyperlink ref="C433" r:id="rId406" xr:uid="{00000000-0004-0000-0000-000095010000}"/>
+    <hyperlink ref="C434" r:id="rId407" xr:uid="{00000000-0004-0000-0000-000096010000}"/>
+    <hyperlink ref="C435" r:id="rId408" xr:uid="{00000000-0004-0000-0000-000097010000}"/>
+    <hyperlink ref="C436" r:id="rId409" xr:uid="{00000000-0004-0000-0000-000098010000}"/>
+    <hyperlink ref="C437" r:id="rId410" xr:uid="{00000000-0004-0000-0000-000099010000}"/>
+    <hyperlink ref="C438" r:id="rId411" xr:uid="{00000000-0004-0000-0000-00009A010000}"/>
+    <hyperlink ref="C439" r:id="rId412" xr:uid="{00000000-0004-0000-0000-00009B010000}"/>
+    <hyperlink ref="C440" r:id="rId413" xr:uid="{00000000-0004-0000-0000-00009C010000}"/>
+    <hyperlink ref="C441" r:id="rId414" xr:uid="{00000000-0004-0000-0000-00009D010000}"/>
+    <hyperlink ref="C442" r:id="rId415" xr:uid="{00000000-0004-0000-0000-00009E010000}"/>
+    <hyperlink ref="C443" r:id="rId416" xr:uid="{00000000-0004-0000-0000-00009F010000}"/>
+    <hyperlink ref="C444" r:id="rId417" xr:uid="{00000000-0004-0000-0000-0000A0010000}"/>
+    <hyperlink ref="C29" r:id="rId418" xr:uid="{00000000-0004-0000-0000-0000A1010000}"/>
+    <hyperlink ref="C445" r:id="rId419" xr:uid="{00000000-0004-0000-0000-0000A2010000}"/>
+    <hyperlink ref="C446" r:id="rId420" xr:uid="{00000000-0004-0000-0000-0000A3010000}"/>
+    <hyperlink ref="C447" r:id="rId421" xr:uid="{00000000-0004-0000-0000-0000A4010000}"/>
+    <hyperlink ref="C448" r:id="rId422" xr:uid="{00000000-0004-0000-0000-0000A5010000}"/>
+    <hyperlink ref="C449" r:id="rId423" xr:uid="{00000000-0004-0000-0000-0000A6010000}"/>
+    <hyperlink ref="C450" r:id="rId424" xr:uid="{00000000-0004-0000-0000-0000A7010000}"/>
+    <hyperlink ref="C30" r:id="rId425" xr:uid="{00000000-0004-0000-0000-0000A8010000}"/>
+    <hyperlink ref="C451" r:id="rId426" xr:uid="{00000000-0004-0000-0000-0000A9010000}"/>
+    <hyperlink ref="C452" r:id="rId427" xr:uid="{00000000-0004-0000-0000-0000AA010000}"/>
+    <hyperlink ref="C453" r:id="rId428" xr:uid="{00000000-0004-0000-0000-0000AB010000}"/>
+    <hyperlink ref="C454" r:id="rId429" xr:uid="{00000000-0004-0000-0000-0000AC010000}"/>
+    <hyperlink ref="C455" r:id="rId430" xr:uid="{00000000-0004-0000-0000-0000AD010000}"/>
+    <hyperlink ref="C456" r:id="rId431" xr:uid="{00000000-0004-0000-0000-0000AE010000}"/>
+    <hyperlink ref="C457" r:id="rId432" xr:uid="{00000000-0004-0000-0000-0000AF010000}"/>
+    <hyperlink ref="C458" r:id="rId433" xr:uid="{00000000-0004-0000-0000-0000B0010000}"/>
+    <hyperlink ref="C459" r:id="rId434" xr:uid="{00000000-0004-0000-0000-0000B1010000}"/>
+    <hyperlink ref="C460" r:id="rId435" xr:uid="{00000000-0004-0000-0000-0000B2010000}"/>
+    <hyperlink ref="C461" r:id="rId436" xr:uid="{00000000-0004-0000-0000-0000B3010000}"/>
+    <hyperlink ref="C462" r:id="rId437" xr:uid="{00000000-0004-0000-0000-0000B4010000}"/>
+    <hyperlink ref="C463" r:id="rId438" xr:uid="{00000000-0004-0000-0000-0000B5010000}"/>
+    <hyperlink ref="C464" r:id="rId439" xr:uid="{00000000-0004-0000-0000-0000B6010000}"/>
+    <hyperlink ref="C465" r:id="rId440" xr:uid="{00000000-0004-0000-0000-0000B7010000}"/>
+    <hyperlink ref="C466" r:id="rId441" xr:uid="{00000000-0004-0000-0000-0000B8010000}"/>
+    <hyperlink ref="C467" r:id="rId442" xr:uid="{00000000-0004-0000-0000-0000B9010000}"/>
+    <hyperlink ref="C468" r:id="rId443" xr:uid="{00000000-0004-0000-0000-0000BA010000}"/>
+    <hyperlink ref="C469" r:id="rId444" xr:uid="{00000000-0004-0000-0000-0000BB010000}"/>
+    <hyperlink ref="C31" r:id="rId445" xr:uid="{00000000-0004-0000-0000-0000BC010000}"/>
+    <hyperlink ref="C470" r:id="rId446" xr:uid="{00000000-0004-0000-0000-0000BD010000}"/>
+    <hyperlink ref="C471" r:id="rId447" xr:uid="{00000000-0004-0000-0000-0000BE010000}"/>
+    <hyperlink ref="C472" r:id="rId448" xr:uid="{00000000-0004-0000-0000-0000BF010000}"/>
+    <hyperlink ref="C473" r:id="rId449" xr:uid="{00000000-0004-0000-0000-0000C0010000}"/>
+    <hyperlink ref="C474" r:id="rId450" xr:uid="{00000000-0004-0000-0000-0000C1010000}"/>
+    <hyperlink ref="C475" r:id="rId451" xr:uid="{00000000-0004-0000-0000-0000C2010000}"/>
+    <hyperlink ref="C32" r:id="rId452" xr:uid="{00000000-0004-0000-0000-0000C3010000}"/>
+    <hyperlink ref="C476" r:id="rId453" xr:uid="{00000000-0004-0000-0000-0000C4010000}"/>
+    <hyperlink ref="C477" r:id="rId454" xr:uid="{00000000-0004-0000-0000-0000C5010000}"/>
+    <hyperlink ref="C478" r:id="rId455" xr:uid="{00000000-0004-0000-0000-0000C6010000}"/>
+    <hyperlink ref="C479" r:id="rId456" xr:uid="{00000000-0004-0000-0000-0000C7010000}"/>
+    <hyperlink ref="C480" r:id="rId457" xr:uid="{00000000-0004-0000-0000-0000C8010000}"/>
+    <hyperlink ref="C481" r:id="rId458" xr:uid="{00000000-0004-0000-0000-0000C9010000}"/>
+    <hyperlink ref="C482" r:id="rId459" xr:uid="{00000000-0004-0000-0000-0000CA010000}"/>
+    <hyperlink ref="C483" r:id="rId460" xr:uid="{00000000-0004-0000-0000-0000CB010000}"/>
+    <hyperlink ref="C484" r:id="rId461" xr:uid="{00000000-0004-0000-0000-0000CC010000}"/>
+    <hyperlink ref="C485" r:id="rId462" xr:uid="{00000000-0004-0000-0000-0000CD010000}"/>
+    <hyperlink ref="C486" r:id="rId463" xr:uid="{00000000-0004-0000-0000-0000CE010000}"/>
+    <hyperlink ref="C33" r:id="rId464" xr:uid="{00000000-0004-0000-0000-0000CF010000}"/>
+    <hyperlink ref="C487" r:id="rId465" xr:uid="{00000000-0004-0000-0000-0000D0010000}"/>
+    <hyperlink ref="C488" r:id="rId466" xr:uid="{00000000-0004-0000-0000-0000D1010000}"/>
+    <hyperlink ref="C489" r:id="rId467" xr:uid="{00000000-0004-0000-0000-0000D2010000}"/>
+    <hyperlink ref="C490" r:id="rId468" xr:uid="{00000000-0004-0000-0000-0000D3010000}"/>
+    <hyperlink ref="C491" r:id="rId469" xr:uid="{00000000-0004-0000-0000-0000D4010000}"/>
+    <hyperlink ref="C492" r:id="rId470" xr:uid="{00000000-0004-0000-0000-0000D5010000}"/>
+    <hyperlink ref="C493" r:id="rId471" xr:uid="{00000000-0004-0000-0000-0000D6010000}"/>
+    <hyperlink ref="C34" r:id="rId472" xr:uid="{00000000-0004-0000-0000-0000D7010000}"/>
+    <hyperlink ref="C494" r:id="rId473" xr:uid="{00000000-0004-0000-0000-0000D8010000}"/>
+    <hyperlink ref="C495" r:id="rId474" xr:uid="{00000000-0004-0000-0000-0000D9010000}"/>
+    <hyperlink ref="C496" r:id="rId475" xr:uid="{00000000-0004-0000-0000-0000DA010000}"/>
+    <hyperlink ref="C497" r:id="rId476" xr:uid="{00000000-0004-0000-0000-0000DB010000}"/>
+    <hyperlink ref="C498" r:id="rId477" xr:uid="{00000000-0004-0000-0000-0000DC010000}"/>
+    <hyperlink ref="C499" r:id="rId478" xr:uid="{00000000-0004-0000-0000-0000DD010000}"/>
+    <hyperlink ref="C500" r:id="rId479" xr:uid="{00000000-0004-0000-0000-0000DE010000}"/>
+    <hyperlink ref="C501" r:id="rId480" xr:uid="{00000000-0004-0000-0000-0000DF010000}"/>
+    <hyperlink ref="C502" r:id="rId481" xr:uid="{00000000-0004-0000-0000-0000E0010000}"/>
+    <hyperlink ref="C503" r:id="rId482" xr:uid="{00000000-0004-0000-0000-0000E1010000}"/>
+    <hyperlink ref="C504" r:id="rId483" xr:uid="{00000000-0004-0000-0000-0000E2010000}"/>
+    <hyperlink ref="C505" r:id="rId484" xr:uid="{00000000-0004-0000-0000-0000E3010000}"/>
+    <hyperlink ref="C506" r:id="rId485" xr:uid="{00000000-0004-0000-0000-0000E4010000}"/>
+    <hyperlink ref="C507" r:id="rId486" xr:uid="{00000000-0004-0000-0000-0000E5010000}"/>
+    <hyperlink ref="C508" r:id="rId487" xr:uid="{00000000-0004-0000-0000-0000E6010000}"/>
+    <hyperlink ref="C509" r:id="rId488" xr:uid="{00000000-0004-0000-0000-0000E7010000}"/>
+    <hyperlink ref="C510" r:id="rId489" xr:uid="{00000000-0004-0000-0000-0000E8010000}"/>
+    <hyperlink ref="C511" r:id="rId490" xr:uid="{00000000-0004-0000-0000-0000E9010000}"/>
+    <hyperlink ref="C512" r:id="rId491" xr:uid="{00000000-0004-0000-0000-0000EA010000}"/>
+    <hyperlink ref="C513" r:id="rId492" xr:uid="{00000000-0004-0000-0000-0000EB010000}"/>
+    <hyperlink ref="C514" r:id="rId493" xr:uid="{00000000-0004-0000-0000-0000EC010000}"/>
+    <hyperlink ref="C515" r:id="rId494" xr:uid="{00000000-0004-0000-0000-0000ED010000}"/>
+    <hyperlink ref="C516" r:id="rId495" xr:uid="{00000000-0004-0000-0000-0000EE010000}"/>
+    <hyperlink ref="C517" r:id="rId496" xr:uid="{00000000-0004-0000-0000-0000EF010000}"/>
+    <hyperlink ref="C518" r:id="rId497" xr:uid="{00000000-0004-0000-0000-0000F0010000}"/>
+    <hyperlink ref="C519" r:id="rId498" xr:uid="{00000000-0004-0000-0000-0000F1010000}"/>
+    <hyperlink ref="C520" r:id="rId499" xr:uid="{00000000-0004-0000-0000-0000F2010000}"/>
+    <hyperlink ref="C521" r:id="rId500" xr:uid="{00000000-0004-0000-0000-0000F3010000}"/>
+    <hyperlink ref="C522" r:id="rId501" xr:uid="{00000000-0004-0000-0000-0000F4010000}"/>
+    <hyperlink ref="C523" r:id="rId502" xr:uid="{00000000-0004-0000-0000-0000F5010000}"/>
+    <hyperlink ref="C524" r:id="rId503" xr:uid="{00000000-0004-0000-0000-0000F6010000}"/>
+    <hyperlink ref="C525" r:id="rId504" xr:uid="{00000000-0004-0000-0000-0000F7010000}"/>
+    <hyperlink ref="C526" r:id="rId505" xr:uid="{00000000-0004-0000-0000-0000F8010000}"/>
+    <hyperlink ref="C527" r:id="rId506" xr:uid="{00000000-0004-0000-0000-0000F9010000}"/>
+    <hyperlink ref="C528" r:id="rId507" xr:uid="{00000000-0004-0000-0000-0000FA010000}"/>
+    <hyperlink ref="C529" r:id="rId508" xr:uid="{00000000-0004-0000-0000-0000FB010000}"/>
+    <hyperlink ref="C530" r:id="rId509" xr:uid="{00000000-0004-0000-0000-0000FC010000}"/>
+    <hyperlink ref="C531" r:id="rId510" xr:uid="{00000000-0004-0000-0000-0000FD010000}"/>
+    <hyperlink ref="C532" r:id="rId511" xr:uid="{00000000-0004-0000-0000-0000FE010000}"/>
+    <hyperlink ref="C533" r:id="rId512" xr:uid="{00000000-0004-0000-0000-0000FF010000}"/>
+    <hyperlink ref="C534" r:id="rId513" xr:uid="{00000000-0004-0000-0000-000000020000}"/>
+    <hyperlink ref="C535" r:id="rId514" xr:uid="{00000000-0004-0000-0000-000001020000}"/>
+    <hyperlink ref="C536" r:id="rId515" xr:uid="{00000000-0004-0000-0000-000002020000}"/>
+    <hyperlink ref="C537" r:id="rId516" xr:uid="{00000000-0004-0000-0000-000003020000}"/>
+    <hyperlink ref="C35" r:id="rId517" xr:uid="{00000000-0004-0000-0000-000004020000}"/>
+    <hyperlink ref="C538" r:id="rId518" xr:uid="{00000000-0004-0000-0000-000005020000}"/>
+    <hyperlink ref="C539" r:id="rId519" xr:uid="{00000000-0004-0000-0000-000006020000}"/>
+    <hyperlink ref="C540" r:id="rId520" xr:uid="{00000000-0004-0000-0000-000007020000}"/>
+    <hyperlink ref="C541" r:id="rId521" xr:uid="{00000000-0004-0000-0000-000008020000}"/>
+    <hyperlink ref="C542" r:id="rId522" xr:uid="{00000000-0004-0000-0000-000009020000}"/>
+    <hyperlink ref="C543" r:id="rId523" xr:uid="{00000000-0004-0000-0000-00000A020000}"/>
+    <hyperlink ref="C544" r:id="rId524" xr:uid="{00000000-0004-0000-0000-00000B020000}"/>
+    <hyperlink ref="C545" r:id="rId525" xr:uid="{00000000-0004-0000-0000-00000C020000}"/>
+    <hyperlink ref="C546" r:id="rId526" xr:uid="{00000000-0004-0000-0000-00000D020000}"/>
+    <hyperlink ref="C547" r:id="rId527" xr:uid="{00000000-0004-0000-0000-00000E020000}"/>
+    <hyperlink ref="C548" r:id="rId528" xr:uid="{00000000-0004-0000-0000-00000F020000}"/>
+    <hyperlink ref="C549" r:id="rId529" xr:uid="{00000000-0004-0000-0000-000010020000}"/>
+    <hyperlink ref="C550" r:id="rId530" xr:uid="{00000000-0004-0000-0000-000011020000}"/>
+    <hyperlink ref="C551" r:id="rId531" xr:uid="{00000000-0004-0000-0000-000012020000}"/>
+    <hyperlink ref="C552" r:id="rId532" xr:uid="{00000000-0004-0000-0000-000013020000}"/>
+    <hyperlink ref="C553" r:id="rId533" xr:uid="{00000000-0004-0000-0000-000014020000}"/>
+    <hyperlink ref="C554" r:id="rId534" xr:uid="{00000000-0004-0000-0000-000015020000}"/>
+    <hyperlink ref="C555" r:id="rId535" xr:uid="{00000000-0004-0000-0000-000016020000}"/>
+    <hyperlink ref="C556" r:id="rId536" xr:uid="{00000000-0004-0000-0000-000017020000}"/>
+    <hyperlink ref="C557" r:id="rId537" xr:uid="{00000000-0004-0000-0000-000018020000}"/>
+    <hyperlink ref="C558" r:id="rId538" xr:uid="{00000000-0004-0000-0000-000019020000}"/>
+    <hyperlink ref="C559" r:id="rId539" xr:uid="{00000000-0004-0000-0000-00001A020000}"/>
+    <hyperlink ref="C560" r:id="rId540" xr:uid="{00000000-0004-0000-0000-00001B020000}"/>
+    <hyperlink ref="C561" r:id="rId541" xr:uid="{00000000-0004-0000-0000-00001C020000}"/>
+    <hyperlink ref="C562" r:id="rId542" xr:uid="{00000000-0004-0000-0000-00001D020000}"/>
+    <hyperlink ref="C563" r:id="rId543" xr:uid="{00000000-0004-0000-0000-00001E020000}"/>
+    <hyperlink ref="C564" r:id="rId544" xr:uid="{00000000-0004-0000-0000-00001F020000}"/>
+    <hyperlink ref="C36" r:id="rId545" xr:uid="{00000000-0004-0000-0000-000020020000}"/>
+    <hyperlink ref="C565" r:id="rId546" xr:uid="{00000000-0004-0000-0000-000021020000}"/>
+    <hyperlink ref="C566" r:id="rId547" xr:uid="{00000000-0004-0000-0000-000022020000}"/>
+    <hyperlink ref="C567" r:id="rId548" xr:uid="{00000000-0004-0000-0000-000023020000}"/>
+    <hyperlink ref="C568" r:id="rId549" xr:uid="{00000000-0004-0000-0000-000024020000}"/>
+    <hyperlink ref="C569" r:id="rId550" xr:uid="{00000000-0004-0000-0000-000025020000}"/>
+    <hyperlink ref="C570" r:id="rId551" xr:uid="{00000000-0004-0000-0000-000026020000}"/>
+    <hyperlink ref="C571" r:id="rId552" xr:uid="{00000000-0004-0000-0000-000027020000}"/>
+    <hyperlink ref="C572" r:id="rId553" xr:uid="{00000000-0004-0000-0000-000028020000}"/>
+    <hyperlink ref="C573" r:id="rId554" xr:uid="{00000000-0004-0000-0000-000029020000}"/>
+    <hyperlink ref="C574" r:id="rId555" xr:uid="{00000000-0004-0000-0000-00002A020000}"/>
+    <hyperlink ref="C575" r:id="rId556" xr:uid="{00000000-0004-0000-0000-00002B020000}"/>
+    <hyperlink ref="C576" r:id="rId557" xr:uid="{00000000-0004-0000-0000-00002C020000}"/>
+    <hyperlink ref="C577" r:id="rId558" xr:uid="{00000000-0004-0000-0000-00002D020000}"/>
+    <hyperlink ref="C578" r:id="rId559" xr:uid="{00000000-0004-0000-0000-00002E020000}"/>
+    <hyperlink ref="C579" r:id="rId560" xr:uid="{00000000-0004-0000-0000-00002F020000}"/>
+    <hyperlink ref="C580" r:id="rId561" xr:uid="{00000000-0004-0000-0000-000030020000}"/>
+    <hyperlink ref="C581" r:id="rId562" xr:uid="{00000000-0004-0000-0000-000031020000}"/>
+    <hyperlink ref="C582" r:id="rId563" xr:uid="{00000000-0004-0000-0000-000032020000}"/>
+    <hyperlink ref="C583" r:id="rId564" xr:uid="{00000000-0004-0000-0000-000033020000}"/>
+    <hyperlink ref="C584" r:id="rId565" xr:uid="{00000000-0004-0000-0000-000034020000}"/>
+    <hyperlink ref="C585" r:id="rId566" xr:uid="{00000000-0004-0000-0000-000035020000}"/>
+    <hyperlink ref="C586" r:id="rId567" xr:uid="{00000000-0004-0000-0000-000036020000}"/>
+    <hyperlink ref="C587" r:id="rId568" xr:uid="{00000000-0004-0000-0000-000037020000}"/>
+    <hyperlink ref="C588" r:id="rId569" xr:uid="{00000000-0004-0000-0000-000038020000}"/>
+    <hyperlink ref="C589" r:id="rId570" xr:uid="{00000000-0004-0000-0000-000039020000}"/>
+    <hyperlink ref="C590" r:id="rId571" xr:uid="{00000000-0004-0000-0000-00003A020000}"/>
+    <hyperlink ref="C591" r:id="rId572" xr:uid="{00000000-0004-0000-0000-00003B020000}"/>
+    <hyperlink ref="C592" r:id="rId573" xr:uid="{00000000-0004-0000-0000-00003C020000}"/>
+    <hyperlink ref="C593" r:id="rId574" xr:uid="{00000000-0004-0000-0000-00003D020000}"/>
+    <hyperlink ref="C594" r:id="rId575" xr:uid="{00000000-0004-0000-0000-00003E020000}"/>
+    <hyperlink ref="C595" r:id="rId576" xr:uid="{00000000-0004-0000-0000-00003F020000}"/>
+    <hyperlink ref="C596" r:id="rId577" xr:uid="{00000000-0004-0000-0000-000040020000}"/>
+    <hyperlink ref="C597" r:id="rId578" xr:uid="{00000000-0004-0000-0000-000041020000}"/>
+    <hyperlink ref="C598" r:id="rId579" xr:uid="{00000000-0004-0000-0000-000042020000}"/>
+    <hyperlink ref="C599" r:id="rId580" xr:uid="{00000000-0004-0000-0000-000043020000}"/>
+    <hyperlink ref="C600" r:id="rId581" xr:uid="{00000000-0004-0000-0000-000044020000}"/>
+    <hyperlink ref="C601" r:id="rId582" xr:uid="{00000000-0004-0000-0000-000045020000}"/>
+    <hyperlink ref="C602" r:id="rId583" xr:uid="{00000000-0004-0000-0000-000046020000}"/>
+    <hyperlink ref="C603" r:id="rId584" xr:uid="{00000000-0004-0000-0000-000047020000}"/>
+    <hyperlink ref="C604" r:id="rId585" xr:uid="{00000000-0004-0000-0000-000048020000}"/>
+    <hyperlink ref="C605" r:id="rId586" xr:uid="{00000000-0004-0000-0000-000049020000}"/>
+    <hyperlink ref="C606" r:id="rId587" xr:uid="{00000000-0004-0000-0000-00004A020000}"/>
+    <hyperlink ref="C607" r:id="rId588" xr:uid="{00000000-0004-0000-0000-00004B020000}"/>
+    <hyperlink ref="C608" r:id="rId589" xr:uid="{00000000-0004-0000-0000-00004C020000}"/>
+    <hyperlink ref="C609" r:id="rId590" xr:uid="{00000000-0004-0000-0000-00004D020000}"/>
+    <hyperlink ref="C610" r:id="rId591" xr:uid="{00000000-0004-0000-0000-00004E020000}"/>
+    <hyperlink ref="C611" r:id="rId592" xr:uid="{00000000-0004-0000-0000-00004F020000}"/>
+    <hyperlink ref="C612" r:id="rId593" xr:uid="{00000000-0004-0000-0000-000050020000}"/>
+    <hyperlink ref="C613" r:id="rId594" xr:uid="{00000000-0004-0000-0000-000051020000}"/>
+    <hyperlink ref="C614" r:id="rId595" xr:uid="{00000000-0004-0000-0000-000052020000}"/>
+    <hyperlink ref="C615" r:id="rId596" xr:uid="{00000000-0004-0000-0000-000053020000}"/>
+    <hyperlink ref="C616" r:id="rId597" xr:uid="{00000000-0004-0000-0000-000054020000}"/>
+    <hyperlink ref="C617" r:id="rId598" xr:uid="{00000000-0004-0000-0000-000055020000}"/>
+    <hyperlink ref="C618" r:id="rId599" xr:uid="{00000000-0004-0000-0000-000056020000}"/>
+    <hyperlink ref="C619" r:id="rId600" xr:uid="{00000000-0004-0000-0000-000057020000}"/>
+    <hyperlink ref="C620" r:id="rId601" xr:uid="{00000000-0004-0000-0000-000058020000}"/>
+    <hyperlink ref="C621" r:id="rId602" xr:uid="{00000000-0004-0000-0000-000059020000}"/>
+    <hyperlink ref="C622" r:id="rId603" xr:uid="{00000000-0004-0000-0000-00005A020000}"/>
+    <hyperlink ref="C623" r:id="rId604" xr:uid="{00000000-0004-0000-0000-00005B020000}"/>
+    <hyperlink ref="C624" r:id="rId605" xr:uid="{00000000-0004-0000-0000-00005C020000}"/>
+    <hyperlink ref="C625" r:id="rId606" xr:uid="{00000000-0004-0000-0000-00005D020000}"/>
+    <hyperlink ref="C626" r:id="rId607" xr:uid="{00000000-0004-0000-0000-00005E020000}"/>
+    <hyperlink ref="C627" r:id="rId608" xr:uid="{00000000-0004-0000-0000-00005F020000}"/>
+    <hyperlink ref="C628" r:id="rId609" xr:uid="{00000000-0004-0000-0000-000060020000}"/>
+    <hyperlink ref="C629" r:id="rId610" xr:uid="{00000000-0004-0000-0000-000061020000}"/>
+    <hyperlink ref="C630" r:id="rId611" xr:uid="{00000000-0004-0000-0000-000062020000}"/>
+    <hyperlink ref="C631" r:id="rId612" xr:uid="{00000000-0004-0000-0000-000063020000}"/>
+    <hyperlink ref="C632" r:id="rId613" xr:uid="{00000000-0004-0000-0000-000064020000}"/>
+    <hyperlink ref="C633" r:id="rId614" xr:uid="{00000000-0004-0000-0000-000065020000}"/>
+    <hyperlink ref="C634" r:id="rId615" xr:uid="{00000000-0004-0000-0000-000066020000}"/>
+    <hyperlink ref="C635" r:id="rId616" xr:uid="{00000000-0004-0000-0000-000067020000}"/>
+    <hyperlink ref="C37" r:id="rId617" xr:uid="{00000000-0004-0000-0000-000068020000}"/>
+    <hyperlink ref="C636" r:id="rId618" xr:uid="{00000000-0004-0000-0000-000069020000}"/>
+    <hyperlink ref="C637" r:id="rId619" xr:uid="{00000000-0004-0000-0000-00006A020000}"/>
+    <hyperlink ref="C638" r:id="rId620" xr:uid="{00000000-0004-0000-0000-00006B020000}"/>
+    <hyperlink ref="C639" r:id="rId621" xr:uid="{00000000-0004-0000-0000-00006C020000}"/>
+    <hyperlink ref="C640" r:id="rId622" xr:uid="{00000000-0004-0000-0000-00006D020000}"/>
+    <hyperlink ref="C641" r:id="rId623" xr:uid="{00000000-0004-0000-0000-00006E020000}"/>
+    <hyperlink ref="C642" r:id="rId624" xr:uid="{00000000-0004-0000-0000-00006F020000}"/>
+    <hyperlink ref="C643" r:id="rId625" xr:uid="{00000000-0004-0000-0000-000070020000}"/>
+    <hyperlink ref="C644" r:id="rId626" xr:uid="{00000000-0004-0000-0000-000071020000}"/>
+    <hyperlink ref="C645" r:id="rId627" xr:uid="{00000000-0004-0000-0000-000072020000}"/>
+    <hyperlink ref="C646" r:id="rId628" xr:uid="{00000000-0004-0000-0000-000073020000}"/>
+    <hyperlink ref="C647" r:id="rId629" xr:uid="{00000000-0004-0000-0000-000074020000}"/>
+    <hyperlink ref="C648" r:id="rId630" xr:uid="{00000000-0004-0000-0000-000075020000}"/>
+    <hyperlink ref="C38" r:id="rId631" xr:uid="{00000000-0004-0000-0000-000076020000}"/>
+    <hyperlink ref="C649" r:id="rId632" xr:uid="{00000000-0004-0000-0000-000077020000}"/>
+    <hyperlink ref="C650" r:id="rId633" xr:uid="{00000000-0004-0000-0000-000078020000}"/>
+    <hyperlink ref="C651" r:id="rId634" xr:uid="{00000000-0004-0000-0000-000079020000}"/>
+    <hyperlink ref="C652" r:id="rId635" xr:uid="{00000000-0004-0000-0000-00007A020000}"/>
+    <hyperlink ref="C653" r:id="rId636" xr:uid="{00000000-0004-0000-0000-00007B020000}"/>
+    <hyperlink ref="C654" r:id="rId637" xr:uid="{00000000-0004-0000-0000-00007C020000}"/>
+    <hyperlink ref="C655" r:id="rId638" xr:uid="{00000000-0004-0000-0000-00007D020000}"/>
+    <hyperlink ref="C656" r:id="rId639" xr:uid="{00000000-0004-0000-0000-00007E020000}"/>
+    <hyperlink ref="C657" r:id="rId640" xr:uid="{00000000-0004-0000-0000-00007F020000}"/>
+    <hyperlink ref="C658" r:id="rId641" xr:uid="{00000000-0004-0000-0000-000080020000}"/>
+    <hyperlink ref="C659" r:id="rId642" xr:uid="{00000000-0004-0000-0000-000081020000}"/>
+    <hyperlink ref="C660" r:id="rId643" xr:uid="{00000000-0004-0000-0000-000082020000}"/>
+    <hyperlink ref="C661" r:id="rId644" xr:uid="{00000000-0004-0000-0000-000083020000}"/>
+    <hyperlink ref="C39" r:id="rId645" xr:uid="{00000000-0004-0000-0000-000084020000}"/>
+    <hyperlink ref="C662" r:id="rId646" xr:uid="{00000000-0004-0000-0000-000085020000}"/>
+    <hyperlink ref="C663" r:id="rId647" xr:uid="{00000000-0004-0000-0000-000086020000}"/>
+    <hyperlink ref="C664" r:id="rId648" xr:uid="{00000000-0004-0000-0000-000087020000}"/>
+    <hyperlink ref="C665" r:id="rId649" xr:uid="{00000000-0004-0000-0000-000088020000}"/>
+    <hyperlink ref="C40" r:id="rId650" xr:uid="{00000000-0004-0000-0000-000089020000}"/>
+    <hyperlink ref="C666" r:id="rId651" xr:uid="{00000000-0004-0000-0000-00008A020000}"/>
+    <hyperlink ref="C667" r:id="rId652" xr:uid="{00000000-0004-0000-0000-00008B020000}"/>
+    <hyperlink ref="C41" r:id="rId653" xr:uid="{00000000-0004-0000-0000-00008C020000}"/>
+    <hyperlink ref="C668" r:id="rId654" xr:uid="{00000000-0004-0000-0000-00008D020000}"/>
+    <hyperlink ref="C669" r:id="rId655" xr:uid="{00000000-0004-0000-0000-00008E020000}"/>
+    <hyperlink ref="C670" r:id="rId656" xr:uid="{00000000-0004-0000-0000-00008F020000}"/>
+    <hyperlink ref="C671" r:id="rId657" xr:uid="{00000000-0004-0000-0000-000090020000}"/>
+    <hyperlink ref="C672" r:id="rId658" xr:uid="{00000000-0004-0000-0000-000091020000}"/>
+    <hyperlink ref="C673" r:id="rId659" xr:uid="{00000000-0004-0000-0000-000092020000}"/>
+    <hyperlink ref="C42" r:id="rId660" xr:uid="{00000000-0004-0000-0000-000093020000}"/>
+    <hyperlink ref="C674" r:id="rId661" xr:uid="{00000000-0004-0000-0000-000094020000}"/>
+    <hyperlink ref="C43" r:id="rId662" xr:uid="{00000000-0004-0000-0000-000095020000}"/>
+    <hyperlink ref="C675" r:id="rId663" xr:uid="{00000000-0004-0000-0000-000096020000}"/>
+    <hyperlink ref="C676" r:id="rId664" xr:uid="{00000000-0004-0000-0000-000097020000}"/>
+    <hyperlink ref="C677" r:id="rId665" xr:uid="{00000000-0004-0000-0000-000098020000}"/>
+    <hyperlink ref="C678" r:id="rId666" xr:uid="{00000000-0004-0000-0000-000099020000}"/>
+    <hyperlink ref="C679" r:id="rId667" xr:uid="{00000000-0004-0000-0000-00009A020000}"/>
+    <hyperlink ref="C680" r:id="rId668" xr:uid="{00000000-0004-0000-0000-00009B020000}"/>
+    <hyperlink ref="C681" r:id="rId669" xr:uid="{00000000-0004-0000-0000-00009C020000}"/>
+    <hyperlink ref="C682" r:id="rId670" xr:uid="{00000000-0004-0000-0000-00009D020000}"/>
+    <hyperlink ref="C683" r:id="rId671" xr:uid="{00000000-0004-0000-0000-00009E020000}"/>
+    <hyperlink ref="C684" r:id="rId672" xr:uid="{00000000-0004-0000-0000-00009F020000}"/>
+    <hyperlink ref="C685" r:id="rId673" xr:uid="{00000000-0004-0000-0000-0000A0020000}"/>
+    <hyperlink ref="C686" r:id="rId674" xr:uid="{00000000-0004-0000-0000-0000A1020000}"/>
+    <hyperlink ref="C687" r:id="rId675" xr:uid="{00000000-0004-0000-0000-0000A2020000}"/>
+    <hyperlink ref="C688" r:id="rId676" xr:uid="{00000000-0004-0000-0000-0000A3020000}"/>
+    <hyperlink ref="C689" r:id="rId677" xr:uid="{00000000-0004-0000-0000-0000A4020000}"/>
+    <hyperlink ref="C690" r:id="rId678" xr:uid="{00000000-0004-0000-0000-0000A5020000}"/>
+    <hyperlink ref="C691" r:id="rId679" xr:uid="{00000000-0004-0000-0000-0000A6020000}"/>
+    <hyperlink ref="C692" r:id="rId680" xr:uid="{00000000-0004-0000-0000-0000A7020000}"/>
+    <hyperlink ref="C693" r:id="rId681" xr:uid="{00000000-0004-0000-0000-0000A8020000}"/>
+    <hyperlink ref="C694" r:id="rId682" xr:uid="{00000000-0004-0000-0000-0000A9020000}"/>
+    <hyperlink ref="C695" r:id="rId683" xr:uid="{00000000-0004-0000-0000-0000AA020000}"/>
+    <hyperlink ref="C696" r:id="rId684" xr:uid="{00000000-0004-0000-0000-0000AB020000}"/>
+    <hyperlink ref="C697" r:id="rId685" xr:uid="{00000000-0004-0000-0000-0000AC020000}"/>
+    <hyperlink ref="C698" r:id="rId686" xr:uid="{00000000-0004-0000-0000-0000AD020000}"/>
+    <hyperlink ref="C699" r:id="rId687" xr:uid="{00000000-0004-0000-0000-0000AE020000}"/>
+    <hyperlink ref="C700" r:id="rId688" xr:uid="{00000000-0004-0000-0000-0000AF020000}"/>
+    <hyperlink ref="C701" r:id="rId689" xr:uid="{00000000-0004-0000-0000-0000B0020000}"/>
+    <hyperlink ref="C702" r:id="rId690" xr:uid="{00000000-0004-0000-0000-0000B1020000}"/>
+    <hyperlink ref="C703" r:id="rId691" xr:uid="{00000000-0004-0000-0000-0000B2020000}"/>
+    <hyperlink ref="C704" r:id="rId692" xr:uid="{00000000-0004-0000-0000-0000B3020000}"/>
+    <hyperlink ref="C705" r:id="rId693" xr:uid="{00000000-0004-0000-0000-0000B4020000}"/>
+    <hyperlink ref="C706" r:id="rId694" xr:uid="{00000000-0004-0000-0000-0000B5020000}"/>
+    <hyperlink ref="C707" r:id="rId695" xr:uid="{00000000-0004-0000-0000-0000B6020000}"/>
+    <hyperlink ref="C708" r:id="rId696" xr:uid="{00000000-0004-0000-0000-0000B7020000}"/>
+    <hyperlink ref="C709" r:id="rId697" xr:uid="{00000000-0004-0000-0000-0000B8020000}"/>
+    <hyperlink ref="C710" r:id="rId698" xr:uid="{00000000-0004-0000-0000-0000B9020000}"/>
+    <hyperlink ref="C711" r:id="rId699" xr:uid="{00000000-0004-0000-0000-0000BA020000}"/>
+    <hyperlink ref="C712" r:id="rId700" xr:uid="{00000000-0004-0000-0000-0000BB020000}"/>
+    <hyperlink ref="C44" r:id="rId701" xr:uid="{00000000-0004-0000-0000-0000BC020000}"/>
+    <hyperlink ref="C713" r:id="rId702" xr:uid="{00000000-0004-0000-0000-0000BD020000}"/>
+    <hyperlink ref="C714" r:id="rId703" xr:uid="{00000000-0004-0000-0000-0000BE020000}"/>
+    <hyperlink ref="C715" r:id="rId704" xr:uid="{00000000-0004-0000-0000-0000BF020000}"/>
+    <hyperlink ref="C716" r:id="rId705" xr:uid="{00000000-0004-0000-0000-0000C0020000}"/>
+    <hyperlink ref="C717" r:id="rId706" xr:uid="{00000000-0004-0000-0000-0000C1020000}"/>
+    <hyperlink ref="C718" r:id="rId707" xr:uid="{00000000-0004-0000-0000-0000C2020000}"/>
+    <hyperlink ref="C719" r:id="rId708" xr:uid="{00000000-0004-0000-0000-0000C3020000}"/>
+    <hyperlink ref="C720" r:id="rId709" xr:uid="{00000000-0004-0000-0000-0000C4020000}"/>
+    <hyperlink ref="C721" r:id="rId710" xr:uid="{00000000-0004-0000-0000-0000C5020000}"/>
+    <hyperlink ref="C722" r:id="rId711" xr:uid="{00000000-0004-0000-0000-0000C6020000}"/>
+    <hyperlink ref="C723" r:id="rId712" xr:uid="{00000000-0004-0000-0000-0000C7020000}"/>
+    <hyperlink ref="C724" r:id="rId713" xr:uid="{00000000-0004-0000-0000-0000C8020000}"/>
+    <hyperlink ref="C725" r:id="rId714" xr:uid="{00000000-0004-0000-0000-0000C9020000}"/>
+    <hyperlink ref="C726" r:id="rId715" xr:uid="{00000000-0004-0000-0000-0000CA020000}"/>
+    <hyperlink ref="C727" r:id="rId716" xr:uid="{00000000-0004-0000-0000-0000CB020000}"/>
+    <hyperlink ref="C728" r:id="rId717" xr:uid="{00000000-0004-0000-0000-0000CC020000}"/>
+    <hyperlink ref="C729" r:id="rId718" xr:uid="{00000000-0004-0000-0000-0000CD020000}"/>
+    <hyperlink ref="C730" r:id="rId719" xr:uid="{00000000-0004-0000-0000-0000CE020000}"/>
+    <hyperlink ref="C731" r:id="rId720" xr:uid="{00000000-0004-0000-0000-0000CF020000}"/>
+    <hyperlink ref="C732" r:id="rId721" xr:uid="{00000000-0004-0000-0000-0000D0020000}"/>
+    <hyperlink ref="C733" r:id="rId722" xr:uid="{00000000-0004-0000-0000-0000D1020000}"/>
+    <hyperlink ref="C734" r:id="rId723" xr:uid="{00000000-0004-0000-0000-0000D2020000}"/>
+    <hyperlink ref="C45" r:id="rId724" xr:uid="{00000000-0004-0000-0000-0000D3020000}"/>
+    <hyperlink ref="C46" r:id="rId725" xr:uid="{00000000-0004-0000-0000-0000D4020000}"/>
+    <hyperlink ref="C735" r:id="rId726" xr:uid="{00000000-0004-0000-0000-0000D5020000}"/>
+    <hyperlink ref="C736" r:id="rId727" xr:uid="{00000000-0004-0000-0000-0000D6020000}"/>
+    <hyperlink ref="C737" r:id="rId728" xr:uid="{00000000-0004-0000-0000-0000D7020000}"/>
+    <hyperlink ref="C738" r:id="rId729" xr:uid="{00000000-0004-0000-0000-0000D8020000}"/>
+    <hyperlink ref="C739" r:id="rId730" xr:uid="{00000000-0004-0000-0000-0000D9020000}"/>
+    <hyperlink ref="C47" r:id="rId731" xr:uid="{00000000-0004-0000-0000-0000DA020000}"/>
+    <hyperlink ref="C48" r:id="rId732" xr:uid="{00000000-0004-0000-0000-0000DB020000}"/>
+    <hyperlink ref="C740" r:id="rId733" xr:uid="{00000000-0004-0000-0000-0000DC020000}"/>
+    <hyperlink ref="C741" r:id="rId734" xr:uid="{00000000-0004-0000-0000-0000DD020000}"/>
+    <hyperlink ref="C742" r:id="rId735" xr:uid="{00000000-0004-0000-0000-0000DE020000}"/>
+    <hyperlink ref="C743" r:id="rId736" xr:uid="{00000000-0004-0000-0000-0000DF020000}"/>
+    <hyperlink ref="C744" r:id="rId737" xr:uid="{00000000-0004-0000-0000-0000E0020000}"/>
+    <hyperlink ref="C745" r:id="rId738" xr:uid="{00000000-0004-0000-0000-0000E1020000}"/>
+    <hyperlink ref="C746" r:id="rId739" xr:uid="{00000000-0004-0000-0000-0000E2020000}"/>
+    <hyperlink ref="C747" r:id="rId740" xr:uid="{00000000-0004-0000-0000-0000E3020000}"/>
+    <hyperlink ref="C49" r:id="rId741" xr:uid="{00000000-0004-0000-0000-0000E4020000}"/>
+    <hyperlink ref="C748" r:id="rId742" xr:uid="{00000000-0004-0000-0000-0000E5020000}"/>
+    <hyperlink ref="C749" r:id="rId743" xr:uid="{00000000-0004-0000-0000-0000E6020000}"/>
+    <hyperlink ref="C750" r:id="rId744" xr:uid="{00000000-0004-0000-0000-0000E7020000}"/>
+    <hyperlink ref="C751" r:id="rId745" xr:uid="{00000000-0004-0000-0000-0000E8020000}"/>
+    <hyperlink ref="C752" r:id="rId746" xr:uid="{00000000-0004-0000-0000-0000E9020000}"/>
+    <hyperlink ref="C753" r:id="rId747" xr:uid="{00000000-0004-0000-0000-0000EA020000}"/>
+    <hyperlink ref="C754" r:id="rId748" xr:uid="{00000000-0004-0000-0000-0000EB020000}"/>
+    <hyperlink ref="C755" r:id="rId749" xr:uid="{00000000-0004-0000-0000-0000EC020000}"/>
+    <hyperlink ref="C756" r:id="rId750" xr:uid="{00000000-0004-0000-0000-0000ED020000}"/>
+    <hyperlink ref="C50" r:id="rId751" xr:uid="{00000000-0004-0000-0000-0000EE020000}"/>
+    <hyperlink ref="C757" r:id="rId752" xr:uid="{00000000-0004-0000-0000-0000EF020000}"/>
+    <hyperlink ref="C758" r:id="rId753" xr:uid="{00000000-0004-0000-0000-0000F0020000}"/>
+    <hyperlink ref="C759" r:id="rId754" xr:uid="{00000000-0004-0000-0000-0000F1020000}"/>
+    <hyperlink ref="C760" r:id="rId755" xr:uid="{00000000-0004-0000-0000-0000F2020000}"/>
+    <hyperlink ref="C761" r:id="rId756" xr:uid="{00000000-0004-0000-0000-0000F3020000}"/>
+    <hyperlink ref="C762" r:id="rId757" xr:uid="{00000000-0004-0000-0000-0000F4020000}"/>
+    <hyperlink ref="C763" r:id="rId758" xr:uid="{00000000-0004-0000-0000-0000F5020000}"/>
+    <hyperlink ref="C764" r:id="rId759" xr:uid="{00000000-0004-0000-0000-0000F6020000}"/>
+    <hyperlink ref="C765" r:id="rId760" xr:uid="{00000000-0004-0000-0000-0000F7020000}"/>
+    <hyperlink ref="C766" r:id="rId761" xr:uid="{00000000-0004-0000-0000-0000F8020000}"/>
+    <hyperlink ref="C767" r:id="rId762" xr:uid="{00000000-0004-0000-0000-0000F9020000}"/>
+    <hyperlink ref="C51" r:id="rId763" xr:uid="{00000000-0004-0000-0000-0000FA020000}"/>
+    <hyperlink ref="C768" r:id="rId764" xr:uid="{00000000-0004-0000-0000-0000FB020000}"/>
+    <hyperlink ref="C769" r:id="rId765" xr:uid="{00000000-0004-0000-0000-0000FC020000}"/>
+    <hyperlink ref="C770" r:id="rId766" xr:uid="{00000000-0004-0000-0000-0000FD020000}"/>
+    <hyperlink ref="C771" r:id="rId767" xr:uid="{00000000-0004-0000-0000-0000FE020000}"/>
+    <hyperlink ref="C772" r:id="rId768" xr:uid="{00000000-0004-0000-0000-0000FF020000}"/>
+    <hyperlink ref="C773" r:id="rId769" xr:uid="{00000000-0004-0000-0000-000000030000}"/>
+    <hyperlink ref="C774" r:id="rId770" xr:uid="{00000000-0004-0000-0000-000001030000}"/>
+    <hyperlink ref="C775" r:id="rId771" xr:uid="{00000000-0004-0000-0000-000002030000}"/>
+    <hyperlink ref="C776" r:id="rId772" xr:uid="{00000000-0004-0000-0000-000003030000}"/>
+    <hyperlink ref="C777" r:id="rId773" xr:uid="{00000000-0004-0000-0000-000004030000}"/>
+    <hyperlink ref="C778" r:id="rId774" xr:uid="{00000000-0004-0000-0000-000005030000}"/>
+    <hyperlink ref="C779" r:id="rId775" xr:uid="{00000000-0004-0000-0000-000006030000}"/>
+    <hyperlink ref="C780" r:id="rId776" xr:uid="{00000000-0004-0000-0000-000007030000}"/>
+    <hyperlink ref="C781" r:id="rId777" xr:uid="{00000000-0004-0000-0000-000008030000}"/>
+    <hyperlink ref="C782" r:id="rId778" xr:uid="{00000000-0004-0000-0000-000009030000}"/>
+    <hyperlink ref="C783" r:id="rId779" xr:uid="{00000000-0004-0000-0000-00000A030000}"/>
+    <hyperlink ref="C784" r:id="rId780" xr:uid="{00000000-0004-0000-0000-00000B030000}"/>
+    <hyperlink ref="C785" r:id="rId781" xr:uid="{00000000-0004-0000-0000-00000C030000}"/>
+    <hyperlink ref="C786" r:id="rId782" xr:uid="{00000000-0004-0000-0000-00000D030000}"/>
+    <hyperlink ref="C52" r:id="rId783" xr:uid="{00000000-0004-0000-0000-00000E030000}"/>
+    <hyperlink ref="C787" r:id="rId784" xr:uid="{00000000-0004-0000-0000-00000F030000}"/>
+    <hyperlink ref="C788" r:id="rId785" xr:uid="{00000000-0004-0000-0000-000010030000}"/>
+    <hyperlink ref="C789" r:id="rId786" xr:uid="{00000000-0004-0000-0000-000011030000}"/>
+    <hyperlink ref="C790" r:id="rId787" xr:uid="{00000000-0004-0000-0000-000012030000}"/>
+    <hyperlink ref="C791" r:id="rId788" xr:uid="{00000000-0004-0000-0000-000013030000}"/>
+    <hyperlink ref="C53" r:id="rId789" xr:uid="{00000000-0004-0000-0000-000014030000}"/>
+    <hyperlink ref="C792" r:id="rId790" xr:uid="{00000000-0004-0000-0000-000015030000}"/>
+    <hyperlink ref="C793" r:id="rId791" xr:uid="{00000000-0004-0000-0000-000016030000}"/>
+    <hyperlink ref="C794" r:id="rId792" xr:uid="{00000000-0004-0000-0000-000017030000}"/>
+    <hyperlink ref="C795" r:id="rId793" xr:uid="{00000000-0004-0000-0000-000018030000}"/>
+    <hyperlink ref="C796" r:id="rId794" xr:uid="{00000000-0004-0000-0000-000019030000}"/>
+    <hyperlink ref="C797" r:id="rId795" xr:uid="{00000000-0004-0000-0000-00001A030000}"/>
+    <hyperlink ref="C798" r:id="rId796" xr:uid="{00000000-0004-0000-0000-00001B030000}"/>
+    <hyperlink ref="C799" r:id="rId797" xr:uid="{00000000-0004-0000-0000-00001C030000}"/>
+    <hyperlink ref="C800" r:id="rId798" xr:uid="{00000000-0004-0000-0000-00001D030000}"/>
+    <hyperlink ref="C801" r:id="rId799" xr:uid="{00000000-0004-0000-0000-00001E030000}"/>
+    <hyperlink ref="C802" r:id="rId800" xr:uid="{00000000-0004-0000-0000-00001F030000}"/>
+    <hyperlink ref="C803" r:id="rId801" xr:uid="{00000000-0004-0000-0000-000020030000}"/>
+    <hyperlink ref="C804" r:id="rId802" xr:uid="{00000000-0004-0000-0000-000021030000}"/>
+    <hyperlink ref="C805" r:id="rId803" xr:uid="{00000000-0004-0000-0000-000022030000}"/>
+    <hyperlink ref="C806" r:id="rId804" xr:uid="{00000000-0004-0000-0000-000023030000}"/>
+    <hyperlink ref="C54" r:id="rId805" xr:uid="{00000000-0004-0000-0000-000024030000}"/>
+    <hyperlink ref="C807" r:id="rId806" xr:uid="{00000000-0004-0000-0000-000025030000}"/>
+    <hyperlink ref="C808" r:id="rId807" xr:uid="{00000000-0004-0000-0000-000026030000}"/>
+    <hyperlink ref="C809" r:id="rId808" xr:uid="{00000000-0004-0000-0000-000027030000}"/>
+    <hyperlink ref="C810" r:id="rId809" xr:uid="{00000000-0004-0000-0000-000028030000}"/>
+    <hyperlink ref="C811" r:id="rId810" xr:uid="{00000000-0004-0000-0000-000029030000}"/>
+    <hyperlink ref="C812" r:id="rId811" xr:uid="{00000000-0004-0000-0000-00002A030000}"/>
+    <hyperlink ref="C813" r:id="rId812" xr:uid="{00000000-0004-0000-0000-00002B030000}"/>
+    <hyperlink ref="C814" r:id="rId813" xr:uid="{00000000-0004-0000-0000-00002C030000}"/>
+    <hyperlink ref="C815" r:id="rId814" xr:uid="{00000000-0004-0000-0000-00002D030000}"/>
+    <hyperlink ref="C816" r:id="rId815" xr:uid="{00000000-0004-0000-0000-00002E030000}"/>
+    <hyperlink ref="C817" r:id="rId816" xr:uid="{00000000-0004-0000-0000-00002F030000}"/>
+    <hyperlink ref="C818" r:id="rId817" xr:uid="{00000000-0004-0000-0000-000030030000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/danish_artwork_review.xlsx
+++ b/data/danish_artwork_review.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EPGoal\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{835781FE-4CF9-4372-87E1-64187A99F4E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{940F0F56-D44E-47D5-AB7B-1AE97F59F8C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3643" uniqueCount="1827">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3663" uniqueCount="1837">
   <si>
     <t>Nøgle (intern)</t>
   </si>
@@ -1670,6 +1670,12 @@
     <t>Flyvende Farmor</t>
   </si>
   <si>
+    <t>flådens friske fyre</t>
+  </si>
+  <si>
+    <t>Flådens friske fyre</t>
+  </si>
+  <si>
     <t>flådens historie</t>
   </si>
   <si>
@@ -2420,6 +2426,12 @@
     <t>Hvor er Kylling?</t>
   </si>
   <si>
+    <t>hvor ondskab bor</t>
+  </si>
+  <si>
+    <t>Hvor ondskab bor</t>
+  </si>
+  <si>
     <t>hvornår var det nu det var</t>
   </si>
   <si>
@@ -2642,6 +2654,12 @@
     <t>Joanna Lumley på den skønne, blå Donau</t>
   </si>
   <si>
+    <t>joanna lumley's spice trail adventure</t>
+  </si>
+  <si>
+    <t>Joanna Lumley's Spice Trail Adventure</t>
+  </si>
+  <si>
     <t>john dillermand</t>
   </si>
   <si>
@@ -2882,6 +2900,12 @@
     <t>Kollision</t>
   </si>
   <si>
+    <t>kommissar dupin</t>
+  </si>
+  <si>
+    <t>Kommissar Dupin</t>
+  </si>
+  <si>
     <t>kommissar van der valk</t>
   </si>
   <si>
@@ -5070,6 +5094,12 @@
   </si>
   <si>
     <t>Tuva og Ronnys græske hotel</t>
+  </si>
+  <si>
+    <t>tøffe vs. graver</t>
+  </si>
+  <si>
+    <t>Tøffe vs. Graver</t>
   </si>
   <si>
     <t>uforglemt</t>
@@ -5879,7 +5909,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F907"/>
+  <dimension ref="A1:F912"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -6247,10 +6277,10 @@
     </row>
     <row r="26" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B26" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>7</v>
@@ -6261,10 +6291,10 @@
     </row>
     <row r="27" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B27" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>7</v>
@@ -6275,10 +6305,10 @@
     </row>
     <row r="28" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B28" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>7</v>
@@ -6289,10 +6319,10 @@
     </row>
     <row r="29" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B29" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>7</v>
@@ -6303,10 +6333,10 @@
     </row>
     <row r="30" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B30" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>7</v>
@@ -6317,10 +6347,10 @@
     </row>
     <row r="31" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="B31" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>7</v>
@@ -6331,10 +6361,10 @@
     </row>
     <row r="32" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="B32" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>7</v>
@@ -6345,10 +6375,10 @@
     </row>
     <row r="33" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="B33" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>7</v>
@@ -6359,10 +6389,10 @@
     </row>
     <row r="34" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="B34" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>7</v>
@@ -6373,10 +6403,10 @@
     </row>
     <row r="35" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>924</v>
+        <v>930</v>
       </c>
       <c r="B35" t="s">
-        <v>925</v>
+        <v>931</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>7</v>
@@ -6387,10 +6417,10 @@
     </row>
     <row r="36" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>942</v>
+        <v>948</v>
       </c>
       <c r="B36" t="s">
-        <v>943</v>
+        <v>949</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>7</v>
@@ -6401,10 +6431,10 @@
     </row>
     <row r="37" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>986</v>
+        <v>994</v>
       </c>
       <c r="B37" t="s">
-        <v>987</v>
+        <v>995</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>7</v>
@@ -6415,10 +6445,10 @@
     </row>
     <row r="38" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>1000</v>
+        <v>1008</v>
       </c>
       <c r="B38" t="s">
-        <v>1001</v>
+        <v>1009</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>7</v>
@@ -6429,10 +6459,10 @@
     </row>
     <row r="39" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>1028</v>
+        <v>1036</v>
       </c>
       <c r="B39" t="s">
-        <v>1029</v>
+        <v>1037</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>7</v>
@@ -6443,10 +6473,10 @@
     </row>
     <row r="40" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>1050</v>
+        <v>1058</v>
       </c>
       <c r="B40" t="s">
-        <v>1051</v>
+        <v>1059</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>7</v>
@@ -6457,10 +6487,10 @@
     </row>
     <row r="41" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>1056</v>
+        <v>1064</v>
       </c>
       <c r="B41" t="s">
-        <v>1057</v>
+        <v>1065</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>7</v>
@@ -6471,10 +6501,10 @@
     </row>
     <row r="42" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>1158</v>
+        <v>1166</v>
       </c>
       <c r="B42" t="s">
-        <v>1159</v>
+        <v>1167</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>7</v>
@@ -6485,10 +6515,10 @@
     </row>
     <row r="43" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>1218</v>
+        <v>1226</v>
       </c>
       <c r="B43" t="s">
-        <v>1219</v>
+        <v>1227</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>7</v>
@@ -6499,10 +6529,10 @@
     </row>
     <row r="44" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>1302</v>
+        <v>1310</v>
       </c>
       <c r="B44" t="s">
-        <v>1303</v>
+        <v>1311</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>7</v>
@@ -6513,10 +6543,10 @@
     </row>
     <row r="45" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>1382</v>
+        <v>1390</v>
       </c>
       <c r="B45" t="s">
-        <v>1383</v>
+        <v>1391</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>7</v>
@@ -6527,10 +6557,10 @@
     </row>
     <row r="46" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>1414</v>
+        <v>1422</v>
       </c>
       <c r="B46" t="s">
-        <v>1415</v>
+        <v>1423</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>7</v>
@@ -6541,10 +6571,10 @@
     </row>
     <row r="47" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>1446</v>
+        <v>1454</v>
       </c>
       <c r="B47" t="s">
-        <v>1447</v>
+        <v>1455</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>7</v>
@@ -6555,10 +6585,10 @@
     </row>
     <row r="48" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>1456</v>
+        <v>1464</v>
       </c>
       <c r="B48" t="s">
-        <v>1457</v>
+        <v>1465</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>7</v>
@@ -6569,10 +6599,10 @@
     </row>
     <row r="49" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>1462</v>
+        <v>1470</v>
       </c>
       <c r="B49" t="s">
-        <v>1463</v>
+        <v>1471</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>7</v>
@@ -6583,10 +6613,10 @@
     </row>
     <row r="50" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>1476</v>
+        <v>1484</v>
       </c>
       <c r="B50" t="s">
-        <v>1477</v>
+        <v>1485</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>7</v>
@@ -6597,10 +6627,10 @@
     </row>
     <row r="51" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>1480</v>
+        <v>1488</v>
       </c>
       <c r="B51" t="s">
-        <v>1481</v>
+        <v>1489</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>7</v>
@@ -6611,10 +6641,10 @@
     </row>
     <row r="52" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>1566</v>
+        <v>1574</v>
       </c>
       <c r="B52" t="s">
-        <v>1567</v>
+        <v>1575</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>7</v>
@@ -6625,10 +6655,10 @@
     </row>
     <row r="53" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>1618</v>
+        <v>1626</v>
       </c>
       <c r="B53" t="s">
-        <v>1619</v>
+        <v>1627</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>7</v>
@@ -6639,10 +6669,10 @@
     </row>
     <row r="54" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>1620</v>
+        <v>1628</v>
       </c>
       <c r="B54" t="s">
-        <v>1621</v>
+        <v>1629</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>7</v>
@@ -6653,10 +6683,10 @@
     </row>
     <row r="55" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>1632</v>
+        <v>1640</v>
       </c>
       <c r="B55" t="s">
-        <v>1633</v>
+        <v>1641</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>7</v>
@@ -6667,10 +6697,10 @@
     </row>
     <row r="56" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>1634</v>
+        <v>1642</v>
       </c>
       <c r="B56" t="s">
-        <v>1635</v>
+        <v>1643</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>7</v>
@@ -6681,10 +6711,10 @@
     </row>
     <row r="57" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>1652</v>
+        <v>1660</v>
       </c>
       <c r="B57" t="s">
-        <v>1653</v>
+        <v>1661</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>7</v>
@@ -6695,10 +6725,10 @@
     </row>
     <row r="58" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>1672</v>
+        <v>1680</v>
       </c>
       <c r="B58" t="s">
-        <v>1673</v>
+        <v>1681</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>7</v>
@@ -6709,10 +6739,10 @@
     </row>
     <row r="59" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>1696</v>
+        <v>1706</v>
       </c>
       <c r="B59" t="s">
-        <v>1697</v>
+        <v>1707</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>7</v>
@@ -6723,10 +6753,10 @@
     </row>
     <row r="60" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>1742</v>
+        <v>1752</v>
       </c>
       <c r="B60" t="s">
-        <v>1743</v>
+        <v>1753</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>7</v>
@@ -6737,10 +6767,10 @@
     </row>
     <row r="61" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>1754</v>
+        <v>1764</v>
       </c>
       <c r="B61" t="s">
-        <v>1755</v>
+        <v>1765</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>7</v>
@@ -6751,10 +6781,10 @@
     </row>
     <row r="62" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>1762</v>
+        <v>1772</v>
       </c>
       <c r="B62" t="s">
-        <v>1763</v>
+        <v>1773</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>7</v>
@@ -6765,10 +6795,10 @@
     </row>
     <row r="63" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>1790</v>
+        <v>1800</v>
       </c>
       <c r="B63" t="s">
-        <v>1791</v>
+        <v>1801</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>7</v>
@@ -10251,10 +10281,10 @@
     </row>
     <row r="312" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B312" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C312" s="2" t="s">
         <v>7</v>
@@ -10265,10 +10295,10 @@
     </row>
     <row r="313" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B313" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C313" s="2" t="s">
         <v>7</v>
@@ -10279,10 +10309,10 @@
     </row>
     <row r="314" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B314" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C314" s="2" t="s">
         <v>7</v>
@@ -10293,10 +10323,10 @@
     </row>
     <row r="315" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B315" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C315" s="2" t="s">
         <v>7</v>
@@ -10307,10 +10337,10 @@
     </row>
     <row r="316" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B316" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C316" s="2" t="s">
         <v>7</v>
@@ -10321,10 +10351,10 @@
     </row>
     <row r="317" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B317" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C317" s="2" t="s">
         <v>7</v>
@@ -10335,10 +10365,10 @@
     </row>
     <row r="318" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B318" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C318" s="2" t="s">
         <v>7</v>
@@ -10349,10 +10379,10 @@
     </row>
     <row r="319" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B319" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C319" s="2" t="s">
         <v>7</v>
@@ -10363,10 +10393,10 @@
     </row>
     <row r="320" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B320" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C320" s="2" t="s">
         <v>7</v>
@@ -10377,10 +10407,10 @@
     </row>
     <row r="321" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B321" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C321" s="2" t="s">
         <v>7</v>
@@ -10391,10 +10421,10 @@
     </row>
     <row r="322" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B322" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="C322" s="2" t="s">
         <v>7</v>
@@ -10405,10 +10435,10 @@
     </row>
     <row r="323" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B323" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C323" s="2" t="s">
         <v>7</v>
@@ -10419,10 +10449,10 @@
     </row>
     <row r="324" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B324" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C324" s="2" t="s">
         <v>7</v>
@@ -10433,10 +10463,10 @@
     </row>
     <row r="325" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B325" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C325" s="2" t="s">
         <v>7</v>
@@ -10447,10 +10477,10 @@
     </row>
     <row r="326" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B326" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C326" s="2" t="s">
         <v>7</v>
@@ -10461,10 +10491,10 @@
     </row>
     <row r="327" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B327" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C327" s="2" t="s">
         <v>7</v>
@@ -10475,10 +10505,10 @@
     </row>
     <row r="328" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B328" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C328" s="2" t="s">
         <v>7</v>
@@ -10489,10 +10519,10 @@
     </row>
     <row r="329" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B329" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="C329" s="2" t="s">
         <v>7</v>
@@ -10503,10 +10533,10 @@
     </row>
     <row r="330" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="B330" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="C330" s="2" t="s">
         <v>7</v>
@@ -10517,10 +10547,10 @@
     </row>
     <row r="331" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="B331" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="C331" s="2" t="s">
         <v>7</v>
@@ -10531,10 +10561,10 @@
     </row>
     <row r="332" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B332" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C332" s="2" t="s">
         <v>7</v>
@@ -10545,10 +10575,10 @@
     </row>
     <row r="333" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="B333" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="C333" s="2" t="s">
         <v>7</v>
@@ -10559,10 +10589,10 @@
     </row>
     <row r="334" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="B334" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="C334" s="2" t="s">
         <v>7</v>
@@ -10573,10 +10603,10 @@
     </row>
     <row r="335" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B335" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="C335" s="2" t="s">
         <v>7</v>
@@ -10587,10 +10617,10 @@
     </row>
     <row r="336" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="B336" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C336" s="2" t="s">
         <v>7</v>
@@ -10601,10 +10631,10 @@
     </row>
     <row r="337" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="B337" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="C337" s="2" t="s">
         <v>7</v>
@@ -10615,10 +10645,10 @@
     </row>
     <row r="338" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="B338" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C338" s="2" t="s">
         <v>7</v>
@@ -10629,10 +10659,10 @@
     </row>
     <row r="339" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="B339" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C339" s="2" t="s">
         <v>7</v>
@@ -10643,10 +10673,10 @@
     </row>
     <row r="340" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="B340" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C340" s="2" t="s">
         <v>7</v>
@@ -10657,10 +10687,10 @@
     </row>
     <row r="341" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="B341" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C341" s="2" t="s">
         <v>7</v>
@@ -10671,10 +10701,10 @@
     </row>
     <row r="342" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B342" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C342" s="2" t="s">
         <v>7</v>
@@ -10685,10 +10715,10 @@
     </row>
     <row r="343" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B343" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C343" s="2" t="s">
         <v>7</v>
@@ -10699,10 +10729,10 @@
     </row>
     <row r="344" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="B344" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="C344" s="2" t="s">
         <v>7</v>
@@ -10713,10 +10743,10 @@
     </row>
     <row r="345" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B345" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="C345" s="2" t="s">
         <v>7</v>
@@ -10727,10 +10757,10 @@
     </row>
     <row r="346" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B346" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C346" s="2" t="s">
         <v>7</v>
@@ -10741,10 +10771,10 @@
     </row>
     <row r="347" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="B347" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="C347" s="2" t="s">
         <v>7</v>
@@ -10755,10 +10785,10 @@
     </row>
     <row r="348" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="B348" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="C348" s="2" t="s">
         <v>7</v>
@@ -10769,10 +10799,10 @@
     </row>
     <row r="349" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="B349" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C349" s="2" t="s">
         <v>7</v>
@@ -10783,10 +10813,10 @@
     </row>
     <row r="350" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B350" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C350" s="2" t="s">
         <v>7</v>
@@ -10797,10 +10827,10 @@
     </row>
     <row r="351" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B351" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="C351" s="2" t="s">
         <v>7</v>
@@ -10811,10 +10841,10 @@
     </row>
     <row r="352" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B352" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="C352" s="2" t="s">
         <v>7</v>
@@ -10825,10 +10855,10 @@
     </row>
     <row r="353" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="B353" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="C353" s="2" t="s">
         <v>7</v>
@@ -10839,10 +10869,10 @@
     </row>
     <row r="354" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="B354" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="C354" s="2" t="s">
         <v>7</v>
@@ -10853,10 +10883,10 @@
     </row>
     <row r="355" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B355" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C355" s="2" t="s">
         <v>7</v>
@@ -10867,10 +10897,10 @@
     </row>
     <row r="356" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="B356" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C356" s="2" t="s">
         <v>7</v>
@@ -10881,10 +10911,10 @@
     </row>
     <row r="357" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B357" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="C357" s="2" t="s">
         <v>7</v>
@@ -10895,10 +10925,10 @@
     </row>
     <row r="358" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="B358" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="C358" s="2" t="s">
         <v>7</v>
@@ -10909,10 +10939,10 @@
     </row>
     <row r="359" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="B359" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C359" s="2" t="s">
         <v>7</v>
@@ -10923,10 +10953,10 @@
     </row>
     <row r="360" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="B360" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="C360" s="2" t="s">
         <v>7</v>
@@ -10937,10 +10967,10 @@
     </row>
     <row r="361" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="B361" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="C361" s="2" t="s">
         <v>7</v>
@@ -10951,10 +10981,10 @@
     </row>
     <row r="362" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="B362" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="C362" s="2" t="s">
         <v>7</v>
@@ -10965,10 +10995,10 @@
     </row>
     <row r="363" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="B363" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="C363" s="2" t="s">
         <v>7</v>
@@ -10979,10 +11009,10 @@
     </row>
     <row r="364" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="B364" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="C364" s="2" t="s">
         <v>7</v>
@@ -10993,10 +11023,10 @@
     </row>
     <row r="365" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="B365" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="C365" s="2" t="s">
         <v>7</v>
@@ -11007,10 +11037,10 @@
     </row>
     <row r="366" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="B366" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="C366" s="2" t="s">
         <v>7</v>
@@ -11021,10 +11051,10 @@
     </row>
     <row r="367" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="B367" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="C367" s="2" t="s">
         <v>7</v>
@@ -11035,10 +11065,10 @@
     </row>
     <row r="368" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="B368" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="C368" s="2" t="s">
         <v>7</v>
@@ -11049,10 +11079,10 @@
     </row>
     <row r="369" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="B369" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="C369" s="2" t="s">
         <v>7</v>
@@ -11063,10 +11093,10 @@
     </row>
     <row r="370" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="B370" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="C370" s="2" t="s">
         <v>7</v>
@@ -11077,10 +11107,10 @@
     </row>
     <row r="371" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="B371" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="C371" s="2" t="s">
         <v>7</v>
@@ -11091,10 +11121,10 @@
     </row>
     <row r="372" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="B372" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="C372" s="2" t="s">
         <v>7</v>
@@ -11105,10 +11135,10 @@
     </row>
     <row r="373" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="B373" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="C373" s="2" t="s">
         <v>7</v>
@@ -11119,10 +11149,10 @@
     </row>
     <row r="374" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="B374" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="C374" s="2" t="s">
         <v>7</v>
@@ -11133,10 +11163,10 @@
     </row>
     <row r="375" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="B375" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="C375" s="2" t="s">
         <v>7</v>
@@ -11147,10 +11177,10 @@
     </row>
     <row r="376" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="B376" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="C376" s="2" t="s">
         <v>7</v>
@@ -11161,10 +11191,10 @@
     </row>
     <row r="377" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="B377" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="C377" s="2" t="s">
         <v>7</v>
@@ -11175,10 +11205,10 @@
     </row>
     <row r="378" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="B378" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="C378" s="2" t="s">
         <v>7</v>
@@ -11189,10 +11219,10 @@
     </row>
     <row r="379" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="B379" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="C379" s="2" t="s">
         <v>7</v>
@@ -11203,10 +11233,10 @@
     </row>
     <row r="380" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="B380" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="C380" s="2" t="s">
         <v>7</v>
@@ -11217,10 +11247,10 @@
     </row>
     <row r="381" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="B381" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="C381" s="2" t="s">
         <v>7</v>
@@ -11231,10 +11261,10 @@
     </row>
     <row r="382" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="B382" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="C382" s="2" t="s">
         <v>7</v>
@@ -11245,10 +11275,10 @@
     </row>
     <row r="383" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="B383" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="C383" s="2" t="s">
         <v>7</v>
@@ -11259,10 +11289,10 @@
     </row>
     <row r="384" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="B384" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="C384" s="2" t="s">
         <v>7</v>
@@ -11273,10 +11303,10 @@
     </row>
     <row r="385" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="B385" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C385" s="2" t="s">
         <v>7</v>
@@ -11287,10 +11317,10 @@
     </row>
     <row r="386" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="B386" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="C386" s="2" t="s">
         <v>7</v>
@@ -11301,10 +11331,10 @@
     </row>
     <row r="387" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="B387" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="C387" s="2" t="s">
         <v>7</v>
@@ -11315,10 +11345,10 @@
     </row>
     <row r="388" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="B388" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="C388" s="2" t="s">
         <v>7</v>
@@ -11329,10 +11359,10 @@
     </row>
     <row r="389" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="B389" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="C389" s="2" t="s">
         <v>7</v>
@@ -11343,10 +11373,10 @@
     </row>
     <row r="390" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="B390" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="C390" s="2" t="s">
         <v>7</v>
@@ -11357,10 +11387,10 @@
     </row>
     <row r="391" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="B391" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="C391" s="2" t="s">
         <v>7</v>
@@ -11371,10 +11401,10 @@
     </row>
     <row r="392" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="B392" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="C392" s="2" t="s">
         <v>7</v>
@@ -11385,10 +11415,10 @@
     </row>
     <row r="393" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="B393" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="C393" s="2" t="s">
         <v>7</v>
@@ -11399,10 +11429,10 @@
     </row>
     <row r="394" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="B394" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="C394" s="2" t="s">
         <v>7</v>
@@ -11413,10 +11443,10 @@
     </row>
     <row r="395" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="B395" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="C395" s="2" t="s">
         <v>7</v>
@@ -11427,10 +11457,10 @@
     </row>
     <row r="396" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="B396" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="C396" s="2" t="s">
         <v>7</v>
@@ -11441,10 +11471,10 @@
     </row>
     <row r="397" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="B397" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="C397" s="2" t="s">
         <v>7</v>
@@ -11455,10 +11485,10 @@
     </row>
     <row r="398" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="B398" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="C398" s="2" t="s">
         <v>7</v>
@@ -11469,10 +11499,10 @@
     </row>
     <row r="399" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="B399" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="C399" s="2" t="s">
         <v>7</v>
@@ -11483,10 +11513,10 @@
     </row>
     <row r="400" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="B400" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="C400" s="2" t="s">
         <v>7</v>
@@ -11497,10 +11527,10 @@
     </row>
     <row r="401" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="B401" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="C401" s="2" t="s">
         <v>7</v>
@@ -11511,10 +11541,10 @@
     </row>
     <row r="402" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="B402" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="C402" s="2" t="s">
         <v>7</v>
@@ -11525,10 +11555,10 @@
     </row>
     <row r="403" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="B403" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="C403" s="2" t="s">
         <v>7</v>
@@ -11539,10 +11569,10 @@
     </row>
     <row r="404" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="B404" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="C404" s="2" t="s">
         <v>7</v>
@@ -11553,10 +11583,10 @@
     </row>
     <row r="405" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="B405" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="C405" s="2" t="s">
         <v>7</v>
@@ -11567,10 +11597,10 @@
     </row>
     <row r="406" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="B406" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="C406" s="2" t="s">
         <v>7</v>
@@ -11581,10 +11611,10 @@
     </row>
     <row r="407" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="B407" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="C407" s="2" t="s">
         <v>7</v>
@@ -11595,10 +11625,10 @@
     </row>
     <row r="408" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="B408" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="C408" s="2" t="s">
         <v>7</v>
@@ -11609,10 +11639,10 @@
     </row>
     <row r="409" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="B409" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="C409" s="2" t="s">
         <v>7</v>
@@ -11623,10 +11653,10 @@
     </row>
     <row r="410" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="B410" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="C410" s="2" t="s">
         <v>7</v>
@@ -11637,10 +11667,10 @@
     </row>
     <row r="411" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="B411" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="C411" s="2" t="s">
         <v>7</v>
@@ -11651,10 +11681,10 @@
     </row>
     <row r="412" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="B412" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="C412" s="2" t="s">
         <v>7</v>
@@ -11665,10 +11695,10 @@
     </row>
     <row r="413" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="B413" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="C413" s="2" t="s">
         <v>7</v>
@@ -11679,10 +11709,10 @@
     </row>
     <row r="414" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="B414" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="C414" s="2" t="s">
         <v>7</v>
@@ -11693,10 +11723,10 @@
     </row>
     <row r="415" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="B415" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="C415" s="2" t="s">
         <v>7</v>
@@ -11707,10 +11737,10 @@
     </row>
     <row r="416" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="B416" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="C416" s="2" t="s">
         <v>7</v>
@@ -11721,10 +11751,10 @@
     </row>
     <row r="417" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="B417" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="C417" s="2" t="s">
         <v>7</v>
@@ -11735,10 +11765,10 @@
     </row>
     <row r="418" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="B418" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="C418" s="2" t="s">
         <v>7</v>
@@ -11749,10 +11779,10 @@
     </row>
     <row r="419" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="B419" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="C419" s="2" t="s">
         <v>7</v>
@@ -11763,10 +11793,10 @@
     </row>
     <row r="420" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="B420" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="C420" s="2" t="s">
         <v>7</v>
@@ -11777,10 +11807,10 @@
     </row>
     <row r="421" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="B421" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="C421" s="2" t="s">
         <v>7</v>
@@ -11791,10 +11821,10 @@
     </row>
     <row r="422" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="B422" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="C422" s="2" t="s">
         <v>7</v>
@@ -11805,10 +11835,10 @@
     </row>
     <row r="423" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="B423" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="C423" s="2" t="s">
         <v>7</v>
@@ -11819,10 +11849,10 @@
     </row>
     <row r="424" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="B424" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="C424" s="2" t="s">
         <v>7</v>
@@ -11833,10 +11863,10 @@
     </row>
     <row r="425" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="B425" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="C425" s="2" t="s">
         <v>7</v>
@@ -11847,10 +11877,10 @@
     </row>
     <row r="426" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="B426" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="C426" s="2" t="s">
         <v>7</v>
@@ -11861,10 +11891,10 @@
     </row>
     <row r="427" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="B427" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="C427" s="2" t="s">
         <v>7</v>
@@ -11875,10 +11905,10 @@
     </row>
     <row r="428" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="B428" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="C428" s="2" t="s">
         <v>7</v>
@@ -11889,10 +11919,10 @@
     </row>
     <row r="429" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="B429" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="C429" s="2" t="s">
         <v>7</v>
@@ -11903,10 +11933,10 @@
     </row>
     <row r="430" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="B430" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="C430" s="2" t="s">
         <v>7</v>
@@ -11917,10 +11947,10 @@
     </row>
     <row r="431" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="B431" t="s">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="C431" s="2" t="s">
         <v>7</v>
@@ -11931,10 +11961,10 @@
     </row>
     <row r="432" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="B432" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="C432" s="2" t="s">
         <v>7</v>
@@ -11945,10 +11975,10 @@
     </row>
     <row r="433" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="B433" t="s">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="C433" s="2" t="s">
         <v>7</v>
@@ -11959,10 +11989,10 @@
     </row>
     <row r="434" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="B434" t="s">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="C434" s="2" t="s">
         <v>7</v>
@@ -11973,10 +12003,10 @@
     </row>
     <row r="435" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="B435" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="C435" s="2" t="s">
         <v>7</v>
@@ -11987,10 +12017,10 @@
     </row>
     <row r="436" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="B436" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="C436" s="2" t="s">
         <v>7</v>
@@ -12001,10 +12031,10 @@
     </row>
     <row r="437" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="B437" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="C437" s="2" t="s">
         <v>7</v>
@@ -12015,10 +12045,10 @@
     </row>
     <row r="438" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="B438" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="C438" s="2" t="s">
         <v>7</v>
@@ -12029,10 +12059,10 @@
     </row>
     <row r="439" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="B439" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="C439" s="2" t="s">
         <v>7</v>
@@ -12043,10 +12073,10 @@
     </row>
     <row r="440" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="B440" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="C440" s="2" t="s">
         <v>7</v>
@@ -12057,10 +12087,10 @@
     </row>
     <row r="441" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="B441" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="C441" s="2" t="s">
         <v>7</v>
@@ -12071,10 +12101,10 @@
     </row>
     <row r="442" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="B442" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="C442" s="2" t="s">
         <v>7</v>
@@ -12085,10 +12115,10 @@
     </row>
     <row r="443" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="B443" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="C443" s="2" t="s">
         <v>7</v>
@@ -12099,10 +12129,10 @@
     </row>
     <row r="444" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="B444" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="C444" s="2" t="s">
         <v>7</v>
@@ -12113,10 +12143,10 @@
     </row>
     <row r="445" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="B445" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="C445" s="2" t="s">
         <v>7</v>
@@ -12127,10 +12157,10 @@
     </row>
     <row r="446" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="B446" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="C446" s="2" t="s">
         <v>7</v>
@@ -12141,10 +12171,10 @@
     </row>
     <row r="447" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="B447" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="C447" s="2" t="s">
         <v>7</v>
@@ -12155,10 +12185,10 @@
     </row>
     <row r="448" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="B448" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="C448" s="2" t="s">
         <v>7</v>
@@ -12169,10 +12199,10 @@
     </row>
     <row r="449" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="B449" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="C449" s="2" t="s">
         <v>7</v>
@@ -12183,10 +12213,10 @@
     </row>
     <row r="450" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="B450" t="s">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="C450" s="2" t="s">
         <v>7</v>
@@ -12197,10 +12227,10 @@
     </row>
     <row r="451" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="B451" t="s">
-        <v>845</v>
+        <v>849</v>
       </c>
       <c r="C451" s="2" t="s">
         <v>7</v>
@@ -12211,10 +12241,10 @@
     </row>
     <row r="452" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="B452" t="s">
-        <v>847</v>
+        <v>851</v>
       </c>
       <c r="C452" s="2" t="s">
         <v>7</v>
@@ -12225,10 +12255,10 @@
     </row>
     <row r="453" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="B453" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="C453" s="2" t="s">
         <v>7</v>
@@ -12239,10 +12269,10 @@
     </row>
     <row r="454" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>850</v>
+        <v>854</v>
       </c>
       <c r="B454" t="s">
-        <v>851</v>
+        <v>855</v>
       </c>
       <c r="C454" s="2" t="s">
         <v>7</v>
@@ -12253,10 +12283,10 @@
     </row>
     <row r="455" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>852</v>
+        <v>856</v>
       </c>
       <c r="B455" t="s">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="C455" s="2" t="s">
         <v>7</v>
@@ -12267,10 +12297,10 @@
     </row>
     <row r="456" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>854</v>
+        <v>858</v>
       </c>
       <c r="B456" t="s">
-        <v>855</v>
+        <v>859</v>
       </c>
       <c r="C456" s="2" t="s">
         <v>7</v>
@@ -12281,10 +12311,10 @@
     </row>
     <row r="457" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="B457" t="s">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="C457" s="2" t="s">
         <v>7</v>
@@ -12295,10 +12325,10 @@
     </row>
     <row r="458" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="B458" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="C458" s="2" t="s">
         <v>7</v>
@@ -12309,10 +12339,10 @@
     </row>
     <row r="459" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="B459" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="C459" s="2" t="s">
         <v>7</v>
@@ -12323,10 +12353,10 @@
     </row>
     <row r="460" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="B460" t="s">
-        <v>863</v>
+        <v>867</v>
       </c>
       <c r="C460" s="2" t="s">
         <v>7</v>
@@ -12337,10 +12367,10 @@
     </row>
     <row r="461" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="B461" t="s">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="C461" s="2" t="s">
         <v>7</v>
@@ -12351,10 +12381,10 @@
     </row>
     <row r="462" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
-        <v>866</v>
+        <v>870</v>
       </c>
       <c r="B462" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="C462" s="2" t="s">
         <v>7</v>
@@ -12365,10 +12395,10 @@
     </row>
     <row r="463" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="B463" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="C463" s="2" t="s">
         <v>7</v>
@@ -12379,10 +12409,10 @@
     </row>
     <row r="464" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="B464" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="C464" s="2" t="s">
         <v>7</v>
@@ -12393,10 +12423,10 @@
     </row>
     <row r="465" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>872</v>
+        <v>878</v>
       </c>
       <c r="B465" t="s">
-        <v>873</v>
+        <v>879</v>
       </c>
       <c r="C465" s="2" t="s">
         <v>7</v>
@@ -12407,10 +12437,10 @@
     </row>
     <row r="466" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
-        <v>874</v>
+        <v>880</v>
       </c>
       <c r="B466" t="s">
-        <v>875</v>
+        <v>881</v>
       </c>
       <c r="C466" s="2" t="s">
         <v>7</v>
@@ -12421,10 +12451,10 @@
     </row>
     <row r="467" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>876</v>
+        <v>882</v>
       </c>
       <c r="B467" t="s">
-        <v>877</v>
+        <v>883</v>
       </c>
       <c r="C467" s="2" t="s">
         <v>7</v>
@@ -12435,10 +12465,10 @@
     </row>
     <row r="468" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>878</v>
+        <v>884</v>
       </c>
       <c r="B468" t="s">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="C468" s="2" t="s">
         <v>7</v>
@@ -12449,10 +12479,10 @@
     </row>
     <row r="469" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>880</v>
+        <v>886</v>
       </c>
       <c r="B469" t="s">
-        <v>881</v>
+        <v>887</v>
       </c>
       <c r="C469" s="2" t="s">
         <v>7</v>
@@ -12463,10 +12493,10 @@
     </row>
     <row r="470" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>882</v>
+        <v>888</v>
       </c>
       <c r="B470" t="s">
-        <v>883</v>
+        <v>889</v>
       </c>
       <c r="C470" s="2" t="s">
         <v>7</v>
@@ -12477,10 +12507,10 @@
     </row>
     <row r="471" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
-        <v>884</v>
+        <v>890</v>
       </c>
       <c r="B471" t="s">
-        <v>885</v>
+        <v>891</v>
       </c>
       <c r="C471" s="2" t="s">
         <v>7</v>
@@ -12491,10 +12521,10 @@
     </row>
     <row r="472" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>886</v>
+        <v>892</v>
       </c>
       <c r="B472" t="s">
-        <v>887</v>
+        <v>893</v>
       </c>
       <c r="C472" s="2" t="s">
         <v>7</v>
@@ -12505,10 +12535,10 @@
     </row>
     <row r="473" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>888</v>
+        <v>894</v>
       </c>
       <c r="B473" t="s">
-        <v>889</v>
+        <v>895</v>
       </c>
       <c r="C473" s="2" t="s">
         <v>7</v>
@@ -12519,10 +12549,10 @@
     </row>
     <row r="474" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
-        <v>890</v>
+        <v>896</v>
       </c>
       <c r="B474" t="s">
-        <v>891</v>
+        <v>897</v>
       </c>
       <c r="C474" s="2" t="s">
         <v>7</v>
@@ -12533,10 +12563,10 @@
     </row>
     <row r="475" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
-        <v>892</v>
+        <v>898</v>
       </c>
       <c r="B475" t="s">
-        <v>893</v>
+        <v>899</v>
       </c>
       <c r="C475" s="2" t="s">
         <v>7</v>
@@ -12547,10 +12577,10 @@
     </row>
     <row r="476" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>894</v>
+        <v>900</v>
       </c>
       <c r="B476" t="s">
-        <v>895</v>
+        <v>901</v>
       </c>
       <c r="C476" s="2" t="s">
         <v>7</v>
@@ -12561,10 +12591,10 @@
     </row>
     <row r="477" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>896</v>
+        <v>902</v>
       </c>
       <c r="B477" t="s">
-        <v>897</v>
+        <v>903</v>
       </c>
       <c r="C477" s="2" t="s">
         <v>7</v>
@@ -12575,10 +12605,10 @@
     </row>
     <row r="478" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>898</v>
+        <v>904</v>
       </c>
       <c r="B478" t="s">
-        <v>899</v>
+        <v>905</v>
       </c>
       <c r="C478" s="2" t="s">
         <v>7</v>
@@ -12589,10 +12619,10 @@
     </row>
     <row r="479" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>900</v>
+        <v>906</v>
       </c>
       <c r="B479" t="s">
-        <v>901</v>
+        <v>907</v>
       </c>
       <c r="C479" s="2" t="s">
         <v>7</v>
@@ -12603,10 +12633,10 @@
     </row>
     <row r="480" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>902</v>
+        <v>908</v>
       </c>
       <c r="B480" t="s">
-        <v>903</v>
+        <v>909</v>
       </c>
       <c r="C480" s="2" t="s">
         <v>7</v>
@@ -12617,10 +12647,10 @@
     </row>
     <row r="481" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
-        <v>904</v>
+        <v>910</v>
       </c>
       <c r="B481" t="s">
-        <v>905</v>
+        <v>911</v>
       </c>
       <c r="C481" s="2" t="s">
         <v>7</v>
@@ -12631,10 +12661,10 @@
     </row>
     <row r="482" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
-        <v>906</v>
+        <v>912</v>
       </c>
       <c r="B482" t="s">
-        <v>907</v>
+        <v>913</v>
       </c>
       <c r="C482" s="2" t="s">
         <v>7</v>
@@ -12645,10 +12675,10 @@
     </row>
     <row r="483" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
-        <v>908</v>
+        <v>914</v>
       </c>
       <c r="B483" t="s">
-        <v>909</v>
+        <v>915</v>
       </c>
       <c r="C483" s="2" t="s">
         <v>7</v>
@@ -12659,10 +12689,10 @@
     </row>
     <row r="484" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
-        <v>910</v>
+        <v>916</v>
       </c>
       <c r="B484" t="s">
-        <v>911</v>
+        <v>917</v>
       </c>
       <c r="C484" s="2" t="s">
         <v>7</v>
@@ -12673,10 +12703,10 @@
     </row>
     <row r="485" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>912</v>
+        <v>918</v>
       </c>
       <c r="B485" t="s">
-        <v>913</v>
+        <v>919</v>
       </c>
       <c r="C485" s="2" t="s">
         <v>7</v>
@@ -12687,10 +12717,10 @@
     </row>
     <row r="486" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>914</v>
+        <v>920</v>
       </c>
       <c r="B486" t="s">
-        <v>915</v>
+        <v>921</v>
       </c>
       <c r="C486" s="2" t="s">
         <v>7</v>
@@ -12701,10 +12731,10 @@
     </row>
     <row r="487" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
-        <v>916</v>
+        <v>922</v>
       </c>
       <c r="B487" t="s">
-        <v>917</v>
+        <v>923</v>
       </c>
       <c r="C487" s="2" t="s">
         <v>7</v>
@@ -12715,10 +12745,10 @@
     </row>
     <row r="488" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
-        <v>918</v>
+        <v>924</v>
       </c>
       <c r="B488" t="s">
-        <v>919</v>
+        <v>925</v>
       </c>
       <c r="C488" s="2" t="s">
         <v>7</v>
@@ -12729,10 +12759,10 @@
     </row>
     <row r="489" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
-        <v>920</v>
+        <v>926</v>
       </c>
       <c r="B489" t="s">
-        <v>921</v>
+        <v>927</v>
       </c>
       <c r="C489" s="2" t="s">
         <v>7</v>
@@ -12743,10 +12773,10 @@
     </row>
     <row r="490" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
-        <v>922</v>
+        <v>928</v>
       </c>
       <c r="B490" t="s">
-        <v>923</v>
+        <v>929</v>
       </c>
       <c r="C490" s="2" t="s">
         <v>7</v>
@@ -12757,10 +12787,10 @@
     </row>
     <row r="491" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>926</v>
+        <v>932</v>
       </c>
       <c r="B491" t="s">
-        <v>927</v>
+        <v>933</v>
       </c>
       <c r="C491" s="2" t="s">
         <v>7</v>
@@ -12771,10 +12801,10 @@
     </row>
     <row r="492" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
-        <v>928</v>
+        <v>934</v>
       </c>
       <c r="B492" t="s">
-        <v>929</v>
+        <v>935</v>
       </c>
       <c r="C492" s="2" t="s">
         <v>7</v>
@@ -12785,10 +12815,10 @@
     </row>
     <row r="493" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>930</v>
+        <v>936</v>
       </c>
       <c r="B493" t="s">
-        <v>931</v>
+        <v>937</v>
       </c>
       <c r="C493" s="2" t="s">
         <v>7</v>
@@ -12799,10 +12829,10 @@
     </row>
     <row r="494" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
-        <v>932</v>
+        <v>938</v>
       </c>
       <c r="B494" t="s">
-        <v>933</v>
+        <v>939</v>
       </c>
       <c r="C494" s="2" t="s">
         <v>7</v>
@@ -12813,10 +12843,10 @@
     </row>
     <row r="495" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
-        <v>934</v>
+        <v>940</v>
       </c>
       <c r="B495" t="s">
-        <v>935</v>
+        <v>941</v>
       </c>
       <c r="C495" s="2" t="s">
         <v>7</v>
@@ -12827,10 +12857,10 @@
     </row>
     <row r="496" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
-        <v>936</v>
+        <v>942</v>
       </c>
       <c r="B496" t="s">
-        <v>937</v>
+        <v>943</v>
       </c>
       <c r="C496" s="2" t="s">
         <v>7</v>
@@ -12841,10 +12871,10 @@
     </row>
     <row r="497" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
-        <v>938</v>
+        <v>944</v>
       </c>
       <c r="B497" t="s">
-        <v>939</v>
+        <v>945</v>
       </c>
       <c r="C497" s="2" t="s">
         <v>7</v>
@@ -12855,10 +12885,10 @@
     </row>
     <row r="498" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>940</v>
+        <v>946</v>
       </c>
       <c r="B498" t="s">
-        <v>941</v>
+        <v>947</v>
       </c>
       <c r="C498" s="2" t="s">
         <v>7</v>
@@ -12869,10 +12899,10 @@
     </row>
     <row r="499" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="B499" t="s">
-        <v>945</v>
+        <v>951</v>
       </c>
       <c r="C499" s="2" t="s">
         <v>7</v>
@@ -12883,10 +12913,10 @@
     </row>
     <row r="500" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
-        <v>946</v>
+        <v>952</v>
       </c>
       <c r="B500" t="s">
-        <v>947</v>
+        <v>953</v>
       </c>
       <c r="C500" s="2" t="s">
         <v>7</v>
@@ -12897,10 +12927,10 @@
     </row>
     <row r="501" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
-        <v>948</v>
+        <v>954</v>
       </c>
       <c r="B501" t="s">
-        <v>949</v>
+        <v>955</v>
       </c>
       <c r="C501" s="2" t="s">
         <v>7</v>
@@ -12911,10 +12941,10 @@
     </row>
     <row r="502" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
-        <v>950</v>
+        <v>956</v>
       </c>
       <c r="B502" t="s">
-        <v>951</v>
+        <v>957</v>
       </c>
       <c r="C502" s="2" t="s">
         <v>7</v>
@@ -12925,10 +12955,10 @@
     </row>
     <row r="503" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
-        <v>952</v>
+        <v>960</v>
       </c>
       <c r="B503" t="s">
-        <v>953</v>
+        <v>961</v>
       </c>
       <c r="C503" s="2" t="s">
         <v>7</v>
@@ -12939,10 +12969,10 @@
     </row>
     <row r="504" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
-        <v>954</v>
+        <v>962</v>
       </c>
       <c r="B504" t="s">
-        <v>955</v>
+        <v>963</v>
       </c>
       <c r="C504" s="2" t="s">
         <v>7</v>
@@ -12953,10 +12983,10 @@
     </row>
     <row r="505" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
-        <v>956</v>
+        <v>964</v>
       </c>
       <c r="B505" t="s">
-        <v>957</v>
+        <v>965</v>
       </c>
       <c r="C505" s="2" t="s">
         <v>7</v>
@@ -12967,10 +12997,10 @@
     </row>
     <row r="506" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
-        <v>958</v>
+        <v>966</v>
       </c>
       <c r="B506" t="s">
-        <v>959</v>
+        <v>967</v>
       </c>
       <c r="C506" s="2" t="s">
         <v>7</v>
@@ -12981,10 +13011,10 @@
     </row>
     <row r="507" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
-        <v>960</v>
+        <v>968</v>
       </c>
       <c r="B507" t="s">
-        <v>961</v>
+        <v>969</v>
       </c>
       <c r="C507" s="2" t="s">
         <v>7</v>
@@ -12995,10 +13025,10 @@
     </row>
     <row r="508" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
-        <v>962</v>
+        <v>970</v>
       </c>
       <c r="B508" t="s">
-        <v>963</v>
+        <v>971</v>
       </c>
       <c r="C508" s="2" t="s">
         <v>7</v>
@@ -13009,10 +13039,10 @@
     </row>
     <row r="509" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
-        <v>964</v>
+        <v>972</v>
       </c>
       <c r="B509" t="s">
-        <v>965</v>
+        <v>973</v>
       </c>
       <c r="C509" s="2" t="s">
         <v>7</v>
@@ -13023,10 +13053,10 @@
     </row>
     <row r="510" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
-        <v>966</v>
+        <v>974</v>
       </c>
       <c r="B510" t="s">
-        <v>967</v>
+        <v>975</v>
       </c>
       <c r="C510" s="2" t="s">
         <v>7</v>
@@ -13037,10 +13067,10 @@
     </row>
     <row r="511" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
-        <v>968</v>
+        <v>976</v>
       </c>
       <c r="B511" t="s">
-        <v>969</v>
+        <v>977</v>
       </c>
       <c r="C511" s="2" t="s">
         <v>7</v>
@@ -13051,10 +13081,10 @@
     </row>
     <row r="512" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
-        <v>970</v>
+        <v>978</v>
       </c>
       <c r="B512" t="s">
-        <v>971</v>
+        <v>979</v>
       </c>
       <c r="C512" s="2" t="s">
         <v>7</v>
@@ -13065,10 +13095,10 @@
     </row>
     <row r="513" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
-        <v>972</v>
+        <v>980</v>
       </c>
       <c r="B513" t="s">
-        <v>973</v>
+        <v>981</v>
       </c>
       <c r="C513" s="2" t="s">
         <v>7</v>
@@ -13079,10 +13109,10 @@
     </row>
     <row r="514" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
-        <v>974</v>
+        <v>982</v>
       </c>
       <c r="B514" t="s">
-        <v>975</v>
+        <v>983</v>
       </c>
       <c r="C514" s="2" t="s">
         <v>7</v>
@@ -13093,10 +13123,10 @@
     </row>
     <row r="515" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
-        <v>976</v>
+        <v>984</v>
       </c>
       <c r="B515" t="s">
-        <v>977</v>
+        <v>985</v>
       </c>
       <c r="C515" s="2" t="s">
         <v>7</v>
@@ -13107,10 +13137,10 @@
     </row>
     <row r="516" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
-        <v>978</v>
+        <v>986</v>
       </c>
       <c r="B516" t="s">
-        <v>979</v>
+        <v>987</v>
       </c>
       <c r="C516" s="2" t="s">
         <v>7</v>
@@ -13121,10 +13151,10 @@
     </row>
     <row r="517" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
-        <v>980</v>
+        <v>988</v>
       </c>
       <c r="B517" t="s">
-        <v>981</v>
+        <v>989</v>
       </c>
       <c r="C517" s="2" t="s">
         <v>7</v>
@@ -13135,10 +13165,10 @@
     </row>
     <row r="518" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
-        <v>982</v>
+        <v>990</v>
       </c>
       <c r="B518" t="s">
-        <v>983</v>
+        <v>991</v>
       </c>
       <c r="C518" s="2" t="s">
         <v>7</v>
@@ -13149,10 +13179,10 @@
     </row>
     <row r="519" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
-        <v>984</v>
+        <v>992</v>
       </c>
       <c r="B519" t="s">
-        <v>985</v>
+        <v>993</v>
       </c>
       <c r="C519" s="2" t="s">
         <v>7</v>
@@ -13163,10 +13193,10 @@
     </row>
     <row r="520" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
-        <v>988</v>
+        <v>996</v>
       </c>
       <c r="B520" t="s">
-        <v>989</v>
+        <v>997</v>
       </c>
       <c r="C520" s="2" t="s">
         <v>7</v>
@@ -13177,10 +13207,10 @@
     </row>
     <row r="521" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
-        <v>990</v>
+        <v>998</v>
       </c>
       <c r="B521" t="s">
-        <v>991</v>
+        <v>999</v>
       </c>
       <c r="C521" s="2" t="s">
         <v>7</v>
@@ -13191,10 +13221,10 @@
     </row>
     <row r="522" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
-        <v>992</v>
+        <v>1000</v>
       </c>
       <c r="B522" t="s">
-        <v>993</v>
+        <v>1001</v>
       </c>
       <c r="C522" s="2" t="s">
         <v>7</v>
@@ -13205,10 +13235,10 @@
     </row>
     <row r="523" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
-        <v>994</v>
+        <v>1002</v>
       </c>
       <c r="B523" t="s">
-        <v>995</v>
+        <v>1003</v>
       </c>
       <c r="C523" s="2" t="s">
         <v>7</v>
@@ -13219,10 +13249,10 @@
     </row>
     <row r="524" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
-        <v>996</v>
+        <v>1004</v>
       </c>
       <c r="B524" t="s">
-        <v>997</v>
+        <v>1005</v>
       </c>
       <c r="C524" s="2" t="s">
         <v>7</v>
@@ -13233,10 +13263,10 @@
     </row>
     <row r="525" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
-        <v>998</v>
+        <v>1006</v>
       </c>
       <c r="B525" t="s">
-        <v>999</v>
+        <v>1007</v>
       </c>
       <c r="C525" s="2" t="s">
         <v>7</v>
@@ -13247,10 +13277,10 @@
     </row>
     <row r="526" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
-        <v>1002</v>
+        <v>1010</v>
       </c>
       <c r="B526" t="s">
-        <v>1003</v>
+        <v>1011</v>
       </c>
       <c r="C526" s="2" t="s">
         <v>7</v>
@@ -13261,10 +13291,10 @@
     </row>
     <row r="527" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="B527" t="s">
-        <v>1005</v>
+        <v>1013</v>
       </c>
       <c r="C527" s="2" t="s">
         <v>7</v>
@@ -13275,10 +13305,10 @@
     </row>
     <row r="528" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
-        <v>1006</v>
+        <v>1014</v>
       </c>
       <c r="B528" t="s">
-        <v>1007</v>
+        <v>1015</v>
       </c>
       <c r="C528" s="2" t="s">
         <v>7</v>
@@ -13289,10 +13319,10 @@
     </row>
     <row r="529" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
-        <v>1008</v>
+        <v>1016</v>
       </c>
       <c r="B529" t="s">
-        <v>1009</v>
+        <v>1017</v>
       </c>
       <c r="C529" s="2" t="s">
         <v>7</v>
@@ -13303,10 +13333,10 @@
     </row>
     <row r="530" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
-        <v>1010</v>
+        <v>1018</v>
       </c>
       <c r="B530" t="s">
-        <v>1011</v>
+        <v>1019</v>
       </c>
       <c r="C530" s="2" t="s">
         <v>7</v>
@@ -13317,10 +13347,10 @@
     </row>
     <row r="531" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
-        <v>1012</v>
+        <v>1020</v>
       </c>
       <c r="B531" t="s">
-        <v>1013</v>
+        <v>1021</v>
       </c>
       <c r="C531" s="2" t="s">
         <v>7</v>
@@ -13331,10 +13361,10 @@
     </row>
     <row r="532" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
-        <v>1014</v>
+        <v>1022</v>
       </c>
       <c r="B532" t="s">
-        <v>1015</v>
+        <v>1023</v>
       </c>
       <c r="C532" s="2" t="s">
         <v>7</v>
@@ -13345,10 +13375,10 @@
     </row>
     <row r="533" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
-        <v>1016</v>
+        <v>1024</v>
       </c>
       <c r="B533" t="s">
-        <v>1017</v>
+        <v>1025</v>
       </c>
       <c r="C533" s="2" t="s">
         <v>7</v>
@@ -13359,10 +13389,10 @@
     </row>
     <row r="534" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
-        <v>1018</v>
+        <v>1026</v>
       </c>
       <c r="B534" t="s">
-        <v>1019</v>
+        <v>1027</v>
       </c>
       <c r="C534" s="2" t="s">
         <v>7</v>
@@ -13373,10 +13403,10 @@
     </row>
     <row r="535" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
-        <v>1020</v>
+        <v>1028</v>
       </c>
       <c r="B535" t="s">
-        <v>1021</v>
+        <v>1029</v>
       </c>
       <c r="C535" s="2" t="s">
         <v>7</v>
@@ -13387,10 +13417,10 @@
     </row>
     <row r="536" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
-        <v>1022</v>
+        <v>1030</v>
       </c>
       <c r="B536" t="s">
-        <v>1023</v>
+        <v>1031</v>
       </c>
       <c r="C536" s="2" t="s">
         <v>7</v>
@@ -13401,10 +13431,10 @@
     </row>
     <row r="537" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
-        <v>1024</v>
+        <v>1032</v>
       </c>
       <c r="B537" t="s">
-        <v>1025</v>
+        <v>1033</v>
       </c>
       <c r="C537" s="2" t="s">
         <v>7</v>
@@ -13415,10 +13445,10 @@
     </row>
     <row r="538" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
-        <v>1026</v>
+        <v>1034</v>
       </c>
       <c r="B538" t="s">
-        <v>1027</v>
+        <v>1035</v>
       </c>
       <c r="C538" s="2" t="s">
         <v>7</v>
@@ -13429,10 +13459,10 @@
     </row>
     <row r="539" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
-        <v>1030</v>
+        <v>1038</v>
       </c>
       <c r="B539" t="s">
-        <v>1031</v>
+        <v>1039</v>
       </c>
       <c r="C539" s="2" t="s">
         <v>7</v>
@@ -13443,10 +13473,10 @@
     </row>
     <row r="540" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
-        <v>1032</v>
+        <v>1040</v>
       </c>
       <c r="B540" t="s">
-        <v>1033</v>
+        <v>1041</v>
       </c>
       <c r="C540" s="2" t="s">
         <v>7</v>
@@ -13457,10 +13487,10 @@
     </row>
     <row r="541" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
-        <v>1034</v>
+        <v>1042</v>
       </c>
       <c r="B541" t="s">
-        <v>1035</v>
+        <v>1043</v>
       </c>
       <c r="C541" s="2" t="s">
         <v>7</v>
@@ -13471,10 +13501,10 @@
     </row>
     <row r="542" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
-        <v>1036</v>
+        <v>1044</v>
       </c>
       <c r="B542" t="s">
-        <v>1037</v>
+        <v>1045</v>
       </c>
       <c r="C542" s="2" t="s">
         <v>7</v>
@@ -13485,10 +13515,10 @@
     </row>
     <row r="543" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
-        <v>1038</v>
+        <v>1046</v>
       </c>
       <c r="B543" t="s">
-        <v>1039</v>
+        <v>1047</v>
       </c>
       <c r="C543" s="2" t="s">
         <v>7</v>
@@ -13499,10 +13529,10 @@
     </row>
     <row r="544" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
-        <v>1040</v>
+        <v>1048</v>
       </c>
       <c r="B544" t="s">
-        <v>1041</v>
+        <v>1049</v>
       </c>
       <c r="C544" s="2" t="s">
         <v>7</v>
@@ -13513,10 +13543,10 @@
     </row>
     <row r="545" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
-        <v>1042</v>
+        <v>1050</v>
       </c>
       <c r="B545" t="s">
-        <v>1043</v>
+        <v>1051</v>
       </c>
       <c r="C545" s="2" t="s">
         <v>7</v>
@@ -13527,10 +13557,10 @@
     </row>
     <row r="546" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
-        <v>1044</v>
+        <v>1052</v>
       </c>
       <c r="B546" t="s">
-        <v>1045</v>
+        <v>1053</v>
       </c>
       <c r="C546" s="2" t="s">
         <v>7</v>
@@ -13541,10 +13571,10 @@
     </row>
     <row r="547" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
-        <v>1046</v>
+        <v>1054</v>
       </c>
       <c r="B547" t="s">
-        <v>1047</v>
+        <v>1055</v>
       </c>
       <c r="C547" s="2" t="s">
         <v>7</v>
@@ -13555,10 +13585,10 @@
     </row>
     <row r="548" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
-        <v>1048</v>
+        <v>1056</v>
       </c>
       <c r="B548" t="s">
-        <v>1049</v>
+        <v>1057</v>
       </c>
       <c r="C548" s="2" t="s">
         <v>7</v>
@@ -13569,10 +13599,10 @@
     </row>
     <row r="549" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
-        <v>1052</v>
+        <v>1060</v>
       </c>
       <c r="B549" t="s">
-        <v>1053</v>
+        <v>1061</v>
       </c>
       <c r="C549" s="2" t="s">
         <v>7</v>
@@ -13583,10 +13613,10 @@
     </row>
     <row r="550" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
-        <v>1054</v>
+        <v>1062</v>
       </c>
       <c r="B550" t="s">
-        <v>1055</v>
+        <v>1063</v>
       </c>
       <c r="C550" s="2" t="s">
         <v>7</v>
@@ -13597,10 +13627,10 @@
     </row>
     <row r="551" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
-        <v>1058</v>
+        <v>1066</v>
       </c>
       <c r="B551" t="s">
-        <v>1059</v>
+        <v>1067</v>
       </c>
       <c r="C551" s="2" t="s">
         <v>7</v>
@@ -13611,10 +13641,10 @@
     </row>
     <row r="552" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
-        <v>1060</v>
+        <v>1068</v>
       </c>
       <c r="B552" t="s">
-        <v>1061</v>
+        <v>1069</v>
       </c>
       <c r="C552" s="2" t="s">
         <v>7</v>
@@ -13625,10 +13655,10 @@
     </row>
     <row r="553" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
-        <v>1062</v>
+        <v>1070</v>
       </c>
       <c r="B553" t="s">
-        <v>1063</v>
+        <v>1071</v>
       </c>
       <c r="C553" s="2" t="s">
         <v>7</v>
@@ -13639,10 +13669,10 @@
     </row>
     <row r="554" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
-        <v>1064</v>
+        <v>1072</v>
       </c>
       <c r="B554" t="s">
-        <v>1065</v>
+        <v>1073</v>
       </c>
       <c r="C554" s="2" t="s">
         <v>7</v>
@@ -13653,10 +13683,10 @@
     </row>
     <row r="555" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
-        <v>1066</v>
+        <v>1074</v>
       </c>
       <c r="B555" t="s">
-        <v>1067</v>
+        <v>1075</v>
       </c>
       <c r="C555" s="2" t="s">
         <v>7</v>
@@ -13667,10 +13697,10 @@
     </row>
     <row r="556" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
-        <v>1068</v>
+        <v>1076</v>
       </c>
       <c r="B556" t="s">
-        <v>1069</v>
+        <v>1077</v>
       </c>
       <c r="C556" s="2" t="s">
         <v>7</v>
@@ -13681,10 +13711,10 @@
     </row>
     <row r="557" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
-        <v>1070</v>
+        <v>1078</v>
       </c>
       <c r="B557" t="s">
-        <v>1071</v>
+        <v>1079</v>
       </c>
       <c r="C557" s="2" t="s">
         <v>7</v>
@@ -13695,10 +13725,10 @@
     </row>
     <row r="558" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
-        <v>1072</v>
+        <v>1080</v>
       </c>
       <c r="B558" t="s">
-        <v>1073</v>
+        <v>1081</v>
       </c>
       <c r="C558" s="2" t="s">
         <v>7</v>
@@ -13709,10 +13739,10 @@
     </row>
     <row r="559" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
-        <v>1074</v>
+        <v>1082</v>
       </c>
       <c r="B559" t="s">
-        <v>1075</v>
+        <v>1083</v>
       </c>
       <c r="C559" s="2" t="s">
         <v>7</v>
@@ -13723,10 +13753,10 @@
     </row>
     <row r="560" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
-        <v>1076</v>
+        <v>1084</v>
       </c>
       <c r="B560" t="s">
-        <v>1077</v>
+        <v>1085</v>
       </c>
       <c r="C560" s="2" t="s">
         <v>7</v>
@@ -13737,10 +13767,10 @@
     </row>
     <row r="561" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
-        <v>1078</v>
+        <v>1086</v>
       </c>
       <c r="B561" t="s">
-        <v>1079</v>
+        <v>1087</v>
       </c>
       <c r="C561" s="2" t="s">
         <v>7</v>
@@ -13751,10 +13781,10 @@
     </row>
     <row r="562" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
-        <v>1080</v>
+        <v>1088</v>
       </c>
       <c r="B562" t="s">
-        <v>1081</v>
+        <v>1089</v>
       </c>
       <c r="C562" s="2" t="s">
         <v>7</v>
@@ -13765,10 +13795,10 @@
     </row>
     <row r="563" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
-        <v>1082</v>
+        <v>1090</v>
       </c>
       <c r="B563" t="s">
-        <v>1083</v>
+        <v>1091</v>
       </c>
       <c r="C563" s="2" t="s">
         <v>7</v>
@@ -13779,10 +13809,10 @@
     </row>
     <row r="564" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
-        <v>1084</v>
+        <v>1092</v>
       </c>
       <c r="B564" t="s">
-        <v>1085</v>
+        <v>1093</v>
       </c>
       <c r="C564" s="2" t="s">
         <v>7</v>
@@ -13793,10 +13823,10 @@
     </row>
     <row r="565" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
-        <v>1086</v>
+        <v>1094</v>
       </c>
       <c r="B565" t="s">
-        <v>1087</v>
+        <v>1095</v>
       </c>
       <c r="C565" s="2" t="s">
         <v>7</v>
@@ -13807,10 +13837,10 @@
     </row>
     <row r="566" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
-        <v>1088</v>
+        <v>1096</v>
       </c>
       <c r="B566" t="s">
-        <v>1089</v>
+        <v>1097</v>
       </c>
       <c r="C566" s="2" t="s">
         <v>7</v>
@@ -13821,10 +13851,10 @@
     </row>
     <row r="567" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
-        <v>1090</v>
+        <v>1098</v>
       </c>
       <c r="B567" t="s">
-        <v>1091</v>
+        <v>1099</v>
       </c>
       <c r="C567" s="2" t="s">
         <v>7</v>
@@ -13835,10 +13865,10 @@
     </row>
     <row r="568" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
-        <v>1092</v>
+        <v>1100</v>
       </c>
       <c r="B568" t="s">
-        <v>1093</v>
+        <v>1101</v>
       </c>
       <c r="C568" s="2" t="s">
         <v>7</v>
@@ -13849,10 +13879,10 @@
     </row>
     <row r="569" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
-        <v>1094</v>
+        <v>1102</v>
       </c>
       <c r="B569" t="s">
-        <v>1095</v>
+        <v>1103</v>
       </c>
       <c r="C569" s="2" t="s">
         <v>7</v>
@@ -13863,10 +13893,10 @@
     </row>
     <row r="570" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
-        <v>1096</v>
+        <v>1104</v>
       </c>
       <c r="B570" t="s">
-        <v>1097</v>
+        <v>1105</v>
       </c>
       <c r="C570" s="2" t="s">
         <v>7</v>
@@ -13877,10 +13907,10 @@
     </row>
     <row r="571" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
-        <v>1098</v>
+        <v>1106</v>
       </c>
       <c r="B571" t="s">
-        <v>1099</v>
+        <v>1107</v>
       </c>
       <c r="C571" s="2" t="s">
         <v>7</v>
@@ -13891,10 +13921,10 @@
     </row>
     <row r="572" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
-        <v>1100</v>
+        <v>1108</v>
       </c>
       <c r="B572" t="s">
-        <v>1101</v>
+        <v>1109</v>
       </c>
       <c r="C572" s="2" t="s">
         <v>7</v>
@@ -13905,10 +13935,10 @@
     </row>
     <row r="573" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
-        <v>1102</v>
+        <v>1110</v>
       </c>
       <c r="B573" t="s">
-        <v>1103</v>
+        <v>1111</v>
       </c>
       <c r="C573" s="2" t="s">
         <v>7</v>
@@ -13919,10 +13949,10 @@
     </row>
     <row r="574" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
-        <v>1104</v>
+        <v>1112</v>
       </c>
       <c r="B574" t="s">
-        <v>1105</v>
+        <v>1113</v>
       </c>
       <c r="C574" s="2" t="s">
         <v>7</v>
@@ -13933,10 +13963,10 @@
     </row>
     <row r="575" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
-        <v>1106</v>
+        <v>1114</v>
       </c>
       <c r="B575" t="s">
-        <v>1107</v>
+        <v>1115</v>
       </c>
       <c r="C575" s="2" t="s">
         <v>7</v>
@@ -13947,10 +13977,10 @@
     </row>
     <row r="576" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
-        <v>1108</v>
+        <v>1116</v>
       </c>
       <c r="B576" t="s">
-        <v>1109</v>
+        <v>1117</v>
       </c>
       <c r="C576" s="2" t="s">
         <v>7</v>
@@ -13961,10 +13991,10 @@
     </row>
     <row r="577" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
-        <v>1110</v>
+        <v>1118</v>
       </c>
       <c r="B577" t="s">
-        <v>1111</v>
+        <v>1119</v>
       </c>
       <c r="C577" s="2" t="s">
         <v>7</v>
@@ -13975,10 +14005,10 @@
     </row>
     <row r="578" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
-        <v>1112</v>
+        <v>1120</v>
       </c>
       <c r="B578" t="s">
-        <v>1113</v>
+        <v>1121</v>
       </c>
       <c r="C578" s="2" t="s">
         <v>7</v>
@@ -13989,10 +14019,10 @@
     </row>
     <row r="579" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
-        <v>1114</v>
+        <v>1122</v>
       </c>
       <c r="B579" t="s">
-        <v>1115</v>
+        <v>1123</v>
       </c>
       <c r="C579" s="2" t="s">
         <v>7</v>
@@ -14003,10 +14033,10 @@
     </row>
     <row r="580" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
-        <v>1116</v>
+        <v>1124</v>
       </c>
       <c r="B580" t="s">
-        <v>1117</v>
+        <v>1125</v>
       </c>
       <c r="C580" s="2" t="s">
         <v>7</v>
@@ -14017,10 +14047,10 @@
     </row>
     <row r="581" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
-        <v>1118</v>
+        <v>1126</v>
       </c>
       <c r="B581" t="s">
-        <v>1119</v>
+        <v>1127</v>
       </c>
       <c r="C581" s="2" t="s">
         <v>7</v>
@@ -14031,10 +14061,10 @@
     </row>
     <row r="582" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
-        <v>1120</v>
+        <v>1128</v>
       </c>
       <c r="B582" t="s">
-        <v>1121</v>
+        <v>1129</v>
       </c>
       <c r="C582" s="2" t="s">
         <v>7</v>
@@ -14045,10 +14075,10 @@
     </row>
     <row r="583" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
-        <v>1122</v>
+        <v>1130</v>
       </c>
       <c r="B583" t="s">
-        <v>1123</v>
+        <v>1131</v>
       </c>
       <c r="C583" s="2" t="s">
         <v>7</v>
@@ -14059,10 +14089,10 @@
     </row>
     <row r="584" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
-        <v>1124</v>
+        <v>1132</v>
       </c>
       <c r="B584" t="s">
-        <v>1125</v>
+        <v>1133</v>
       </c>
       <c r="C584" s="2" t="s">
         <v>7</v>
@@ -14073,10 +14103,10 @@
     </row>
     <row r="585" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
-        <v>1126</v>
+        <v>1134</v>
       </c>
       <c r="B585" t="s">
-        <v>1127</v>
+        <v>1135</v>
       </c>
       <c r="C585" s="2" t="s">
         <v>7</v>
@@ -14087,10 +14117,10 @@
     </row>
     <row r="586" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
-        <v>1128</v>
+        <v>1136</v>
       </c>
       <c r="B586" t="s">
-        <v>1129</v>
+        <v>1137</v>
       </c>
       <c r="C586" s="2" t="s">
         <v>7</v>
@@ -14101,10 +14131,10 @@
     </row>
     <row r="587" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
-        <v>1130</v>
+        <v>1138</v>
       </c>
       <c r="B587" t="s">
-        <v>1131</v>
+        <v>1139</v>
       </c>
       <c r="C587" s="2" t="s">
         <v>7</v>
@@ -14115,10 +14145,10 @@
     </row>
     <row r="588" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
-        <v>1132</v>
+        <v>1140</v>
       </c>
       <c r="B588" t="s">
-        <v>1133</v>
+        <v>1141</v>
       </c>
       <c r="C588" s="2" t="s">
         <v>7</v>
@@ -14129,10 +14159,10 @@
     </row>
     <row r="589" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
-        <v>1134</v>
+        <v>1142</v>
       </c>
       <c r="B589" t="s">
-        <v>1135</v>
+        <v>1143</v>
       </c>
       <c r="C589" s="2" t="s">
         <v>7</v>
@@ -14143,10 +14173,10 @@
     </row>
     <row r="590" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
-        <v>1136</v>
+        <v>1144</v>
       </c>
       <c r="B590" t="s">
-        <v>1137</v>
+        <v>1145</v>
       </c>
       <c r="C590" s="2" t="s">
         <v>7</v>
@@ -14157,10 +14187,10 @@
     </row>
     <row r="591" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
-        <v>1138</v>
+        <v>1146</v>
       </c>
       <c r="B591" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
       <c r="C591" s="2" t="s">
         <v>7</v>
@@ -14171,10 +14201,10 @@
     </row>
     <row r="592" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
-        <v>1140</v>
+        <v>1148</v>
       </c>
       <c r="B592" t="s">
-        <v>1141</v>
+        <v>1149</v>
       </c>
       <c r="C592" s="2" t="s">
         <v>7</v>
@@ -14185,10 +14215,10 @@
     </row>
     <row r="593" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
-        <v>1142</v>
+        <v>1150</v>
       </c>
       <c r="B593" t="s">
-        <v>1143</v>
+        <v>1151</v>
       </c>
       <c r="C593" s="2" t="s">
         <v>7</v>
@@ -14199,10 +14229,10 @@
     </row>
     <row r="594" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
-        <v>1144</v>
+        <v>1152</v>
       </c>
       <c r="B594" t="s">
-        <v>1145</v>
+        <v>1153</v>
       </c>
       <c r="C594" s="2" t="s">
         <v>7</v>
@@ -14213,10 +14243,10 @@
     </row>
     <row r="595" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
-        <v>1146</v>
+        <v>1154</v>
       </c>
       <c r="B595" t="s">
-        <v>1147</v>
+        <v>1155</v>
       </c>
       <c r="C595" s="2" t="s">
         <v>7</v>
@@ -14227,10 +14257,10 @@
     </row>
     <row r="596" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
-        <v>1148</v>
+        <v>1156</v>
       </c>
       <c r="B596" t="s">
-        <v>1149</v>
+        <v>1157</v>
       </c>
       <c r="C596" s="2" t="s">
         <v>7</v>
@@ -14241,10 +14271,10 @@
     </row>
     <row r="597" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
-        <v>1150</v>
+        <v>1158</v>
       </c>
       <c r="B597" t="s">
-        <v>1151</v>
+        <v>1159</v>
       </c>
       <c r="C597" s="2" t="s">
         <v>7</v>
@@ -14255,10 +14285,10 @@
     </row>
     <row r="598" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
-        <v>1152</v>
+        <v>1160</v>
       </c>
       <c r="B598" t="s">
-        <v>1153</v>
+        <v>1161</v>
       </c>
       <c r="C598" s="2" t="s">
         <v>7</v>
@@ -14269,10 +14299,10 @@
     </row>
     <row r="599" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
-        <v>1154</v>
+        <v>1162</v>
       </c>
       <c r="B599" t="s">
-        <v>1155</v>
+        <v>1163</v>
       </c>
       <c r="C599" s="2" t="s">
         <v>7</v>
@@ -14283,10 +14313,10 @@
     </row>
     <row r="600" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
-        <v>1156</v>
+        <v>1164</v>
       </c>
       <c r="B600" t="s">
-        <v>1157</v>
+        <v>1165</v>
       </c>
       <c r="C600" s="2" t="s">
         <v>7</v>
@@ -14297,10 +14327,10 @@
     </row>
     <row r="601" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
-        <v>1160</v>
+        <v>1168</v>
       </c>
       <c r="B601" t="s">
-        <v>1161</v>
+        <v>1169</v>
       </c>
       <c r="C601" s="2" t="s">
         <v>7</v>
@@ -14311,10 +14341,10 @@
     </row>
     <row r="602" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
-        <v>1162</v>
+        <v>1170</v>
       </c>
       <c r="B602" t="s">
-        <v>1163</v>
+        <v>1171</v>
       </c>
       <c r="C602" s="2" t="s">
         <v>7</v>
@@ -14325,10 +14355,10 @@
     </row>
     <row r="603" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
-        <v>1164</v>
+        <v>1172</v>
       </c>
       <c r="B603" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
       <c r="C603" s="2" t="s">
         <v>7</v>
@@ -14339,10 +14369,10 @@
     </row>
     <row r="604" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
-        <v>1166</v>
+        <v>1174</v>
       </c>
       <c r="B604" t="s">
-        <v>1167</v>
+        <v>1175</v>
       </c>
       <c r="C604" s="2" t="s">
         <v>7</v>
@@ -14353,10 +14383,10 @@
     </row>
     <row r="605" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
-        <v>1168</v>
+        <v>1176</v>
       </c>
       <c r="B605" t="s">
-        <v>1169</v>
+        <v>1177</v>
       </c>
       <c r="C605" s="2" t="s">
         <v>7</v>
@@ -14367,10 +14397,10 @@
     </row>
     <row r="606" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
-        <v>1170</v>
+        <v>1178</v>
       </c>
       <c r="B606" t="s">
-        <v>1171</v>
+        <v>1179</v>
       </c>
       <c r="C606" s="2" t="s">
         <v>7</v>
@@ -14381,10 +14411,10 @@
     </row>
     <row r="607" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
-        <v>1172</v>
+        <v>1180</v>
       </c>
       <c r="B607" t="s">
-        <v>1173</v>
+        <v>1181</v>
       </c>
       <c r="C607" s="2" t="s">
         <v>7</v>
@@ -14395,10 +14425,10 @@
     </row>
     <row r="608" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
-        <v>1174</v>
+        <v>1182</v>
       </c>
       <c r="B608" t="s">
-        <v>1175</v>
+        <v>1183</v>
       </c>
       <c r="C608" s="2" t="s">
         <v>7</v>
@@ -14409,10 +14439,10 @@
     </row>
     <row r="609" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
-        <v>1176</v>
+        <v>1184</v>
       </c>
       <c r="B609" t="s">
-        <v>1177</v>
+        <v>1185</v>
       </c>
       <c r="C609" s="2" t="s">
         <v>7</v>
@@ -14423,10 +14453,10 @@
     </row>
     <row r="610" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
-        <v>1178</v>
+        <v>1186</v>
       </c>
       <c r="B610" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="C610" s="2" t="s">
         <v>7</v>
@@ -14437,10 +14467,10 @@
     </row>
     <row r="611" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="B611" t="s">
-        <v>1181</v>
+        <v>1189</v>
       </c>
       <c r="C611" s="2" t="s">
         <v>7</v>
@@ -14451,10 +14481,10 @@
     </row>
     <row r="612" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
-        <v>1182</v>
+        <v>1190</v>
       </c>
       <c r="B612" t="s">
-        <v>1183</v>
+        <v>1191</v>
       </c>
       <c r="C612" s="2" t="s">
         <v>7</v>
@@ -14465,10 +14495,10 @@
     </row>
     <row r="613" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
-        <v>1184</v>
+        <v>1192</v>
       </c>
       <c r="B613" t="s">
-        <v>1185</v>
+        <v>1193</v>
       </c>
       <c r="C613" s="2" t="s">
         <v>7</v>
@@ -14479,10 +14509,10 @@
     </row>
     <row r="614" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
-        <v>1186</v>
+        <v>1194</v>
       </c>
       <c r="B614" t="s">
-        <v>1187</v>
+        <v>1195</v>
       </c>
       <c r="C614" s="2" t="s">
         <v>7</v>
@@ -14493,10 +14523,10 @@
     </row>
     <row r="615" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
-        <v>1188</v>
+        <v>1196</v>
       </c>
       <c r="B615" t="s">
-        <v>1189</v>
+        <v>1197</v>
       </c>
       <c r="C615" s="2" t="s">
         <v>7</v>
@@ -14507,10 +14537,10 @@
     </row>
     <row r="616" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
-        <v>1190</v>
+        <v>1198</v>
       </c>
       <c r="B616" t="s">
-        <v>1191</v>
+        <v>1199</v>
       </c>
       <c r="C616" s="2" t="s">
         <v>7</v>
@@ -14521,10 +14551,10 @@
     </row>
     <row r="617" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
-        <v>1192</v>
+        <v>1200</v>
       </c>
       <c r="B617" t="s">
-        <v>1193</v>
+        <v>1201</v>
       </c>
       <c r="C617" s="2" t="s">
         <v>7</v>
@@ -14535,10 +14565,10 @@
     </row>
     <row r="618" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
-        <v>1194</v>
+        <v>1202</v>
       </c>
       <c r="B618" t="s">
-        <v>1195</v>
+        <v>1203</v>
       </c>
       <c r="C618" s="2" t="s">
         <v>7</v>
@@ -14549,10 +14579,10 @@
     </row>
     <row r="619" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
-        <v>1196</v>
+        <v>1204</v>
       </c>
       <c r="B619" t="s">
-        <v>1197</v>
+        <v>1205</v>
       </c>
       <c r="C619" s="2" t="s">
         <v>7</v>
@@ -14563,10 +14593,10 @@
     </row>
     <row r="620" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
-        <v>1198</v>
+        <v>1206</v>
       </c>
       <c r="B620" t="s">
-        <v>1199</v>
+        <v>1207</v>
       </c>
       <c r="C620" s="2" t="s">
         <v>7</v>
@@ -14577,10 +14607,10 @@
     </row>
     <row r="621" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
-        <v>1200</v>
+        <v>1208</v>
       </c>
       <c r="B621" t="s">
-        <v>1201</v>
+        <v>1209</v>
       </c>
       <c r="C621" s="2" t="s">
         <v>7</v>
@@ -14591,10 +14621,10 @@
     </row>
     <row r="622" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
       <c r="B622" t="s">
-        <v>1203</v>
+        <v>1211</v>
       </c>
       <c r="C622" s="2" t="s">
         <v>7</v>
@@ -14605,10 +14635,10 @@
     </row>
     <row r="623" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
-        <v>1204</v>
+        <v>1212</v>
       </c>
       <c r="B623" t="s">
-        <v>1205</v>
+        <v>1213</v>
       </c>
       <c r="C623" s="2" t="s">
         <v>7</v>
@@ -14619,10 +14649,10 @@
     </row>
     <row r="624" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
-        <v>1206</v>
+        <v>1214</v>
       </c>
       <c r="B624" t="s">
-        <v>1207</v>
+        <v>1215</v>
       </c>
       <c r="C624" s="2" t="s">
         <v>7</v>
@@ -14633,10 +14663,10 @@
     </row>
     <row r="625" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
-        <v>1208</v>
+        <v>1216</v>
       </c>
       <c r="B625" t="s">
-        <v>1209</v>
+        <v>1217</v>
       </c>
       <c r="C625" s="2" t="s">
         <v>7</v>
@@ -14647,10 +14677,10 @@
     </row>
     <row r="626" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
-        <v>1210</v>
+        <v>1218</v>
       </c>
       <c r="B626" t="s">
-        <v>1211</v>
+        <v>1219</v>
       </c>
       <c r="C626" s="2" t="s">
         <v>7</v>
@@ -14661,10 +14691,10 @@
     </row>
     <row r="627" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
-        <v>1212</v>
+        <v>1220</v>
       </c>
       <c r="B627" t="s">
-        <v>1213</v>
+        <v>1221</v>
       </c>
       <c r="C627" s="2" t="s">
         <v>7</v>
@@ -14675,10 +14705,10 @@
     </row>
     <row r="628" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
-        <v>1214</v>
+        <v>1222</v>
       </c>
       <c r="B628" t="s">
-        <v>1215</v>
+        <v>1223</v>
       </c>
       <c r="C628" s="2" t="s">
         <v>7</v>
@@ -14689,10 +14719,10 @@
     </row>
     <row r="629" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
-        <v>1216</v>
+        <v>1224</v>
       </c>
       <c r="B629" t="s">
-        <v>1217</v>
+        <v>1225</v>
       </c>
       <c r="C629" s="2" t="s">
         <v>7</v>
@@ -14703,10 +14733,10 @@
     </row>
     <row r="630" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
-        <v>1220</v>
+        <v>1228</v>
       </c>
       <c r="B630" t="s">
-        <v>1221</v>
+        <v>1229</v>
       </c>
       <c r="C630" s="2" t="s">
         <v>7</v>
@@ -14717,10 +14747,10 @@
     </row>
     <row r="631" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
-        <v>1222</v>
+        <v>1230</v>
       </c>
       <c r="B631" t="s">
-        <v>1223</v>
+        <v>1231</v>
       </c>
       <c r="C631" s="2" t="s">
         <v>7</v>
@@ -14731,10 +14761,10 @@
     </row>
     <row r="632" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
-        <v>1224</v>
+        <v>1232</v>
       </c>
       <c r="B632" t="s">
-        <v>1225</v>
+        <v>1233</v>
       </c>
       <c r="C632" s="2" t="s">
         <v>7</v>
@@ -14745,10 +14775,10 @@
     </row>
     <row r="633" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
-        <v>1226</v>
+        <v>1234</v>
       </c>
       <c r="B633" t="s">
-        <v>1227</v>
+        <v>1235</v>
       </c>
       <c r="C633" s="2" t="s">
         <v>7</v>
@@ -14759,10 +14789,10 @@
     </row>
     <row r="634" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
-        <v>1228</v>
+        <v>1236</v>
       </c>
       <c r="B634" t="s">
-        <v>1229</v>
+        <v>1237</v>
       </c>
       <c r="C634" s="2" t="s">
         <v>7</v>
@@ -14773,10 +14803,10 @@
     </row>
     <row r="635" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
-        <v>1230</v>
+        <v>1238</v>
       </c>
       <c r="B635" t="s">
-        <v>1231</v>
+        <v>1239</v>
       </c>
       <c r="C635" s="2" t="s">
         <v>7</v>
@@ -14787,10 +14817,10 @@
     </row>
     <row r="636" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
-        <v>1232</v>
+        <v>1240</v>
       </c>
       <c r="B636" t="s">
-        <v>1233</v>
+        <v>1241</v>
       </c>
       <c r="C636" s="2" t="s">
         <v>7</v>
@@ -14801,10 +14831,10 @@
     </row>
     <row r="637" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
       <c r="B637" t="s">
-        <v>1235</v>
+        <v>1243</v>
       </c>
       <c r="C637" s="2" t="s">
         <v>7</v>
@@ -14815,10 +14845,10 @@
     </row>
     <row r="638" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
-        <v>1236</v>
+        <v>1244</v>
       </c>
       <c r="B638" t="s">
-        <v>1237</v>
+        <v>1245</v>
       </c>
       <c r="C638" s="2" t="s">
         <v>7</v>
@@ -14829,10 +14859,10 @@
     </row>
     <row r="639" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
-        <v>1238</v>
+        <v>1246</v>
       </c>
       <c r="B639" t="s">
-        <v>1239</v>
+        <v>1247</v>
       </c>
       <c r="C639" s="2" t="s">
         <v>7</v>
@@ -14843,10 +14873,10 @@
     </row>
     <row r="640" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
-        <v>1240</v>
+        <v>1248</v>
       </c>
       <c r="B640" t="s">
-        <v>1241</v>
+        <v>1249</v>
       </c>
       <c r="C640" s="2" t="s">
         <v>7</v>
@@ -14857,10 +14887,10 @@
     </row>
     <row r="641" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
-        <v>1242</v>
+        <v>1250</v>
       </c>
       <c r="B641" t="s">
-        <v>1243</v>
+        <v>1251</v>
       </c>
       <c r="C641" s="2" t="s">
         <v>7</v>
@@ -14871,10 +14901,10 @@
     </row>
     <row r="642" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
-        <v>1244</v>
+        <v>1252</v>
       </c>
       <c r="B642" t="s">
-        <v>1245</v>
+        <v>1253</v>
       </c>
       <c r="C642" s="2" t="s">
         <v>7</v>
@@ -14885,10 +14915,10 @@
     </row>
     <row r="643" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
-        <v>1246</v>
+        <v>1254</v>
       </c>
       <c r="B643" t="s">
-        <v>1247</v>
+        <v>1255</v>
       </c>
       <c r="C643" s="2" t="s">
         <v>7</v>
@@ -14899,10 +14929,10 @@
     </row>
     <row r="644" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
-        <v>1248</v>
+        <v>1256</v>
       </c>
       <c r="B644" t="s">
-        <v>1249</v>
+        <v>1257</v>
       </c>
       <c r="C644" s="2" t="s">
         <v>7</v>
@@ -14913,10 +14943,10 @@
     </row>
     <row r="645" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
-        <v>1250</v>
+        <v>1258</v>
       </c>
       <c r="B645" t="s">
-        <v>1251</v>
+        <v>1259</v>
       </c>
       <c r="C645" s="2" t="s">
         <v>7</v>
@@ -14927,10 +14957,10 @@
     </row>
     <row r="646" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
-        <v>1252</v>
+        <v>1260</v>
       </c>
       <c r="B646" t="s">
-        <v>1253</v>
+        <v>1261</v>
       </c>
       <c r="C646" s="2" t="s">
         <v>7</v>
@@ -14941,10 +14971,10 @@
     </row>
     <row r="647" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
-        <v>1254</v>
+        <v>1262</v>
       </c>
       <c r="B647" t="s">
-        <v>1255</v>
+        <v>1263</v>
       </c>
       <c r="C647" s="2" t="s">
         <v>7</v>
@@ -14955,10 +14985,10 @@
     </row>
     <row r="648" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
-        <v>1256</v>
+        <v>1264</v>
       </c>
       <c r="B648" t="s">
-        <v>1257</v>
+        <v>1265</v>
       </c>
       <c r="C648" s="2" t="s">
         <v>7</v>
@@ -14969,10 +14999,10 @@
     </row>
     <row r="649" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
-        <v>1258</v>
+        <v>1266</v>
       </c>
       <c r="B649" t="s">
-        <v>1259</v>
+        <v>1267</v>
       </c>
       <c r="C649" s="2" t="s">
         <v>7</v>
@@ -14983,10 +15013,10 @@
     </row>
     <row r="650" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
-        <v>1260</v>
+        <v>1268</v>
       </c>
       <c r="B650" t="s">
-        <v>1261</v>
+        <v>1269</v>
       </c>
       <c r="C650" s="2" t="s">
         <v>7</v>
@@ -14997,10 +15027,10 @@
     </row>
     <row r="651" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
-        <v>1262</v>
+        <v>1270</v>
       </c>
       <c r="B651" t="s">
-        <v>1263</v>
+        <v>1271</v>
       </c>
       <c r="C651" s="2" t="s">
         <v>7</v>
@@ -15011,10 +15041,10 @@
     </row>
     <row r="652" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
-        <v>1264</v>
+        <v>1272</v>
       </c>
       <c r="B652" t="s">
-        <v>1265</v>
+        <v>1273</v>
       </c>
       <c r="C652" s="2" t="s">
         <v>7</v>
@@ -15025,10 +15055,10 @@
     </row>
     <row r="653" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
-        <v>1266</v>
+        <v>1274</v>
       </c>
       <c r="B653" t="s">
-        <v>1267</v>
+        <v>1275</v>
       </c>
       <c r="C653" s="2" t="s">
         <v>7</v>
@@ -15039,10 +15069,10 @@
     </row>
     <row r="654" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
-        <v>1268</v>
+        <v>1276</v>
       </c>
       <c r="B654" t="s">
-        <v>1269</v>
+        <v>1277</v>
       </c>
       <c r="C654" s="2" t="s">
         <v>7</v>
@@ -15053,10 +15083,10 @@
     </row>
     <row r="655" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
-        <v>1270</v>
+        <v>1278</v>
       </c>
       <c r="B655" t="s">
-        <v>1271</v>
+        <v>1279</v>
       </c>
       <c r="C655" s="2" t="s">
         <v>7</v>
@@ -15067,10 +15097,10 @@
     </row>
     <row r="656" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
-        <v>1272</v>
+        <v>1280</v>
       </c>
       <c r="B656" t="s">
-        <v>1273</v>
+        <v>1281</v>
       </c>
       <c r="C656" s="2" t="s">
         <v>7</v>
@@ -15081,10 +15111,10 @@
     </row>
     <row r="657" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
-        <v>1274</v>
+        <v>1282</v>
       </c>
       <c r="B657" t="s">
-        <v>1275</v>
+        <v>1283</v>
       </c>
       <c r="C657" s="2" t="s">
         <v>7</v>
@@ -15095,10 +15125,10 @@
     </row>
     <row r="658" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
-        <v>1276</v>
+        <v>1284</v>
       </c>
       <c r="B658" t="s">
-        <v>1277</v>
+        <v>1285</v>
       </c>
       <c r="C658" s="2" t="s">
         <v>7</v>
@@ -15109,10 +15139,10 @@
     </row>
     <row r="659" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
-        <v>1278</v>
+        <v>1286</v>
       </c>
       <c r="B659" t="s">
-        <v>1279</v>
+        <v>1287</v>
       </c>
       <c r="C659" s="2" t="s">
         <v>7</v>
@@ -15123,10 +15153,10 @@
     </row>
     <row r="660" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
-        <v>1280</v>
+        <v>1288</v>
       </c>
       <c r="B660" t="s">
-        <v>1281</v>
+        <v>1289</v>
       </c>
       <c r="C660" s="2" t="s">
         <v>7</v>
@@ -15137,10 +15167,10 @@
     </row>
     <row r="661" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
-        <v>1282</v>
+        <v>1290</v>
       </c>
       <c r="B661" t="s">
-        <v>1283</v>
+        <v>1291</v>
       </c>
       <c r="C661" s="2" t="s">
         <v>7</v>
@@ -15151,10 +15181,10 @@
     </row>
     <row r="662" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
-        <v>1284</v>
+        <v>1292</v>
       </c>
       <c r="B662" t="s">
-        <v>1285</v>
+        <v>1293</v>
       </c>
       <c r="C662" s="2" t="s">
         <v>7</v>
@@ -15165,10 +15195,10 @@
     </row>
     <row r="663" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
-        <v>1286</v>
+        <v>1294</v>
       </c>
       <c r="B663" t="s">
-        <v>1287</v>
+        <v>1295</v>
       </c>
       <c r="C663" s="2" t="s">
         <v>7</v>
@@ -15179,10 +15209,10 @@
     </row>
     <row r="664" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
-        <v>1288</v>
+        <v>1296</v>
       </c>
       <c r="B664" t="s">
-        <v>1289</v>
+        <v>1297</v>
       </c>
       <c r="C664" s="2" t="s">
         <v>7</v>
@@ -15193,10 +15223,10 @@
     </row>
     <row r="665" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
-        <v>1290</v>
+        <v>1298</v>
       </c>
       <c r="B665" t="s">
-        <v>1291</v>
+        <v>1299</v>
       </c>
       <c r="C665" s="2" t="s">
         <v>7</v>
@@ -15207,10 +15237,10 @@
     </row>
     <row r="666" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
-        <v>1292</v>
+        <v>1300</v>
       </c>
       <c r="B666" t="s">
-        <v>1293</v>
+        <v>1301</v>
       </c>
       <c r="C666" s="2" t="s">
         <v>7</v>
@@ -15221,10 +15251,10 @@
     </row>
     <row r="667" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
-        <v>1294</v>
+        <v>1302</v>
       </c>
       <c r="B667" t="s">
-        <v>1295</v>
+        <v>1303</v>
       </c>
       <c r="C667" s="2" t="s">
         <v>7</v>
@@ -15235,10 +15265,10 @@
     </row>
     <row r="668" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
-        <v>1296</v>
+        <v>1304</v>
       </c>
       <c r="B668" t="s">
-        <v>1297</v>
+        <v>1305</v>
       </c>
       <c r="C668" s="2" t="s">
         <v>7</v>
@@ -15249,10 +15279,10 @@
     </row>
     <row r="669" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
-        <v>1298</v>
+        <v>1306</v>
       </c>
       <c r="B669" t="s">
-        <v>1299</v>
+        <v>1307</v>
       </c>
       <c r="C669" s="2" t="s">
         <v>7</v>
@@ -15263,10 +15293,10 @@
     </row>
     <row r="670" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
-        <v>1300</v>
+        <v>1308</v>
       </c>
       <c r="B670" t="s">
-        <v>1301</v>
+        <v>1309</v>
       </c>
       <c r="C670" s="2" t="s">
         <v>7</v>
@@ -15277,10 +15307,10 @@
     </row>
     <row r="671" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
-        <v>1304</v>
+        <v>1312</v>
       </c>
       <c r="B671" t="s">
-        <v>1305</v>
+        <v>1313</v>
       </c>
       <c r="C671" s="2" t="s">
         <v>7</v>
@@ -15291,10 +15321,10 @@
     </row>
     <row r="672" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
-        <v>1306</v>
+        <v>1314</v>
       </c>
       <c r="B672" t="s">
-        <v>1307</v>
+        <v>1315</v>
       </c>
       <c r="C672" s="2" t="s">
         <v>7</v>
@@ -15305,10 +15335,10 @@
     </row>
     <row r="673" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
-        <v>1308</v>
+        <v>1316</v>
       </c>
       <c r="B673" t="s">
-        <v>1309</v>
+        <v>1317</v>
       </c>
       <c r="C673" s="2" t="s">
         <v>7</v>
@@ -15319,10 +15349,10 @@
     </row>
     <row r="674" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
-        <v>1310</v>
+        <v>1318</v>
       </c>
       <c r="B674" t="s">
-        <v>1311</v>
+        <v>1319</v>
       </c>
       <c r="C674" s="2" t="s">
         <v>7</v>
@@ -15333,10 +15363,10 @@
     </row>
     <row r="675" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
-        <v>1312</v>
+        <v>1320</v>
       </c>
       <c r="B675" t="s">
-        <v>1313</v>
+        <v>1321</v>
       </c>
       <c r="C675" s="2" t="s">
         <v>7</v>
@@ -15347,10 +15377,10 @@
     </row>
     <row r="676" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
-        <v>1314</v>
+        <v>1322</v>
       </c>
       <c r="B676" t="s">
-        <v>1315</v>
+        <v>1323</v>
       </c>
       <c r="C676" s="2" t="s">
         <v>7</v>
@@ -15361,10 +15391,10 @@
     </row>
     <row r="677" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
-        <v>1316</v>
+        <v>1324</v>
       </c>
       <c r="B677" t="s">
-        <v>1317</v>
+        <v>1325</v>
       </c>
       <c r="C677" s="2" t="s">
         <v>7</v>
@@ -15375,10 +15405,10 @@
     </row>
     <row r="678" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
-        <v>1318</v>
+        <v>1326</v>
       </c>
       <c r="B678" t="s">
-        <v>1319</v>
+        <v>1327</v>
       </c>
       <c r="C678" s="2" t="s">
         <v>7</v>
@@ -15389,10 +15419,10 @@
     </row>
     <row r="679" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
-        <v>1320</v>
+        <v>1328</v>
       </c>
       <c r="B679" t="s">
-        <v>1321</v>
+        <v>1329</v>
       </c>
       <c r="C679" s="2" t="s">
         <v>7</v>
@@ -15403,10 +15433,10 @@
     </row>
     <row r="680" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
-        <v>1322</v>
+        <v>1330</v>
       </c>
       <c r="B680" t="s">
-        <v>1323</v>
+        <v>1331</v>
       </c>
       <c r="C680" s="2" t="s">
         <v>7</v>
@@ -15417,10 +15447,10 @@
     </row>
     <row r="681" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
-        <v>1324</v>
+        <v>1332</v>
       </c>
       <c r="B681" t="s">
-        <v>1325</v>
+        <v>1333</v>
       </c>
       <c r="C681" s="2" t="s">
         <v>7</v>
@@ -15431,10 +15461,10 @@
     </row>
     <row r="682" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
-        <v>1326</v>
+        <v>1334</v>
       </c>
       <c r="B682" t="s">
-        <v>1327</v>
+        <v>1335</v>
       </c>
       <c r="C682" s="2" t="s">
         <v>7</v>
@@ -15445,10 +15475,10 @@
     </row>
     <row r="683" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
-        <v>1328</v>
+        <v>1336</v>
       </c>
       <c r="B683" t="s">
-        <v>1329</v>
+        <v>1337</v>
       </c>
       <c r="C683" s="2" t="s">
         <v>7</v>
@@ -15459,10 +15489,10 @@
     </row>
     <row r="684" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
-        <v>1330</v>
+        <v>1338</v>
       </c>
       <c r="B684" t="s">
-        <v>1331</v>
+        <v>1339</v>
       </c>
       <c r="C684" s="2" t="s">
         <v>7</v>
@@ -15473,10 +15503,10 @@
     </row>
     <row r="685" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
-        <v>1332</v>
+        <v>1340</v>
       </c>
       <c r="B685" t="s">
-        <v>1333</v>
+        <v>1341</v>
       </c>
       <c r="C685" s="2" t="s">
         <v>7</v>
@@ -15487,10 +15517,10 @@
     </row>
     <row r="686" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
-        <v>1334</v>
+        <v>1342</v>
       </c>
       <c r="B686" t="s">
-        <v>1335</v>
+        <v>1343</v>
       </c>
       <c r="C686" s="2" t="s">
         <v>7</v>
@@ -15501,10 +15531,10 @@
     </row>
     <row r="687" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
-        <v>1336</v>
+        <v>1344</v>
       </c>
       <c r="B687" t="s">
-        <v>1337</v>
+        <v>1345</v>
       </c>
       <c r="C687" s="2" t="s">
         <v>7</v>
@@ -15515,10 +15545,10 @@
     </row>
     <row r="688" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
-        <v>1338</v>
+        <v>1346</v>
       </c>
       <c r="B688" t="s">
-        <v>1339</v>
+        <v>1347</v>
       </c>
       <c r="C688" s="2" t="s">
         <v>7</v>
@@ -15529,10 +15559,10 @@
     </row>
     <row r="689" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
-        <v>1340</v>
+        <v>1348</v>
       </c>
       <c r="B689" t="s">
-        <v>1341</v>
+        <v>1349</v>
       </c>
       <c r="C689" s="2" t="s">
         <v>7</v>
@@ -15543,10 +15573,10 @@
     </row>
     <row r="690" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
-        <v>1342</v>
+        <v>1350</v>
       </c>
       <c r="B690" t="s">
-        <v>1343</v>
+        <v>1351</v>
       </c>
       <c r="C690" s="2" t="s">
         <v>7</v>
@@ -15557,10 +15587,10 @@
     </row>
     <row r="691" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
-        <v>1344</v>
+        <v>1352</v>
       </c>
       <c r="B691" t="s">
-        <v>1345</v>
+        <v>1353</v>
       </c>
       <c r="C691" s="2" t="s">
         <v>7</v>
@@ -15571,10 +15601,10 @@
     </row>
     <row r="692" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
-        <v>1346</v>
+        <v>1354</v>
       </c>
       <c r="B692" t="s">
-        <v>1347</v>
+        <v>1355</v>
       </c>
       <c r="C692" s="2" t="s">
         <v>7</v>
@@ -15585,10 +15615,10 @@
     </row>
     <row r="693" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
-        <v>1348</v>
+        <v>1356</v>
       </c>
       <c r="B693" t="s">
-        <v>1349</v>
+        <v>1357</v>
       </c>
       <c r="C693" s="2" t="s">
         <v>7</v>
@@ -15599,10 +15629,10 @@
     </row>
     <row r="694" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
-        <v>1350</v>
+        <v>1358</v>
       </c>
       <c r="B694" t="s">
-        <v>1351</v>
+        <v>1359</v>
       </c>
       <c r="C694" s="2" t="s">
         <v>7</v>
@@ -15613,10 +15643,10 @@
     </row>
     <row r="695" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
-        <v>1352</v>
+        <v>1360</v>
       </c>
       <c r="B695" t="s">
-        <v>1353</v>
+        <v>1361</v>
       </c>
       <c r="C695" s="2" t="s">
         <v>7</v>
@@ -15627,10 +15657,10 @@
     </row>
     <row r="696" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
-        <v>1354</v>
+        <v>1362</v>
       </c>
       <c r="B696" t="s">
-        <v>1355</v>
+        <v>1363</v>
       </c>
       <c r="C696" s="2" t="s">
         <v>7</v>
@@ -15641,10 +15671,10 @@
     </row>
     <row r="697" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
-        <v>1356</v>
+        <v>1364</v>
       </c>
       <c r="B697" t="s">
-        <v>1357</v>
+        <v>1365</v>
       </c>
       <c r="C697" s="2" t="s">
         <v>7</v>
@@ -15655,10 +15685,10 @@
     </row>
     <row r="698" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
-        <v>1358</v>
+        <v>1366</v>
       </c>
       <c r="B698" t="s">
-        <v>1359</v>
+        <v>1367</v>
       </c>
       <c r="C698" s="2" t="s">
         <v>7</v>
@@ -15669,10 +15699,10 @@
     </row>
     <row r="699" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
-        <v>1360</v>
+        <v>1368</v>
       </c>
       <c r="B699" t="s">
-        <v>1361</v>
+        <v>1369</v>
       </c>
       <c r="C699" s="2" t="s">
         <v>7</v>
@@ -15683,10 +15713,10 @@
     </row>
     <row r="700" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
-        <v>1362</v>
+        <v>1370</v>
       </c>
       <c r="B700" t="s">
-        <v>1363</v>
+        <v>1371</v>
       </c>
       <c r="C700" s="2" t="s">
         <v>7</v>
@@ -15697,10 +15727,10 @@
     </row>
     <row r="701" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
-        <v>1364</v>
+        <v>1372</v>
       </c>
       <c r="B701" t="s">
-        <v>1365</v>
+        <v>1373</v>
       </c>
       <c r="C701" s="2" t="s">
         <v>7</v>
@@ -15711,10 +15741,10 @@
     </row>
     <row r="702" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
-        <v>1366</v>
+        <v>1374</v>
       </c>
       <c r="B702" t="s">
-        <v>1367</v>
+        <v>1375</v>
       </c>
       <c r="C702" s="2" t="s">
         <v>7</v>
@@ -15725,10 +15755,10 @@
     </row>
     <row r="703" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
-        <v>1368</v>
+        <v>1376</v>
       </c>
       <c r="B703" t="s">
-        <v>1369</v>
+        <v>1377</v>
       </c>
       <c r="C703" s="2" t="s">
         <v>7</v>
@@ -15739,10 +15769,10 @@
     </row>
     <row r="704" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
-        <v>1372</v>
+        <v>1378</v>
       </c>
       <c r="B704" t="s">
-        <v>1373</v>
+        <v>1379</v>
       </c>
       <c r="C704" s="2" t="s">
         <v>7</v>
@@ -15753,10 +15783,10 @@
     </row>
     <row r="705" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
-        <v>1374</v>
+        <v>1380</v>
       </c>
       <c r="B705" t="s">
-        <v>1375</v>
+        <v>1381</v>
       </c>
       <c r="C705" s="2" t="s">
         <v>7</v>
@@ -15767,10 +15797,10 @@
     </row>
     <row r="706" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
-        <v>1376</v>
+        <v>1382</v>
       </c>
       <c r="B706" t="s">
-        <v>1377</v>
+        <v>1383</v>
       </c>
       <c r="C706" s="2" t="s">
         <v>7</v>
@@ -15781,10 +15811,10 @@
     </row>
     <row r="707" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="B707" t="s">
-        <v>1379</v>
+        <v>1385</v>
       </c>
       <c r="C707" s="2" t="s">
         <v>7</v>
@@ -15795,10 +15825,10 @@
     </row>
     <row r="708" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="B708" t="s">
-        <v>1381</v>
+        <v>1387</v>
       </c>
       <c r="C708" s="2" t="s">
         <v>7</v>
@@ -15809,10 +15839,10 @@
     </row>
     <row r="709" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
-        <v>1384</v>
+        <v>1388</v>
       </c>
       <c r="B709" t="s">
-        <v>1385</v>
+        <v>1389</v>
       </c>
       <c r="C709" s="2" t="s">
         <v>7</v>
@@ -15823,10 +15853,10 @@
     </row>
     <row r="710" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
-        <v>1386</v>
+        <v>1392</v>
       </c>
       <c r="B710" t="s">
-        <v>1387</v>
+        <v>1393</v>
       </c>
       <c r="C710" s="2" t="s">
         <v>7</v>
@@ -15837,10 +15867,10 @@
     </row>
     <row r="711" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
-        <v>1388</v>
+        <v>1394</v>
       </c>
       <c r="B711" t="s">
-        <v>1389</v>
+        <v>1395</v>
       </c>
       <c r="C711" s="2" t="s">
         <v>7</v>
@@ -15851,10 +15881,10 @@
     </row>
     <row r="712" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
-        <v>1390</v>
+        <v>1396</v>
       </c>
       <c r="B712" t="s">
-        <v>1391</v>
+        <v>1397</v>
       </c>
       <c r="C712" s="2" t="s">
         <v>7</v>
@@ -15865,10 +15895,10 @@
     </row>
     <row r="713" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A713" t="s">
-        <v>1392</v>
+        <v>1398</v>
       </c>
       <c r="B713" t="s">
-        <v>1393</v>
+        <v>1399</v>
       </c>
       <c r="C713" s="2" t="s">
         <v>7</v>
@@ -15879,10 +15909,10 @@
     </row>
     <row r="714" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A714" t="s">
-        <v>1394</v>
+        <v>1400</v>
       </c>
       <c r="B714" t="s">
-        <v>1395</v>
+        <v>1401</v>
       </c>
       <c r="C714" s="2" t="s">
         <v>7</v>
@@ -15893,10 +15923,10 @@
     </row>
     <row r="715" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
-        <v>1396</v>
+        <v>1402</v>
       </c>
       <c r="B715" t="s">
-        <v>1397</v>
+        <v>1403</v>
       </c>
       <c r="C715" s="2" t="s">
         <v>7</v>
@@ -15907,10 +15937,10 @@
     </row>
     <row r="716" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
-        <v>1398</v>
+        <v>1404</v>
       </c>
       <c r="B716" t="s">
-        <v>1399</v>
+        <v>1405</v>
       </c>
       <c r="C716" s="2" t="s">
         <v>7</v>
@@ -15921,10 +15951,10 @@
     </row>
     <row r="717" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A717" t="s">
-        <v>1400</v>
+        <v>1406</v>
       </c>
       <c r="B717" t="s">
-        <v>1401</v>
+        <v>1407</v>
       </c>
       <c r="C717" s="2" t="s">
         <v>7</v>
@@ -15935,10 +15965,10 @@
     </row>
     <row r="718" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
-        <v>1402</v>
+        <v>1408</v>
       </c>
       <c r="B718" t="s">
-        <v>1403</v>
+        <v>1409</v>
       </c>
       <c r="C718" s="2" t="s">
         <v>7</v>
@@ -15949,10 +15979,10 @@
     </row>
     <row r="719" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
-        <v>1404</v>
+        <v>1410</v>
       </c>
       <c r="B719" t="s">
-        <v>1405</v>
+        <v>1411</v>
       </c>
       <c r="C719" s="2" t="s">
         <v>7</v>
@@ -15963,10 +15993,10 @@
     </row>
     <row r="720" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A720" t="s">
-        <v>1406</v>
+        <v>1412</v>
       </c>
       <c r="B720" t="s">
-        <v>1407</v>
+        <v>1413</v>
       </c>
       <c r="C720" s="2" t="s">
         <v>7</v>
@@ -15977,10 +16007,10 @@
     </row>
     <row r="721" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
-        <v>1408</v>
+        <v>1414</v>
       </c>
       <c r="B721" t="s">
-        <v>1409</v>
+        <v>1415</v>
       </c>
       <c r="C721" s="2" t="s">
         <v>7</v>
@@ -15991,10 +16021,10 @@
     </row>
     <row r="722" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
-        <v>1410</v>
+        <v>1416</v>
       </c>
       <c r="B722" t="s">
-        <v>1411</v>
+        <v>1417</v>
       </c>
       <c r="C722" s="2" t="s">
         <v>7</v>
@@ -16005,10 +16035,10 @@
     </row>
     <row r="723" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
-        <v>1412</v>
+        <v>1418</v>
       </c>
       <c r="B723" t="s">
-        <v>1413</v>
+        <v>1419</v>
       </c>
       <c r="C723" s="2" t="s">
         <v>7</v>
@@ -16019,10 +16049,10 @@
     </row>
     <row r="724" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A724" t="s">
-        <v>1416</v>
+        <v>1420</v>
       </c>
       <c r="B724" t="s">
-        <v>1417</v>
+        <v>1421</v>
       </c>
       <c r="C724" s="2" t="s">
         <v>7</v>
@@ -16033,10 +16063,10 @@
     </row>
     <row r="725" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A725" t="s">
-        <v>1418</v>
+        <v>1424</v>
       </c>
       <c r="B725" t="s">
-        <v>1419</v>
+        <v>1425</v>
       </c>
       <c r="C725" s="2" t="s">
         <v>7</v>
@@ -16047,10 +16077,10 @@
     </row>
     <row r="726" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A726" t="s">
-        <v>1420</v>
+        <v>1426</v>
       </c>
       <c r="B726" t="s">
-        <v>1421</v>
+        <v>1427</v>
       </c>
       <c r="C726" s="2" t="s">
         <v>7</v>
@@ -16061,10 +16091,10 @@
     </row>
     <row r="727" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A727" t="s">
-        <v>1422</v>
+        <v>1428</v>
       </c>
       <c r="B727" t="s">
-        <v>1423</v>
+        <v>1429</v>
       </c>
       <c r="C727" s="2" t="s">
         <v>7</v>
@@ -16075,10 +16105,10 @@
     </row>
     <row r="728" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A728" t="s">
-        <v>1424</v>
+        <v>1430</v>
       </c>
       <c r="B728" t="s">
-        <v>1425</v>
+        <v>1431</v>
       </c>
       <c r="C728" s="2" t="s">
         <v>7</v>
@@ -16089,10 +16119,10 @@
     </row>
     <row r="729" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A729" t="s">
-        <v>1426</v>
+        <v>1432</v>
       </c>
       <c r="B729" t="s">
-        <v>1427</v>
+        <v>1433</v>
       </c>
       <c r="C729" s="2" t="s">
         <v>7</v>
@@ -16103,10 +16133,10 @@
     </row>
     <row r="730" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A730" t="s">
-        <v>1428</v>
+        <v>1434</v>
       </c>
       <c r="B730" t="s">
-        <v>1429</v>
+        <v>1435</v>
       </c>
       <c r="C730" s="2" t="s">
         <v>7</v>
@@ -16117,10 +16147,10 @@
     </row>
     <row r="731" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A731" t="s">
-        <v>1430</v>
+        <v>1436</v>
       </c>
       <c r="B731" t="s">
-        <v>1431</v>
+        <v>1437</v>
       </c>
       <c r="C731" s="2" t="s">
         <v>7</v>
@@ -16131,10 +16161,10 @@
     </row>
     <row r="732" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A732" t="s">
-        <v>1432</v>
+        <v>1438</v>
       </c>
       <c r="B732" t="s">
-        <v>1433</v>
+        <v>1439</v>
       </c>
       <c r="C732" s="2" t="s">
         <v>7</v>
@@ -16145,10 +16175,10 @@
     </row>
     <row r="733" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A733" t="s">
-        <v>1434</v>
+        <v>1440</v>
       </c>
       <c r="B733" t="s">
-        <v>1435</v>
+        <v>1441</v>
       </c>
       <c r="C733" s="2" t="s">
         <v>7</v>
@@ -16159,10 +16189,10 @@
     </row>
     <row r="734" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A734" t="s">
-        <v>1436</v>
+        <v>1442</v>
       </c>
       <c r="B734" t="s">
-        <v>1437</v>
+        <v>1443</v>
       </c>
       <c r="C734" s="2" t="s">
         <v>7</v>
@@ -16173,10 +16203,10 @@
     </row>
     <row r="735" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A735" t="s">
-        <v>1438</v>
+        <v>1444</v>
       </c>
       <c r="B735" t="s">
-        <v>1439</v>
+        <v>1445</v>
       </c>
       <c r="C735" s="2" t="s">
         <v>7</v>
@@ -16187,10 +16217,10 @@
     </row>
     <row r="736" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A736" t="s">
-        <v>1440</v>
+        <v>1446</v>
       </c>
       <c r="B736" t="s">
-        <v>1441</v>
+        <v>1447</v>
       </c>
       <c r="C736" s="2" t="s">
         <v>7</v>
@@ -16201,10 +16231,10 @@
     </row>
     <row r="737" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A737" t="s">
-        <v>1442</v>
+        <v>1448</v>
       </c>
       <c r="B737" t="s">
-        <v>1443</v>
+        <v>1449</v>
       </c>
       <c r="C737" s="2" t="s">
         <v>7</v>
@@ -16215,10 +16245,10 @@
     </row>
     <row r="738" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A738" t="s">
-        <v>1444</v>
+        <v>1450</v>
       </c>
       <c r="B738" t="s">
-        <v>1445</v>
+        <v>1451</v>
       </c>
       <c r="C738" s="2" t="s">
         <v>7</v>
@@ -16229,10 +16259,10 @@
     </row>
     <row r="739" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A739" t="s">
-        <v>1448</v>
+        <v>1452</v>
       </c>
       <c r="B739" t="s">
-        <v>1449</v>
+        <v>1453</v>
       </c>
       <c r="C739" s="2" t="s">
         <v>7</v>
@@ -16243,10 +16273,10 @@
     </row>
     <row r="740" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A740" t="s">
-        <v>1450</v>
+        <v>1456</v>
       </c>
       <c r="B740" t="s">
-        <v>1451</v>
+        <v>1457</v>
       </c>
       <c r="C740" s="2" t="s">
         <v>7</v>
@@ -16257,10 +16287,10 @@
     </row>
     <row r="741" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A741" t="s">
-        <v>1452</v>
+        <v>1458</v>
       </c>
       <c r="B741" t="s">
-        <v>1453</v>
+        <v>1459</v>
       </c>
       <c r="C741" s="2" t="s">
         <v>7</v>
@@ -16271,10 +16301,10 @@
     </row>
     <row r="742" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A742" t="s">
-        <v>1454</v>
+        <v>1460</v>
       </c>
       <c r="B742" t="s">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="C742" s="2" t="s">
         <v>7</v>
@@ -16285,10 +16315,10 @@
     </row>
     <row r="743" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A743" t="s">
-        <v>1458</v>
+        <v>1462</v>
       </c>
       <c r="B743" t="s">
-        <v>1459</v>
+        <v>1463</v>
       </c>
       <c r="C743" s="2" t="s">
         <v>7</v>
@@ -16299,10 +16329,10 @@
     </row>
     <row r="744" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A744" t="s">
-        <v>1460</v>
+        <v>1466</v>
       </c>
       <c r="B744" t="s">
-        <v>1461</v>
+        <v>1467</v>
       </c>
       <c r="C744" s="2" t="s">
         <v>7</v>
@@ -16313,10 +16343,10 @@
     </row>
     <row r="745" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A745" t="s">
-        <v>1464</v>
+        <v>1468</v>
       </c>
       <c r="B745" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="C745" s="2" t="s">
         <v>7</v>
@@ -16327,10 +16357,10 @@
     </row>
     <row r="746" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A746" t="s">
-        <v>1466</v>
+        <v>1472</v>
       </c>
       <c r="B746" t="s">
-        <v>1467</v>
+        <v>1473</v>
       </c>
       <c r="C746" s="2" t="s">
         <v>7</v>
@@ -16341,10 +16371,10 @@
     </row>
     <row r="747" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A747" t="s">
-        <v>1468</v>
+        <v>1474</v>
       </c>
       <c r="B747" t="s">
-        <v>1469</v>
+        <v>1475</v>
       </c>
       <c r="C747" s="2" t="s">
         <v>7</v>
@@ -16355,10 +16385,10 @@
     </row>
     <row r="748" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A748" t="s">
-        <v>1470</v>
+        <v>1476</v>
       </c>
       <c r="B748" t="s">
-        <v>1471</v>
+        <v>1477</v>
       </c>
       <c r="C748" s="2" t="s">
         <v>7</v>
@@ -16369,10 +16399,10 @@
     </row>
     <row r="749" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A749" t="s">
-        <v>1472</v>
+        <v>1478</v>
       </c>
       <c r="B749" t="s">
-        <v>1473</v>
+        <v>1479</v>
       </c>
       <c r="C749" s="2" t="s">
         <v>7</v>
@@ -16383,10 +16413,10 @@
     </row>
     <row r="750" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A750" t="s">
-        <v>1474</v>
+        <v>1480</v>
       </c>
       <c r="B750" t="s">
-        <v>1475</v>
+        <v>1481</v>
       </c>
       <c r="C750" s="2" t="s">
         <v>7</v>
@@ -16397,10 +16427,10 @@
     </row>
     <row r="751" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A751" t="s">
-        <v>1478</v>
+        <v>1482</v>
       </c>
       <c r="B751" t="s">
-        <v>1479</v>
+        <v>1483</v>
       </c>
       <c r="C751" s="2" t="s">
         <v>7</v>
@@ -16411,10 +16441,10 @@
     </row>
     <row r="752" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A752" t="s">
-        <v>1482</v>
+        <v>1486</v>
       </c>
       <c r="B752" t="s">
-        <v>1483</v>
+        <v>1487</v>
       </c>
       <c r="C752" s="2" t="s">
         <v>7</v>
@@ -16425,10 +16455,10 @@
     </row>
     <row r="753" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A753" t="s">
-        <v>1484</v>
+        <v>1490</v>
       </c>
       <c r="B753" t="s">
-        <v>1485</v>
+        <v>1491</v>
       </c>
       <c r="C753" s="2" t="s">
         <v>7</v>
@@ -16439,10 +16469,10 @@
     </row>
     <row r="754" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A754" t="s">
-        <v>1486</v>
+        <v>1492</v>
       </c>
       <c r="B754" t="s">
-        <v>1487</v>
+        <v>1493</v>
       </c>
       <c r="C754" s="2" t="s">
         <v>7</v>
@@ -16453,10 +16483,10 @@
     </row>
     <row r="755" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A755" t="s">
-        <v>1488</v>
+        <v>1494</v>
       </c>
       <c r="B755" t="s">
-        <v>1489</v>
+        <v>1495</v>
       </c>
       <c r="C755" s="2" t="s">
         <v>7</v>
@@ -16467,10 +16497,10 @@
     </row>
     <row r="756" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A756" t="s">
-        <v>1490</v>
+        <v>1496</v>
       </c>
       <c r="B756" t="s">
-        <v>1491</v>
+        <v>1497</v>
       </c>
       <c r="C756" s="2" t="s">
         <v>7</v>
@@ -16481,10 +16511,10 @@
     </row>
     <row r="757" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A757" t="s">
-        <v>1492</v>
+        <v>1498</v>
       </c>
       <c r="B757" t="s">
-        <v>1493</v>
+        <v>1499</v>
       </c>
       <c r="C757" s="2" t="s">
         <v>7</v>
@@ -16495,10 +16525,10 @@
     </row>
     <row r="758" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A758" t="s">
-        <v>1494</v>
+        <v>1500</v>
       </c>
       <c r="B758" t="s">
-        <v>1495</v>
+        <v>1501</v>
       </c>
       <c r="C758" s="2" t="s">
         <v>7</v>
@@ -16509,10 +16539,10 @@
     </row>
     <row r="759" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A759" t="s">
-        <v>1496</v>
+        <v>1502</v>
       </c>
       <c r="B759" t="s">
-        <v>1497</v>
+        <v>1503</v>
       </c>
       <c r="C759" s="2" t="s">
         <v>7</v>
@@ -16523,10 +16553,10 @@
     </row>
     <row r="760" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A760" t="s">
-        <v>1498</v>
+        <v>1504</v>
       </c>
       <c r="B760" t="s">
-        <v>1499</v>
+        <v>1505</v>
       </c>
       <c r="C760" s="2" t="s">
         <v>7</v>
@@ -16537,10 +16567,10 @@
     </row>
     <row r="761" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A761" t="s">
-        <v>1500</v>
+        <v>1506</v>
       </c>
       <c r="B761" t="s">
-        <v>1501</v>
+        <v>1507</v>
       </c>
       <c r="C761" s="2" t="s">
         <v>7</v>
@@ -16551,10 +16581,10 @@
     </row>
     <row r="762" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A762" t="s">
-        <v>1502</v>
+        <v>1508</v>
       </c>
       <c r="B762" t="s">
-        <v>1503</v>
+        <v>1509</v>
       </c>
       <c r="C762" s="2" t="s">
         <v>7</v>
@@ -16565,10 +16595,10 @@
     </row>
     <row r="763" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A763" t="s">
-        <v>1504</v>
+        <v>1510</v>
       </c>
       <c r="B763" t="s">
-        <v>1505</v>
+        <v>1511</v>
       </c>
       <c r="C763" s="2" t="s">
         <v>7</v>
@@ -16579,10 +16609,10 @@
     </row>
     <row r="764" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A764" t="s">
-        <v>1506</v>
+        <v>1512</v>
       </c>
       <c r="B764" t="s">
-        <v>1507</v>
+        <v>1513</v>
       </c>
       <c r="C764" s="2" t="s">
         <v>7</v>
@@ -16593,10 +16623,10 @@
     </row>
     <row r="765" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A765" t="s">
-        <v>1508</v>
+        <v>1514</v>
       </c>
       <c r="B765" t="s">
-        <v>1509</v>
+        <v>1515</v>
       </c>
       <c r="C765" s="2" t="s">
         <v>7</v>
@@ -16607,10 +16637,10 @@
     </row>
     <row r="766" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A766" t="s">
-        <v>1510</v>
+        <v>1516</v>
       </c>
       <c r="B766" t="s">
-        <v>1511</v>
+        <v>1517</v>
       </c>
       <c r="C766" s="2" t="s">
         <v>7</v>
@@ -16621,10 +16651,10 @@
     </row>
     <row r="767" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A767" t="s">
-        <v>1512</v>
+        <v>1518</v>
       </c>
       <c r="B767" t="s">
-        <v>1513</v>
+        <v>1519</v>
       </c>
       <c r="C767" s="2" t="s">
         <v>7</v>
@@ -16635,10 +16665,10 @@
     </row>
     <row r="768" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A768" t="s">
-        <v>1514</v>
+        <v>1520</v>
       </c>
       <c r="B768" t="s">
-        <v>1515</v>
+        <v>1521</v>
       </c>
       <c r="C768" s="2" t="s">
         <v>7</v>
@@ -16649,10 +16679,10 @@
     </row>
     <row r="769" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A769" t="s">
-        <v>1516</v>
+        <v>1522</v>
       </c>
       <c r="B769" t="s">
-        <v>1517</v>
+        <v>1523</v>
       </c>
       <c r="C769" s="2" t="s">
         <v>7</v>
@@ -16663,10 +16693,10 @@
     </row>
     <row r="770" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A770" t="s">
-        <v>1518</v>
+        <v>1524</v>
       </c>
       <c r="B770" t="s">
-        <v>1519</v>
+        <v>1525</v>
       </c>
       <c r="C770" s="2" t="s">
         <v>7</v>
@@ -16677,10 +16707,10 @@
     </row>
     <row r="771" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A771" t="s">
-        <v>1520</v>
+        <v>1526</v>
       </c>
       <c r="B771" t="s">
-        <v>1521</v>
+        <v>1527</v>
       </c>
       <c r="C771" s="2" t="s">
         <v>7</v>
@@ -16691,10 +16721,10 @@
     </row>
     <row r="772" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A772" t="s">
-        <v>1522</v>
+        <v>1528</v>
       </c>
       <c r="B772" t="s">
-        <v>1523</v>
+        <v>1529</v>
       </c>
       <c r="C772" s="2" t="s">
         <v>7</v>
@@ -16705,10 +16735,10 @@
     </row>
     <row r="773" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A773" t="s">
-        <v>1524</v>
+        <v>1530</v>
       </c>
       <c r="B773" t="s">
-        <v>1525</v>
+        <v>1531</v>
       </c>
       <c r="C773" s="2" t="s">
         <v>7</v>
@@ -16719,10 +16749,10 @@
     </row>
     <row r="774" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A774" t="s">
-        <v>1526</v>
+        <v>1532</v>
       </c>
       <c r="B774" t="s">
-        <v>1527</v>
+        <v>1533</v>
       </c>
       <c r="C774" s="2" t="s">
         <v>7</v>
@@ -16733,10 +16763,10 @@
     </row>
     <row r="775" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A775" t="s">
-        <v>1528</v>
+        <v>1534</v>
       </c>
       <c r="B775" t="s">
-        <v>1529</v>
+        <v>1535</v>
       </c>
       <c r="C775" s="2" t="s">
         <v>7</v>
@@ -16747,10 +16777,10 @@
     </row>
     <row r="776" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A776" t="s">
-        <v>1530</v>
+        <v>1536</v>
       </c>
       <c r="B776" t="s">
-        <v>1531</v>
+        <v>1537</v>
       </c>
       <c r="C776" s="2" t="s">
         <v>7</v>
@@ -16761,10 +16791,10 @@
     </row>
     <row r="777" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A777" t="s">
-        <v>1532</v>
+        <v>1538</v>
       </c>
       <c r="B777" t="s">
-        <v>1533</v>
+        <v>1539</v>
       </c>
       <c r="C777" s="2" t="s">
         <v>7</v>
@@ -16775,10 +16805,10 @@
     </row>
     <row r="778" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A778" t="s">
-        <v>1534</v>
+        <v>1540</v>
       </c>
       <c r="B778" t="s">
-        <v>1535</v>
+        <v>1541</v>
       </c>
       <c r="C778" s="2" t="s">
         <v>7</v>
@@ -16789,10 +16819,10 @@
     </row>
     <row r="779" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A779" t="s">
-        <v>1536</v>
+        <v>1542</v>
       </c>
       <c r="B779" t="s">
-        <v>1537</v>
+        <v>1543</v>
       </c>
       <c r="C779" s="2" t="s">
         <v>7</v>
@@ -16803,10 +16833,10 @@
     </row>
     <row r="780" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A780" t="s">
-        <v>1538</v>
+        <v>1544</v>
       </c>
       <c r="B780" t="s">
-        <v>1539</v>
+        <v>1545</v>
       </c>
       <c r="C780" s="2" t="s">
         <v>7</v>
@@ -16817,10 +16847,10 @@
     </row>
     <row r="781" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A781" t="s">
-        <v>1540</v>
+        <v>1546</v>
       </c>
       <c r="B781" t="s">
-        <v>1541</v>
+        <v>1547</v>
       </c>
       <c r="C781" s="2" t="s">
         <v>7</v>
@@ -16831,10 +16861,10 @@
     </row>
     <row r="782" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A782" t="s">
-        <v>1542</v>
+        <v>1548</v>
       </c>
       <c r="B782" t="s">
-        <v>1543</v>
+        <v>1549</v>
       </c>
       <c r="C782" s="2" t="s">
         <v>7</v>
@@ -16845,10 +16875,10 @@
     </row>
     <row r="783" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A783" t="s">
-        <v>1544</v>
+        <v>1550</v>
       </c>
       <c r="B783" t="s">
-        <v>1545</v>
+        <v>1551</v>
       </c>
       <c r="C783" s="2" t="s">
         <v>7</v>
@@ -16859,10 +16889,10 @@
     </row>
     <row r="784" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A784" t="s">
-        <v>1546</v>
+        <v>1552</v>
       </c>
       <c r="B784" t="s">
-        <v>1547</v>
+        <v>1553</v>
       </c>
       <c r="C784" s="2" t="s">
         <v>7</v>
@@ -16873,10 +16903,10 @@
     </row>
     <row r="785" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A785" t="s">
-        <v>1548</v>
+        <v>1554</v>
       </c>
       <c r="B785" t="s">
-        <v>1549</v>
+        <v>1555</v>
       </c>
       <c r="C785" s="2" t="s">
         <v>7</v>
@@ -16887,10 +16917,10 @@
     </row>
     <row r="786" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A786" t="s">
-        <v>1550</v>
+        <v>1556</v>
       </c>
       <c r="B786" t="s">
-        <v>1551</v>
+        <v>1557</v>
       </c>
       <c r="C786" s="2" t="s">
         <v>7</v>
@@ -16901,10 +16931,10 @@
     </row>
     <row r="787" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A787" t="s">
-        <v>1552</v>
+        <v>1558</v>
       </c>
       <c r="B787" t="s">
-        <v>1553</v>
+        <v>1559</v>
       </c>
       <c r="C787" s="2" t="s">
         <v>7</v>
@@ -16915,10 +16945,10 @@
     </row>
     <row r="788" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A788" t="s">
-        <v>1554</v>
+        <v>1560</v>
       </c>
       <c r="B788" t="s">
-        <v>1555</v>
+        <v>1561</v>
       </c>
       <c r="C788" s="2" t="s">
         <v>7</v>
@@ -16929,10 +16959,10 @@
     </row>
     <row r="789" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A789" t="s">
-        <v>1556</v>
+        <v>1562</v>
       </c>
       <c r="B789" t="s">
-        <v>1557</v>
+        <v>1563</v>
       </c>
       <c r="C789" s="2" t="s">
         <v>7</v>
@@ -16943,10 +16973,10 @@
     </row>
     <row r="790" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A790" t="s">
-        <v>1558</v>
+        <v>1564</v>
       </c>
       <c r="B790" t="s">
-        <v>1559</v>
+        <v>1565</v>
       </c>
       <c r="C790" s="2" t="s">
         <v>7</v>
@@ -16957,10 +16987,10 @@
     </row>
     <row r="791" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A791" t="s">
-        <v>1560</v>
+        <v>1566</v>
       </c>
       <c r="B791" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="C791" s="2" t="s">
         <v>7</v>
@@ -16971,10 +17001,10 @@
     </row>
     <row r="792" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A792" t="s">
-        <v>1562</v>
+        <v>1568</v>
       </c>
       <c r="B792" t="s">
-        <v>1563</v>
+        <v>1569</v>
       </c>
       <c r="C792" s="2" t="s">
         <v>7</v>
@@ -16985,10 +17015,10 @@
     </row>
     <row r="793" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A793" t="s">
-        <v>1564</v>
+        <v>1570</v>
       </c>
       <c r="B793" t="s">
-        <v>1565</v>
+        <v>1571</v>
       </c>
       <c r="C793" s="2" t="s">
         <v>7</v>
@@ -16999,10 +17029,10 @@
     </row>
     <row r="794" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A794" t="s">
-        <v>1568</v>
+        <v>1572</v>
       </c>
       <c r="B794" t="s">
-        <v>1569</v>
+        <v>1573</v>
       </c>
       <c r="C794" s="2" t="s">
         <v>7</v>
@@ -17013,10 +17043,10 @@
     </row>
     <row r="795" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A795" t="s">
-        <v>1570</v>
+        <v>1576</v>
       </c>
       <c r="B795" t="s">
-        <v>1571</v>
+        <v>1577</v>
       </c>
       <c r="C795" s="2" t="s">
         <v>7</v>
@@ -17027,10 +17057,10 @@
     </row>
     <row r="796" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A796" t="s">
-        <v>1572</v>
+        <v>1578</v>
       </c>
       <c r="B796" t="s">
-        <v>1573</v>
+        <v>1579</v>
       </c>
       <c r="C796" s="2" t="s">
         <v>7</v>
@@ -17041,10 +17071,10 @@
     </row>
     <row r="797" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A797" t="s">
-        <v>1574</v>
+        <v>1580</v>
       </c>
       <c r="B797" t="s">
-        <v>1575</v>
+        <v>1581</v>
       </c>
       <c r="C797" s="2" t="s">
         <v>7</v>
@@ -17055,10 +17085,10 @@
     </row>
     <row r="798" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A798" t="s">
-        <v>1576</v>
+        <v>1582</v>
       </c>
       <c r="B798" t="s">
-        <v>1577</v>
+        <v>1583</v>
       </c>
       <c r="C798" s="2" t="s">
         <v>7</v>
@@ -17069,10 +17099,10 @@
     </row>
     <row r="799" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A799" t="s">
-        <v>1578</v>
+        <v>1584</v>
       </c>
       <c r="B799" t="s">
-        <v>1579</v>
+        <v>1585</v>
       </c>
       <c r="C799" s="2" t="s">
         <v>7</v>
@@ -17083,10 +17113,10 @@
     </row>
     <row r="800" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A800" t="s">
-        <v>1580</v>
+        <v>1586</v>
       </c>
       <c r="B800" t="s">
-        <v>1581</v>
+        <v>1587</v>
       </c>
       <c r="C800" s="2" t="s">
         <v>7</v>
@@ -17097,10 +17127,10 @@
     </row>
     <row r="801" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A801" t="s">
-        <v>1582</v>
+        <v>1588</v>
       </c>
       <c r="B801" t="s">
-        <v>1583</v>
+        <v>1589</v>
       </c>
       <c r="C801" s="2" t="s">
         <v>7</v>
@@ -17111,10 +17141,10 @@
     </row>
     <row r="802" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A802" t="s">
-        <v>1584</v>
+        <v>1590</v>
       </c>
       <c r="B802" t="s">
-        <v>1585</v>
+        <v>1591</v>
       </c>
       <c r="C802" s="2" t="s">
         <v>7</v>
@@ -17125,10 +17155,10 @@
     </row>
     <row r="803" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A803" t="s">
-        <v>1586</v>
+        <v>1592</v>
       </c>
       <c r="B803" t="s">
-        <v>1587</v>
+        <v>1593</v>
       </c>
       <c r="C803" s="2" t="s">
         <v>7</v>
@@ -17139,10 +17169,10 @@
     </row>
     <row r="804" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A804" t="s">
-        <v>1588</v>
+        <v>1594</v>
       </c>
       <c r="B804" t="s">
-        <v>1589</v>
+        <v>1595</v>
       </c>
       <c r="C804" s="2" t="s">
         <v>7</v>
@@ -17153,10 +17183,10 @@
     </row>
     <row r="805" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A805" t="s">
-        <v>1590</v>
+        <v>1596</v>
       </c>
       <c r="B805" t="s">
-        <v>1591</v>
+        <v>1597</v>
       </c>
       <c r="C805" s="2" t="s">
         <v>7</v>
@@ -17167,10 +17197,10 @@
     </row>
     <row r="806" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A806" t="s">
-        <v>1592</v>
+        <v>1598</v>
       </c>
       <c r="B806" t="s">
-        <v>1593</v>
+        <v>1599</v>
       </c>
       <c r="C806" s="2" t="s">
         <v>7</v>
@@ -17181,10 +17211,10 @@
     </row>
     <row r="807" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A807" t="s">
-        <v>1594</v>
+        <v>1600</v>
       </c>
       <c r="B807" t="s">
-        <v>1595</v>
+        <v>1601</v>
       </c>
       <c r="C807" s="2" t="s">
         <v>7</v>
@@ -17195,10 +17225,10 @@
     </row>
     <row r="808" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A808" t="s">
-        <v>1596</v>
+        <v>1602</v>
       </c>
       <c r="B808" t="s">
-        <v>1597</v>
+        <v>1603</v>
       </c>
       <c r="C808" s="2" t="s">
         <v>7</v>
@@ -17209,10 +17239,10 @@
     </row>
     <row r="809" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A809" t="s">
-        <v>1598</v>
+        <v>1604</v>
       </c>
       <c r="B809" t="s">
-        <v>1599</v>
+        <v>1605</v>
       </c>
       <c r="C809" s="2" t="s">
         <v>7</v>
@@ -17223,10 +17253,10 @@
     </row>
     <row r="810" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A810" t="s">
-        <v>1600</v>
+        <v>1606</v>
       </c>
       <c r="B810" t="s">
-        <v>1601</v>
+        <v>1607</v>
       </c>
       <c r="C810" s="2" t="s">
         <v>7</v>
@@ -17237,10 +17267,10 @@
     </row>
     <row r="811" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A811" t="s">
-        <v>1602</v>
+        <v>1608</v>
       </c>
       <c r="B811" t="s">
-        <v>1603</v>
+        <v>1609</v>
       </c>
       <c r="C811" s="2" t="s">
         <v>7</v>
@@ -17251,10 +17281,10 @@
     </row>
     <row r="812" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A812" t="s">
-        <v>1604</v>
+        <v>1610</v>
       </c>
       <c r="B812" t="s">
-        <v>1605</v>
+        <v>1611</v>
       </c>
       <c r="C812" s="2" t="s">
         <v>7</v>
@@ -17265,10 +17295,10 @@
     </row>
     <row r="813" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A813" t="s">
-        <v>1606</v>
+        <v>1612</v>
       </c>
       <c r="B813" t="s">
-        <v>1607</v>
+        <v>1613</v>
       </c>
       <c r="C813" s="2" t="s">
         <v>7</v>
@@ -17279,10 +17309,10 @@
     </row>
     <row r="814" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A814" t="s">
-        <v>1608</v>
+        <v>1614</v>
       </c>
       <c r="B814" t="s">
-        <v>1609</v>
+        <v>1615</v>
       </c>
       <c r="C814" s="2" t="s">
         <v>7</v>
@@ -17293,10 +17323,10 @@
     </row>
     <row r="815" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A815" t="s">
-        <v>1610</v>
+        <v>1616</v>
       </c>
       <c r="B815" t="s">
-        <v>1611</v>
+        <v>1617</v>
       </c>
       <c r="C815" s="2" t="s">
         <v>7</v>
@@ -17307,10 +17337,10 @@
     </row>
     <row r="816" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A816" t="s">
-        <v>1612</v>
+        <v>1618</v>
       </c>
       <c r="B816" t="s">
-        <v>1613</v>
+        <v>1619</v>
       </c>
       <c r="C816" s="2" t="s">
         <v>7</v>
@@ -17321,10 +17351,10 @@
     </row>
     <row r="817" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A817" t="s">
-        <v>1614</v>
+        <v>1620</v>
       </c>
       <c r="B817" t="s">
-        <v>1615</v>
+        <v>1621</v>
       </c>
       <c r="C817" s="2" t="s">
         <v>7</v>
@@ -17335,10 +17365,10 @@
     </row>
     <row r="818" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A818" t="s">
-        <v>1616</v>
+        <v>1622</v>
       </c>
       <c r="B818" t="s">
-        <v>1617</v>
+        <v>1623</v>
       </c>
       <c r="C818" s="2" t="s">
         <v>7</v>
@@ -17349,10 +17379,10 @@
     </row>
     <row r="819" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A819" t="s">
-        <v>1622</v>
+        <v>1624</v>
       </c>
       <c r="B819" t="s">
-        <v>1623</v>
+        <v>1625</v>
       </c>
       <c r="C819" s="2" t="s">
         <v>7</v>
@@ -17363,10 +17393,10 @@
     </row>
     <row r="820" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A820" t="s">
-        <v>1624</v>
+        <v>1630</v>
       </c>
       <c r="B820" t="s">
-        <v>1625</v>
+        <v>1631</v>
       </c>
       <c r="C820" s="2" t="s">
         <v>7</v>
@@ -17377,10 +17407,10 @@
     </row>
     <row r="821" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A821" t="s">
-        <v>1626</v>
+        <v>1632</v>
       </c>
       <c r="B821" t="s">
-        <v>1627</v>
+        <v>1633</v>
       </c>
       <c r="C821" s="2" t="s">
         <v>7</v>
@@ -17391,10 +17421,10 @@
     </row>
     <row r="822" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A822" t="s">
-        <v>1628</v>
+        <v>1634</v>
       </c>
       <c r="B822" t="s">
-        <v>1629</v>
+        <v>1635</v>
       </c>
       <c r="C822" s="2" t="s">
         <v>7</v>
@@ -17405,10 +17435,10 @@
     </row>
     <row r="823" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A823" t="s">
-        <v>1630</v>
+        <v>1636</v>
       </c>
       <c r="B823" t="s">
-        <v>1631</v>
+        <v>1637</v>
       </c>
       <c r="C823" s="2" t="s">
         <v>7</v>
@@ -17419,10 +17449,10 @@
     </row>
     <row r="824" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A824" t="s">
-        <v>1636</v>
+        <v>1638</v>
       </c>
       <c r="B824" t="s">
-        <v>1637</v>
+        <v>1639</v>
       </c>
       <c r="C824" s="2" t="s">
         <v>7</v>
@@ -17433,10 +17463,10 @@
     </row>
     <row r="825" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A825" t="s">
-        <v>1638</v>
+        <v>1644</v>
       </c>
       <c r="B825" t="s">
-        <v>1639</v>
+        <v>1645</v>
       </c>
       <c r="C825" s="2" t="s">
         <v>7</v>
@@ -17447,10 +17477,10 @@
     </row>
     <row r="826" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A826" t="s">
-        <v>1640</v>
+        <v>1646</v>
       </c>
       <c r="B826" t="s">
-        <v>1641</v>
+        <v>1647</v>
       </c>
       <c r="C826" s="2" t="s">
         <v>7</v>
@@ -17461,10 +17491,10 @@
     </row>
     <row r="827" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A827" t="s">
-        <v>1642</v>
+        <v>1648</v>
       </c>
       <c r="B827" t="s">
-        <v>1643</v>
+        <v>1649</v>
       </c>
       <c r="C827" s="2" t="s">
         <v>7</v>
@@ -17475,10 +17505,10 @@
     </row>
     <row r="828" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A828" t="s">
-        <v>1644</v>
+        <v>1650</v>
       </c>
       <c r="B828" t="s">
-        <v>1645</v>
+        <v>1651</v>
       </c>
       <c r="C828" s="2" t="s">
         <v>7</v>
@@ -17489,10 +17519,10 @@
     </row>
     <row r="829" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A829" t="s">
-        <v>1646</v>
+        <v>1652</v>
       </c>
       <c r="B829" t="s">
-        <v>1647</v>
+        <v>1653</v>
       </c>
       <c r="C829" s="2" t="s">
         <v>7</v>
@@ -17503,10 +17533,10 @@
     </row>
     <row r="830" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A830" t="s">
-        <v>1648</v>
+        <v>1654</v>
       </c>
       <c r="B830" t="s">
-        <v>1649</v>
+        <v>1655</v>
       </c>
       <c r="C830" s="2" t="s">
         <v>7</v>
@@ -17517,10 +17547,10 @@
     </row>
     <row r="831" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A831" t="s">
-        <v>1650</v>
+        <v>1656</v>
       </c>
       <c r="B831" t="s">
-        <v>1651</v>
+        <v>1657</v>
       </c>
       <c r="C831" s="2" t="s">
         <v>7</v>
@@ -17531,10 +17561,10 @@
     </row>
     <row r="832" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A832" t="s">
-        <v>1654</v>
+        <v>1658</v>
       </c>
       <c r="B832" t="s">
-        <v>1655</v>
+        <v>1659</v>
       </c>
       <c r="C832" s="2" t="s">
         <v>7</v>
@@ -17545,10 +17575,10 @@
     </row>
     <row r="833" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A833" t="s">
-        <v>1656</v>
+        <v>1662</v>
       </c>
       <c r="B833" t="s">
-        <v>1657</v>
+        <v>1663</v>
       </c>
       <c r="C833" s="2" t="s">
         <v>7</v>
@@ -17559,10 +17589,10 @@
     </row>
     <row r="834" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A834" t="s">
-        <v>1658</v>
+        <v>1664</v>
       </c>
       <c r="B834" t="s">
-        <v>1659</v>
+        <v>1665</v>
       </c>
       <c r="C834" s="2" t="s">
         <v>7</v>
@@ -17573,10 +17603,10 @@
     </row>
     <row r="835" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A835" t="s">
-        <v>1660</v>
+        <v>1666</v>
       </c>
       <c r="B835" t="s">
-        <v>1661</v>
+        <v>1667</v>
       </c>
       <c r="C835" s="2" t="s">
         <v>7</v>
@@ -17587,10 +17617,10 @@
     </row>
     <row r="836" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A836" t="s">
-        <v>1662</v>
+        <v>1668</v>
       </c>
       <c r="B836" t="s">
-        <v>1663</v>
+        <v>1669</v>
       </c>
       <c r="C836" s="2" t="s">
         <v>7</v>
@@ -17601,10 +17631,10 @@
     </row>
     <row r="837" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A837" t="s">
-        <v>1664</v>
+        <v>1670</v>
       </c>
       <c r="B837" t="s">
-        <v>1665</v>
+        <v>1671</v>
       </c>
       <c r="C837" s="2" t="s">
         <v>7</v>
@@ -17615,10 +17645,10 @@
     </row>
     <row r="838" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A838" t="s">
-        <v>1666</v>
+        <v>1672</v>
       </c>
       <c r="B838" t="s">
-        <v>1667</v>
+        <v>1673</v>
       </c>
       <c r="C838" s="2" t="s">
         <v>7</v>
@@ -17629,10 +17659,10 @@
     </row>
     <row r="839" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A839" t="s">
-        <v>1668</v>
+        <v>1674</v>
       </c>
       <c r="B839" t="s">
-        <v>1669</v>
+        <v>1675</v>
       </c>
       <c r="C839" s="2" t="s">
         <v>7</v>
@@ -17643,10 +17673,10 @@
     </row>
     <row r="840" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A840" t="s">
-        <v>1670</v>
+        <v>1676</v>
       </c>
       <c r="B840" t="s">
-        <v>1671</v>
+        <v>1677</v>
       </c>
       <c r="C840" s="2" t="s">
         <v>7</v>
@@ -17657,10 +17687,10 @@
     </row>
     <row r="841" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A841" t="s">
-        <v>1674</v>
+        <v>1678</v>
       </c>
       <c r="B841" t="s">
-        <v>1675</v>
+        <v>1679</v>
       </c>
       <c r="C841" s="2" t="s">
         <v>7</v>
@@ -17671,10 +17701,10 @@
     </row>
     <row r="842" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A842" t="s">
-        <v>1676</v>
+        <v>1682</v>
       </c>
       <c r="B842" t="s">
-        <v>1677</v>
+        <v>1683</v>
       </c>
       <c r="C842" s="2" t="s">
         <v>7</v>
@@ -17685,10 +17715,10 @@
     </row>
     <row r="843" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A843" t="s">
-        <v>1678</v>
+        <v>1684</v>
       </c>
       <c r="B843" t="s">
-        <v>1679</v>
+        <v>1685</v>
       </c>
       <c r="C843" s="2" t="s">
         <v>7</v>
@@ -17699,10 +17729,10 @@
     </row>
     <row r="844" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A844" t="s">
-        <v>1680</v>
+        <v>1686</v>
       </c>
       <c r="B844" t="s">
-        <v>1681</v>
+        <v>1687</v>
       </c>
       <c r="C844" s="2" t="s">
         <v>7</v>
@@ -17713,10 +17743,10 @@
     </row>
     <row r="845" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A845" t="s">
-        <v>1682</v>
+        <v>1688</v>
       </c>
       <c r="B845" t="s">
-        <v>1683</v>
+        <v>1689</v>
       </c>
       <c r="C845" s="2" t="s">
         <v>7</v>
@@ -17727,10 +17757,10 @@
     </row>
     <row r="846" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A846" t="s">
-        <v>1684</v>
+        <v>1692</v>
       </c>
       <c r="B846" t="s">
-        <v>1685</v>
+        <v>1693</v>
       </c>
       <c r="C846" s="2" t="s">
         <v>7</v>
@@ -17741,10 +17771,10 @@
     </row>
     <row r="847" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A847" t="s">
-        <v>1686</v>
+        <v>1694</v>
       </c>
       <c r="B847" t="s">
-        <v>1687</v>
+        <v>1695</v>
       </c>
       <c r="C847" s="2" t="s">
         <v>7</v>
@@ -17755,10 +17785,10 @@
     </row>
     <row r="848" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A848" t="s">
-        <v>1688</v>
+        <v>1696</v>
       </c>
       <c r="B848" t="s">
-        <v>1689</v>
+        <v>1697</v>
       </c>
       <c r="C848" s="2" t="s">
         <v>7</v>
@@ -17769,10 +17799,10 @@
     </row>
     <row r="849" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A849" t="s">
-        <v>1690</v>
+        <v>1698</v>
       </c>
       <c r="B849" t="s">
-        <v>1691</v>
+        <v>1699</v>
       </c>
       <c r="C849" s="2" t="s">
         <v>7</v>
@@ -17783,10 +17813,10 @@
     </row>
     <row r="850" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A850" t="s">
-        <v>1692</v>
+        <v>1700</v>
       </c>
       <c r="B850" t="s">
-        <v>1693</v>
+        <v>1701</v>
       </c>
       <c r="C850" s="2" t="s">
         <v>7</v>
@@ -17797,10 +17827,10 @@
     </row>
     <row r="851" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A851" t="s">
-        <v>1694</v>
+        <v>1702</v>
       </c>
       <c r="B851" t="s">
-        <v>1695</v>
+        <v>1703</v>
       </c>
       <c r="C851" s="2" t="s">
         <v>7</v>
@@ -17811,10 +17841,10 @@
     </row>
     <row r="852" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A852" t="s">
-        <v>1698</v>
+        <v>1704</v>
       </c>
       <c r="B852" t="s">
-        <v>1699</v>
+        <v>1705</v>
       </c>
       <c r="C852" s="2" t="s">
         <v>7</v>
@@ -17825,10 +17855,10 @@
     </row>
     <row r="853" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A853" t="s">
-        <v>1700</v>
+        <v>1708</v>
       </c>
       <c r="B853" t="s">
-        <v>1701</v>
+        <v>1709</v>
       </c>
       <c r="C853" s="2" t="s">
         <v>7</v>
@@ -17839,10 +17869,10 @@
     </row>
     <row r="854" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A854" t="s">
-        <v>1702</v>
+        <v>1710</v>
       </c>
       <c r="B854" t="s">
-        <v>1703</v>
+        <v>1711</v>
       </c>
       <c r="C854" s="2" t="s">
         <v>7</v>
@@ -17853,10 +17883,10 @@
     </row>
     <row r="855" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A855" t="s">
-        <v>1704</v>
+        <v>1712</v>
       </c>
       <c r="B855" t="s">
-        <v>1705</v>
+        <v>1713</v>
       </c>
       <c r="C855" s="2" t="s">
         <v>7</v>
@@ -17867,10 +17897,10 @@
     </row>
     <row r="856" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A856" t="s">
-        <v>1706</v>
+        <v>1714</v>
       </c>
       <c r="B856" t="s">
-        <v>1707</v>
+        <v>1715</v>
       </c>
       <c r="C856" s="2" t="s">
         <v>7</v>
@@ -17881,10 +17911,10 @@
     </row>
     <row r="857" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A857" t="s">
-        <v>1708</v>
+        <v>1716</v>
       </c>
       <c r="B857" t="s">
-        <v>1709</v>
+        <v>1717</v>
       </c>
       <c r="C857" s="2" t="s">
         <v>7</v>
@@ -17895,10 +17925,10 @@
     </row>
     <row r="858" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A858" t="s">
-        <v>1710</v>
+        <v>1718</v>
       </c>
       <c r="B858" t="s">
-        <v>1711</v>
+        <v>1719</v>
       </c>
       <c r="C858" s="2" t="s">
         <v>7</v>
@@ -17909,10 +17939,10 @@
     </row>
     <row r="859" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A859" t="s">
-        <v>1712</v>
+        <v>1720</v>
       </c>
       <c r="B859" t="s">
-        <v>1713</v>
+        <v>1721</v>
       </c>
       <c r="C859" s="2" t="s">
         <v>7</v>
@@ -17923,10 +17953,10 @@
     </row>
     <row r="860" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A860" t="s">
-        <v>1714</v>
+        <v>1722</v>
       </c>
       <c r="B860" t="s">
-        <v>1715</v>
+        <v>1723</v>
       </c>
       <c r="C860" s="2" t="s">
         <v>7</v>
@@ -17937,10 +17967,10 @@
     </row>
     <row r="861" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A861" t="s">
-        <v>1718</v>
+        <v>1724</v>
       </c>
       <c r="B861" t="s">
-        <v>1719</v>
+        <v>1725</v>
       </c>
       <c r="C861" s="2" t="s">
         <v>7</v>
@@ -17951,10 +17981,10 @@
     </row>
     <row r="862" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A862" t="s">
-        <v>1720</v>
+        <v>1726</v>
       </c>
       <c r="B862" t="s">
-        <v>1721</v>
+        <v>1727</v>
       </c>
       <c r="C862" s="2" t="s">
         <v>7</v>
@@ -17965,10 +17995,10 @@
     </row>
     <row r="863" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A863" t="s">
-        <v>1722</v>
+        <v>1728</v>
       </c>
       <c r="B863" t="s">
-        <v>1723</v>
+        <v>1729</v>
       </c>
       <c r="C863" s="2" t="s">
         <v>7</v>
@@ -17979,10 +18009,10 @@
     </row>
     <row r="864" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A864" t="s">
-        <v>1724</v>
+        <v>1730</v>
       </c>
       <c r="B864" t="s">
-        <v>1725</v>
+        <v>1731</v>
       </c>
       <c r="C864" s="2" t="s">
         <v>7</v>
@@ -17993,10 +18023,10 @@
     </row>
     <row r="865" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A865" t="s">
-        <v>1726</v>
+        <v>1732</v>
       </c>
       <c r="B865" t="s">
-        <v>1727</v>
+        <v>1733</v>
       </c>
       <c r="C865" s="2" t="s">
         <v>7</v>
@@ -18007,10 +18037,10 @@
     </row>
     <row r="866" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A866" t="s">
-        <v>1728</v>
+        <v>1734</v>
       </c>
       <c r="B866" t="s">
-        <v>1729</v>
+        <v>1735</v>
       </c>
       <c r="C866" s="2" t="s">
         <v>7</v>
@@ -18021,10 +18051,10 @@
     </row>
     <row r="867" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A867" t="s">
-        <v>1730</v>
+        <v>1736</v>
       </c>
       <c r="B867" t="s">
-        <v>1731</v>
+        <v>1737</v>
       </c>
       <c r="C867" s="2" t="s">
         <v>7</v>
@@ -18035,10 +18065,10 @@
     </row>
     <row r="868" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A868" t="s">
-        <v>1732</v>
+        <v>1738</v>
       </c>
       <c r="B868" t="s">
-        <v>1733</v>
+        <v>1739</v>
       </c>
       <c r="C868" s="2" t="s">
         <v>7</v>
@@ -18049,10 +18079,10 @@
     </row>
     <row r="869" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A869" t="s">
-        <v>1734</v>
+        <v>1740</v>
       </c>
       <c r="B869" t="s">
-        <v>1735</v>
+        <v>1741</v>
       </c>
       <c r="C869" s="2" t="s">
         <v>7</v>
@@ -18063,10 +18093,10 @@
     </row>
     <row r="870" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A870" t="s">
-        <v>1736</v>
+        <v>1742</v>
       </c>
       <c r="B870" t="s">
-        <v>1737</v>
+        <v>1743</v>
       </c>
       <c r="C870" s="2" t="s">
         <v>7</v>
@@ -18077,10 +18107,10 @@
     </row>
     <row r="871" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A871" t="s">
-        <v>1738</v>
+        <v>1744</v>
       </c>
       <c r="B871" t="s">
-        <v>1739</v>
+        <v>1745</v>
       </c>
       <c r="C871" s="2" t="s">
         <v>7</v>
@@ -18091,10 +18121,10 @@
     </row>
     <row r="872" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A872" t="s">
-        <v>1740</v>
+        <v>1746</v>
       </c>
       <c r="B872" t="s">
-        <v>1741</v>
+        <v>1747</v>
       </c>
       <c r="C872" s="2" t="s">
         <v>7</v>
@@ -18105,10 +18135,10 @@
     </row>
     <row r="873" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A873" t="s">
-        <v>1744</v>
+        <v>1748</v>
       </c>
       <c r="B873" t="s">
-        <v>1745</v>
+        <v>1749</v>
       </c>
       <c r="C873" s="2" t="s">
         <v>7</v>
@@ -18119,10 +18149,10 @@
     </row>
     <row r="874" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A874" t="s">
-        <v>1746</v>
+        <v>1750</v>
       </c>
       <c r="B874" t="s">
-        <v>1747</v>
+        <v>1751</v>
       </c>
       <c r="C874" s="2" t="s">
         <v>7</v>
@@ -18133,10 +18163,10 @@
     </row>
     <row r="875" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A875" t="s">
-        <v>1748</v>
+        <v>1754</v>
       </c>
       <c r="B875" t="s">
-        <v>1749</v>
+        <v>1755</v>
       </c>
       <c r="C875" s="2" t="s">
         <v>7</v>
@@ -18147,10 +18177,10 @@
     </row>
     <row r="876" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A876" t="s">
-        <v>1750</v>
+        <v>1756</v>
       </c>
       <c r="B876" t="s">
-        <v>1751</v>
+        <v>1757</v>
       </c>
       <c r="C876" s="2" t="s">
         <v>7</v>
@@ -18161,10 +18191,10 @@
     </row>
     <row r="877" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A877" t="s">
-        <v>1752</v>
+        <v>1758</v>
       </c>
       <c r="B877" t="s">
-        <v>1753</v>
+        <v>1759</v>
       </c>
       <c r="C877" s="2" t="s">
         <v>7</v>
@@ -18175,10 +18205,10 @@
     </row>
     <row r="878" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A878" t="s">
-        <v>1756</v>
+        <v>1760</v>
       </c>
       <c r="B878" t="s">
-        <v>1757</v>
+        <v>1761</v>
       </c>
       <c r="C878" s="2" t="s">
         <v>7</v>
@@ -18189,10 +18219,10 @@
     </row>
     <row r="879" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A879" t="s">
-        <v>1758</v>
+        <v>1762</v>
       </c>
       <c r="B879" t="s">
-        <v>1759</v>
+        <v>1763</v>
       </c>
       <c r="C879" s="2" t="s">
         <v>7</v>
@@ -18203,10 +18233,10 @@
     </row>
     <row r="880" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A880" t="s">
-        <v>1760</v>
+        <v>1766</v>
       </c>
       <c r="B880" t="s">
-        <v>1761</v>
+        <v>1767</v>
       </c>
       <c r="C880" s="2" t="s">
         <v>7</v>
@@ -18217,10 +18247,10 @@
     </row>
     <row r="881" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A881" t="s">
-        <v>1764</v>
+        <v>1768</v>
       </c>
       <c r="B881" t="s">
-        <v>1765</v>
+        <v>1769</v>
       </c>
       <c r="C881" s="2" t="s">
         <v>7</v>
@@ -18231,10 +18261,10 @@
     </row>
     <row r="882" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A882" t="s">
-        <v>1766</v>
+        <v>1770</v>
       </c>
       <c r="B882" t="s">
-        <v>1767</v>
+        <v>1771</v>
       </c>
       <c r="C882" s="2" t="s">
         <v>7</v>
@@ -18245,10 +18275,10 @@
     </row>
     <row r="883" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A883" t="s">
-        <v>1768</v>
+        <v>1774</v>
       </c>
       <c r="B883" t="s">
-        <v>1769</v>
+        <v>1775</v>
       </c>
       <c r="C883" s="2" t="s">
         <v>7</v>
@@ -18259,10 +18289,10 @@
     </row>
     <row r="884" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A884" t="s">
-        <v>1770</v>
+        <v>1776</v>
       </c>
       <c r="B884" t="s">
-        <v>1771</v>
+        <v>1777</v>
       </c>
       <c r="C884" s="2" t="s">
         <v>7</v>
@@ -18273,10 +18303,10 @@
     </row>
     <row r="885" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A885" t="s">
-        <v>1772</v>
+        <v>1778</v>
       </c>
       <c r="B885" t="s">
-        <v>1773</v>
+        <v>1779</v>
       </c>
       <c r="C885" s="2" t="s">
         <v>7</v>
@@ -18287,10 +18317,10 @@
     </row>
     <row r="886" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A886" t="s">
-        <v>1774</v>
+        <v>1780</v>
       </c>
       <c r="B886" t="s">
-        <v>1775</v>
+        <v>1781</v>
       </c>
       <c r="C886" s="2" t="s">
         <v>7</v>
@@ -18301,10 +18331,10 @@
     </row>
     <row r="887" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A887" t="s">
-        <v>1776</v>
+        <v>1782</v>
       </c>
       <c r="B887" t="s">
-        <v>1777</v>
+        <v>1783</v>
       </c>
       <c r="C887" s="2" t="s">
         <v>7</v>
@@ -18315,10 +18345,10 @@
     </row>
     <row r="888" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A888" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="B888" t="s">
-        <v>1779</v>
+        <v>1785</v>
       </c>
       <c r="C888" s="2" t="s">
         <v>7</v>
@@ -18329,10 +18359,10 @@
     </row>
     <row r="889" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A889" t="s">
-        <v>1780</v>
+        <v>1786</v>
       </c>
       <c r="B889" t="s">
-        <v>1781</v>
+        <v>1787</v>
       </c>
       <c r="C889" s="2" t="s">
         <v>7</v>
@@ -18343,10 +18373,10 @@
     </row>
     <row r="890" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A890" t="s">
-        <v>1782</v>
+        <v>1788</v>
       </c>
       <c r="B890" t="s">
-        <v>1783</v>
+        <v>1789</v>
       </c>
       <c r="C890" s="2" t="s">
         <v>7</v>
@@ -18357,10 +18387,10 @@
     </row>
     <row r="891" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A891" t="s">
-        <v>1784</v>
+        <v>1790</v>
       </c>
       <c r="B891" t="s">
-        <v>1785</v>
+        <v>1791</v>
       </c>
       <c r="C891" s="2" t="s">
         <v>7</v>
@@ -18371,10 +18401,10 @@
     </row>
     <row r="892" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A892" t="s">
-        <v>1786</v>
+        <v>1792</v>
       </c>
       <c r="B892" t="s">
-        <v>1787</v>
+        <v>1793</v>
       </c>
       <c r="C892" s="2" t="s">
         <v>7</v>
@@ -18385,10 +18415,10 @@
     </row>
     <row r="893" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A893" t="s">
-        <v>1788</v>
+        <v>1794</v>
       </c>
       <c r="B893" t="s">
-        <v>1789</v>
+        <v>1795</v>
       </c>
       <c r="C893" s="2" t="s">
         <v>7</v>
@@ -18399,10 +18429,10 @@
     </row>
     <row r="894" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A894" t="s">
-        <v>1792</v>
+        <v>1796</v>
       </c>
       <c r="B894" t="s">
-        <v>1793</v>
+        <v>1797</v>
       </c>
       <c r="C894" s="2" t="s">
         <v>7</v>
@@ -18413,10 +18443,10 @@
     </row>
     <row r="895" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A895" t="s">
-        <v>1794</v>
+        <v>1798</v>
       </c>
       <c r="B895" t="s">
-        <v>1795</v>
+        <v>1799</v>
       </c>
       <c r="C895" s="2" t="s">
         <v>7</v>
@@ -18427,10 +18457,10 @@
     </row>
     <row r="896" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A896" t="s">
-        <v>1796</v>
+        <v>1802</v>
       </c>
       <c r="B896" t="s">
-        <v>1797</v>
+        <v>1803</v>
       </c>
       <c r="C896" s="2" t="s">
         <v>7</v>
@@ -18441,10 +18471,10 @@
     </row>
     <row r="897" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A897" t="s">
-        <v>1798</v>
+        <v>1804</v>
       </c>
       <c r="B897" t="s">
-        <v>1799</v>
+        <v>1805</v>
       </c>
       <c r="C897" s="2" t="s">
         <v>7</v>
@@ -18455,10 +18485,10 @@
     </row>
     <row r="898" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A898" t="s">
-        <v>1800</v>
+        <v>1806</v>
       </c>
       <c r="B898" t="s">
-        <v>1801</v>
+        <v>1807</v>
       </c>
       <c r="C898" s="2" t="s">
         <v>7</v>
@@ -18469,10 +18499,10 @@
     </row>
     <row r="899" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A899" t="s">
-        <v>1802</v>
+        <v>1808</v>
       </c>
       <c r="B899" t="s">
-        <v>1803</v>
+        <v>1809</v>
       </c>
       <c r="C899" s="2" t="s">
         <v>7</v>
@@ -18483,10 +18513,10 @@
     </row>
     <row r="900" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A900" t="s">
-        <v>1804</v>
+        <v>1810</v>
       </c>
       <c r="B900" t="s">
-        <v>1805</v>
+        <v>1811</v>
       </c>
       <c r="C900" s="2" t="s">
         <v>7</v>
@@ -18497,10 +18527,10 @@
     </row>
     <row r="901" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A901" t="s">
-        <v>1806</v>
+        <v>1812</v>
       </c>
       <c r="B901" t="s">
-        <v>1807</v>
+        <v>1813</v>
       </c>
       <c r="C901" s="2" t="s">
         <v>7</v>
@@ -18511,10 +18541,10 @@
     </row>
     <row r="902" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A902" t="s">
-        <v>1808</v>
+        <v>1814</v>
       </c>
       <c r="B902" t="s">
-        <v>1809</v>
+        <v>1815</v>
       </c>
       <c r="C902" s="2" t="s">
         <v>7</v>
@@ -18525,10 +18555,10 @@
     </row>
     <row r="903" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A903" t="s">
-        <v>1810</v>
+        <v>1816</v>
       </c>
       <c r="B903" t="s">
-        <v>1811</v>
+        <v>1817</v>
       </c>
       <c r="C903" s="2" t="s">
         <v>7</v>
@@ -18539,10 +18569,10 @@
     </row>
     <row r="904" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A904" t="s">
-        <v>1812</v>
+        <v>1818</v>
       </c>
       <c r="B904" t="s">
-        <v>1813</v>
+        <v>1819</v>
       </c>
       <c r="C904" s="2" t="s">
         <v>7</v>
@@ -18553,10 +18583,10 @@
     </row>
     <row r="905" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A905" t="s">
-        <v>1814</v>
+        <v>1820</v>
       </c>
       <c r="B905" t="s">
-        <v>1815</v>
+        <v>1821</v>
       </c>
       <c r="C905" s="2" t="s">
         <v>7</v>
@@ -18567,10 +18597,10 @@
     </row>
     <row r="906" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A906" t="s">
-        <v>1370</v>
+        <v>1822</v>
       </c>
       <c r="B906" t="s">
-        <v>1371</v>
+        <v>1823</v>
       </c>
       <c r="C906" s="2" t="s">
         <v>7</v>
@@ -18581,26 +18611,96 @@
     </row>
     <row r="907" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A907" t="s">
-        <v>1716</v>
+        <v>1824</v>
       </c>
       <c r="B907" t="s">
-        <v>1717</v>
+        <v>1825</v>
       </c>
       <c r="C907" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D907" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="908" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A908" t="s">
+        <v>548</v>
+      </c>
+      <c r="B908" t="s">
+        <v>549</v>
+      </c>
+      <c r="C908" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D908" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="909" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A909" t="s">
+        <v>800</v>
+      </c>
+      <c r="B909" t="s">
+        <v>801</v>
+      </c>
+      <c r="C909" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D909" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="910" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A910" t="s">
+        <v>876</v>
+      </c>
+      <c r="B910" t="s">
+        <v>877</v>
+      </c>
+      <c r="C910" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D910" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="911" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A911" t="s">
+        <v>958</v>
+      </c>
+      <c r="B911" t="s">
+        <v>959</v>
+      </c>
+      <c r="C911" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D911" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="912" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A912" t="s">
+        <v>1690</v>
+      </c>
+      <c r="B912" t="s">
+        <v>1691</v>
+      </c>
+      <c r="C912" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D912" t="s">
         <v>8</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F907">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F912">
       <sortCondition ref="E1"/>
     </sortState>
   </autoFilter>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="D2:E907" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D2:E912" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"X"</formula1>
     </dataValidation>
   </dataValidations>
@@ -18877,640 +18977,645 @@
     <hyperlink ref="C310" r:id="rId270" xr:uid="{00000000-0004-0000-0000-00000D010000}"/>
     <hyperlink ref="C25" r:id="rId271" xr:uid="{00000000-0004-0000-0000-00000E010000}"/>
     <hyperlink ref="C311" r:id="rId272" xr:uid="{00000000-0004-0000-0000-00000F010000}"/>
-    <hyperlink ref="C312" r:id="rId273" xr:uid="{00000000-0004-0000-0000-000010010000}"/>
-    <hyperlink ref="C313" r:id="rId274" xr:uid="{00000000-0004-0000-0000-000011010000}"/>
-    <hyperlink ref="C314" r:id="rId275" xr:uid="{00000000-0004-0000-0000-000012010000}"/>
-    <hyperlink ref="C315" r:id="rId276" xr:uid="{00000000-0004-0000-0000-000013010000}"/>
-    <hyperlink ref="C316" r:id="rId277" xr:uid="{00000000-0004-0000-0000-000014010000}"/>
-    <hyperlink ref="C26" r:id="rId278" xr:uid="{00000000-0004-0000-0000-000015010000}"/>
-    <hyperlink ref="C317" r:id="rId279" xr:uid="{00000000-0004-0000-0000-000016010000}"/>
-    <hyperlink ref="C318" r:id="rId280" xr:uid="{00000000-0004-0000-0000-000017010000}"/>
-    <hyperlink ref="C319" r:id="rId281" xr:uid="{00000000-0004-0000-0000-000018010000}"/>
-    <hyperlink ref="C320" r:id="rId282" xr:uid="{00000000-0004-0000-0000-000019010000}"/>
-    <hyperlink ref="C321" r:id="rId283" xr:uid="{00000000-0004-0000-0000-00001A010000}"/>
-    <hyperlink ref="C322" r:id="rId284" xr:uid="{00000000-0004-0000-0000-00001B010000}"/>
-    <hyperlink ref="C323" r:id="rId285" xr:uid="{00000000-0004-0000-0000-00001C010000}"/>
-    <hyperlink ref="C324" r:id="rId286" xr:uid="{00000000-0004-0000-0000-00001D010000}"/>
-    <hyperlink ref="C325" r:id="rId287" xr:uid="{00000000-0004-0000-0000-00001E010000}"/>
-    <hyperlink ref="C27" r:id="rId288" xr:uid="{00000000-0004-0000-0000-00001F010000}"/>
-    <hyperlink ref="C326" r:id="rId289" xr:uid="{00000000-0004-0000-0000-000020010000}"/>
-    <hyperlink ref="C28" r:id="rId290" xr:uid="{00000000-0004-0000-0000-000021010000}"/>
-    <hyperlink ref="C327" r:id="rId291" xr:uid="{00000000-0004-0000-0000-000022010000}"/>
-    <hyperlink ref="C328" r:id="rId292" xr:uid="{00000000-0004-0000-0000-000023010000}"/>
-    <hyperlink ref="C329" r:id="rId293" xr:uid="{00000000-0004-0000-0000-000024010000}"/>
-    <hyperlink ref="C330" r:id="rId294" xr:uid="{00000000-0004-0000-0000-000025010000}"/>
-    <hyperlink ref="C331" r:id="rId295" xr:uid="{00000000-0004-0000-0000-000026010000}"/>
-    <hyperlink ref="C332" r:id="rId296" xr:uid="{00000000-0004-0000-0000-000027010000}"/>
-    <hyperlink ref="C333" r:id="rId297" xr:uid="{00000000-0004-0000-0000-000028010000}"/>
-    <hyperlink ref="C334" r:id="rId298" xr:uid="{00000000-0004-0000-0000-000029010000}"/>
-    <hyperlink ref="C335" r:id="rId299" xr:uid="{00000000-0004-0000-0000-00002A010000}"/>
-    <hyperlink ref="C336" r:id="rId300" xr:uid="{00000000-0004-0000-0000-00002B010000}"/>
-    <hyperlink ref="C337" r:id="rId301" xr:uid="{00000000-0004-0000-0000-00002C010000}"/>
-    <hyperlink ref="C338" r:id="rId302" xr:uid="{00000000-0004-0000-0000-00002D010000}"/>
-    <hyperlink ref="C339" r:id="rId303" xr:uid="{00000000-0004-0000-0000-00002E010000}"/>
-    <hyperlink ref="C340" r:id="rId304" xr:uid="{00000000-0004-0000-0000-00002F010000}"/>
-    <hyperlink ref="C341" r:id="rId305" xr:uid="{00000000-0004-0000-0000-000030010000}"/>
-    <hyperlink ref="C342" r:id="rId306" xr:uid="{00000000-0004-0000-0000-000031010000}"/>
-    <hyperlink ref="C343" r:id="rId307" xr:uid="{00000000-0004-0000-0000-000032010000}"/>
-    <hyperlink ref="C344" r:id="rId308" xr:uid="{00000000-0004-0000-0000-000033010000}"/>
-    <hyperlink ref="C345" r:id="rId309" xr:uid="{00000000-0004-0000-0000-000034010000}"/>
-    <hyperlink ref="C29" r:id="rId310" xr:uid="{00000000-0004-0000-0000-000035010000}"/>
-    <hyperlink ref="C346" r:id="rId311" xr:uid="{00000000-0004-0000-0000-000036010000}"/>
-    <hyperlink ref="C347" r:id="rId312" xr:uid="{00000000-0004-0000-0000-000037010000}"/>
-    <hyperlink ref="C348" r:id="rId313" xr:uid="{00000000-0004-0000-0000-000038010000}"/>
-    <hyperlink ref="C349" r:id="rId314" xr:uid="{00000000-0004-0000-0000-000039010000}"/>
-    <hyperlink ref="C350" r:id="rId315" xr:uid="{00000000-0004-0000-0000-00003A010000}"/>
-    <hyperlink ref="C351" r:id="rId316" xr:uid="{00000000-0004-0000-0000-00003B010000}"/>
-    <hyperlink ref="C352" r:id="rId317" xr:uid="{00000000-0004-0000-0000-00003C010000}"/>
-    <hyperlink ref="C353" r:id="rId318" xr:uid="{00000000-0004-0000-0000-00003D010000}"/>
-    <hyperlink ref="C354" r:id="rId319" xr:uid="{00000000-0004-0000-0000-00003E010000}"/>
-    <hyperlink ref="C30" r:id="rId320" xr:uid="{00000000-0004-0000-0000-00003F010000}"/>
-    <hyperlink ref="C355" r:id="rId321" xr:uid="{00000000-0004-0000-0000-000040010000}"/>
-    <hyperlink ref="C356" r:id="rId322" xr:uid="{00000000-0004-0000-0000-000041010000}"/>
-    <hyperlink ref="C357" r:id="rId323" xr:uid="{00000000-0004-0000-0000-000042010000}"/>
-    <hyperlink ref="C358" r:id="rId324" xr:uid="{00000000-0004-0000-0000-000043010000}"/>
-    <hyperlink ref="C359" r:id="rId325" xr:uid="{00000000-0004-0000-0000-000044010000}"/>
-    <hyperlink ref="C360" r:id="rId326" xr:uid="{00000000-0004-0000-0000-000045010000}"/>
-    <hyperlink ref="C361" r:id="rId327" xr:uid="{00000000-0004-0000-0000-000046010000}"/>
-    <hyperlink ref="C362" r:id="rId328" xr:uid="{00000000-0004-0000-0000-000047010000}"/>
-    <hyperlink ref="C363" r:id="rId329" xr:uid="{00000000-0004-0000-0000-000048010000}"/>
-    <hyperlink ref="C364" r:id="rId330" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
-    <hyperlink ref="C365" r:id="rId331" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
-    <hyperlink ref="C366" r:id="rId332" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
-    <hyperlink ref="C367" r:id="rId333" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
-    <hyperlink ref="C368" r:id="rId334" xr:uid="{00000000-0004-0000-0000-00004D010000}"/>
-    <hyperlink ref="C369" r:id="rId335" xr:uid="{00000000-0004-0000-0000-00004E010000}"/>
-    <hyperlink ref="C370" r:id="rId336" xr:uid="{00000000-0004-0000-0000-00004F010000}"/>
-    <hyperlink ref="C371" r:id="rId337" xr:uid="{00000000-0004-0000-0000-000050010000}"/>
-    <hyperlink ref="C372" r:id="rId338" xr:uid="{00000000-0004-0000-0000-000051010000}"/>
-    <hyperlink ref="C373" r:id="rId339" xr:uid="{00000000-0004-0000-0000-000052010000}"/>
-    <hyperlink ref="C374" r:id="rId340" xr:uid="{00000000-0004-0000-0000-000053010000}"/>
-    <hyperlink ref="C375" r:id="rId341" xr:uid="{00000000-0004-0000-0000-000054010000}"/>
-    <hyperlink ref="C376" r:id="rId342" xr:uid="{00000000-0004-0000-0000-000055010000}"/>
-    <hyperlink ref="C377" r:id="rId343" xr:uid="{00000000-0004-0000-0000-000056010000}"/>
-    <hyperlink ref="C378" r:id="rId344" xr:uid="{00000000-0004-0000-0000-000057010000}"/>
-    <hyperlink ref="C379" r:id="rId345" xr:uid="{00000000-0004-0000-0000-000058010000}"/>
-    <hyperlink ref="C380" r:id="rId346" xr:uid="{00000000-0004-0000-0000-000059010000}"/>
-    <hyperlink ref="C381" r:id="rId347" xr:uid="{00000000-0004-0000-0000-00005A010000}"/>
-    <hyperlink ref="C382" r:id="rId348" xr:uid="{00000000-0004-0000-0000-00005B010000}"/>
-    <hyperlink ref="C383" r:id="rId349" xr:uid="{00000000-0004-0000-0000-00005C010000}"/>
-    <hyperlink ref="C384" r:id="rId350" xr:uid="{00000000-0004-0000-0000-00005D010000}"/>
-    <hyperlink ref="C31" r:id="rId351" xr:uid="{00000000-0004-0000-0000-00005E010000}"/>
-    <hyperlink ref="C32" r:id="rId352" xr:uid="{00000000-0004-0000-0000-00005F010000}"/>
-    <hyperlink ref="C385" r:id="rId353" xr:uid="{00000000-0004-0000-0000-000060010000}"/>
-    <hyperlink ref="C386" r:id="rId354" xr:uid="{00000000-0004-0000-0000-000061010000}"/>
-    <hyperlink ref="C387" r:id="rId355" xr:uid="{00000000-0004-0000-0000-000062010000}"/>
-    <hyperlink ref="C388" r:id="rId356" xr:uid="{00000000-0004-0000-0000-000063010000}"/>
-    <hyperlink ref="C389" r:id="rId357" xr:uid="{00000000-0004-0000-0000-000064010000}"/>
-    <hyperlink ref="C33" r:id="rId358" xr:uid="{00000000-0004-0000-0000-000065010000}"/>
-    <hyperlink ref="C390" r:id="rId359" xr:uid="{00000000-0004-0000-0000-000066010000}"/>
-    <hyperlink ref="C391" r:id="rId360" xr:uid="{00000000-0004-0000-0000-000067010000}"/>
-    <hyperlink ref="C392" r:id="rId361" xr:uid="{00000000-0004-0000-0000-000068010000}"/>
-    <hyperlink ref="C393" r:id="rId362" xr:uid="{00000000-0004-0000-0000-000069010000}"/>
-    <hyperlink ref="C394" r:id="rId363" xr:uid="{00000000-0004-0000-0000-00006A010000}"/>
-    <hyperlink ref="C395" r:id="rId364" xr:uid="{00000000-0004-0000-0000-00006B010000}"/>
-    <hyperlink ref="C396" r:id="rId365" xr:uid="{00000000-0004-0000-0000-00006C010000}"/>
-    <hyperlink ref="C397" r:id="rId366" xr:uid="{00000000-0004-0000-0000-00006D010000}"/>
-    <hyperlink ref="C398" r:id="rId367" xr:uid="{00000000-0004-0000-0000-00006E010000}"/>
-    <hyperlink ref="C399" r:id="rId368" xr:uid="{00000000-0004-0000-0000-00006F010000}"/>
-    <hyperlink ref="C400" r:id="rId369" xr:uid="{00000000-0004-0000-0000-000070010000}"/>
-    <hyperlink ref="C401" r:id="rId370" xr:uid="{00000000-0004-0000-0000-000071010000}"/>
-    <hyperlink ref="C402" r:id="rId371" xr:uid="{00000000-0004-0000-0000-000072010000}"/>
-    <hyperlink ref="C403" r:id="rId372" xr:uid="{00000000-0004-0000-0000-000073010000}"/>
-    <hyperlink ref="C404" r:id="rId373" xr:uid="{00000000-0004-0000-0000-000074010000}"/>
-    <hyperlink ref="C405" r:id="rId374" xr:uid="{00000000-0004-0000-0000-000075010000}"/>
-    <hyperlink ref="C406" r:id="rId375" xr:uid="{00000000-0004-0000-0000-000076010000}"/>
-    <hyperlink ref="C407" r:id="rId376" xr:uid="{00000000-0004-0000-0000-000077010000}"/>
-    <hyperlink ref="C408" r:id="rId377" xr:uid="{00000000-0004-0000-0000-000078010000}"/>
-    <hyperlink ref="C409" r:id="rId378" xr:uid="{00000000-0004-0000-0000-000079010000}"/>
-    <hyperlink ref="C410" r:id="rId379" xr:uid="{00000000-0004-0000-0000-00007A010000}"/>
-    <hyperlink ref="C411" r:id="rId380" xr:uid="{00000000-0004-0000-0000-00007B010000}"/>
-    <hyperlink ref="C412" r:id="rId381" xr:uid="{00000000-0004-0000-0000-00007C010000}"/>
-    <hyperlink ref="C413" r:id="rId382" xr:uid="{00000000-0004-0000-0000-00007D010000}"/>
-    <hyperlink ref="C414" r:id="rId383" xr:uid="{00000000-0004-0000-0000-00007E010000}"/>
-    <hyperlink ref="C415" r:id="rId384" xr:uid="{00000000-0004-0000-0000-00007F010000}"/>
-    <hyperlink ref="C416" r:id="rId385" xr:uid="{00000000-0004-0000-0000-000080010000}"/>
-    <hyperlink ref="C417" r:id="rId386" xr:uid="{00000000-0004-0000-0000-000081010000}"/>
-    <hyperlink ref="C418" r:id="rId387" xr:uid="{00000000-0004-0000-0000-000082010000}"/>
-    <hyperlink ref="C419" r:id="rId388" xr:uid="{00000000-0004-0000-0000-000083010000}"/>
-    <hyperlink ref="C420" r:id="rId389" xr:uid="{00000000-0004-0000-0000-000084010000}"/>
-    <hyperlink ref="C421" r:id="rId390" xr:uid="{00000000-0004-0000-0000-000085010000}"/>
-    <hyperlink ref="C422" r:id="rId391" xr:uid="{00000000-0004-0000-0000-000086010000}"/>
-    <hyperlink ref="C423" r:id="rId392" xr:uid="{00000000-0004-0000-0000-000087010000}"/>
-    <hyperlink ref="C424" r:id="rId393" xr:uid="{00000000-0004-0000-0000-000088010000}"/>
-    <hyperlink ref="C425" r:id="rId394" xr:uid="{00000000-0004-0000-0000-000089010000}"/>
-    <hyperlink ref="C426" r:id="rId395" xr:uid="{00000000-0004-0000-0000-00008A010000}"/>
-    <hyperlink ref="C427" r:id="rId396" xr:uid="{00000000-0004-0000-0000-00008B010000}"/>
-    <hyperlink ref="C428" r:id="rId397" xr:uid="{00000000-0004-0000-0000-00008C010000}"/>
-    <hyperlink ref="C429" r:id="rId398" xr:uid="{00000000-0004-0000-0000-00008D010000}"/>
-    <hyperlink ref="C430" r:id="rId399" xr:uid="{00000000-0004-0000-0000-00008E010000}"/>
-    <hyperlink ref="C431" r:id="rId400" xr:uid="{00000000-0004-0000-0000-00008F010000}"/>
-    <hyperlink ref="C432" r:id="rId401" xr:uid="{00000000-0004-0000-0000-000090010000}"/>
-    <hyperlink ref="C433" r:id="rId402" xr:uid="{00000000-0004-0000-0000-000091010000}"/>
-    <hyperlink ref="C434" r:id="rId403" xr:uid="{00000000-0004-0000-0000-000092010000}"/>
-    <hyperlink ref="C435" r:id="rId404" xr:uid="{00000000-0004-0000-0000-000093010000}"/>
-    <hyperlink ref="C436" r:id="rId405" xr:uid="{00000000-0004-0000-0000-000094010000}"/>
-    <hyperlink ref="C437" r:id="rId406" xr:uid="{00000000-0004-0000-0000-000095010000}"/>
-    <hyperlink ref="C438" r:id="rId407" xr:uid="{00000000-0004-0000-0000-000096010000}"/>
-    <hyperlink ref="C439" r:id="rId408" xr:uid="{00000000-0004-0000-0000-000097010000}"/>
-    <hyperlink ref="C440" r:id="rId409" xr:uid="{00000000-0004-0000-0000-000098010000}"/>
-    <hyperlink ref="C441" r:id="rId410" xr:uid="{00000000-0004-0000-0000-000099010000}"/>
-    <hyperlink ref="C442" r:id="rId411" xr:uid="{00000000-0004-0000-0000-00009A010000}"/>
-    <hyperlink ref="C34" r:id="rId412" xr:uid="{00000000-0004-0000-0000-00009B010000}"/>
-    <hyperlink ref="C443" r:id="rId413" xr:uid="{00000000-0004-0000-0000-00009C010000}"/>
-    <hyperlink ref="C444" r:id="rId414" xr:uid="{00000000-0004-0000-0000-00009D010000}"/>
-    <hyperlink ref="C445" r:id="rId415" xr:uid="{00000000-0004-0000-0000-00009E010000}"/>
-    <hyperlink ref="C446" r:id="rId416" xr:uid="{00000000-0004-0000-0000-00009F010000}"/>
-    <hyperlink ref="C447" r:id="rId417" xr:uid="{00000000-0004-0000-0000-0000A0010000}"/>
-    <hyperlink ref="C448" r:id="rId418" xr:uid="{00000000-0004-0000-0000-0000A1010000}"/>
-    <hyperlink ref="C449" r:id="rId419" xr:uid="{00000000-0004-0000-0000-0000A2010000}"/>
-    <hyperlink ref="C450" r:id="rId420" xr:uid="{00000000-0004-0000-0000-0000A3010000}"/>
-    <hyperlink ref="C451" r:id="rId421" xr:uid="{00000000-0004-0000-0000-0000A4010000}"/>
-    <hyperlink ref="C452" r:id="rId422" xr:uid="{00000000-0004-0000-0000-0000A5010000}"/>
-    <hyperlink ref="C453" r:id="rId423" xr:uid="{00000000-0004-0000-0000-0000A6010000}"/>
-    <hyperlink ref="C454" r:id="rId424" xr:uid="{00000000-0004-0000-0000-0000A7010000}"/>
-    <hyperlink ref="C455" r:id="rId425" xr:uid="{00000000-0004-0000-0000-0000A8010000}"/>
-    <hyperlink ref="C456" r:id="rId426" xr:uid="{00000000-0004-0000-0000-0000A9010000}"/>
-    <hyperlink ref="C457" r:id="rId427" xr:uid="{00000000-0004-0000-0000-0000AA010000}"/>
-    <hyperlink ref="C458" r:id="rId428" xr:uid="{00000000-0004-0000-0000-0000AB010000}"/>
-    <hyperlink ref="C459" r:id="rId429" xr:uid="{00000000-0004-0000-0000-0000AC010000}"/>
-    <hyperlink ref="C460" r:id="rId430" xr:uid="{00000000-0004-0000-0000-0000AD010000}"/>
-    <hyperlink ref="C461" r:id="rId431" xr:uid="{00000000-0004-0000-0000-0000AE010000}"/>
-    <hyperlink ref="C462" r:id="rId432" xr:uid="{00000000-0004-0000-0000-0000AF010000}"/>
-    <hyperlink ref="C463" r:id="rId433" xr:uid="{00000000-0004-0000-0000-0000B0010000}"/>
-    <hyperlink ref="C464" r:id="rId434" xr:uid="{00000000-0004-0000-0000-0000B1010000}"/>
-    <hyperlink ref="C465" r:id="rId435" xr:uid="{00000000-0004-0000-0000-0000B2010000}"/>
-    <hyperlink ref="C466" r:id="rId436" xr:uid="{00000000-0004-0000-0000-0000B3010000}"/>
-    <hyperlink ref="C467" r:id="rId437" xr:uid="{00000000-0004-0000-0000-0000B4010000}"/>
-    <hyperlink ref="C468" r:id="rId438" xr:uid="{00000000-0004-0000-0000-0000B5010000}"/>
-    <hyperlink ref="C469" r:id="rId439" xr:uid="{00000000-0004-0000-0000-0000B6010000}"/>
-    <hyperlink ref="C470" r:id="rId440" xr:uid="{00000000-0004-0000-0000-0000B7010000}"/>
-    <hyperlink ref="C471" r:id="rId441" xr:uid="{00000000-0004-0000-0000-0000B8010000}"/>
-    <hyperlink ref="C472" r:id="rId442" xr:uid="{00000000-0004-0000-0000-0000B9010000}"/>
-    <hyperlink ref="C473" r:id="rId443" xr:uid="{00000000-0004-0000-0000-0000BA010000}"/>
-    <hyperlink ref="C474" r:id="rId444" xr:uid="{00000000-0004-0000-0000-0000BB010000}"/>
-    <hyperlink ref="C475" r:id="rId445" xr:uid="{00000000-0004-0000-0000-0000BC010000}"/>
-    <hyperlink ref="C476" r:id="rId446" xr:uid="{00000000-0004-0000-0000-0000BD010000}"/>
-    <hyperlink ref="C477" r:id="rId447" xr:uid="{00000000-0004-0000-0000-0000BE010000}"/>
-    <hyperlink ref="C478" r:id="rId448" xr:uid="{00000000-0004-0000-0000-0000BF010000}"/>
-    <hyperlink ref="C479" r:id="rId449" xr:uid="{00000000-0004-0000-0000-0000C0010000}"/>
-    <hyperlink ref="C480" r:id="rId450" xr:uid="{00000000-0004-0000-0000-0000C1010000}"/>
-    <hyperlink ref="C481" r:id="rId451" xr:uid="{00000000-0004-0000-0000-0000C2010000}"/>
-    <hyperlink ref="C482" r:id="rId452" xr:uid="{00000000-0004-0000-0000-0000C3010000}"/>
-    <hyperlink ref="C483" r:id="rId453" xr:uid="{00000000-0004-0000-0000-0000C4010000}"/>
-    <hyperlink ref="C484" r:id="rId454" xr:uid="{00000000-0004-0000-0000-0000C5010000}"/>
-    <hyperlink ref="C485" r:id="rId455" xr:uid="{00000000-0004-0000-0000-0000C6010000}"/>
-    <hyperlink ref="C486" r:id="rId456" xr:uid="{00000000-0004-0000-0000-0000C7010000}"/>
-    <hyperlink ref="C487" r:id="rId457" xr:uid="{00000000-0004-0000-0000-0000C8010000}"/>
-    <hyperlink ref="C488" r:id="rId458" xr:uid="{00000000-0004-0000-0000-0000C9010000}"/>
-    <hyperlink ref="C489" r:id="rId459" xr:uid="{00000000-0004-0000-0000-0000CA010000}"/>
-    <hyperlink ref="C490" r:id="rId460" xr:uid="{00000000-0004-0000-0000-0000CB010000}"/>
-    <hyperlink ref="C35" r:id="rId461" xr:uid="{00000000-0004-0000-0000-0000CC010000}"/>
-    <hyperlink ref="C491" r:id="rId462" xr:uid="{00000000-0004-0000-0000-0000CD010000}"/>
-    <hyperlink ref="C492" r:id="rId463" xr:uid="{00000000-0004-0000-0000-0000CE010000}"/>
-    <hyperlink ref="C493" r:id="rId464" xr:uid="{00000000-0004-0000-0000-0000CF010000}"/>
-    <hyperlink ref="C494" r:id="rId465" xr:uid="{00000000-0004-0000-0000-0000D0010000}"/>
-    <hyperlink ref="C495" r:id="rId466" xr:uid="{00000000-0004-0000-0000-0000D1010000}"/>
-    <hyperlink ref="C496" r:id="rId467" xr:uid="{00000000-0004-0000-0000-0000D2010000}"/>
-    <hyperlink ref="C497" r:id="rId468" xr:uid="{00000000-0004-0000-0000-0000D3010000}"/>
-    <hyperlink ref="C498" r:id="rId469" xr:uid="{00000000-0004-0000-0000-0000D4010000}"/>
-    <hyperlink ref="C36" r:id="rId470" xr:uid="{00000000-0004-0000-0000-0000D5010000}"/>
-    <hyperlink ref="C499" r:id="rId471" xr:uid="{00000000-0004-0000-0000-0000D6010000}"/>
-    <hyperlink ref="C500" r:id="rId472" xr:uid="{00000000-0004-0000-0000-0000D7010000}"/>
-    <hyperlink ref="C501" r:id="rId473" xr:uid="{00000000-0004-0000-0000-0000D8010000}"/>
-    <hyperlink ref="C502" r:id="rId474" xr:uid="{00000000-0004-0000-0000-0000D9010000}"/>
-    <hyperlink ref="C503" r:id="rId475" xr:uid="{00000000-0004-0000-0000-0000DA010000}"/>
-    <hyperlink ref="C504" r:id="rId476" xr:uid="{00000000-0004-0000-0000-0000DB010000}"/>
-    <hyperlink ref="C505" r:id="rId477" xr:uid="{00000000-0004-0000-0000-0000DC010000}"/>
-    <hyperlink ref="C506" r:id="rId478" xr:uid="{00000000-0004-0000-0000-0000DD010000}"/>
-    <hyperlink ref="C507" r:id="rId479" xr:uid="{00000000-0004-0000-0000-0000DE010000}"/>
-    <hyperlink ref="C508" r:id="rId480" xr:uid="{00000000-0004-0000-0000-0000DF010000}"/>
-    <hyperlink ref="C509" r:id="rId481" xr:uid="{00000000-0004-0000-0000-0000E0010000}"/>
-    <hyperlink ref="C510" r:id="rId482" xr:uid="{00000000-0004-0000-0000-0000E1010000}"/>
-    <hyperlink ref="C511" r:id="rId483" xr:uid="{00000000-0004-0000-0000-0000E2010000}"/>
-    <hyperlink ref="C512" r:id="rId484" xr:uid="{00000000-0004-0000-0000-0000E3010000}"/>
-    <hyperlink ref="C513" r:id="rId485" xr:uid="{00000000-0004-0000-0000-0000E4010000}"/>
-    <hyperlink ref="C514" r:id="rId486" xr:uid="{00000000-0004-0000-0000-0000E5010000}"/>
-    <hyperlink ref="C515" r:id="rId487" xr:uid="{00000000-0004-0000-0000-0000E6010000}"/>
-    <hyperlink ref="C516" r:id="rId488" xr:uid="{00000000-0004-0000-0000-0000E7010000}"/>
-    <hyperlink ref="C517" r:id="rId489" xr:uid="{00000000-0004-0000-0000-0000E8010000}"/>
-    <hyperlink ref="C518" r:id="rId490" xr:uid="{00000000-0004-0000-0000-0000E9010000}"/>
-    <hyperlink ref="C519" r:id="rId491" xr:uid="{00000000-0004-0000-0000-0000EA010000}"/>
-    <hyperlink ref="C37" r:id="rId492" xr:uid="{00000000-0004-0000-0000-0000EB010000}"/>
-    <hyperlink ref="C520" r:id="rId493" xr:uid="{00000000-0004-0000-0000-0000EC010000}"/>
-    <hyperlink ref="C521" r:id="rId494" xr:uid="{00000000-0004-0000-0000-0000ED010000}"/>
-    <hyperlink ref="C522" r:id="rId495" xr:uid="{00000000-0004-0000-0000-0000EE010000}"/>
-    <hyperlink ref="C523" r:id="rId496" xr:uid="{00000000-0004-0000-0000-0000EF010000}"/>
-    <hyperlink ref="C524" r:id="rId497" xr:uid="{00000000-0004-0000-0000-0000F0010000}"/>
-    <hyperlink ref="C525" r:id="rId498" xr:uid="{00000000-0004-0000-0000-0000F1010000}"/>
-    <hyperlink ref="C38" r:id="rId499" xr:uid="{00000000-0004-0000-0000-0000F2010000}"/>
-    <hyperlink ref="C526" r:id="rId500" xr:uid="{00000000-0004-0000-0000-0000F3010000}"/>
-    <hyperlink ref="C527" r:id="rId501" xr:uid="{00000000-0004-0000-0000-0000F4010000}"/>
-    <hyperlink ref="C528" r:id="rId502" xr:uid="{00000000-0004-0000-0000-0000F5010000}"/>
-    <hyperlink ref="C529" r:id="rId503" xr:uid="{00000000-0004-0000-0000-0000F6010000}"/>
-    <hyperlink ref="C530" r:id="rId504" xr:uid="{00000000-0004-0000-0000-0000F7010000}"/>
-    <hyperlink ref="C531" r:id="rId505" xr:uid="{00000000-0004-0000-0000-0000F8010000}"/>
-    <hyperlink ref="C532" r:id="rId506" xr:uid="{00000000-0004-0000-0000-0000F9010000}"/>
-    <hyperlink ref="C533" r:id="rId507" xr:uid="{00000000-0004-0000-0000-0000FA010000}"/>
-    <hyperlink ref="C534" r:id="rId508" xr:uid="{00000000-0004-0000-0000-0000FB010000}"/>
-    <hyperlink ref="C535" r:id="rId509" xr:uid="{00000000-0004-0000-0000-0000FC010000}"/>
-    <hyperlink ref="C536" r:id="rId510" xr:uid="{00000000-0004-0000-0000-0000FD010000}"/>
-    <hyperlink ref="C537" r:id="rId511" xr:uid="{00000000-0004-0000-0000-0000FE010000}"/>
-    <hyperlink ref="C538" r:id="rId512" xr:uid="{00000000-0004-0000-0000-0000FF010000}"/>
-    <hyperlink ref="C39" r:id="rId513" xr:uid="{00000000-0004-0000-0000-000000020000}"/>
-    <hyperlink ref="C539" r:id="rId514" xr:uid="{00000000-0004-0000-0000-000001020000}"/>
-    <hyperlink ref="C540" r:id="rId515" xr:uid="{00000000-0004-0000-0000-000002020000}"/>
-    <hyperlink ref="C541" r:id="rId516" xr:uid="{00000000-0004-0000-0000-000003020000}"/>
-    <hyperlink ref="C542" r:id="rId517" xr:uid="{00000000-0004-0000-0000-000004020000}"/>
-    <hyperlink ref="C543" r:id="rId518" xr:uid="{00000000-0004-0000-0000-000005020000}"/>
-    <hyperlink ref="C544" r:id="rId519" xr:uid="{00000000-0004-0000-0000-000006020000}"/>
-    <hyperlink ref="C545" r:id="rId520" xr:uid="{00000000-0004-0000-0000-000007020000}"/>
-    <hyperlink ref="C546" r:id="rId521" xr:uid="{00000000-0004-0000-0000-000008020000}"/>
-    <hyperlink ref="C547" r:id="rId522" xr:uid="{00000000-0004-0000-0000-000009020000}"/>
-    <hyperlink ref="C548" r:id="rId523" xr:uid="{00000000-0004-0000-0000-00000A020000}"/>
-    <hyperlink ref="C40" r:id="rId524" xr:uid="{00000000-0004-0000-0000-00000B020000}"/>
-    <hyperlink ref="C549" r:id="rId525" xr:uid="{00000000-0004-0000-0000-00000C020000}"/>
-    <hyperlink ref="C550" r:id="rId526" xr:uid="{00000000-0004-0000-0000-00000D020000}"/>
-    <hyperlink ref="C41" r:id="rId527" xr:uid="{00000000-0004-0000-0000-00000E020000}"/>
-    <hyperlink ref="C551" r:id="rId528" xr:uid="{00000000-0004-0000-0000-00000F020000}"/>
-    <hyperlink ref="C552" r:id="rId529" xr:uid="{00000000-0004-0000-0000-000010020000}"/>
-    <hyperlink ref="C553" r:id="rId530" xr:uid="{00000000-0004-0000-0000-000011020000}"/>
-    <hyperlink ref="C554" r:id="rId531" xr:uid="{00000000-0004-0000-0000-000012020000}"/>
-    <hyperlink ref="C555" r:id="rId532" xr:uid="{00000000-0004-0000-0000-000013020000}"/>
-    <hyperlink ref="C556" r:id="rId533" xr:uid="{00000000-0004-0000-0000-000014020000}"/>
-    <hyperlink ref="C557" r:id="rId534" xr:uid="{00000000-0004-0000-0000-000015020000}"/>
-    <hyperlink ref="C558" r:id="rId535" xr:uid="{00000000-0004-0000-0000-000016020000}"/>
-    <hyperlink ref="C559" r:id="rId536" xr:uid="{00000000-0004-0000-0000-000017020000}"/>
-    <hyperlink ref="C560" r:id="rId537" xr:uid="{00000000-0004-0000-0000-000018020000}"/>
-    <hyperlink ref="C561" r:id="rId538" xr:uid="{00000000-0004-0000-0000-000019020000}"/>
-    <hyperlink ref="C562" r:id="rId539" xr:uid="{00000000-0004-0000-0000-00001A020000}"/>
-    <hyperlink ref="C563" r:id="rId540" xr:uid="{00000000-0004-0000-0000-00001B020000}"/>
-    <hyperlink ref="C564" r:id="rId541" xr:uid="{00000000-0004-0000-0000-00001C020000}"/>
-    <hyperlink ref="C565" r:id="rId542" xr:uid="{00000000-0004-0000-0000-00001D020000}"/>
-    <hyperlink ref="C566" r:id="rId543" xr:uid="{00000000-0004-0000-0000-00001E020000}"/>
-    <hyperlink ref="C567" r:id="rId544" xr:uid="{00000000-0004-0000-0000-00001F020000}"/>
-    <hyperlink ref="C568" r:id="rId545" xr:uid="{00000000-0004-0000-0000-000020020000}"/>
-    <hyperlink ref="C569" r:id="rId546" xr:uid="{00000000-0004-0000-0000-000021020000}"/>
-    <hyperlink ref="C570" r:id="rId547" xr:uid="{00000000-0004-0000-0000-000022020000}"/>
-    <hyperlink ref="C571" r:id="rId548" xr:uid="{00000000-0004-0000-0000-000023020000}"/>
-    <hyperlink ref="C572" r:id="rId549" xr:uid="{00000000-0004-0000-0000-000024020000}"/>
-    <hyperlink ref="C573" r:id="rId550" xr:uid="{00000000-0004-0000-0000-000025020000}"/>
-    <hyperlink ref="C574" r:id="rId551" xr:uid="{00000000-0004-0000-0000-000026020000}"/>
-    <hyperlink ref="C575" r:id="rId552" xr:uid="{00000000-0004-0000-0000-000027020000}"/>
-    <hyperlink ref="C576" r:id="rId553" xr:uid="{00000000-0004-0000-0000-000028020000}"/>
-    <hyperlink ref="C577" r:id="rId554" xr:uid="{00000000-0004-0000-0000-000029020000}"/>
-    <hyperlink ref="C578" r:id="rId555" xr:uid="{00000000-0004-0000-0000-00002A020000}"/>
-    <hyperlink ref="C579" r:id="rId556" xr:uid="{00000000-0004-0000-0000-00002B020000}"/>
-    <hyperlink ref="C580" r:id="rId557" xr:uid="{00000000-0004-0000-0000-00002C020000}"/>
-    <hyperlink ref="C581" r:id="rId558" xr:uid="{00000000-0004-0000-0000-00002D020000}"/>
-    <hyperlink ref="C582" r:id="rId559" xr:uid="{00000000-0004-0000-0000-00002E020000}"/>
-    <hyperlink ref="C583" r:id="rId560" xr:uid="{00000000-0004-0000-0000-00002F020000}"/>
-    <hyperlink ref="C584" r:id="rId561" xr:uid="{00000000-0004-0000-0000-000030020000}"/>
-    <hyperlink ref="C585" r:id="rId562" xr:uid="{00000000-0004-0000-0000-000031020000}"/>
-    <hyperlink ref="C586" r:id="rId563" xr:uid="{00000000-0004-0000-0000-000032020000}"/>
-    <hyperlink ref="C587" r:id="rId564" xr:uid="{00000000-0004-0000-0000-000033020000}"/>
-    <hyperlink ref="C588" r:id="rId565" xr:uid="{00000000-0004-0000-0000-000034020000}"/>
-    <hyperlink ref="C589" r:id="rId566" xr:uid="{00000000-0004-0000-0000-000035020000}"/>
-    <hyperlink ref="C590" r:id="rId567" xr:uid="{00000000-0004-0000-0000-000036020000}"/>
-    <hyperlink ref="C591" r:id="rId568" xr:uid="{00000000-0004-0000-0000-000037020000}"/>
-    <hyperlink ref="C592" r:id="rId569" xr:uid="{00000000-0004-0000-0000-000038020000}"/>
-    <hyperlink ref="C593" r:id="rId570" xr:uid="{00000000-0004-0000-0000-000039020000}"/>
-    <hyperlink ref="C594" r:id="rId571" xr:uid="{00000000-0004-0000-0000-00003A020000}"/>
-    <hyperlink ref="C595" r:id="rId572" xr:uid="{00000000-0004-0000-0000-00003B020000}"/>
-    <hyperlink ref="C596" r:id="rId573" xr:uid="{00000000-0004-0000-0000-00003C020000}"/>
-    <hyperlink ref="C597" r:id="rId574" xr:uid="{00000000-0004-0000-0000-00003D020000}"/>
-    <hyperlink ref="C598" r:id="rId575" xr:uid="{00000000-0004-0000-0000-00003E020000}"/>
-    <hyperlink ref="C599" r:id="rId576" xr:uid="{00000000-0004-0000-0000-00003F020000}"/>
-    <hyperlink ref="C600" r:id="rId577" xr:uid="{00000000-0004-0000-0000-000040020000}"/>
-    <hyperlink ref="C42" r:id="rId578" xr:uid="{00000000-0004-0000-0000-000041020000}"/>
-    <hyperlink ref="C601" r:id="rId579" xr:uid="{00000000-0004-0000-0000-000042020000}"/>
-    <hyperlink ref="C602" r:id="rId580" xr:uid="{00000000-0004-0000-0000-000043020000}"/>
-    <hyperlink ref="C603" r:id="rId581" xr:uid="{00000000-0004-0000-0000-000044020000}"/>
-    <hyperlink ref="C604" r:id="rId582" xr:uid="{00000000-0004-0000-0000-000045020000}"/>
-    <hyperlink ref="C605" r:id="rId583" xr:uid="{00000000-0004-0000-0000-000046020000}"/>
-    <hyperlink ref="C606" r:id="rId584" xr:uid="{00000000-0004-0000-0000-000047020000}"/>
-    <hyperlink ref="C607" r:id="rId585" xr:uid="{00000000-0004-0000-0000-000048020000}"/>
-    <hyperlink ref="C608" r:id="rId586" xr:uid="{00000000-0004-0000-0000-000049020000}"/>
-    <hyperlink ref="C609" r:id="rId587" xr:uid="{00000000-0004-0000-0000-00004A020000}"/>
-    <hyperlink ref="C610" r:id="rId588" xr:uid="{00000000-0004-0000-0000-00004B020000}"/>
-    <hyperlink ref="C611" r:id="rId589" xr:uid="{00000000-0004-0000-0000-00004C020000}"/>
-    <hyperlink ref="C612" r:id="rId590" xr:uid="{00000000-0004-0000-0000-00004D020000}"/>
-    <hyperlink ref="C613" r:id="rId591" xr:uid="{00000000-0004-0000-0000-00004E020000}"/>
-    <hyperlink ref="C614" r:id="rId592" xr:uid="{00000000-0004-0000-0000-00004F020000}"/>
-    <hyperlink ref="C615" r:id="rId593" xr:uid="{00000000-0004-0000-0000-000050020000}"/>
-    <hyperlink ref="C616" r:id="rId594" xr:uid="{00000000-0004-0000-0000-000051020000}"/>
-    <hyperlink ref="C617" r:id="rId595" xr:uid="{00000000-0004-0000-0000-000052020000}"/>
-    <hyperlink ref="C618" r:id="rId596" xr:uid="{00000000-0004-0000-0000-000053020000}"/>
-    <hyperlink ref="C619" r:id="rId597" xr:uid="{00000000-0004-0000-0000-000054020000}"/>
-    <hyperlink ref="C620" r:id="rId598" xr:uid="{00000000-0004-0000-0000-000055020000}"/>
-    <hyperlink ref="C621" r:id="rId599" xr:uid="{00000000-0004-0000-0000-000056020000}"/>
-    <hyperlink ref="C622" r:id="rId600" xr:uid="{00000000-0004-0000-0000-000057020000}"/>
-    <hyperlink ref="C623" r:id="rId601" xr:uid="{00000000-0004-0000-0000-000058020000}"/>
-    <hyperlink ref="C624" r:id="rId602" xr:uid="{00000000-0004-0000-0000-000059020000}"/>
-    <hyperlink ref="C625" r:id="rId603" xr:uid="{00000000-0004-0000-0000-00005A020000}"/>
-    <hyperlink ref="C626" r:id="rId604" xr:uid="{00000000-0004-0000-0000-00005B020000}"/>
-    <hyperlink ref="C627" r:id="rId605" xr:uid="{00000000-0004-0000-0000-00005C020000}"/>
-    <hyperlink ref="C628" r:id="rId606" xr:uid="{00000000-0004-0000-0000-00005D020000}"/>
-    <hyperlink ref="C629" r:id="rId607" xr:uid="{00000000-0004-0000-0000-00005E020000}"/>
-    <hyperlink ref="C43" r:id="rId608" xr:uid="{00000000-0004-0000-0000-00005F020000}"/>
-    <hyperlink ref="C630" r:id="rId609" xr:uid="{00000000-0004-0000-0000-000060020000}"/>
-    <hyperlink ref="C631" r:id="rId610" xr:uid="{00000000-0004-0000-0000-000061020000}"/>
-    <hyperlink ref="C632" r:id="rId611" xr:uid="{00000000-0004-0000-0000-000062020000}"/>
-    <hyperlink ref="C633" r:id="rId612" xr:uid="{00000000-0004-0000-0000-000063020000}"/>
-    <hyperlink ref="C634" r:id="rId613" xr:uid="{00000000-0004-0000-0000-000064020000}"/>
-    <hyperlink ref="C635" r:id="rId614" xr:uid="{00000000-0004-0000-0000-000065020000}"/>
-    <hyperlink ref="C636" r:id="rId615" xr:uid="{00000000-0004-0000-0000-000066020000}"/>
-    <hyperlink ref="C637" r:id="rId616" xr:uid="{00000000-0004-0000-0000-000067020000}"/>
-    <hyperlink ref="C638" r:id="rId617" xr:uid="{00000000-0004-0000-0000-000068020000}"/>
-    <hyperlink ref="C639" r:id="rId618" xr:uid="{00000000-0004-0000-0000-000069020000}"/>
-    <hyperlink ref="C640" r:id="rId619" xr:uid="{00000000-0004-0000-0000-00006A020000}"/>
-    <hyperlink ref="C641" r:id="rId620" xr:uid="{00000000-0004-0000-0000-00006B020000}"/>
-    <hyperlink ref="C642" r:id="rId621" xr:uid="{00000000-0004-0000-0000-00006C020000}"/>
-    <hyperlink ref="C643" r:id="rId622" xr:uid="{00000000-0004-0000-0000-00006D020000}"/>
-    <hyperlink ref="C644" r:id="rId623" xr:uid="{00000000-0004-0000-0000-00006E020000}"/>
-    <hyperlink ref="C645" r:id="rId624" xr:uid="{00000000-0004-0000-0000-00006F020000}"/>
-    <hyperlink ref="C646" r:id="rId625" xr:uid="{00000000-0004-0000-0000-000070020000}"/>
-    <hyperlink ref="C647" r:id="rId626" xr:uid="{00000000-0004-0000-0000-000071020000}"/>
-    <hyperlink ref="C648" r:id="rId627" xr:uid="{00000000-0004-0000-0000-000072020000}"/>
-    <hyperlink ref="C649" r:id="rId628" xr:uid="{00000000-0004-0000-0000-000073020000}"/>
-    <hyperlink ref="C650" r:id="rId629" xr:uid="{00000000-0004-0000-0000-000074020000}"/>
-    <hyperlink ref="C651" r:id="rId630" xr:uid="{00000000-0004-0000-0000-000075020000}"/>
-    <hyperlink ref="C652" r:id="rId631" xr:uid="{00000000-0004-0000-0000-000076020000}"/>
-    <hyperlink ref="C653" r:id="rId632" xr:uid="{00000000-0004-0000-0000-000077020000}"/>
-    <hyperlink ref="C654" r:id="rId633" xr:uid="{00000000-0004-0000-0000-000078020000}"/>
-    <hyperlink ref="C655" r:id="rId634" xr:uid="{00000000-0004-0000-0000-000079020000}"/>
-    <hyperlink ref="C656" r:id="rId635" xr:uid="{00000000-0004-0000-0000-00007A020000}"/>
-    <hyperlink ref="C657" r:id="rId636" xr:uid="{00000000-0004-0000-0000-00007B020000}"/>
-    <hyperlink ref="C658" r:id="rId637" xr:uid="{00000000-0004-0000-0000-00007C020000}"/>
-    <hyperlink ref="C659" r:id="rId638" xr:uid="{00000000-0004-0000-0000-00007D020000}"/>
-    <hyperlink ref="C660" r:id="rId639" xr:uid="{00000000-0004-0000-0000-00007E020000}"/>
-    <hyperlink ref="C661" r:id="rId640" xr:uid="{00000000-0004-0000-0000-00007F020000}"/>
-    <hyperlink ref="C662" r:id="rId641" xr:uid="{00000000-0004-0000-0000-000080020000}"/>
-    <hyperlink ref="C663" r:id="rId642" xr:uid="{00000000-0004-0000-0000-000081020000}"/>
-    <hyperlink ref="C664" r:id="rId643" xr:uid="{00000000-0004-0000-0000-000082020000}"/>
-    <hyperlink ref="C665" r:id="rId644" xr:uid="{00000000-0004-0000-0000-000083020000}"/>
-    <hyperlink ref="C666" r:id="rId645" xr:uid="{00000000-0004-0000-0000-000084020000}"/>
-    <hyperlink ref="C667" r:id="rId646" xr:uid="{00000000-0004-0000-0000-000085020000}"/>
-    <hyperlink ref="C668" r:id="rId647" xr:uid="{00000000-0004-0000-0000-000086020000}"/>
-    <hyperlink ref="C669" r:id="rId648" xr:uid="{00000000-0004-0000-0000-000087020000}"/>
-    <hyperlink ref="C670" r:id="rId649" xr:uid="{00000000-0004-0000-0000-000088020000}"/>
-    <hyperlink ref="C44" r:id="rId650" xr:uid="{00000000-0004-0000-0000-000089020000}"/>
-    <hyperlink ref="C671" r:id="rId651" xr:uid="{00000000-0004-0000-0000-00008A020000}"/>
-    <hyperlink ref="C672" r:id="rId652" xr:uid="{00000000-0004-0000-0000-00008B020000}"/>
-    <hyperlink ref="C673" r:id="rId653" xr:uid="{00000000-0004-0000-0000-00008C020000}"/>
-    <hyperlink ref="C674" r:id="rId654" xr:uid="{00000000-0004-0000-0000-00008D020000}"/>
-    <hyperlink ref="C675" r:id="rId655" xr:uid="{00000000-0004-0000-0000-00008E020000}"/>
-    <hyperlink ref="C676" r:id="rId656" xr:uid="{00000000-0004-0000-0000-00008F020000}"/>
-    <hyperlink ref="C677" r:id="rId657" xr:uid="{00000000-0004-0000-0000-000090020000}"/>
-    <hyperlink ref="C678" r:id="rId658" xr:uid="{00000000-0004-0000-0000-000091020000}"/>
-    <hyperlink ref="C679" r:id="rId659" xr:uid="{00000000-0004-0000-0000-000092020000}"/>
-    <hyperlink ref="C680" r:id="rId660" xr:uid="{00000000-0004-0000-0000-000093020000}"/>
-    <hyperlink ref="C681" r:id="rId661" xr:uid="{00000000-0004-0000-0000-000094020000}"/>
-    <hyperlink ref="C682" r:id="rId662" xr:uid="{00000000-0004-0000-0000-000095020000}"/>
-    <hyperlink ref="C683" r:id="rId663" xr:uid="{00000000-0004-0000-0000-000096020000}"/>
-    <hyperlink ref="C684" r:id="rId664" xr:uid="{00000000-0004-0000-0000-000097020000}"/>
-    <hyperlink ref="C685" r:id="rId665" xr:uid="{00000000-0004-0000-0000-000098020000}"/>
-    <hyperlink ref="C686" r:id="rId666" xr:uid="{00000000-0004-0000-0000-000099020000}"/>
-    <hyperlink ref="C687" r:id="rId667" xr:uid="{00000000-0004-0000-0000-00009A020000}"/>
-    <hyperlink ref="C688" r:id="rId668" xr:uid="{00000000-0004-0000-0000-00009B020000}"/>
-    <hyperlink ref="C689" r:id="rId669" xr:uid="{00000000-0004-0000-0000-00009C020000}"/>
-    <hyperlink ref="C690" r:id="rId670" xr:uid="{00000000-0004-0000-0000-00009D020000}"/>
-    <hyperlink ref="C691" r:id="rId671" xr:uid="{00000000-0004-0000-0000-00009E020000}"/>
-    <hyperlink ref="C692" r:id="rId672" xr:uid="{00000000-0004-0000-0000-00009F020000}"/>
-    <hyperlink ref="C693" r:id="rId673" xr:uid="{00000000-0004-0000-0000-0000A0020000}"/>
-    <hyperlink ref="C694" r:id="rId674" xr:uid="{00000000-0004-0000-0000-0000A1020000}"/>
-    <hyperlink ref="C695" r:id="rId675" xr:uid="{00000000-0004-0000-0000-0000A2020000}"/>
-    <hyperlink ref="C696" r:id="rId676" xr:uid="{00000000-0004-0000-0000-0000A3020000}"/>
-    <hyperlink ref="C697" r:id="rId677" xr:uid="{00000000-0004-0000-0000-0000A4020000}"/>
-    <hyperlink ref="C698" r:id="rId678" xr:uid="{00000000-0004-0000-0000-0000A5020000}"/>
-    <hyperlink ref="C699" r:id="rId679" xr:uid="{00000000-0004-0000-0000-0000A6020000}"/>
-    <hyperlink ref="C700" r:id="rId680" xr:uid="{00000000-0004-0000-0000-0000A7020000}"/>
-    <hyperlink ref="C701" r:id="rId681" xr:uid="{00000000-0004-0000-0000-0000A8020000}"/>
-    <hyperlink ref="C702" r:id="rId682" xr:uid="{00000000-0004-0000-0000-0000A9020000}"/>
-    <hyperlink ref="C703" r:id="rId683" xr:uid="{00000000-0004-0000-0000-0000AA020000}"/>
-    <hyperlink ref="C906" r:id="rId684" xr:uid="{00000000-0004-0000-0000-0000AB020000}"/>
-    <hyperlink ref="C704" r:id="rId685" xr:uid="{00000000-0004-0000-0000-0000AC020000}"/>
-    <hyperlink ref="C705" r:id="rId686" xr:uid="{00000000-0004-0000-0000-0000AD020000}"/>
-    <hyperlink ref="C706" r:id="rId687" xr:uid="{00000000-0004-0000-0000-0000AE020000}"/>
-    <hyperlink ref="C707" r:id="rId688" xr:uid="{00000000-0004-0000-0000-0000AF020000}"/>
-    <hyperlink ref="C708" r:id="rId689" xr:uid="{00000000-0004-0000-0000-0000B0020000}"/>
-    <hyperlink ref="C45" r:id="rId690" xr:uid="{00000000-0004-0000-0000-0000B1020000}"/>
-    <hyperlink ref="C709" r:id="rId691" xr:uid="{00000000-0004-0000-0000-0000B2020000}"/>
-    <hyperlink ref="C710" r:id="rId692" xr:uid="{00000000-0004-0000-0000-0000B3020000}"/>
-    <hyperlink ref="C711" r:id="rId693" xr:uid="{00000000-0004-0000-0000-0000B4020000}"/>
-    <hyperlink ref="C712" r:id="rId694" xr:uid="{00000000-0004-0000-0000-0000B5020000}"/>
-    <hyperlink ref="C713" r:id="rId695" xr:uid="{00000000-0004-0000-0000-0000B6020000}"/>
-    <hyperlink ref="C714" r:id="rId696" xr:uid="{00000000-0004-0000-0000-0000B7020000}"/>
-    <hyperlink ref="C715" r:id="rId697" xr:uid="{00000000-0004-0000-0000-0000B8020000}"/>
-    <hyperlink ref="C716" r:id="rId698" xr:uid="{00000000-0004-0000-0000-0000B9020000}"/>
-    <hyperlink ref="C717" r:id="rId699" xr:uid="{00000000-0004-0000-0000-0000BA020000}"/>
-    <hyperlink ref="C718" r:id="rId700" xr:uid="{00000000-0004-0000-0000-0000BB020000}"/>
-    <hyperlink ref="C719" r:id="rId701" xr:uid="{00000000-0004-0000-0000-0000BC020000}"/>
-    <hyperlink ref="C720" r:id="rId702" xr:uid="{00000000-0004-0000-0000-0000BD020000}"/>
-    <hyperlink ref="C721" r:id="rId703" xr:uid="{00000000-0004-0000-0000-0000BE020000}"/>
-    <hyperlink ref="C722" r:id="rId704" xr:uid="{00000000-0004-0000-0000-0000BF020000}"/>
-    <hyperlink ref="C723" r:id="rId705" xr:uid="{00000000-0004-0000-0000-0000C0020000}"/>
-    <hyperlink ref="C46" r:id="rId706" xr:uid="{00000000-0004-0000-0000-0000C1020000}"/>
-    <hyperlink ref="C724" r:id="rId707" xr:uid="{00000000-0004-0000-0000-0000C2020000}"/>
-    <hyperlink ref="C725" r:id="rId708" xr:uid="{00000000-0004-0000-0000-0000C3020000}"/>
-    <hyperlink ref="C726" r:id="rId709" xr:uid="{00000000-0004-0000-0000-0000C4020000}"/>
-    <hyperlink ref="C727" r:id="rId710" xr:uid="{00000000-0004-0000-0000-0000C5020000}"/>
-    <hyperlink ref="C728" r:id="rId711" xr:uid="{00000000-0004-0000-0000-0000C6020000}"/>
-    <hyperlink ref="C729" r:id="rId712" xr:uid="{00000000-0004-0000-0000-0000C7020000}"/>
-    <hyperlink ref="C730" r:id="rId713" xr:uid="{00000000-0004-0000-0000-0000C8020000}"/>
-    <hyperlink ref="C731" r:id="rId714" xr:uid="{00000000-0004-0000-0000-0000C9020000}"/>
-    <hyperlink ref="C732" r:id="rId715" xr:uid="{00000000-0004-0000-0000-0000CA020000}"/>
-    <hyperlink ref="C733" r:id="rId716" xr:uid="{00000000-0004-0000-0000-0000CB020000}"/>
-    <hyperlink ref="C734" r:id="rId717" xr:uid="{00000000-0004-0000-0000-0000CC020000}"/>
-    <hyperlink ref="C735" r:id="rId718" xr:uid="{00000000-0004-0000-0000-0000CD020000}"/>
-    <hyperlink ref="C736" r:id="rId719" xr:uid="{00000000-0004-0000-0000-0000CE020000}"/>
-    <hyperlink ref="C737" r:id="rId720" xr:uid="{00000000-0004-0000-0000-0000CF020000}"/>
-    <hyperlink ref="C738" r:id="rId721" xr:uid="{00000000-0004-0000-0000-0000D0020000}"/>
-    <hyperlink ref="C47" r:id="rId722" xr:uid="{00000000-0004-0000-0000-0000D1020000}"/>
-    <hyperlink ref="C739" r:id="rId723" xr:uid="{00000000-0004-0000-0000-0000D2020000}"/>
-    <hyperlink ref="C740" r:id="rId724" xr:uid="{00000000-0004-0000-0000-0000D3020000}"/>
-    <hyperlink ref="C741" r:id="rId725" xr:uid="{00000000-0004-0000-0000-0000D4020000}"/>
-    <hyperlink ref="C742" r:id="rId726" xr:uid="{00000000-0004-0000-0000-0000D5020000}"/>
-    <hyperlink ref="C48" r:id="rId727" xr:uid="{00000000-0004-0000-0000-0000D6020000}"/>
-    <hyperlink ref="C743" r:id="rId728" xr:uid="{00000000-0004-0000-0000-0000D7020000}"/>
-    <hyperlink ref="C744" r:id="rId729" xr:uid="{00000000-0004-0000-0000-0000D8020000}"/>
-    <hyperlink ref="C49" r:id="rId730" xr:uid="{00000000-0004-0000-0000-0000D9020000}"/>
-    <hyperlink ref="C745" r:id="rId731" xr:uid="{00000000-0004-0000-0000-0000DA020000}"/>
-    <hyperlink ref="C746" r:id="rId732" xr:uid="{00000000-0004-0000-0000-0000DB020000}"/>
-    <hyperlink ref="C747" r:id="rId733" xr:uid="{00000000-0004-0000-0000-0000DC020000}"/>
-    <hyperlink ref="C748" r:id="rId734" xr:uid="{00000000-0004-0000-0000-0000DD020000}"/>
-    <hyperlink ref="C749" r:id="rId735" xr:uid="{00000000-0004-0000-0000-0000DE020000}"/>
-    <hyperlink ref="C750" r:id="rId736" xr:uid="{00000000-0004-0000-0000-0000DF020000}"/>
-    <hyperlink ref="C50" r:id="rId737" xr:uid="{00000000-0004-0000-0000-0000E0020000}"/>
-    <hyperlink ref="C751" r:id="rId738" xr:uid="{00000000-0004-0000-0000-0000E1020000}"/>
-    <hyperlink ref="C51" r:id="rId739" xr:uid="{00000000-0004-0000-0000-0000E2020000}"/>
-    <hyperlink ref="C752" r:id="rId740" xr:uid="{00000000-0004-0000-0000-0000E3020000}"/>
-    <hyperlink ref="C753" r:id="rId741" xr:uid="{00000000-0004-0000-0000-0000E4020000}"/>
-    <hyperlink ref="C754" r:id="rId742" xr:uid="{00000000-0004-0000-0000-0000E5020000}"/>
-    <hyperlink ref="C755" r:id="rId743" xr:uid="{00000000-0004-0000-0000-0000E6020000}"/>
-    <hyperlink ref="C756" r:id="rId744" xr:uid="{00000000-0004-0000-0000-0000E7020000}"/>
-    <hyperlink ref="C757" r:id="rId745" xr:uid="{00000000-0004-0000-0000-0000E8020000}"/>
-    <hyperlink ref="C758" r:id="rId746" xr:uid="{00000000-0004-0000-0000-0000E9020000}"/>
-    <hyperlink ref="C759" r:id="rId747" xr:uid="{00000000-0004-0000-0000-0000EA020000}"/>
-    <hyperlink ref="C760" r:id="rId748" xr:uid="{00000000-0004-0000-0000-0000EB020000}"/>
-    <hyperlink ref="C761" r:id="rId749" xr:uid="{00000000-0004-0000-0000-0000EC020000}"/>
-    <hyperlink ref="C762" r:id="rId750" xr:uid="{00000000-0004-0000-0000-0000ED020000}"/>
-    <hyperlink ref="C763" r:id="rId751" xr:uid="{00000000-0004-0000-0000-0000EE020000}"/>
-    <hyperlink ref="C764" r:id="rId752" xr:uid="{00000000-0004-0000-0000-0000EF020000}"/>
-    <hyperlink ref="C765" r:id="rId753" xr:uid="{00000000-0004-0000-0000-0000F0020000}"/>
-    <hyperlink ref="C766" r:id="rId754" xr:uid="{00000000-0004-0000-0000-0000F1020000}"/>
-    <hyperlink ref="C767" r:id="rId755" xr:uid="{00000000-0004-0000-0000-0000F2020000}"/>
-    <hyperlink ref="C768" r:id="rId756" xr:uid="{00000000-0004-0000-0000-0000F3020000}"/>
-    <hyperlink ref="C769" r:id="rId757" xr:uid="{00000000-0004-0000-0000-0000F4020000}"/>
-    <hyperlink ref="C770" r:id="rId758" xr:uid="{00000000-0004-0000-0000-0000F5020000}"/>
-    <hyperlink ref="C771" r:id="rId759" xr:uid="{00000000-0004-0000-0000-0000F6020000}"/>
-    <hyperlink ref="C772" r:id="rId760" xr:uid="{00000000-0004-0000-0000-0000F7020000}"/>
-    <hyperlink ref="C773" r:id="rId761" xr:uid="{00000000-0004-0000-0000-0000F8020000}"/>
-    <hyperlink ref="C774" r:id="rId762" xr:uid="{00000000-0004-0000-0000-0000F9020000}"/>
-    <hyperlink ref="C775" r:id="rId763" xr:uid="{00000000-0004-0000-0000-0000FA020000}"/>
-    <hyperlink ref="C776" r:id="rId764" xr:uid="{00000000-0004-0000-0000-0000FB020000}"/>
-    <hyperlink ref="C777" r:id="rId765" xr:uid="{00000000-0004-0000-0000-0000FC020000}"/>
-    <hyperlink ref="C778" r:id="rId766" xr:uid="{00000000-0004-0000-0000-0000FD020000}"/>
-    <hyperlink ref="C779" r:id="rId767" xr:uid="{00000000-0004-0000-0000-0000FE020000}"/>
-    <hyperlink ref="C780" r:id="rId768" xr:uid="{00000000-0004-0000-0000-0000FF020000}"/>
-    <hyperlink ref="C781" r:id="rId769" xr:uid="{00000000-0004-0000-0000-000000030000}"/>
-    <hyperlink ref="C782" r:id="rId770" xr:uid="{00000000-0004-0000-0000-000001030000}"/>
-    <hyperlink ref="C783" r:id="rId771" xr:uid="{00000000-0004-0000-0000-000002030000}"/>
-    <hyperlink ref="C784" r:id="rId772" xr:uid="{00000000-0004-0000-0000-000003030000}"/>
-    <hyperlink ref="C785" r:id="rId773" xr:uid="{00000000-0004-0000-0000-000004030000}"/>
-    <hyperlink ref="C786" r:id="rId774" xr:uid="{00000000-0004-0000-0000-000005030000}"/>
-    <hyperlink ref="C787" r:id="rId775" xr:uid="{00000000-0004-0000-0000-000006030000}"/>
-    <hyperlink ref="C788" r:id="rId776" xr:uid="{00000000-0004-0000-0000-000007030000}"/>
-    <hyperlink ref="C789" r:id="rId777" xr:uid="{00000000-0004-0000-0000-000008030000}"/>
-    <hyperlink ref="C790" r:id="rId778" xr:uid="{00000000-0004-0000-0000-000009030000}"/>
-    <hyperlink ref="C791" r:id="rId779" xr:uid="{00000000-0004-0000-0000-00000A030000}"/>
-    <hyperlink ref="C792" r:id="rId780" xr:uid="{00000000-0004-0000-0000-00000B030000}"/>
-    <hyperlink ref="C793" r:id="rId781" xr:uid="{00000000-0004-0000-0000-00000C030000}"/>
-    <hyperlink ref="C52" r:id="rId782" xr:uid="{00000000-0004-0000-0000-00000D030000}"/>
-    <hyperlink ref="C794" r:id="rId783" xr:uid="{00000000-0004-0000-0000-00000E030000}"/>
-    <hyperlink ref="C795" r:id="rId784" xr:uid="{00000000-0004-0000-0000-00000F030000}"/>
-    <hyperlink ref="C796" r:id="rId785" xr:uid="{00000000-0004-0000-0000-000010030000}"/>
-    <hyperlink ref="C797" r:id="rId786" xr:uid="{00000000-0004-0000-0000-000011030000}"/>
-    <hyperlink ref="C798" r:id="rId787" xr:uid="{00000000-0004-0000-0000-000012030000}"/>
-    <hyperlink ref="C799" r:id="rId788" xr:uid="{00000000-0004-0000-0000-000013030000}"/>
-    <hyperlink ref="C800" r:id="rId789" xr:uid="{00000000-0004-0000-0000-000014030000}"/>
-    <hyperlink ref="C801" r:id="rId790" xr:uid="{00000000-0004-0000-0000-000015030000}"/>
-    <hyperlink ref="C802" r:id="rId791" xr:uid="{00000000-0004-0000-0000-000016030000}"/>
-    <hyperlink ref="C803" r:id="rId792" xr:uid="{00000000-0004-0000-0000-000017030000}"/>
-    <hyperlink ref="C804" r:id="rId793" xr:uid="{00000000-0004-0000-0000-000018030000}"/>
-    <hyperlink ref="C805" r:id="rId794" xr:uid="{00000000-0004-0000-0000-000019030000}"/>
-    <hyperlink ref="C806" r:id="rId795" xr:uid="{00000000-0004-0000-0000-00001A030000}"/>
-    <hyperlink ref="C807" r:id="rId796" xr:uid="{00000000-0004-0000-0000-00001B030000}"/>
-    <hyperlink ref="C808" r:id="rId797" xr:uid="{00000000-0004-0000-0000-00001C030000}"/>
-    <hyperlink ref="C809" r:id="rId798" xr:uid="{00000000-0004-0000-0000-00001D030000}"/>
-    <hyperlink ref="C810" r:id="rId799" xr:uid="{00000000-0004-0000-0000-00001E030000}"/>
-    <hyperlink ref="C811" r:id="rId800" xr:uid="{00000000-0004-0000-0000-00001F030000}"/>
-    <hyperlink ref="C812" r:id="rId801" xr:uid="{00000000-0004-0000-0000-000020030000}"/>
-    <hyperlink ref="C813" r:id="rId802" xr:uid="{00000000-0004-0000-0000-000021030000}"/>
-    <hyperlink ref="C814" r:id="rId803" xr:uid="{00000000-0004-0000-0000-000022030000}"/>
-    <hyperlink ref="C815" r:id="rId804" xr:uid="{00000000-0004-0000-0000-000023030000}"/>
-    <hyperlink ref="C816" r:id="rId805" xr:uid="{00000000-0004-0000-0000-000024030000}"/>
-    <hyperlink ref="C817" r:id="rId806" xr:uid="{00000000-0004-0000-0000-000025030000}"/>
-    <hyperlink ref="C818" r:id="rId807" xr:uid="{00000000-0004-0000-0000-000026030000}"/>
-    <hyperlink ref="C53" r:id="rId808" xr:uid="{00000000-0004-0000-0000-000027030000}"/>
-    <hyperlink ref="C54" r:id="rId809" xr:uid="{00000000-0004-0000-0000-000028030000}"/>
-    <hyperlink ref="C819" r:id="rId810" xr:uid="{00000000-0004-0000-0000-000029030000}"/>
-    <hyperlink ref="C820" r:id="rId811" xr:uid="{00000000-0004-0000-0000-00002A030000}"/>
-    <hyperlink ref="C821" r:id="rId812" xr:uid="{00000000-0004-0000-0000-00002B030000}"/>
-    <hyperlink ref="C822" r:id="rId813" xr:uid="{00000000-0004-0000-0000-00002C030000}"/>
-    <hyperlink ref="C823" r:id="rId814" xr:uid="{00000000-0004-0000-0000-00002D030000}"/>
-    <hyperlink ref="C55" r:id="rId815" xr:uid="{00000000-0004-0000-0000-00002E030000}"/>
-    <hyperlink ref="C56" r:id="rId816" xr:uid="{00000000-0004-0000-0000-00002F030000}"/>
-    <hyperlink ref="C824" r:id="rId817" xr:uid="{00000000-0004-0000-0000-000030030000}"/>
-    <hyperlink ref="C825" r:id="rId818" xr:uid="{00000000-0004-0000-0000-000031030000}"/>
-    <hyperlink ref="C826" r:id="rId819" xr:uid="{00000000-0004-0000-0000-000032030000}"/>
-    <hyperlink ref="C827" r:id="rId820" xr:uid="{00000000-0004-0000-0000-000033030000}"/>
-    <hyperlink ref="C828" r:id="rId821" xr:uid="{00000000-0004-0000-0000-000034030000}"/>
-    <hyperlink ref="C829" r:id="rId822" xr:uid="{00000000-0004-0000-0000-000035030000}"/>
-    <hyperlink ref="C830" r:id="rId823" xr:uid="{00000000-0004-0000-0000-000036030000}"/>
-    <hyperlink ref="C831" r:id="rId824" xr:uid="{00000000-0004-0000-0000-000037030000}"/>
-    <hyperlink ref="C57" r:id="rId825" xr:uid="{00000000-0004-0000-0000-000038030000}"/>
-    <hyperlink ref="C832" r:id="rId826" xr:uid="{00000000-0004-0000-0000-000039030000}"/>
-    <hyperlink ref="C833" r:id="rId827" xr:uid="{00000000-0004-0000-0000-00003A030000}"/>
-    <hyperlink ref="C834" r:id="rId828" xr:uid="{00000000-0004-0000-0000-00003B030000}"/>
-    <hyperlink ref="C835" r:id="rId829" xr:uid="{00000000-0004-0000-0000-00003C030000}"/>
-    <hyperlink ref="C836" r:id="rId830" xr:uid="{00000000-0004-0000-0000-00003D030000}"/>
-    <hyperlink ref="C837" r:id="rId831" xr:uid="{00000000-0004-0000-0000-00003E030000}"/>
-    <hyperlink ref="C838" r:id="rId832" xr:uid="{00000000-0004-0000-0000-00003F030000}"/>
-    <hyperlink ref="C839" r:id="rId833" xr:uid="{00000000-0004-0000-0000-000040030000}"/>
-    <hyperlink ref="C840" r:id="rId834" xr:uid="{00000000-0004-0000-0000-000041030000}"/>
-    <hyperlink ref="C58" r:id="rId835" xr:uid="{00000000-0004-0000-0000-000042030000}"/>
-    <hyperlink ref="C841" r:id="rId836" xr:uid="{00000000-0004-0000-0000-000043030000}"/>
-    <hyperlink ref="C842" r:id="rId837" xr:uid="{00000000-0004-0000-0000-000044030000}"/>
-    <hyperlink ref="C843" r:id="rId838" xr:uid="{00000000-0004-0000-0000-000045030000}"/>
-    <hyperlink ref="C844" r:id="rId839" xr:uid="{00000000-0004-0000-0000-000046030000}"/>
-    <hyperlink ref="C845" r:id="rId840" xr:uid="{00000000-0004-0000-0000-000047030000}"/>
-    <hyperlink ref="C846" r:id="rId841" xr:uid="{00000000-0004-0000-0000-000048030000}"/>
-    <hyperlink ref="C847" r:id="rId842" xr:uid="{00000000-0004-0000-0000-000049030000}"/>
-    <hyperlink ref="C848" r:id="rId843" xr:uid="{00000000-0004-0000-0000-00004A030000}"/>
-    <hyperlink ref="C849" r:id="rId844" xr:uid="{00000000-0004-0000-0000-00004B030000}"/>
-    <hyperlink ref="C850" r:id="rId845" xr:uid="{00000000-0004-0000-0000-00004C030000}"/>
-    <hyperlink ref="C851" r:id="rId846" xr:uid="{00000000-0004-0000-0000-00004D030000}"/>
-    <hyperlink ref="C59" r:id="rId847" xr:uid="{00000000-0004-0000-0000-00004E030000}"/>
-    <hyperlink ref="C852" r:id="rId848" xr:uid="{00000000-0004-0000-0000-00004F030000}"/>
-    <hyperlink ref="C853" r:id="rId849" xr:uid="{00000000-0004-0000-0000-000050030000}"/>
-    <hyperlink ref="C854" r:id="rId850" xr:uid="{00000000-0004-0000-0000-000051030000}"/>
-    <hyperlink ref="C855" r:id="rId851" xr:uid="{00000000-0004-0000-0000-000052030000}"/>
-    <hyperlink ref="C856" r:id="rId852" xr:uid="{00000000-0004-0000-0000-000053030000}"/>
-    <hyperlink ref="C857" r:id="rId853" xr:uid="{00000000-0004-0000-0000-000054030000}"/>
-    <hyperlink ref="C858" r:id="rId854" xr:uid="{00000000-0004-0000-0000-000055030000}"/>
-    <hyperlink ref="C859" r:id="rId855" xr:uid="{00000000-0004-0000-0000-000056030000}"/>
-    <hyperlink ref="C860" r:id="rId856" xr:uid="{00000000-0004-0000-0000-000057030000}"/>
-    <hyperlink ref="C907" r:id="rId857" xr:uid="{00000000-0004-0000-0000-000058030000}"/>
-    <hyperlink ref="C861" r:id="rId858" xr:uid="{00000000-0004-0000-0000-000059030000}"/>
-    <hyperlink ref="C862" r:id="rId859" xr:uid="{00000000-0004-0000-0000-00005A030000}"/>
-    <hyperlink ref="C863" r:id="rId860" xr:uid="{00000000-0004-0000-0000-00005B030000}"/>
-    <hyperlink ref="C864" r:id="rId861" xr:uid="{00000000-0004-0000-0000-00005C030000}"/>
-    <hyperlink ref="C865" r:id="rId862" xr:uid="{00000000-0004-0000-0000-00005D030000}"/>
-    <hyperlink ref="C866" r:id="rId863" xr:uid="{00000000-0004-0000-0000-00005E030000}"/>
-    <hyperlink ref="C867" r:id="rId864" xr:uid="{00000000-0004-0000-0000-00005F030000}"/>
-    <hyperlink ref="C868" r:id="rId865" xr:uid="{00000000-0004-0000-0000-000060030000}"/>
-    <hyperlink ref="C869" r:id="rId866" xr:uid="{00000000-0004-0000-0000-000061030000}"/>
-    <hyperlink ref="C870" r:id="rId867" xr:uid="{00000000-0004-0000-0000-000062030000}"/>
-    <hyperlink ref="C871" r:id="rId868" xr:uid="{00000000-0004-0000-0000-000063030000}"/>
-    <hyperlink ref="C872" r:id="rId869" xr:uid="{00000000-0004-0000-0000-000064030000}"/>
-    <hyperlink ref="C60" r:id="rId870" xr:uid="{00000000-0004-0000-0000-000065030000}"/>
-    <hyperlink ref="C873" r:id="rId871" xr:uid="{00000000-0004-0000-0000-000066030000}"/>
-    <hyperlink ref="C874" r:id="rId872" xr:uid="{00000000-0004-0000-0000-000067030000}"/>
-    <hyperlink ref="C875" r:id="rId873" xr:uid="{00000000-0004-0000-0000-000068030000}"/>
-    <hyperlink ref="C876" r:id="rId874" xr:uid="{00000000-0004-0000-0000-000069030000}"/>
-    <hyperlink ref="C877" r:id="rId875" xr:uid="{00000000-0004-0000-0000-00006A030000}"/>
-    <hyperlink ref="C61" r:id="rId876" xr:uid="{00000000-0004-0000-0000-00006B030000}"/>
-    <hyperlink ref="C878" r:id="rId877" xr:uid="{00000000-0004-0000-0000-00006C030000}"/>
-    <hyperlink ref="C879" r:id="rId878" xr:uid="{00000000-0004-0000-0000-00006D030000}"/>
-    <hyperlink ref="C880" r:id="rId879" xr:uid="{00000000-0004-0000-0000-00006E030000}"/>
-    <hyperlink ref="C62" r:id="rId880" xr:uid="{00000000-0004-0000-0000-00006F030000}"/>
-    <hyperlink ref="C881" r:id="rId881" xr:uid="{00000000-0004-0000-0000-000070030000}"/>
-    <hyperlink ref="C882" r:id="rId882" xr:uid="{00000000-0004-0000-0000-000071030000}"/>
-    <hyperlink ref="C883" r:id="rId883" xr:uid="{00000000-0004-0000-0000-000072030000}"/>
-    <hyperlink ref="C884" r:id="rId884" xr:uid="{00000000-0004-0000-0000-000073030000}"/>
-    <hyperlink ref="C885" r:id="rId885" xr:uid="{00000000-0004-0000-0000-000074030000}"/>
-    <hyperlink ref="C886" r:id="rId886" xr:uid="{00000000-0004-0000-0000-000075030000}"/>
-    <hyperlink ref="C887" r:id="rId887" xr:uid="{00000000-0004-0000-0000-000076030000}"/>
-    <hyperlink ref="C888" r:id="rId888" xr:uid="{00000000-0004-0000-0000-000077030000}"/>
-    <hyperlink ref="C889" r:id="rId889" xr:uid="{00000000-0004-0000-0000-000078030000}"/>
-    <hyperlink ref="C890" r:id="rId890" xr:uid="{00000000-0004-0000-0000-000079030000}"/>
-    <hyperlink ref="C891" r:id="rId891" xr:uid="{00000000-0004-0000-0000-00007A030000}"/>
-    <hyperlink ref="C892" r:id="rId892" xr:uid="{00000000-0004-0000-0000-00007B030000}"/>
-    <hyperlink ref="C893" r:id="rId893" xr:uid="{00000000-0004-0000-0000-00007C030000}"/>
-    <hyperlink ref="C63" r:id="rId894" xr:uid="{00000000-0004-0000-0000-00007D030000}"/>
-    <hyperlink ref="C894" r:id="rId895" xr:uid="{00000000-0004-0000-0000-00007E030000}"/>
-    <hyperlink ref="C895" r:id="rId896" xr:uid="{00000000-0004-0000-0000-00007F030000}"/>
-    <hyperlink ref="C896" r:id="rId897" xr:uid="{00000000-0004-0000-0000-000080030000}"/>
-    <hyperlink ref="C897" r:id="rId898" xr:uid="{00000000-0004-0000-0000-000081030000}"/>
-    <hyperlink ref="C898" r:id="rId899" xr:uid="{00000000-0004-0000-0000-000082030000}"/>
-    <hyperlink ref="C899" r:id="rId900" xr:uid="{00000000-0004-0000-0000-000083030000}"/>
-    <hyperlink ref="C900" r:id="rId901" xr:uid="{00000000-0004-0000-0000-000084030000}"/>
-    <hyperlink ref="C901" r:id="rId902" xr:uid="{00000000-0004-0000-0000-000085030000}"/>
-    <hyperlink ref="C902" r:id="rId903" xr:uid="{00000000-0004-0000-0000-000086030000}"/>
-    <hyperlink ref="C903" r:id="rId904" xr:uid="{00000000-0004-0000-0000-000087030000}"/>
-    <hyperlink ref="C904" r:id="rId905" xr:uid="{00000000-0004-0000-0000-000088030000}"/>
-    <hyperlink ref="C905" r:id="rId906" xr:uid="{00000000-0004-0000-0000-000089030000}"/>
+    <hyperlink ref="C908" r:id="rId273" xr:uid="{00000000-0004-0000-0000-000010010000}"/>
+    <hyperlink ref="C312" r:id="rId274" xr:uid="{00000000-0004-0000-0000-000011010000}"/>
+    <hyperlink ref="C313" r:id="rId275" xr:uid="{00000000-0004-0000-0000-000012010000}"/>
+    <hyperlink ref="C314" r:id="rId276" xr:uid="{00000000-0004-0000-0000-000013010000}"/>
+    <hyperlink ref="C315" r:id="rId277" xr:uid="{00000000-0004-0000-0000-000014010000}"/>
+    <hyperlink ref="C316" r:id="rId278" xr:uid="{00000000-0004-0000-0000-000015010000}"/>
+    <hyperlink ref="C26" r:id="rId279" xr:uid="{00000000-0004-0000-0000-000016010000}"/>
+    <hyperlink ref="C317" r:id="rId280" xr:uid="{00000000-0004-0000-0000-000017010000}"/>
+    <hyperlink ref="C318" r:id="rId281" xr:uid="{00000000-0004-0000-0000-000018010000}"/>
+    <hyperlink ref="C319" r:id="rId282" xr:uid="{00000000-0004-0000-0000-000019010000}"/>
+    <hyperlink ref="C320" r:id="rId283" xr:uid="{00000000-0004-0000-0000-00001A010000}"/>
+    <hyperlink ref="C321" r:id="rId284" xr:uid="{00000000-0004-0000-0000-00001B010000}"/>
+    <hyperlink ref="C322" r:id="rId285" xr:uid="{00000000-0004-0000-0000-00001C010000}"/>
+    <hyperlink ref="C323" r:id="rId286" xr:uid="{00000000-0004-0000-0000-00001D010000}"/>
+    <hyperlink ref="C324" r:id="rId287" xr:uid="{00000000-0004-0000-0000-00001E010000}"/>
+    <hyperlink ref="C325" r:id="rId288" xr:uid="{00000000-0004-0000-0000-00001F010000}"/>
+    <hyperlink ref="C27" r:id="rId289" xr:uid="{00000000-0004-0000-0000-000020010000}"/>
+    <hyperlink ref="C326" r:id="rId290" xr:uid="{00000000-0004-0000-0000-000021010000}"/>
+    <hyperlink ref="C28" r:id="rId291" xr:uid="{00000000-0004-0000-0000-000022010000}"/>
+    <hyperlink ref="C327" r:id="rId292" xr:uid="{00000000-0004-0000-0000-000023010000}"/>
+    <hyperlink ref="C328" r:id="rId293" xr:uid="{00000000-0004-0000-0000-000024010000}"/>
+    <hyperlink ref="C329" r:id="rId294" xr:uid="{00000000-0004-0000-0000-000025010000}"/>
+    <hyperlink ref="C330" r:id="rId295" xr:uid="{00000000-0004-0000-0000-000026010000}"/>
+    <hyperlink ref="C331" r:id="rId296" xr:uid="{00000000-0004-0000-0000-000027010000}"/>
+    <hyperlink ref="C332" r:id="rId297" xr:uid="{00000000-0004-0000-0000-000028010000}"/>
+    <hyperlink ref="C333" r:id="rId298" xr:uid="{00000000-0004-0000-0000-000029010000}"/>
+    <hyperlink ref="C334" r:id="rId299" xr:uid="{00000000-0004-0000-0000-00002A010000}"/>
+    <hyperlink ref="C335" r:id="rId300" xr:uid="{00000000-0004-0000-0000-00002B010000}"/>
+    <hyperlink ref="C336" r:id="rId301" xr:uid="{00000000-0004-0000-0000-00002C010000}"/>
+    <hyperlink ref="C337" r:id="rId302" xr:uid="{00000000-0004-0000-0000-00002D010000}"/>
+    <hyperlink ref="C338" r:id="rId303" xr:uid="{00000000-0004-0000-0000-00002E010000}"/>
+    <hyperlink ref="C339" r:id="rId304" xr:uid="{00000000-0004-0000-0000-00002F010000}"/>
+    <hyperlink ref="C340" r:id="rId305" xr:uid="{00000000-0004-0000-0000-000030010000}"/>
+    <hyperlink ref="C341" r:id="rId306" xr:uid="{00000000-0004-0000-0000-000031010000}"/>
+    <hyperlink ref="C342" r:id="rId307" xr:uid="{00000000-0004-0000-0000-000032010000}"/>
+    <hyperlink ref="C343" r:id="rId308" xr:uid="{00000000-0004-0000-0000-000033010000}"/>
+    <hyperlink ref="C344" r:id="rId309" xr:uid="{00000000-0004-0000-0000-000034010000}"/>
+    <hyperlink ref="C345" r:id="rId310" xr:uid="{00000000-0004-0000-0000-000035010000}"/>
+    <hyperlink ref="C29" r:id="rId311" xr:uid="{00000000-0004-0000-0000-000036010000}"/>
+    <hyperlink ref="C346" r:id="rId312" xr:uid="{00000000-0004-0000-0000-000037010000}"/>
+    <hyperlink ref="C347" r:id="rId313" xr:uid="{00000000-0004-0000-0000-000038010000}"/>
+    <hyperlink ref="C348" r:id="rId314" xr:uid="{00000000-0004-0000-0000-000039010000}"/>
+    <hyperlink ref="C349" r:id="rId315" xr:uid="{00000000-0004-0000-0000-00003A010000}"/>
+    <hyperlink ref="C350" r:id="rId316" xr:uid="{00000000-0004-0000-0000-00003B010000}"/>
+    <hyperlink ref="C351" r:id="rId317" xr:uid="{00000000-0004-0000-0000-00003C010000}"/>
+    <hyperlink ref="C352" r:id="rId318" xr:uid="{00000000-0004-0000-0000-00003D010000}"/>
+    <hyperlink ref="C353" r:id="rId319" xr:uid="{00000000-0004-0000-0000-00003E010000}"/>
+    <hyperlink ref="C354" r:id="rId320" xr:uid="{00000000-0004-0000-0000-00003F010000}"/>
+    <hyperlink ref="C30" r:id="rId321" xr:uid="{00000000-0004-0000-0000-000040010000}"/>
+    <hyperlink ref="C355" r:id="rId322" xr:uid="{00000000-0004-0000-0000-000041010000}"/>
+    <hyperlink ref="C356" r:id="rId323" xr:uid="{00000000-0004-0000-0000-000042010000}"/>
+    <hyperlink ref="C357" r:id="rId324" xr:uid="{00000000-0004-0000-0000-000043010000}"/>
+    <hyperlink ref="C358" r:id="rId325" xr:uid="{00000000-0004-0000-0000-000044010000}"/>
+    <hyperlink ref="C359" r:id="rId326" xr:uid="{00000000-0004-0000-0000-000045010000}"/>
+    <hyperlink ref="C360" r:id="rId327" xr:uid="{00000000-0004-0000-0000-000046010000}"/>
+    <hyperlink ref="C361" r:id="rId328" xr:uid="{00000000-0004-0000-0000-000047010000}"/>
+    <hyperlink ref="C362" r:id="rId329" xr:uid="{00000000-0004-0000-0000-000048010000}"/>
+    <hyperlink ref="C363" r:id="rId330" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
+    <hyperlink ref="C364" r:id="rId331" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
+    <hyperlink ref="C365" r:id="rId332" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
+    <hyperlink ref="C366" r:id="rId333" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
+    <hyperlink ref="C367" r:id="rId334" xr:uid="{00000000-0004-0000-0000-00004D010000}"/>
+    <hyperlink ref="C368" r:id="rId335" xr:uid="{00000000-0004-0000-0000-00004E010000}"/>
+    <hyperlink ref="C369" r:id="rId336" xr:uid="{00000000-0004-0000-0000-00004F010000}"/>
+    <hyperlink ref="C370" r:id="rId337" xr:uid="{00000000-0004-0000-0000-000050010000}"/>
+    <hyperlink ref="C371" r:id="rId338" xr:uid="{00000000-0004-0000-0000-000051010000}"/>
+    <hyperlink ref="C372" r:id="rId339" xr:uid="{00000000-0004-0000-0000-000052010000}"/>
+    <hyperlink ref="C373" r:id="rId340" xr:uid="{00000000-0004-0000-0000-000053010000}"/>
+    <hyperlink ref="C374" r:id="rId341" xr:uid="{00000000-0004-0000-0000-000054010000}"/>
+    <hyperlink ref="C375" r:id="rId342" xr:uid="{00000000-0004-0000-0000-000055010000}"/>
+    <hyperlink ref="C376" r:id="rId343" xr:uid="{00000000-0004-0000-0000-000056010000}"/>
+    <hyperlink ref="C377" r:id="rId344" xr:uid="{00000000-0004-0000-0000-000057010000}"/>
+    <hyperlink ref="C378" r:id="rId345" xr:uid="{00000000-0004-0000-0000-000058010000}"/>
+    <hyperlink ref="C379" r:id="rId346" xr:uid="{00000000-0004-0000-0000-000059010000}"/>
+    <hyperlink ref="C380" r:id="rId347" xr:uid="{00000000-0004-0000-0000-00005A010000}"/>
+    <hyperlink ref="C381" r:id="rId348" xr:uid="{00000000-0004-0000-0000-00005B010000}"/>
+    <hyperlink ref="C382" r:id="rId349" xr:uid="{00000000-0004-0000-0000-00005C010000}"/>
+    <hyperlink ref="C383" r:id="rId350" xr:uid="{00000000-0004-0000-0000-00005D010000}"/>
+    <hyperlink ref="C384" r:id="rId351" xr:uid="{00000000-0004-0000-0000-00005E010000}"/>
+    <hyperlink ref="C31" r:id="rId352" xr:uid="{00000000-0004-0000-0000-00005F010000}"/>
+    <hyperlink ref="C32" r:id="rId353" xr:uid="{00000000-0004-0000-0000-000060010000}"/>
+    <hyperlink ref="C385" r:id="rId354" xr:uid="{00000000-0004-0000-0000-000061010000}"/>
+    <hyperlink ref="C386" r:id="rId355" xr:uid="{00000000-0004-0000-0000-000062010000}"/>
+    <hyperlink ref="C387" r:id="rId356" xr:uid="{00000000-0004-0000-0000-000063010000}"/>
+    <hyperlink ref="C388" r:id="rId357" xr:uid="{00000000-0004-0000-0000-000064010000}"/>
+    <hyperlink ref="C389" r:id="rId358" xr:uid="{00000000-0004-0000-0000-000065010000}"/>
+    <hyperlink ref="C33" r:id="rId359" xr:uid="{00000000-0004-0000-0000-000066010000}"/>
+    <hyperlink ref="C390" r:id="rId360" xr:uid="{00000000-0004-0000-0000-000067010000}"/>
+    <hyperlink ref="C391" r:id="rId361" xr:uid="{00000000-0004-0000-0000-000068010000}"/>
+    <hyperlink ref="C392" r:id="rId362" xr:uid="{00000000-0004-0000-0000-000069010000}"/>
+    <hyperlink ref="C393" r:id="rId363" xr:uid="{00000000-0004-0000-0000-00006A010000}"/>
+    <hyperlink ref="C394" r:id="rId364" xr:uid="{00000000-0004-0000-0000-00006B010000}"/>
+    <hyperlink ref="C395" r:id="rId365" xr:uid="{00000000-0004-0000-0000-00006C010000}"/>
+    <hyperlink ref="C396" r:id="rId366" xr:uid="{00000000-0004-0000-0000-00006D010000}"/>
+    <hyperlink ref="C397" r:id="rId367" xr:uid="{00000000-0004-0000-0000-00006E010000}"/>
+    <hyperlink ref="C398" r:id="rId368" xr:uid="{00000000-0004-0000-0000-00006F010000}"/>
+    <hyperlink ref="C399" r:id="rId369" xr:uid="{00000000-0004-0000-0000-000070010000}"/>
+    <hyperlink ref="C400" r:id="rId370" xr:uid="{00000000-0004-0000-0000-000071010000}"/>
+    <hyperlink ref="C401" r:id="rId371" xr:uid="{00000000-0004-0000-0000-000072010000}"/>
+    <hyperlink ref="C402" r:id="rId372" xr:uid="{00000000-0004-0000-0000-000073010000}"/>
+    <hyperlink ref="C403" r:id="rId373" xr:uid="{00000000-0004-0000-0000-000074010000}"/>
+    <hyperlink ref="C404" r:id="rId374" xr:uid="{00000000-0004-0000-0000-000075010000}"/>
+    <hyperlink ref="C405" r:id="rId375" xr:uid="{00000000-0004-0000-0000-000076010000}"/>
+    <hyperlink ref="C406" r:id="rId376" xr:uid="{00000000-0004-0000-0000-000077010000}"/>
+    <hyperlink ref="C407" r:id="rId377" xr:uid="{00000000-0004-0000-0000-000078010000}"/>
+    <hyperlink ref="C408" r:id="rId378" xr:uid="{00000000-0004-0000-0000-000079010000}"/>
+    <hyperlink ref="C409" r:id="rId379" xr:uid="{00000000-0004-0000-0000-00007A010000}"/>
+    <hyperlink ref="C410" r:id="rId380" xr:uid="{00000000-0004-0000-0000-00007B010000}"/>
+    <hyperlink ref="C411" r:id="rId381" xr:uid="{00000000-0004-0000-0000-00007C010000}"/>
+    <hyperlink ref="C412" r:id="rId382" xr:uid="{00000000-0004-0000-0000-00007D010000}"/>
+    <hyperlink ref="C413" r:id="rId383" xr:uid="{00000000-0004-0000-0000-00007E010000}"/>
+    <hyperlink ref="C414" r:id="rId384" xr:uid="{00000000-0004-0000-0000-00007F010000}"/>
+    <hyperlink ref="C415" r:id="rId385" xr:uid="{00000000-0004-0000-0000-000080010000}"/>
+    <hyperlink ref="C416" r:id="rId386" xr:uid="{00000000-0004-0000-0000-000081010000}"/>
+    <hyperlink ref="C417" r:id="rId387" xr:uid="{00000000-0004-0000-0000-000082010000}"/>
+    <hyperlink ref="C418" r:id="rId388" xr:uid="{00000000-0004-0000-0000-000083010000}"/>
+    <hyperlink ref="C419" r:id="rId389" xr:uid="{00000000-0004-0000-0000-000084010000}"/>
+    <hyperlink ref="C420" r:id="rId390" xr:uid="{00000000-0004-0000-0000-000085010000}"/>
+    <hyperlink ref="C421" r:id="rId391" xr:uid="{00000000-0004-0000-0000-000086010000}"/>
+    <hyperlink ref="C422" r:id="rId392" xr:uid="{00000000-0004-0000-0000-000087010000}"/>
+    <hyperlink ref="C423" r:id="rId393" xr:uid="{00000000-0004-0000-0000-000088010000}"/>
+    <hyperlink ref="C424" r:id="rId394" xr:uid="{00000000-0004-0000-0000-000089010000}"/>
+    <hyperlink ref="C425" r:id="rId395" xr:uid="{00000000-0004-0000-0000-00008A010000}"/>
+    <hyperlink ref="C426" r:id="rId396" xr:uid="{00000000-0004-0000-0000-00008B010000}"/>
+    <hyperlink ref="C427" r:id="rId397" xr:uid="{00000000-0004-0000-0000-00008C010000}"/>
+    <hyperlink ref="C428" r:id="rId398" xr:uid="{00000000-0004-0000-0000-00008D010000}"/>
+    <hyperlink ref="C909" r:id="rId399" xr:uid="{00000000-0004-0000-0000-00008E010000}"/>
+    <hyperlink ref="C429" r:id="rId400" xr:uid="{00000000-0004-0000-0000-00008F010000}"/>
+    <hyperlink ref="C430" r:id="rId401" xr:uid="{00000000-0004-0000-0000-000090010000}"/>
+    <hyperlink ref="C431" r:id="rId402" xr:uid="{00000000-0004-0000-0000-000091010000}"/>
+    <hyperlink ref="C432" r:id="rId403" xr:uid="{00000000-0004-0000-0000-000092010000}"/>
+    <hyperlink ref="C433" r:id="rId404" xr:uid="{00000000-0004-0000-0000-000093010000}"/>
+    <hyperlink ref="C434" r:id="rId405" xr:uid="{00000000-0004-0000-0000-000094010000}"/>
+    <hyperlink ref="C435" r:id="rId406" xr:uid="{00000000-0004-0000-0000-000095010000}"/>
+    <hyperlink ref="C436" r:id="rId407" xr:uid="{00000000-0004-0000-0000-000096010000}"/>
+    <hyperlink ref="C437" r:id="rId408" xr:uid="{00000000-0004-0000-0000-000097010000}"/>
+    <hyperlink ref="C438" r:id="rId409" xr:uid="{00000000-0004-0000-0000-000098010000}"/>
+    <hyperlink ref="C439" r:id="rId410" xr:uid="{00000000-0004-0000-0000-000099010000}"/>
+    <hyperlink ref="C440" r:id="rId411" xr:uid="{00000000-0004-0000-0000-00009A010000}"/>
+    <hyperlink ref="C441" r:id="rId412" xr:uid="{00000000-0004-0000-0000-00009B010000}"/>
+    <hyperlink ref="C442" r:id="rId413" xr:uid="{00000000-0004-0000-0000-00009C010000}"/>
+    <hyperlink ref="C34" r:id="rId414" xr:uid="{00000000-0004-0000-0000-00009D010000}"/>
+    <hyperlink ref="C443" r:id="rId415" xr:uid="{00000000-0004-0000-0000-00009E010000}"/>
+    <hyperlink ref="C444" r:id="rId416" xr:uid="{00000000-0004-0000-0000-00009F010000}"/>
+    <hyperlink ref="C445" r:id="rId417" xr:uid="{00000000-0004-0000-0000-0000A0010000}"/>
+    <hyperlink ref="C446" r:id="rId418" xr:uid="{00000000-0004-0000-0000-0000A1010000}"/>
+    <hyperlink ref="C447" r:id="rId419" xr:uid="{00000000-0004-0000-0000-0000A2010000}"/>
+    <hyperlink ref="C448" r:id="rId420" xr:uid="{00000000-0004-0000-0000-0000A3010000}"/>
+    <hyperlink ref="C449" r:id="rId421" xr:uid="{00000000-0004-0000-0000-0000A4010000}"/>
+    <hyperlink ref="C450" r:id="rId422" xr:uid="{00000000-0004-0000-0000-0000A5010000}"/>
+    <hyperlink ref="C451" r:id="rId423" xr:uid="{00000000-0004-0000-0000-0000A6010000}"/>
+    <hyperlink ref="C452" r:id="rId424" xr:uid="{00000000-0004-0000-0000-0000A7010000}"/>
+    <hyperlink ref="C453" r:id="rId425" xr:uid="{00000000-0004-0000-0000-0000A8010000}"/>
+    <hyperlink ref="C454" r:id="rId426" xr:uid="{00000000-0004-0000-0000-0000A9010000}"/>
+    <hyperlink ref="C455" r:id="rId427" xr:uid="{00000000-0004-0000-0000-0000AA010000}"/>
+    <hyperlink ref="C456" r:id="rId428" xr:uid="{00000000-0004-0000-0000-0000AB010000}"/>
+    <hyperlink ref="C457" r:id="rId429" xr:uid="{00000000-0004-0000-0000-0000AC010000}"/>
+    <hyperlink ref="C458" r:id="rId430" xr:uid="{00000000-0004-0000-0000-0000AD010000}"/>
+    <hyperlink ref="C459" r:id="rId431" xr:uid="{00000000-0004-0000-0000-0000AE010000}"/>
+    <hyperlink ref="C460" r:id="rId432" xr:uid="{00000000-0004-0000-0000-0000AF010000}"/>
+    <hyperlink ref="C461" r:id="rId433" xr:uid="{00000000-0004-0000-0000-0000B0010000}"/>
+    <hyperlink ref="C462" r:id="rId434" xr:uid="{00000000-0004-0000-0000-0000B1010000}"/>
+    <hyperlink ref="C463" r:id="rId435" xr:uid="{00000000-0004-0000-0000-0000B2010000}"/>
+    <hyperlink ref="C464" r:id="rId436" xr:uid="{00000000-0004-0000-0000-0000B3010000}"/>
+    <hyperlink ref="C910" r:id="rId437" xr:uid="{00000000-0004-0000-0000-0000B4010000}"/>
+    <hyperlink ref="C465" r:id="rId438" xr:uid="{00000000-0004-0000-0000-0000B5010000}"/>
+    <hyperlink ref="C466" r:id="rId439" xr:uid="{00000000-0004-0000-0000-0000B6010000}"/>
+    <hyperlink ref="C467" r:id="rId440" xr:uid="{00000000-0004-0000-0000-0000B7010000}"/>
+    <hyperlink ref="C468" r:id="rId441" xr:uid="{00000000-0004-0000-0000-0000B8010000}"/>
+    <hyperlink ref="C469" r:id="rId442" xr:uid="{00000000-0004-0000-0000-0000B9010000}"/>
+    <hyperlink ref="C470" r:id="rId443" xr:uid="{00000000-0004-0000-0000-0000BA010000}"/>
+    <hyperlink ref="C471" r:id="rId444" xr:uid="{00000000-0004-0000-0000-0000BB010000}"/>
+    <hyperlink ref="C472" r:id="rId445" xr:uid="{00000000-0004-0000-0000-0000BC010000}"/>
+    <hyperlink ref="C473" r:id="rId446" xr:uid="{00000000-0004-0000-0000-0000BD010000}"/>
+    <hyperlink ref="C474" r:id="rId447" xr:uid="{00000000-0004-0000-0000-0000BE010000}"/>
+    <hyperlink ref="C475" r:id="rId448" xr:uid="{00000000-0004-0000-0000-0000BF010000}"/>
+    <hyperlink ref="C476" r:id="rId449" xr:uid="{00000000-0004-0000-0000-0000C0010000}"/>
+    <hyperlink ref="C477" r:id="rId450" xr:uid="{00000000-0004-0000-0000-0000C1010000}"/>
+    <hyperlink ref="C478" r:id="rId451" xr:uid="{00000000-0004-0000-0000-0000C2010000}"/>
+    <hyperlink ref="C479" r:id="rId452" xr:uid="{00000000-0004-0000-0000-0000C3010000}"/>
+    <hyperlink ref="C480" r:id="rId453" xr:uid="{00000000-0004-0000-0000-0000C4010000}"/>
+    <hyperlink ref="C481" r:id="rId454" xr:uid="{00000000-0004-0000-0000-0000C5010000}"/>
+    <hyperlink ref="C482" r:id="rId455" xr:uid="{00000000-0004-0000-0000-0000C6010000}"/>
+    <hyperlink ref="C483" r:id="rId456" xr:uid="{00000000-0004-0000-0000-0000C7010000}"/>
+    <hyperlink ref="C484" r:id="rId457" xr:uid="{00000000-0004-0000-0000-0000C8010000}"/>
+    <hyperlink ref="C485" r:id="rId458" xr:uid="{00000000-0004-0000-0000-0000C9010000}"/>
+    <hyperlink ref="C486" r:id="rId459" xr:uid="{00000000-0004-0000-0000-0000CA010000}"/>
+    <hyperlink ref="C487" r:id="rId460" xr:uid="{00000000-0004-0000-0000-0000CB010000}"/>
+    <hyperlink ref="C488" r:id="rId461" xr:uid="{00000000-0004-0000-0000-0000CC010000}"/>
+    <hyperlink ref="C489" r:id="rId462" xr:uid="{00000000-0004-0000-0000-0000CD010000}"/>
+    <hyperlink ref="C490" r:id="rId463" xr:uid="{00000000-0004-0000-0000-0000CE010000}"/>
+    <hyperlink ref="C35" r:id="rId464" xr:uid="{00000000-0004-0000-0000-0000CF010000}"/>
+    <hyperlink ref="C491" r:id="rId465" xr:uid="{00000000-0004-0000-0000-0000D0010000}"/>
+    <hyperlink ref="C492" r:id="rId466" xr:uid="{00000000-0004-0000-0000-0000D1010000}"/>
+    <hyperlink ref="C493" r:id="rId467" xr:uid="{00000000-0004-0000-0000-0000D2010000}"/>
+    <hyperlink ref="C494" r:id="rId468" xr:uid="{00000000-0004-0000-0000-0000D3010000}"/>
+    <hyperlink ref="C495" r:id="rId469" xr:uid="{00000000-0004-0000-0000-0000D4010000}"/>
+    <hyperlink ref="C496" r:id="rId470" xr:uid="{00000000-0004-0000-0000-0000D5010000}"/>
+    <hyperlink ref="C497" r:id="rId471" xr:uid="{00000000-0004-0000-0000-0000D6010000}"/>
+    <hyperlink ref="C498" r:id="rId472" xr:uid="{00000000-0004-0000-0000-0000D7010000}"/>
+    <hyperlink ref="C36" r:id="rId473" xr:uid="{00000000-0004-0000-0000-0000D8010000}"/>
+    <hyperlink ref="C499" r:id="rId474" xr:uid="{00000000-0004-0000-0000-0000D9010000}"/>
+    <hyperlink ref="C500" r:id="rId475" xr:uid="{00000000-0004-0000-0000-0000DA010000}"/>
+    <hyperlink ref="C501" r:id="rId476" xr:uid="{00000000-0004-0000-0000-0000DB010000}"/>
+    <hyperlink ref="C502" r:id="rId477" xr:uid="{00000000-0004-0000-0000-0000DC010000}"/>
+    <hyperlink ref="C911" r:id="rId478" xr:uid="{00000000-0004-0000-0000-0000DD010000}"/>
+    <hyperlink ref="C503" r:id="rId479" xr:uid="{00000000-0004-0000-0000-0000DE010000}"/>
+    <hyperlink ref="C504" r:id="rId480" xr:uid="{00000000-0004-0000-0000-0000DF010000}"/>
+    <hyperlink ref="C505" r:id="rId481" xr:uid="{00000000-0004-0000-0000-0000E0010000}"/>
+    <hyperlink ref="C506" r:id="rId482" xr:uid="{00000000-0004-0000-0000-0000E1010000}"/>
+    <hyperlink ref="C507" r:id="rId483" xr:uid="{00000000-0004-0000-0000-0000E2010000}"/>
+    <hyperlink ref="C508" r:id="rId484" xr:uid="{00000000-0004-0000-0000-0000E3010000}"/>
+    <hyperlink ref="C509" r:id="rId485" xr:uid="{00000000-0004-0000-0000-0000E4010000}"/>
+    <hyperlink ref="C510" r:id="rId486" xr:uid="{00000000-0004-0000-0000-0000E5010000}"/>
+    <hyperlink ref="C511" r:id="rId487" xr:uid="{00000000-0004-0000-0000-0000E6010000}"/>
+    <hyperlink ref="C512" r:id="rId488" xr:uid="{00000000-0004-0000-0000-0000E7010000}"/>
+    <hyperlink ref="C513" r:id="rId489" xr:uid="{00000000-0004-0000-0000-0000E8010000}"/>
+    <hyperlink ref="C514" r:id="rId490" xr:uid="{00000000-0004-0000-0000-0000E9010000}"/>
+    <hyperlink ref="C515" r:id="rId491" xr:uid="{00000000-0004-0000-0000-0000EA010000}"/>
+    <hyperlink ref="C516" r:id="rId492" xr:uid="{00000000-0004-0000-0000-0000EB010000}"/>
+    <hyperlink ref="C517" r:id="rId493" xr:uid="{00000000-0004-0000-0000-0000EC010000}"/>
+    <hyperlink ref="C518" r:id="rId494" xr:uid="{00000000-0004-0000-0000-0000ED010000}"/>
+    <hyperlink ref="C519" r:id="rId495" xr:uid="{00000000-0004-0000-0000-0000EE010000}"/>
+    <hyperlink ref="C37" r:id="rId496" xr:uid="{00000000-0004-0000-0000-0000EF010000}"/>
+    <hyperlink ref="C520" r:id="rId497" xr:uid="{00000000-0004-0000-0000-0000F0010000}"/>
+    <hyperlink ref="C521" r:id="rId498" xr:uid="{00000000-0004-0000-0000-0000F1010000}"/>
+    <hyperlink ref="C522" r:id="rId499" xr:uid="{00000000-0004-0000-0000-0000F2010000}"/>
+    <hyperlink ref="C523" r:id="rId500" xr:uid="{00000000-0004-0000-0000-0000F3010000}"/>
+    <hyperlink ref="C524" r:id="rId501" xr:uid="{00000000-0004-0000-0000-0000F4010000}"/>
+    <hyperlink ref="C525" r:id="rId502" xr:uid="{00000000-0004-0000-0000-0000F5010000}"/>
+    <hyperlink ref="C38" r:id="rId503" xr:uid="{00000000-0004-0000-0000-0000F6010000}"/>
+    <hyperlink ref="C526" r:id="rId504" xr:uid="{00000000-0004-0000-0000-0000F7010000}"/>
+    <hyperlink ref="C527" r:id="rId505" xr:uid="{00000000-0004-0000-0000-0000F8010000}"/>
+    <hyperlink ref="C528" r:id="rId506" xr:uid="{00000000-0004-0000-0000-0000F9010000}"/>
+    <hyperlink ref="C529" r:id="rId507" xr:uid="{00000000-0004-0000-0000-0000FA010000}"/>
+    <hyperlink ref="C530" r:id="rId508" xr:uid="{00000000-0004-0000-0000-0000FB010000}"/>
+    <hyperlink ref="C531" r:id="rId509" xr:uid="{00000000-0004-0000-0000-0000FC010000}"/>
+    <hyperlink ref="C532" r:id="rId510" xr:uid="{00000000-0004-0000-0000-0000FD010000}"/>
+    <hyperlink ref="C533" r:id="rId511" xr:uid="{00000000-0004-0000-0000-0000FE010000}"/>
+    <hyperlink ref="C534" r:id="rId512" xr:uid="{00000000-0004-0000-0000-0000FF010000}"/>
+    <hyperlink ref="C535" r:id="rId513" xr:uid="{00000000-0004-0000-0000-000000020000}"/>
+    <hyperlink ref="C536" r:id="rId514" xr:uid="{00000000-0004-0000-0000-000001020000}"/>
+    <hyperlink ref="C537" r:id="rId515" xr:uid="{00000000-0004-0000-0000-000002020000}"/>
+    <hyperlink ref="C538" r:id="rId516" xr:uid="{00000000-0004-0000-0000-000003020000}"/>
+    <hyperlink ref="C39" r:id="rId517" xr:uid="{00000000-0004-0000-0000-000004020000}"/>
+    <hyperlink ref="C539" r:id="rId518" xr:uid="{00000000-0004-0000-0000-000005020000}"/>
+    <hyperlink ref="C540" r:id="rId519" xr:uid="{00000000-0004-0000-0000-000006020000}"/>
+    <hyperlink ref="C541" r:id="rId520" xr:uid="{00000000-0004-0000-0000-000007020000}"/>
+    <hyperlink ref="C542" r:id="rId521" xr:uid="{00000000-0004-0000-0000-000008020000}"/>
+    <hyperlink ref="C543" r:id="rId522" xr:uid="{00000000-0004-0000-0000-000009020000}"/>
+    <hyperlink ref="C544" r:id="rId523" xr:uid="{00000000-0004-0000-0000-00000A020000}"/>
+    <hyperlink ref="C545" r:id="rId524" xr:uid="{00000000-0004-0000-0000-00000B020000}"/>
+    <hyperlink ref="C546" r:id="rId525" xr:uid="{00000000-0004-0000-0000-00000C020000}"/>
+    <hyperlink ref="C547" r:id="rId526" xr:uid="{00000000-0004-0000-0000-00000D020000}"/>
+    <hyperlink ref="C548" r:id="rId527" xr:uid="{00000000-0004-0000-0000-00000E020000}"/>
+    <hyperlink ref="C40" r:id="rId528" xr:uid="{00000000-0004-0000-0000-00000F020000}"/>
+    <hyperlink ref="C549" r:id="rId529" xr:uid="{00000000-0004-0000-0000-000010020000}"/>
+    <hyperlink ref="C550" r:id="rId530" xr:uid="{00000000-0004-0000-0000-000011020000}"/>
+    <hyperlink ref="C41" r:id="rId531" xr:uid="{00000000-0004-0000-0000-000012020000}"/>
+    <hyperlink ref="C551" r:id="rId532" xr:uid="{00000000-0004-0000-0000-000013020000}"/>
+    <hyperlink ref="C552" r:id="rId533" xr:uid="{00000000-0004-0000-0000-000014020000}"/>
+    <hyperlink ref="C553" r:id="rId534" xr:uid="{00000000-0004-0000-0000-000015020000}"/>
+    <hyperlink ref="C554" r:id="rId535" xr:uid="{00000000-0004-0000-0000-000016020000}"/>
+    <hyperlink ref="C555" r:id="rId536" xr:uid="{00000000-0004-0000-0000-000017020000}"/>
+    <hyperlink ref="C556" r:id="rId537" xr:uid="{00000000-0004-0000-0000-000018020000}"/>
+    <hyperlink ref="C557" r:id="rId538" xr:uid="{00000000-0004-0000-0000-000019020000}"/>
+    <hyperlink ref="C558" r:id="rId539" xr:uid="{00000000-0004-0000-0000-00001A020000}"/>
+    <hyperlink ref="C559" r:id="rId540" xr:uid="{00000000-0004-0000-0000-00001B020000}"/>
+    <hyperlink ref="C560" r:id="rId541" xr:uid="{00000000-0004-0000-0000-00001C020000}"/>
+    <hyperlink ref="C561" r:id="rId542" xr:uid="{00000000-0004-0000-0000-00001D020000}"/>
+    <hyperlink ref="C562" r:id="rId543" xr:uid="{00000000-0004-0000-0000-00001E020000}"/>
+    <hyperlink ref="C563" r:id="rId544" xr:uid="{00000000-0004-0000-0000-00001F020000}"/>
+    <hyperlink ref="C564" r:id="rId545" xr:uid="{00000000-0004-0000-0000-000020020000}"/>
+    <hyperlink ref="C565" r:id="rId546" xr:uid="{00000000-0004-0000-0000-000021020000}"/>
+    <hyperlink ref="C566" r:id="rId547" xr:uid="{00000000-0004-0000-0000-000022020000}"/>
+    <hyperlink ref="C567" r:id="rId548" xr:uid="{00000000-0004-0000-0000-000023020000}"/>
+    <hyperlink ref="C568" r:id="rId549" xr:uid="{00000000-0004-0000-0000-000024020000}"/>
+    <hyperlink ref="C569" r:id="rId550" xr:uid="{00000000-0004-0000-0000-000025020000}"/>
+    <hyperlink ref="C570" r:id="rId551" xr:uid="{00000000-0004-0000-0000-000026020000}"/>
+    <hyperlink ref="C571" r:id="rId552" xr:uid="{00000000-0004-0000-0000-000027020000}"/>
+    <hyperlink ref="C572" r:id="rId553" xr:uid="{00000000-0004-0000-0000-000028020000}"/>
+    <hyperlink ref="C573" r:id="rId554" xr:uid="{00000000-0004-0000-0000-000029020000}"/>
+    <hyperlink ref="C574" r:id="rId555" xr:uid="{00000000-0004-0000-0000-00002A020000}"/>
+    <hyperlink ref="C575" r:id="rId556" xr:uid="{00000000-0004-0000-0000-00002B020000}"/>
+    <hyperlink ref="C576" r:id="rId557" xr:uid="{00000000-0004-0000-0000-00002C020000}"/>
+    <hyperlink ref="C577" r:id="rId558" xr:uid="{00000000-0004-0000-0000-00002D020000}"/>
+    <hyperlink ref="C578" r:id="rId559" xr:uid="{00000000-0004-0000-0000-00002E020000}"/>
+    <hyperlink ref="C579" r:id="rId560" xr:uid="{00000000-0004-0000-0000-00002F020000}"/>
+    <hyperlink ref="C580" r:id="rId561" xr:uid="{00000000-0004-0000-0000-000030020000}"/>
+    <hyperlink ref="C581" r:id="rId562" xr:uid="{00000000-0004-0000-0000-000031020000}"/>
+    <hyperlink ref="C582" r:id="rId563" xr:uid="{00000000-0004-0000-0000-000032020000}"/>
+    <hyperlink ref="C583" r:id="rId564" xr:uid="{00000000-0004-0000-0000-000033020000}"/>
+    <hyperlink ref="C584" r:id="rId565" xr:uid="{00000000-0004-0000-0000-000034020000}"/>
+    <hyperlink ref="C585" r:id="rId566" xr:uid="{00000000-0004-0000-0000-000035020000}"/>
+    <hyperlink ref="C586" r:id="rId567" xr:uid="{00000000-0004-0000-0000-000036020000}"/>
+    <hyperlink ref="C587" r:id="rId568" xr:uid="{00000000-0004-0000-0000-000037020000}"/>
+    <hyperlink ref="C588" r:id="rId569" xr:uid="{00000000-0004-0000-0000-000038020000}"/>
+    <hyperlink ref="C589" r:id="rId570" xr:uid="{00000000-0004-0000-0000-000039020000}"/>
+    <hyperlink ref="C590" r:id="rId571" xr:uid="{00000000-0004-0000-0000-00003A020000}"/>
+    <hyperlink ref="C591" r:id="rId572" xr:uid="{00000000-0004-0000-0000-00003B020000}"/>
+    <hyperlink ref="C592" r:id="rId573" xr:uid="{00000000-0004-0000-0000-00003C020000}"/>
+    <hyperlink ref="C593" r:id="rId574" xr:uid="{00000000-0004-0000-0000-00003D020000}"/>
+    <hyperlink ref="C594" r:id="rId575" xr:uid="{00000000-0004-0000-0000-00003E020000}"/>
+    <hyperlink ref="C595" r:id="rId576" xr:uid="{00000000-0004-0000-0000-00003F020000}"/>
+    <hyperlink ref="C596" r:id="rId577" xr:uid="{00000000-0004-0000-0000-000040020000}"/>
+    <hyperlink ref="C597" r:id="rId578" xr:uid="{00000000-0004-0000-0000-000041020000}"/>
+    <hyperlink ref="C598" r:id="rId579" xr:uid="{00000000-0004-0000-0000-000042020000}"/>
+    <hyperlink ref="C599" r:id="rId580" xr:uid="{00000000-0004-0000-0000-000043020000}"/>
+    <hyperlink ref="C600" r:id="rId581" xr:uid="{00000000-0004-0000-0000-000044020000}"/>
+    <hyperlink ref="C42" r:id="rId582" xr:uid="{00000000-0004-0000-0000-000045020000}"/>
+    <hyperlink ref="C601" r:id="rId583" xr:uid="{00000000-0004-0000-0000-000046020000}"/>
+    <hyperlink ref="C602" r:id="rId584" xr:uid="{00000000-0004-0000-0000-000047020000}"/>
+    <hyperlink ref="C603" r:id="rId585" xr:uid="{00000000-0004-0000-0000-000048020000}"/>
+    <hyperlink ref="C604" r:id="rId586" xr:uid="{00000000-0004-0000-0000-000049020000}"/>
+    <hyperlink ref="C605" r:id="rId587" xr:uid="{00000000-0004-0000-0000-00004A020000}"/>
+    <hyperlink ref="C606" r:id="rId588" xr:uid="{00000000-0004-0000-0000-00004B020000}"/>
+    <hyperlink ref="C607" r:id="rId589" xr:uid="{00000000-0004-0000-0000-00004C020000}"/>
+    <hyperlink ref="C608" r:id="rId590" xr:uid="{00000000-0004-0000-0000-00004D020000}"/>
+    <hyperlink ref="C609" r:id="rId591" xr:uid="{00000000-0004-0000-0000-00004E020000}"/>
+    <hyperlink ref="C610" r:id="rId592" xr:uid="{00000000-0004-0000-0000-00004F020000}"/>
+    <hyperlink ref="C611" r:id="rId593" xr:uid="{00000000-0004-0000-0000-000050020000}"/>
+    <hyperlink ref="C612" r:id="rId594" xr:uid="{00000000-0004-0000-0000-000051020000}"/>
+    <hyperlink ref="C613" r:id="rId595" xr:uid="{00000000-0004-0000-0000-000052020000}"/>
+    <hyperlink ref="C614" r:id="rId596" xr:uid="{00000000-0004-0000-0000-000053020000}"/>
+    <hyperlink ref="C615" r:id="rId597" xr:uid="{00000000-0004-0000-0000-000054020000}"/>
+    <hyperlink ref="C616" r:id="rId598" xr:uid="{00000000-0004-0000-0000-000055020000}"/>
+    <hyperlink ref="C617" r:id="rId599" xr:uid="{00000000-0004-0000-0000-000056020000}"/>
+    <hyperlink ref="C618" r:id="rId600" xr:uid="{00000000-0004-0000-0000-000057020000}"/>
+    <hyperlink ref="C619" r:id="rId601" xr:uid="{00000000-0004-0000-0000-000058020000}"/>
+    <hyperlink ref="C620" r:id="rId602" xr:uid="{00000000-0004-0000-0000-000059020000}"/>
+    <hyperlink ref="C621" r:id="rId603" xr:uid="{00000000-0004-0000-0000-00005A020000}"/>
+    <hyperlink ref="C622" r:id="rId604" xr:uid="{00000000-0004-0000-0000-00005B020000}"/>
+    <hyperlink ref="C623" r:id="rId605" xr:uid="{00000000-0004-0000-0000-00005C020000}"/>
+    <hyperlink ref="C624" r:id="rId606" xr:uid="{00000000-0004-0000-0000-00005D020000}"/>
+    <hyperlink ref="C625" r:id="rId607" xr:uid="{00000000-0004-0000-0000-00005E020000}"/>
+    <hyperlink ref="C626" r:id="rId608" xr:uid="{00000000-0004-0000-0000-00005F020000}"/>
+    <hyperlink ref="C627" r:id="rId609" xr:uid="{00000000-0004-0000-0000-000060020000}"/>
+    <hyperlink ref="C628" r:id="rId610" xr:uid="{00000000-0004-0000-0000-000061020000}"/>
+    <hyperlink ref="C629" r:id="rId611" xr:uid="{00000000-0004-0000-0000-000062020000}"/>
+    <hyperlink ref="C43" r:id="rId612" xr:uid="{00000000-0004-0000-0000-000063020000}"/>
+    <hyperlink ref="C630" r:id="rId613" xr:uid="{00000000-0004-0000-0000-000064020000}"/>
+    <hyperlink ref="C631" r:id="rId614" xr:uid="{00000000-0004-0000-0000-000065020000}"/>
+    <hyperlink ref="C632" r:id="rId615" xr:uid="{00000000-0004-0000-0000-000066020000}"/>
+    <hyperlink ref="C633" r:id="rId616" xr:uid="{00000000-0004-0000-0000-000067020000}"/>
+    <hyperlink ref="C634" r:id="rId617" xr:uid="{00000000-0004-0000-0000-000068020000}"/>
+    <hyperlink ref="C635" r:id="rId618" xr:uid="{00000000-0004-0000-0000-000069020000}"/>
+    <hyperlink ref="C636" r:id="rId619" xr:uid="{00000000-0004-0000-0000-00006A020000}"/>
+    <hyperlink ref="C637" r:id="rId620" xr:uid="{00000000-0004-0000-0000-00006B020000}"/>
+    <hyperlink ref="C638" r:id="rId621" xr:uid="{00000000-0004-0000-0000-00006C020000}"/>
+    <hyperlink ref="C639" r:id="rId622" xr:uid="{00000000-0004-0000-0000-00006D020000}"/>
+    <hyperlink ref="C640" r:id="rId623" xr:uid="{00000000-0004-0000-0000-00006E020000}"/>
+    <hyperlink ref="C641" r:id="rId624" xr:uid="{00000000-0004-0000-0000-00006F020000}"/>
+    <hyperlink ref="C642" r:id="rId625" xr:uid="{00000000-0004-0000-0000-000070020000}"/>
+    <hyperlink ref="C643" r:id="rId626" xr:uid="{00000000-0004-0000-0000-000071020000}"/>
+    <hyperlink ref="C644" r:id="rId627" xr:uid="{00000000-0004-0000-0000-000072020000}"/>
+    <hyperlink ref="C645" r:id="rId628" xr:uid="{00000000-0004-0000-0000-000073020000}"/>
+    <hyperlink ref="C646" r:id="rId629" xr:uid="{00000000-0004-0000-0000-000074020000}"/>
+    <hyperlink ref="C647" r:id="rId630" xr:uid="{00000000-0004-0000-0000-000075020000}"/>
+    <hyperlink ref="C648" r:id="rId631" xr:uid="{00000000-0004-0000-0000-000076020000}"/>
+    <hyperlink ref="C649" r:id="rId632" xr:uid="{00000000-0004-0000-0000-000077020000}"/>
+    <hyperlink ref="C650" r:id="rId633" xr:uid="{00000000-0004-0000-0000-000078020000}"/>
+    <hyperlink ref="C651" r:id="rId634" xr:uid="{00000000-0004-0000-0000-000079020000}"/>
+    <hyperlink ref="C652" r:id="rId635" xr:uid="{00000000-0004-0000-0000-00007A020000}"/>
+    <hyperlink ref="C653" r:id="rId636" xr:uid="{00000000-0004-0000-0000-00007B020000}"/>
+    <hyperlink ref="C654" r:id="rId637" xr:uid="{00000000-0004-0000-0000-00007C020000}"/>
+    <hyperlink ref="C655" r:id="rId638" xr:uid="{00000000-0004-0000-0000-00007D020000}"/>
+    <hyperlink ref="C656" r:id="rId639" xr:uid="{00000000-0004-0000-0000-00007E020000}"/>
+    <hyperlink ref="C657" r:id="rId640" xr:uid="{00000000-0004-0000-0000-00007F020000}"/>
+    <hyperlink ref="C658" r:id="rId641" xr:uid="{00000000-0004-0000-0000-000080020000}"/>
+    <hyperlink ref="C659" r:id="rId642" xr:uid="{00000000-0004-0000-0000-000081020000}"/>
+    <hyperlink ref="C660" r:id="rId643" xr:uid="{00000000-0004-0000-0000-000082020000}"/>
+    <hyperlink ref="C661" r:id="rId644" xr:uid="{00000000-0004-0000-0000-000083020000}"/>
+    <hyperlink ref="C662" r:id="rId645" xr:uid="{00000000-0004-0000-0000-000084020000}"/>
+    <hyperlink ref="C663" r:id="rId646" xr:uid="{00000000-0004-0000-0000-000085020000}"/>
+    <hyperlink ref="C664" r:id="rId647" xr:uid="{00000000-0004-0000-0000-000086020000}"/>
+    <hyperlink ref="C665" r:id="rId648" xr:uid="{00000000-0004-0000-0000-000087020000}"/>
+    <hyperlink ref="C666" r:id="rId649" xr:uid="{00000000-0004-0000-0000-000088020000}"/>
+    <hyperlink ref="C667" r:id="rId650" xr:uid="{00000000-0004-0000-0000-000089020000}"/>
+    <hyperlink ref="C668" r:id="rId651" xr:uid="{00000000-0004-0000-0000-00008A020000}"/>
+    <hyperlink ref="C669" r:id="rId652" xr:uid="{00000000-0004-0000-0000-00008B020000}"/>
+    <hyperlink ref="C670" r:id="rId653" xr:uid="{00000000-0004-0000-0000-00008C020000}"/>
+    <hyperlink ref="C44" r:id="rId654" xr:uid="{00000000-0004-0000-0000-00008D020000}"/>
+    <hyperlink ref="C671" r:id="rId655" xr:uid="{00000000-0004-0000-0000-00008E020000}"/>
+    <hyperlink ref="C672" r:id="rId656" xr:uid="{00000000-0004-0000-0000-00008F020000}"/>
+    <hyperlink ref="C673" r:id="rId657" xr:uid="{00000000-0004-0000-0000-000090020000}"/>
+    <hyperlink ref="C674" r:id="rId658" xr:uid="{00000000-0004-0000-0000-000091020000}"/>
+    <hyperlink ref="C675" r:id="rId659" xr:uid="{00000000-0004-0000-0000-000092020000}"/>
+    <hyperlink ref="C676" r:id="rId660" xr:uid="{00000000-0004-0000-0000-000093020000}"/>
+    <hyperlink ref="C677" r:id="rId661" xr:uid="{00000000-0004-0000-0000-000094020000}"/>
+    <hyperlink ref="C678" r:id="rId662" xr:uid="{00000000-0004-0000-0000-000095020000}"/>
+    <hyperlink ref="C679" r:id="rId663" xr:uid="{00000000-0004-0000-0000-000096020000}"/>
+    <hyperlink ref="C680" r:id="rId664" xr:uid="{00000000-0004-0000-0000-000097020000}"/>
+    <hyperlink ref="C681" r:id="rId665" xr:uid="{00000000-0004-0000-0000-000098020000}"/>
+    <hyperlink ref="C682" r:id="rId666" xr:uid="{00000000-0004-0000-0000-000099020000}"/>
+    <hyperlink ref="C683" r:id="rId667" xr:uid="{00000000-0004-0000-0000-00009A020000}"/>
+    <hyperlink ref="C684" r:id="rId668" xr:uid="{00000000-0004-0000-0000-00009B020000}"/>
+    <hyperlink ref="C685" r:id="rId669" xr:uid="{00000000-0004-0000-0000-00009C020000}"/>
+    <hyperlink ref="C686" r:id="rId670" xr:uid="{00000000-0004-0000-0000-00009D020000}"/>
+    <hyperlink ref="C687" r:id="rId671" xr:uid="{00000000-0004-0000-0000-00009E020000}"/>
+    <hyperlink ref="C688" r:id="rId672" xr:uid="{00000000-0004-0000-0000-00009F020000}"/>
+    <hyperlink ref="C689" r:id="rId673" xr:uid="{00000000-0004-0000-0000-0000A0020000}"/>
+    <hyperlink ref="C690" r:id="rId674" xr:uid="{00000000-0004-0000-0000-0000A1020000}"/>
+    <hyperlink ref="C691" r:id="rId675" xr:uid="{00000000-0004-0000-0000-0000A2020000}"/>
+    <hyperlink ref="C692" r:id="rId676" xr:uid="{00000000-0004-0000-0000-0000A3020000}"/>
+    <hyperlink ref="C693" r:id="rId677" xr:uid="{00000000-0004-0000-0000-0000A4020000}"/>
+    <hyperlink ref="C694" r:id="rId678" xr:uid="{00000000-0004-0000-0000-0000A5020000}"/>
+    <hyperlink ref="C695" r:id="rId679" xr:uid="{00000000-0004-0000-0000-0000A6020000}"/>
+    <hyperlink ref="C696" r:id="rId680" xr:uid="{00000000-0004-0000-0000-0000A7020000}"/>
+    <hyperlink ref="C697" r:id="rId681" xr:uid="{00000000-0004-0000-0000-0000A8020000}"/>
+    <hyperlink ref="C698" r:id="rId682" xr:uid="{00000000-0004-0000-0000-0000A9020000}"/>
+    <hyperlink ref="C699" r:id="rId683" xr:uid="{00000000-0004-0000-0000-0000AA020000}"/>
+    <hyperlink ref="C700" r:id="rId684" xr:uid="{00000000-0004-0000-0000-0000AB020000}"/>
+    <hyperlink ref="C701" r:id="rId685" xr:uid="{00000000-0004-0000-0000-0000AC020000}"/>
+    <hyperlink ref="C702" r:id="rId686" xr:uid="{00000000-0004-0000-0000-0000AD020000}"/>
+    <hyperlink ref="C703" r:id="rId687" xr:uid="{00000000-0004-0000-0000-0000AE020000}"/>
+    <hyperlink ref="C704" r:id="rId688" xr:uid="{00000000-0004-0000-0000-0000AF020000}"/>
+    <hyperlink ref="C705" r:id="rId689" xr:uid="{00000000-0004-0000-0000-0000B0020000}"/>
+    <hyperlink ref="C706" r:id="rId690" xr:uid="{00000000-0004-0000-0000-0000B1020000}"/>
+    <hyperlink ref="C707" r:id="rId691" xr:uid="{00000000-0004-0000-0000-0000B2020000}"/>
+    <hyperlink ref="C708" r:id="rId692" xr:uid="{00000000-0004-0000-0000-0000B3020000}"/>
+    <hyperlink ref="C709" r:id="rId693" xr:uid="{00000000-0004-0000-0000-0000B4020000}"/>
+    <hyperlink ref="C45" r:id="rId694" xr:uid="{00000000-0004-0000-0000-0000B5020000}"/>
+    <hyperlink ref="C710" r:id="rId695" xr:uid="{00000000-0004-0000-0000-0000B6020000}"/>
+    <hyperlink ref="C711" r:id="rId696" xr:uid="{00000000-0004-0000-0000-0000B7020000}"/>
+    <hyperlink ref="C712" r:id="rId697" xr:uid="{00000000-0004-0000-0000-0000B8020000}"/>
+    <hyperlink ref="C713" r:id="rId698" xr:uid="{00000000-0004-0000-0000-0000B9020000}"/>
+    <hyperlink ref="C714" r:id="rId699" xr:uid="{00000000-0004-0000-0000-0000BA020000}"/>
+    <hyperlink ref="C715" r:id="rId700" xr:uid="{00000000-0004-0000-0000-0000BB020000}"/>
+    <hyperlink ref="C716" r:id="rId701" xr:uid="{00000000-0004-0000-0000-0000BC020000}"/>
+    <hyperlink ref="C717" r:id="rId702" xr:uid="{00000000-0004-0000-0000-0000BD020000}"/>
+    <hyperlink ref="C718" r:id="rId703" xr:uid="{00000000-0004-0000-0000-0000BE020000}"/>
+    <hyperlink ref="C719" r:id="rId704" xr:uid="{00000000-0004-0000-0000-0000BF020000}"/>
+    <hyperlink ref="C720" r:id="rId705" xr:uid="{00000000-0004-0000-0000-0000C0020000}"/>
+    <hyperlink ref="C721" r:id="rId706" xr:uid="{00000000-0004-0000-0000-0000C1020000}"/>
+    <hyperlink ref="C722" r:id="rId707" xr:uid="{00000000-0004-0000-0000-0000C2020000}"/>
+    <hyperlink ref="C723" r:id="rId708" xr:uid="{00000000-0004-0000-0000-0000C3020000}"/>
+    <hyperlink ref="C724" r:id="rId709" xr:uid="{00000000-0004-0000-0000-0000C4020000}"/>
+    <hyperlink ref="C46" r:id="rId710" xr:uid="{00000000-0004-0000-0000-0000C5020000}"/>
+    <hyperlink ref="C725" r:id="rId711" xr:uid="{00000000-0004-0000-0000-0000C6020000}"/>
+    <hyperlink ref="C726" r:id="rId712" xr:uid="{00000000-0004-0000-0000-0000C7020000}"/>
+    <hyperlink ref="C727" r:id="rId713" xr:uid="{00000000-0004-0000-0000-0000C8020000}"/>
+    <hyperlink ref="C728" r:id="rId714" xr:uid="{00000000-0004-0000-0000-0000C9020000}"/>
+    <hyperlink ref="C729" r:id="rId715" xr:uid="{00000000-0004-0000-0000-0000CA020000}"/>
+    <hyperlink ref="C730" r:id="rId716" xr:uid="{00000000-0004-0000-0000-0000CB020000}"/>
+    <hyperlink ref="C731" r:id="rId717" xr:uid="{00000000-0004-0000-0000-0000CC020000}"/>
+    <hyperlink ref="C732" r:id="rId718" xr:uid="{00000000-0004-0000-0000-0000CD020000}"/>
+    <hyperlink ref="C733" r:id="rId719" xr:uid="{00000000-0004-0000-0000-0000CE020000}"/>
+    <hyperlink ref="C734" r:id="rId720" xr:uid="{00000000-0004-0000-0000-0000CF020000}"/>
+    <hyperlink ref="C735" r:id="rId721" xr:uid="{00000000-0004-0000-0000-0000D0020000}"/>
+    <hyperlink ref="C736" r:id="rId722" xr:uid="{00000000-0004-0000-0000-0000D1020000}"/>
+    <hyperlink ref="C737" r:id="rId723" xr:uid="{00000000-0004-0000-0000-0000D2020000}"/>
+    <hyperlink ref="C738" r:id="rId724" xr:uid="{00000000-0004-0000-0000-0000D3020000}"/>
+    <hyperlink ref="C739" r:id="rId725" xr:uid="{00000000-0004-0000-0000-0000D4020000}"/>
+    <hyperlink ref="C47" r:id="rId726" xr:uid="{00000000-0004-0000-0000-0000D5020000}"/>
+    <hyperlink ref="C740" r:id="rId727" xr:uid="{00000000-0004-0000-0000-0000D6020000}"/>
+    <hyperlink ref="C741" r:id="rId728" xr:uid="{00000000-0004-0000-0000-0000D7020000}"/>
+    <hyperlink ref="C742" r:id="rId729" xr:uid="{00000000-0004-0000-0000-0000D8020000}"/>
+    <hyperlink ref="C743" r:id="rId730" xr:uid="{00000000-0004-0000-0000-0000D9020000}"/>
+    <hyperlink ref="C48" r:id="rId731" xr:uid="{00000000-0004-0000-0000-0000DA020000}"/>
+    <hyperlink ref="C744" r:id="rId732" xr:uid="{00000000-0004-0000-0000-0000DB020000}"/>
+    <hyperlink ref="C745" r:id="rId733" xr:uid="{00000000-0004-0000-0000-0000DC020000}"/>
+    <hyperlink ref="C49" r:id="rId734" xr:uid="{00000000-0004-0000-0000-0000DD020000}"/>
+    <hyperlink ref="C746" r:id="rId735" xr:uid="{00000000-0004-0000-0000-0000DE020000}"/>
+    <hyperlink ref="C747" r:id="rId736" xr:uid="{00000000-0004-0000-0000-0000DF020000}"/>
+    <hyperlink ref="C748" r:id="rId737" xr:uid="{00000000-0004-0000-0000-0000E0020000}"/>
+    <hyperlink ref="C749" r:id="rId738" xr:uid="{00000000-0004-0000-0000-0000E1020000}"/>
+    <hyperlink ref="C750" r:id="rId739" xr:uid="{00000000-0004-0000-0000-0000E2020000}"/>
+    <hyperlink ref="C751" r:id="rId740" xr:uid="{00000000-0004-0000-0000-0000E3020000}"/>
+    <hyperlink ref="C50" r:id="rId741" xr:uid="{00000000-0004-0000-0000-0000E4020000}"/>
+    <hyperlink ref="C752" r:id="rId742" xr:uid="{00000000-0004-0000-0000-0000E5020000}"/>
+    <hyperlink ref="C51" r:id="rId743" xr:uid="{00000000-0004-0000-0000-0000E6020000}"/>
+    <hyperlink ref="C753" r:id="rId744" xr:uid="{00000000-0004-0000-0000-0000E7020000}"/>
+    <hyperlink ref="C754" r:id="rId745" xr:uid="{00000000-0004-0000-0000-0000E8020000}"/>
+    <hyperlink ref="C755" r:id="rId746" xr:uid="{00000000-0004-0000-0000-0000E9020000}"/>
+    <hyperlink ref="C756" r:id="rId747" xr:uid="{00000000-0004-0000-0000-0000EA020000}"/>
+    <hyperlink ref="C757" r:id="rId748" xr:uid="{00000000-0004-0000-0000-0000EB020000}"/>
+    <hyperlink ref="C758" r:id="rId749" xr:uid="{00000000-0004-0000-0000-0000EC020000}"/>
+    <hyperlink ref="C759" r:id="rId750" xr:uid="{00000000-0004-0000-0000-0000ED020000}"/>
+    <hyperlink ref="C760" r:id="rId751" xr:uid="{00000000-0004-0000-0000-0000EE020000}"/>
+    <hyperlink ref="C761" r:id="rId752" xr:uid="{00000000-0004-0000-0000-0000EF020000}"/>
+    <hyperlink ref="C762" r:id="rId753" xr:uid="{00000000-0004-0000-0000-0000F0020000}"/>
+    <hyperlink ref="C763" r:id="rId754" xr:uid="{00000000-0004-0000-0000-0000F1020000}"/>
+    <hyperlink ref="C764" r:id="rId755" xr:uid="{00000000-0004-0000-0000-0000F2020000}"/>
+    <hyperlink ref="C765" r:id="rId756" xr:uid="{00000000-0004-0000-0000-0000F3020000}"/>
+    <hyperlink ref="C766" r:id="rId757" xr:uid="{00000000-0004-0000-0000-0000F4020000}"/>
+    <hyperlink ref="C767" r:id="rId758" xr:uid="{00000000-0004-0000-0000-0000F5020000}"/>
+    <hyperlink ref="C768" r:id="rId759" xr:uid="{00000000-0004-0000-0000-0000F6020000}"/>
+    <hyperlink ref="C769" r:id="rId760" xr:uid="{00000000-0004-0000-0000-0000F7020000}"/>
+    <hyperlink ref="C770" r:id="rId761" xr:uid="{00000000-0004-0000-0000-0000F8020000}"/>
+    <hyperlink ref="C771" r:id="rId762" xr:uid="{00000000-0004-0000-0000-0000F9020000}"/>
+    <hyperlink ref="C772" r:id="rId763" xr:uid="{00000000-0004-0000-0000-0000FA020000}"/>
+    <hyperlink ref="C773" r:id="rId764" xr:uid="{00000000-0004-0000-0000-0000FB020000}"/>
+    <hyperlink ref="C774" r:id="rId765" xr:uid="{00000000-0004-0000-0000-0000FC020000}"/>
+    <hyperlink ref="C775" r:id="rId766" xr:uid="{00000000-0004-0000-0000-0000FD020000}"/>
+    <hyperlink ref="C776" r:id="rId767" xr:uid="{00000000-0004-0000-0000-0000FE020000}"/>
+    <hyperlink ref="C777" r:id="rId768" xr:uid="{00000000-0004-0000-0000-0000FF020000}"/>
+    <hyperlink ref="C778" r:id="rId769" xr:uid="{00000000-0004-0000-0000-000000030000}"/>
+    <hyperlink ref="C779" r:id="rId770" xr:uid="{00000000-0004-0000-0000-000001030000}"/>
+    <hyperlink ref="C780" r:id="rId771" xr:uid="{00000000-0004-0000-0000-000002030000}"/>
+    <hyperlink ref="C781" r:id="rId772" xr:uid="{00000000-0004-0000-0000-000003030000}"/>
+    <hyperlink ref="C782" r:id="rId773" xr:uid="{00000000-0004-0000-0000-000004030000}"/>
+    <hyperlink ref="C783" r:id="rId774" xr:uid="{00000000-0004-0000-0000-000005030000}"/>
+    <hyperlink ref="C784" r:id="rId775" xr:uid="{00000000-0004-0000-0000-000006030000}"/>
+    <hyperlink ref="C785" r:id="rId776" xr:uid="{00000000-0004-0000-0000-000007030000}"/>
+    <hyperlink ref="C786" r:id="rId777" xr:uid="{00000000-0004-0000-0000-000008030000}"/>
+    <hyperlink ref="C787" r:id="rId778" xr:uid="{00000000-0004-0000-0000-000009030000}"/>
+    <hyperlink ref="C788" r:id="rId779" xr:uid="{00000000-0004-0000-0000-00000A030000}"/>
+    <hyperlink ref="C789" r:id="rId780" xr:uid="{00000000-0004-0000-0000-00000B030000}"/>
+    <hyperlink ref="C790" r:id="rId781" xr:uid="{00000000-0004-0000-0000-00000C030000}"/>
+    <hyperlink ref="C791" r:id="rId782" xr:uid="{00000000-0004-0000-0000-00000D030000}"/>
+    <hyperlink ref="C792" r:id="rId783" xr:uid="{00000000-0004-0000-0000-00000E030000}"/>
+    <hyperlink ref="C793" r:id="rId784" xr:uid="{00000000-0004-0000-0000-00000F030000}"/>
+    <hyperlink ref="C794" r:id="rId785" xr:uid="{00000000-0004-0000-0000-000010030000}"/>
+    <hyperlink ref="C52" r:id="rId786" xr:uid="{00000000-0004-0000-0000-000011030000}"/>
+    <hyperlink ref="C795" r:id="rId787" xr:uid="{00000000-0004-0000-0000-000012030000}"/>
+    <hyperlink ref="C796" r:id="rId788" xr:uid="{00000000-0004-0000-0000-000013030000}"/>
+    <hyperlink ref="C797" r:id="rId789" xr:uid="{00000000-0004-0000-0000-000014030000}"/>
+    <hyperlink ref="C798" r:id="rId790" xr:uid="{00000000-0004-0000-0000-000015030000}"/>
+    <hyperlink ref="C799" r:id="rId791" xr:uid="{00000000-0004-0000-0000-000016030000}"/>
+    <hyperlink ref="C800" r:id="rId792" xr:uid="{00000000-0004-0000-0000-000017030000}"/>
+    <hyperlink ref="C801" r:id="rId793" xr:uid="{00000000-0004-0000-0000-000018030000}"/>
+    <hyperlink ref="C802" r:id="rId794" xr:uid="{00000000-0004-0000-0000-000019030000}"/>
+    <hyperlink ref="C803" r:id="rId795" xr:uid="{00000000-0004-0000-0000-00001A030000}"/>
+    <hyperlink ref="C804" r:id="rId796" xr:uid="{00000000-0004-0000-0000-00001B030000}"/>
+    <hyperlink ref="C805" r:id="rId797" xr:uid="{00000000-0004-0000-0000-00001C030000}"/>
+    <hyperlink ref="C806" r:id="rId798" xr:uid="{00000000-0004-0000-0000-00001D030000}"/>
+    <hyperlink ref="C807" r:id="rId799" xr:uid="{00000000-0004-0000-0000-00001E030000}"/>
+    <hyperlink ref="C808" r:id="rId800" xr:uid="{00000000-0004-0000-0000-00001F030000}"/>
+    <hyperlink ref="C809" r:id="rId801" xr:uid="{00000000-0004-0000-0000-000020030000}"/>
+    <hyperlink ref="C810" r:id="rId802" xr:uid="{00000000-0004-0000-0000-000021030000}"/>
+    <hyperlink ref="C811" r:id="rId803" xr:uid="{00000000-0004-0000-0000-000022030000}"/>
+    <hyperlink ref="C812" r:id="rId804" xr:uid="{00000000-0004-0000-0000-000023030000}"/>
+    <hyperlink ref="C813" r:id="rId805" xr:uid="{00000000-0004-0000-0000-000024030000}"/>
+    <hyperlink ref="C814" r:id="rId806" xr:uid="{00000000-0004-0000-0000-000025030000}"/>
+    <hyperlink ref="C815" r:id="rId807" xr:uid="{00000000-0004-0000-0000-000026030000}"/>
+    <hyperlink ref="C816" r:id="rId808" xr:uid="{00000000-0004-0000-0000-000027030000}"/>
+    <hyperlink ref="C817" r:id="rId809" xr:uid="{00000000-0004-0000-0000-000028030000}"/>
+    <hyperlink ref="C818" r:id="rId810" xr:uid="{00000000-0004-0000-0000-000029030000}"/>
+    <hyperlink ref="C819" r:id="rId811" xr:uid="{00000000-0004-0000-0000-00002A030000}"/>
+    <hyperlink ref="C53" r:id="rId812" xr:uid="{00000000-0004-0000-0000-00002B030000}"/>
+    <hyperlink ref="C54" r:id="rId813" xr:uid="{00000000-0004-0000-0000-00002C030000}"/>
+    <hyperlink ref="C820" r:id="rId814" xr:uid="{00000000-0004-0000-0000-00002D030000}"/>
+    <hyperlink ref="C821" r:id="rId815" xr:uid="{00000000-0004-0000-0000-00002E030000}"/>
+    <hyperlink ref="C822" r:id="rId816" xr:uid="{00000000-0004-0000-0000-00002F030000}"/>
+    <hyperlink ref="C823" r:id="rId817" xr:uid="{00000000-0004-0000-0000-000030030000}"/>
+    <hyperlink ref="C824" r:id="rId818" xr:uid="{00000000-0004-0000-0000-000031030000}"/>
+    <hyperlink ref="C55" r:id="rId819" xr:uid="{00000000-0004-0000-0000-000032030000}"/>
+    <hyperlink ref="C56" r:id="rId820" xr:uid="{00000000-0004-0000-0000-000033030000}"/>
+    <hyperlink ref="C825" r:id="rId821" xr:uid="{00000000-0004-0000-0000-000034030000}"/>
+    <hyperlink ref="C826" r:id="rId822" xr:uid="{00000000-0004-0000-0000-000035030000}"/>
+    <hyperlink ref="C827" r:id="rId823" xr:uid="{00000000-0004-0000-0000-000036030000}"/>
+    <hyperlink ref="C828" r:id="rId824" xr:uid="{00000000-0004-0000-0000-000037030000}"/>
+    <hyperlink ref="C829" r:id="rId825" xr:uid="{00000000-0004-0000-0000-000038030000}"/>
+    <hyperlink ref="C830" r:id="rId826" xr:uid="{00000000-0004-0000-0000-000039030000}"/>
+    <hyperlink ref="C831" r:id="rId827" xr:uid="{00000000-0004-0000-0000-00003A030000}"/>
+    <hyperlink ref="C832" r:id="rId828" xr:uid="{00000000-0004-0000-0000-00003B030000}"/>
+    <hyperlink ref="C57" r:id="rId829" xr:uid="{00000000-0004-0000-0000-00003C030000}"/>
+    <hyperlink ref="C833" r:id="rId830" xr:uid="{00000000-0004-0000-0000-00003D030000}"/>
+    <hyperlink ref="C834" r:id="rId831" xr:uid="{00000000-0004-0000-0000-00003E030000}"/>
+    <hyperlink ref="C835" r:id="rId832" xr:uid="{00000000-0004-0000-0000-00003F030000}"/>
+    <hyperlink ref="C836" r:id="rId833" xr:uid="{00000000-0004-0000-0000-000040030000}"/>
+    <hyperlink ref="C837" r:id="rId834" xr:uid="{00000000-0004-0000-0000-000041030000}"/>
+    <hyperlink ref="C838" r:id="rId835" xr:uid="{00000000-0004-0000-0000-000042030000}"/>
+    <hyperlink ref="C839" r:id="rId836" xr:uid="{00000000-0004-0000-0000-000043030000}"/>
+    <hyperlink ref="C840" r:id="rId837" xr:uid="{00000000-0004-0000-0000-000044030000}"/>
+    <hyperlink ref="C841" r:id="rId838" xr:uid="{00000000-0004-0000-0000-000045030000}"/>
+    <hyperlink ref="C58" r:id="rId839" xr:uid="{00000000-0004-0000-0000-000046030000}"/>
+    <hyperlink ref="C842" r:id="rId840" xr:uid="{00000000-0004-0000-0000-000047030000}"/>
+    <hyperlink ref="C843" r:id="rId841" xr:uid="{00000000-0004-0000-0000-000048030000}"/>
+    <hyperlink ref="C844" r:id="rId842" xr:uid="{00000000-0004-0000-0000-000049030000}"/>
+    <hyperlink ref="C845" r:id="rId843" xr:uid="{00000000-0004-0000-0000-00004A030000}"/>
+    <hyperlink ref="C912" r:id="rId844" xr:uid="{00000000-0004-0000-0000-00004B030000}"/>
+    <hyperlink ref="C846" r:id="rId845" xr:uid="{00000000-0004-0000-0000-00004C030000}"/>
+    <hyperlink ref="C847" r:id="rId846" xr:uid="{00000000-0004-0000-0000-00004D030000}"/>
+    <hyperlink ref="C848" r:id="rId847" xr:uid="{00000000-0004-0000-0000-00004E030000}"/>
+    <hyperlink ref="C849" r:id="rId848" xr:uid="{00000000-0004-0000-0000-00004F030000}"/>
+    <hyperlink ref="C850" r:id="rId849" xr:uid="{00000000-0004-0000-0000-000050030000}"/>
+    <hyperlink ref="C851" r:id="rId850" xr:uid="{00000000-0004-0000-0000-000051030000}"/>
+    <hyperlink ref="C852" r:id="rId851" xr:uid="{00000000-0004-0000-0000-000052030000}"/>
+    <hyperlink ref="C59" r:id="rId852" xr:uid="{00000000-0004-0000-0000-000053030000}"/>
+    <hyperlink ref="C853" r:id="rId853" xr:uid="{00000000-0004-0000-0000-000054030000}"/>
+    <hyperlink ref="C854" r:id="rId854" xr:uid="{00000000-0004-0000-0000-000055030000}"/>
+    <hyperlink ref="C855" r:id="rId855" xr:uid="{00000000-0004-0000-0000-000056030000}"/>
+    <hyperlink ref="C856" r:id="rId856" xr:uid="{00000000-0004-0000-0000-000057030000}"/>
+    <hyperlink ref="C857" r:id="rId857" xr:uid="{00000000-0004-0000-0000-000058030000}"/>
+    <hyperlink ref="C858" r:id="rId858" xr:uid="{00000000-0004-0000-0000-000059030000}"/>
+    <hyperlink ref="C859" r:id="rId859" xr:uid="{00000000-0004-0000-0000-00005A030000}"/>
+    <hyperlink ref="C860" r:id="rId860" xr:uid="{00000000-0004-0000-0000-00005B030000}"/>
+    <hyperlink ref="C861" r:id="rId861" xr:uid="{00000000-0004-0000-0000-00005C030000}"/>
+    <hyperlink ref="C862" r:id="rId862" xr:uid="{00000000-0004-0000-0000-00005D030000}"/>
+    <hyperlink ref="C863" r:id="rId863" xr:uid="{00000000-0004-0000-0000-00005E030000}"/>
+    <hyperlink ref="C864" r:id="rId864" xr:uid="{00000000-0004-0000-0000-00005F030000}"/>
+    <hyperlink ref="C865" r:id="rId865" xr:uid="{00000000-0004-0000-0000-000060030000}"/>
+    <hyperlink ref="C866" r:id="rId866" xr:uid="{00000000-0004-0000-0000-000061030000}"/>
+    <hyperlink ref="C867" r:id="rId867" xr:uid="{00000000-0004-0000-0000-000062030000}"/>
+    <hyperlink ref="C868" r:id="rId868" xr:uid="{00000000-0004-0000-0000-000063030000}"/>
+    <hyperlink ref="C869" r:id="rId869" xr:uid="{00000000-0004-0000-0000-000064030000}"/>
+    <hyperlink ref="C870" r:id="rId870" xr:uid="{00000000-0004-0000-0000-000065030000}"/>
+    <hyperlink ref="C871" r:id="rId871" xr:uid="{00000000-0004-0000-0000-000066030000}"/>
+    <hyperlink ref="C872" r:id="rId872" xr:uid="{00000000-0004-0000-0000-000067030000}"/>
+    <hyperlink ref="C873" r:id="rId873" xr:uid="{00000000-0004-0000-0000-000068030000}"/>
+    <hyperlink ref="C874" r:id="rId874" xr:uid="{00000000-0004-0000-0000-000069030000}"/>
+    <hyperlink ref="C60" r:id="rId875" xr:uid="{00000000-0004-0000-0000-00006A030000}"/>
+    <hyperlink ref="C875" r:id="rId876" xr:uid="{00000000-0004-0000-0000-00006B030000}"/>
+    <hyperlink ref="C876" r:id="rId877" xr:uid="{00000000-0004-0000-0000-00006C030000}"/>
+    <hyperlink ref="C877" r:id="rId878" xr:uid="{00000000-0004-0000-0000-00006D030000}"/>
+    <hyperlink ref="C878" r:id="rId879" xr:uid="{00000000-0004-0000-0000-00006E030000}"/>
+    <hyperlink ref="C879" r:id="rId880" xr:uid="{00000000-0004-0000-0000-00006F030000}"/>
+    <hyperlink ref="C61" r:id="rId881" xr:uid="{00000000-0004-0000-0000-000070030000}"/>
+    <hyperlink ref="C880" r:id="rId882" xr:uid="{00000000-0004-0000-0000-000071030000}"/>
+    <hyperlink ref="C881" r:id="rId883" xr:uid="{00000000-0004-0000-0000-000072030000}"/>
+    <hyperlink ref="C882" r:id="rId884" xr:uid="{00000000-0004-0000-0000-000073030000}"/>
+    <hyperlink ref="C62" r:id="rId885" xr:uid="{00000000-0004-0000-0000-000074030000}"/>
+    <hyperlink ref="C883" r:id="rId886" xr:uid="{00000000-0004-0000-0000-000075030000}"/>
+    <hyperlink ref="C884" r:id="rId887" xr:uid="{00000000-0004-0000-0000-000076030000}"/>
+    <hyperlink ref="C885" r:id="rId888" xr:uid="{00000000-0004-0000-0000-000077030000}"/>
+    <hyperlink ref="C886" r:id="rId889" xr:uid="{00000000-0004-0000-0000-000078030000}"/>
+    <hyperlink ref="C887" r:id="rId890" xr:uid="{00000000-0004-0000-0000-000079030000}"/>
+    <hyperlink ref="C888" r:id="rId891" xr:uid="{00000000-0004-0000-0000-00007A030000}"/>
+    <hyperlink ref="C889" r:id="rId892" xr:uid="{00000000-0004-0000-0000-00007B030000}"/>
+    <hyperlink ref="C890" r:id="rId893" xr:uid="{00000000-0004-0000-0000-00007C030000}"/>
+    <hyperlink ref="C891" r:id="rId894" xr:uid="{00000000-0004-0000-0000-00007D030000}"/>
+    <hyperlink ref="C892" r:id="rId895" xr:uid="{00000000-0004-0000-0000-00007E030000}"/>
+    <hyperlink ref="C893" r:id="rId896" xr:uid="{00000000-0004-0000-0000-00007F030000}"/>
+    <hyperlink ref="C894" r:id="rId897" xr:uid="{00000000-0004-0000-0000-000080030000}"/>
+    <hyperlink ref="C895" r:id="rId898" xr:uid="{00000000-0004-0000-0000-000081030000}"/>
+    <hyperlink ref="C63" r:id="rId899" xr:uid="{00000000-0004-0000-0000-000082030000}"/>
+    <hyperlink ref="C896" r:id="rId900" xr:uid="{00000000-0004-0000-0000-000083030000}"/>
+    <hyperlink ref="C897" r:id="rId901" xr:uid="{00000000-0004-0000-0000-000084030000}"/>
+    <hyperlink ref="C898" r:id="rId902" xr:uid="{00000000-0004-0000-0000-000085030000}"/>
+    <hyperlink ref="C899" r:id="rId903" xr:uid="{00000000-0004-0000-0000-000086030000}"/>
+    <hyperlink ref="C900" r:id="rId904" xr:uid="{00000000-0004-0000-0000-000087030000}"/>
+    <hyperlink ref="C901" r:id="rId905" xr:uid="{00000000-0004-0000-0000-000088030000}"/>
+    <hyperlink ref="C902" r:id="rId906" xr:uid="{00000000-0004-0000-0000-000089030000}"/>
+    <hyperlink ref="C903" r:id="rId907" xr:uid="{00000000-0004-0000-0000-00008A030000}"/>
+    <hyperlink ref="C904" r:id="rId908" xr:uid="{00000000-0004-0000-0000-00008B030000}"/>
+    <hyperlink ref="C905" r:id="rId909" xr:uid="{00000000-0004-0000-0000-00008C030000}"/>
+    <hyperlink ref="C906" r:id="rId910" xr:uid="{00000000-0004-0000-0000-00008D030000}"/>
+    <hyperlink ref="C907" r:id="rId911" xr:uid="{00000000-0004-0000-0000-00008E030000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19527,7 +19632,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>1816</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -19535,26 +19640,26 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>1817</v>
+        <v>1827</v>
       </c>
       <c r="B3" t="s">
-        <v>1818</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>1819</v>
+        <v>1829</v>
       </c>
       <c r="B4" t="s">
-        <v>1820</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>1821</v>
+        <v>1831</v>
       </c>
       <c r="B5" t="s">
-        <v>1822</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -19562,26 +19667,26 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>1823</v>
+        <v>1833</v>
       </c>
       <c r="B7" t="s">
-        <v>1824</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>1823</v>
+        <v>1833</v>
       </c>
       <c r="B8" t="s">
-        <v>1825</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>1823</v>
+        <v>1833</v>
       </c>
       <c r="B9" t="s">
-        <v>1826</v>
+        <v>1836</v>
       </c>
     </row>
   </sheetData>

--- a/data/danish_artwork_review.xlsx
+++ b/data/danish_artwork_review.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EPGoal\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{940F0F56-D44E-47D5-AB7B-1AE97F59F8C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D3B698E-E104-4D10-AEDF-A2A31CD8ED93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3663" uniqueCount="1837">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3671" uniqueCount="1841">
   <si>
     <t>Nøgle (intern)</t>
   </si>
@@ -2660,6 +2660,12 @@
     <t>Joanna Lumley's Spice Trail Adventure</t>
   </si>
   <si>
+    <t>joanna lumleys eventyr på krydderiruten</t>
+  </si>
+  <si>
+    <t>Joanna Lumleys eventyr på krydderiruten</t>
+  </si>
+  <si>
     <t>john dillermand</t>
   </si>
   <si>
@@ -2910,6 +2916,12 @@
   </si>
   <si>
     <t>Kommissar Van der Valk</t>
+  </si>
+  <si>
+    <t>kommissær dupin</t>
+  </si>
+  <si>
+    <t>Kommissær Dupin</t>
   </si>
   <si>
     <t>kompani o.r.d.</t>
@@ -5909,7 +5921,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F912"/>
+  <dimension ref="A1:F914"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -6403,10 +6415,10 @@
     </row>
     <row r="35" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="B35" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>7</v>
@@ -6417,10 +6429,10 @@
     </row>
     <row r="36" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="B36" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>7</v>
@@ -6431,10 +6443,10 @@
     </row>
     <row r="37" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>994</v>
+        <v>998</v>
       </c>
       <c r="B37" t="s">
-        <v>995</v>
+        <v>999</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>7</v>
@@ -6445,10 +6457,10 @@
     </row>
     <row r="38" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>1008</v>
+        <v>1012</v>
       </c>
       <c r="B38" t="s">
-        <v>1009</v>
+        <v>1013</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>7</v>
@@ -6459,10 +6471,10 @@
     </row>
     <row r="39" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
       <c r="B39" t="s">
-        <v>1037</v>
+        <v>1041</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>7</v>
@@ -6473,10 +6485,10 @@
     </row>
     <row r="40" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>1058</v>
+        <v>1062</v>
       </c>
       <c r="B40" t="s">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>7</v>
@@ -6487,10 +6499,10 @@
     </row>
     <row r="41" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>1064</v>
+        <v>1068</v>
       </c>
       <c r="B41" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>7</v>
@@ -6501,10 +6513,10 @@
     </row>
     <row r="42" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>1166</v>
+        <v>1170</v>
       </c>
       <c r="B42" t="s">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>7</v>
@@ -6515,10 +6527,10 @@
     </row>
     <row r="43" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>1226</v>
+        <v>1230</v>
       </c>
       <c r="B43" t="s">
-        <v>1227</v>
+        <v>1231</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>7</v>
@@ -6529,10 +6541,10 @@
     </row>
     <row r="44" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>1310</v>
+        <v>1314</v>
       </c>
       <c r="B44" t="s">
-        <v>1311</v>
+        <v>1315</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>7</v>
@@ -6543,10 +6555,10 @@
     </row>
     <row r="45" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>1390</v>
+        <v>1394</v>
       </c>
       <c r="B45" t="s">
-        <v>1391</v>
+        <v>1395</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>7</v>
@@ -6557,10 +6569,10 @@
     </row>
     <row r="46" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>1422</v>
+        <v>1426</v>
       </c>
       <c r="B46" t="s">
-        <v>1423</v>
+        <v>1427</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>7</v>
@@ -6571,10 +6583,10 @@
     </row>
     <row r="47" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>1454</v>
+        <v>1458</v>
       </c>
       <c r="B47" t="s">
-        <v>1455</v>
+        <v>1459</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>7</v>
@@ -6585,10 +6597,10 @@
     </row>
     <row r="48" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>1464</v>
+        <v>1468</v>
       </c>
       <c r="B48" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>7</v>
@@ -6599,10 +6611,10 @@
     </row>
     <row r="49" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>1470</v>
+        <v>1474</v>
       </c>
       <c r="B49" t="s">
-        <v>1471</v>
+        <v>1475</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>7</v>
@@ -6613,10 +6625,10 @@
     </row>
     <row r="50" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>1484</v>
+        <v>1488</v>
       </c>
       <c r="B50" t="s">
-        <v>1485</v>
+        <v>1489</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>7</v>
@@ -6627,10 +6639,10 @@
     </row>
     <row r="51" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>1488</v>
+        <v>1492</v>
       </c>
       <c r="B51" t="s">
-        <v>1489</v>
+        <v>1493</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>7</v>
@@ -6641,10 +6653,10 @@
     </row>
     <row r="52" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>1574</v>
+        <v>1578</v>
       </c>
       <c r="B52" t="s">
-        <v>1575</v>
+        <v>1579</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>7</v>
@@ -6655,10 +6667,10 @@
     </row>
     <row r="53" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>1626</v>
+        <v>1630</v>
       </c>
       <c r="B53" t="s">
-        <v>1627</v>
+        <v>1631</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>7</v>
@@ -6669,10 +6681,10 @@
     </row>
     <row r="54" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>1628</v>
+        <v>1632</v>
       </c>
       <c r="B54" t="s">
-        <v>1629</v>
+        <v>1633</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>7</v>
@@ -6683,10 +6695,10 @@
     </row>
     <row r="55" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>1640</v>
+        <v>1644</v>
       </c>
       <c r="B55" t="s">
-        <v>1641</v>
+        <v>1645</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>7</v>
@@ -6697,10 +6709,10 @@
     </row>
     <row r="56" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="B56" t="s">
-        <v>1643</v>
+        <v>1647</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>7</v>
@@ -6711,10 +6723,10 @@
     </row>
     <row r="57" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>1660</v>
+        <v>1664</v>
       </c>
       <c r="B57" t="s">
-        <v>1661</v>
+        <v>1665</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>7</v>
@@ -6725,10 +6737,10 @@
     </row>
     <row r="58" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>1680</v>
+        <v>1684</v>
       </c>
       <c r="B58" t="s">
-        <v>1681</v>
+        <v>1685</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>7</v>
@@ -6739,10 +6751,10 @@
     </row>
     <row r="59" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>1706</v>
+        <v>1710</v>
       </c>
       <c r="B59" t="s">
-        <v>1707</v>
+        <v>1711</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>7</v>
@@ -6753,10 +6765,10 @@
     </row>
     <row r="60" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>1752</v>
+        <v>1756</v>
       </c>
       <c r="B60" t="s">
-        <v>1753</v>
+        <v>1757</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>7</v>
@@ -6767,10 +6779,10 @@
     </row>
     <row r="61" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>1764</v>
+        <v>1768</v>
       </c>
       <c r="B61" t="s">
-        <v>1765</v>
+        <v>1769</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>7</v>
@@ -6781,10 +6793,10 @@
     </row>
     <row r="62" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>1772</v>
+        <v>1776</v>
       </c>
       <c r="B62" t="s">
-        <v>1773</v>
+        <v>1777</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>7</v>
@@ -6795,10 +6807,10 @@
     </row>
     <row r="63" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>1800</v>
+        <v>1804</v>
       </c>
       <c r="B63" t="s">
-        <v>1801</v>
+        <v>1805</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>7</v>
@@ -10281,10 +10293,10 @@
     </row>
     <row r="312" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="B312" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C312" s="2" t="s">
         <v>7</v>
@@ -10295,10 +10307,10 @@
     </row>
     <row r="313" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B313" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="C313" s="2" t="s">
         <v>7</v>
@@ -10309,10 +10321,10 @@
     </row>
     <row r="314" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B314" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="C314" s="2" t="s">
         <v>7</v>
@@ -10323,10 +10335,10 @@
     </row>
     <row r="315" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="B315" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="C315" s="2" t="s">
         <v>7</v>
@@ -10337,10 +10349,10 @@
     </row>
     <row r="316" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="B316" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C316" s="2" t="s">
         <v>7</v>
@@ -10351,10 +10363,10 @@
     </row>
     <row r="317" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B317" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="C317" s="2" t="s">
         <v>7</v>
@@ -10365,10 +10377,10 @@
     </row>
     <row r="318" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="B318" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="C318" s="2" t="s">
         <v>7</v>
@@ -10379,10 +10391,10 @@
     </row>
     <row r="319" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="B319" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C319" s="2" t="s">
         <v>7</v>
@@ -10393,10 +10405,10 @@
     </row>
     <row r="320" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="B320" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C320" s="2" t="s">
         <v>7</v>
@@ -10407,10 +10419,10 @@
     </row>
     <row r="321" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="B321" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C321" s="2" t="s">
         <v>7</v>
@@ -10421,10 +10433,10 @@
     </row>
     <row r="322" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="B322" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C322" s="2" t="s">
         <v>7</v>
@@ -10435,10 +10447,10 @@
     </row>
     <row r="323" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B323" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C323" s="2" t="s">
         <v>7</v>
@@ -10449,10 +10461,10 @@
     </row>
     <row r="324" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="B324" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C324" s="2" t="s">
         <v>7</v>
@@ -10463,10 +10475,10 @@
     </row>
     <row r="325" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="B325" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="C325" s="2" t="s">
         <v>7</v>
@@ -10477,10 +10489,10 @@
     </row>
     <row r="326" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="B326" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="C326" s="2" t="s">
         <v>7</v>
@@ -10491,10 +10503,10 @@
     </row>
     <row r="327" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="B327" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="C327" s="2" t="s">
         <v>7</v>
@@ -10505,10 +10517,10 @@
     </row>
     <row r="328" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="B328" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C328" s="2" t="s">
         <v>7</v>
@@ -10519,10 +10531,10 @@
     </row>
     <row r="329" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="B329" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="C329" s="2" t="s">
         <v>7</v>
@@ -10533,10 +10545,10 @@
     </row>
     <row r="330" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="B330" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="C330" s="2" t="s">
         <v>7</v>
@@ -10547,10 +10559,10 @@
     </row>
     <row r="331" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B331" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="C331" s="2" t="s">
         <v>7</v>
@@ -10561,10 +10573,10 @@
     </row>
     <row r="332" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="B332" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="C332" s="2" t="s">
         <v>7</v>
@@ -10575,10 +10587,10 @@
     </row>
     <row r="333" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="B333" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="C333" s="2" t="s">
         <v>7</v>
@@ -10589,10 +10601,10 @@
     </row>
     <row r="334" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="B334" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C334" s="2" t="s">
         <v>7</v>
@@ -10603,10 +10615,10 @@
     </row>
     <row r="335" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="B335" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C335" s="2" t="s">
         <v>7</v>
@@ -10617,10 +10629,10 @@
     </row>
     <row r="336" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="B336" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="C336" s="2" t="s">
         <v>7</v>
@@ -10631,10 +10643,10 @@
     </row>
     <row r="337" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="B337" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C337" s="2" t="s">
         <v>7</v>
@@ -10645,10 +10657,10 @@
     </row>
     <row r="338" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="B338" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="C338" s="2" t="s">
         <v>7</v>
@@ -10659,10 +10671,10 @@
     </row>
     <row r="339" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="B339" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="C339" s="2" t="s">
         <v>7</v>
@@ -10673,10 +10685,10 @@
     </row>
     <row r="340" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="B340" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="C340" s="2" t="s">
         <v>7</v>
@@ -10687,10 +10699,10 @@
     </row>
     <row r="341" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="B341" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="C341" s="2" t="s">
         <v>7</v>
@@ -10701,10 +10713,10 @@
     </row>
     <row r="342" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="B342" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="C342" s="2" t="s">
         <v>7</v>
@@ -10715,10 +10727,10 @@
     </row>
     <row r="343" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="B343" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="C343" s="2" t="s">
         <v>7</v>
@@ -10729,10 +10741,10 @@
     </row>
     <row r="344" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="B344" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="C344" s="2" t="s">
         <v>7</v>
@@ -10743,10 +10755,10 @@
     </row>
     <row r="345" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B345" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="C345" s="2" t="s">
         <v>7</v>
@@ -10757,10 +10769,10 @@
     </row>
     <row r="346" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="B346" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="C346" s="2" t="s">
         <v>7</v>
@@ -10771,10 +10783,10 @@
     </row>
     <row r="347" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B347" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="C347" s="2" t="s">
         <v>7</v>
@@ -10785,10 +10797,10 @@
     </row>
     <row r="348" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="B348" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="C348" s="2" t="s">
         <v>7</v>
@@ -10799,10 +10811,10 @@
     </row>
     <row r="349" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="B349" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C349" s="2" t="s">
         <v>7</v>
@@ -10813,10 +10825,10 @@
     </row>
     <row r="350" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B350" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C350" s="2" t="s">
         <v>7</v>
@@ -10827,10 +10839,10 @@
     </row>
     <row r="351" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B351" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="C351" s="2" t="s">
         <v>7</v>
@@ -10841,10 +10853,10 @@
     </row>
     <row r="352" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="B352" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="C352" s="2" t="s">
         <v>7</v>
@@ -10855,10 +10867,10 @@
     </row>
     <row r="353" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B353" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="C353" s="2" t="s">
         <v>7</v>
@@ -10869,10 +10881,10 @@
     </row>
     <row r="354" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B354" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C354" s="2" t="s">
         <v>7</v>
@@ -10883,10 +10895,10 @@
     </row>
     <row r="355" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="B355" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="C355" s="2" t="s">
         <v>7</v>
@@ -10897,10 +10909,10 @@
     </row>
     <row r="356" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="B356" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="C356" s="2" t="s">
         <v>7</v>
@@ -10911,10 +10923,10 @@
     </row>
     <row r="357" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="B357" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C357" s="2" t="s">
         <v>7</v>
@@ -10925,10 +10937,10 @@
     </row>
     <row r="358" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B358" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="C358" s="2" t="s">
         <v>7</v>
@@ -10939,10 +10951,10 @@
     </row>
     <row r="359" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="B359" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="C359" s="2" t="s">
         <v>7</v>
@@ -10953,10 +10965,10 @@
     </row>
     <row r="360" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B360" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C360" s="2" t="s">
         <v>7</v>
@@ -10967,10 +10979,10 @@
     </row>
     <row r="361" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="B361" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="C361" s="2" t="s">
         <v>7</v>
@@ -10981,10 +10993,10 @@
     </row>
     <row r="362" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B362" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="C362" s="2" t="s">
         <v>7</v>
@@ -10995,10 +11007,10 @@
     </row>
     <row r="363" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="B363" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="C363" s="2" t="s">
         <v>7</v>
@@ -11009,10 +11021,10 @@
     </row>
     <row r="364" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B364" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="C364" s="2" t="s">
         <v>7</v>
@@ -11023,10 +11035,10 @@
     </row>
     <row r="365" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="B365" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="C365" s="2" t="s">
         <v>7</v>
@@ -11037,10 +11049,10 @@
     </row>
     <row r="366" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="B366" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="C366" s="2" t="s">
         <v>7</v>
@@ -11051,10 +11063,10 @@
     </row>
     <row r="367" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B367" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C367" s="2" t="s">
         <v>7</v>
@@ -11065,10 +11077,10 @@
     </row>
     <row r="368" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="B368" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="C368" s="2" t="s">
         <v>7</v>
@@ -11079,10 +11091,10 @@
     </row>
     <row r="369" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="B369" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="C369" s="2" t="s">
         <v>7</v>
@@ -11093,10 +11105,10 @@
     </row>
     <row r="370" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="B370" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="C370" s="2" t="s">
         <v>7</v>
@@ -11107,10 +11119,10 @@
     </row>
     <row r="371" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="B371" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C371" s="2" t="s">
         <v>7</v>
@@ -11121,10 +11133,10 @@
     </row>
     <row r="372" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="B372" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C372" s="2" t="s">
         <v>7</v>
@@ -11135,10 +11147,10 @@
     </row>
     <row r="373" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B373" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="C373" s="2" t="s">
         <v>7</v>
@@ -11149,10 +11161,10 @@
     </row>
     <row r="374" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="B374" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="C374" s="2" t="s">
         <v>7</v>
@@ -11163,10 +11175,10 @@
     </row>
     <row r="375" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="B375" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="C375" s="2" t="s">
         <v>7</v>
@@ -11177,10 +11189,10 @@
     </row>
     <row r="376" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="B376" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C376" s="2" t="s">
         <v>7</v>
@@ -11191,10 +11203,10 @@
     </row>
     <row r="377" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="B377" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="C377" s="2" t="s">
         <v>7</v>
@@ -11205,10 +11217,10 @@
     </row>
     <row r="378" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="B378" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="C378" s="2" t="s">
         <v>7</v>
@@ -11219,10 +11231,10 @@
     </row>
     <row r="379" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="B379" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C379" s="2" t="s">
         <v>7</v>
@@ -11233,10 +11245,10 @@
     </row>
     <row r="380" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="B380" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="C380" s="2" t="s">
         <v>7</v>
@@ -11247,10 +11259,10 @@
     </row>
     <row r="381" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="B381" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="C381" s="2" t="s">
         <v>7</v>
@@ -11261,10 +11273,10 @@
     </row>
     <row r="382" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="B382" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="C382" s="2" t="s">
         <v>7</v>
@@ -11275,10 +11287,10 @@
     </row>
     <row r="383" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="B383" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="C383" s="2" t="s">
         <v>7</v>
@@ -11289,10 +11301,10 @@
     </row>
     <row r="384" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="B384" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="C384" s="2" t="s">
         <v>7</v>
@@ -11303,10 +11315,10 @@
     </row>
     <row r="385" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="B385" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="C385" s="2" t="s">
         <v>7</v>
@@ -11317,10 +11329,10 @@
     </row>
     <row r="386" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="B386" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="C386" s="2" t="s">
         <v>7</v>
@@ -11331,10 +11343,10 @@
     </row>
     <row r="387" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="B387" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="C387" s="2" t="s">
         <v>7</v>
@@ -11345,10 +11357,10 @@
     </row>
     <row r="388" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="B388" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="C388" s="2" t="s">
         <v>7</v>
@@ -11359,10 +11371,10 @@
     </row>
     <row r="389" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="B389" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="C389" s="2" t="s">
         <v>7</v>
@@ -11373,10 +11385,10 @@
     </row>
     <row r="390" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="B390" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="C390" s="2" t="s">
         <v>7</v>
@@ -11387,10 +11399,10 @@
     </row>
     <row r="391" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="B391" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="C391" s="2" t="s">
         <v>7</v>
@@ -11401,10 +11413,10 @@
     </row>
     <row r="392" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="B392" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C392" s="2" t="s">
         <v>7</v>
@@ -11415,10 +11427,10 @@
     </row>
     <row r="393" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="B393" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="C393" s="2" t="s">
         <v>7</v>
@@ -11429,10 +11441,10 @@
     </row>
     <row r="394" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="B394" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="C394" s="2" t="s">
         <v>7</v>
@@ -11443,10 +11455,10 @@
     </row>
     <row r="395" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="B395" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="C395" s="2" t="s">
         <v>7</v>
@@ -11457,10 +11469,10 @@
     </row>
     <row r="396" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="B396" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="C396" s="2" t="s">
         <v>7</v>
@@ -11471,10 +11483,10 @@
     </row>
     <row r="397" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="B397" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="C397" s="2" t="s">
         <v>7</v>
@@ -11485,10 +11497,10 @@
     </row>
     <row r="398" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="B398" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="C398" s="2" t="s">
         <v>7</v>
@@ -11499,10 +11511,10 @@
     </row>
     <row r="399" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="B399" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C399" s="2" t="s">
         <v>7</v>
@@ -11513,10 +11525,10 @@
     </row>
     <row r="400" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="B400" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="C400" s="2" t="s">
         <v>7</v>
@@ -11527,10 +11539,10 @@
     </row>
     <row r="401" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B401" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="C401" s="2" t="s">
         <v>7</v>
@@ -11541,10 +11553,10 @@
     </row>
     <row r="402" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="B402" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="C402" s="2" t="s">
         <v>7</v>
@@ -11555,10 +11567,10 @@
     </row>
     <row r="403" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="B403" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="C403" s="2" t="s">
         <v>7</v>
@@ -11569,10 +11581,10 @@
     </row>
     <row r="404" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="B404" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="C404" s="2" t="s">
         <v>7</v>
@@ -11583,10 +11595,10 @@
     </row>
     <row r="405" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="B405" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="C405" s="2" t="s">
         <v>7</v>
@@ -11597,10 +11609,10 @@
     </row>
     <row r="406" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="B406" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="C406" s="2" t="s">
         <v>7</v>
@@ -11611,10 +11623,10 @@
     </row>
     <row r="407" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="B407" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="C407" s="2" t="s">
         <v>7</v>
@@ -11625,10 +11637,10 @@
     </row>
     <row r="408" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="B408" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="C408" s="2" t="s">
         <v>7</v>
@@ -11639,10 +11651,10 @@
     </row>
     <row r="409" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="B409" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="C409" s="2" t="s">
         <v>7</v>
@@ -11653,10 +11665,10 @@
     </row>
     <row r="410" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="B410" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="C410" s="2" t="s">
         <v>7</v>
@@ -11667,10 +11679,10 @@
     </row>
     <row r="411" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="B411" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="C411" s="2" t="s">
         <v>7</v>
@@ -11681,10 +11693,10 @@
     </row>
     <row r="412" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="B412" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="C412" s="2" t="s">
         <v>7</v>
@@ -11695,10 +11707,10 @@
     </row>
     <row r="413" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="B413" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="C413" s="2" t="s">
         <v>7</v>
@@ -11709,10 +11721,10 @@
     </row>
     <row r="414" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="B414" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="C414" s="2" t="s">
         <v>7</v>
@@ -11723,10 +11735,10 @@
     </row>
     <row r="415" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="B415" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="C415" s="2" t="s">
         <v>7</v>
@@ -11737,10 +11749,10 @@
     </row>
     <row r="416" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="B416" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="C416" s="2" t="s">
         <v>7</v>
@@ -11751,10 +11763,10 @@
     </row>
     <row r="417" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="B417" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="C417" s="2" t="s">
         <v>7</v>
@@ -11765,10 +11777,10 @@
     </row>
     <row r="418" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="B418" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="C418" s="2" t="s">
         <v>7</v>
@@ -11779,10 +11791,10 @@
     </row>
     <row r="419" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="B419" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="C419" s="2" t="s">
         <v>7</v>
@@ -11793,10 +11805,10 @@
     </row>
     <row r="420" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="B420" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C420" s="2" t="s">
         <v>7</v>
@@ -11807,10 +11819,10 @@
     </row>
     <row r="421" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="B421" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="C421" s="2" t="s">
         <v>7</v>
@@ -11821,10 +11833,10 @@
     </row>
     <row r="422" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="B422" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="C422" s="2" t="s">
         <v>7</v>
@@ -11835,10 +11847,10 @@
     </row>
     <row r="423" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="B423" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="C423" s="2" t="s">
         <v>7</v>
@@ -11849,10 +11861,10 @@
     </row>
     <row r="424" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="B424" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="C424" s="2" t="s">
         <v>7</v>
@@ -11863,10 +11875,10 @@
     </row>
     <row r="425" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="B425" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="C425" s="2" t="s">
         <v>7</v>
@@ -11877,10 +11889,10 @@
     </row>
     <row r="426" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="B426" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="C426" s="2" t="s">
         <v>7</v>
@@ -11891,10 +11903,10 @@
     </row>
     <row r="427" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="B427" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="C427" s="2" t="s">
         <v>7</v>
@@ -11905,10 +11917,10 @@
     </row>
     <row r="428" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="B428" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="C428" s="2" t="s">
         <v>7</v>
@@ -11919,10 +11931,10 @@
     </row>
     <row r="429" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="B429" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="C429" s="2" t="s">
         <v>7</v>
@@ -11933,10 +11945,10 @@
     </row>
     <row r="430" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="B430" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="C430" s="2" t="s">
         <v>7</v>
@@ -11947,10 +11959,10 @@
     </row>
     <row r="431" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="B431" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="C431" s="2" t="s">
         <v>7</v>
@@ -11961,10 +11973,10 @@
     </row>
     <row r="432" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="B432" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="C432" s="2" t="s">
         <v>7</v>
@@ -11975,10 +11987,10 @@
     </row>
     <row r="433" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="B433" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="C433" s="2" t="s">
         <v>7</v>
@@ -11989,10 +12001,10 @@
     </row>
     <row r="434" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="B434" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="C434" s="2" t="s">
         <v>7</v>
@@ -12003,10 +12015,10 @@
     </row>
     <row r="435" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="B435" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
       <c r="C435" s="2" t="s">
         <v>7</v>
@@ -12017,10 +12029,10 @@
     </row>
     <row r="436" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="B436" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
       <c r="C436" s="2" t="s">
         <v>7</v>
@@ -12031,10 +12043,10 @@
     </row>
     <row r="437" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
       <c r="B437" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
       <c r="C437" s="2" t="s">
         <v>7</v>
@@ -12045,10 +12057,10 @@
     </row>
     <row r="438" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
       <c r="B438" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
       <c r="C438" s="2" t="s">
         <v>7</v>
@@ -12059,10 +12071,10 @@
     </row>
     <row r="439" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="B439" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="C439" s="2" t="s">
         <v>7</v>
@@ -12073,10 +12085,10 @@
     </row>
     <row r="440" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
       <c r="B440" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="C440" s="2" t="s">
         <v>7</v>
@@ -12087,10 +12099,10 @@
     </row>
     <row r="441" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="B441" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="C441" s="2" t="s">
         <v>7</v>
@@ -12101,10 +12113,10 @@
     </row>
     <row r="442" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="B442" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="C442" s="2" t="s">
         <v>7</v>
@@ -12115,10 +12127,10 @@
     </row>
     <row r="443" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
-        <v>832</v>
+        <v>826</v>
       </c>
       <c r="B443" t="s">
-        <v>833</v>
+        <v>827</v>
       </c>
       <c r="C443" s="2" t="s">
         <v>7</v>
@@ -12129,10 +12141,10 @@
     </row>
     <row r="444" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
-        <v>834</v>
+        <v>828</v>
       </c>
       <c r="B444" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="C444" s="2" t="s">
         <v>7</v>
@@ -12143,10 +12155,10 @@
     </row>
     <row r="445" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="B445" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="C445" s="2" t="s">
         <v>7</v>
@@ -12157,10 +12169,10 @@
     </row>
     <row r="446" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="B446" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="C446" s="2" t="s">
         <v>7</v>
@@ -12171,10 +12183,10 @@
     </row>
     <row r="447" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="B447" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
       <c r="C447" s="2" t="s">
         <v>7</v>
@@ -12185,10 +12197,10 @@
     </row>
     <row r="448" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="B448" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="C448" s="2" t="s">
         <v>7</v>
@@ -12199,10 +12211,10 @@
     </row>
     <row r="449" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="B449" t="s">
-        <v>845</v>
+        <v>841</v>
       </c>
       <c r="C449" s="2" t="s">
         <v>7</v>
@@ -12213,10 +12225,10 @@
     </row>
     <row r="450" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
-        <v>846</v>
+        <v>842</v>
       </c>
       <c r="B450" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="C450" s="2" t="s">
         <v>7</v>
@@ -12227,10 +12239,10 @@
     </row>
     <row r="451" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="B451" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="C451" s="2" t="s">
         <v>7</v>
@@ -12241,10 +12253,10 @@
     </row>
     <row r="452" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="B452" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="C452" s="2" t="s">
         <v>7</v>
@@ -12255,10 +12267,10 @@
     </row>
     <row r="453" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="B453" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
       <c r="C453" s="2" t="s">
         <v>7</v>
@@ -12269,10 +12281,10 @@
     </row>
     <row r="454" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
       <c r="B454" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="C454" s="2" t="s">
         <v>7</v>
@@ -12283,10 +12295,10 @@
     </row>
     <row r="455" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
       <c r="B455" t="s">
-        <v>857</v>
+        <v>853</v>
       </c>
       <c r="C455" s="2" t="s">
         <v>7</v>
@@ -12297,10 +12309,10 @@
     </row>
     <row r="456" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
       <c r="B456" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="C456" s="2" t="s">
         <v>7</v>
@@ -12311,10 +12323,10 @@
     </row>
     <row r="457" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="B457" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
       <c r="C457" s="2" t="s">
         <v>7</v>
@@ -12325,10 +12337,10 @@
     </row>
     <row r="458" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="B458" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
       <c r="C458" s="2" t="s">
         <v>7</v>
@@ -12339,10 +12351,10 @@
     </row>
     <row r="459" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="B459" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="C459" s="2" t="s">
         <v>7</v>
@@ -12353,10 +12365,10 @@
     </row>
     <row r="460" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="B460" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="C460" s="2" t="s">
         <v>7</v>
@@ -12367,10 +12379,10 @@
     </row>
     <row r="461" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="B461" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
       <c r="C461" s="2" t="s">
         <v>7</v>
@@ -12381,10 +12393,10 @@
     </row>
     <row r="462" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
       <c r="B462" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
       <c r="C462" s="2" t="s">
         <v>7</v>
@@ -12395,10 +12407,10 @@
     </row>
     <row r="463" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="B463" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
       <c r="C463" s="2" t="s">
         <v>7</v>
@@ -12409,10 +12421,10 @@
     </row>
     <row r="464" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="B464" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="C464" s="2" t="s">
         <v>7</v>
@@ -12423,10 +12435,10 @@
     </row>
     <row r="465" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>878</v>
+        <v>872</v>
       </c>
       <c r="B465" t="s">
-        <v>879</v>
+        <v>873</v>
       </c>
       <c r="C465" s="2" t="s">
         <v>7</v>
@@ -12437,10 +12449,10 @@
     </row>
     <row r="466" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
-        <v>880</v>
+        <v>874</v>
       </c>
       <c r="B466" t="s">
-        <v>881</v>
+        <v>875</v>
       </c>
       <c r="C466" s="2" t="s">
         <v>7</v>
@@ -12451,10 +12463,10 @@
     </row>
     <row r="467" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>882</v>
+        <v>876</v>
       </c>
       <c r="B467" t="s">
-        <v>883</v>
+        <v>877</v>
       </c>
       <c r="C467" s="2" t="s">
         <v>7</v>
@@ -12465,10 +12477,10 @@
     </row>
     <row r="468" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
       <c r="B468" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="C468" s="2" t="s">
         <v>7</v>
@@ -12479,10 +12491,10 @@
     </row>
     <row r="469" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="B469" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="C469" s="2" t="s">
         <v>7</v>
@@ -12493,10 +12505,10 @@
     </row>
     <row r="470" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
       <c r="B470" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
       <c r="C470" s="2" t="s">
         <v>7</v>
@@ -12507,10 +12519,10 @@
     </row>
     <row r="471" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="B471" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="C471" s="2" t="s">
         <v>7</v>
@@ -12521,10 +12533,10 @@
     </row>
     <row r="472" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="B472" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="C472" s="2" t="s">
         <v>7</v>
@@ -12535,10 +12547,10 @@
     </row>
     <row r="473" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="B473" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="C473" s="2" t="s">
         <v>7</v>
@@ -12549,10 +12561,10 @@
     </row>
     <row r="474" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="B474" t="s">
-        <v>897</v>
+        <v>893</v>
       </c>
       <c r="C474" s="2" t="s">
         <v>7</v>
@@ -12563,10 +12575,10 @@
     </row>
     <row r="475" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
-        <v>898</v>
+        <v>894</v>
       </c>
       <c r="B475" t="s">
-        <v>899</v>
+        <v>895</v>
       </c>
       <c r="C475" s="2" t="s">
         <v>7</v>
@@ -12577,10 +12589,10 @@
     </row>
     <row r="476" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
       <c r="B476" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
       <c r="C476" s="2" t="s">
         <v>7</v>
@@ -12591,10 +12603,10 @@
     </row>
     <row r="477" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
       <c r="B477" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
       <c r="C477" s="2" t="s">
         <v>7</v>
@@ -12605,10 +12617,10 @@
     </row>
     <row r="478" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
       <c r="B478" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="C478" s="2" t="s">
         <v>7</v>
@@ -12619,10 +12631,10 @@
     </row>
     <row r="479" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
       <c r="B479" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="C479" s="2" t="s">
         <v>7</v>
@@ -12633,10 +12645,10 @@
     </row>
     <row r="480" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
       <c r="B480" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="C480" s="2" t="s">
         <v>7</v>
@@ -12647,10 +12659,10 @@
     </row>
     <row r="481" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B481" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="C481" s="2" t="s">
         <v>7</v>
@@ -12661,10 +12673,10 @@
     </row>
     <row r="482" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="B482" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="C482" s="2" t="s">
         <v>7</v>
@@ -12675,10 +12687,10 @@
     </row>
     <row r="483" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
-        <v>914</v>
+        <v>910</v>
       </c>
       <c r="B483" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
       <c r="C483" s="2" t="s">
         <v>7</v>
@@ -12689,10 +12701,10 @@
     </row>
     <row r="484" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
       <c r="B484" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
       <c r="C484" s="2" t="s">
         <v>7</v>
@@ -12703,10 +12715,10 @@
     </row>
     <row r="485" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="B485" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
       <c r="C485" s="2" t="s">
         <v>7</v>
@@ -12717,10 +12729,10 @@
     </row>
     <row r="486" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="B486" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="C486" s="2" t="s">
         <v>7</v>
@@ -12731,10 +12743,10 @@
     </row>
     <row r="487" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="B487" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
       <c r="C487" s="2" t="s">
         <v>7</v>
@@ -12745,10 +12757,10 @@
     </row>
     <row r="488" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="B488" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="C488" s="2" t="s">
         <v>7</v>
@@ -12759,10 +12771,10 @@
     </row>
     <row r="489" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
       <c r="B489" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="C489" s="2" t="s">
         <v>7</v>
@@ -12773,10 +12785,10 @@
     </row>
     <row r="490" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
-        <v>928</v>
+        <v>924</v>
       </c>
       <c r="B490" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="C490" s="2" t="s">
         <v>7</v>
@@ -12787,10 +12799,10 @@
     </row>
     <row r="491" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>932</v>
+        <v>926</v>
       </c>
       <c r="B491" t="s">
-        <v>933</v>
+        <v>927</v>
       </c>
       <c r="C491" s="2" t="s">
         <v>7</v>
@@ -12801,10 +12813,10 @@
     </row>
     <row r="492" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
-        <v>934</v>
+        <v>928</v>
       </c>
       <c r="B492" t="s">
-        <v>935</v>
+        <v>929</v>
       </c>
       <c r="C492" s="2" t="s">
         <v>7</v>
@@ -12815,10 +12827,10 @@
     </row>
     <row r="493" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="B493" t="s">
-        <v>937</v>
+        <v>931</v>
       </c>
       <c r="C493" s="2" t="s">
         <v>7</v>
@@ -12829,10 +12841,10 @@
     </row>
     <row r="494" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
       <c r="B494" t="s">
-        <v>939</v>
+        <v>935</v>
       </c>
       <c r="C494" s="2" t="s">
         <v>7</v>
@@ -12843,10 +12855,10 @@
     </row>
     <row r="495" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
-        <v>940</v>
+        <v>936</v>
       </c>
       <c r="B495" t="s">
-        <v>941</v>
+        <v>937</v>
       </c>
       <c r="C495" s="2" t="s">
         <v>7</v>
@@ -12857,10 +12869,10 @@
     </row>
     <row r="496" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
-        <v>942</v>
+        <v>938</v>
       </c>
       <c r="B496" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
       <c r="C496" s="2" t="s">
         <v>7</v>
@@ -12871,10 +12883,10 @@
     </row>
     <row r="497" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
-        <v>944</v>
+        <v>940</v>
       </c>
       <c r="B497" t="s">
-        <v>945</v>
+        <v>941</v>
       </c>
       <c r="C497" s="2" t="s">
         <v>7</v>
@@ -12885,10 +12897,10 @@
     </row>
     <row r="498" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
       <c r="B498" t="s">
-        <v>947</v>
+        <v>943</v>
       </c>
       <c r="C498" s="2" t="s">
         <v>7</v>
@@ -12899,10 +12911,10 @@
     </row>
     <row r="499" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
-        <v>950</v>
+        <v>944</v>
       </c>
       <c r="B499" t="s">
-        <v>951</v>
+        <v>945</v>
       </c>
       <c r="C499" s="2" t="s">
         <v>7</v>
@@ -12913,10 +12925,10 @@
     </row>
     <row r="500" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
-        <v>952</v>
+        <v>946</v>
       </c>
       <c r="B500" t="s">
-        <v>953</v>
+        <v>947</v>
       </c>
       <c r="C500" s="2" t="s">
         <v>7</v>
@@ -12927,10 +12939,10 @@
     </row>
     <row r="501" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
-        <v>954</v>
+        <v>948</v>
       </c>
       <c r="B501" t="s">
-        <v>955</v>
+        <v>949</v>
       </c>
       <c r="C501" s="2" t="s">
         <v>7</v>
@@ -12941,10 +12953,10 @@
     </row>
     <row r="502" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
-        <v>956</v>
+        <v>952</v>
       </c>
       <c r="B502" t="s">
-        <v>957</v>
+        <v>953</v>
       </c>
       <c r="C502" s="2" t="s">
         <v>7</v>
@@ -12955,10 +12967,10 @@
     </row>
     <row r="503" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
-        <v>960</v>
+        <v>954</v>
       </c>
       <c r="B503" t="s">
-        <v>961</v>
+        <v>955</v>
       </c>
       <c r="C503" s="2" t="s">
         <v>7</v>
@@ -12969,10 +12981,10 @@
     </row>
     <row r="504" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
-        <v>962</v>
+        <v>956</v>
       </c>
       <c r="B504" t="s">
-        <v>963</v>
+        <v>957</v>
       </c>
       <c r="C504" s="2" t="s">
         <v>7</v>
@@ -12983,10 +12995,10 @@
     </row>
     <row r="505" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
-        <v>964</v>
+        <v>958</v>
       </c>
       <c r="B505" t="s">
-        <v>965</v>
+        <v>959</v>
       </c>
       <c r="C505" s="2" t="s">
         <v>7</v>
@@ -12997,10 +13009,10 @@
     </row>
     <row r="506" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
-        <v>966</v>
+        <v>960</v>
       </c>
       <c r="B506" t="s">
-        <v>967</v>
+        <v>961</v>
       </c>
       <c r="C506" s="2" t="s">
         <v>7</v>
@@ -13011,10 +13023,10 @@
     </row>
     <row r="507" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
-        <v>968</v>
+        <v>962</v>
       </c>
       <c r="B507" t="s">
-        <v>969</v>
+        <v>963</v>
       </c>
       <c r="C507" s="2" t="s">
         <v>7</v>
@@ -13025,10 +13037,10 @@
     </row>
     <row r="508" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
-        <v>970</v>
+        <v>966</v>
       </c>
       <c r="B508" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="C508" s="2" t="s">
         <v>7</v>
@@ -13039,10 +13051,10 @@
     </row>
     <row r="509" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
-        <v>972</v>
+        <v>968</v>
       </c>
       <c r="B509" t="s">
-        <v>973</v>
+        <v>969</v>
       </c>
       <c r="C509" s="2" t="s">
         <v>7</v>
@@ -13053,10 +13065,10 @@
     </row>
     <row r="510" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
-        <v>974</v>
+        <v>970</v>
       </c>
       <c r="B510" t="s">
-        <v>975</v>
+        <v>971</v>
       </c>
       <c r="C510" s="2" t="s">
         <v>7</v>
@@ -13067,10 +13079,10 @@
     </row>
     <row r="511" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
-        <v>976</v>
+        <v>972</v>
       </c>
       <c r="B511" t="s">
-        <v>977</v>
+        <v>973</v>
       </c>
       <c r="C511" s="2" t="s">
         <v>7</v>
@@ -13081,10 +13093,10 @@
     </row>
     <row r="512" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
-        <v>978</v>
+        <v>974</v>
       </c>
       <c r="B512" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="C512" s="2" t="s">
         <v>7</v>
@@ -13095,10 +13107,10 @@
     </row>
     <row r="513" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
-        <v>980</v>
+        <v>976</v>
       </c>
       <c r="B513" t="s">
-        <v>981</v>
+        <v>977</v>
       </c>
       <c r="C513" s="2" t="s">
         <v>7</v>
@@ -13109,10 +13121,10 @@
     </row>
     <row r="514" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
-        <v>982</v>
+        <v>978</v>
       </c>
       <c r="B514" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="C514" s="2" t="s">
         <v>7</v>
@@ -13123,10 +13135,10 @@
     </row>
     <row r="515" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
       <c r="B515" t="s">
-        <v>985</v>
+        <v>981</v>
       </c>
       <c r="C515" s="2" t="s">
         <v>7</v>
@@ -13137,10 +13149,10 @@
     </row>
     <row r="516" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
-        <v>986</v>
+        <v>982</v>
       </c>
       <c r="B516" t="s">
-        <v>987</v>
+        <v>983</v>
       </c>
       <c r="C516" s="2" t="s">
         <v>7</v>
@@ -13151,10 +13163,10 @@
     </row>
     <row r="517" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
-        <v>988</v>
+        <v>984</v>
       </c>
       <c r="B517" t="s">
-        <v>989</v>
+        <v>985</v>
       </c>
       <c r="C517" s="2" t="s">
         <v>7</v>
@@ -13165,10 +13177,10 @@
     </row>
     <row r="518" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
-        <v>990</v>
+        <v>986</v>
       </c>
       <c r="B518" t="s">
-        <v>991</v>
+        <v>987</v>
       </c>
       <c r="C518" s="2" t="s">
         <v>7</v>
@@ -13179,10 +13191,10 @@
     </row>
     <row r="519" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
-        <v>992</v>
+        <v>988</v>
       </c>
       <c r="B519" t="s">
-        <v>993</v>
+        <v>989</v>
       </c>
       <c r="C519" s="2" t="s">
         <v>7</v>
@@ -13193,10 +13205,10 @@
     </row>
     <row r="520" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
-        <v>996</v>
+        <v>990</v>
       </c>
       <c r="B520" t="s">
-        <v>997</v>
+        <v>991</v>
       </c>
       <c r="C520" s="2" t="s">
         <v>7</v>
@@ -13207,10 +13219,10 @@
     </row>
     <row r="521" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
-        <v>998</v>
+        <v>992</v>
       </c>
       <c r="B521" t="s">
-        <v>999</v>
+        <v>993</v>
       </c>
       <c r="C521" s="2" t="s">
         <v>7</v>
@@ -13221,10 +13233,10 @@
     </row>
     <row r="522" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
-        <v>1000</v>
+        <v>994</v>
       </c>
       <c r="B522" t="s">
-        <v>1001</v>
+        <v>995</v>
       </c>
       <c r="C522" s="2" t="s">
         <v>7</v>
@@ -13235,10 +13247,10 @@
     </row>
     <row r="523" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
-        <v>1002</v>
+        <v>996</v>
       </c>
       <c r="B523" t="s">
-        <v>1003</v>
+        <v>997</v>
       </c>
       <c r="C523" s="2" t="s">
         <v>7</v>
@@ -13249,10 +13261,10 @@
     </row>
     <row r="524" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
-        <v>1004</v>
+        <v>1000</v>
       </c>
       <c r="B524" t="s">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="C524" s="2" t="s">
         <v>7</v>
@@ -13263,10 +13275,10 @@
     </row>
     <row r="525" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
-        <v>1006</v>
+        <v>1002</v>
       </c>
       <c r="B525" t="s">
-        <v>1007</v>
+        <v>1003</v>
       </c>
       <c r="C525" s="2" t="s">
         <v>7</v>
@@ -13277,10 +13289,10 @@
     </row>
     <row r="526" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
-        <v>1010</v>
+        <v>1004</v>
       </c>
       <c r="B526" t="s">
-        <v>1011</v>
+        <v>1005</v>
       </c>
       <c r="C526" s="2" t="s">
         <v>7</v>
@@ -13291,10 +13303,10 @@
     </row>
     <row r="527" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
-        <v>1012</v>
+        <v>1006</v>
       </c>
       <c r="B527" t="s">
-        <v>1013</v>
+        <v>1007</v>
       </c>
       <c r="C527" s="2" t="s">
         <v>7</v>
@@ -13305,10 +13317,10 @@
     </row>
     <row r="528" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
-        <v>1014</v>
+        <v>1008</v>
       </c>
       <c r="B528" t="s">
-        <v>1015</v>
+        <v>1009</v>
       </c>
       <c r="C528" s="2" t="s">
         <v>7</v>
@@ -13319,10 +13331,10 @@
     </row>
     <row r="529" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
-        <v>1016</v>
+        <v>1010</v>
       </c>
       <c r="B529" t="s">
-        <v>1017</v>
+        <v>1011</v>
       </c>
       <c r="C529" s="2" t="s">
         <v>7</v>
@@ -13333,10 +13345,10 @@
     </row>
     <row r="530" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
       <c r="B530" t="s">
-        <v>1019</v>
+        <v>1015</v>
       </c>
       <c r="C530" s="2" t="s">
         <v>7</v>
@@ -13347,10 +13359,10 @@
     </row>
     <row r="531" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
-        <v>1020</v>
+        <v>1016</v>
       </c>
       <c r="B531" t="s">
-        <v>1021</v>
+        <v>1017</v>
       </c>
       <c r="C531" s="2" t="s">
         <v>7</v>
@@ -13361,10 +13373,10 @@
     </row>
     <row r="532" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
-        <v>1022</v>
+        <v>1018</v>
       </c>
       <c r="B532" t="s">
-        <v>1023</v>
+        <v>1019</v>
       </c>
       <c r="C532" s="2" t="s">
         <v>7</v>
@@ -13375,10 +13387,10 @@
     </row>
     <row r="533" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
-        <v>1024</v>
+        <v>1020</v>
       </c>
       <c r="B533" t="s">
-        <v>1025</v>
+        <v>1021</v>
       </c>
       <c r="C533" s="2" t="s">
         <v>7</v>
@@ -13389,10 +13401,10 @@
     </row>
     <row r="534" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
-        <v>1026</v>
+        <v>1022</v>
       </c>
       <c r="B534" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="C534" s="2" t="s">
         <v>7</v>
@@ -13403,10 +13415,10 @@
     </row>
     <row r="535" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
-        <v>1028</v>
+        <v>1024</v>
       </c>
       <c r="B535" t="s">
-        <v>1029</v>
+        <v>1025</v>
       </c>
       <c r="C535" s="2" t="s">
         <v>7</v>
@@ -13417,10 +13429,10 @@
     </row>
     <row r="536" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
-        <v>1030</v>
+        <v>1026</v>
       </c>
       <c r="B536" t="s">
-        <v>1031</v>
+        <v>1027</v>
       </c>
       <c r="C536" s="2" t="s">
         <v>7</v>
@@ -13431,10 +13443,10 @@
     </row>
     <row r="537" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
-        <v>1032</v>
+        <v>1028</v>
       </c>
       <c r="B537" t="s">
-        <v>1033</v>
+        <v>1029</v>
       </c>
       <c r="C537" s="2" t="s">
         <v>7</v>
@@ -13445,10 +13457,10 @@
     </row>
     <row r="538" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
-        <v>1034</v>
+        <v>1030</v>
       </c>
       <c r="B538" t="s">
-        <v>1035</v>
+        <v>1031</v>
       </c>
       <c r="C538" s="2" t="s">
         <v>7</v>
@@ -13459,10 +13471,10 @@
     </row>
     <row r="539" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
-        <v>1038</v>
+        <v>1032</v>
       </c>
       <c r="B539" t="s">
-        <v>1039</v>
+        <v>1033</v>
       </c>
       <c r="C539" s="2" t="s">
         <v>7</v>
@@ -13473,10 +13485,10 @@
     </row>
     <row r="540" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
-        <v>1040</v>
+        <v>1034</v>
       </c>
       <c r="B540" t="s">
-        <v>1041</v>
+        <v>1035</v>
       </c>
       <c r="C540" s="2" t="s">
         <v>7</v>
@@ -13487,10 +13499,10 @@
     </row>
     <row r="541" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
-        <v>1042</v>
+        <v>1036</v>
       </c>
       <c r="B541" t="s">
-        <v>1043</v>
+        <v>1037</v>
       </c>
       <c r="C541" s="2" t="s">
         <v>7</v>
@@ -13501,10 +13513,10 @@
     </row>
     <row r="542" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
-        <v>1044</v>
+        <v>1038</v>
       </c>
       <c r="B542" t="s">
-        <v>1045</v>
+        <v>1039</v>
       </c>
       <c r="C542" s="2" t="s">
         <v>7</v>
@@ -13515,10 +13527,10 @@
     </row>
     <row r="543" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
-        <v>1046</v>
+        <v>1042</v>
       </c>
       <c r="B543" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
       <c r="C543" s="2" t="s">
         <v>7</v>
@@ -13529,10 +13541,10 @@
     </row>
     <row r="544" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
-        <v>1048</v>
+        <v>1044</v>
       </c>
       <c r="B544" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="C544" s="2" t="s">
         <v>7</v>
@@ -13543,10 +13555,10 @@
     </row>
     <row r="545" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
       <c r="B545" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="C545" s="2" t="s">
         <v>7</v>
@@ -13557,10 +13569,10 @@
     </row>
     <row r="546" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="B546" t="s">
-        <v>1053</v>
+        <v>1049</v>
       </c>
       <c r="C546" s="2" t="s">
         <v>7</v>
@@ -13571,10 +13583,10 @@
     </row>
     <row r="547" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
-        <v>1054</v>
+        <v>1050</v>
       </c>
       <c r="B547" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="C547" s="2" t="s">
         <v>7</v>
@@ -13585,10 +13597,10 @@
     </row>
     <row r="548" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
-        <v>1056</v>
+        <v>1052</v>
       </c>
       <c r="B548" t="s">
-        <v>1057</v>
+        <v>1053</v>
       </c>
       <c r="C548" s="2" t="s">
         <v>7</v>
@@ -13599,10 +13611,10 @@
     </row>
     <row r="549" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
-        <v>1060</v>
+        <v>1054</v>
       </c>
       <c r="B549" t="s">
-        <v>1061</v>
+        <v>1055</v>
       </c>
       <c r="C549" s="2" t="s">
         <v>7</v>
@@ -13613,10 +13625,10 @@
     </row>
     <row r="550" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
-        <v>1062</v>
+        <v>1056</v>
       </c>
       <c r="B550" t="s">
-        <v>1063</v>
+        <v>1057</v>
       </c>
       <c r="C550" s="2" t="s">
         <v>7</v>
@@ -13627,10 +13639,10 @@
     </row>
     <row r="551" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
-        <v>1066</v>
+        <v>1058</v>
       </c>
       <c r="B551" t="s">
-        <v>1067</v>
+        <v>1059</v>
       </c>
       <c r="C551" s="2" t="s">
         <v>7</v>
@@ -13641,10 +13653,10 @@
     </row>
     <row r="552" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
-        <v>1068</v>
+        <v>1060</v>
       </c>
       <c r="B552" t="s">
-        <v>1069</v>
+        <v>1061</v>
       </c>
       <c r="C552" s="2" t="s">
         <v>7</v>
@@ -13655,10 +13667,10 @@
     </row>
     <row r="553" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
-        <v>1070</v>
+        <v>1064</v>
       </c>
       <c r="B553" t="s">
-        <v>1071</v>
+        <v>1065</v>
       </c>
       <c r="C553" s="2" t="s">
         <v>7</v>
@@ -13669,10 +13681,10 @@
     </row>
     <row r="554" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
-        <v>1072</v>
+        <v>1066</v>
       </c>
       <c r="B554" t="s">
-        <v>1073</v>
+        <v>1067</v>
       </c>
       <c r="C554" s="2" t="s">
         <v>7</v>
@@ -13683,10 +13695,10 @@
     </row>
     <row r="555" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
-        <v>1074</v>
+        <v>1070</v>
       </c>
       <c r="B555" t="s">
-        <v>1075</v>
+        <v>1071</v>
       </c>
       <c r="C555" s="2" t="s">
         <v>7</v>
@@ -13697,10 +13709,10 @@
     </row>
     <row r="556" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
-        <v>1076</v>
+        <v>1072</v>
       </c>
       <c r="B556" t="s">
-        <v>1077</v>
+        <v>1073</v>
       </c>
       <c r="C556" s="2" t="s">
         <v>7</v>
@@ -13711,10 +13723,10 @@
     </row>
     <row r="557" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
-        <v>1078</v>
+        <v>1074</v>
       </c>
       <c r="B557" t="s">
-        <v>1079</v>
+        <v>1075</v>
       </c>
       <c r="C557" s="2" t="s">
         <v>7</v>
@@ -13725,10 +13737,10 @@
     </row>
     <row r="558" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
-        <v>1080</v>
+        <v>1076</v>
       </c>
       <c r="B558" t="s">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="C558" s="2" t="s">
         <v>7</v>
@@ -13739,10 +13751,10 @@
     </row>
     <row r="559" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
-        <v>1082</v>
+        <v>1078</v>
       </c>
       <c r="B559" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="C559" s="2" t="s">
         <v>7</v>
@@ -13753,10 +13765,10 @@
     </row>
     <row r="560" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
-        <v>1084</v>
+        <v>1080</v>
       </c>
       <c r="B560" t="s">
-        <v>1085</v>
+        <v>1081</v>
       </c>
       <c r="C560" s="2" t="s">
         <v>7</v>
@@ -13767,10 +13779,10 @@
     </row>
     <row r="561" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
-        <v>1086</v>
+        <v>1082</v>
       </c>
       <c r="B561" t="s">
-        <v>1087</v>
+        <v>1083</v>
       </c>
       <c r="C561" s="2" t="s">
         <v>7</v>
@@ -13781,10 +13793,10 @@
     </row>
     <row r="562" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
-        <v>1088</v>
+        <v>1084</v>
       </c>
       <c r="B562" t="s">
-        <v>1089</v>
+        <v>1085</v>
       </c>
       <c r="C562" s="2" t="s">
         <v>7</v>
@@ -13795,10 +13807,10 @@
     </row>
     <row r="563" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
-        <v>1090</v>
+        <v>1086</v>
       </c>
       <c r="B563" t="s">
-        <v>1091</v>
+        <v>1087</v>
       </c>
       <c r="C563" s="2" t="s">
         <v>7</v>
@@ -13809,10 +13821,10 @@
     </row>
     <row r="564" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
-        <v>1092</v>
+        <v>1088</v>
       </c>
       <c r="B564" t="s">
-        <v>1093</v>
+        <v>1089</v>
       </c>
       <c r="C564" s="2" t="s">
         <v>7</v>
@@ -13823,10 +13835,10 @@
     </row>
     <row r="565" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
-        <v>1094</v>
+        <v>1090</v>
       </c>
       <c r="B565" t="s">
-        <v>1095</v>
+        <v>1091</v>
       </c>
       <c r="C565" s="2" t="s">
         <v>7</v>
@@ -13837,10 +13849,10 @@
     </row>
     <row r="566" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
-        <v>1096</v>
+        <v>1092</v>
       </c>
       <c r="B566" t="s">
-        <v>1097</v>
+        <v>1093</v>
       </c>
       <c r="C566" s="2" t="s">
         <v>7</v>
@@ -13851,10 +13863,10 @@
     </row>
     <row r="567" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
-        <v>1098</v>
+        <v>1094</v>
       </c>
       <c r="B567" t="s">
-        <v>1099</v>
+        <v>1095</v>
       </c>
       <c r="C567" s="2" t="s">
         <v>7</v>
@@ -13865,10 +13877,10 @@
     </row>
     <row r="568" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
-        <v>1100</v>
+        <v>1096</v>
       </c>
       <c r="B568" t="s">
-        <v>1101</v>
+        <v>1097</v>
       </c>
       <c r="C568" s="2" t="s">
         <v>7</v>
@@ -13879,10 +13891,10 @@
     </row>
     <row r="569" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
-        <v>1102</v>
+        <v>1098</v>
       </c>
       <c r="B569" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="C569" s="2" t="s">
         <v>7</v>
@@ -13893,10 +13905,10 @@
     </row>
     <row r="570" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
-        <v>1104</v>
+        <v>1100</v>
       </c>
       <c r="B570" t="s">
-        <v>1105</v>
+        <v>1101</v>
       </c>
       <c r="C570" s="2" t="s">
         <v>7</v>
@@ -13907,10 +13919,10 @@
     </row>
     <row r="571" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
-        <v>1106</v>
+        <v>1102</v>
       </c>
       <c r="B571" t="s">
-        <v>1107</v>
+        <v>1103</v>
       </c>
       <c r="C571" s="2" t="s">
         <v>7</v>
@@ -13921,10 +13933,10 @@
     </row>
     <row r="572" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
-        <v>1108</v>
+        <v>1104</v>
       </c>
       <c r="B572" t="s">
-        <v>1109</v>
+        <v>1105</v>
       </c>
       <c r="C572" s="2" t="s">
         <v>7</v>
@@ -13935,10 +13947,10 @@
     </row>
     <row r="573" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
-        <v>1110</v>
+        <v>1106</v>
       </c>
       <c r="B573" t="s">
-        <v>1111</v>
+        <v>1107</v>
       </c>
       <c r="C573" s="2" t="s">
         <v>7</v>
@@ -13949,10 +13961,10 @@
     </row>
     <row r="574" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
-        <v>1112</v>
+        <v>1108</v>
       </c>
       <c r="B574" t="s">
-        <v>1113</v>
+        <v>1109</v>
       </c>
       <c r="C574" s="2" t="s">
         <v>7</v>
@@ -13963,10 +13975,10 @@
     </row>
     <row r="575" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
-        <v>1114</v>
+        <v>1110</v>
       </c>
       <c r="B575" t="s">
-        <v>1115</v>
+        <v>1111</v>
       </c>
       <c r="C575" s="2" t="s">
         <v>7</v>
@@ -13977,10 +13989,10 @@
     </row>
     <row r="576" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
-        <v>1116</v>
+        <v>1112</v>
       </c>
       <c r="B576" t="s">
-        <v>1117</v>
+        <v>1113</v>
       </c>
       <c r="C576" s="2" t="s">
         <v>7</v>
@@ -13991,10 +14003,10 @@
     </row>
     <row r="577" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
-        <v>1118</v>
+        <v>1114</v>
       </c>
       <c r="B577" t="s">
-        <v>1119</v>
+        <v>1115</v>
       </c>
       <c r="C577" s="2" t="s">
         <v>7</v>
@@ -14005,10 +14017,10 @@
     </row>
     <row r="578" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
-        <v>1120</v>
+        <v>1116</v>
       </c>
       <c r="B578" t="s">
-        <v>1121</v>
+        <v>1117</v>
       </c>
       <c r="C578" s="2" t="s">
         <v>7</v>
@@ -14019,10 +14031,10 @@
     </row>
     <row r="579" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
-        <v>1122</v>
+        <v>1118</v>
       </c>
       <c r="B579" t="s">
-        <v>1123</v>
+        <v>1119</v>
       </c>
       <c r="C579" s="2" t="s">
         <v>7</v>
@@ -14033,10 +14045,10 @@
     </row>
     <row r="580" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
-        <v>1124</v>
+        <v>1120</v>
       </c>
       <c r="B580" t="s">
-        <v>1125</v>
+        <v>1121</v>
       </c>
       <c r="C580" s="2" t="s">
         <v>7</v>
@@ -14047,10 +14059,10 @@
     </row>
     <row r="581" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
-        <v>1126</v>
+        <v>1122</v>
       </c>
       <c r="B581" t="s">
-        <v>1127</v>
+        <v>1123</v>
       </c>
       <c r="C581" s="2" t="s">
         <v>7</v>
@@ -14061,10 +14073,10 @@
     </row>
     <row r="582" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
-        <v>1128</v>
+        <v>1124</v>
       </c>
       <c r="B582" t="s">
-        <v>1129</v>
+        <v>1125</v>
       </c>
       <c r="C582" s="2" t="s">
         <v>7</v>
@@ -14075,10 +14087,10 @@
     </row>
     <row r="583" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
-        <v>1130</v>
+        <v>1126</v>
       </c>
       <c r="B583" t="s">
-        <v>1131</v>
+        <v>1127</v>
       </c>
       <c r="C583" s="2" t="s">
         <v>7</v>
@@ -14089,10 +14101,10 @@
     </row>
     <row r="584" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="B584" t="s">
-        <v>1133</v>
+        <v>1129</v>
       </c>
       <c r="C584" s="2" t="s">
         <v>7</v>
@@ -14103,10 +14115,10 @@
     </row>
     <row r="585" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
-        <v>1134</v>
+        <v>1130</v>
       </c>
       <c r="B585" t="s">
-        <v>1135</v>
+        <v>1131</v>
       </c>
       <c r="C585" s="2" t="s">
         <v>7</v>
@@ -14117,10 +14129,10 @@
     </row>
     <row r="586" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
-        <v>1136</v>
+        <v>1132</v>
       </c>
       <c r="B586" t="s">
-        <v>1137</v>
+        <v>1133</v>
       </c>
       <c r="C586" s="2" t="s">
         <v>7</v>
@@ -14131,10 +14143,10 @@
     </row>
     <row r="587" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
-        <v>1138</v>
+        <v>1134</v>
       </c>
       <c r="B587" t="s">
-        <v>1139</v>
+        <v>1135</v>
       </c>
       <c r="C587" s="2" t="s">
         <v>7</v>
@@ -14145,10 +14157,10 @@
     </row>
     <row r="588" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
-        <v>1140</v>
+        <v>1136</v>
       </c>
       <c r="B588" t="s">
-        <v>1141</v>
+        <v>1137</v>
       </c>
       <c r="C588" s="2" t="s">
         <v>7</v>
@@ -14159,10 +14171,10 @@
     </row>
     <row r="589" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
-        <v>1142</v>
+        <v>1138</v>
       </c>
       <c r="B589" t="s">
-        <v>1143</v>
+        <v>1139</v>
       </c>
       <c r="C589" s="2" t="s">
         <v>7</v>
@@ -14173,10 +14185,10 @@
     </row>
     <row r="590" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
-        <v>1144</v>
+        <v>1140</v>
       </c>
       <c r="B590" t="s">
-        <v>1145</v>
+        <v>1141</v>
       </c>
       <c r="C590" s="2" t="s">
         <v>7</v>
@@ -14187,10 +14199,10 @@
     </row>
     <row r="591" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
-        <v>1146</v>
+        <v>1142</v>
       </c>
       <c r="B591" t="s">
-        <v>1147</v>
+        <v>1143</v>
       </c>
       <c r="C591" s="2" t="s">
         <v>7</v>
@@ -14201,10 +14213,10 @@
     </row>
     <row r="592" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
-        <v>1148</v>
+        <v>1144</v>
       </c>
       <c r="B592" t="s">
-        <v>1149</v>
+        <v>1145</v>
       </c>
       <c r="C592" s="2" t="s">
         <v>7</v>
@@ -14215,10 +14227,10 @@
     </row>
     <row r="593" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
       <c r="B593" t="s">
-        <v>1151</v>
+        <v>1147</v>
       </c>
       <c r="C593" s="2" t="s">
         <v>7</v>
@@ -14229,10 +14241,10 @@
     </row>
     <row r="594" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B594" t="s">
-        <v>1153</v>
+        <v>1149</v>
       </c>
       <c r="C594" s="2" t="s">
         <v>7</v>
@@ -14243,10 +14255,10 @@
     </row>
     <row r="595" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
-        <v>1154</v>
+        <v>1150</v>
       </c>
       <c r="B595" t="s">
-        <v>1155</v>
+        <v>1151</v>
       </c>
       <c r="C595" s="2" t="s">
         <v>7</v>
@@ -14257,10 +14269,10 @@
     </row>
     <row r="596" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
-        <v>1156</v>
+        <v>1152</v>
       </c>
       <c r="B596" t="s">
-        <v>1157</v>
+        <v>1153</v>
       </c>
       <c r="C596" s="2" t="s">
         <v>7</v>
@@ -14271,10 +14283,10 @@
     </row>
     <row r="597" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
-        <v>1158</v>
+        <v>1154</v>
       </c>
       <c r="B597" t="s">
-        <v>1159</v>
+        <v>1155</v>
       </c>
       <c r="C597" s="2" t="s">
         <v>7</v>
@@ -14285,10 +14297,10 @@
     </row>
     <row r="598" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
-        <v>1160</v>
+        <v>1156</v>
       </c>
       <c r="B598" t="s">
-        <v>1161</v>
+        <v>1157</v>
       </c>
       <c r="C598" s="2" t="s">
         <v>7</v>
@@ -14299,10 +14311,10 @@
     </row>
     <row r="599" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
-        <v>1162</v>
+        <v>1158</v>
       </c>
       <c r="B599" t="s">
-        <v>1163</v>
+        <v>1159</v>
       </c>
       <c r="C599" s="2" t="s">
         <v>7</v>
@@ -14313,10 +14325,10 @@
     </row>
     <row r="600" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
-        <v>1164</v>
+        <v>1160</v>
       </c>
       <c r="B600" t="s">
-        <v>1165</v>
+        <v>1161</v>
       </c>
       <c r="C600" s="2" t="s">
         <v>7</v>
@@ -14327,10 +14339,10 @@
     </row>
     <row r="601" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
-        <v>1168</v>
+        <v>1162</v>
       </c>
       <c r="B601" t="s">
-        <v>1169</v>
+        <v>1163</v>
       </c>
       <c r="C601" s="2" t="s">
         <v>7</v>
@@ -14341,10 +14353,10 @@
     </row>
     <row r="602" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
-        <v>1170</v>
+        <v>1164</v>
       </c>
       <c r="B602" t="s">
-        <v>1171</v>
+        <v>1165</v>
       </c>
       <c r="C602" s="2" t="s">
         <v>7</v>
@@ -14355,10 +14367,10 @@
     </row>
     <row r="603" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
-        <v>1172</v>
+        <v>1166</v>
       </c>
       <c r="B603" t="s">
-        <v>1173</v>
+        <v>1167</v>
       </c>
       <c r="C603" s="2" t="s">
         <v>7</v>
@@ -14369,10 +14381,10 @@
     </row>
     <row r="604" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
-        <v>1174</v>
+        <v>1168</v>
       </c>
       <c r="B604" t="s">
-        <v>1175</v>
+        <v>1169</v>
       </c>
       <c r="C604" s="2" t="s">
         <v>7</v>
@@ -14383,10 +14395,10 @@
     </row>
     <row r="605" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
-        <v>1176</v>
+        <v>1172</v>
       </c>
       <c r="B605" t="s">
-        <v>1177</v>
+        <v>1173</v>
       </c>
       <c r="C605" s="2" t="s">
         <v>7</v>
@@ -14397,10 +14409,10 @@
     </row>
     <row r="606" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
-        <v>1178</v>
+        <v>1174</v>
       </c>
       <c r="B606" t="s">
-        <v>1179</v>
+        <v>1175</v>
       </c>
       <c r="C606" s="2" t="s">
         <v>7</v>
@@ -14411,10 +14423,10 @@
     </row>
     <row r="607" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="B607" t="s">
-        <v>1181</v>
+        <v>1177</v>
       </c>
       <c r="C607" s="2" t="s">
         <v>7</v>
@@ -14425,10 +14437,10 @@
     </row>
     <row r="608" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
-        <v>1182</v>
+        <v>1178</v>
       </c>
       <c r="B608" t="s">
-        <v>1183</v>
+        <v>1179</v>
       </c>
       <c r="C608" s="2" t="s">
         <v>7</v>
@@ -14439,10 +14451,10 @@
     </row>
     <row r="609" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
-        <v>1184</v>
+        <v>1180</v>
       </c>
       <c r="B609" t="s">
-        <v>1185</v>
+        <v>1181</v>
       </c>
       <c r="C609" s="2" t="s">
         <v>7</v>
@@ -14453,10 +14465,10 @@
     </row>
     <row r="610" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
-        <v>1186</v>
+        <v>1182</v>
       </c>
       <c r="B610" t="s">
-        <v>1187</v>
+        <v>1183</v>
       </c>
       <c r="C610" s="2" t="s">
         <v>7</v>
@@ -14467,10 +14479,10 @@
     </row>
     <row r="611" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
-        <v>1188</v>
+        <v>1184</v>
       </c>
       <c r="B611" t="s">
-        <v>1189</v>
+        <v>1185</v>
       </c>
       <c r="C611" s="2" t="s">
         <v>7</v>
@@ -14481,10 +14493,10 @@
     </row>
     <row r="612" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
-        <v>1190</v>
+        <v>1186</v>
       </c>
       <c r="B612" t="s">
-        <v>1191</v>
+        <v>1187</v>
       </c>
       <c r="C612" s="2" t="s">
         <v>7</v>
@@ -14495,10 +14507,10 @@
     </row>
     <row r="613" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
-        <v>1192</v>
+        <v>1188</v>
       </c>
       <c r="B613" t="s">
-        <v>1193</v>
+        <v>1189</v>
       </c>
       <c r="C613" s="2" t="s">
         <v>7</v>
@@ -14509,10 +14521,10 @@
     </row>
     <row r="614" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
-        <v>1194</v>
+        <v>1190</v>
       </c>
       <c r="B614" t="s">
-        <v>1195</v>
+        <v>1191</v>
       </c>
       <c r="C614" s="2" t="s">
         <v>7</v>
@@ -14523,10 +14535,10 @@
     </row>
     <row r="615" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
-        <v>1196</v>
+        <v>1192</v>
       </c>
       <c r="B615" t="s">
-        <v>1197</v>
+        <v>1193</v>
       </c>
       <c r="C615" s="2" t="s">
         <v>7</v>
@@ -14537,10 +14549,10 @@
     </row>
     <row r="616" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
-        <v>1198</v>
+        <v>1194</v>
       </c>
       <c r="B616" t="s">
-        <v>1199</v>
+        <v>1195</v>
       </c>
       <c r="C616" s="2" t="s">
         <v>7</v>
@@ -14551,10 +14563,10 @@
     </row>
     <row r="617" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
-        <v>1200</v>
+        <v>1196</v>
       </c>
       <c r="B617" t="s">
-        <v>1201</v>
+        <v>1197</v>
       </c>
       <c r="C617" s="2" t="s">
         <v>7</v>
@@ -14565,10 +14577,10 @@
     </row>
     <row r="618" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
-        <v>1202</v>
+        <v>1198</v>
       </c>
       <c r="B618" t="s">
-        <v>1203</v>
+        <v>1199</v>
       </c>
       <c r="C618" s="2" t="s">
         <v>7</v>
@@ -14579,10 +14591,10 @@
     </row>
     <row r="619" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
-        <v>1204</v>
+        <v>1200</v>
       </c>
       <c r="B619" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="C619" s="2" t="s">
         <v>7</v>
@@ -14593,10 +14605,10 @@
     </row>
     <row r="620" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
-        <v>1206</v>
+        <v>1202</v>
       </c>
       <c r="B620" t="s">
-        <v>1207</v>
+        <v>1203</v>
       </c>
       <c r="C620" s="2" t="s">
         <v>7</v>
@@ -14607,10 +14619,10 @@
     </row>
     <row r="621" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
-        <v>1208</v>
+        <v>1204</v>
       </c>
       <c r="B621" t="s">
-        <v>1209</v>
+        <v>1205</v>
       </c>
       <c r="C621" s="2" t="s">
         <v>7</v>
@@ -14621,10 +14633,10 @@
     </row>
     <row r="622" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
-        <v>1210</v>
+        <v>1206</v>
       </c>
       <c r="B622" t="s">
-        <v>1211</v>
+        <v>1207</v>
       </c>
       <c r="C622" s="2" t="s">
         <v>7</v>
@@ -14635,10 +14647,10 @@
     </row>
     <row r="623" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
-        <v>1212</v>
+        <v>1208</v>
       </c>
       <c r="B623" t="s">
-        <v>1213</v>
+        <v>1209</v>
       </c>
       <c r="C623" s="2" t="s">
         <v>7</v>
@@ -14649,10 +14661,10 @@
     </row>
     <row r="624" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
-        <v>1214</v>
+        <v>1210</v>
       </c>
       <c r="B624" t="s">
-        <v>1215</v>
+        <v>1211</v>
       </c>
       <c r="C624" s="2" t="s">
         <v>7</v>
@@ -14663,10 +14675,10 @@
     </row>
     <row r="625" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
-        <v>1216</v>
+        <v>1212</v>
       </c>
       <c r="B625" t="s">
-        <v>1217</v>
+        <v>1213</v>
       </c>
       <c r="C625" s="2" t="s">
         <v>7</v>
@@ -14677,10 +14689,10 @@
     </row>
     <row r="626" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
-        <v>1218</v>
+        <v>1214</v>
       </c>
       <c r="B626" t="s">
-        <v>1219</v>
+        <v>1215</v>
       </c>
       <c r="C626" s="2" t="s">
         <v>7</v>
@@ -14691,10 +14703,10 @@
     </row>
     <row r="627" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
-        <v>1220</v>
+        <v>1216</v>
       </c>
       <c r="B627" t="s">
-        <v>1221</v>
+        <v>1217</v>
       </c>
       <c r="C627" s="2" t="s">
         <v>7</v>
@@ -14705,10 +14717,10 @@
     </row>
     <row r="628" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
-        <v>1222</v>
+        <v>1218</v>
       </c>
       <c r="B628" t="s">
-        <v>1223</v>
+        <v>1219</v>
       </c>
       <c r="C628" s="2" t="s">
         <v>7</v>
@@ -14719,10 +14731,10 @@
     </row>
     <row r="629" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
-        <v>1224</v>
+        <v>1220</v>
       </c>
       <c r="B629" t="s">
-        <v>1225</v>
+        <v>1221</v>
       </c>
       <c r="C629" s="2" t="s">
         <v>7</v>
@@ -14733,10 +14745,10 @@
     </row>
     <row r="630" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
-        <v>1228</v>
+        <v>1222</v>
       </c>
       <c r="B630" t="s">
-        <v>1229</v>
+        <v>1223</v>
       </c>
       <c r="C630" s="2" t="s">
         <v>7</v>
@@ -14747,10 +14759,10 @@
     </row>
     <row r="631" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="B631" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
       <c r="C631" s="2" t="s">
         <v>7</v>
@@ -14761,10 +14773,10 @@
     </row>
     <row r="632" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
-        <v>1232</v>
+        <v>1226</v>
       </c>
       <c r="B632" t="s">
-        <v>1233</v>
+        <v>1227</v>
       </c>
       <c r="C632" s="2" t="s">
         <v>7</v>
@@ -14775,10 +14787,10 @@
     </row>
     <row r="633" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
-        <v>1234</v>
+        <v>1228</v>
       </c>
       <c r="B633" t="s">
-        <v>1235</v>
+        <v>1229</v>
       </c>
       <c r="C633" s="2" t="s">
         <v>7</v>
@@ -14789,10 +14801,10 @@
     </row>
     <row r="634" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
-        <v>1236</v>
+        <v>1232</v>
       </c>
       <c r="B634" t="s">
-        <v>1237</v>
+        <v>1233</v>
       </c>
       <c r="C634" s="2" t="s">
         <v>7</v>
@@ -14803,10 +14815,10 @@
     </row>
     <row r="635" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
-        <v>1238</v>
+        <v>1234</v>
       </c>
       <c r="B635" t="s">
-        <v>1239</v>
+        <v>1235</v>
       </c>
       <c r="C635" s="2" t="s">
         <v>7</v>
@@ -14817,10 +14829,10 @@
     </row>
     <row r="636" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
-        <v>1240</v>
+        <v>1236</v>
       </c>
       <c r="B636" t="s">
-        <v>1241</v>
+        <v>1237</v>
       </c>
       <c r="C636" s="2" t="s">
         <v>7</v>
@@ -14831,10 +14843,10 @@
     </row>
     <row r="637" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
-        <v>1242</v>
+        <v>1238</v>
       </c>
       <c r="B637" t="s">
-        <v>1243</v>
+        <v>1239</v>
       </c>
       <c r="C637" s="2" t="s">
         <v>7</v>
@@ -14845,10 +14857,10 @@
     </row>
     <row r="638" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
-        <v>1244</v>
+        <v>1240</v>
       </c>
       <c r="B638" t="s">
-        <v>1245</v>
+        <v>1241</v>
       </c>
       <c r="C638" s="2" t="s">
         <v>7</v>
@@ -14859,10 +14871,10 @@
     </row>
     <row r="639" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
-        <v>1246</v>
+        <v>1242</v>
       </c>
       <c r="B639" t="s">
-        <v>1247</v>
+        <v>1243</v>
       </c>
       <c r="C639" s="2" t="s">
         <v>7</v>
@@ -14873,10 +14885,10 @@
     </row>
     <row r="640" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
-        <v>1248</v>
+        <v>1244</v>
       </c>
       <c r="B640" t="s">
-        <v>1249</v>
+        <v>1245</v>
       </c>
       <c r="C640" s="2" t="s">
         <v>7</v>
@@ -14887,10 +14899,10 @@
     </row>
     <row r="641" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
-        <v>1250</v>
+        <v>1246</v>
       </c>
       <c r="B641" t="s">
-        <v>1251</v>
+        <v>1247</v>
       </c>
       <c r="C641" s="2" t="s">
         <v>7</v>
@@ -14901,10 +14913,10 @@
     </row>
     <row r="642" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
-        <v>1252</v>
+        <v>1248</v>
       </c>
       <c r="B642" t="s">
-        <v>1253</v>
+        <v>1249</v>
       </c>
       <c r="C642" s="2" t="s">
         <v>7</v>
@@ -14915,10 +14927,10 @@
     </row>
     <row r="643" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
-        <v>1254</v>
+        <v>1250</v>
       </c>
       <c r="B643" t="s">
-        <v>1255</v>
+        <v>1251</v>
       </c>
       <c r="C643" s="2" t="s">
         <v>7</v>
@@ -14929,10 +14941,10 @@
     </row>
     <row r="644" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
-        <v>1256</v>
+        <v>1252</v>
       </c>
       <c r="B644" t="s">
-        <v>1257</v>
+        <v>1253</v>
       </c>
       <c r="C644" s="2" t="s">
         <v>7</v>
@@ -14943,10 +14955,10 @@
     </row>
     <row r="645" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
-        <v>1258</v>
+        <v>1254</v>
       </c>
       <c r="B645" t="s">
-        <v>1259</v>
+        <v>1255</v>
       </c>
       <c r="C645" s="2" t="s">
         <v>7</v>
@@ -14957,10 +14969,10 @@
     </row>
     <row r="646" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
-        <v>1260</v>
+        <v>1256</v>
       </c>
       <c r="B646" t="s">
-        <v>1261</v>
+        <v>1257</v>
       </c>
       <c r="C646" s="2" t="s">
         <v>7</v>
@@ -14971,10 +14983,10 @@
     </row>
     <row r="647" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
-        <v>1262</v>
+        <v>1258</v>
       </c>
       <c r="B647" t="s">
-        <v>1263</v>
+        <v>1259</v>
       </c>
       <c r="C647" s="2" t="s">
         <v>7</v>
@@ -14985,10 +14997,10 @@
     </row>
     <row r="648" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
-        <v>1264</v>
+        <v>1260</v>
       </c>
       <c r="B648" t="s">
-        <v>1265</v>
+        <v>1261</v>
       </c>
       <c r="C648" s="2" t="s">
         <v>7</v>
@@ -14999,10 +15011,10 @@
     </row>
     <row r="649" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
-        <v>1266</v>
+        <v>1262</v>
       </c>
       <c r="B649" t="s">
-        <v>1267</v>
+        <v>1263</v>
       </c>
       <c r="C649" s="2" t="s">
         <v>7</v>
@@ -15013,10 +15025,10 @@
     </row>
     <row r="650" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
-        <v>1268</v>
+        <v>1264</v>
       </c>
       <c r="B650" t="s">
-        <v>1269</v>
+        <v>1265</v>
       </c>
       <c r="C650" s="2" t="s">
         <v>7</v>
@@ -15027,10 +15039,10 @@
     </row>
     <row r="651" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
-        <v>1270</v>
+        <v>1266</v>
       </c>
       <c r="B651" t="s">
-        <v>1271</v>
+        <v>1267</v>
       </c>
       <c r="C651" s="2" t="s">
         <v>7</v>
@@ -15041,10 +15053,10 @@
     </row>
     <row r="652" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
-        <v>1272</v>
+        <v>1268</v>
       </c>
       <c r="B652" t="s">
-        <v>1273</v>
+        <v>1269</v>
       </c>
       <c r="C652" s="2" t="s">
         <v>7</v>
@@ -15055,10 +15067,10 @@
     </row>
     <row r="653" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
-        <v>1274</v>
+        <v>1270</v>
       </c>
       <c r="B653" t="s">
-        <v>1275</v>
+        <v>1271</v>
       </c>
       <c r="C653" s="2" t="s">
         <v>7</v>
@@ -15069,10 +15081,10 @@
     </row>
     <row r="654" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
-        <v>1276</v>
+        <v>1272</v>
       </c>
       <c r="B654" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="C654" s="2" t="s">
         <v>7</v>
@@ -15083,10 +15095,10 @@
     </row>
     <row r="655" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
-        <v>1278</v>
+        <v>1274</v>
       </c>
       <c r="B655" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="C655" s="2" t="s">
         <v>7</v>
@@ -15097,10 +15109,10 @@
     </row>
     <row r="656" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
-        <v>1280</v>
+        <v>1276</v>
       </c>
       <c r="B656" t="s">
-        <v>1281</v>
+        <v>1277</v>
       </c>
       <c r="C656" s="2" t="s">
         <v>7</v>
@@ -15111,10 +15123,10 @@
     </row>
     <row r="657" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="B657" t="s">
-        <v>1283</v>
+        <v>1279</v>
       </c>
       <c r="C657" s="2" t="s">
         <v>7</v>
@@ -15125,10 +15137,10 @@
     </row>
     <row r="658" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
-        <v>1284</v>
+        <v>1280</v>
       </c>
       <c r="B658" t="s">
-        <v>1285</v>
+        <v>1281</v>
       </c>
       <c r="C658" s="2" t="s">
         <v>7</v>
@@ -15139,10 +15151,10 @@
     </row>
     <row r="659" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
-        <v>1286</v>
+        <v>1282</v>
       </c>
       <c r="B659" t="s">
-        <v>1287</v>
+        <v>1283</v>
       </c>
       <c r="C659" s="2" t="s">
         <v>7</v>
@@ -15153,10 +15165,10 @@
     </row>
     <row r="660" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
-        <v>1288</v>
+        <v>1284</v>
       </c>
       <c r="B660" t="s">
-        <v>1289</v>
+        <v>1285</v>
       </c>
       <c r="C660" s="2" t="s">
         <v>7</v>
@@ -15167,10 +15179,10 @@
     </row>
     <row r="661" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
-        <v>1290</v>
+        <v>1286</v>
       </c>
       <c r="B661" t="s">
-        <v>1291</v>
+        <v>1287</v>
       </c>
       <c r="C661" s="2" t="s">
         <v>7</v>
@@ -15181,10 +15193,10 @@
     </row>
     <row r="662" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
-        <v>1292</v>
+        <v>1288</v>
       </c>
       <c r="B662" t="s">
-        <v>1293</v>
+        <v>1289</v>
       </c>
       <c r="C662" s="2" t="s">
         <v>7</v>
@@ -15195,10 +15207,10 @@
     </row>
     <row r="663" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
-        <v>1294</v>
+        <v>1290</v>
       </c>
       <c r="B663" t="s">
-        <v>1295</v>
+        <v>1291</v>
       </c>
       <c r="C663" s="2" t="s">
         <v>7</v>
@@ -15209,10 +15221,10 @@
     </row>
     <row r="664" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
-        <v>1296</v>
+        <v>1292</v>
       </c>
       <c r="B664" t="s">
-        <v>1297</v>
+        <v>1293</v>
       </c>
       <c r="C664" s="2" t="s">
         <v>7</v>
@@ -15223,10 +15235,10 @@
     </row>
     <row r="665" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
-        <v>1298</v>
+        <v>1294</v>
       </c>
       <c r="B665" t="s">
-        <v>1299</v>
+        <v>1295</v>
       </c>
       <c r="C665" s="2" t="s">
         <v>7</v>
@@ -15237,10 +15249,10 @@
     </row>
     <row r="666" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
-        <v>1300</v>
+        <v>1296</v>
       </c>
       <c r="B666" t="s">
-        <v>1301</v>
+        <v>1297</v>
       </c>
       <c r="C666" s="2" t="s">
         <v>7</v>
@@ -15251,10 +15263,10 @@
     </row>
     <row r="667" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
-        <v>1302</v>
+        <v>1298</v>
       </c>
       <c r="B667" t="s">
-        <v>1303</v>
+        <v>1299</v>
       </c>
       <c r="C667" s="2" t="s">
         <v>7</v>
@@ -15265,10 +15277,10 @@
     </row>
     <row r="668" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
-        <v>1304</v>
+        <v>1300</v>
       </c>
       <c r="B668" t="s">
-        <v>1305</v>
+        <v>1301</v>
       </c>
       <c r="C668" s="2" t="s">
         <v>7</v>
@@ -15279,10 +15291,10 @@
     </row>
     <row r="669" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
-        <v>1306</v>
+        <v>1302</v>
       </c>
       <c r="B669" t="s">
-        <v>1307</v>
+        <v>1303</v>
       </c>
       <c r="C669" s="2" t="s">
         <v>7</v>
@@ -15293,10 +15305,10 @@
     </row>
     <row r="670" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
-        <v>1308</v>
+        <v>1304</v>
       </c>
       <c r="B670" t="s">
-        <v>1309</v>
+        <v>1305</v>
       </c>
       <c r="C670" s="2" t="s">
         <v>7</v>
@@ -15307,10 +15319,10 @@
     </row>
     <row r="671" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
-        <v>1312</v>
+        <v>1306</v>
       </c>
       <c r="B671" t="s">
-        <v>1313</v>
+        <v>1307</v>
       </c>
       <c r="C671" s="2" t="s">
         <v>7</v>
@@ -15321,10 +15333,10 @@
     </row>
     <row r="672" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
-        <v>1314</v>
+        <v>1308</v>
       </c>
       <c r="B672" t="s">
-        <v>1315</v>
+        <v>1309</v>
       </c>
       <c r="C672" s="2" t="s">
         <v>7</v>
@@ -15335,10 +15347,10 @@
     </row>
     <row r="673" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
-        <v>1316</v>
+        <v>1310</v>
       </c>
       <c r="B673" t="s">
-        <v>1317</v>
+        <v>1311</v>
       </c>
       <c r="C673" s="2" t="s">
         <v>7</v>
@@ -15349,10 +15361,10 @@
     </row>
     <row r="674" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
-        <v>1318</v>
+        <v>1312</v>
       </c>
       <c r="B674" t="s">
-        <v>1319</v>
+        <v>1313</v>
       </c>
       <c r="C674" s="2" t="s">
         <v>7</v>
@@ -15363,10 +15375,10 @@
     </row>
     <row r="675" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
-        <v>1320</v>
+        <v>1316</v>
       </c>
       <c r="B675" t="s">
-        <v>1321</v>
+        <v>1317</v>
       </c>
       <c r="C675" s="2" t="s">
         <v>7</v>
@@ -15377,10 +15389,10 @@
     </row>
     <row r="676" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
-        <v>1322</v>
+        <v>1318</v>
       </c>
       <c r="B676" t="s">
-        <v>1323</v>
+        <v>1319</v>
       </c>
       <c r="C676" s="2" t="s">
         <v>7</v>
@@ -15391,10 +15403,10 @@
     </row>
     <row r="677" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
-        <v>1324</v>
+        <v>1320</v>
       </c>
       <c r="B677" t="s">
-        <v>1325</v>
+        <v>1321</v>
       </c>
       <c r="C677" s="2" t="s">
         <v>7</v>
@@ -15405,10 +15417,10 @@
     </row>
     <row r="678" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
-        <v>1326</v>
+        <v>1322</v>
       </c>
       <c r="B678" t="s">
-        <v>1327</v>
+        <v>1323</v>
       </c>
       <c r="C678" s="2" t="s">
         <v>7</v>
@@ -15419,10 +15431,10 @@
     </row>
     <row r="679" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
-        <v>1328</v>
+        <v>1324</v>
       </c>
       <c r="B679" t="s">
-        <v>1329</v>
+        <v>1325</v>
       </c>
       <c r="C679" s="2" t="s">
         <v>7</v>
@@ -15433,10 +15445,10 @@
     </row>
     <row r="680" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
-        <v>1330</v>
+        <v>1326</v>
       </c>
       <c r="B680" t="s">
-        <v>1331</v>
+        <v>1327</v>
       </c>
       <c r="C680" s="2" t="s">
         <v>7</v>
@@ -15447,10 +15459,10 @@
     </row>
     <row r="681" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
-        <v>1332</v>
+        <v>1328</v>
       </c>
       <c r="B681" t="s">
-        <v>1333</v>
+        <v>1329</v>
       </c>
       <c r="C681" s="2" t="s">
         <v>7</v>
@@ -15461,10 +15473,10 @@
     </row>
     <row r="682" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
-        <v>1334</v>
+        <v>1330</v>
       </c>
       <c r="B682" t="s">
-        <v>1335</v>
+        <v>1331</v>
       </c>
       <c r="C682" s="2" t="s">
         <v>7</v>
@@ -15475,10 +15487,10 @@
     </row>
     <row r="683" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
-        <v>1336</v>
+        <v>1332</v>
       </c>
       <c r="B683" t="s">
-        <v>1337</v>
+        <v>1333</v>
       </c>
       <c r="C683" s="2" t="s">
         <v>7</v>
@@ -15489,10 +15501,10 @@
     </row>
     <row r="684" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
-        <v>1338</v>
+        <v>1334</v>
       </c>
       <c r="B684" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="C684" s="2" t="s">
         <v>7</v>
@@ -15503,10 +15515,10 @@
     </row>
     <row r="685" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
-        <v>1340</v>
+        <v>1336</v>
       </c>
       <c r="B685" t="s">
-        <v>1341</v>
+        <v>1337</v>
       </c>
       <c r="C685" s="2" t="s">
         <v>7</v>
@@ -15517,10 +15529,10 @@
     </row>
     <row r="686" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
-        <v>1342</v>
+        <v>1338</v>
       </c>
       <c r="B686" t="s">
-        <v>1343</v>
+        <v>1339</v>
       </c>
       <c r="C686" s="2" t="s">
         <v>7</v>
@@ -15531,10 +15543,10 @@
     </row>
     <row r="687" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
-        <v>1344</v>
+        <v>1340</v>
       </c>
       <c r="B687" t="s">
-        <v>1345</v>
+        <v>1341</v>
       </c>
       <c r="C687" s="2" t="s">
         <v>7</v>
@@ -15545,10 +15557,10 @@
     </row>
     <row r="688" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
-        <v>1346</v>
+        <v>1342</v>
       </c>
       <c r="B688" t="s">
-        <v>1347</v>
+        <v>1343</v>
       </c>
       <c r="C688" s="2" t="s">
         <v>7</v>
@@ -15559,10 +15571,10 @@
     </row>
     <row r="689" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
-        <v>1348</v>
+        <v>1344</v>
       </c>
       <c r="B689" t="s">
-        <v>1349</v>
+        <v>1345</v>
       </c>
       <c r="C689" s="2" t="s">
         <v>7</v>
@@ -15573,10 +15585,10 @@
     </row>
     <row r="690" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
       <c r="B690" t="s">
-        <v>1351</v>
+        <v>1347</v>
       </c>
       <c r="C690" s="2" t="s">
         <v>7</v>
@@ -15587,10 +15599,10 @@
     </row>
     <row r="691" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
-        <v>1352</v>
+        <v>1348</v>
       </c>
       <c r="B691" t="s">
-        <v>1353</v>
+        <v>1349</v>
       </c>
       <c r="C691" s="2" t="s">
         <v>7</v>
@@ -15601,10 +15613,10 @@
     </row>
     <row r="692" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
-        <v>1354</v>
+        <v>1350</v>
       </c>
       <c r="B692" t="s">
-        <v>1355</v>
+        <v>1351</v>
       </c>
       <c r="C692" s="2" t="s">
         <v>7</v>
@@ -15615,10 +15627,10 @@
     </row>
     <row r="693" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
-        <v>1356</v>
+        <v>1352</v>
       </c>
       <c r="B693" t="s">
-        <v>1357</v>
+        <v>1353</v>
       </c>
       <c r="C693" s="2" t="s">
         <v>7</v>
@@ -15629,10 +15641,10 @@
     </row>
     <row r="694" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
-        <v>1358</v>
+        <v>1354</v>
       </c>
       <c r="B694" t="s">
-        <v>1359</v>
+        <v>1355</v>
       </c>
       <c r="C694" s="2" t="s">
         <v>7</v>
@@ -15643,10 +15655,10 @@
     </row>
     <row r="695" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
-        <v>1360</v>
+        <v>1356</v>
       </c>
       <c r="B695" t="s">
-        <v>1361</v>
+        <v>1357</v>
       </c>
       <c r="C695" s="2" t="s">
         <v>7</v>
@@ -15657,10 +15669,10 @@
     </row>
     <row r="696" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
-        <v>1362</v>
+        <v>1358</v>
       </c>
       <c r="B696" t="s">
-        <v>1363</v>
+        <v>1359</v>
       </c>
       <c r="C696" s="2" t="s">
         <v>7</v>
@@ -15671,10 +15683,10 @@
     </row>
     <row r="697" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="B697" t="s">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="C697" s="2" t="s">
         <v>7</v>
@@ -15685,10 +15697,10 @@
     </row>
     <row r="698" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
-        <v>1366</v>
+        <v>1362</v>
       </c>
       <c r="B698" t="s">
-        <v>1367</v>
+        <v>1363</v>
       </c>
       <c r="C698" s="2" t="s">
         <v>7</v>
@@ -15699,10 +15711,10 @@
     </row>
     <row r="699" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="B699" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="C699" s="2" t="s">
         <v>7</v>
@@ -15713,10 +15725,10 @@
     </row>
     <row r="700" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="B700" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="C700" s="2" t="s">
         <v>7</v>
@@ -15727,10 +15739,10 @@
     </row>
     <row r="701" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
-        <v>1372</v>
+        <v>1368</v>
       </c>
       <c r="B701" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="C701" s="2" t="s">
         <v>7</v>
@@ -15741,10 +15753,10 @@
     </row>
     <row r="702" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
-        <v>1374</v>
+        <v>1370</v>
       </c>
       <c r="B702" t="s">
-        <v>1375</v>
+        <v>1371</v>
       </c>
       <c r="C702" s="2" t="s">
         <v>7</v>
@@ -15755,10 +15767,10 @@
     </row>
     <row r="703" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
-        <v>1376</v>
+        <v>1372</v>
       </c>
       <c r="B703" t="s">
-        <v>1377</v>
+        <v>1373</v>
       </c>
       <c r="C703" s="2" t="s">
         <v>7</v>
@@ -15769,10 +15781,10 @@
     </row>
     <row r="704" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
-        <v>1378</v>
+        <v>1374</v>
       </c>
       <c r="B704" t="s">
-        <v>1379</v>
+        <v>1375</v>
       </c>
       <c r="C704" s="2" t="s">
         <v>7</v>
@@ -15783,10 +15795,10 @@
     </row>
     <row r="705" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
-        <v>1380</v>
+        <v>1376</v>
       </c>
       <c r="B705" t="s">
-        <v>1381</v>
+        <v>1377</v>
       </c>
       <c r="C705" s="2" t="s">
         <v>7</v>
@@ -15797,10 +15809,10 @@
     </row>
     <row r="706" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
-        <v>1382</v>
+        <v>1378</v>
       </c>
       <c r="B706" t="s">
-        <v>1383</v>
+        <v>1379</v>
       </c>
       <c r="C706" s="2" t="s">
         <v>7</v>
@@ -15811,10 +15823,10 @@
     </row>
     <row r="707" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
-        <v>1384</v>
+        <v>1380</v>
       </c>
       <c r="B707" t="s">
-        <v>1385</v>
+        <v>1381</v>
       </c>
       <c r="C707" s="2" t="s">
         <v>7</v>
@@ -15825,10 +15837,10 @@
     </row>
     <row r="708" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
-        <v>1386</v>
+        <v>1382</v>
       </c>
       <c r="B708" t="s">
-        <v>1387</v>
+        <v>1383</v>
       </c>
       <c r="C708" s="2" t="s">
         <v>7</v>
@@ -15839,10 +15851,10 @@
     </row>
     <row r="709" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
-        <v>1388</v>
+        <v>1384</v>
       </c>
       <c r="B709" t="s">
-        <v>1389</v>
+        <v>1385</v>
       </c>
       <c r="C709" s="2" t="s">
         <v>7</v>
@@ -15853,10 +15865,10 @@
     </row>
     <row r="710" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
-        <v>1392</v>
+        <v>1386</v>
       </c>
       <c r="B710" t="s">
-        <v>1393</v>
+        <v>1387</v>
       </c>
       <c r="C710" s="2" t="s">
         <v>7</v>
@@ -15867,10 +15879,10 @@
     </row>
     <row r="711" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
-        <v>1394</v>
+        <v>1388</v>
       </c>
       <c r="B711" t="s">
-        <v>1395</v>
+        <v>1389</v>
       </c>
       <c r="C711" s="2" t="s">
         <v>7</v>
@@ -15881,10 +15893,10 @@
     </row>
     <row r="712" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
-        <v>1396</v>
+        <v>1390</v>
       </c>
       <c r="B712" t="s">
-        <v>1397</v>
+        <v>1391</v>
       </c>
       <c r="C712" s="2" t="s">
         <v>7</v>
@@ -15895,10 +15907,10 @@
     </row>
     <row r="713" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A713" t="s">
-        <v>1398</v>
+        <v>1392</v>
       </c>
       <c r="B713" t="s">
-        <v>1399</v>
+        <v>1393</v>
       </c>
       <c r="C713" s="2" t="s">
         <v>7</v>
@@ -15909,10 +15921,10 @@
     </row>
     <row r="714" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A714" t="s">
-        <v>1400</v>
+        <v>1396</v>
       </c>
       <c r="B714" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="C714" s="2" t="s">
         <v>7</v>
@@ -15923,10 +15935,10 @@
     </row>
     <row r="715" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B715" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="C715" s="2" t="s">
         <v>7</v>
@@ -15937,10 +15949,10 @@
     </row>
     <row r="716" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="B716" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="C716" s="2" t="s">
         <v>7</v>
@@ -15951,10 +15963,10 @@
     </row>
     <row r="717" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A717" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="B717" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="C717" s="2" t="s">
         <v>7</v>
@@ -15965,10 +15977,10 @@
     </row>
     <row r="718" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
-        <v>1408</v>
+        <v>1404</v>
       </c>
       <c r="B718" t="s">
-        <v>1409</v>
+        <v>1405</v>
       </c>
       <c r="C718" s="2" t="s">
         <v>7</v>
@@ -15979,10 +15991,10 @@
     </row>
     <row r="719" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
-        <v>1410</v>
+        <v>1406</v>
       </c>
       <c r="B719" t="s">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="C719" s="2" t="s">
         <v>7</v>
@@ -15993,10 +16005,10 @@
     </row>
     <row r="720" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A720" t="s">
-        <v>1412</v>
+        <v>1408</v>
       </c>
       <c r="B720" t="s">
-        <v>1413</v>
+        <v>1409</v>
       </c>
       <c r="C720" s="2" t="s">
         <v>7</v>
@@ -16007,10 +16019,10 @@
     </row>
     <row r="721" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
-        <v>1414</v>
+        <v>1410</v>
       </c>
       <c r="B721" t="s">
-        <v>1415</v>
+        <v>1411</v>
       </c>
       <c r="C721" s="2" t="s">
         <v>7</v>
@@ -16021,10 +16033,10 @@
     </row>
     <row r="722" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
-        <v>1416</v>
+        <v>1412</v>
       </c>
       <c r="B722" t="s">
-        <v>1417</v>
+        <v>1413</v>
       </c>
       <c r="C722" s="2" t="s">
         <v>7</v>
@@ -16035,10 +16047,10 @@
     </row>
     <row r="723" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
-        <v>1418</v>
+        <v>1414</v>
       </c>
       <c r="B723" t="s">
-        <v>1419</v>
+        <v>1415</v>
       </c>
       <c r="C723" s="2" t="s">
         <v>7</v>
@@ -16049,10 +16061,10 @@
     </row>
     <row r="724" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A724" t="s">
-        <v>1420</v>
+        <v>1416</v>
       </c>
       <c r="B724" t="s">
-        <v>1421</v>
+        <v>1417</v>
       </c>
       <c r="C724" s="2" t="s">
         <v>7</v>
@@ -16063,10 +16075,10 @@
     </row>
     <row r="725" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A725" t="s">
-        <v>1424</v>
+        <v>1418</v>
       </c>
       <c r="B725" t="s">
-        <v>1425</v>
+        <v>1419</v>
       </c>
       <c r="C725" s="2" t="s">
         <v>7</v>
@@ -16077,10 +16089,10 @@
     </row>
     <row r="726" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A726" t="s">
-        <v>1426</v>
+        <v>1420</v>
       </c>
       <c r="B726" t="s">
-        <v>1427</v>
+        <v>1421</v>
       </c>
       <c r="C726" s="2" t="s">
         <v>7</v>
@@ -16091,10 +16103,10 @@
     </row>
     <row r="727" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A727" t="s">
-        <v>1428</v>
+        <v>1422</v>
       </c>
       <c r="B727" t="s">
-        <v>1429</v>
+        <v>1423</v>
       </c>
       <c r="C727" s="2" t="s">
         <v>7</v>
@@ -16105,10 +16117,10 @@
     </row>
     <row r="728" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A728" t="s">
-        <v>1430</v>
+        <v>1424</v>
       </c>
       <c r="B728" t="s">
-        <v>1431</v>
+        <v>1425</v>
       </c>
       <c r="C728" s="2" t="s">
         <v>7</v>
@@ -16119,10 +16131,10 @@
     </row>
     <row r="729" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A729" t="s">
-        <v>1432</v>
+        <v>1428</v>
       </c>
       <c r="B729" t="s">
-        <v>1433</v>
+        <v>1429</v>
       </c>
       <c r="C729" s="2" t="s">
         <v>7</v>
@@ -16133,10 +16145,10 @@
     </row>
     <row r="730" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A730" t="s">
-        <v>1434</v>
+        <v>1430</v>
       </c>
       <c r="B730" t="s">
-        <v>1435</v>
+        <v>1431</v>
       </c>
       <c r="C730" s="2" t="s">
         <v>7</v>
@@ -16147,10 +16159,10 @@
     </row>
     <row r="731" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A731" t="s">
-        <v>1436</v>
+        <v>1432</v>
       </c>
       <c r="B731" t="s">
-        <v>1437</v>
+        <v>1433</v>
       </c>
       <c r="C731" s="2" t="s">
         <v>7</v>
@@ -16161,10 +16173,10 @@
     </row>
     <row r="732" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A732" t="s">
-        <v>1438</v>
+        <v>1434</v>
       </c>
       <c r="B732" t="s">
-        <v>1439</v>
+        <v>1435</v>
       </c>
       <c r="C732" s="2" t="s">
         <v>7</v>
@@ -16175,10 +16187,10 @@
     </row>
     <row r="733" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A733" t="s">
-        <v>1440</v>
+        <v>1436</v>
       </c>
       <c r="B733" t="s">
-        <v>1441</v>
+        <v>1437</v>
       </c>
       <c r="C733" s="2" t="s">
         <v>7</v>
@@ -16189,10 +16201,10 @@
     </row>
     <row r="734" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A734" t="s">
-        <v>1442</v>
+        <v>1438</v>
       </c>
       <c r="B734" t="s">
-        <v>1443</v>
+        <v>1439</v>
       </c>
       <c r="C734" s="2" t="s">
         <v>7</v>
@@ -16203,10 +16215,10 @@
     </row>
     <row r="735" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A735" t="s">
-        <v>1444</v>
+        <v>1440</v>
       </c>
       <c r="B735" t="s">
-        <v>1445</v>
+        <v>1441</v>
       </c>
       <c r="C735" s="2" t="s">
         <v>7</v>
@@ -16217,10 +16229,10 @@
     </row>
     <row r="736" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A736" t="s">
-        <v>1446</v>
+        <v>1442</v>
       </c>
       <c r="B736" t="s">
-        <v>1447</v>
+        <v>1443</v>
       </c>
       <c r="C736" s="2" t="s">
         <v>7</v>
@@ -16231,10 +16243,10 @@
     </row>
     <row r="737" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A737" t="s">
-        <v>1448</v>
+        <v>1444</v>
       </c>
       <c r="B737" t="s">
-        <v>1449</v>
+        <v>1445</v>
       </c>
       <c r="C737" s="2" t="s">
         <v>7</v>
@@ -16245,10 +16257,10 @@
     </row>
     <row r="738" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A738" t="s">
-        <v>1450</v>
+        <v>1446</v>
       </c>
       <c r="B738" t="s">
-        <v>1451</v>
+        <v>1447</v>
       </c>
       <c r="C738" s="2" t="s">
         <v>7</v>
@@ -16259,10 +16271,10 @@
     </row>
     <row r="739" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A739" t="s">
-        <v>1452</v>
+        <v>1448</v>
       </c>
       <c r="B739" t="s">
-        <v>1453</v>
+        <v>1449</v>
       </c>
       <c r="C739" s="2" t="s">
         <v>7</v>
@@ -16273,10 +16285,10 @@
     </row>
     <row r="740" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A740" t="s">
-        <v>1456</v>
+        <v>1450</v>
       </c>
       <c r="B740" t="s">
-        <v>1457</v>
+        <v>1451</v>
       </c>
       <c r="C740" s="2" t="s">
         <v>7</v>
@@ -16287,10 +16299,10 @@
     </row>
     <row r="741" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A741" t="s">
-        <v>1458</v>
+        <v>1452</v>
       </c>
       <c r="B741" t="s">
-        <v>1459</v>
+        <v>1453</v>
       </c>
       <c r="C741" s="2" t="s">
         <v>7</v>
@@ -16301,10 +16313,10 @@
     </row>
     <row r="742" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A742" t="s">
-        <v>1460</v>
+        <v>1454</v>
       </c>
       <c r="B742" t="s">
-        <v>1461</v>
+        <v>1455</v>
       </c>
       <c r="C742" s="2" t="s">
         <v>7</v>
@@ -16315,10 +16327,10 @@
     </row>
     <row r="743" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A743" t="s">
-        <v>1462</v>
+        <v>1456</v>
       </c>
       <c r="B743" t="s">
-        <v>1463</v>
+        <v>1457</v>
       </c>
       <c r="C743" s="2" t="s">
         <v>7</v>
@@ -16329,10 +16341,10 @@
     </row>
     <row r="744" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A744" t="s">
-        <v>1466</v>
+        <v>1460</v>
       </c>
       <c r="B744" t="s">
-        <v>1467</v>
+        <v>1461</v>
       </c>
       <c r="C744" s="2" t="s">
         <v>7</v>
@@ -16343,10 +16355,10 @@
     </row>
     <row r="745" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A745" t="s">
-        <v>1468</v>
+        <v>1462</v>
       </c>
       <c r="B745" t="s">
-        <v>1469</v>
+        <v>1463</v>
       </c>
       <c r="C745" s="2" t="s">
         <v>7</v>
@@ -16357,10 +16369,10 @@
     </row>
     <row r="746" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A746" t="s">
-        <v>1472</v>
+        <v>1464</v>
       </c>
       <c r="B746" t="s">
-        <v>1473</v>
+        <v>1465</v>
       </c>
       <c r="C746" s="2" t="s">
         <v>7</v>
@@ -16371,10 +16383,10 @@
     </row>
     <row r="747" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A747" t="s">
-        <v>1474</v>
+        <v>1466</v>
       </c>
       <c r="B747" t="s">
-        <v>1475</v>
+        <v>1467</v>
       </c>
       <c r="C747" s="2" t="s">
         <v>7</v>
@@ -16385,10 +16397,10 @@
     </row>
     <row r="748" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A748" t="s">
-        <v>1476</v>
+        <v>1470</v>
       </c>
       <c r="B748" t="s">
-        <v>1477</v>
+        <v>1471</v>
       </c>
       <c r="C748" s="2" t="s">
         <v>7</v>
@@ -16399,10 +16411,10 @@
     </row>
     <row r="749" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A749" t="s">
-        <v>1478</v>
+        <v>1472</v>
       </c>
       <c r="B749" t="s">
-        <v>1479</v>
+        <v>1473</v>
       </c>
       <c r="C749" s="2" t="s">
         <v>7</v>
@@ -16413,10 +16425,10 @@
     </row>
     <row r="750" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A750" t="s">
-        <v>1480</v>
+        <v>1476</v>
       </c>
       <c r="B750" t="s">
-        <v>1481</v>
+        <v>1477</v>
       </c>
       <c r="C750" s="2" t="s">
         <v>7</v>
@@ -16427,10 +16439,10 @@
     </row>
     <row r="751" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A751" t="s">
-        <v>1482</v>
+        <v>1478</v>
       </c>
       <c r="B751" t="s">
-        <v>1483</v>
+        <v>1479</v>
       </c>
       <c r="C751" s="2" t="s">
         <v>7</v>
@@ -16441,10 +16453,10 @@
     </row>
     <row r="752" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A752" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
       <c r="B752" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
       <c r="C752" s="2" t="s">
         <v>7</v>
@@ -16455,10 +16467,10 @@
     </row>
     <row r="753" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A753" t="s">
-        <v>1490</v>
+        <v>1482</v>
       </c>
       <c r="B753" t="s">
-        <v>1491</v>
+        <v>1483</v>
       </c>
       <c r="C753" s="2" t="s">
         <v>7</v>
@@ -16469,10 +16481,10 @@
     </row>
     <row r="754" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A754" t="s">
-        <v>1492</v>
+        <v>1484</v>
       </c>
       <c r="B754" t="s">
-        <v>1493</v>
+        <v>1485</v>
       </c>
       <c r="C754" s="2" t="s">
         <v>7</v>
@@ -16483,10 +16495,10 @@
     </row>
     <row r="755" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A755" t="s">
-        <v>1494</v>
+        <v>1486</v>
       </c>
       <c r="B755" t="s">
-        <v>1495</v>
+        <v>1487</v>
       </c>
       <c r="C755" s="2" t="s">
         <v>7</v>
@@ -16497,10 +16509,10 @@
     </row>
     <row r="756" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A756" t="s">
-        <v>1496</v>
+        <v>1490</v>
       </c>
       <c r="B756" t="s">
-        <v>1497</v>
+        <v>1491</v>
       </c>
       <c r="C756" s="2" t="s">
         <v>7</v>
@@ -16511,10 +16523,10 @@
     </row>
     <row r="757" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A757" t="s">
-        <v>1498</v>
+        <v>1494</v>
       </c>
       <c r="B757" t="s">
-        <v>1499</v>
+        <v>1495</v>
       </c>
       <c r="C757" s="2" t="s">
         <v>7</v>
@@ -16525,10 +16537,10 @@
     </row>
     <row r="758" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A758" t="s">
-        <v>1500</v>
+        <v>1496</v>
       </c>
       <c r="B758" t="s">
-        <v>1501</v>
+        <v>1497</v>
       </c>
       <c r="C758" s="2" t="s">
         <v>7</v>
@@ -16539,10 +16551,10 @@
     </row>
     <row r="759" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A759" t="s">
-        <v>1502</v>
+        <v>1498</v>
       </c>
       <c r="B759" t="s">
-        <v>1503</v>
+        <v>1499</v>
       </c>
       <c r="C759" s="2" t="s">
         <v>7</v>
@@ -16553,10 +16565,10 @@
     </row>
     <row r="760" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A760" t="s">
-        <v>1504</v>
+        <v>1500</v>
       </c>
       <c r="B760" t="s">
-        <v>1505</v>
+        <v>1501</v>
       </c>
       <c r="C760" s="2" t="s">
         <v>7</v>
@@ -16567,10 +16579,10 @@
     </row>
     <row r="761" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A761" t="s">
-        <v>1506</v>
+        <v>1502</v>
       </c>
       <c r="B761" t="s">
-        <v>1507</v>
+        <v>1503</v>
       </c>
       <c r="C761" s="2" t="s">
         <v>7</v>
@@ -16581,10 +16593,10 @@
     </row>
     <row r="762" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A762" t="s">
-        <v>1508</v>
+        <v>1504</v>
       </c>
       <c r="B762" t="s">
-        <v>1509</v>
+        <v>1505</v>
       </c>
       <c r="C762" s="2" t="s">
         <v>7</v>
@@ -16595,10 +16607,10 @@
     </row>
     <row r="763" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A763" t="s">
-        <v>1510</v>
+        <v>1506</v>
       </c>
       <c r="B763" t="s">
-        <v>1511</v>
+        <v>1507</v>
       </c>
       <c r="C763" s="2" t="s">
         <v>7</v>
@@ -16609,10 +16621,10 @@
     </row>
     <row r="764" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A764" t="s">
-        <v>1512</v>
+        <v>1508</v>
       </c>
       <c r="B764" t="s">
-        <v>1513</v>
+        <v>1509</v>
       </c>
       <c r="C764" s="2" t="s">
         <v>7</v>
@@ -16623,10 +16635,10 @@
     </row>
     <row r="765" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A765" t="s">
-        <v>1514</v>
+        <v>1510</v>
       </c>
       <c r="B765" t="s">
-        <v>1515</v>
+        <v>1511</v>
       </c>
       <c r="C765" s="2" t="s">
         <v>7</v>
@@ -16637,10 +16649,10 @@
     </row>
     <row r="766" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A766" t="s">
-        <v>1516</v>
+        <v>1512</v>
       </c>
       <c r="B766" t="s">
-        <v>1517</v>
+        <v>1513</v>
       </c>
       <c r="C766" s="2" t="s">
         <v>7</v>
@@ -16651,10 +16663,10 @@
     </row>
     <row r="767" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A767" t="s">
-        <v>1518</v>
+        <v>1514</v>
       </c>
       <c r="B767" t="s">
-        <v>1519</v>
+        <v>1515</v>
       </c>
       <c r="C767" s="2" t="s">
         <v>7</v>
@@ -16665,10 +16677,10 @@
     </row>
     <row r="768" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A768" t="s">
-        <v>1520</v>
+        <v>1516</v>
       </c>
       <c r="B768" t="s">
-        <v>1521</v>
+        <v>1517</v>
       </c>
       <c r="C768" s="2" t="s">
         <v>7</v>
@@ -16679,10 +16691,10 @@
     </row>
     <row r="769" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A769" t="s">
-        <v>1522</v>
+        <v>1518</v>
       </c>
       <c r="B769" t="s">
-        <v>1523</v>
+        <v>1519</v>
       </c>
       <c r="C769" s="2" t="s">
         <v>7</v>
@@ -16693,10 +16705,10 @@
     </row>
     <row r="770" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A770" t="s">
-        <v>1524</v>
+        <v>1520</v>
       </c>
       <c r="B770" t="s">
-        <v>1525</v>
+        <v>1521</v>
       </c>
       <c r="C770" s="2" t="s">
         <v>7</v>
@@ -16707,10 +16719,10 @@
     </row>
     <row r="771" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A771" t="s">
-        <v>1526</v>
+        <v>1522</v>
       </c>
       <c r="B771" t="s">
-        <v>1527</v>
+        <v>1523</v>
       </c>
       <c r="C771" s="2" t="s">
         <v>7</v>
@@ -16721,10 +16733,10 @@
     </row>
     <row r="772" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A772" t="s">
-        <v>1528</v>
+        <v>1524</v>
       </c>
       <c r="B772" t="s">
-        <v>1529</v>
+        <v>1525</v>
       </c>
       <c r="C772" s="2" t="s">
         <v>7</v>
@@ -16735,10 +16747,10 @@
     </row>
     <row r="773" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A773" t="s">
-        <v>1530</v>
+        <v>1526</v>
       </c>
       <c r="B773" t="s">
-        <v>1531</v>
+        <v>1527</v>
       </c>
       <c r="C773" s="2" t="s">
         <v>7</v>
@@ -16749,10 +16761,10 @@
     </row>
     <row r="774" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A774" t="s">
-        <v>1532</v>
+        <v>1528</v>
       </c>
       <c r="B774" t="s">
-        <v>1533</v>
+        <v>1529</v>
       </c>
       <c r="C774" s="2" t="s">
         <v>7</v>
@@ -16763,10 +16775,10 @@
     </row>
     <row r="775" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A775" t="s">
-        <v>1534</v>
+        <v>1530</v>
       </c>
       <c r="B775" t="s">
-        <v>1535</v>
+        <v>1531</v>
       </c>
       <c r="C775" s="2" t="s">
         <v>7</v>
@@ -16777,10 +16789,10 @@
     </row>
     <row r="776" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A776" t="s">
-        <v>1536</v>
+        <v>1532</v>
       </c>
       <c r="B776" t="s">
-        <v>1537</v>
+        <v>1533</v>
       </c>
       <c r="C776" s="2" t="s">
         <v>7</v>
@@ -16791,10 +16803,10 @@
     </row>
     <row r="777" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A777" t="s">
-        <v>1538</v>
+        <v>1534</v>
       </c>
       <c r="B777" t="s">
-        <v>1539</v>
+        <v>1535</v>
       </c>
       <c r="C777" s="2" t="s">
         <v>7</v>
@@ -16805,10 +16817,10 @@
     </row>
     <row r="778" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A778" t="s">
-        <v>1540</v>
+        <v>1536</v>
       </c>
       <c r="B778" t="s">
-        <v>1541</v>
+        <v>1537</v>
       </c>
       <c r="C778" s="2" t="s">
         <v>7</v>
@@ -16819,10 +16831,10 @@
     </row>
     <row r="779" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A779" t="s">
-        <v>1542</v>
+        <v>1538</v>
       </c>
       <c r="B779" t="s">
-        <v>1543</v>
+        <v>1539</v>
       </c>
       <c r="C779" s="2" t="s">
         <v>7</v>
@@ -16833,10 +16845,10 @@
     </row>
     <row r="780" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A780" t="s">
-        <v>1544</v>
+        <v>1540</v>
       </c>
       <c r="B780" t="s">
-        <v>1545</v>
+        <v>1541</v>
       </c>
       <c r="C780" s="2" t="s">
         <v>7</v>
@@ -16847,10 +16859,10 @@
     </row>
     <row r="781" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A781" t="s">
-        <v>1546</v>
+        <v>1542</v>
       </c>
       <c r="B781" t="s">
-        <v>1547</v>
+        <v>1543</v>
       </c>
       <c r="C781" s="2" t="s">
         <v>7</v>
@@ -16861,10 +16873,10 @@
     </row>
     <row r="782" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A782" t="s">
-        <v>1548</v>
+        <v>1544</v>
       </c>
       <c r="B782" t="s">
-        <v>1549</v>
+        <v>1545</v>
       </c>
       <c r="C782" s="2" t="s">
         <v>7</v>
@@ -16875,10 +16887,10 @@
     </row>
     <row r="783" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A783" t="s">
-        <v>1550</v>
+        <v>1546</v>
       </c>
       <c r="B783" t="s">
-        <v>1551</v>
+        <v>1547</v>
       </c>
       <c r="C783" s="2" t="s">
         <v>7</v>
@@ -16889,10 +16901,10 @@
     </row>
     <row r="784" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A784" t="s">
-        <v>1552</v>
+        <v>1548</v>
       </c>
       <c r="B784" t="s">
-        <v>1553</v>
+        <v>1549</v>
       </c>
       <c r="C784" s="2" t="s">
         <v>7</v>
@@ -16903,10 +16915,10 @@
     </row>
     <row r="785" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A785" t="s">
-        <v>1554</v>
+        <v>1550</v>
       </c>
       <c r="B785" t="s">
-        <v>1555</v>
+        <v>1551</v>
       </c>
       <c r="C785" s="2" t="s">
         <v>7</v>
@@ -16917,10 +16929,10 @@
     </row>
     <row r="786" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A786" t="s">
-        <v>1556</v>
+        <v>1552</v>
       </c>
       <c r="B786" t="s">
-        <v>1557</v>
+        <v>1553</v>
       </c>
       <c r="C786" s="2" t="s">
         <v>7</v>
@@ -16931,10 +16943,10 @@
     </row>
     <row r="787" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A787" t="s">
-        <v>1558</v>
+        <v>1554</v>
       </c>
       <c r="B787" t="s">
-        <v>1559</v>
+        <v>1555</v>
       </c>
       <c r="C787" s="2" t="s">
         <v>7</v>
@@ -16945,10 +16957,10 @@
     </row>
     <row r="788" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A788" t="s">
-        <v>1560</v>
+        <v>1556</v>
       </c>
       <c r="B788" t="s">
-        <v>1561</v>
+        <v>1557</v>
       </c>
       <c r="C788" s="2" t="s">
         <v>7</v>
@@ -16959,10 +16971,10 @@
     </row>
     <row r="789" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A789" t="s">
-        <v>1562</v>
+        <v>1558</v>
       </c>
       <c r="B789" t="s">
-        <v>1563</v>
+        <v>1559</v>
       </c>
       <c r="C789" s="2" t="s">
         <v>7</v>
@@ -16973,10 +16985,10 @@
     </row>
     <row r="790" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A790" t="s">
-        <v>1564</v>
+        <v>1560</v>
       </c>
       <c r="B790" t="s">
-        <v>1565</v>
+        <v>1561</v>
       </c>
       <c r="C790" s="2" t="s">
         <v>7</v>
@@ -16987,10 +16999,10 @@
     </row>
     <row r="791" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A791" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="B791" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="C791" s="2" t="s">
         <v>7</v>
@@ -17001,10 +17013,10 @@
     </row>
     <row r="792" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A792" t="s">
-        <v>1568</v>
+        <v>1564</v>
       </c>
       <c r="B792" t="s">
-        <v>1569</v>
+        <v>1565</v>
       </c>
       <c r="C792" s="2" t="s">
         <v>7</v>
@@ -17015,10 +17027,10 @@
     </row>
     <row r="793" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A793" t="s">
-        <v>1570</v>
+        <v>1566</v>
       </c>
       <c r="B793" t="s">
-        <v>1571</v>
+        <v>1567</v>
       </c>
       <c r="C793" s="2" t="s">
         <v>7</v>
@@ -17029,10 +17041,10 @@
     </row>
     <row r="794" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A794" t="s">
-        <v>1572</v>
+        <v>1568</v>
       </c>
       <c r="B794" t="s">
-        <v>1573</v>
+        <v>1569</v>
       </c>
       <c r="C794" s="2" t="s">
         <v>7</v>
@@ -17043,10 +17055,10 @@
     </row>
     <row r="795" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A795" t="s">
-        <v>1576</v>
+        <v>1570</v>
       </c>
       <c r="B795" t="s">
-        <v>1577</v>
+        <v>1571</v>
       </c>
       <c r="C795" s="2" t="s">
         <v>7</v>
@@ -17057,10 +17069,10 @@
     </row>
     <row r="796" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A796" t="s">
-        <v>1578</v>
+        <v>1572</v>
       </c>
       <c r="B796" t="s">
-        <v>1579</v>
+        <v>1573</v>
       </c>
       <c r="C796" s="2" t="s">
         <v>7</v>
@@ -17071,10 +17083,10 @@
     </row>
     <row r="797" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A797" t="s">
-        <v>1580</v>
+        <v>1574</v>
       </c>
       <c r="B797" t="s">
-        <v>1581</v>
+        <v>1575</v>
       </c>
       <c r="C797" s="2" t="s">
         <v>7</v>
@@ -17085,10 +17097,10 @@
     </row>
     <row r="798" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A798" t="s">
-        <v>1582</v>
+        <v>1576</v>
       </c>
       <c r="B798" t="s">
-        <v>1583</v>
+        <v>1577</v>
       </c>
       <c r="C798" s="2" t="s">
         <v>7</v>
@@ -17099,10 +17111,10 @@
     </row>
     <row r="799" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A799" t="s">
-        <v>1584</v>
+        <v>1580</v>
       </c>
       <c r="B799" t="s">
-        <v>1585</v>
+        <v>1581</v>
       </c>
       <c r="C799" s="2" t="s">
         <v>7</v>
@@ -17113,10 +17125,10 @@
     </row>
     <row r="800" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A800" t="s">
-        <v>1586</v>
+        <v>1582</v>
       </c>
       <c r="B800" t="s">
-        <v>1587</v>
+        <v>1583</v>
       </c>
       <c r="C800" s="2" t="s">
         <v>7</v>
@@ -17127,10 +17139,10 @@
     </row>
     <row r="801" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A801" t="s">
-        <v>1588</v>
+        <v>1584</v>
       </c>
       <c r="B801" t="s">
-        <v>1589</v>
+        <v>1585</v>
       </c>
       <c r="C801" s="2" t="s">
         <v>7</v>
@@ -17141,10 +17153,10 @@
     </row>
     <row r="802" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A802" t="s">
-        <v>1590</v>
+        <v>1586</v>
       </c>
       <c r="B802" t="s">
-        <v>1591</v>
+        <v>1587</v>
       </c>
       <c r="C802" s="2" t="s">
         <v>7</v>
@@ -17155,10 +17167,10 @@
     </row>
     <row r="803" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A803" t="s">
-        <v>1592</v>
+        <v>1588</v>
       </c>
       <c r="B803" t="s">
-        <v>1593</v>
+        <v>1589</v>
       </c>
       <c r="C803" s="2" t="s">
         <v>7</v>
@@ -17169,10 +17181,10 @@
     </row>
     <row r="804" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A804" t="s">
-        <v>1594</v>
+        <v>1590</v>
       </c>
       <c r="B804" t="s">
-        <v>1595</v>
+        <v>1591</v>
       </c>
       <c r="C804" s="2" t="s">
         <v>7</v>
@@ -17183,10 +17195,10 @@
     </row>
     <row r="805" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A805" t="s">
-        <v>1596</v>
+        <v>1592</v>
       </c>
       <c r="B805" t="s">
-        <v>1597</v>
+        <v>1593</v>
       </c>
       <c r="C805" s="2" t="s">
         <v>7</v>
@@ -17197,10 +17209,10 @@
     </row>
     <row r="806" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A806" t="s">
-        <v>1598</v>
+        <v>1594</v>
       </c>
       <c r="B806" t="s">
-        <v>1599</v>
+        <v>1595</v>
       </c>
       <c r="C806" s="2" t="s">
         <v>7</v>
@@ -17211,10 +17223,10 @@
     </row>
     <row r="807" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A807" t="s">
-        <v>1600</v>
+        <v>1596</v>
       </c>
       <c r="B807" t="s">
-        <v>1601</v>
+        <v>1597</v>
       </c>
       <c r="C807" s="2" t="s">
         <v>7</v>
@@ -17225,10 +17237,10 @@
     </row>
     <row r="808" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A808" t="s">
-        <v>1602</v>
+        <v>1598</v>
       </c>
       <c r="B808" t="s">
-        <v>1603</v>
+        <v>1599</v>
       </c>
       <c r="C808" s="2" t="s">
         <v>7</v>
@@ -17239,10 +17251,10 @@
     </row>
     <row r="809" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A809" t="s">
-        <v>1604</v>
+        <v>1600</v>
       </c>
       <c r="B809" t="s">
-        <v>1605</v>
+        <v>1601</v>
       </c>
       <c r="C809" s="2" t="s">
         <v>7</v>
@@ -17253,10 +17265,10 @@
     </row>
     <row r="810" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A810" t="s">
-        <v>1606</v>
+        <v>1602</v>
       </c>
       <c r="B810" t="s">
-        <v>1607</v>
+        <v>1603</v>
       </c>
       <c r="C810" s="2" t="s">
         <v>7</v>
@@ -17267,10 +17279,10 @@
     </row>
     <row r="811" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A811" t="s">
-        <v>1608</v>
+        <v>1604</v>
       </c>
       <c r="B811" t="s">
-        <v>1609</v>
+        <v>1605</v>
       </c>
       <c r="C811" s="2" t="s">
         <v>7</v>
@@ -17281,10 +17293,10 @@
     </row>
     <row r="812" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A812" t="s">
-        <v>1610</v>
+        <v>1606</v>
       </c>
       <c r="B812" t="s">
-        <v>1611</v>
+        <v>1607</v>
       </c>
       <c r="C812" s="2" t="s">
         <v>7</v>
@@ -17295,10 +17307,10 @@
     </row>
     <row r="813" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A813" t="s">
-        <v>1612</v>
+        <v>1608</v>
       </c>
       <c r="B813" t="s">
-        <v>1613</v>
+        <v>1609</v>
       </c>
       <c r="C813" s="2" t="s">
         <v>7</v>
@@ -17309,10 +17321,10 @@
     </row>
     <row r="814" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A814" t="s">
-        <v>1614</v>
+        <v>1610</v>
       </c>
       <c r="B814" t="s">
-        <v>1615</v>
+        <v>1611</v>
       </c>
       <c r="C814" s="2" t="s">
         <v>7</v>
@@ -17323,10 +17335,10 @@
     </row>
     <row r="815" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A815" t="s">
-        <v>1616</v>
+        <v>1612</v>
       </c>
       <c r="B815" t="s">
-        <v>1617</v>
+        <v>1613</v>
       </c>
       <c r="C815" s="2" t="s">
         <v>7</v>
@@ -17337,10 +17349,10 @@
     </row>
     <row r="816" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A816" t="s">
-        <v>1618</v>
+        <v>1614</v>
       </c>
       <c r="B816" t="s">
-        <v>1619</v>
+        <v>1615</v>
       </c>
       <c r="C816" s="2" t="s">
         <v>7</v>
@@ -17351,10 +17363,10 @@
     </row>
     <row r="817" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A817" t="s">
-        <v>1620</v>
+        <v>1616</v>
       </c>
       <c r="B817" t="s">
-        <v>1621</v>
+        <v>1617</v>
       </c>
       <c r="C817" s="2" t="s">
         <v>7</v>
@@ -17365,10 +17377,10 @@
     </row>
     <row r="818" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A818" t="s">
-        <v>1622</v>
+        <v>1618</v>
       </c>
       <c r="B818" t="s">
-        <v>1623</v>
+        <v>1619</v>
       </c>
       <c r="C818" s="2" t="s">
         <v>7</v>
@@ -17379,10 +17391,10 @@
     </row>
     <row r="819" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A819" t="s">
-        <v>1624</v>
+        <v>1620</v>
       </c>
       <c r="B819" t="s">
-        <v>1625</v>
+        <v>1621</v>
       </c>
       <c r="C819" s="2" t="s">
         <v>7</v>
@@ -17393,10 +17405,10 @@
     </row>
     <row r="820" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A820" t="s">
-        <v>1630</v>
+        <v>1622</v>
       </c>
       <c r="B820" t="s">
-        <v>1631</v>
+        <v>1623</v>
       </c>
       <c r="C820" s="2" t="s">
         <v>7</v>
@@ -17407,10 +17419,10 @@
     </row>
     <row r="821" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A821" t="s">
-        <v>1632</v>
+        <v>1624</v>
       </c>
       <c r="B821" t="s">
-        <v>1633</v>
+        <v>1625</v>
       </c>
       <c r="C821" s="2" t="s">
         <v>7</v>
@@ -17421,10 +17433,10 @@
     </row>
     <row r="822" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A822" t="s">
-        <v>1634</v>
+        <v>1626</v>
       </c>
       <c r="B822" t="s">
-        <v>1635</v>
+        <v>1627</v>
       </c>
       <c r="C822" s="2" t="s">
         <v>7</v>
@@ -17435,10 +17447,10 @@
     </row>
     <row r="823" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A823" t="s">
-        <v>1636</v>
+        <v>1628</v>
       </c>
       <c r="B823" t="s">
-        <v>1637</v>
+        <v>1629</v>
       </c>
       <c r="C823" s="2" t="s">
         <v>7</v>
@@ -17449,10 +17461,10 @@
     </row>
     <row r="824" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A824" t="s">
-        <v>1638</v>
+        <v>1634</v>
       </c>
       <c r="B824" t="s">
-        <v>1639</v>
+        <v>1635</v>
       </c>
       <c r="C824" s="2" t="s">
         <v>7</v>
@@ -17463,10 +17475,10 @@
     </row>
     <row r="825" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A825" t="s">
-        <v>1644</v>
+        <v>1636</v>
       </c>
       <c r="B825" t="s">
-        <v>1645</v>
+        <v>1637</v>
       </c>
       <c r="C825" s="2" t="s">
         <v>7</v>
@@ -17477,10 +17489,10 @@
     </row>
     <row r="826" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A826" t="s">
-        <v>1646</v>
+        <v>1638</v>
       </c>
       <c r="B826" t="s">
-        <v>1647</v>
+        <v>1639</v>
       </c>
       <c r="C826" s="2" t="s">
         <v>7</v>
@@ -17491,10 +17503,10 @@
     </row>
     <row r="827" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A827" t="s">
-        <v>1648</v>
+        <v>1640</v>
       </c>
       <c r="B827" t="s">
-        <v>1649</v>
+        <v>1641</v>
       </c>
       <c r="C827" s="2" t="s">
         <v>7</v>
@@ -17505,10 +17517,10 @@
     </row>
     <row r="828" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A828" t="s">
-        <v>1650</v>
+        <v>1642</v>
       </c>
       <c r="B828" t="s">
-        <v>1651</v>
+        <v>1643</v>
       </c>
       <c r="C828" s="2" t="s">
         <v>7</v>
@@ -17519,10 +17531,10 @@
     </row>
     <row r="829" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A829" t="s">
-        <v>1652</v>
+        <v>1648</v>
       </c>
       <c r="B829" t="s">
-        <v>1653</v>
+        <v>1649</v>
       </c>
       <c r="C829" s="2" t="s">
         <v>7</v>
@@ -17533,10 +17545,10 @@
     </row>
     <row r="830" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A830" t="s">
-        <v>1654</v>
+        <v>1650</v>
       </c>
       <c r="B830" t="s">
-        <v>1655</v>
+        <v>1651</v>
       </c>
       <c r="C830" s="2" t="s">
         <v>7</v>
@@ -17547,10 +17559,10 @@
     </row>
     <row r="831" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A831" t="s">
-        <v>1656</v>
+        <v>1652</v>
       </c>
       <c r="B831" t="s">
-        <v>1657</v>
+        <v>1653</v>
       </c>
       <c r="C831" s="2" t="s">
         <v>7</v>
@@ -17561,10 +17573,10 @@
     </row>
     <row r="832" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A832" t="s">
-        <v>1658</v>
+        <v>1654</v>
       </c>
       <c r="B832" t="s">
-        <v>1659</v>
+        <v>1655</v>
       </c>
       <c r="C832" s="2" t="s">
         <v>7</v>
@@ -17575,10 +17587,10 @@
     </row>
     <row r="833" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A833" t="s">
-        <v>1662</v>
+        <v>1656</v>
       </c>
       <c r="B833" t="s">
-        <v>1663</v>
+        <v>1657</v>
       </c>
       <c r="C833" s="2" t="s">
         <v>7</v>
@@ -17589,10 +17601,10 @@
     </row>
     <row r="834" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A834" t="s">
-        <v>1664</v>
+        <v>1658</v>
       </c>
       <c r="B834" t="s">
-        <v>1665</v>
+        <v>1659</v>
       </c>
       <c r="C834" s="2" t="s">
         <v>7</v>
@@ -17603,10 +17615,10 @@
     </row>
     <row r="835" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A835" t="s">
-        <v>1666</v>
+        <v>1660</v>
       </c>
       <c r="B835" t="s">
-        <v>1667</v>
+        <v>1661</v>
       </c>
       <c r="C835" s="2" t="s">
         <v>7</v>
@@ -17617,10 +17629,10 @@
     </row>
     <row r="836" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A836" t="s">
-        <v>1668</v>
+        <v>1662</v>
       </c>
       <c r="B836" t="s">
-        <v>1669</v>
+        <v>1663</v>
       </c>
       <c r="C836" s="2" t="s">
         <v>7</v>
@@ -17631,10 +17643,10 @@
     </row>
     <row r="837" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A837" t="s">
-        <v>1670</v>
+        <v>1666</v>
       </c>
       <c r="B837" t="s">
-        <v>1671</v>
+        <v>1667</v>
       </c>
       <c r="C837" s="2" t="s">
         <v>7</v>
@@ -17645,10 +17657,10 @@
     </row>
     <row r="838" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A838" t="s">
-        <v>1672</v>
+        <v>1668</v>
       </c>
       <c r="B838" t="s">
-        <v>1673</v>
+        <v>1669</v>
       </c>
       <c r="C838" s="2" t="s">
         <v>7</v>
@@ -17659,10 +17671,10 @@
     </row>
     <row r="839" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A839" t="s">
-        <v>1674</v>
+        <v>1670</v>
       </c>
       <c r="B839" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="C839" s="2" t="s">
         <v>7</v>
@@ -17673,10 +17685,10 @@
     </row>
     <row r="840" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A840" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="B840" t="s">
-        <v>1677</v>
+        <v>1673</v>
       </c>
       <c r="C840" s="2" t="s">
         <v>7</v>
@@ -17687,10 +17699,10 @@
     </row>
     <row r="841" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A841" t="s">
-        <v>1678</v>
+        <v>1674</v>
       </c>
       <c r="B841" t="s">
-        <v>1679</v>
+        <v>1675</v>
       </c>
       <c r="C841" s="2" t="s">
         <v>7</v>
@@ -17701,10 +17713,10 @@
     </row>
     <row r="842" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A842" t="s">
-        <v>1682</v>
+        <v>1676</v>
       </c>
       <c r="B842" t="s">
-        <v>1683</v>
+        <v>1677</v>
       </c>
       <c r="C842" s="2" t="s">
         <v>7</v>
@@ -17715,10 +17727,10 @@
     </row>
     <row r="843" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A843" t="s">
-        <v>1684</v>
+        <v>1678</v>
       </c>
       <c r="B843" t="s">
-        <v>1685</v>
+        <v>1679</v>
       </c>
       <c r="C843" s="2" t="s">
         <v>7</v>
@@ -17729,10 +17741,10 @@
     </row>
     <row r="844" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A844" t="s">
-        <v>1686</v>
+        <v>1680</v>
       </c>
       <c r="B844" t="s">
-        <v>1687</v>
+        <v>1681</v>
       </c>
       <c r="C844" s="2" t="s">
         <v>7</v>
@@ -17743,10 +17755,10 @@
     </row>
     <row r="845" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A845" t="s">
-        <v>1688</v>
+        <v>1682</v>
       </c>
       <c r="B845" t="s">
-        <v>1689</v>
+        <v>1683</v>
       </c>
       <c r="C845" s="2" t="s">
         <v>7</v>
@@ -17757,10 +17769,10 @@
     </row>
     <row r="846" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A846" t="s">
-        <v>1692</v>
+        <v>1686</v>
       </c>
       <c r="B846" t="s">
-        <v>1693</v>
+        <v>1687</v>
       </c>
       <c r="C846" s="2" t="s">
         <v>7</v>
@@ -17771,10 +17783,10 @@
     </row>
     <row r="847" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A847" t="s">
-        <v>1694</v>
+        <v>1688</v>
       </c>
       <c r="B847" t="s">
-        <v>1695</v>
+        <v>1689</v>
       </c>
       <c r="C847" s="2" t="s">
         <v>7</v>
@@ -17785,10 +17797,10 @@
     </row>
     <row r="848" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A848" t="s">
-        <v>1696</v>
+        <v>1690</v>
       </c>
       <c r="B848" t="s">
-        <v>1697</v>
+        <v>1691</v>
       </c>
       <c r="C848" s="2" t="s">
         <v>7</v>
@@ -17799,10 +17811,10 @@
     </row>
     <row r="849" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A849" t="s">
-        <v>1698</v>
+        <v>1692</v>
       </c>
       <c r="B849" t="s">
-        <v>1699</v>
+        <v>1693</v>
       </c>
       <c r="C849" s="2" t="s">
         <v>7</v>
@@ -17813,10 +17825,10 @@
     </row>
     <row r="850" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A850" t="s">
-        <v>1700</v>
+        <v>1694</v>
       </c>
       <c r="B850" t="s">
-        <v>1701</v>
+        <v>1695</v>
       </c>
       <c r="C850" s="2" t="s">
         <v>7</v>
@@ -17827,10 +17839,10 @@
     </row>
     <row r="851" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A851" t="s">
-        <v>1702</v>
+        <v>1696</v>
       </c>
       <c r="B851" t="s">
-        <v>1703</v>
+        <v>1697</v>
       </c>
       <c r="C851" s="2" t="s">
         <v>7</v>
@@ -17841,10 +17853,10 @@
     </row>
     <row r="852" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A852" t="s">
-        <v>1704</v>
+        <v>1698</v>
       </c>
       <c r="B852" t="s">
-        <v>1705</v>
+        <v>1699</v>
       </c>
       <c r="C852" s="2" t="s">
         <v>7</v>
@@ -17855,10 +17867,10 @@
     </row>
     <row r="853" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A853" t="s">
-        <v>1708</v>
+        <v>1700</v>
       </c>
       <c r="B853" t="s">
-        <v>1709</v>
+        <v>1701</v>
       </c>
       <c r="C853" s="2" t="s">
         <v>7</v>
@@ -17869,10 +17881,10 @@
     </row>
     <row r="854" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A854" t="s">
-        <v>1710</v>
+        <v>1702</v>
       </c>
       <c r="B854" t="s">
-        <v>1711</v>
+        <v>1703</v>
       </c>
       <c r="C854" s="2" t="s">
         <v>7</v>
@@ -17883,10 +17895,10 @@
     </row>
     <row r="855" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A855" t="s">
-        <v>1712</v>
+        <v>1704</v>
       </c>
       <c r="B855" t="s">
-        <v>1713</v>
+        <v>1705</v>
       </c>
       <c r="C855" s="2" t="s">
         <v>7</v>
@@ -17897,10 +17909,10 @@
     </row>
     <row r="856" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A856" t="s">
-        <v>1714</v>
+        <v>1706</v>
       </c>
       <c r="B856" t="s">
-        <v>1715</v>
+        <v>1707</v>
       </c>
       <c r="C856" s="2" t="s">
         <v>7</v>
@@ -17911,10 +17923,10 @@
     </row>
     <row r="857" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A857" t="s">
-        <v>1716</v>
+        <v>1708</v>
       </c>
       <c r="B857" t="s">
-        <v>1717</v>
+        <v>1709</v>
       </c>
       <c r="C857" s="2" t="s">
         <v>7</v>
@@ -17925,10 +17937,10 @@
     </row>
     <row r="858" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A858" t="s">
-        <v>1718</v>
+        <v>1712</v>
       </c>
       <c r="B858" t="s">
-        <v>1719</v>
+        <v>1713</v>
       </c>
       <c r="C858" s="2" t="s">
         <v>7</v>
@@ -17939,10 +17951,10 @@
     </row>
     <row r="859" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A859" t="s">
-        <v>1720</v>
+        <v>1714</v>
       </c>
       <c r="B859" t="s">
-        <v>1721</v>
+        <v>1715</v>
       </c>
       <c r="C859" s="2" t="s">
         <v>7</v>
@@ -17953,10 +17965,10 @@
     </row>
     <row r="860" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A860" t="s">
-        <v>1722</v>
+        <v>1716</v>
       </c>
       <c r="B860" t="s">
-        <v>1723</v>
+        <v>1717</v>
       </c>
       <c r="C860" s="2" t="s">
         <v>7</v>
@@ -17967,10 +17979,10 @@
     </row>
     <row r="861" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A861" t="s">
-        <v>1724</v>
+        <v>1718</v>
       </c>
       <c r="B861" t="s">
-        <v>1725</v>
+        <v>1719</v>
       </c>
       <c r="C861" s="2" t="s">
         <v>7</v>
@@ -17981,10 +17993,10 @@
     </row>
     <row r="862" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A862" t="s">
-        <v>1726</v>
+        <v>1720</v>
       </c>
       <c r="B862" t="s">
-        <v>1727</v>
+        <v>1721</v>
       </c>
       <c r="C862" s="2" t="s">
         <v>7</v>
@@ -17995,10 +18007,10 @@
     </row>
     <row r="863" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A863" t="s">
-        <v>1728</v>
+        <v>1722</v>
       </c>
       <c r="B863" t="s">
-        <v>1729</v>
+        <v>1723</v>
       </c>
       <c r="C863" s="2" t="s">
         <v>7</v>
@@ -18009,10 +18021,10 @@
     </row>
     <row r="864" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A864" t="s">
-        <v>1730</v>
+        <v>1724</v>
       </c>
       <c r="B864" t="s">
-        <v>1731</v>
+        <v>1725</v>
       </c>
       <c r="C864" s="2" t="s">
         <v>7</v>
@@ -18023,10 +18035,10 @@
     </row>
     <row r="865" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A865" t="s">
-        <v>1732</v>
+        <v>1726</v>
       </c>
       <c r="B865" t="s">
-        <v>1733</v>
+        <v>1727</v>
       </c>
       <c r="C865" s="2" t="s">
         <v>7</v>
@@ -18037,10 +18049,10 @@
     </row>
     <row r="866" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A866" t="s">
-        <v>1734</v>
+        <v>1728</v>
       </c>
       <c r="B866" t="s">
-        <v>1735</v>
+        <v>1729</v>
       </c>
       <c r="C866" s="2" t="s">
         <v>7</v>
@@ -18051,10 +18063,10 @@
     </row>
     <row r="867" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A867" t="s">
-        <v>1736</v>
+        <v>1730</v>
       </c>
       <c r="B867" t="s">
-        <v>1737</v>
+        <v>1731</v>
       </c>
       <c r="C867" s="2" t="s">
         <v>7</v>
@@ -18065,10 +18077,10 @@
     </row>
     <row r="868" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A868" t="s">
-        <v>1738</v>
+        <v>1732</v>
       </c>
       <c r="B868" t="s">
-        <v>1739</v>
+        <v>1733</v>
       </c>
       <c r="C868" s="2" t="s">
         <v>7</v>
@@ -18079,10 +18091,10 @@
     </row>
     <row r="869" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A869" t="s">
-        <v>1740</v>
+        <v>1734</v>
       </c>
       <c r="B869" t="s">
-        <v>1741</v>
+        <v>1735</v>
       </c>
       <c r="C869" s="2" t="s">
         <v>7</v>
@@ -18093,10 +18105,10 @@
     </row>
     <row r="870" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A870" t="s">
-        <v>1742</v>
+        <v>1736</v>
       </c>
       <c r="B870" t="s">
-        <v>1743</v>
+        <v>1737</v>
       </c>
       <c r="C870" s="2" t="s">
         <v>7</v>
@@ -18107,10 +18119,10 @@
     </row>
     <row r="871" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A871" t="s">
-        <v>1744</v>
+        <v>1738</v>
       </c>
       <c r="B871" t="s">
-        <v>1745</v>
+        <v>1739</v>
       </c>
       <c r="C871" s="2" t="s">
         <v>7</v>
@@ -18121,10 +18133,10 @@
     </row>
     <row r="872" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A872" t="s">
-        <v>1746</v>
+        <v>1740</v>
       </c>
       <c r="B872" t="s">
-        <v>1747</v>
+        <v>1741</v>
       </c>
       <c r="C872" s="2" t="s">
         <v>7</v>
@@ -18135,10 +18147,10 @@
     </row>
     <row r="873" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A873" t="s">
-        <v>1748</v>
+        <v>1742</v>
       </c>
       <c r="B873" t="s">
-        <v>1749</v>
+        <v>1743</v>
       </c>
       <c r="C873" s="2" t="s">
         <v>7</v>
@@ -18149,10 +18161,10 @@
     </row>
     <row r="874" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A874" t="s">
-        <v>1750</v>
+        <v>1744</v>
       </c>
       <c r="B874" t="s">
-        <v>1751</v>
+        <v>1745</v>
       </c>
       <c r="C874" s="2" t="s">
         <v>7</v>
@@ -18163,10 +18175,10 @@
     </row>
     <row r="875" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A875" t="s">
-        <v>1754</v>
+        <v>1746</v>
       </c>
       <c r="B875" t="s">
-        <v>1755</v>
+        <v>1747</v>
       </c>
       <c r="C875" s="2" t="s">
         <v>7</v>
@@ -18177,10 +18189,10 @@
     </row>
     <row r="876" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A876" t="s">
-        <v>1756</v>
+        <v>1748</v>
       </c>
       <c r="B876" t="s">
-        <v>1757</v>
+        <v>1749</v>
       </c>
       <c r="C876" s="2" t="s">
         <v>7</v>
@@ -18191,10 +18203,10 @@
     </row>
     <row r="877" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A877" t="s">
-        <v>1758</v>
+        <v>1750</v>
       </c>
       <c r="B877" t="s">
-        <v>1759</v>
+        <v>1751</v>
       </c>
       <c r="C877" s="2" t="s">
         <v>7</v>
@@ -18205,10 +18217,10 @@
     </row>
     <row r="878" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A878" t="s">
-        <v>1760</v>
+        <v>1752</v>
       </c>
       <c r="B878" t="s">
-        <v>1761</v>
+        <v>1753</v>
       </c>
       <c r="C878" s="2" t="s">
         <v>7</v>
@@ -18219,10 +18231,10 @@
     </row>
     <row r="879" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A879" t="s">
-        <v>1762</v>
+        <v>1754</v>
       </c>
       <c r="B879" t="s">
-        <v>1763</v>
+        <v>1755</v>
       </c>
       <c r="C879" s="2" t="s">
         <v>7</v>
@@ -18233,10 +18245,10 @@
     </row>
     <row r="880" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A880" t="s">
-        <v>1766</v>
+        <v>1758</v>
       </c>
       <c r="B880" t="s">
-        <v>1767</v>
+        <v>1759</v>
       </c>
       <c r="C880" s="2" t="s">
         <v>7</v>
@@ -18247,10 +18259,10 @@
     </row>
     <row r="881" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A881" t="s">
-        <v>1768</v>
+        <v>1760</v>
       </c>
       <c r="B881" t="s">
-        <v>1769</v>
+        <v>1761</v>
       </c>
       <c r="C881" s="2" t="s">
         <v>7</v>
@@ -18261,10 +18273,10 @@
     </row>
     <row r="882" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A882" t="s">
-        <v>1770</v>
+        <v>1762</v>
       </c>
       <c r="B882" t="s">
-        <v>1771</v>
+        <v>1763</v>
       </c>
       <c r="C882" s="2" t="s">
         <v>7</v>
@@ -18275,10 +18287,10 @@
     </row>
     <row r="883" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A883" t="s">
-        <v>1774</v>
+        <v>1764</v>
       </c>
       <c r="B883" t="s">
-        <v>1775</v>
+        <v>1765</v>
       </c>
       <c r="C883" s="2" t="s">
         <v>7</v>
@@ -18289,10 +18301,10 @@
     </row>
     <row r="884" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A884" t="s">
-        <v>1776</v>
+        <v>1766</v>
       </c>
       <c r="B884" t="s">
-        <v>1777</v>
+        <v>1767</v>
       </c>
       <c r="C884" s="2" t="s">
         <v>7</v>
@@ -18303,10 +18315,10 @@
     </row>
     <row r="885" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A885" t="s">
-        <v>1778</v>
+        <v>1770</v>
       </c>
       <c r="B885" t="s">
-        <v>1779</v>
+        <v>1771</v>
       </c>
       <c r="C885" s="2" t="s">
         <v>7</v>
@@ -18317,10 +18329,10 @@
     </row>
     <row r="886" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A886" t="s">
-        <v>1780</v>
+        <v>1772</v>
       </c>
       <c r="B886" t="s">
-        <v>1781</v>
+        <v>1773</v>
       </c>
       <c r="C886" s="2" t="s">
         <v>7</v>
@@ -18331,10 +18343,10 @@
     </row>
     <row r="887" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A887" t="s">
-        <v>1782</v>
+        <v>1774</v>
       </c>
       <c r="B887" t="s">
-        <v>1783</v>
+        <v>1775</v>
       </c>
       <c r="C887" s="2" t="s">
         <v>7</v>
@@ -18345,10 +18357,10 @@
     </row>
     <row r="888" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A888" t="s">
-        <v>1784</v>
+        <v>1778</v>
       </c>
       <c r="B888" t="s">
-        <v>1785</v>
+        <v>1779</v>
       </c>
       <c r="C888" s="2" t="s">
         <v>7</v>
@@ -18359,10 +18371,10 @@
     </row>
     <row r="889" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A889" t="s">
-        <v>1786</v>
+        <v>1780</v>
       </c>
       <c r="B889" t="s">
-        <v>1787</v>
+        <v>1781</v>
       </c>
       <c r="C889" s="2" t="s">
         <v>7</v>
@@ -18373,10 +18385,10 @@
     </row>
     <row r="890" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A890" t="s">
-        <v>1788</v>
+        <v>1782</v>
       </c>
       <c r="B890" t="s">
-        <v>1789</v>
+        <v>1783</v>
       </c>
       <c r="C890" s="2" t="s">
         <v>7</v>
@@ -18387,10 +18399,10 @@
     </row>
     <row r="891" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A891" t="s">
-        <v>1790</v>
+        <v>1784</v>
       </c>
       <c r="B891" t="s">
-        <v>1791</v>
+        <v>1785</v>
       </c>
       <c r="C891" s="2" t="s">
         <v>7</v>
@@ -18401,10 +18413,10 @@
     </row>
     <row r="892" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A892" t="s">
-        <v>1792</v>
+        <v>1786</v>
       </c>
       <c r="B892" t="s">
-        <v>1793</v>
+        <v>1787</v>
       </c>
       <c r="C892" s="2" t="s">
         <v>7</v>
@@ -18415,10 +18427,10 @@
     </row>
     <row r="893" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A893" t="s">
-        <v>1794</v>
+        <v>1788</v>
       </c>
       <c r="B893" t="s">
-        <v>1795</v>
+        <v>1789</v>
       </c>
       <c r="C893" s="2" t="s">
         <v>7</v>
@@ -18429,10 +18441,10 @@
     </row>
     <row r="894" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A894" t="s">
-        <v>1796</v>
+        <v>1790</v>
       </c>
       <c r="B894" t="s">
-        <v>1797</v>
+        <v>1791</v>
       </c>
       <c r="C894" s="2" t="s">
         <v>7</v>
@@ -18443,10 +18455,10 @@
     </row>
     <row r="895" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A895" t="s">
-        <v>1798</v>
+        <v>1792</v>
       </c>
       <c r="B895" t="s">
-        <v>1799</v>
+        <v>1793</v>
       </c>
       <c r="C895" s="2" t="s">
         <v>7</v>
@@ -18457,10 +18469,10 @@
     </row>
     <row r="896" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A896" t="s">
-        <v>1802</v>
+        <v>1794</v>
       </c>
       <c r="B896" t="s">
-        <v>1803</v>
+        <v>1795</v>
       </c>
       <c r="C896" s="2" t="s">
         <v>7</v>
@@ -18471,10 +18483,10 @@
     </row>
     <row r="897" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A897" t="s">
-        <v>1804</v>
+        <v>1796</v>
       </c>
       <c r="B897" t="s">
-        <v>1805</v>
+        <v>1797</v>
       </c>
       <c r="C897" s="2" t="s">
         <v>7</v>
@@ -18485,10 +18497,10 @@
     </row>
     <row r="898" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A898" t="s">
-        <v>1806</v>
+        <v>1798</v>
       </c>
       <c r="B898" t="s">
-        <v>1807</v>
+        <v>1799</v>
       </c>
       <c r="C898" s="2" t="s">
         <v>7</v>
@@ -18499,10 +18511,10 @@
     </row>
     <row r="899" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A899" t="s">
-        <v>1808</v>
+        <v>1800</v>
       </c>
       <c r="B899" t="s">
-        <v>1809</v>
+        <v>1801</v>
       </c>
       <c r="C899" s="2" t="s">
         <v>7</v>
@@ -18513,10 +18525,10 @@
     </row>
     <row r="900" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A900" t="s">
-        <v>1810</v>
+        <v>1802</v>
       </c>
       <c r="B900" t="s">
-        <v>1811</v>
+        <v>1803</v>
       </c>
       <c r="C900" s="2" t="s">
         <v>7</v>
@@ -18527,10 +18539,10 @@
     </row>
     <row r="901" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A901" t="s">
-        <v>1812</v>
+        <v>1806</v>
       </c>
       <c r="B901" t="s">
-        <v>1813</v>
+        <v>1807</v>
       </c>
       <c r="C901" s="2" t="s">
         <v>7</v>
@@ -18541,10 +18553,10 @@
     </row>
     <row r="902" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A902" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
       <c r="B902" t="s">
-        <v>1815</v>
+        <v>1809</v>
       </c>
       <c r="C902" s="2" t="s">
         <v>7</v>
@@ -18555,10 +18567,10 @@
     </row>
     <row r="903" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A903" t="s">
-        <v>1816</v>
+        <v>1810</v>
       </c>
       <c r="B903" t="s">
-        <v>1817</v>
+        <v>1811</v>
       </c>
       <c r="C903" s="2" t="s">
         <v>7</v>
@@ -18569,10 +18581,10 @@
     </row>
     <row r="904" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A904" t="s">
-        <v>1818</v>
+        <v>1812</v>
       </c>
       <c r="B904" t="s">
-        <v>1819</v>
+        <v>1813</v>
       </c>
       <c r="C904" s="2" t="s">
         <v>7</v>
@@ -18583,10 +18595,10 @@
     </row>
     <row r="905" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A905" t="s">
-        <v>1820</v>
+        <v>1814</v>
       </c>
       <c r="B905" t="s">
-        <v>1821</v>
+        <v>1815</v>
       </c>
       <c r="C905" s="2" t="s">
         <v>7</v>
@@ -18597,10 +18609,10 @@
     </row>
     <row r="906" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A906" t="s">
-        <v>1822</v>
+        <v>1816</v>
       </c>
       <c r="B906" t="s">
-        <v>1823</v>
+        <v>1817</v>
       </c>
       <c r="C906" s="2" t="s">
         <v>7</v>
@@ -18611,10 +18623,10 @@
     </row>
     <row r="907" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A907" t="s">
-        <v>1824</v>
+        <v>1818</v>
       </c>
       <c r="B907" t="s">
-        <v>1825</v>
+        <v>1819</v>
       </c>
       <c r="C907" s="2" t="s">
         <v>7</v>
@@ -18625,10 +18637,10 @@
     </row>
     <row r="908" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A908" t="s">
-        <v>548</v>
+        <v>1820</v>
       </c>
       <c r="B908" t="s">
-        <v>549</v>
+        <v>1821</v>
       </c>
       <c r="C908" s="2" t="s">
         <v>7</v>
@@ -18639,10 +18651,10 @@
     </row>
     <row r="909" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A909" t="s">
-        <v>800</v>
+        <v>1822</v>
       </c>
       <c r="B909" t="s">
-        <v>801</v>
+        <v>1823</v>
       </c>
       <c r="C909" s="2" t="s">
         <v>7</v>
@@ -18653,10 +18665,10 @@
     </row>
     <row r="910" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A910" t="s">
-        <v>876</v>
+        <v>1824</v>
       </c>
       <c r="B910" t="s">
-        <v>877</v>
+        <v>1825</v>
       </c>
       <c r="C910" s="2" t="s">
         <v>7</v>
@@ -18667,10 +18679,10 @@
     </row>
     <row r="911" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A911" t="s">
-        <v>958</v>
+        <v>1826</v>
       </c>
       <c r="B911" t="s">
-        <v>959</v>
+        <v>1827</v>
       </c>
       <c r="C911" s="2" t="s">
         <v>7</v>
@@ -18681,26 +18693,54 @@
     </row>
     <row r="912" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A912" t="s">
-        <v>1690</v>
+        <v>1828</v>
       </c>
       <c r="B912" t="s">
-        <v>1691</v>
+        <v>1829</v>
       </c>
       <c r="C912" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D912" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="913" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A913" t="s">
+        <v>878</v>
+      </c>
+      <c r="B913" t="s">
+        <v>879</v>
+      </c>
+      <c r="C913" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D913" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="914" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A914" t="s">
+        <v>964</v>
+      </c>
+      <c r="B914" t="s">
+        <v>965</v>
+      </c>
+      <c r="C914" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D914" t="s">
         <v>8</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F912">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F914">
       <sortCondition ref="E1"/>
     </sortState>
   </autoFilter>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="D2:E912" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D2:E914" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"X"</formula1>
     </dataValidation>
   </dataValidations>
@@ -18977,645 +19017,647 @@
     <hyperlink ref="C310" r:id="rId270" xr:uid="{00000000-0004-0000-0000-00000D010000}"/>
     <hyperlink ref="C25" r:id="rId271" xr:uid="{00000000-0004-0000-0000-00000E010000}"/>
     <hyperlink ref="C311" r:id="rId272" xr:uid="{00000000-0004-0000-0000-00000F010000}"/>
-    <hyperlink ref="C908" r:id="rId273" xr:uid="{00000000-0004-0000-0000-000010010000}"/>
-    <hyperlink ref="C312" r:id="rId274" xr:uid="{00000000-0004-0000-0000-000011010000}"/>
-    <hyperlink ref="C313" r:id="rId275" xr:uid="{00000000-0004-0000-0000-000012010000}"/>
-    <hyperlink ref="C314" r:id="rId276" xr:uid="{00000000-0004-0000-0000-000013010000}"/>
-    <hyperlink ref="C315" r:id="rId277" xr:uid="{00000000-0004-0000-0000-000014010000}"/>
-    <hyperlink ref="C316" r:id="rId278" xr:uid="{00000000-0004-0000-0000-000015010000}"/>
+    <hyperlink ref="C312" r:id="rId273" xr:uid="{00000000-0004-0000-0000-000010010000}"/>
+    <hyperlink ref="C313" r:id="rId274" xr:uid="{00000000-0004-0000-0000-000011010000}"/>
+    <hyperlink ref="C314" r:id="rId275" xr:uid="{00000000-0004-0000-0000-000012010000}"/>
+    <hyperlink ref="C315" r:id="rId276" xr:uid="{00000000-0004-0000-0000-000013010000}"/>
+    <hyperlink ref="C316" r:id="rId277" xr:uid="{00000000-0004-0000-0000-000014010000}"/>
+    <hyperlink ref="C317" r:id="rId278" xr:uid="{00000000-0004-0000-0000-000015010000}"/>
     <hyperlink ref="C26" r:id="rId279" xr:uid="{00000000-0004-0000-0000-000016010000}"/>
-    <hyperlink ref="C317" r:id="rId280" xr:uid="{00000000-0004-0000-0000-000017010000}"/>
-    <hyperlink ref="C318" r:id="rId281" xr:uid="{00000000-0004-0000-0000-000018010000}"/>
-    <hyperlink ref="C319" r:id="rId282" xr:uid="{00000000-0004-0000-0000-000019010000}"/>
-    <hyperlink ref="C320" r:id="rId283" xr:uid="{00000000-0004-0000-0000-00001A010000}"/>
-    <hyperlink ref="C321" r:id="rId284" xr:uid="{00000000-0004-0000-0000-00001B010000}"/>
-    <hyperlink ref="C322" r:id="rId285" xr:uid="{00000000-0004-0000-0000-00001C010000}"/>
-    <hyperlink ref="C323" r:id="rId286" xr:uid="{00000000-0004-0000-0000-00001D010000}"/>
-    <hyperlink ref="C324" r:id="rId287" xr:uid="{00000000-0004-0000-0000-00001E010000}"/>
-    <hyperlink ref="C325" r:id="rId288" xr:uid="{00000000-0004-0000-0000-00001F010000}"/>
+    <hyperlink ref="C318" r:id="rId280" xr:uid="{00000000-0004-0000-0000-000017010000}"/>
+    <hyperlink ref="C319" r:id="rId281" xr:uid="{00000000-0004-0000-0000-000018010000}"/>
+    <hyperlink ref="C320" r:id="rId282" xr:uid="{00000000-0004-0000-0000-000019010000}"/>
+    <hyperlink ref="C321" r:id="rId283" xr:uid="{00000000-0004-0000-0000-00001A010000}"/>
+    <hyperlink ref="C322" r:id="rId284" xr:uid="{00000000-0004-0000-0000-00001B010000}"/>
+    <hyperlink ref="C323" r:id="rId285" xr:uid="{00000000-0004-0000-0000-00001C010000}"/>
+    <hyperlink ref="C324" r:id="rId286" xr:uid="{00000000-0004-0000-0000-00001D010000}"/>
+    <hyperlink ref="C325" r:id="rId287" xr:uid="{00000000-0004-0000-0000-00001E010000}"/>
+    <hyperlink ref="C326" r:id="rId288" xr:uid="{00000000-0004-0000-0000-00001F010000}"/>
     <hyperlink ref="C27" r:id="rId289" xr:uid="{00000000-0004-0000-0000-000020010000}"/>
-    <hyperlink ref="C326" r:id="rId290" xr:uid="{00000000-0004-0000-0000-000021010000}"/>
+    <hyperlink ref="C327" r:id="rId290" xr:uid="{00000000-0004-0000-0000-000021010000}"/>
     <hyperlink ref="C28" r:id="rId291" xr:uid="{00000000-0004-0000-0000-000022010000}"/>
-    <hyperlink ref="C327" r:id="rId292" xr:uid="{00000000-0004-0000-0000-000023010000}"/>
-    <hyperlink ref="C328" r:id="rId293" xr:uid="{00000000-0004-0000-0000-000024010000}"/>
-    <hyperlink ref="C329" r:id="rId294" xr:uid="{00000000-0004-0000-0000-000025010000}"/>
-    <hyperlink ref="C330" r:id="rId295" xr:uid="{00000000-0004-0000-0000-000026010000}"/>
-    <hyperlink ref="C331" r:id="rId296" xr:uid="{00000000-0004-0000-0000-000027010000}"/>
-    <hyperlink ref="C332" r:id="rId297" xr:uid="{00000000-0004-0000-0000-000028010000}"/>
-    <hyperlink ref="C333" r:id="rId298" xr:uid="{00000000-0004-0000-0000-000029010000}"/>
-    <hyperlink ref="C334" r:id="rId299" xr:uid="{00000000-0004-0000-0000-00002A010000}"/>
-    <hyperlink ref="C335" r:id="rId300" xr:uid="{00000000-0004-0000-0000-00002B010000}"/>
-    <hyperlink ref="C336" r:id="rId301" xr:uid="{00000000-0004-0000-0000-00002C010000}"/>
-    <hyperlink ref="C337" r:id="rId302" xr:uid="{00000000-0004-0000-0000-00002D010000}"/>
-    <hyperlink ref="C338" r:id="rId303" xr:uid="{00000000-0004-0000-0000-00002E010000}"/>
-    <hyperlink ref="C339" r:id="rId304" xr:uid="{00000000-0004-0000-0000-00002F010000}"/>
-    <hyperlink ref="C340" r:id="rId305" xr:uid="{00000000-0004-0000-0000-000030010000}"/>
-    <hyperlink ref="C341" r:id="rId306" xr:uid="{00000000-0004-0000-0000-000031010000}"/>
-    <hyperlink ref="C342" r:id="rId307" xr:uid="{00000000-0004-0000-0000-000032010000}"/>
-    <hyperlink ref="C343" r:id="rId308" xr:uid="{00000000-0004-0000-0000-000033010000}"/>
-    <hyperlink ref="C344" r:id="rId309" xr:uid="{00000000-0004-0000-0000-000034010000}"/>
-    <hyperlink ref="C345" r:id="rId310" xr:uid="{00000000-0004-0000-0000-000035010000}"/>
+    <hyperlink ref="C328" r:id="rId292" xr:uid="{00000000-0004-0000-0000-000023010000}"/>
+    <hyperlink ref="C329" r:id="rId293" xr:uid="{00000000-0004-0000-0000-000024010000}"/>
+    <hyperlink ref="C330" r:id="rId294" xr:uid="{00000000-0004-0000-0000-000025010000}"/>
+    <hyperlink ref="C331" r:id="rId295" xr:uid="{00000000-0004-0000-0000-000026010000}"/>
+    <hyperlink ref="C332" r:id="rId296" xr:uid="{00000000-0004-0000-0000-000027010000}"/>
+    <hyperlink ref="C333" r:id="rId297" xr:uid="{00000000-0004-0000-0000-000028010000}"/>
+    <hyperlink ref="C334" r:id="rId298" xr:uid="{00000000-0004-0000-0000-000029010000}"/>
+    <hyperlink ref="C335" r:id="rId299" xr:uid="{00000000-0004-0000-0000-00002A010000}"/>
+    <hyperlink ref="C336" r:id="rId300" xr:uid="{00000000-0004-0000-0000-00002B010000}"/>
+    <hyperlink ref="C337" r:id="rId301" xr:uid="{00000000-0004-0000-0000-00002C010000}"/>
+    <hyperlink ref="C338" r:id="rId302" xr:uid="{00000000-0004-0000-0000-00002D010000}"/>
+    <hyperlink ref="C339" r:id="rId303" xr:uid="{00000000-0004-0000-0000-00002E010000}"/>
+    <hyperlink ref="C340" r:id="rId304" xr:uid="{00000000-0004-0000-0000-00002F010000}"/>
+    <hyperlink ref="C341" r:id="rId305" xr:uid="{00000000-0004-0000-0000-000030010000}"/>
+    <hyperlink ref="C342" r:id="rId306" xr:uid="{00000000-0004-0000-0000-000031010000}"/>
+    <hyperlink ref="C343" r:id="rId307" xr:uid="{00000000-0004-0000-0000-000032010000}"/>
+    <hyperlink ref="C344" r:id="rId308" xr:uid="{00000000-0004-0000-0000-000033010000}"/>
+    <hyperlink ref="C345" r:id="rId309" xr:uid="{00000000-0004-0000-0000-000034010000}"/>
+    <hyperlink ref="C346" r:id="rId310" xr:uid="{00000000-0004-0000-0000-000035010000}"/>
     <hyperlink ref="C29" r:id="rId311" xr:uid="{00000000-0004-0000-0000-000036010000}"/>
-    <hyperlink ref="C346" r:id="rId312" xr:uid="{00000000-0004-0000-0000-000037010000}"/>
-    <hyperlink ref="C347" r:id="rId313" xr:uid="{00000000-0004-0000-0000-000038010000}"/>
-    <hyperlink ref="C348" r:id="rId314" xr:uid="{00000000-0004-0000-0000-000039010000}"/>
-    <hyperlink ref="C349" r:id="rId315" xr:uid="{00000000-0004-0000-0000-00003A010000}"/>
-    <hyperlink ref="C350" r:id="rId316" xr:uid="{00000000-0004-0000-0000-00003B010000}"/>
-    <hyperlink ref="C351" r:id="rId317" xr:uid="{00000000-0004-0000-0000-00003C010000}"/>
-    <hyperlink ref="C352" r:id="rId318" xr:uid="{00000000-0004-0000-0000-00003D010000}"/>
-    <hyperlink ref="C353" r:id="rId319" xr:uid="{00000000-0004-0000-0000-00003E010000}"/>
-    <hyperlink ref="C354" r:id="rId320" xr:uid="{00000000-0004-0000-0000-00003F010000}"/>
+    <hyperlink ref="C347" r:id="rId312" xr:uid="{00000000-0004-0000-0000-000037010000}"/>
+    <hyperlink ref="C348" r:id="rId313" xr:uid="{00000000-0004-0000-0000-000038010000}"/>
+    <hyperlink ref="C349" r:id="rId314" xr:uid="{00000000-0004-0000-0000-000039010000}"/>
+    <hyperlink ref="C350" r:id="rId315" xr:uid="{00000000-0004-0000-0000-00003A010000}"/>
+    <hyperlink ref="C351" r:id="rId316" xr:uid="{00000000-0004-0000-0000-00003B010000}"/>
+    <hyperlink ref="C352" r:id="rId317" xr:uid="{00000000-0004-0000-0000-00003C010000}"/>
+    <hyperlink ref="C353" r:id="rId318" xr:uid="{00000000-0004-0000-0000-00003D010000}"/>
+    <hyperlink ref="C354" r:id="rId319" xr:uid="{00000000-0004-0000-0000-00003E010000}"/>
+    <hyperlink ref="C355" r:id="rId320" xr:uid="{00000000-0004-0000-0000-00003F010000}"/>
     <hyperlink ref="C30" r:id="rId321" xr:uid="{00000000-0004-0000-0000-000040010000}"/>
-    <hyperlink ref="C355" r:id="rId322" xr:uid="{00000000-0004-0000-0000-000041010000}"/>
-    <hyperlink ref="C356" r:id="rId323" xr:uid="{00000000-0004-0000-0000-000042010000}"/>
-    <hyperlink ref="C357" r:id="rId324" xr:uid="{00000000-0004-0000-0000-000043010000}"/>
-    <hyperlink ref="C358" r:id="rId325" xr:uid="{00000000-0004-0000-0000-000044010000}"/>
-    <hyperlink ref="C359" r:id="rId326" xr:uid="{00000000-0004-0000-0000-000045010000}"/>
-    <hyperlink ref="C360" r:id="rId327" xr:uid="{00000000-0004-0000-0000-000046010000}"/>
-    <hyperlink ref="C361" r:id="rId328" xr:uid="{00000000-0004-0000-0000-000047010000}"/>
-    <hyperlink ref="C362" r:id="rId329" xr:uid="{00000000-0004-0000-0000-000048010000}"/>
-    <hyperlink ref="C363" r:id="rId330" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
-    <hyperlink ref="C364" r:id="rId331" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
-    <hyperlink ref="C365" r:id="rId332" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
-    <hyperlink ref="C366" r:id="rId333" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
-    <hyperlink ref="C367" r:id="rId334" xr:uid="{00000000-0004-0000-0000-00004D010000}"/>
-    <hyperlink ref="C368" r:id="rId335" xr:uid="{00000000-0004-0000-0000-00004E010000}"/>
-    <hyperlink ref="C369" r:id="rId336" xr:uid="{00000000-0004-0000-0000-00004F010000}"/>
-    <hyperlink ref="C370" r:id="rId337" xr:uid="{00000000-0004-0000-0000-000050010000}"/>
-    <hyperlink ref="C371" r:id="rId338" xr:uid="{00000000-0004-0000-0000-000051010000}"/>
-    <hyperlink ref="C372" r:id="rId339" xr:uid="{00000000-0004-0000-0000-000052010000}"/>
-    <hyperlink ref="C373" r:id="rId340" xr:uid="{00000000-0004-0000-0000-000053010000}"/>
-    <hyperlink ref="C374" r:id="rId341" xr:uid="{00000000-0004-0000-0000-000054010000}"/>
-    <hyperlink ref="C375" r:id="rId342" xr:uid="{00000000-0004-0000-0000-000055010000}"/>
-    <hyperlink ref="C376" r:id="rId343" xr:uid="{00000000-0004-0000-0000-000056010000}"/>
-    <hyperlink ref="C377" r:id="rId344" xr:uid="{00000000-0004-0000-0000-000057010000}"/>
-    <hyperlink ref="C378" r:id="rId345" xr:uid="{00000000-0004-0000-0000-000058010000}"/>
-    <hyperlink ref="C379" r:id="rId346" xr:uid="{00000000-0004-0000-0000-000059010000}"/>
-    <hyperlink ref="C380" r:id="rId347" xr:uid="{00000000-0004-0000-0000-00005A010000}"/>
-    <hyperlink ref="C381" r:id="rId348" xr:uid="{00000000-0004-0000-0000-00005B010000}"/>
-    <hyperlink ref="C382" r:id="rId349" xr:uid="{00000000-0004-0000-0000-00005C010000}"/>
-    <hyperlink ref="C383" r:id="rId350" xr:uid="{00000000-0004-0000-0000-00005D010000}"/>
-    <hyperlink ref="C384" r:id="rId351" xr:uid="{00000000-0004-0000-0000-00005E010000}"/>
+    <hyperlink ref="C356" r:id="rId322" xr:uid="{00000000-0004-0000-0000-000041010000}"/>
+    <hyperlink ref="C357" r:id="rId323" xr:uid="{00000000-0004-0000-0000-000042010000}"/>
+    <hyperlink ref="C358" r:id="rId324" xr:uid="{00000000-0004-0000-0000-000043010000}"/>
+    <hyperlink ref="C359" r:id="rId325" xr:uid="{00000000-0004-0000-0000-000044010000}"/>
+    <hyperlink ref="C360" r:id="rId326" xr:uid="{00000000-0004-0000-0000-000045010000}"/>
+    <hyperlink ref="C361" r:id="rId327" xr:uid="{00000000-0004-0000-0000-000046010000}"/>
+    <hyperlink ref="C362" r:id="rId328" xr:uid="{00000000-0004-0000-0000-000047010000}"/>
+    <hyperlink ref="C363" r:id="rId329" xr:uid="{00000000-0004-0000-0000-000048010000}"/>
+    <hyperlink ref="C364" r:id="rId330" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
+    <hyperlink ref="C365" r:id="rId331" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
+    <hyperlink ref="C366" r:id="rId332" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
+    <hyperlink ref="C367" r:id="rId333" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
+    <hyperlink ref="C368" r:id="rId334" xr:uid="{00000000-0004-0000-0000-00004D010000}"/>
+    <hyperlink ref="C369" r:id="rId335" xr:uid="{00000000-0004-0000-0000-00004E010000}"/>
+    <hyperlink ref="C370" r:id="rId336" xr:uid="{00000000-0004-0000-0000-00004F010000}"/>
+    <hyperlink ref="C371" r:id="rId337" xr:uid="{00000000-0004-0000-0000-000050010000}"/>
+    <hyperlink ref="C372" r:id="rId338" xr:uid="{00000000-0004-0000-0000-000051010000}"/>
+    <hyperlink ref="C373" r:id="rId339" xr:uid="{00000000-0004-0000-0000-000052010000}"/>
+    <hyperlink ref="C374" r:id="rId340" xr:uid="{00000000-0004-0000-0000-000053010000}"/>
+    <hyperlink ref="C375" r:id="rId341" xr:uid="{00000000-0004-0000-0000-000054010000}"/>
+    <hyperlink ref="C376" r:id="rId342" xr:uid="{00000000-0004-0000-0000-000055010000}"/>
+    <hyperlink ref="C377" r:id="rId343" xr:uid="{00000000-0004-0000-0000-000056010000}"/>
+    <hyperlink ref="C378" r:id="rId344" xr:uid="{00000000-0004-0000-0000-000057010000}"/>
+    <hyperlink ref="C379" r:id="rId345" xr:uid="{00000000-0004-0000-0000-000058010000}"/>
+    <hyperlink ref="C380" r:id="rId346" xr:uid="{00000000-0004-0000-0000-000059010000}"/>
+    <hyperlink ref="C381" r:id="rId347" xr:uid="{00000000-0004-0000-0000-00005A010000}"/>
+    <hyperlink ref="C382" r:id="rId348" xr:uid="{00000000-0004-0000-0000-00005B010000}"/>
+    <hyperlink ref="C383" r:id="rId349" xr:uid="{00000000-0004-0000-0000-00005C010000}"/>
+    <hyperlink ref="C384" r:id="rId350" xr:uid="{00000000-0004-0000-0000-00005D010000}"/>
+    <hyperlink ref="C385" r:id="rId351" xr:uid="{00000000-0004-0000-0000-00005E010000}"/>
     <hyperlink ref="C31" r:id="rId352" xr:uid="{00000000-0004-0000-0000-00005F010000}"/>
     <hyperlink ref="C32" r:id="rId353" xr:uid="{00000000-0004-0000-0000-000060010000}"/>
-    <hyperlink ref="C385" r:id="rId354" xr:uid="{00000000-0004-0000-0000-000061010000}"/>
-    <hyperlink ref="C386" r:id="rId355" xr:uid="{00000000-0004-0000-0000-000062010000}"/>
-    <hyperlink ref="C387" r:id="rId356" xr:uid="{00000000-0004-0000-0000-000063010000}"/>
-    <hyperlink ref="C388" r:id="rId357" xr:uid="{00000000-0004-0000-0000-000064010000}"/>
-    <hyperlink ref="C389" r:id="rId358" xr:uid="{00000000-0004-0000-0000-000065010000}"/>
+    <hyperlink ref="C386" r:id="rId354" xr:uid="{00000000-0004-0000-0000-000061010000}"/>
+    <hyperlink ref="C387" r:id="rId355" xr:uid="{00000000-0004-0000-0000-000062010000}"/>
+    <hyperlink ref="C388" r:id="rId356" xr:uid="{00000000-0004-0000-0000-000063010000}"/>
+    <hyperlink ref="C389" r:id="rId357" xr:uid="{00000000-0004-0000-0000-000064010000}"/>
+    <hyperlink ref="C390" r:id="rId358" xr:uid="{00000000-0004-0000-0000-000065010000}"/>
     <hyperlink ref="C33" r:id="rId359" xr:uid="{00000000-0004-0000-0000-000066010000}"/>
-    <hyperlink ref="C390" r:id="rId360" xr:uid="{00000000-0004-0000-0000-000067010000}"/>
-    <hyperlink ref="C391" r:id="rId361" xr:uid="{00000000-0004-0000-0000-000068010000}"/>
-    <hyperlink ref="C392" r:id="rId362" xr:uid="{00000000-0004-0000-0000-000069010000}"/>
-    <hyperlink ref="C393" r:id="rId363" xr:uid="{00000000-0004-0000-0000-00006A010000}"/>
-    <hyperlink ref="C394" r:id="rId364" xr:uid="{00000000-0004-0000-0000-00006B010000}"/>
-    <hyperlink ref="C395" r:id="rId365" xr:uid="{00000000-0004-0000-0000-00006C010000}"/>
-    <hyperlink ref="C396" r:id="rId366" xr:uid="{00000000-0004-0000-0000-00006D010000}"/>
-    <hyperlink ref="C397" r:id="rId367" xr:uid="{00000000-0004-0000-0000-00006E010000}"/>
-    <hyperlink ref="C398" r:id="rId368" xr:uid="{00000000-0004-0000-0000-00006F010000}"/>
-    <hyperlink ref="C399" r:id="rId369" xr:uid="{00000000-0004-0000-0000-000070010000}"/>
-    <hyperlink ref="C400" r:id="rId370" xr:uid="{00000000-0004-0000-0000-000071010000}"/>
-    <hyperlink ref="C401" r:id="rId371" xr:uid="{00000000-0004-0000-0000-000072010000}"/>
-    <hyperlink ref="C402" r:id="rId372" xr:uid="{00000000-0004-0000-0000-000073010000}"/>
-    <hyperlink ref="C403" r:id="rId373" xr:uid="{00000000-0004-0000-0000-000074010000}"/>
-    <hyperlink ref="C404" r:id="rId374" xr:uid="{00000000-0004-0000-0000-000075010000}"/>
-    <hyperlink ref="C405" r:id="rId375" xr:uid="{00000000-0004-0000-0000-000076010000}"/>
-    <hyperlink ref="C406" r:id="rId376" xr:uid="{00000000-0004-0000-0000-000077010000}"/>
-    <hyperlink ref="C407" r:id="rId377" xr:uid="{00000000-0004-0000-0000-000078010000}"/>
-    <hyperlink ref="C408" r:id="rId378" xr:uid="{00000000-0004-0000-0000-000079010000}"/>
-    <hyperlink ref="C409" r:id="rId379" xr:uid="{00000000-0004-0000-0000-00007A010000}"/>
-    <hyperlink ref="C410" r:id="rId380" xr:uid="{00000000-0004-0000-0000-00007B010000}"/>
-    <hyperlink ref="C411" r:id="rId381" xr:uid="{00000000-0004-0000-0000-00007C010000}"/>
-    <hyperlink ref="C412" r:id="rId382" xr:uid="{00000000-0004-0000-0000-00007D010000}"/>
-    <hyperlink ref="C413" r:id="rId383" xr:uid="{00000000-0004-0000-0000-00007E010000}"/>
-    <hyperlink ref="C414" r:id="rId384" xr:uid="{00000000-0004-0000-0000-00007F010000}"/>
-    <hyperlink ref="C415" r:id="rId385" xr:uid="{00000000-0004-0000-0000-000080010000}"/>
-    <hyperlink ref="C416" r:id="rId386" xr:uid="{00000000-0004-0000-0000-000081010000}"/>
-    <hyperlink ref="C417" r:id="rId387" xr:uid="{00000000-0004-0000-0000-000082010000}"/>
-    <hyperlink ref="C418" r:id="rId388" xr:uid="{00000000-0004-0000-0000-000083010000}"/>
-    <hyperlink ref="C419" r:id="rId389" xr:uid="{00000000-0004-0000-0000-000084010000}"/>
-    <hyperlink ref="C420" r:id="rId390" xr:uid="{00000000-0004-0000-0000-000085010000}"/>
-    <hyperlink ref="C421" r:id="rId391" xr:uid="{00000000-0004-0000-0000-000086010000}"/>
-    <hyperlink ref="C422" r:id="rId392" xr:uid="{00000000-0004-0000-0000-000087010000}"/>
-    <hyperlink ref="C423" r:id="rId393" xr:uid="{00000000-0004-0000-0000-000088010000}"/>
-    <hyperlink ref="C424" r:id="rId394" xr:uid="{00000000-0004-0000-0000-000089010000}"/>
-    <hyperlink ref="C425" r:id="rId395" xr:uid="{00000000-0004-0000-0000-00008A010000}"/>
-    <hyperlink ref="C426" r:id="rId396" xr:uid="{00000000-0004-0000-0000-00008B010000}"/>
-    <hyperlink ref="C427" r:id="rId397" xr:uid="{00000000-0004-0000-0000-00008C010000}"/>
-    <hyperlink ref="C428" r:id="rId398" xr:uid="{00000000-0004-0000-0000-00008D010000}"/>
-    <hyperlink ref="C909" r:id="rId399" xr:uid="{00000000-0004-0000-0000-00008E010000}"/>
-    <hyperlink ref="C429" r:id="rId400" xr:uid="{00000000-0004-0000-0000-00008F010000}"/>
-    <hyperlink ref="C430" r:id="rId401" xr:uid="{00000000-0004-0000-0000-000090010000}"/>
-    <hyperlink ref="C431" r:id="rId402" xr:uid="{00000000-0004-0000-0000-000091010000}"/>
-    <hyperlink ref="C432" r:id="rId403" xr:uid="{00000000-0004-0000-0000-000092010000}"/>
-    <hyperlink ref="C433" r:id="rId404" xr:uid="{00000000-0004-0000-0000-000093010000}"/>
-    <hyperlink ref="C434" r:id="rId405" xr:uid="{00000000-0004-0000-0000-000094010000}"/>
-    <hyperlink ref="C435" r:id="rId406" xr:uid="{00000000-0004-0000-0000-000095010000}"/>
-    <hyperlink ref="C436" r:id="rId407" xr:uid="{00000000-0004-0000-0000-000096010000}"/>
-    <hyperlink ref="C437" r:id="rId408" xr:uid="{00000000-0004-0000-0000-000097010000}"/>
-    <hyperlink ref="C438" r:id="rId409" xr:uid="{00000000-0004-0000-0000-000098010000}"/>
-    <hyperlink ref="C439" r:id="rId410" xr:uid="{00000000-0004-0000-0000-000099010000}"/>
-    <hyperlink ref="C440" r:id="rId411" xr:uid="{00000000-0004-0000-0000-00009A010000}"/>
-    <hyperlink ref="C441" r:id="rId412" xr:uid="{00000000-0004-0000-0000-00009B010000}"/>
-    <hyperlink ref="C442" r:id="rId413" xr:uid="{00000000-0004-0000-0000-00009C010000}"/>
+    <hyperlink ref="C391" r:id="rId360" xr:uid="{00000000-0004-0000-0000-000067010000}"/>
+    <hyperlink ref="C392" r:id="rId361" xr:uid="{00000000-0004-0000-0000-000068010000}"/>
+    <hyperlink ref="C393" r:id="rId362" xr:uid="{00000000-0004-0000-0000-000069010000}"/>
+    <hyperlink ref="C394" r:id="rId363" xr:uid="{00000000-0004-0000-0000-00006A010000}"/>
+    <hyperlink ref="C395" r:id="rId364" xr:uid="{00000000-0004-0000-0000-00006B010000}"/>
+    <hyperlink ref="C396" r:id="rId365" xr:uid="{00000000-0004-0000-0000-00006C010000}"/>
+    <hyperlink ref="C397" r:id="rId366" xr:uid="{00000000-0004-0000-0000-00006D010000}"/>
+    <hyperlink ref="C398" r:id="rId367" xr:uid="{00000000-0004-0000-0000-00006E010000}"/>
+    <hyperlink ref="C399" r:id="rId368" xr:uid="{00000000-0004-0000-0000-00006F010000}"/>
+    <hyperlink ref="C400" r:id="rId369" xr:uid="{00000000-0004-0000-0000-000070010000}"/>
+    <hyperlink ref="C401" r:id="rId370" xr:uid="{00000000-0004-0000-0000-000071010000}"/>
+    <hyperlink ref="C402" r:id="rId371" xr:uid="{00000000-0004-0000-0000-000072010000}"/>
+    <hyperlink ref="C403" r:id="rId372" xr:uid="{00000000-0004-0000-0000-000073010000}"/>
+    <hyperlink ref="C404" r:id="rId373" xr:uid="{00000000-0004-0000-0000-000074010000}"/>
+    <hyperlink ref="C405" r:id="rId374" xr:uid="{00000000-0004-0000-0000-000075010000}"/>
+    <hyperlink ref="C406" r:id="rId375" xr:uid="{00000000-0004-0000-0000-000076010000}"/>
+    <hyperlink ref="C407" r:id="rId376" xr:uid="{00000000-0004-0000-0000-000077010000}"/>
+    <hyperlink ref="C408" r:id="rId377" xr:uid="{00000000-0004-0000-0000-000078010000}"/>
+    <hyperlink ref="C409" r:id="rId378" xr:uid="{00000000-0004-0000-0000-000079010000}"/>
+    <hyperlink ref="C410" r:id="rId379" xr:uid="{00000000-0004-0000-0000-00007A010000}"/>
+    <hyperlink ref="C411" r:id="rId380" xr:uid="{00000000-0004-0000-0000-00007B010000}"/>
+    <hyperlink ref="C412" r:id="rId381" xr:uid="{00000000-0004-0000-0000-00007C010000}"/>
+    <hyperlink ref="C413" r:id="rId382" xr:uid="{00000000-0004-0000-0000-00007D010000}"/>
+    <hyperlink ref="C414" r:id="rId383" xr:uid="{00000000-0004-0000-0000-00007E010000}"/>
+    <hyperlink ref="C415" r:id="rId384" xr:uid="{00000000-0004-0000-0000-00007F010000}"/>
+    <hyperlink ref="C416" r:id="rId385" xr:uid="{00000000-0004-0000-0000-000080010000}"/>
+    <hyperlink ref="C417" r:id="rId386" xr:uid="{00000000-0004-0000-0000-000081010000}"/>
+    <hyperlink ref="C418" r:id="rId387" xr:uid="{00000000-0004-0000-0000-000082010000}"/>
+    <hyperlink ref="C419" r:id="rId388" xr:uid="{00000000-0004-0000-0000-000083010000}"/>
+    <hyperlink ref="C420" r:id="rId389" xr:uid="{00000000-0004-0000-0000-000084010000}"/>
+    <hyperlink ref="C421" r:id="rId390" xr:uid="{00000000-0004-0000-0000-000085010000}"/>
+    <hyperlink ref="C422" r:id="rId391" xr:uid="{00000000-0004-0000-0000-000086010000}"/>
+    <hyperlink ref="C423" r:id="rId392" xr:uid="{00000000-0004-0000-0000-000087010000}"/>
+    <hyperlink ref="C424" r:id="rId393" xr:uid="{00000000-0004-0000-0000-000088010000}"/>
+    <hyperlink ref="C425" r:id="rId394" xr:uid="{00000000-0004-0000-0000-000089010000}"/>
+    <hyperlink ref="C426" r:id="rId395" xr:uid="{00000000-0004-0000-0000-00008A010000}"/>
+    <hyperlink ref="C427" r:id="rId396" xr:uid="{00000000-0004-0000-0000-00008B010000}"/>
+    <hyperlink ref="C428" r:id="rId397" xr:uid="{00000000-0004-0000-0000-00008C010000}"/>
+    <hyperlink ref="C429" r:id="rId398" xr:uid="{00000000-0004-0000-0000-00008D010000}"/>
+    <hyperlink ref="C430" r:id="rId399" xr:uid="{00000000-0004-0000-0000-00008E010000}"/>
+    <hyperlink ref="C431" r:id="rId400" xr:uid="{00000000-0004-0000-0000-00008F010000}"/>
+    <hyperlink ref="C432" r:id="rId401" xr:uid="{00000000-0004-0000-0000-000090010000}"/>
+    <hyperlink ref="C433" r:id="rId402" xr:uid="{00000000-0004-0000-0000-000091010000}"/>
+    <hyperlink ref="C434" r:id="rId403" xr:uid="{00000000-0004-0000-0000-000092010000}"/>
+    <hyperlink ref="C435" r:id="rId404" xr:uid="{00000000-0004-0000-0000-000093010000}"/>
+    <hyperlink ref="C436" r:id="rId405" xr:uid="{00000000-0004-0000-0000-000094010000}"/>
+    <hyperlink ref="C437" r:id="rId406" xr:uid="{00000000-0004-0000-0000-000095010000}"/>
+    <hyperlink ref="C438" r:id="rId407" xr:uid="{00000000-0004-0000-0000-000096010000}"/>
+    <hyperlink ref="C439" r:id="rId408" xr:uid="{00000000-0004-0000-0000-000097010000}"/>
+    <hyperlink ref="C440" r:id="rId409" xr:uid="{00000000-0004-0000-0000-000098010000}"/>
+    <hyperlink ref="C441" r:id="rId410" xr:uid="{00000000-0004-0000-0000-000099010000}"/>
+    <hyperlink ref="C442" r:id="rId411" xr:uid="{00000000-0004-0000-0000-00009A010000}"/>
+    <hyperlink ref="C443" r:id="rId412" xr:uid="{00000000-0004-0000-0000-00009B010000}"/>
+    <hyperlink ref="C444" r:id="rId413" xr:uid="{00000000-0004-0000-0000-00009C010000}"/>
     <hyperlink ref="C34" r:id="rId414" xr:uid="{00000000-0004-0000-0000-00009D010000}"/>
-    <hyperlink ref="C443" r:id="rId415" xr:uid="{00000000-0004-0000-0000-00009E010000}"/>
-    <hyperlink ref="C444" r:id="rId416" xr:uid="{00000000-0004-0000-0000-00009F010000}"/>
-    <hyperlink ref="C445" r:id="rId417" xr:uid="{00000000-0004-0000-0000-0000A0010000}"/>
-    <hyperlink ref="C446" r:id="rId418" xr:uid="{00000000-0004-0000-0000-0000A1010000}"/>
-    <hyperlink ref="C447" r:id="rId419" xr:uid="{00000000-0004-0000-0000-0000A2010000}"/>
-    <hyperlink ref="C448" r:id="rId420" xr:uid="{00000000-0004-0000-0000-0000A3010000}"/>
-    <hyperlink ref="C449" r:id="rId421" xr:uid="{00000000-0004-0000-0000-0000A4010000}"/>
-    <hyperlink ref="C450" r:id="rId422" xr:uid="{00000000-0004-0000-0000-0000A5010000}"/>
-    <hyperlink ref="C451" r:id="rId423" xr:uid="{00000000-0004-0000-0000-0000A6010000}"/>
-    <hyperlink ref="C452" r:id="rId424" xr:uid="{00000000-0004-0000-0000-0000A7010000}"/>
-    <hyperlink ref="C453" r:id="rId425" xr:uid="{00000000-0004-0000-0000-0000A8010000}"/>
-    <hyperlink ref="C454" r:id="rId426" xr:uid="{00000000-0004-0000-0000-0000A9010000}"/>
-    <hyperlink ref="C455" r:id="rId427" xr:uid="{00000000-0004-0000-0000-0000AA010000}"/>
-    <hyperlink ref="C456" r:id="rId428" xr:uid="{00000000-0004-0000-0000-0000AB010000}"/>
-    <hyperlink ref="C457" r:id="rId429" xr:uid="{00000000-0004-0000-0000-0000AC010000}"/>
-    <hyperlink ref="C458" r:id="rId430" xr:uid="{00000000-0004-0000-0000-0000AD010000}"/>
-    <hyperlink ref="C459" r:id="rId431" xr:uid="{00000000-0004-0000-0000-0000AE010000}"/>
-    <hyperlink ref="C460" r:id="rId432" xr:uid="{00000000-0004-0000-0000-0000AF010000}"/>
-    <hyperlink ref="C461" r:id="rId433" xr:uid="{00000000-0004-0000-0000-0000B0010000}"/>
-    <hyperlink ref="C462" r:id="rId434" xr:uid="{00000000-0004-0000-0000-0000B1010000}"/>
-    <hyperlink ref="C463" r:id="rId435" xr:uid="{00000000-0004-0000-0000-0000B2010000}"/>
-    <hyperlink ref="C464" r:id="rId436" xr:uid="{00000000-0004-0000-0000-0000B3010000}"/>
-    <hyperlink ref="C910" r:id="rId437" xr:uid="{00000000-0004-0000-0000-0000B4010000}"/>
-    <hyperlink ref="C465" r:id="rId438" xr:uid="{00000000-0004-0000-0000-0000B5010000}"/>
-    <hyperlink ref="C466" r:id="rId439" xr:uid="{00000000-0004-0000-0000-0000B6010000}"/>
-    <hyperlink ref="C467" r:id="rId440" xr:uid="{00000000-0004-0000-0000-0000B7010000}"/>
-    <hyperlink ref="C468" r:id="rId441" xr:uid="{00000000-0004-0000-0000-0000B8010000}"/>
-    <hyperlink ref="C469" r:id="rId442" xr:uid="{00000000-0004-0000-0000-0000B9010000}"/>
-    <hyperlink ref="C470" r:id="rId443" xr:uid="{00000000-0004-0000-0000-0000BA010000}"/>
-    <hyperlink ref="C471" r:id="rId444" xr:uid="{00000000-0004-0000-0000-0000BB010000}"/>
-    <hyperlink ref="C472" r:id="rId445" xr:uid="{00000000-0004-0000-0000-0000BC010000}"/>
-    <hyperlink ref="C473" r:id="rId446" xr:uid="{00000000-0004-0000-0000-0000BD010000}"/>
-    <hyperlink ref="C474" r:id="rId447" xr:uid="{00000000-0004-0000-0000-0000BE010000}"/>
-    <hyperlink ref="C475" r:id="rId448" xr:uid="{00000000-0004-0000-0000-0000BF010000}"/>
-    <hyperlink ref="C476" r:id="rId449" xr:uid="{00000000-0004-0000-0000-0000C0010000}"/>
-    <hyperlink ref="C477" r:id="rId450" xr:uid="{00000000-0004-0000-0000-0000C1010000}"/>
-    <hyperlink ref="C478" r:id="rId451" xr:uid="{00000000-0004-0000-0000-0000C2010000}"/>
-    <hyperlink ref="C479" r:id="rId452" xr:uid="{00000000-0004-0000-0000-0000C3010000}"/>
-    <hyperlink ref="C480" r:id="rId453" xr:uid="{00000000-0004-0000-0000-0000C4010000}"/>
-    <hyperlink ref="C481" r:id="rId454" xr:uid="{00000000-0004-0000-0000-0000C5010000}"/>
-    <hyperlink ref="C482" r:id="rId455" xr:uid="{00000000-0004-0000-0000-0000C6010000}"/>
-    <hyperlink ref="C483" r:id="rId456" xr:uid="{00000000-0004-0000-0000-0000C7010000}"/>
-    <hyperlink ref="C484" r:id="rId457" xr:uid="{00000000-0004-0000-0000-0000C8010000}"/>
-    <hyperlink ref="C485" r:id="rId458" xr:uid="{00000000-0004-0000-0000-0000C9010000}"/>
-    <hyperlink ref="C486" r:id="rId459" xr:uid="{00000000-0004-0000-0000-0000CA010000}"/>
-    <hyperlink ref="C487" r:id="rId460" xr:uid="{00000000-0004-0000-0000-0000CB010000}"/>
-    <hyperlink ref="C488" r:id="rId461" xr:uid="{00000000-0004-0000-0000-0000CC010000}"/>
-    <hyperlink ref="C489" r:id="rId462" xr:uid="{00000000-0004-0000-0000-0000CD010000}"/>
-    <hyperlink ref="C490" r:id="rId463" xr:uid="{00000000-0004-0000-0000-0000CE010000}"/>
-    <hyperlink ref="C35" r:id="rId464" xr:uid="{00000000-0004-0000-0000-0000CF010000}"/>
-    <hyperlink ref="C491" r:id="rId465" xr:uid="{00000000-0004-0000-0000-0000D0010000}"/>
-    <hyperlink ref="C492" r:id="rId466" xr:uid="{00000000-0004-0000-0000-0000D1010000}"/>
-    <hyperlink ref="C493" r:id="rId467" xr:uid="{00000000-0004-0000-0000-0000D2010000}"/>
-    <hyperlink ref="C494" r:id="rId468" xr:uid="{00000000-0004-0000-0000-0000D3010000}"/>
-    <hyperlink ref="C495" r:id="rId469" xr:uid="{00000000-0004-0000-0000-0000D4010000}"/>
-    <hyperlink ref="C496" r:id="rId470" xr:uid="{00000000-0004-0000-0000-0000D5010000}"/>
-    <hyperlink ref="C497" r:id="rId471" xr:uid="{00000000-0004-0000-0000-0000D6010000}"/>
-    <hyperlink ref="C498" r:id="rId472" xr:uid="{00000000-0004-0000-0000-0000D7010000}"/>
-    <hyperlink ref="C36" r:id="rId473" xr:uid="{00000000-0004-0000-0000-0000D8010000}"/>
-    <hyperlink ref="C499" r:id="rId474" xr:uid="{00000000-0004-0000-0000-0000D9010000}"/>
-    <hyperlink ref="C500" r:id="rId475" xr:uid="{00000000-0004-0000-0000-0000DA010000}"/>
-    <hyperlink ref="C501" r:id="rId476" xr:uid="{00000000-0004-0000-0000-0000DB010000}"/>
-    <hyperlink ref="C502" r:id="rId477" xr:uid="{00000000-0004-0000-0000-0000DC010000}"/>
-    <hyperlink ref="C911" r:id="rId478" xr:uid="{00000000-0004-0000-0000-0000DD010000}"/>
-    <hyperlink ref="C503" r:id="rId479" xr:uid="{00000000-0004-0000-0000-0000DE010000}"/>
-    <hyperlink ref="C504" r:id="rId480" xr:uid="{00000000-0004-0000-0000-0000DF010000}"/>
-    <hyperlink ref="C505" r:id="rId481" xr:uid="{00000000-0004-0000-0000-0000E0010000}"/>
-    <hyperlink ref="C506" r:id="rId482" xr:uid="{00000000-0004-0000-0000-0000E1010000}"/>
-    <hyperlink ref="C507" r:id="rId483" xr:uid="{00000000-0004-0000-0000-0000E2010000}"/>
-    <hyperlink ref="C508" r:id="rId484" xr:uid="{00000000-0004-0000-0000-0000E3010000}"/>
-    <hyperlink ref="C509" r:id="rId485" xr:uid="{00000000-0004-0000-0000-0000E4010000}"/>
-    <hyperlink ref="C510" r:id="rId486" xr:uid="{00000000-0004-0000-0000-0000E5010000}"/>
-    <hyperlink ref="C511" r:id="rId487" xr:uid="{00000000-0004-0000-0000-0000E6010000}"/>
-    <hyperlink ref="C512" r:id="rId488" xr:uid="{00000000-0004-0000-0000-0000E7010000}"/>
-    <hyperlink ref="C513" r:id="rId489" xr:uid="{00000000-0004-0000-0000-0000E8010000}"/>
-    <hyperlink ref="C514" r:id="rId490" xr:uid="{00000000-0004-0000-0000-0000E9010000}"/>
-    <hyperlink ref="C515" r:id="rId491" xr:uid="{00000000-0004-0000-0000-0000EA010000}"/>
-    <hyperlink ref="C516" r:id="rId492" xr:uid="{00000000-0004-0000-0000-0000EB010000}"/>
-    <hyperlink ref="C517" r:id="rId493" xr:uid="{00000000-0004-0000-0000-0000EC010000}"/>
-    <hyperlink ref="C518" r:id="rId494" xr:uid="{00000000-0004-0000-0000-0000ED010000}"/>
-    <hyperlink ref="C519" r:id="rId495" xr:uid="{00000000-0004-0000-0000-0000EE010000}"/>
-    <hyperlink ref="C37" r:id="rId496" xr:uid="{00000000-0004-0000-0000-0000EF010000}"/>
-    <hyperlink ref="C520" r:id="rId497" xr:uid="{00000000-0004-0000-0000-0000F0010000}"/>
-    <hyperlink ref="C521" r:id="rId498" xr:uid="{00000000-0004-0000-0000-0000F1010000}"/>
-    <hyperlink ref="C522" r:id="rId499" xr:uid="{00000000-0004-0000-0000-0000F2010000}"/>
-    <hyperlink ref="C523" r:id="rId500" xr:uid="{00000000-0004-0000-0000-0000F3010000}"/>
-    <hyperlink ref="C524" r:id="rId501" xr:uid="{00000000-0004-0000-0000-0000F4010000}"/>
-    <hyperlink ref="C525" r:id="rId502" xr:uid="{00000000-0004-0000-0000-0000F5010000}"/>
-    <hyperlink ref="C38" r:id="rId503" xr:uid="{00000000-0004-0000-0000-0000F6010000}"/>
-    <hyperlink ref="C526" r:id="rId504" xr:uid="{00000000-0004-0000-0000-0000F7010000}"/>
-    <hyperlink ref="C527" r:id="rId505" xr:uid="{00000000-0004-0000-0000-0000F8010000}"/>
-    <hyperlink ref="C528" r:id="rId506" xr:uid="{00000000-0004-0000-0000-0000F9010000}"/>
-    <hyperlink ref="C529" r:id="rId507" xr:uid="{00000000-0004-0000-0000-0000FA010000}"/>
-    <hyperlink ref="C530" r:id="rId508" xr:uid="{00000000-0004-0000-0000-0000FB010000}"/>
-    <hyperlink ref="C531" r:id="rId509" xr:uid="{00000000-0004-0000-0000-0000FC010000}"/>
-    <hyperlink ref="C532" r:id="rId510" xr:uid="{00000000-0004-0000-0000-0000FD010000}"/>
-    <hyperlink ref="C533" r:id="rId511" xr:uid="{00000000-0004-0000-0000-0000FE010000}"/>
-    <hyperlink ref="C534" r:id="rId512" xr:uid="{00000000-0004-0000-0000-0000FF010000}"/>
-    <hyperlink ref="C535" r:id="rId513" xr:uid="{00000000-0004-0000-0000-000000020000}"/>
-    <hyperlink ref="C536" r:id="rId514" xr:uid="{00000000-0004-0000-0000-000001020000}"/>
-    <hyperlink ref="C537" r:id="rId515" xr:uid="{00000000-0004-0000-0000-000002020000}"/>
-    <hyperlink ref="C538" r:id="rId516" xr:uid="{00000000-0004-0000-0000-000003020000}"/>
-    <hyperlink ref="C39" r:id="rId517" xr:uid="{00000000-0004-0000-0000-000004020000}"/>
-    <hyperlink ref="C539" r:id="rId518" xr:uid="{00000000-0004-0000-0000-000005020000}"/>
-    <hyperlink ref="C540" r:id="rId519" xr:uid="{00000000-0004-0000-0000-000006020000}"/>
-    <hyperlink ref="C541" r:id="rId520" xr:uid="{00000000-0004-0000-0000-000007020000}"/>
-    <hyperlink ref="C542" r:id="rId521" xr:uid="{00000000-0004-0000-0000-000008020000}"/>
-    <hyperlink ref="C543" r:id="rId522" xr:uid="{00000000-0004-0000-0000-000009020000}"/>
-    <hyperlink ref="C544" r:id="rId523" xr:uid="{00000000-0004-0000-0000-00000A020000}"/>
-    <hyperlink ref="C545" r:id="rId524" xr:uid="{00000000-0004-0000-0000-00000B020000}"/>
-    <hyperlink ref="C546" r:id="rId525" xr:uid="{00000000-0004-0000-0000-00000C020000}"/>
-    <hyperlink ref="C547" r:id="rId526" xr:uid="{00000000-0004-0000-0000-00000D020000}"/>
-    <hyperlink ref="C548" r:id="rId527" xr:uid="{00000000-0004-0000-0000-00000E020000}"/>
-    <hyperlink ref="C40" r:id="rId528" xr:uid="{00000000-0004-0000-0000-00000F020000}"/>
-    <hyperlink ref="C549" r:id="rId529" xr:uid="{00000000-0004-0000-0000-000010020000}"/>
-    <hyperlink ref="C550" r:id="rId530" xr:uid="{00000000-0004-0000-0000-000011020000}"/>
-    <hyperlink ref="C41" r:id="rId531" xr:uid="{00000000-0004-0000-0000-000012020000}"/>
-    <hyperlink ref="C551" r:id="rId532" xr:uid="{00000000-0004-0000-0000-000013020000}"/>
-    <hyperlink ref="C552" r:id="rId533" xr:uid="{00000000-0004-0000-0000-000014020000}"/>
-    <hyperlink ref="C553" r:id="rId534" xr:uid="{00000000-0004-0000-0000-000015020000}"/>
-    <hyperlink ref="C554" r:id="rId535" xr:uid="{00000000-0004-0000-0000-000016020000}"/>
-    <hyperlink ref="C555" r:id="rId536" xr:uid="{00000000-0004-0000-0000-000017020000}"/>
-    <hyperlink ref="C556" r:id="rId537" xr:uid="{00000000-0004-0000-0000-000018020000}"/>
-    <hyperlink ref="C557" r:id="rId538" xr:uid="{00000000-0004-0000-0000-000019020000}"/>
-    <hyperlink ref="C558" r:id="rId539" xr:uid="{00000000-0004-0000-0000-00001A020000}"/>
-    <hyperlink ref="C559" r:id="rId540" xr:uid="{00000000-0004-0000-0000-00001B020000}"/>
-    <hyperlink ref="C560" r:id="rId541" xr:uid="{00000000-0004-0000-0000-00001C020000}"/>
-    <hyperlink ref="C561" r:id="rId542" xr:uid="{00000000-0004-0000-0000-00001D020000}"/>
-    <hyperlink ref="C562" r:id="rId543" xr:uid="{00000000-0004-0000-0000-00001E020000}"/>
-    <hyperlink ref="C563" r:id="rId544" xr:uid="{00000000-0004-0000-0000-00001F020000}"/>
-    <hyperlink ref="C564" r:id="rId545" xr:uid="{00000000-0004-0000-0000-000020020000}"/>
-    <hyperlink ref="C565" r:id="rId546" xr:uid="{00000000-0004-0000-0000-000021020000}"/>
-    <hyperlink ref="C566" r:id="rId547" xr:uid="{00000000-0004-0000-0000-000022020000}"/>
-    <hyperlink ref="C567" r:id="rId548" xr:uid="{00000000-0004-0000-0000-000023020000}"/>
-    <hyperlink ref="C568" r:id="rId549" xr:uid="{00000000-0004-0000-0000-000024020000}"/>
-    <hyperlink ref="C569" r:id="rId550" xr:uid="{00000000-0004-0000-0000-000025020000}"/>
-    <hyperlink ref="C570" r:id="rId551" xr:uid="{00000000-0004-0000-0000-000026020000}"/>
-    <hyperlink ref="C571" r:id="rId552" xr:uid="{00000000-0004-0000-0000-000027020000}"/>
-    <hyperlink ref="C572" r:id="rId553" xr:uid="{00000000-0004-0000-0000-000028020000}"/>
-    <hyperlink ref="C573" r:id="rId554" xr:uid="{00000000-0004-0000-0000-000029020000}"/>
-    <hyperlink ref="C574" r:id="rId555" xr:uid="{00000000-0004-0000-0000-00002A020000}"/>
-    <hyperlink ref="C575" r:id="rId556" xr:uid="{00000000-0004-0000-0000-00002B020000}"/>
-    <hyperlink ref="C576" r:id="rId557" xr:uid="{00000000-0004-0000-0000-00002C020000}"/>
-    <hyperlink ref="C577" r:id="rId558" xr:uid="{00000000-0004-0000-0000-00002D020000}"/>
-    <hyperlink ref="C578" r:id="rId559" xr:uid="{00000000-0004-0000-0000-00002E020000}"/>
-    <hyperlink ref="C579" r:id="rId560" xr:uid="{00000000-0004-0000-0000-00002F020000}"/>
-    <hyperlink ref="C580" r:id="rId561" xr:uid="{00000000-0004-0000-0000-000030020000}"/>
-    <hyperlink ref="C581" r:id="rId562" xr:uid="{00000000-0004-0000-0000-000031020000}"/>
-    <hyperlink ref="C582" r:id="rId563" xr:uid="{00000000-0004-0000-0000-000032020000}"/>
-    <hyperlink ref="C583" r:id="rId564" xr:uid="{00000000-0004-0000-0000-000033020000}"/>
-    <hyperlink ref="C584" r:id="rId565" xr:uid="{00000000-0004-0000-0000-000034020000}"/>
-    <hyperlink ref="C585" r:id="rId566" xr:uid="{00000000-0004-0000-0000-000035020000}"/>
-    <hyperlink ref="C586" r:id="rId567" xr:uid="{00000000-0004-0000-0000-000036020000}"/>
-    <hyperlink ref="C587" r:id="rId568" xr:uid="{00000000-0004-0000-0000-000037020000}"/>
-    <hyperlink ref="C588" r:id="rId569" xr:uid="{00000000-0004-0000-0000-000038020000}"/>
-    <hyperlink ref="C589" r:id="rId570" xr:uid="{00000000-0004-0000-0000-000039020000}"/>
-    <hyperlink ref="C590" r:id="rId571" xr:uid="{00000000-0004-0000-0000-00003A020000}"/>
-    <hyperlink ref="C591" r:id="rId572" xr:uid="{00000000-0004-0000-0000-00003B020000}"/>
-    <hyperlink ref="C592" r:id="rId573" xr:uid="{00000000-0004-0000-0000-00003C020000}"/>
-    <hyperlink ref="C593" r:id="rId574" xr:uid="{00000000-0004-0000-0000-00003D020000}"/>
-    <hyperlink ref="C594" r:id="rId575" xr:uid="{00000000-0004-0000-0000-00003E020000}"/>
-    <hyperlink ref="C595" r:id="rId576" xr:uid="{00000000-0004-0000-0000-00003F020000}"/>
-    <hyperlink ref="C596" r:id="rId577" xr:uid="{00000000-0004-0000-0000-000040020000}"/>
-    <hyperlink ref="C597" r:id="rId578" xr:uid="{00000000-0004-0000-0000-000041020000}"/>
-    <hyperlink ref="C598" r:id="rId579" xr:uid="{00000000-0004-0000-0000-000042020000}"/>
-    <hyperlink ref="C599" r:id="rId580" xr:uid="{00000000-0004-0000-0000-000043020000}"/>
-    <hyperlink ref="C600" r:id="rId581" xr:uid="{00000000-0004-0000-0000-000044020000}"/>
-    <hyperlink ref="C42" r:id="rId582" xr:uid="{00000000-0004-0000-0000-000045020000}"/>
-    <hyperlink ref="C601" r:id="rId583" xr:uid="{00000000-0004-0000-0000-000046020000}"/>
-    <hyperlink ref="C602" r:id="rId584" xr:uid="{00000000-0004-0000-0000-000047020000}"/>
-    <hyperlink ref="C603" r:id="rId585" xr:uid="{00000000-0004-0000-0000-000048020000}"/>
-    <hyperlink ref="C604" r:id="rId586" xr:uid="{00000000-0004-0000-0000-000049020000}"/>
-    <hyperlink ref="C605" r:id="rId587" xr:uid="{00000000-0004-0000-0000-00004A020000}"/>
-    <hyperlink ref="C606" r:id="rId588" xr:uid="{00000000-0004-0000-0000-00004B020000}"/>
-    <hyperlink ref="C607" r:id="rId589" xr:uid="{00000000-0004-0000-0000-00004C020000}"/>
-    <hyperlink ref="C608" r:id="rId590" xr:uid="{00000000-0004-0000-0000-00004D020000}"/>
-    <hyperlink ref="C609" r:id="rId591" xr:uid="{00000000-0004-0000-0000-00004E020000}"/>
-    <hyperlink ref="C610" r:id="rId592" xr:uid="{00000000-0004-0000-0000-00004F020000}"/>
-    <hyperlink ref="C611" r:id="rId593" xr:uid="{00000000-0004-0000-0000-000050020000}"/>
-    <hyperlink ref="C612" r:id="rId594" xr:uid="{00000000-0004-0000-0000-000051020000}"/>
-    <hyperlink ref="C613" r:id="rId595" xr:uid="{00000000-0004-0000-0000-000052020000}"/>
-    <hyperlink ref="C614" r:id="rId596" xr:uid="{00000000-0004-0000-0000-000053020000}"/>
-    <hyperlink ref="C615" r:id="rId597" xr:uid="{00000000-0004-0000-0000-000054020000}"/>
-    <hyperlink ref="C616" r:id="rId598" xr:uid="{00000000-0004-0000-0000-000055020000}"/>
-    <hyperlink ref="C617" r:id="rId599" xr:uid="{00000000-0004-0000-0000-000056020000}"/>
-    <hyperlink ref="C618" r:id="rId600" xr:uid="{00000000-0004-0000-0000-000057020000}"/>
-    <hyperlink ref="C619" r:id="rId601" xr:uid="{00000000-0004-0000-0000-000058020000}"/>
-    <hyperlink ref="C620" r:id="rId602" xr:uid="{00000000-0004-0000-0000-000059020000}"/>
-    <hyperlink ref="C621" r:id="rId603" xr:uid="{00000000-0004-0000-0000-00005A020000}"/>
-    <hyperlink ref="C622" r:id="rId604" xr:uid="{00000000-0004-0000-0000-00005B020000}"/>
-    <hyperlink ref="C623" r:id="rId605" xr:uid="{00000000-0004-0000-0000-00005C020000}"/>
-    <hyperlink ref="C624" r:id="rId606" xr:uid="{00000000-0004-0000-0000-00005D020000}"/>
-    <hyperlink ref="C625" r:id="rId607" xr:uid="{00000000-0004-0000-0000-00005E020000}"/>
-    <hyperlink ref="C626" r:id="rId608" xr:uid="{00000000-0004-0000-0000-00005F020000}"/>
-    <hyperlink ref="C627" r:id="rId609" xr:uid="{00000000-0004-0000-0000-000060020000}"/>
-    <hyperlink ref="C628" r:id="rId610" xr:uid="{00000000-0004-0000-0000-000061020000}"/>
-    <hyperlink ref="C629" r:id="rId611" xr:uid="{00000000-0004-0000-0000-000062020000}"/>
-    <hyperlink ref="C43" r:id="rId612" xr:uid="{00000000-0004-0000-0000-000063020000}"/>
-    <hyperlink ref="C630" r:id="rId613" xr:uid="{00000000-0004-0000-0000-000064020000}"/>
-    <hyperlink ref="C631" r:id="rId614" xr:uid="{00000000-0004-0000-0000-000065020000}"/>
-    <hyperlink ref="C632" r:id="rId615" xr:uid="{00000000-0004-0000-0000-000066020000}"/>
-    <hyperlink ref="C633" r:id="rId616" xr:uid="{00000000-0004-0000-0000-000067020000}"/>
-    <hyperlink ref="C634" r:id="rId617" xr:uid="{00000000-0004-0000-0000-000068020000}"/>
-    <hyperlink ref="C635" r:id="rId618" xr:uid="{00000000-0004-0000-0000-000069020000}"/>
-    <hyperlink ref="C636" r:id="rId619" xr:uid="{00000000-0004-0000-0000-00006A020000}"/>
-    <hyperlink ref="C637" r:id="rId620" xr:uid="{00000000-0004-0000-0000-00006B020000}"/>
-    <hyperlink ref="C638" r:id="rId621" xr:uid="{00000000-0004-0000-0000-00006C020000}"/>
-    <hyperlink ref="C639" r:id="rId622" xr:uid="{00000000-0004-0000-0000-00006D020000}"/>
-    <hyperlink ref="C640" r:id="rId623" xr:uid="{00000000-0004-0000-0000-00006E020000}"/>
-    <hyperlink ref="C641" r:id="rId624" xr:uid="{00000000-0004-0000-0000-00006F020000}"/>
-    <hyperlink ref="C642" r:id="rId625" xr:uid="{00000000-0004-0000-0000-000070020000}"/>
-    <hyperlink ref="C643" r:id="rId626" xr:uid="{00000000-0004-0000-0000-000071020000}"/>
-    <hyperlink ref="C644" r:id="rId627" xr:uid="{00000000-0004-0000-0000-000072020000}"/>
-    <hyperlink ref="C645" r:id="rId628" xr:uid="{00000000-0004-0000-0000-000073020000}"/>
-    <hyperlink ref="C646" r:id="rId629" xr:uid="{00000000-0004-0000-0000-000074020000}"/>
-    <hyperlink ref="C647" r:id="rId630" xr:uid="{00000000-0004-0000-0000-000075020000}"/>
-    <hyperlink ref="C648" r:id="rId631" xr:uid="{00000000-0004-0000-0000-000076020000}"/>
-    <hyperlink ref="C649" r:id="rId632" xr:uid="{00000000-0004-0000-0000-000077020000}"/>
-    <hyperlink ref="C650" r:id="rId633" xr:uid="{00000000-0004-0000-0000-000078020000}"/>
-    <hyperlink ref="C651" r:id="rId634" xr:uid="{00000000-0004-0000-0000-000079020000}"/>
-    <hyperlink ref="C652" r:id="rId635" xr:uid="{00000000-0004-0000-0000-00007A020000}"/>
-    <hyperlink ref="C653" r:id="rId636" xr:uid="{00000000-0004-0000-0000-00007B020000}"/>
-    <hyperlink ref="C654" r:id="rId637" xr:uid="{00000000-0004-0000-0000-00007C020000}"/>
-    <hyperlink ref="C655" r:id="rId638" xr:uid="{00000000-0004-0000-0000-00007D020000}"/>
-    <hyperlink ref="C656" r:id="rId639" xr:uid="{00000000-0004-0000-0000-00007E020000}"/>
-    <hyperlink ref="C657" r:id="rId640" xr:uid="{00000000-0004-0000-0000-00007F020000}"/>
-    <hyperlink ref="C658" r:id="rId641" xr:uid="{00000000-0004-0000-0000-000080020000}"/>
-    <hyperlink ref="C659" r:id="rId642" xr:uid="{00000000-0004-0000-0000-000081020000}"/>
-    <hyperlink ref="C660" r:id="rId643" xr:uid="{00000000-0004-0000-0000-000082020000}"/>
-    <hyperlink ref="C661" r:id="rId644" xr:uid="{00000000-0004-0000-0000-000083020000}"/>
-    <hyperlink ref="C662" r:id="rId645" xr:uid="{00000000-0004-0000-0000-000084020000}"/>
-    <hyperlink ref="C663" r:id="rId646" xr:uid="{00000000-0004-0000-0000-000085020000}"/>
-    <hyperlink ref="C664" r:id="rId647" xr:uid="{00000000-0004-0000-0000-000086020000}"/>
-    <hyperlink ref="C665" r:id="rId648" xr:uid="{00000000-0004-0000-0000-000087020000}"/>
-    <hyperlink ref="C666" r:id="rId649" xr:uid="{00000000-0004-0000-0000-000088020000}"/>
-    <hyperlink ref="C667" r:id="rId650" xr:uid="{00000000-0004-0000-0000-000089020000}"/>
-    <hyperlink ref="C668" r:id="rId651" xr:uid="{00000000-0004-0000-0000-00008A020000}"/>
-    <hyperlink ref="C669" r:id="rId652" xr:uid="{00000000-0004-0000-0000-00008B020000}"/>
-    <hyperlink ref="C670" r:id="rId653" xr:uid="{00000000-0004-0000-0000-00008C020000}"/>
-    <hyperlink ref="C44" r:id="rId654" xr:uid="{00000000-0004-0000-0000-00008D020000}"/>
-    <hyperlink ref="C671" r:id="rId655" xr:uid="{00000000-0004-0000-0000-00008E020000}"/>
-    <hyperlink ref="C672" r:id="rId656" xr:uid="{00000000-0004-0000-0000-00008F020000}"/>
-    <hyperlink ref="C673" r:id="rId657" xr:uid="{00000000-0004-0000-0000-000090020000}"/>
-    <hyperlink ref="C674" r:id="rId658" xr:uid="{00000000-0004-0000-0000-000091020000}"/>
-    <hyperlink ref="C675" r:id="rId659" xr:uid="{00000000-0004-0000-0000-000092020000}"/>
-    <hyperlink ref="C676" r:id="rId660" xr:uid="{00000000-0004-0000-0000-000093020000}"/>
-    <hyperlink ref="C677" r:id="rId661" xr:uid="{00000000-0004-0000-0000-000094020000}"/>
-    <hyperlink ref="C678" r:id="rId662" xr:uid="{00000000-0004-0000-0000-000095020000}"/>
-    <hyperlink ref="C679" r:id="rId663" xr:uid="{00000000-0004-0000-0000-000096020000}"/>
-    <hyperlink ref="C680" r:id="rId664" xr:uid="{00000000-0004-0000-0000-000097020000}"/>
-    <hyperlink ref="C681" r:id="rId665" xr:uid="{00000000-0004-0000-0000-000098020000}"/>
-    <hyperlink ref="C682" r:id="rId666" xr:uid="{00000000-0004-0000-0000-000099020000}"/>
-    <hyperlink ref="C683" r:id="rId667" xr:uid="{00000000-0004-0000-0000-00009A020000}"/>
-    <hyperlink ref="C684" r:id="rId668" xr:uid="{00000000-0004-0000-0000-00009B020000}"/>
-    <hyperlink ref="C685" r:id="rId669" xr:uid="{00000000-0004-0000-0000-00009C020000}"/>
-    <hyperlink ref="C686" r:id="rId670" xr:uid="{00000000-0004-0000-0000-00009D020000}"/>
-    <hyperlink ref="C687" r:id="rId671" xr:uid="{00000000-0004-0000-0000-00009E020000}"/>
-    <hyperlink ref="C688" r:id="rId672" xr:uid="{00000000-0004-0000-0000-00009F020000}"/>
-    <hyperlink ref="C689" r:id="rId673" xr:uid="{00000000-0004-0000-0000-0000A0020000}"/>
-    <hyperlink ref="C690" r:id="rId674" xr:uid="{00000000-0004-0000-0000-0000A1020000}"/>
-    <hyperlink ref="C691" r:id="rId675" xr:uid="{00000000-0004-0000-0000-0000A2020000}"/>
-    <hyperlink ref="C692" r:id="rId676" xr:uid="{00000000-0004-0000-0000-0000A3020000}"/>
-    <hyperlink ref="C693" r:id="rId677" xr:uid="{00000000-0004-0000-0000-0000A4020000}"/>
-    <hyperlink ref="C694" r:id="rId678" xr:uid="{00000000-0004-0000-0000-0000A5020000}"/>
-    <hyperlink ref="C695" r:id="rId679" xr:uid="{00000000-0004-0000-0000-0000A6020000}"/>
-    <hyperlink ref="C696" r:id="rId680" xr:uid="{00000000-0004-0000-0000-0000A7020000}"/>
-    <hyperlink ref="C697" r:id="rId681" xr:uid="{00000000-0004-0000-0000-0000A8020000}"/>
-    <hyperlink ref="C698" r:id="rId682" xr:uid="{00000000-0004-0000-0000-0000A9020000}"/>
-    <hyperlink ref="C699" r:id="rId683" xr:uid="{00000000-0004-0000-0000-0000AA020000}"/>
-    <hyperlink ref="C700" r:id="rId684" xr:uid="{00000000-0004-0000-0000-0000AB020000}"/>
-    <hyperlink ref="C701" r:id="rId685" xr:uid="{00000000-0004-0000-0000-0000AC020000}"/>
-    <hyperlink ref="C702" r:id="rId686" xr:uid="{00000000-0004-0000-0000-0000AD020000}"/>
-    <hyperlink ref="C703" r:id="rId687" xr:uid="{00000000-0004-0000-0000-0000AE020000}"/>
-    <hyperlink ref="C704" r:id="rId688" xr:uid="{00000000-0004-0000-0000-0000AF020000}"/>
-    <hyperlink ref="C705" r:id="rId689" xr:uid="{00000000-0004-0000-0000-0000B0020000}"/>
-    <hyperlink ref="C706" r:id="rId690" xr:uid="{00000000-0004-0000-0000-0000B1020000}"/>
-    <hyperlink ref="C707" r:id="rId691" xr:uid="{00000000-0004-0000-0000-0000B2020000}"/>
-    <hyperlink ref="C708" r:id="rId692" xr:uid="{00000000-0004-0000-0000-0000B3020000}"/>
-    <hyperlink ref="C709" r:id="rId693" xr:uid="{00000000-0004-0000-0000-0000B4020000}"/>
-    <hyperlink ref="C45" r:id="rId694" xr:uid="{00000000-0004-0000-0000-0000B5020000}"/>
-    <hyperlink ref="C710" r:id="rId695" xr:uid="{00000000-0004-0000-0000-0000B6020000}"/>
-    <hyperlink ref="C711" r:id="rId696" xr:uid="{00000000-0004-0000-0000-0000B7020000}"/>
-    <hyperlink ref="C712" r:id="rId697" xr:uid="{00000000-0004-0000-0000-0000B8020000}"/>
-    <hyperlink ref="C713" r:id="rId698" xr:uid="{00000000-0004-0000-0000-0000B9020000}"/>
-    <hyperlink ref="C714" r:id="rId699" xr:uid="{00000000-0004-0000-0000-0000BA020000}"/>
-    <hyperlink ref="C715" r:id="rId700" xr:uid="{00000000-0004-0000-0000-0000BB020000}"/>
-    <hyperlink ref="C716" r:id="rId701" xr:uid="{00000000-0004-0000-0000-0000BC020000}"/>
-    <hyperlink ref="C717" r:id="rId702" xr:uid="{00000000-0004-0000-0000-0000BD020000}"/>
-    <hyperlink ref="C718" r:id="rId703" xr:uid="{00000000-0004-0000-0000-0000BE020000}"/>
-    <hyperlink ref="C719" r:id="rId704" xr:uid="{00000000-0004-0000-0000-0000BF020000}"/>
-    <hyperlink ref="C720" r:id="rId705" xr:uid="{00000000-0004-0000-0000-0000C0020000}"/>
-    <hyperlink ref="C721" r:id="rId706" xr:uid="{00000000-0004-0000-0000-0000C1020000}"/>
-    <hyperlink ref="C722" r:id="rId707" xr:uid="{00000000-0004-0000-0000-0000C2020000}"/>
-    <hyperlink ref="C723" r:id="rId708" xr:uid="{00000000-0004-0000-0000-0000C3020000}"/>
-    <hyperlink ref="C724" r:id="rId709" xr:uid="{00000000-0004-0000-0000-0000C4020000}"/>
-    <hyperlink ref="C46" r:id="rId710" xr:uid="{00000000-0004-0000-0000-0000C5020000}"/>
-    <hyperlink ref="C725" r:id="rId711" xr:uid="{00000000-0004-0000-0000-0000C6020000}"/>
-    <hyperlink ref="C726" r:id="rId712" xr:uid="{00000000-0004-0000-0000-0000C7020000}"/>
-    <hyperlink ref="C727" r:id="rId713" xr:uid="{00000000-0004-0000-0000-0000C8020000}"/>
-    <hyperlink ref="C728" r:id="rId714" xr:uid="{00000000-0004-0000-0000-0000C9020000}"/>
-    <hyperlink ref="C729" r:id="rId715" xr:uid="{00000000-0004-0000-0000-0000CA020000}"/>
-    <hyperlink ref="C730" r:id="rId716" xr:uid="{00000000-0004-0000-0000-0000CB020000}"/>
-    <hyperlink ref="C731" r:id="rId717" xr:uid="{00000000-0004-0000-0000-0000CC020000}"/>
-    <hyperlink ref="C732" r:id="rId718" xr:uid="{00000000-0004-0000-0000-0000CD020000}"/>
-    <hyperlink ref="C733" r:id="rId719" xr:uid="{00000000-0004-0000-0000-0000CE020000}"/>
-    <hyperlink ref="C734" r:id="rId720" xr:uid="{00000000-0004-0000-0000-0000CF020000}"/>
-    <hyperlink ref="C735" r:id="rId721" xr:uid="{00000000-0004-0000-0000-0000D0020000}"/>
-    <hyperlink ref="C736" r:id="rId722" xr:uid="{00000000-0004-0000-0000-0000D1020000}"/>
-    <hyperlink ref="C737" r:id="rId723" xr:uid="{00000000-0004-0000-0000-0000D2020000}"/>
-    <hyperlink ref="C738" r:id="rId724" xr:uid="{00000000-0004-0000-0000-0000D3020000}"/>
-    <hyperlink ref="C739" r:id="rId725" xr:uid="{00000000-0004-0000-0000-0000D4020000}"/>
-    <hyperlink ref="C47" r:id="rId726" xr:uid="{00000000-0004-0000-0000-0000D5020000}"/>
-    <hyperlink ref="C740" r:id="rId727" xr:uid="{00000000-0004-0000-0000-0000D6020000}"/>
-    <hyperlink ref="C741" r:id="rId728" xr:uid="{00000000-0004-0000-0000-0000D7020000}"/>
-    <hyperlink ref="C742" r:id="rId729" xr:uid="{00000000-0004-0000-0000-0000D8020000}"/>
-    <hyperlink ref="C743" r:id="rId730" xr:uid="{00000000-0004-0000-0000-0000D9020000}"/>
-    <hyperlink ref="C48" r:id="rId731" xr:uid="{00000000-0004-0000-0000-0000DA020000}"/>
-    <hyperlink ref="C744" r:id="rId732" xr:uid="{00000000-0004-0000-0000-0000DB020000}"/>
-    <hyperlink ref="C745" r:id="rId733" xr:uid="{00000000-0004-0000-0000-0000DC020000}"/>
-    <hyperlink ref="C49" r:id="rId734" xr:uid="{00000000-0004-0000-0000-0000DD020000}"/>
-    <hyperlink ref="C746" r:id="rId735" xr:uid="{00000000-0004-0000-0000-0000DE020000}"/>
-    <hyperlink ref="C747" r:id="rId736" xr:uid="{00000000-0004-0000-0000-0000DF020000}"/>
-    <hyperlink ref="C748" r:id="rId737" xr:uid="{00000000-0004-0000-0000-0000E0020000}"/>
-    <hyperlink ref="C749" r:id="rId738" xr:uid="{00000000-0004-0000-0000-0000E1020000}"/>
-    <hyperlink ref="C750" r:id="rId739" xr:uid="{00000000-0004-0000-0000-0000E2020000}"/>
-    <hyperlink ref="C751" r:id="rId740" xr:uid="{00000000-0004-0000-0000-0000E3020000}"/>
-    <hyperlink ref="C50" r:id="rId741" xr:uid="{00000000-0004-0000-0000-0000E4020000}"/>
-    <hyperlink ref="C752" r:id="rId742" xr:uid="{00000000-0004-0000-0000-0000E5020000}"/>
-    <hyperlink ref="C51" r:id="rId743" xr:uid="{00000000-0004-0000-0000-0000E6020000}"/>
-    <hyperlink ref="C753" r:id="rId744" xr:uid="{00000000-0004-0000-0000-0000E7020000}"/>
-    <hyperlink ref="C754" r:id="rId745" xr:uid="{00000000-0004-0000-0000-0000E8020000}"/>
-    <hyperlink ref="C755" r:id="rId746" xr:uid="{00000000-0004-0000-0000-0000E9020000}"/>
-    <hyperlink ref="C756" r:id="rId747" xr:uid="{00000000-0004-0000-0000-0000EA020000}"/>
-    <hyperlink ref="C757" r:id="rId748" xr:uid="{00000000-0004-0000-0000-0000EB020000}"/>
-    <hyperlink ref="C758" r:id="rId749" xr:uid="{00000000-0004-0000-0000-0000EC020000}"/>
-    <hyperlink ref="C759" r:id="rId750" xr:uid="{00000000-0004-0000-0000-0000ED020000}"/>
-    <hyperlink ref="C760" r:id="rId751" xr:uid="{00000000-0004-0000-0000-0000EE020000}"/>
-    <hyperlink ref="C761" r:id="rId752" xr:uid="{00000000-0004-0000-0000-0000EF020000}"/>
-    <hyperlink ref="C762" r:id="rId753" xr:uid="{00000000-0004-0000-0000-0000F0020000}"/>
-    <hyperlink ref="C763" r:id="rId754" xr:uid="{00000000-0004-0000-0000-0000F1020000}"/>
-    <hyperlink ref="C764" r:id="rId755" xr:uid="{00000000-0004-0000-0000-0000F2020000}"/>
-    <hyperlink ref="C765" r:id="rId756" xr:uid="{00000000-0004-0000-0000-0000F3020000}"/>
-    <hyperlink ref="C766" r:id="rId757" xr:uid="{00000000-0004-0000-0000-0000F4020000}"/>
-    <hyperlink ref="C767" r:id="rId758" xr:uid="{00000000-0004-0000-0000-0000F5020000}"/>
-    <hyperlink ref="C768" r:id="rId759" xr:uid="{00000000-0004-0000-0000-0000F6020000}"/>
-    <hyperlink ref="C769" r:id="rId760" xr:uid="{00000000-0004-0000-0000-0000F7020000}"/>
-    <hyperlink ref="C770" r:id="rId761" xr:uid="{00000000-0004-0000-0000-0000F8020000}"/>
-    <hyperlink ref="C771" r:id="rId762" xr:uid="{00000000-0004-0000-0000-0000F9020000}"/>
-    <hyperlink ref="C772" r:id="rId763" xr:uid="{00000000-0004-0000-0000-0000FA020000}"/>
-    <hyperlink ref="C773" r:id="rId764" xr:uid="{00000000-0004-0000-0000-0000FB020000}"/>
-    <hyperlink ref="C774" r:id="rId765" xr:uid="{00000000-0004-0000-0000-0000FC020000}"/>
-    <hyperlink ref="C775" r:id="rId766" xr:uid="{00000000-0004-0000-0000-0000FD020000}"/>
-    <hyperlink ref="C776" r:id="rId767" xr:uid="{00000000-0004-0000-0000-0000FE020000}"/>
-    <hyperlink ref="C777" r:id="rId768" xr:uid="{00000000-0004-0000-0000-0000FF020000}"/>
-    <hyperlink ref="C778" r:id="rId769" xr:uid="{00000000-0004-0000-0000-000000030000}"/>
-    <hyperlink ref="C779" r:id="rId770" xr:uid="{00000000-0004-0000-0000-000001030000}"/>
-    <hyperlink ref="C780" r:id="rId771" xr:uid="{00000000-0004-0000-0000-000002030000}"/>
-    <hyperlink ref="C781" r:id="rId772" xr:uid="{00000000-0004-0000-0000-000003030000}"/>
-    <hyperlink ref="C782" r:id="rId773" xr:uid="{00000000-0004-0000-0000-000004030000}"/>
-    <hyperlink ref="C783" r:id="rId774" xr:uid="{00000000-0004-0000-0000-000005030000}"/>
-    <hyperlink ref="C784" r:id="rId775" xr:uid="{00000000-0004-0000-0000-000006030000}"/>
-    <hyperlink ref="C785" r:id="rId776" xr:uid="{00000000-0004-0000-0000-000007030000}"/>
-    <hyperlink ref="C786" r:id="rId777" xr:uid="{00000000-0004-0000-0000-000008030000}"/>
-    <hyperlink ref="C787" r:id="rId778" xr:uid="{00000000-0004-0000-0000-000009030000}"/>
-    <hyperlink ref="C788" r:id="rId779" xr:uid="{00000000-0004-0000-0000-00000A030000}"/>
-    <hyperlink ref="C789" r:id="rId780" xr:uid="{00000000-0004-0000-0000-00000B030000}"/>
-    <hyperlink ref="C790" r:id="rId781" xr:uid="{00000000-0004-0000-0000-00000C030000}"/>
-    <hyperlink ref="C791" r:id="rId782" xr:uid="{00000000-0004-0000-0000-00000D030000}"/>
-    <hyperlink ref="C792" r:id="rId783" xr:uid="{00000000-0004-0000-0000-00000E030000}"/>
-    <hyperlink ref="C793" r:id="rId784" xr:uid="{00000000-0004-0000-0000-00000F030000}"/>
-    <hyperlink ref="C794" r:id="rId785" xr:uid="{00000000-0004-0000-0000-000010030000}"/>
-    <hyperlink ref="C52" r:id="rId786" xr:uid="{00000000-0004-0000-0000-000011030000}"/>
-    <hyperlink ref="C795" r:id="rId787" xr:uid="{00000000-0004-0000-0000-000012030000}"/>
-    <hyperlink ref="C796" r:id="rId788" xr:uid="{00000000-0004-0000-0000-000013030000}"/>
-    <hyperlink ref="C797" r:id="rId789" xr:uid="{00000000-0004-0000-0000-000014030000}"/>
-    <hyperlink ref="C798" r:id="rId790" xr:uid="{00000000-0004-0000-0000-000015030000}"/>
-    <hyperlink ref="C799" r:id="rId791" xr:uid="{00000000-0004-0000-0000-000016030000}"/>
-    <hyperlink ref="C800" r:id="rId792" xr:uid="{00000000-0004-0000-0000-000017030000}"/>
-    <hyperlink ref="C801" r:id="rId793" xr:uid="{00000000-0004-0000-0000-000018030000}"/>
-    <hyperlink ref="C802" r:id="rId794" xr:uid="{00000000-0004-0000-0000-000019030000}"/>
-    <hyperlink ref="C803" r:id="rId795" xr:uid="{00000000-0004-0000-0000-00001A030000}"/>
-    <hyperlink ref="C804" r:id="rId796" xr:uid="{00000000-0004-0000-0000-00001B030000}"/>
-    <hyperlink ref="C805" r:id="rId797" xr:uid="{00000000-0004-0000-0000-00001C030000}"/>
-    <hyperlink ref="C806" r:id="rId798" xr:uid="{00000000-0004-0000-0000-00001D030000}"/>
-    <hyperlink ref="C807" r:id="rId799" xr:uid="{00000000-0004-0000-0000-00001E030000}"/>
-    <hyperlink ref="C808" r:id="rId800" xr:uid="{00000000-0004-0000-0000-00001F030000}"/>
-    <hyperlink ref="C809" r:id="rId801" xr:uid="{00000000-0004-0000-0000-000020030000}"/>
-    <hyperlink ref="C810" r:id="rId802" xr:uid="{00000000-0004-0000-0000-000021030000}"/>
-    <hyperlink ref="C811" r:id="rId803" xr:uid="{00000000-0004-0000-0000-000022030000}"/>
-    <hyperlink ref="C812" r:id="rId804" xr:uid="{00000000-0004-0000-0000-000023030000}"/>
-    <hyperlink ref="C813" r:id="rId805" xr:uid="{00000000-0004-0000-0000-000024030000}"/>
-    <hyperlink ref="C814" r:id="rId806" xr:uid="{00000000-0004-0000-0000-000025030000}"/>
-    <hyperlink ref="C815" r:id="rId807" xr:uid="{00000000-0004-0000-0000-000026030000}"/>
-    <hyperlink ref="C816" r:id="rId808" xr:uid="{00000000-0004-0000-0000-000027030000}"/>
-    <hyperlink ref="C817" r:id="rId809" xr:uid="{00000000-0004-0000-0000-000028030000}"/>
-    <hyperlink ref="C818" r:id="rId810" xr:uid="{00000000-0004-0000-0000-000029030000}"/>
-    <hyperlink ref="C819" r:id="rId811" xr:uid="{00000000-0004-0000-0000-00002A030000}"/>
-    <hyperlink ref="C53" r:id="rId812" xr:uid="{00000000-0004-0000-0000-00002B030000}"/>
-    <hyperlink ref="C54" r:id="rId813" xr:uid="{00000000-0004-0000-0000-00002C030000}"/>
-    <hyperlink ref="C820" r:id="rId814" xr:uid="{00000000-0004-0000-0000-00002D030000}"/>
-    <hyperlink ref="C821" r:id="rId815" xr:uid="{00000000-0004-0000-0000-00002E030000}"/>
-    <hyperlink ref="C822" r:id="rId816" xr:uid="{00000000-0004-0000-0000-00002F030000}"/>
-    <hyperlink ref="C823" r:id="rId817" xr:uid="{00000000-0004-0000-0000-000030030000}"/>
-    <hyperlink ref="C824" r:id="rId818" xr:uid="{00000000-0004-0000-0000-000031030000}"/>
-    <hyperlink ref="C55" r:id="rId819" xr:uid="{00000000-0004-0000-0000-000032030000}"/>
-    <hyperlink ref="C56" r:id="rId820" xr:uid="{00000000-0004-0000-0000-000033030000}"/>
-    <hyperlink ref="C825" r:id="rId821" xr:uid="{00000000-0004-0000-0000-000034030000}"/>
-    <hyperlink ref="C826" r:id="rId822" xr:uid="{00000000-0004-0000-0000-000035030000}"/>
-    <hyperlink ref="C827" r:id="rId823" xr:uid="{00000000-0004-0000-0000-000036030000}"/>
-    <hyperlink ref="C828" r:id="rId824" xr:uid="{00000000-0004-0000-0000-000037030000}"/>
-    <hyperlink ref="C829" r:id="rId825" xr:uid="{00000000-0004-0000-0000-000038030000}"/>
-    <hyperlink ref="C830" r:id="rId826" xr:uid="{00000000-0004-0000-0000-000039030000}"/>
-    <hyperlink ref="C831" r:id="rId827" xr:uid="{00000000-0004-0000-0000-00003A030000}"/>
-    <hyperlink ref="C832" r:id="rId828" xr:uid="{00000000-0004-0000-0000-00003B030000}"/>
-    <hyperlink ref="C57" r:id="rId829" xr:uid="{00000000-0004-0000-0000-00003C030000}"/>
-    <hyperlink ref="C833" r:id="rId830" xr:uid="{00000000-0004-0000-0000-00003D030000}"/>
-    <hyperlink ref="C834" r:id="rId831" xr:uid="{00000000-0004-0000-0000-00003E030000}"/>
-    <hyperlink ref="C835" r:id="rId832" xr:uid="{00000000-0004-0000-0000-00003F030000}"/>
-    <hyperlink ref="C836" r:id="rId833" xr:uid="{00000000-0004-0000-0000-000040030000}"/>
-    <hyperlink ref="C837" r:id="rId834" xr:uid="{00000000-0004-0000-0000-000041030000}"/>
-    <hyperlink ref="C838" r:id="rId835" xr:uid="{00000000-0004-0000-0000-000042030000}"/>
-    <hyperlink ref="C839" r:id="rId836" xr:uid="{00000000-0004-0000-0000-000043030000}"/>
-    <hyperlink ref="C840" r:id="rId837" xr:uid="{00000000-0004-0000-0000-000044030000}"/>
-    <hyperlink ref="C841" r:id="rId838" xr:uid="{00000000-0004-0000-0000-000045030000}"/>
-    <hyperlink ref="C58" r:id="rId839" xr:uid="{00000000-0004-0000-0000-000046030000}"/>
-    <hyperlink ref="C842" r:id="rId840" xr:uid="{00000000-0004-0000-0000-000047030000}"/>
-    <hyperlink ref="C843" r:id="rId841" xr:uid="{00000000-0004-0000-0000-000048030000}"/>
-    <hyperlink ref="C844" r:id="rId842" xr:uid="{00000000-0004-0000-0000-000049030000}"/>
-    <hyperlink ref="C845" r:id="rId843" xr:uid="{00000000-0004-0000-0000-00004A030000}"/>
-    <hyperlink ref="C912" r:id="rId844" xr:uid="{00000000-0004-0000-0000-00004B030000}"/>
-    <hyperlink ref="C846" r:id="rId845" xr:uid="{00000000-0004-0000-0000-00004C030000}"/>
-    <hyperlink ref="C847" r:id="rId846" xr:uid="{00000000-0004-0000-0000-00004D030000}"/>
-    <hyperlink ref="C848" r:id="rId847" xr:uid="{00000000-0004-0000-0000-00004E030000}"/>
-    <hyperlink ref="C849" r:id="rId848" xr:uid="{00000000-0004-0000-0000-00004F030000}"/>
-    <hyperlink ref="C850" r:id="rId849" xr:uid="{00000000-0004-0000-0000-000050030000}"/>
-    <hyperlink ref="C851" r:id="rId850" xr:uid="{00000000-0004-0000-0000-000051030000}"/>
-    <hyperlink ref="C852" r:id="rId851" xr:uid="{00000000-0004-0000-0000-000052030000}"/>
-    <hyperlink ref="C59" r:id="rId852" xr:uid="{00000000-0004-0000-0000-000053030000}"/>
-    <hyperlink ref="C853" r:id="rId853" xr:uid="{00000000-0004-0000-0000-000054030000}"/>
-    <hyperlink ref="C854" r:id="rId854" xr:uid="{00000000-0004-0000-0000-000055030000}"/>
-    <hyperlink ref="C855" r:id="rId855" xr:uid="{00000000-0004-0000-0000-000056030000}"/>
-    <hyperlink ref="C856" r:id="rId856" xr:uid="{00000000-0004-0000-0000-000057030000}"/>
-    <hyperlink ref="C857" r:id="rId857" xr:uid="{00000000-0004-0000-0000-000058030000}"/>
-    <hyperlink ref="C858" r:id="rId858" xr:uid="{00000000-0004-0000-0000-000059030000}"/>
-    <hyperlink ref="C859" r:id="rId859" xr:uid="{00000000-0004-0000-0000-00005A030000}"/>
-    <hyperlink ref="C860" r:id="rId860" xr:uid="{00000000-0004-0000-0000-00005B030000}"/>
-    <hyperlink ref="C861" r:id="rId861" xr:uid="{00000000-0004-0000-0000-00005C030000}"/>
-    <hyperlink ref="C862" r:id="rId862" xr:uid="{00000000-0004-0000-0000-00005D030000}"/>
-    <hyperlink ref="C863" r:id="rId863" xr:uid="{00000000-0004-0000-0000-00005E030000}"/>
-    <hyperlink ref="C864" r:id="rId864" xr:uid="{00000000-0004-0000-0000-00005F030000}"/>
-    <hyperlink ref="C865" r:id="rId865" xr:uid="{00000000-0004-0000-0000-000060030000}"/>
-    <hyperlink ref="C866" r:id="rId866" xr:uid="{00000000-0004-0000-0000-000061030000}"/>
-    <hyperlink ref="C867" r:id="rId867" xr:uid="{00000000-0004-0000-0000-000062030000}"/>
-    <hyperlink ref="C868" r:id="rId868" xr:uid="{00000000-0004-0000-0000-000063030000}"/>
-    <hyperlink ref="C869" r:id="rId869" xr:uid="{00000000-0004-0000-0000-000064030000}"/>
-    <hyperlink ref="C870" r:id="rId870" xr:uid="{00000000-0004-0000-0000-000065030000}"/>
-    <hyperlink ref="C871" r:id="rId871" xr:uid="{00000000-0004-0000-0000-000066030000}"/>
-    <hyperlink ref="C872" r:id="rId872" xr:uid="{00000000-0004-0000-0000-000067030000}"/>
-    <hyperlink ref="C873" r:id="rId873" xr:uid="{00000000-0004-0000-0000-000068030000}"/>
-    <hyperlink ref="C874" r:id="rId874" xr:uid="{00000000-0004-0000-0000-000069030000}"/>
-    <hyperlink ref="C60" r:id="rId875" xr:uid="{00000000-0004-0000-0000-00006A030000}"/>
-    <hyperlink ref="C875" r:id="rId876" xr:uid="{00000000-0004-0000-0000-00006B030000}"/>
-    <hyperlink ref="C876" r:id="rId877" xr:uid="{00000000-0004-0000-0000-00006C030000}"/>
-    <hyperlink ref="C877" r:id="rId878" xr:uid="{00000000-0004-0000-0000-00006D030000}"/>
-    <hyperlink ref="C878" r:id="rId879" xr:uid="{00000000-0004-0000-0000-00006E030000}"/>
-    <hyperlink ref="C879" r:id="rId880" xr:uid="{00000000-0004-0000-0000-00006F030000}"/>
-    <hyperlink ref="C61" r:id="rId881" xr:uid="{00000000-0004-0000-0000-000070030000}"/>
-    <hyperlink ref="C880" r:id="rId882" xr:uid="{00000000-0004-0000-0000-000071030000}"/>
-    <hyperlink ref="C881" r:id="rId883" xr:uid="{00000000-0004-0000-0000-000072030000}"/>
-    <hyperlink ref="C882" r:id="rId884" xr:uid="{00000000-0004-0000-0000-000073030000}"/>
-    <hyperlink ref="C62" r:id="rId885" xr:uid="{00000000-0004-0000-0000-000074030000}"/>
-    <hyperlink ref="C883" r:id="rId886" xr:uid="{00000000-0004-0000-0000-000075030000}"/>
-    <hyperlink ref="C884" r:id="rId887" xr:uid="{00000000-0004-0000-0000-000076030000}"/>
-    <hyperlink ref="C885" r:id="rId888" xr:uid="{00000000-0004-0000-0000-000077030000}"/>
-    <hyperlink ref="C886" r:id="rId889" xr:uid="{00000000-0004-0000-0000-000078030000}"/>
-    <hyperlink ref="C887" r:id="rId890" xr:uid="{00000000-0004-0000-0000-000079030000}"/>
-    <hyperlink ref="C888" r:id="rId891" xr:uid="{00000000-0004-0000-0000-00007A030000}"/>
-    <hyperlink ref="C889" r:id="rId892" xr:uid="{00000000-0004-0000-0000-00007B030000}"/>
-    <hyperlink ref="C890" r:id="rId893" xr:uid="{00000000-0004-0000-0000-00007C030000}"/>
-    <hyperlink ref="C891" r:id="rId894" xr:uid="{00000000-0004-0000-0000-00007D030000}"/>
-    <hyperlink ref="C892" r:id="rId895" xr:uid="{00000000-0004-0000-0000-00007E030000}"/>
-    <hyperlink ref="C893" r:id="rId896" xr:uid="{00000000-0004-0000-0000-00007F030000}"/>
-    <hyperlink ref="C894" r:id="rId897" xr:uid="{00000000-0004-0000-0000-000080030000}"/>
-    <hyperlink ref="C895" r:id="rId898" xr:uid="{00000000-0004-0000-0000-000081030000}"/>
-    <hyperlink ref="C63" r:id="rId899" xr:uid="{00000000-0004-0000-0000-000082030000}"/>
-    <hyperlink ref="C896" r:id="rId900" xr:uid="{00000000-0004-0000-0000-000083030000}"/>
-    <hyperlink ref="C897" r:id="rId901" xr:uid="{00000000-0004-0000-0000-000084030000}"/>
-    <hyperlink ref="C898" r:id="rId902" xr:uid="{00000000-0004-0000-0000-000085030000}"/>
-    <hyperlink ref="C899" r:id="rId903" xr:uid="{00000000-0004-0000-0000-000086030000}"/>
-    <hyperlink ref="C900" r:id="rId904" xr:uid="{00000000-0004-0000-0000-000087030000}"/>
-    <hyperlink ref="C901" r:id="rId905" xr:uid="{00000000-0004-0000-0000-000088030000}"/>
-    <hyperlink ref="C902" r:id="rId906" xr:uid="{00000000-0004-0000-0000-000089030000}"/>
-    <hyperlink ref="C903" r:id="rId907" xr:uid="{00000000-0004-0000-0000-00008A030000}"/>
-    <hyperlink ref="C904" r:id="rId908" xr:uid="{00000000-0004-0000-0000-00008B030000}"/>
-    <hyperlink ref="C905" r:id="rId909" xr:uid="{00000000-0004-0000-0000-00008C030000}"/>
-    <hyperlink ref="C906" r:id="rId910" xr:uid="{00000000-0004-0000-0000-00008D030000}"/>
-    <hyperlink ref="C907" r:id="rId911" xr:uid="{00000000-0004-0000-0000-00008E030000}"/>
+    <hyperlink ref="C445" r:id="rId415" xr:uid="{00000000-0004-0000-0000-00009E010000}"/>
+    <hyperlink ref="C446" r:id="rId416" xr:uid="{00000000-0004-0000-0000-00009F010000}"/>
+    <hyperlink ref="C447" r:id="rId417" xr:uid="{00000000-0004-0000-0000-0000A0010000}"/>
+    <hyperlink ref="C448" r:id="rId418" xr:uid="{00000000-0004-0000-0000-0000A1010000}"/>
+    <hyperlink ref="C449" r:id="rId419" xr:uid="{00000000-0004-0000-0000-0000A2010000}"/>
+    <hyperlink ref="C450" r:id="rId420" xr:uid="{00000000-0004-0000-0000-0000A3010000}"/>
+    <hyperlink ref="C451" r:id="rId421" xr:uid="{00000000-0004-0000-0000-0000A4010000}"/>
+    <hyperlink ref="C452" r:id="rId422" xr:uid="{00000000-0004-0000-0000-0000A5010000}"/>
+    <hyperlink ref="C453" r:id="rId423" xr:uid="{00000000-0004-0000-0000-0000A6010000}"/>
+    <hyperlink ref="C454" r:id="rId424" xr:uid="{00000000-0004-0000-0000-0000A7010000}"/>
+    <hyperlink ref="C455" r:id="rId425" xr:uid="{00000000-0004-0000-0000-0000A8010000}"/>
+    <hyperlink ref="C456" r:id="rId426" xr:uid="{00000000-0004-0000-0000-0000A9010000}"/>
+    <hyperlink ref="C457" r:id="rId427" xr:uid="{00000000-0004-0000-0000-0000AA010000}"/>
+    <hyperlink ref="C458" r:id="rId428" xr:uid="{00000000-0004-0000-0000-0000AB010000}"/>
+    <hyperlink ref="C459" r:id="rId429" xr:uid="{00000000-0004-0000-0000-0000AC010000}"/>
+    <hyperlink ref="C460" r:id="rId430" xr:uid="{00000000-0004-0000-0000-0000AD010000}"/>
+    <hyperlink ref="C461" r:id="rId431" xr:uid="{00000000-0004-0000-0000-0000AE010000}"/>
+    <hyperlink ref="C462" r:id="rId432" xr:uid="{00000000-0004-0000-0000-0000AF010000}"/>
+    <hyperlink ref="C463" r:id="rId433" xr:uid="{00000000-0004-0000-0000-0000B0010000}"/>
+    <hyperlink ref="C464" r:id="rId434" xr:uid="{00000000-0004-0000-0000-0000B1010000}"/>
+    <hyperlink ref="C465" r:id="rId435" xr:uid="{00000000-0004-0000-0000-0000B2010000}"/>
+    <hyperlink ref="C466" r:id="rId436" xr:uid="{00000000-0004-0000-0000-0000B3010000}"/>
+    <hyperlink ref="C467" r:id="rId437" xr:uid="{00000000-0004-0000-0000-0000B4010000}"/>
+    <hyperlink ref="C913" r:id="rId438" xr:uid="{00000000-0004-0000-0000-0000B5010000}"/>
+    <hyperlink ref="C468" r:id="rId439" xr:uid="{00000000-0004-0000-0000-0000B6010000}"/>
+    <hyperlink ref="C469" r:id="rId440" xr:uid="{00000000-0004-0000-0000-0000B7010000}"/>
+    <hyperlink ref="C470" r:id="rId441" xr:uid="{00000000-0004-0000-0000-0000B8010000}"/>
+    <hyperlink ref="C471" r:id="rId442" xr:uid="{00000000-0004-0000-0000-0000B9010000}"/>
+    <hyperlink ref="C472" r:id="rId443" xr:uid="{00000000-0004-0000-0000-0000BA010000}"/>
+    <hyperlink ref="C473" r:id="rId444" xr:uid="{00000000-0004-0000-0000-0000BB010000}"/>
+    <hyperlink ref="C474" r:id="rId445" xr:uid="{00000000-0004-0000-0000-0000BC010000}"/>
+    <hyperlink ref="C475" r:id="rId446" xr:uid="{00000000-0004-0000-0000-0000BD010000}"/>
+    <hyperlink ref="C476" r:id="rId447" xr:uid="{00000000-0004-0000-0000-0000BE010000}"/>
+    <hyperlink ref="C477" r:id="rId448" xr:uid="{00000000-0004-0000-0000-0000BF010000}"/>
+    <hyperlink ref="C478" r:id="rId449" xr:uid="{00000000-0004-0000-0000-0000C0010000}"/>
+    <hyperlink ref="C479" r:id="rId450" xr:uid="{00000000-0004-0000-0000-0000C1010000}"/>
+    <hyperlink ref="C480" r:id="rId451" xr:uid="{00000000-0004-0000-0000-0000C2010000}"/>
+    <hyperlink ref="C481" r:id="rId452" xr:uid="{00000000-0004-0000-0000-0000C3010000}"/>
+    <hyperlink ref="C482" r:id="rId453" xr:uid="{00000000-0004-0000-0000-0000C4010000}"/>
+    <hyperlink ref="C483" r:id="rId454" xr:uid="{00000000-0004-0000-0000-0000C5010000}"/>
+    <hyperlink ref="C484" r:id="rId455" xr:uid="{00000000-0004-0000-0000-0000C6010000}"/>
+    <hyperlink ref="C485" r:id="rId456" xr:uid="{00000000-0004-0000-0000-0000C7010000}"/>
+    <hyperlink ref="C486" r:id="rId457" xr:uid="{00000000-0004-0000-0000-0000C8010000}"/>
+    <hyperlink ref="C487" r:id="rId458" xr:uid="{00000000-0004-0000-0000-0000C9010000}"/>
+    <hyperlink ref="C488" r:id="rId459" xr:uid="{00000000-0004-0000-0000-0000CA010000}"/>
+    <hyperlink ref="C489" r:id="rId460" xr:uid="{00000000-0004-0000-0000-0000CB010000}"/>
+    <hyperlink ref="C490" r:id="rId461" xr:uid="{00000000-0004-0000-0000-0000CC010000}"/>
+    <hyperlink ref="C491" r:id="rId462" xr:uid="{00000000-0004-0000-0000-0000CD010000}"/>
+    <hyperlink ref="C492" r:id="rId463" xr:uid="{00000000-0004-0000-0000-0000CE010000}"/>
+    <hyperlink ref="C493" r:id="rId464" xr:uid="{00000000-0004-0000-0000-0000CF010000}"/>
+    <hyperlink ref="C35" r:id="rId465" xr:uid="{00000000-0004-0000-0000-0000D0010000}"/>
+    <hyperlink ref="C494" r:id="rId466" xr:uid="{00000000-0004-0000-0000-0000D1010000}"/>
+    <hyperlink ref="C495" r:id="rId467" xr:uid="{00000000-0004-0000-0000-0000D2010000}"/>
+    <hyperlink ref="C496" r:id="rId468" xr:uid="{00000000-0004-0000-0000-0000D3010000}"/>
+    <hyperlink ref="C497" r:id="rId469" xr:uid="{00000000-0004-0000-0000-0000D4010000}"/>
+    <hyperlink ref="C498" r:id="rId470" xr:uid="{00000000-0004-0000-0000-0000D5010000}"/>
+    <hyperlink ref="C499" r:id="rId471" xr:uid="{00000000-0004-0000-0000-0000D6010000}"/>
+    <hyperlink ref="C500" r:id="rId472" xr:uid="{00000000-0004-0000-0000-0000D7010000}"/>
+    <hyperlink ref="C501" r:id="rId473" xr:uid="{00000000-0004-0000-0000-0000D8010000}"/>
+    <hyperlink ref="C36" r:id="rId474" xr:uid="{00000000-0004-0000-0000-0000D9010000}"/>
+    <hyperlink ref="C502" r:id="rId475" xr:uid="{00000000-0004-0000-0000-0000DA010000}"/>
+    <hyperlink ref="C503" r:id="rId476" xr:uid="{00000000-0004-0000-0000-0000DB010000}"/>
+    <hyperlink ref="C504" r:id="rId477" xr:uid="{00000000-0004-0000-0000-0000DC010000}"/>
+    <hyperlink ref="C505" r:id="rId478" xr:uid="{00000000-0004-0000-0000-0000DD010000}"/>
+    <hyperlink ref="C506" r:id="rId479" xr:uid="{00000000-0004-0000-0000-0000DE010000}"/>
+    <hyperlink ref="C507" r:id="rId480" xr:uid="{00000000-0004-0000-0000-0000DF010000}"/>
+    <hyperlink ref="C914" r:id="rId481" xr:uid="{00000000-0004-0000-0000-0000E0010000}"/>
+    <hyperlink ref="C508" r:id="rId482" xr:uid="{00000000-0004-0000-0000-0000E1010000}"/>
+    <hyperlink ref="C509" r:id="rId483" xr:uid="{00000000-0004-0000-0000-0000E2010000}"/>
+    <hyperlink ref="C510" r:id="rId484" xr:uid="{00000000-0004-0000-0000-0000E3010000}"/>
+    <hyperlink ref="C511" r:id="rId485" xr:uid="{00000000-0004-0000-0000-0000E4010000}"/>
+    <hyperlink ref="C512" r:id="rId486" xr:uid="{00000000-0004-0000-0000-0000E5010000}"/>
+    <hyperlink ref="C513" r:id="rId487" xr:uid="{00000000-0004-0000-0000-0000E6010000}"/>
+    <hyperlink ref="C514" r:id="rId488" xr:uid="{00000000-0004-0000-0000-0000E7010000}"/>
+    <hyperlink ref="C515" r:id="rId489" xr:uid="{00000000-0004-0000-0000-0000E8010000}"/>
+    <hyperlink ref="C516" r:id="rId490" xr:uid="{00000000-0004-0000-0000-0000E9010000}"/>
+    <hyperlink ref="C517" r:id="rId491" xr:uid="{00000000-0004-0000-0000-0000EA010000}"/>
+    <hyperlink ref="C518" r:id="rId492" xr:uid="{00000000-0004-0000-0000-0000EB010000}"/>
+    <hyperlink ref="C519" r:id="rId493" xr:uid="{00000000-0004-0000-0000-0000EC010000}"/>
+    <hyperlink ref="C520" r:id="rId494" xr:uid="{00000000-0004-0000-0000-0000ED010000}"/>
+    <hyperlink ref="C521" r:id="rId495" xr:uid="{00000000-0004-0000-0000-0000EE010000}"/>
+    <hyperlink ref="C522" r:id="rId496" xr:uid="{00000000-0004-0000-0000-0000EF010000}"/>
+    <hyperlink ref="C523" r:id="rId497" xr:uid="{00000000-0004-0000-0000-0000F0010000}"/>
+    <hyperlink ref="C37" r:id="rId498" xr:uid="{00000000-0004-0000-0000-0000F1010000}"/>
+    <hyperlink ref="C524" r:id="rId499" xr:uid="{00000000-0004-0000-0000-0000F2010000}"/>
+    <hyperlink ref="C525" r:id="rId500" xr:uid="{00000000-0004-0000-0000-0000F3010000}"/>
+    <hyperlink ref="C526" r:id="rId501" xr:uid="{00000000-0004-0000-0000-0000F4010000}"/>
+    <hyperlink ref="C527" r:id="rId502" xr:uid="{00000000-0004-0000-0000-0000F5010000}"/>
+    <hyperlink ref="C528" r:id="rId503" xr:uid="{00000000-0004-0000-0000-0000F6010000}"/>
+    <hyperlink ref="C529" r:id="rId504" xr:uid="{00000000-0004-0000-0000-0000F7010000}"/>
+    <hyperlink ref="C38" r:id="rId505" xr:uid="{00000000-0004-0000-0000-0000F8010000}"/>
+    <hyperlink ref="C530" r:id="rId506" xr:uid="{00000000-0004-0000-0000-0000F9010000}"/>
+    <hyperlink ref="C531" r:id="rId507" xr:uid="{00000000-0004-0000-0000-0000FA010000}"/>
+    <hyperlink ref="C532" r:id="rId508" xr:uid="{00000000-0004-0000-0000-0000FB010000}"/>
+    <hyperlink ref="C533" r:id="rId509" xr:uid="{00000000-0004-0000-0000-0000FC010000}"/>
+    <hyperlink ref="C534" r:id="rId510" xr:uid="{00000000-0004-0000-0000-0000FD010000}"/>
+    <hyperlink ref="C535" r:id="rId511" xr:uid="{00000000-0004-0000-0000-0000FE010000}"/>
+    <hyperlink ref="C536" r:id="rId512" xr:uid="{00000000-0004-0000-0000-0000FF010000}"/>
+    <hyperlink ref="C537" r:id="rId513" xr:uid="{00000000-0004-0000-0000-000000020000}"/>
+    <hyperlink ref="C538" r:id="rId514" xr:uid="{00000000-0004-0000-0000-000001020000}"/>
+    <hyperlink ref="C539" r:id="rId515" xr:uid="{00000000-0004-0000-0000-000002020000}"/>
+    <hyperlink ref="C540" r:id="rId516" xr:uid="{00000000-0004-0000-0000-000003020000}"/>
+    <hyperlink ref="C541" r:id="rId517" xr:uid="{00000000-0004-0000-0000-000004020000}"/>
+    <hyperlink ref="C542" r:id="rId518" xr:uid="{00000000-0004-0000-0000-000005020000}"/>
+    <hyperlink ref="C39" r:id="rId519" xr:uid="{00000000-0004-0000-0000-000006020000}"/>
+    <hyperlink ref="C543" r:id="rId520" xr:uid="{00000000-0004-0000-0000-000007020000}"/>
+    <hyperlink ref="C544" r:id="rId521" xr:uid="{00000000-0004-0000-0000-000008020000}"/>
+    <hyperlink ref="C545" r:id="rId522" xr:uid="{00000000-0004-0000-0000-000009020000}"/>
+    <hyperlink ref="C546" r:id="rId523" xr:uid="{00000000-0004-0000-0000-00000A020000}"/>
+    <hyperlink ref="C547" r:id="rId524" xr:uid="{00000000-0004-0000-0000-00000B020000}"/>
+    <hyperlink ref="C548" r:id="rId525" xr:uid="{00000000-0004-0000-0000-00000C020000}"/>
+    <hyperlink ref="C549" r:id="rId526" xr:uid="{00000000-0004-0000-0000-00000D020000}"/>
+    <hyperlink ref="C550" r:id="rId527" xr:uid="{00000000-0004-0000-0000-00000E020000}"/>
+    <hyperlink ref="C551" r:id="rId528" xr:uid="{00000000-0004-0000-0000-00000F020000}"/>
+    <hyperlink ref="C552" r:id="rId529" xr:uid="{00000000-0004-0000-0000-000010020000}"/>
+    <hyperlink ref="C40" r:id="rId530" xr:uid="{00000000-0004-0000-0000-000011020000}"/>
+    <hyperlink ref="C553" r:id="rId531" xr:uid="{00000000-0004-0000-0000-000012020000}"/>
+    <hyperlink ref="C554" r:id="rId532" xr:uid="{00000000-0004-0000-0000-000013020000}"/>
+    <hyperlink ref="C41" r:id="rId533" xr:uid="{00000000-0004-0000-0000-000014020000}"/>
+    <hyperlink ref="C555" r:id="rId534" xr:uid="{00000000-0004-0000-0000-000015020000}"/>
+    <hyperlink ref="C556" r:id="rId535" xr:uid="{00000000-0004-0000-0000-000016020000}"/>
+    <hyperlink ref="C557" r:id="rId536" xr:uid="{00000000-0004-0000-0000-000017020000}"/>
+    <hyperlink ref="C558" r:id="rId537" xr:uid="{00000000-0004-0000-0000-000018020000}"/>
+    <hyperlink ref="C559" r:id="rId538" xr:uid="{00000000-0004-0000-0000-000019020000}"/>
+    <hyperlink ref="C560" r:id="rId539" xr:uid="{00000000-0004-0000-0000-00001A020000}"/>
+    <hyperlink ref="C561" r:id="rId540" xr:uid="{00000000-0004-0000-0000-00001B020000}"/>
+    <hyperlink ref="C562" r:id="rId541" xr:uid="{00000000-0004-0000-0000-00001C020000}"/>
+    <hyperlink ref="C563" r:id="rId542" xr:uid="{00000000-0004-0000-0000-00001D020000}"/>
+    <hyperlink ref="C564" r:id="rId543" xr:uid="{00000000-0004-0000-0000-00001E020000}"/>
+    <hyperlink ref="C565" r:id="rId544" xr:uid="{00000000-0004-0000-0000-00001F020000}"/>
+    <hyperlink ref="C566" r:id="rId545" xr:uid="{00000000-0004-0000-0000-000020020000}"/>
+    <hyperlink ref="C567" r:id="rId546" xr:uid="{00000000-0004-0000-0000-000021020000}"/>
+    <hyperlink ref="C568" r:id="rId547" xr:uid="{00000000-0004-0000-0000-000022020000}"/>
+    <hyperlink ref="C569" r:id="rId548" xr:uid="{00000000-0004-0000-0000-000023020000}"/>
+    <hyperlink ref="C570" r:id="rId549" xr:uid="{00000000-0004-0000-0000-000024020000}"/>
+    <hyperlink ref="C571" r:id="rId550" xr:uid="{00000000-0004-0000-0000-000025020000}"/>
+    <hyperlink ref="C572" r:id="rId551" xr:uid="{00000000-0004-0000-0000-000026020000}"/>
+    <hyperlink ref="C573" r:id="rId552" xr:uid="{00000000-0004-0000-0000-000027020000}"/>
+    <hyperlink ref="C574" r:id="rId553" xr:uid="{00000000-0004-0000-0000-000028020000}"/>
+    <hyperlink ref="C575" r:id="rId554" xr:uid="{00000000-0004-0000-0000-000029020000}"/>
+    <hyperlink ref="C576" r:id="rId555" xr:uid="{00000000-0004-0000-0000-00002A020000}"/>
+    <hyperlink ref="C577" r:id="rId556" xr:uid="{00000000-0004-0000-0000-00002B020000}"/>
+    <hyperlink ref="C578" r:id="rId557" xr:uid="{00000000-0004-0000-0000-00002C020000}"/>
+    <hyperlink ref="C579" r:id="rId558" xr:uid="{00000000-0004-0000-0000-00002D020000}"/>
+    <hyperlink ref="C580" r:id="rId559" xr:uid="{00000000-0004-0000-0000-00002E020000}"/>
+    <hyperlink ref="C581" r:id="rId560" xr:uid="{00000000-0004-0000-0000-00002F020000}"/>
+    <hyperlink ref="C582" r:id="rId561" xr:uid="{00000000-0004-0000-0000-000030020000}"/>
+    <hyperlink ref="C583" r:id="rId562" xr:uid="{00000000-0004-0000-0000-000031020000}"/>
+    <hyperlink ref="C584" r:id="rId563" xr:uid="{00000000-0004-0000-0000-000032020000}"/>
+    <hyperlink ref="C585" r:id="rId564" xr:uid="{00000000-0004-0000-0000-000033020000}"/>
+    <hyperlink ref="C586" r:id="rId565" xr:uid="{00000000-0004-0000-0000-000034020000}"/>
+    <hyperlink ref="C587" r:id="rId566" xr:uid="{00000000-0004-0000-0000-000035020000}"/>
+    <hyperlink ref="C588" r:id="rId567" xr:uid="{00000000-0004-0000-0000-000036020000}"/>
+    <hyperlink ref="C589" r:id="rId568" xr:uid="{00000000-0004-0000-0000-000037020000}"/>
+    <hyperlink ref="C590" r:id="rId569" xr:uid="{00000000-0004-0000-0000-000038020000}"/>
+    <hyperlink ref="C591" r:id="rId570" xr:uid="{00000000-0004-0000-0000-000039020000}"/>
+    <hyperlink ref="C592" r:id="rId571" xr:uid="{00000000-0004-0000-0000-00003A020000}"/>
+    <hyperlink ref="C593" r:id="rId572" xr:uid="{00000000-0004-0000-0000-00003B020000}"/>
+    <hyperlink ref="C594" r:id="rId573" xr:uid="{00000000-0004-0000-0000-00003C020000}"/>
+    <hyperlink ref="C595" r:id="rId574" xr:uid="{00000000-0004-0000-0000-00003D020000}"/>
+    <hyperlink ref="C596" r:id="rId575" xr:uid="{00000000-0004-0000-0000-00003E020000}"/>
+    <hyperlink ref="C597" r:id="rId576" xr:uid="{00000000-0004-0000-0000-00003F020000}"/>
+    <hyperlink ref="C598" r:id="rId577" xr:uid="{00000000-0004-0000-0000-000040020000}"/>
+    <hyperlink ref="C599" r:id="rId578" xr:uid="{00000000-0004-0000-0000-000041020000}"/>
+    <hyperlink ref="C600" r:id="rId579" xr:uid="{00000000-0004-0000-0000-000042020000}"/>
+    <hyperlink ref="C601" r:id="rId580" xr:uid="{00000000-0004-0000-0000-000043020000}"/>
+    <hyperlink ref="C602" r:id="rId581" xr:uid="{00000000-0004-0000-0000-000044020000}"/>
+    <hyperlink ref="C603" r:id="rId582" xr:uid="{00000000-0004-0000-0000-000045020000}"/>
+    <hyperlink ref="C604" r:id="rId583" xr:uid="{00000000-0004-0000-0000-000046020000}"/>
+    <hyperlink ref="C42" r:id="rId584" xr:uid="{00000000-0004-0000-0000-000047020000}"/>
+    <hyperlink ref="C605" r:id="rId585" xr:uid="{00000000-0004-0000-0000-000048020000}"/>
+    <hyperlink ref="C606" r:id="rId586" xr:uid="{00000000-0004-0000-0000-000049020000}"/>
+    <hyperlink ref="C607" r:id="rId587" xr:uid="{00000000-0004-0000-0000-00004A020000}"/>
+    <hyperlink ref="C608" r:id="rId588" xr:uid="{00000000-0004-0000-0000-00004B020000}"/>
+    <hyperlink ref="C609" r:id="rId589" xr:uid="{00000000-0004-0000-0000-00004C020000}"/>
+    <hyperlink ref="C610" r:id="rId590" xr:uid="{00000000-0004-0000-0000-00004D020000}"/>
+    <hyperlink ref="C611" r:id="rId591" xr:uid="{00000000-0004-0000-0000-00004E020000}"/>
+    <hyperlink ref="C612" r:id="rId592" xr:uid="{00000000-0004-0000-0000-00004F020000}"/>
+    <hyperlink ref="C613" r:id="rId593" xr:uid="{00000000-0004-0000-0000-000050020000}"/>
+    <hyperlink ref="C614" r:id="rId594" xr:uid="{00000000-0004-0000-0000-000051020000}"/>
+    <hyperlink ref="C615" r:id="rId595" xr:uid="{00000000-0004-0000-0000-000052020000}"/>
+    <hyperlink ref="C616" r:id="rId596" xr:uid="{00000000-0004-0000-0000-000053020000}"/>
+    <hyperlink ref="C617" r:id="rId597" xr:uid="{00000000-0004-0000-0000-000054020000}"/>
+    <hyperlink ref="C618" r:id="rId598" xr:uid="{00000000-0004-0000-0000-000055020000}"/>
+    <hyperlink ref="C619" r:id="rId599" xr:uid="{00000000-0004-0000-0000-000056020000}"/>
+    <hyperlink ref="C620" r:id="rId600" xr:uid="{00000000-0004-0000-0000-000057020000}"/>
+    <hyperlink ref="C621" r:id="rId601" xr:uid="{00000000-0004-0000-0000-000058020000}"/>
+    <hyperlink ref="C622" r:id="rId602" xr:uid="{00000000-0004-0000-0000-000059020000}"/>
+    <hyperlink ref="C623" r:id="rId603" xr:uid="{00000000-0004-0000-0000-00005A020000}"/>
+    <hyperlink ref="C624" r:id="rId604" xr:uid="{00000000-0004-0000-0000-00005B020000}"/>
+    <hyperlink ref="C625" r:id="rId605" xr:uid="{00000000-0004-0000-0000-00005C020000}"/>
+    <hyperlink ref="C626" r:id="rId606" xr:uid="{00000000-0004-0000-0000-00005D020000}"/>
+    <hyperlink ref="C627" r:id="rId607" xr:uid="{00000000-0004-0000-0000-00005E020000}"/>
+    <hyperlink ref="C628" r:id="rId608" xr:uid="{00000000-0004-0000-0000-00005F020000}"/>
+    <hyperlink ref="C629" r:id="rId609" xr:uid="{00000000-0004-0000-0000-000060020000}"/>
+    <hyperlink ref="C630" r:id="rId610" xr:uid="{00000000-0004-0000-0000-000061020000}"/>
+    <hyperlink ref="C631" r:id="rId611" xr:uid="{00000000-0004-0000-0000-000062020000}"/>
+    <hyperlink ref="C632" r:id="rId612" xr:uid="{00000000-0004-0000-0000-000063020000}"/>
+    <hyperlink ref="C633" r:id="rId613" xr:uid="{00000000-0004-0000-0000-000064020000}"/>
+    <hyperlink ref="C43" r:id="rId614" xr:uid="{00000000-0004-0000-0000-000065020000}"/>
+    <hyperlink ref="C634" r:id="rId615" xr:uid="{00000000-0004-0000-0000-000066020000}"/>
+    <hyperlink ref="C635" r:id="rId616" xr:uid="{00000000-0004-0000-0000-000067020000}"/>
+    <hyperlink ref="C636" r:id="rId617" xr:uid="{00000000-0004-0000-0000-000068020000}"/>
+    <hyperlink ref="C637" r:id="rId618" xr:uid="{00000000-0004-0000-0000-000069020000}"/>
+    <hyperlink ref="C638" r:id="rId619" xr:uid="{00000000-0004-0000-0000-00006A020000}"/>
+    <hyperlink ref="C639" r:id="rId620" xr:uid="{00000000-0004-0000-0000-00006B020000}"/>
+    <hyperlink ref="C640" r:id="rId621" xr:uid="{00000000-0004-0000-0000-00006C020000}"/>
+    <hyperlink ref="C641" r:id="rId622" xr:uid="{00000000-0004-0000-0000-00006D020000}"/>
+    <hyperlink ref="C642" r:id="rId623" xr:uid="{00000000-0004-0000-0000-00006E020000}"/>
+    <hyperlink ref="C643" r:id="rId624" xr:uid="{00000000-0004-0000-0000-00006F020000}"/>
+    <hyperlink ref="C644" r:id="rId625" xr:uid="{00000000-0004-0000-0000-000070020000}"/>
+    <hyperlink ref="C645" r:id="rId626" xr:uid="{00000000-0004-0000-0000-000071020000}"/>
+    <hyperlink ref="C646" r:id="rId627" xr:uid="{00000000-0004-0000-0000-000072020000}"/>
+    <hyperlink ref="C647" r:id="rId628" xr:uid="{00000000-0004-0000-0000-000073020000}"/>
+    <hyperlink ref="C648" r:id="rId629" xr:uid="{00000000-0004-0000-0000-000074020000}"/>
+    <hyperlink ref="C649" r:id="rId630" xr:uid="{00000000-0004-0000-0000-000075020000}"/>
+    <hyperlink ref="C650" r:id="rId631" xr:uid="{00000000-0004-0000-0000-000076020000}"/>
+    <hyperlink ref="C651" r:id="rId632" xr:uid="{00000000-0004-0000-0000-000077020000}"/>
+    <hyperlink ref="C652" r:id="rId633" xr:uid="{00000000-0004-0000-0000-000078020000}"/>
+    <hyperlink ref="C653" r:id="rId634" xr:uid="{00000000-0004-0000-0000-000079020000}"/>
+    <hyperlink ref="C654" r:id="rId635" xr:uid="{00000000-0004-0000-0000-00007A020000}"/>
+    <hyperlink ref="C655" r:id="rId636" xr:uid="{00000000-0004-0000-0000-00007B020000}"/>
+    <hyperlink ref="C656" r:id="rId637" xr:uid="{00000000-0004-0000-0000-00007C020000}"/>
+    <hyperlink ref="C657" r:id="rId638" xr:uid="{00000000-0004-0000-0000-00007D020000}"/>
+    <hyperlink ref="C658" r:id="rId639" xr:uid="{00000000-0004-0000-0000-00007E020000}"/>
+    <hyperlink ref="C659" r:id="rId640" xr:uid="{00000000-0004-0000-0000-00007F020000}"/>
+    <hyperlink ref="C660" r:id="rId641" xr:uid="{00000000-0004-0000-0000-000080020000}"/>
+    <hyperlink ref="C661" r:id="rId642" xr:uid="{00000000-0004-0000-0000-000081020000}"/>
+    <hyperlink ref="C662" r:id="rId643" xr:uid="{00000000-0004-0000-0000-000082020000}"/>
+    <hyperlink ref="C663" r:id="rId644" xr:uid="{00000000-0004-0000-0000-000083020000}"/>
+    <hyperlink ref="C664" r:id="rId645" xr:uid="{00000000-0004-0000-0000-000084020000}"/>
+    <hyperlink ref="C665" r:id="rId646" xr:uid="{00000000-0004-0000-0000-000085020000}"/>
+    <hyperlink ref="C666" r:id="rId647" xr:uid="{00000000-0004-0000-0000-000086020000}"/>
+    <hyperlink ref="C667" r:id="rId648" xr:uid="{00000000-0004-0000-0000-000087020000}"/>
+    <hyperlink ref="C668" r:id="rId649" xr:uid="{00000000-0004-0000-0000-000088020000}"/>
+    <hyperlink ref="C669" r:id="rId650" xr:uid="{00000000-0004-0000-0000-000089020000}"/>
+    <hyperlink ref="C670" r:id="rId651" xr:uid="{00000000-0004-0000-0000-00008A020000}"/>
+    <hyperlink ref="C671" r:id="rId652" xr:uid="{00000000-0004-0000-0000-00008B020000}"/>
+    <hyperlink ref="C672" r:id="rId653" xr:uid="{00000000-0004-0000-0000-00008C020000}"/>
+    <hyperlink ref="C673" r:id="rId654" xr:uid="{00000000-0004-0000-0000-00008D020000}"/>
+    <hyperlink ref="C674" r:id="rId655" xr:uid="{00000000-0004-0000-0000-00008E020000}"/>
+    <hyperlink ref="C44" r:id="rId656" xr:uid="{00000000-0004-0000-0000-00008F020000}"/>
+    <hyperlink ref="C675" r:id="rId657" xr:uid="{00000000-0004-0000-0000-000090020000}"/>
+    <hyperlink ref="C676" r:id="rId658" xr:uid="{00000000-0004-0000-0000-000091020000}"/>
+    <hyperlink ref="C677" r:id="rId659" xr:uid="{00000000-0004-0000-0000-000092020000}"/>
+    <hyperlink ref="C678" r:id="rId660" xr:uid="{00000000-0004-0000-0000-000093020000}"/>
+    <hyperlink ref="C679" r:id="rId661" xr:uid="{00000000-0004-0000-0000-000094020000}"/>
+    <hyperlink ref="C680" r:id="rId662" xr:uid="{00000000-0004-0000-0000-000095020000}"/>
+    <hyperlink ref="C681" r:id="rId663" xr:uid="{00000000-0004-0000-0000-000096020000}"/>
+    <hyperlink ref="C682" r:id="rId664" xr:uid="{00000000-0004-0000-0000-000097020000}"/>
+    <hyperlink ref="C683" r:id="rId665" xr:uid="{00000000-0004-0000-0000-000098020000}"/>
+    <hyperlink ref="C684" r:id="rId666" xr:uid="{00000000-0004-0000-0000-000099020000}"/>
+    <hyperlink ref="C685" r:id="rId667" xr:uid="{00000000-0004-0000-0000-00009A020000}"/>
+    <hyperlink ref="C686" r:id="rId668" xr:uid="{00000000-0004-0000-0000-00009B020000}"/>
+    <hyperlink ref="C687" r:id="rId669" xr:uid="{00000000-0004-0000-0000-00009C020000}"/>
+    <hyperlink ref="C688" r:id="rId670" xr:uid="{00000000-0004-0000-0000-00009D020000}"/>
+    <hyperlink ref="C689" r:id="rId671" xr:uid="{00000000-0004-0000-0000-00009E020000}"/>
+    <hyperlink ref="C690" r:id="rId672" xr:uid="{00000000-0004-0000-0000-00009F020000}"/>
+    <hyperlink ref="C691" r:id="rId673" xr:uid="{00000000-0004-0000-0000-0000A0020000}"/>
+    <hyperlink ref="C692" r:id="rId674" xr:uid="{00000000-0004-0000-0000-0000A1020000}"/>
+    <hyperlink ref="C693" r:id="rId675" xr:uid="{00000000-0004-0000-0000-0000A2020000}"/>
+    <hyperlink ref="C694" r:id="rId676" xr:uid="{00000000-0004-0000-0000-0000A3020000}"/>
+    <hyperlink ref="C695" r:id="rId677" xr:uid="{00000000-0004-0000-0000-0000A4020000}"/>
+    <hyperlink ref="C696" r:id="rId678" xr:uid="{00000000-0004-0000-0000-0000A5020000}"/>
+    <hyperlink ref="C697" r:id="rId679" xr:uid="{00000000-0004-0000-0000-0000A6020000}"/>
+    <hyperlink ref="C698" r:id="rId680" xr:uid="{00000000-0004-0000-0000-0000A7020000}"/>
+    <hyperlink ref="C699" r:id="rId681" xr:uid="{00000000-0004-0000-0000-0000A8020000}"/>
+    <hyperlink ref="C700" r:id="rId682" xr:uid="{00000000-0004-0000-0000-0000A9020000}"/>
+    <hyperlink ref="C701" r:id="rId683" xr:uid="{00000000-0004-0000-0000-0000AA020000}"/>
+    <hyperlink ref="C702" r:id="rId684" xr:uid="{00000000-0004-0000-0000-0000AB020000}"/>
+    <hyperlink ref="C703" r:id="rId685" xr:uid="{00000000-0004-0000-0000-0000AC020000}"/>
+    <hyperlink ref="C704" r:id="rId686" xr:uid="{00000000-0004-0000-0000-0000AD020000}"/>
+    <hyperlink ref="C705" r:id="rId687" xr:uid="{00000000-0004-0000-0000-0000AE020000}"/>
+    <hyperlink ref="C706" r:id="rId688" xr:uid="{00000000-0004-0000-0000-0000AF020000}"/>
+    <hyperlink ref="C707" r:id="rId689" xr:uid="{00000000-0004-0000-0000-0000B0020000}"/>
+    <hyperlink ref="C708" r:id="rId690" xr:uid="{00000000-0004-0000-0000-0000B1020000}"/>
+    <hyperlink ref="C709" r:id="rId691" xr:uid="{00000000-0004-0000-0000-0000B2020000}"/>
+    <hyperlink ref="C710" r:id="rId692" xr:uid="{00000000-0004-0000-0000-0000B3020000}"/>
+    <hyperlink ref="C711" r:id="rId693" xr:uid="{00000000-0004-0000-0000-0000B4020000}"/>
+    <hyperlink ref="C712" r:id="rId694" xr:uid="{00000000-0004-0000-0000-0000B5020000}"/>
+    <hyperlink ref="C713" r:id="rId695" xr:uid="{00000000-0004-0000-0000-0000B6020000}"/>
+    <hyperlink ref="C45" r:id="rId696" xr:uid="{00000000-0004-0000-0000-0000B7020000}"/>
+    <hyperlink ref="C714" r:id="rId697" xr:uid="{00000000-0004-0000-0000-0000B8020000}"/>
+    <hyperlink ref="C715" r:id="rId698" xr:uid="{00000000-0004-0000-0000-0000B9020000}"/>
+    <hyperlink ref="C716" r:id="rId699" xr:uid="{00000000-0004-0000-0000-0000BA020000}"/>
+    <hyperlink ref="C717" r:id="rId700" xr:uid="{00000000-0004-0000-0000-0000BB020000}"/>
+    <hyperlink ref="C718" r:id="rId701" xr:uid="{00000000-0004-0000-0000-0000BC020000}"/>
+    <hyperlink ref="C719" r:id="rId702" xr:uid="{00000000-0004-0000-0000-0000BD020000}"/>
+    <hyperlink ref="C720" r:id="rId703" xr:uid="{00000000-0004-0000-0000-0000BE020000}"/>
+    <hyperlink ref="C721" r:id="rId704" xr:uid="{00000000-0004-0000-0000-0000BF020000}"/>
+    <hyperlink ref="C722" r:id="rId705" xr:uid="{00000000-0004-0000-0000-0000C0020000}"/>
+    <hyperlink ref="C723" r:id="rId706" xr:uid="{00000000-0004-0000-0000-0000C1020000}"/>
+    <hyperlink ref="C724" r:id="rId707" xr:uid="{00000000-0004-0000-0000-0000C2020000}"/>
+    <hyperlink ref="C725" r:id="rId708" xr:uid="{00000000-0004-0000-0000-0000C3020000}"/>
+    <hyperlink ref="C726" r:id="rId709" xr:uid="{00000000-0004-0000-0000-0000C4020000}"/>
+    <hyperlink ref="C727" r:id="rId710" xr:uid="{00000000-0004-0000-0000-0000C5020000}"/>
+    <hyperlink ref="C728" r:id="rId711" xr:uid="{00000000-0004-0000-0000-0000C6020000}"/>
+    <hyperlink ref="C46" r:id="rId712" xr:uid="{00000000-0004-0000-0000-0000C7020000}"/>
+    <hyperlink ref="C729" r:id="rId713" xr:uid="{00000000-0004-0000-0000-0000C8020000}"/>
+    <hyperlink ref="C730" r:id="rId714" xr:uid="{00000000-0004-0000-0000-0000C9020000}"/>
+    <hyperlink ref="C731" r:id="rId715" xr:uid="{00000000-0004-0000-0000-0000CA020000}"/>
+    <hyperlink ref="C732" r:id="rId716" xr:uid="{00000000-0004-0000-0000-0000CB020000}"/>
+    <hyperlink ref="C733" r:id="rId717" xr:uid="{00000000-0004-0000-0000-0000CC020000}"/>
+    <hyperlink ref="C734" r:id="rId718" xr:uid="{00000000-0004-0000-0000-0000CD020000}"/>
+    <hyperlink ref="C735" r:id="rId719" xr:uid="{00000000-0004-0000-0000-0000CE020000}"/>
+    <hyperlink ref="C736" r:id="rId720" xr:uid="{00000000-0004-0000-0000-0000CF020000}"/>
+    <hyperlink ref="C737" r:id="rId721" xr:uid="{00000000-0004-0000-0000-0000D0020000}"/>
+    <hyperlink ref="C738" r:id="rId722" xr:uid="{00000000-0004-0000-0000-0000D1020000}"/>
+    <hyperlink ref="C739" r:id="rId723" xr:uid="{00000000-0004-0000-0000-0000D2020000}"/>
+    <hyperlink ref="C740" r:id="rId724" xr:uid="{00000000-0004-0000-0000-0000D3020000}"/>
+    <hyperlink ref="C741" r:id="rId725" xr:uid="{00000000-0004-0000-0000-0000D4020000}"/>
+    <hyperlink ref="C742" r:id="rId726" xr:uid="{00000000-0004-0000-0000-0000D5020000}"/>
+    <hyperlink ref="C743" r:id="rId727" xr:uid="{00000000-0004-0000-0000-0000D6020000}"/>
+    <hyperlink ref="C47" r:id="rId728" xr:uid="{00000000-0004-0000-0000-0000D7020000}"/>
+    <hyperlink ref="C744" r:id="rId729" xr:uid="{00000000-0004-0000-0000-0000D8020000}"/>
+    <hyperlink ref="C745" r:id="rId730" xr:uid="{00000000-0004-0000-0000-0000D9020000}"/>
+    <hyperlink ref="C746" r:id="rId731" xr:uid="{00000000-0004-0000-0000-0000DA020000}"/>
+    <hyperlink ref="C747" r:id="rId732" xr:uid="{00000000-0004-0000-0000-0000DB020000}"/>
+    <hyperlink ref="C48" r:id="rId733" xr:uid="{00000000-0004-0000-0000-0000DC020000}"/>
+    <hyperlink ref="C748" r:id="rId734" xr:uid="{00000000-0004-0000-0000-0000DD020000}"/>
+    <hyperlink ref="C749" r:id="rId735" xr:uid="{00000000-0004-0000-0000-0000DE020000}"/>
+    <hyperlink ref="C49" r:id="rId736" xr:uid="{00000000-0004-0000-0000-0000DF020000}"/>
+    <hyperlink ref="C750" r:id="rId737" xr:uid="{00000000-0004-0000-0000-0000E0020000}"/>
+    <hyperlink ref="C751" r:id="rId738" xr:uid="{00000000-0004-0000-0000-0000E1020000}"/>
+    <hyperlink ref="C752" r:id="rId739" xr:uid="{00000000-0004-0000-0000-0000E2020000}"/>
+    <hyperlink ref="C753" r:id="rId740" xr:uid="{00000000-0004-0000-0000-0000E3020000}"/>
+    <hyperlink ref="C754" r:id="rId741" xr:uid="{00000000-0004-0000-0000-0000E4020000}"/>
+    <hyperlink ref="C755" r:id="rId742" xr:uid="{00000000-0004-0000-0000-0000E5020000}"/>
+    <hyperlink ref="C50" r:id="rId743" xr:uid="{00000000-0004-0000-0000-0000E6020000}"/>
+    <hyperlink ref="C756" r:id="rId744" xr:uid="{00000000-0004-0000-0000-0000E7020000}"/>
+    <hyperlink ref="C51" r:id="rId745" xr:uid="{00000000-0004-0000-0000-0000E8020000}"/>
+    <hyperlink ref="C757" r:id="rId746" xr:uid="{00000000-0004-0000-0000-0000E9020000}"/>
+    <hyperlink ref="C758" r:id="rId747" xr:uid="{00000000-0004-0000-0000-0000EA020000}"/>
+    <hyperlink ref="C759" r:id="rId748" xr:uid="{00000000-0004-0000-0000-0000EB020000}"/>
+    <hyperlink ref="C760" r:id="rId749" xr:uid="{00000000-0004-0000-0000-0000EC020000}"/>
+    <hyperlink ref="C761" r:id="rId750" xr:uid="{00000000-0004-0000-0000-0000ED020000}"/>
+    <hyperlink ref="C762" r:id="rId751" xr:uid="{00000000-0004-0000-0000-0000EE020000}"/>
+    <hyperlink ref="C763" r:id="rId752" xr:uid="{00000000-0004-0000-0000-0000EF020000}"/>
+    <hyperlink ref="C764" r:id="rId753" xr:uid="{00000000-0004-0000-0000-0000F0020000}"/>
+    <hyperlink ref="C765" r:id="rId754" xr:uid="{00000000-0004-0000-0000-0000F1020000}"/>
+    <hyperlink ref="C766" r:id="rId755" xr:uid="{00000000-0004-0000-0000-0000F2020000}"/>
+    <hyperlink ref="C767" r:id="rId756" xr:uid="{00000000-0004-0000-0000-0000F3020000}"/>
+    <hyperlink ref="C768" r:id="rId757" xr:uid="{00000000-0004-0000-0000-0000F4020000}"/>
+    <hyperlink ref="C769" r:id="rId758" xr:uid="{00000000-0004-0000-0000-0000F5020000}"/>
+    <hyperlink ref="C770" r:id="rId759" xr:uid="{00000000-0004-0000-0000-0000F6020000}"/>
+    <hyperlink ref="C771" r:id="rId760" xr:uid="{00000000-0004-0000-0000-0000F7020000}"/>
+    <hyperlink ref="C772" r:id="rId761" xr:uid="{00000000-0004-0000-0000-0000F8020000}"/>
+    <hyperlink ref="C773" r:id="rId762" xr:uid="{00000000-0004-0000-0000-0000F9020000}"/>
+    <hyperlink ref="C774" r:id="rId763" xr:uid="{00000000-0004-0000-0000-0000FA020000}"/>
+    <hyperlink ref="C775" r:id="rId764" xr:uid="{00000000-0004-0000-0000-0000FB020000}"/>
+    <hyperlink ref="C776" r:id="rId765" xr:uid="{00000000-0004-0000-0000-0000FC020000}"/>
+    <hyperlink ref="C777" r:id="rId766" xr:uid="{00000000-0004-0000-0000-0000FD020000}"/>
+    <hyperlink ref="C778" r:id="rId767" xr:uid="{00000000-0004-0000-0000-0000FE020000}"/>
+    <hyperlink ref="C779" r:id="rId768" xr:uid="{00000000-0004-0000-0000-0000FF020000}"/>
+    <hyperlink ref="C780" r:id="rId769" xr:uid="{00000000-0004-0000-0000-000000030000}"/>
+    <hyperlink ref="C781" r:id="rId770" xr:uid="{00000000-0004-0000-0000-000001030000}"/>
+    <hyperlink ref="C782" r:id="rId771" xr:uid="{00000000-0004-0000-0000-000002030000}"/>
+    <hyperlink ref="C783" r:id="rId772" xr:uid="{00000000-0004-0000-0000-000003030000}"/>
+    <hyperlink ref="C784" r:id="rId773" xr:uid="{00000000-0004-0000-0000-000004030000}"/>
+    <hyperlink ref="C785" r:id="rId774" xr:uid="{00000000-0004-0000-0000-000005030000}"/>
+    <hyperlink ref="C786" r:id="rId775" xr:uid="{00000000-0004-0000-0000-000006030000}"/>
+    <hyperlink ref="C787" r:id="rId776" xr:uid="{00000000-0004-0000-0000-000007030000}"/>
+    <hyperlink ref="C788" r:id="rId777" xr:uid="{00000000-0004-0000-0000-000008030000}"/>
+    <hyperlink ref="C789" r:id="rId778" xr:uid="{00000000-0004-0000-0000-000009030000}"/>
+    <hyperlink ref="C790" r:id="rId779" xr:uid="{00000000-0004-0000-0000-00000A030000}"/>
+    <hyperlink ref="C791" r:id="rId780" xr:uid="{00000000-0004-0000-0000-00000B030000}"/>
+    <hyperlink ref="C792" r:id="rId781" xr:uid="{00000000-0004-0000-0000-00000C030000}"/>
+    <hyperlink ref="C793" r:id="rId782" xr:uid="{00000000-0004-0000-0000-00000D030000}"/>
+    <hyperlink ref="C794" r:id="rId783" xr:uid="{00000000-0004-0000-0000-00000E030000}"/>
+    <hyperlink ref="C795" r:id="rId784" xr:uid="{00000000-0004-0000-0000-00000F030000}"/>
+    <hyperlink ref="C796" r:id="rId785" xr:uid="{00000000-0004-0000-0000-000010030000}"/>
+    <hyperlink ref="C797" r:id="rId786" xr:uid="{00000000-0004-0000-0000-000011030000}"/>
+    <hyperlink ref="C798" r:id="rId787" xr:uid="{00000000-0004-0000-0000-000012030000}"/>
+    <hyperlink ref="C52" r:id="rId788" xr:uid="{00000000-0004-0000-0000-000013030000}"/>
+    <hyperlink ref="C799" r:id="rId789" xr:uid="{00000000-0004-0000-0000-000014030000}"/>
+    <hyperlink ref="C800" r:id="rId790" xr:uid="{00000000-0004-0000-0000-000015030000}"/>
+    <hyperlink ref="C801" r:id="rId791" xr:uid="{00000000-0004-0000-0000-000016030000}"/>
+    <hyperlink ref="C802" r:id="rId792" xr:uid="{00000000-0004-0000-0000-000017030000}"/>
+    <hyperlink ref="C803" r:id="rId793" xr:uid="{00000000-0004-0000-0000-000018030000}"/>
+    <hyperlink ref="C804" r:id="rId794" xr:uid="{00000000-0004-0000-0000-000019030000}"/>
+    <hyperlink ref="C805" r:id="rId795" xr:uid="{00000000-0004-0000-0000-00001A030000}"/>
+    <hyperlink ref="C806" r:id="rId796" xr:uid="{00000000-0004-0000-0000-00001B030000}"/>
+    <hyperlink ref="C807" r:id="rId797" xr:uid="{00000000-0004-0000-0000-00001C030000}"/>
+    <hyperlink ref="C808" r:id="rId798" xr:uid="{00000000-0004-0000-0000-00001D030000}"/>
+    <hyperlink ref="C809" r:id="rId799" xr:uid="{00000000-0004-0000-0000-00001E030000}"/>
+    <hyperlink ref="C810" r:id="rId800" xr:uid="{00000000-0004-0000-0000-00001F030000}"/>
+    <hyperlink ref="C811" r:id="rId801" xr:uid="{00000000-0004-0000-0000-000020030000}"/>
+    <hyperlink ref="C812" r:id="rId802" xr:uid="{00000000-0004-0000-0000-000021030000}"/>
+    <hyperlink ref="C813" r:id="rId803" xr:uid="{00000000-0004-0000-0000-000022030000}"/>
+    <hyperlink ref="C814" r:id="rId804" xr:uid="{00000000-0004-0000-0000-000023030000}"/>
+    <hyperlink ref="C815" r:id="rId805" xr:uid="{00000000-0004-0000-0000-000024030000}"/>
+    <hyperlink ref="C816" r:id="rId806" xr:uid="{00000000-0004-0000-0000-000025030000}"/>
+    <hyperlink ref="C817" r:id="rId807" xr:uid="{00000000-0004-0000-0000-000026030000}"/>
+    <hyperlink ref="C818" r:id="rId808" xr:uid="{00000000-0004-0000-0000-000027030000}"/>
+    <hyperlink ref="C819" r:id="rId809" xr:uid="{00000000-0004-0000-0000-000028030000}"/>
+    <hyperlink ref="C820" r:id="rId810" xr:uid="{00000000-0004-0000-0000-000029030000}"/>
+    <hyperlink ref="C821" r:id="rId811" xr:uid="{00000000-0004-0000-0000-00002A030000}"/>
+    <hyperlink ref="C822" r:id="rId812" xr:uid="{00000000-0004-0000-0000-00002B030000}"/>
+    <hyperlink ref="C823" r:id="rId813" xr:uid="{00000000-0004-0000-0000-00002C030000}"/>
+    <hyperlink ref="C53" r:id="rId814" xr:uid="{00000000-0004-0000-0000-00002D030000}"/>
+    <hyperlink ref="C54" r:id="rId815" xr:uid="{00000000-0004-0000-0000-00002E030000}"/>
+    <hyperlink ref="C824" r:id="rId816" xr:uid="{00000000-0004-0000-0000-00002F030000}"/>
+    <hyperlink ref="C825" r:id="rId817" xr:uid="{00000000-0004-0000-0000-000030030000}"/>
+    <hyperlink ref="C826" r:id="rId818" xr:uid="{00000000-0004-0000-0000-000031030000}"/>
+    <hyperlink ref="C827" r:id="rId819" xr:uid="{00000000-0004-0000-0000-000032030000}"/>
+    <hyperlink ref="C828" r:id="rId820" xr:uid="{00000000-0004-0000-0000-000033030000}"/>
+    <hyperlink ref="C55" r:id="rId821" xr:uid="{00000000-0004-0000-0000-000034030000}"/>
+    <hyperlink ref="C56" r:id="rId822" xr:uid="{00000000-0004-0000-0000-000035030000}"/>
+    <hyperlink ref="C829" r:id="rId823" xr:uid="{00000000-0004-0000-0000-000036030000}"/>
+    <hyperlink ref="C830" r:id="rId824" xr:uid="{00000000-0004-0000-0000-000037030000}"/>
+    <hyperlink ref="C831" r:id="rId825" xr:uid="{00000000-0004-0000-0000-000038030000}"/>
+    <hyperlink ref="C832" r:id="rId826" xr:uid="{00000000-0004-0000-0000-000039030000}"/>
+    <hyperlink ref="C833" r:id="rId827" xr:uid="{00000000-0004-0000-0000-00003A030000}"/>
+    <hyperlink ref="C834" r:id="rId828" xr:uid="{00000000-0004-0000-0000-00003B030000}"/>
+    <hyperlink ref="C835" r:id="rId829" xr:uid="{00000000-0004-0000-0000-00003C030000}"/>
+    <hyperlink ref="C836" r:id="rId830" xr:uid="{00000000-0004-0000-0000-00003D030000}"/>
+    <hyperlink ref="C57" r:id="rId831" xr:uid="{00000000-0004-0000-0000-00003E030000}"/>
+    <hyperlink ref="C837" r:id="rId832" xr:uid="{00000000-0004-0000-0000-00003F030000}"/>
+    <hyperlink ref="C838" r:id="rId833" xr:uid="{00000000-0004-0000-0000-000040030000}"/>
+    <hyperlink ref="C839" r:id="rId834" xr:uid="{00000000-0004-0000-0000-000041030000}"/>
+    <hyperlink ref="C840" r:id="rId835" xr:uid="{00000000-0004-0000-0000-000042030000}"/>
+    <hyperlink ref="C841" r:id="rId836" xr:uid="{00000000-0004-0000-0000-000043030000}"/>
+    <hyperlink ref="C842" r:id="rId837" xr:uid="{00000000-0004-0000-0000-000044030000}"/>
+    <hyperlink ref="C843" r:id="rId838" xr:uid="{00000000-0004-0000-0000-000045030000}"/>
+    <hyperlink ref="C844" r:id="rId839" xr:uid="{00000000-0004-0000-0000-000046030000}"/>
+    <hyperlink ref="C845" r:id="rId840" xr:uid="{00000000-0004-0000-0000-000047030000}"/>
+    <hyperlink ref="C58" r:id="rId841" xr:uid="{00000000-0004-0000-0000-000048030000}"/>
+    <hyperlink ref="C846" r:id="rId842" xr:uid="{00000000-0004-0000-0000-000049030000}"/>
+    <hyperlink ref="C847" r:id="rId843" xr:uid="{00000000-0004-0000-0000-00004A030000}"/>
+    <hyperlink ref="C848" r:id="rId844" xr:uid="{00000000-0004-0000-0000-00004B030000}"/>
+    <hyperlink ref="C849" r:id="rId845" xr:uid="{00000000-0004-0000-0000-00004C030000}"/>
+    <hyperlink ref="C850" r:id="rId846" xr:uid="{00000000-0004-0000-0000-00004D030000}"/>
+    <hyperlink ref="C851" r:id="rId847" xr:uid="{00000000-0004-0000-0000-00004E030000}"/>
+    <hyperlink ref="C852" r:id="rId848" xr:uid="{00000000-0004-0000-0000-00004F030000}"/>
+    <hyperlink ref="C853" r:id="rId849" xr:uid="{00000000-0004-0000-0000-000050030000}"/>
+    <hyperlink ref="C854" r:id="rId850" xr:uid="{00000000-0004-0000-0000-000051030000}"/>
+    <hyperlink ref="C855" r:id="rId851" xr:uid="{00000000-0004-0000-0000-000052030000}"/>
+    <hyperlink ref="C856" r:id="rId852" xr:uid="{00000000-0004-0000-0000-000053030000}"/>
+    <hyperlink ref="C857" r:id="rId853" xr:uid="{00000000-0004-0000-0000-000054030000}"/>
+    <hyperlink ref="C59" r:id="rId854" xr:uid="{00000000-0004-0000-0000-000055030000}"/>
+    <hyperlink ref="C858" r:id="rId855" xr:uid="{00000000-0004-0000-0000-000056030000}"/>
+    <hyperlink ref="C859" r:id="rId856" xr:uid="{00000000-0004-0000-0000-000057030000}"/>
+    <hyperlink ref="C860" r:id="rId857" xr:uid="{00000000-0004-0000-0000-000058030000}"/>
+    <hyperlink ref="C861" r:id="rId858" xr:uid="{00000000-0004-0000-0000-000059030000}"/>
+    <hyperlink ref="C862" r:id="rId859" xr:uid="{00000000-0004-0000-0000-00005A030000}"/>
+    <hyperlink ref="C863" r:id="rId860" xr:uid="{00000000-0004-0000-0000-00005B030000}"/>
+    <hyperlink ref="C864" r:id="rId861" xr:uid="{00000000-0004-0000-0000-00005C030000}"/>
+    <hyperlink ref="C865" r:id="rId862" xr:uid="{00000000-0004-0000-0000-00005D030000}"/>
+    <hyperlink ref="C866" r:id="rId863" xr:uid="{00000000-0004-0000-0000-00005E030000}"/>
+    <hyperlink ref="C867" r:id="rId864" xr:uid="{00000000-0004-0000-0000-00005F030000}"/>
+    <hyperlink ref="C868" r:id="rId865" xr:uid="{00000000-0004-0000-0000-000060030000}"/>
+    <hyperlink ref="C869" r:id="rId866" xr:uid="{00000000-0004-0000-0000-000061030000}"/>
+    <hyperlink ref="C870" r:id="rId867" xr:uid="{00000000-0004-0000-0000-000062030000}"/>
+    <hyperlink ref="C871" r:id="rId868" xr:uid="{00000000-0004-0000-0000-000063030000}"/>
+    <hyperlink ref="C872" r:id="rId869" xr:uid="{00000000-0004-0000-0000-000064030000}"/>
+    <hyperlink ref="C873" r:id="rId870" xr:uid="{00000000-0004-0000-0000-000065030000}"/>
+    <hyperlink ref="C874" r:id="rId871" xr:uid="{00000000-0004-0000-0000-000066030000}"/>
+    <hyperlink ref="C875" r:id="rId872" xr:uid="{00000000-0004-0000-0000-000067030000}"/>
+    <hyperlink ref="C876" r:id="rId873" xr:uid="{00000000-0004-0000-0000-000068030000}"/>
+    <hyperlink ref="C877" r:id="rId874" xr:uid="{00000000-0004-0000-0000-000069030000}"/>
+    <hyperlink ref="C878" r:id="rId875" xr:uid="{00000000-0004-0000-0000-00006A030000}"/>
+    <hyperlink ref="C879" r:id="rId876" xr:uid="{00000000-0004-0000-0000-00006B030000}"/>
+    <hyperlink ref="C60" r:id="rId877" xr:uid="{00000000-0004-0000-0000-00006C030000}"/>
+    <hyperlink ref="C880" r:id="rId878" xr:uid="{00000000-0004-0000-0000-00006D030000}"/>
+    <hyperlink ref="C881" r:id="rId879" xr:uid="{00000000-0004-0000-0000-00006E030000}"/>
+    <hyperlink ref="C882" r:id="rId880" xr:uid="{00000000-0004-0000-0000-00006F030000}"/>
+    <hyperlink ref="C883" r:id="rId881" xr:uid="{00000000-0004-0000-0000-000070030000}"/>
+    <hyperlink ref="C884" r:id="rId882" xr:uid="{00000000-0004-0000-0000-000071030000}"/>
+    <hyperlink ref="C61" r:id="rId883" xr:uid="{00000000-0004-0000-0000-000072030000}"/>
+    <hyperlink ref="C885" r:id="rId884" xr:uid="{00000000-0004-0000-0000-000073030000}"/>
+    <hyperlink ref="C886" r:id="rId885" xr:uid="{00000000-0004-0000-0000-000074030000}"/>
+    <hyperlink ref="C887" r:id="rId886" xr:uid="{00000000-0004-0000-0000-000075030000}"/>
+    <hyperlink ref="C62" r:id="rId887" xr:uid="{00000000-0004-0000-0000-000076030000}"/>
+    <hyperlink ref="C888" r:id="rId888" xr:uid="{00000000-0004-0000-0000-000077030000}"/>
+    <hyperlink ref="C889" r:id="rId889" xr:uid="{00000000-0004-0000-0000-000078030000}"/>
+    <hyperlink ref="C890" r:id="rId890" xr:uid="{00000000-0004-0000-0000-000079030000}"/>
+    <hyperlink ref="C891" r:id="rId891" xr:uid="{00000000-0004-0000-0000-00007A030000}"/>
+    <hyperlink ref="C892" r:id="rId892" xr:uid="{00000000-0004-0000-0000-00007B030000}"/>
+    <hyperlink ref="C893" r:id="rId893" xr:uid="{00000000-0004-0000-0000-00007C030000}"/>
+    <hyperlink ref="C894" r:id="rId894" xr:uid="{00000000-0004-0000-0000-00007D030000}"/>
+    <hyperlink ref="C895" r:id="rId895" xr:uid="{00000000-0004-0000-0000-00007E030000}"/>
+    <hyperlink ref="C896" r:id="rId896" xr:uid="{00000000-0004-0000-0000-00007F030000}"/>
+    <hyperlink ref="C897" r:id="rId897" xr:uid="{00000000-0004-0000-0000-000080030000}"/>
+    <hyperlink ref="C898" r:id="rId898" xr:uid="{00000000-0004-0000-0000-000081030000}"/>
+    <hyperlink ref="C899" r:id="rId899" xr:uid="{00000000-0004-0000-0000-000082030000}"/>
+    <hyperlink ref="C900" r:id="rId900" xr:uid="{00000000-0004-0000-0000-000083030000}"/>
+    <hyperlink ref="C63" r:id="rId901" xr:uid="{00000000-0004-0000-0000-000084030000}"/>
+    <hyperlink ref="C901" r:id="rId902" xr:uid="{00000000-0004-0000-0000-000085030000}"/>
+    <hyperlink ref="C902" r:id="rId903" xr:uid="{00000000-0004-0000-0000-000086030000}"/>
+    <hyperlink ref="C903" r:id="rId904" xr:uid="{00000000-0004-0000-0000-000087030000}"/>
+    <hyperlink ref="C904" r:id="rId905" xr:uid="{00000000-0004-0000-0000-000088030000}"/>
+    <hyperlink ref="C905" r:id="rId906" xr:uid="{00000000-0004-0000-0000-000089030000}"/>
+    <hyperlink ref="C906" r:id="rId907" xr:uid="{00000000-0004-0000-0000-00008A030000}"/>
+    <hyperlink ref="C907" r:id="rId908" xr:uid="{00000000-0004-0000-0000-00008B030000}"/>
+    <hyperlink ref="C908" r:id="rId909" xr:uid="{00000000-0004-0000-0000-00008C030000}"/>
+    <hyperlink ref="C909" r:id="rId910" xr:uid="{00000000-0004-0000-0000-00008D030000}"/>
+    <hyperlink ref="C910" r:id="rId911" xr:uid="{00000000-0004-0000-0000-00008E030000}"/>
+    <hyperlink ref="C911" r:id="rId912" xr:uid="{00000000-0004-0000-0000-00008F030000}"/>
+    <hyperlink ref="C912" r:id="rId913" xr:uid="{00000000-0004-0000-0000-000090030000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19632,7 +19674,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>1826</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -19640,26 +19682,26 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>1827</v>
+        <v>1831</v>
       </c>
       <c r="B3" t="s">
-        <v>1828</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>1829</v>
+        <v>1833</v>
       </c>
       <c r="B4" t="s">
-        <v>1830</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>1831</v>
+        <v>1835</v>
       </c>
       <c r="B5" t="s">
-        <v>1832</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -19667,26 +19709,26 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>1833</v>
+        <v>1837</v>
       </c>
       <c r="B7" t="s">
-        <v>1834</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>1833</v>
+        <v>1837</v>
       </c>
       <c r="B8" t="s">
-        <v>1835</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>1833</v>
+        <v>1837</v>
       </c>
       <c r="B9" t="s">
-        <v>1836</v>
+        <v>1840</v>
       </c>
     </row>
   </sheetData>

--- a/data/danish_artwork_review.xlsx
+++ b/data/danish_artwork_review.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EPGoal\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1FA2325-C22F-4E93-9C0E-7D1926092C4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2257F572-88AF-4F5B-A5CF-1AB6D85636EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="23520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Danske backdrops" sheetId="1" r:id="rId1"/>
@@ -19073,10 +19073,10 @@
     </row>
     <row r="829" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A829" t="s">
-        <v>1630</v>
+        <v>1628</v>
       </c>
       <c r="B829" t="s">
-        <v>1631</v>
+        <v>1629</v>
       </c>
       <c r="C829" s="2" t="s">
         <v>7</v>
@@ -19087,10 +19087,10 @@
     </row>
     <row r="830" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A830" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="B830" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
       <c r="C830" s="2" t="s">
         <v>7</v>
@@ -19101,10 +19101,10 @@
     </row>
     <row r="831" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A831" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="B831" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
       <c r="C831" s="2" t="s">
         <v>7</v>
@@ -19115,10 +19115,10 @@
     </row>
     <row r="832" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A832" t="s">
-        <v>1636</v>
+        <v>1634</v>
       </c>
       <c r="B832" t="s">
-        <v>1637</v>
+        <v>1635</v>
       </c>
       <c r="C832" s="2" t="s">
         <v>7</v>
@@ -19129,10 +19129,10 @@
     </row>
     <row r="833" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A833" t="s">
-        <v>1638</v>
+        <v>1636</v>
       </c>
       <c r="B833" t="s">
-        <v>1639</v>
+        <v>1637</v>
       </c>
       <c r="C833" s="2" t="s">
         <v>7</v>
@@ -19143,10 +19143,10 @@
     </row>
     <row r="834" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A834" t="s">
-        <v>1640</v>
+        <v>1638</v>
       </c>
       <c r="B834" t="s">
-        <v>1641</v>
+        <v>1639</v>
       </c>
       <c r="C834" s="2" t="s">
         <v>7</v>
@@ -19157,10 +19157,10 @@
     </row>
     <row r="835" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A835" t="s">
-        <v>1642</v>
+        <v>1640</v>
       </c>
       <c r="B835" t="s">
-        <v>1643</v>
+        <v>1641</v>
       </c>
       <c r="C835" s="2" t="s">
         <v>7</v>
@@ -19171,10 +19171,10 @@
     </row>
     <row r="836" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A836" t="s">
-        <v>1644</v>
+        <v>1642</v>
       </c>
       <c r="B836" t="s">
-        <v>1645</v>
+        <v>1643</v>
       </c>
       <c r="C836" s="2" t="s">
         <v>7</v>
@@ -19185,10 +19185,10 @@
     </row>
     <row r="837" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A837" t="s">
-        <v>1646</v>
+        <v>1644</v>
       </c>
       <c r="B837" t="s">
-        <v>1647</v>
+        <v>1645</v>
       </c>
       <c r="C837" s="2" t="s">
         <v>7</v>
@@ -19199,10 +19199,10 @@
     </row>
     <row r="838" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A838" t="s">
-        <v>1648</v>
+        <v>1646</v>
       </c>
       <c r="B838" t="s">
-        <v>1649</v>
+        <v>1647</v>
       </c>
       <c r="C838" s="2" t="s">
         <v>7</v>
@@ -19213,10 +19213,10 @@
     </row>
     <row r="839" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A839" t="s">
-        <v>1650</v>
+        <v>1648</v>
       </c>
       <c r="B839" t="s">
-        <v>1651</v>
+        <v>1649</v>
       </c>
       <c r="C839" s="2" t="s">
         <v>7</v>
@@ -19227,10 +19227,10 @@
     </row>
     <row r="840" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A840" t="s">
-        <v>1652</v>
+        <v>1650</v>
       </c>
       <c r="B840" t="s">
-        <v>1653</v>
+        <v>1651</v>
       </c>
       <c r="C840" s="2" t="s">
         <v>7</v>
@@ -19241,10 +19241,10 @@
     </row>
     <row r="841" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A841" t="s">
-        <v>1654</v>
+        <v>1652</v>
       </c>
       <c r="B841" t="s">
-        <v>1655</v>
+        <v>1653</v>
       </c>
       <c r="C841" s="2" t="s">
         <v>7</v>
@@ -19255,10 +19255,10 @@
     </row>
     <row r="842" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A842" t="s">
-        <v>1656</v>
+        <v>1654</v>
       </c>
       <c r="B842" t="s">
-        <v>1657</v>
+        <v>1655</v>
       </c>
       <c r="C842" s="2" t="s">
         <v>7</v>
@@ -19269,10 +19269,10 @@
     </row>
     <row r="843" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A843" t="s">
-        <v>1658</v>
+        <v>1656</v>
       </c>
       <c r="B843" t="s">
-        <v>1659</v>
+        <v>1657</v>
       </c>
       <c r="C843" s="2" t="s">
         <v>7</v>
@@ -19283,10 +19283,10 @@
     </row>
     <row r="844" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A844" t="s">
-        <v>1660</v>
+        <v>1658</v>
       </c>
       <c r="B844" t="s">
-        <v>1661</v>
+        <v>1659</v>
       </c>
       <c r="C844" s="2" t="s">
         <v>7</v>
@@ -19297,10 +19297,10 @@
     </row>
     <row r="845" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A845" t="s">
-        <v>1662</v>
+        <v>1660</v>
       </c>
       <c r="B845" t="s">
-        <v>1663</v>
+        <v>1661</v>
       </c>
       <c r="C845" s="2" t="s">
         <v>7</v>
@@ -19311,10 +19311,10 @@
     </row>
     <row r="846" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A846" t="s">
-        <v>1664</v>
+        <v>1662</v>
       </c>
       <c r="B846" t="s">
-        <v>1665</v>
+        <v>1663</v>
       </c>
       <c r="C846" s="2" t="s">
         <v>7</v>
@@ -19325,10 +19325,10 @@
     </row>
     <row r="847" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A847" t="s">
-        <v>1666</v>
+        <v>1664</v>
       </c>
       <c r="B847" t="s">
-        <v>1667</v>
+        <v>1665</v>
       </c>
       <c r="C847" s="2" t="s">
         <v>7</v>
@@ -19339,10 +19339,10 @@
     </row>
     <row r="848" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A848" t="s">
-        <v>1668</v>
+        <v>1666</v>
       </c>
       <c r="B848" t="s">
-        <v>1669</v>
+        <v>1667</v>
       </c>
       <c r="C848" s="2" t="s">
         <v>7</v>
@@ -19353,10 +19353,10 @@
     </row>
     <row r="849" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A849" t="s">
-        <v>1670</v>
+        <v>1668</v>
       </c>
       <c r="B849" t="s">
-        <v>1671</v>
+        <v>1669</v>
       </c>
       <c r="C849" s="2" t="s">
         <v>7</v>
@@ -19367,10 +19367,10 @@
     </row>
     <row r="850" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A850" t="s">
-        <v>1672</v>
+        <v>1670</v>
       </c>
       <c r="B850" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="C850" s="2" t="s">
         <v>7</v>
@@ -19381,10 +19381,10 @@
     </row>
     <row r="851" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A851" t="s">
-        <v>1674</v>
+        <v>1672</v>
       </c>
       <c r="B851" t="s">
-        <v>1675</v>
+        <v>1673</v>
       </c>
       <c r="C851" s="2" t="s">
         <v>7</v>
@@ -19395,10 +19395,10 @@
     </row>
     <row r="852" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A852" t="s">
-        <v>1676</v>
+        <v>1674</v>
       </c>
       <c r="B852" t="s">
-        <v>1677</v>
+        <v>1675</v>
       </c>
       <c r="C852" s="2" t="s">
         <v>7</v>
@@ -19409,10 +19409,10 @@
     </row>
     <row r="853" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A853" t="s">
-        <v>1678</v>
+        <v>1676</v>
       </c>
       <c r="B853" t="s">
-        <v>1679</v>
+        <v>1677</v>
       </c>
       <c r="C853" s="2" t="s">
         <v>7</v>
@@ -19423,10 +19423,10 @@
     </row>
     <row r="854" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A854" t="s">
-        <v>1682</v>
+        <v>1678</v>
       </c>
       <c r="B854" t="s">
-        <v>1683</v>
+        <v>1679</v>
       </c>
       <c r="C854" s="2" t="s">
         <v>7</v>
@@ -19437,10 +19437,10 @@
     </row>
     <row r="855" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A855" t="s">
-        <v>1684</v>
+        <v>1682</v>
       </c>
       <c r="B855" t="s">
-        <v>1685</v>
+        <v>1683</v>
       </c>
       <c r="C855" s="2" t="s">
         <v>7</v>
@@ -19451,10 +19451,10 @@
     </row>
     <row r="856" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A856" t="s">
-        <v>1686</v>
+        <v>1684</v>
       </c>
       <c r="B856" t="s">
-        <v>1687</v>
+        <v>1685</v>
       </c>
       <c r="C856" s="2" t="s">
         <v>7</v>
@@ -19465,10 +19465,10 @@
     </row>
     <row r="857" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A857" t="s">
-        <v>1688</v>
+        <v>1686</v>
       </c>
       <c r="B857" t="s">
-        <v>1689</v>
+        <v>1687</v>
       </c>
       <c r="C857" s="2" t="s">
         <v>7</v>
@@ -19479,10 +19479,10 @@
     </row>
     <row r="858" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A858" t="s">
-        <v>1690</v>
+        <v>1688</v>
       </c>
       <c r="B858" t="s">
-        <v>1691</v>
+        <v>1689</v>
       </c>
       <c r="C858" s="2" t="s">
         <v>7</v>
@@ -19493,10 +19493,10 @@
     </row>
     <row r="859" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A859" t="s">
-        <v>1692</v>
+        <v>1690</v>
       </c>
       <c r="B859" t="s">
-        <v>1693</v>
+        <v>1691</v>
       </c>
       <c r="C859" s="2" t="s">
         <v>7</v>
@@ -19507,10 +19507,10 @@
     </row>
     <row r="860" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A860" t="s">
-        <v>1694</v>
+        <v>1692</v>
       </c>
       <c r="B860" t="s">
-        <v>1695</v>
+        <v>1693</v>
       </c>
       <c r="C860" s="2" t="s">
         <v>7</v>
@@ -19521,10 +19521,10 @@
     </row>
     <row r="861" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A861" t="s">
-        <v>1696</v>
+        <v>1694</v>
       </c>
       <c r="B861" t="s">
-        <v>1697</v>
+        <v>1695</v>
       </c>
       <c r="C861" s="2" t="s">
         <v>7</v>
@@ -19535,10 +19535,10 @@
     </row>
     <row r="862" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A862" t="s">
-        <v>1698</v>
+        <v>1696</v>
       </c>
       <c r="B862" t="s">
-        <v>1699</v>
+        <v>1697</v>
       </c>
       <c r="C862" s="2" t="s">
         <v>7</v>
@@ -19549,10 +19549,10 @@
     </row>
     <row r="863" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A863" t="s">
-        <v>1700</v>
+        <v>1698</v>
       </c>
       <c r="B863" t="s">
-        <v>1701</v>
+        <v>1699</v>
       </c>
       <c r="C863" s="2" t="s">
         <v>7</v>
@@ -19563,10 +19563,10 @@
     </row>
     <row r="864" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A864" t="s">
-        <v>1702</v>
+        <v>1700</v>
       </c>
       <c r="B864" t="s">
-        <v>1703</v>
+        <v>1701</v>
       </c>
       <c r="C864" s="2" t="s">
         <v>7</v>
@@ -19577,10 +19577,10 @@
     </row>
     <row r="865" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A865" t="s">
-        <v>1704</v>
+        <v>1702</v>
       </c>
       <c r="B865" t="s">
-        <v>1705</v>
+        <v>1703</v>
       </c>
       <c r="C865" s="2" t="s">
         <v>7</v>
@@ -19591,10 +19591,10 @@
     </row>
     <row r="866" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A866" t="s">
-        <v>1706</v>
+        <v>1704</v>
       </c>
       <c r="B866" t="s">
-        <v>1707</v>
+        <v>1705</v>
       </c>
       <c r="C866" s="2" t="s">
         <v>7</v>
@@ -19605,10 +19605,10 @@
     </row>
     <row r="867" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A867" t="s">
-        <v>1708</v>
+        <v>1706</v>
       </c>
       <c r="B867" t="s">
-        <v>1709</v>
+        <v>1707</v>
       </c>
       <c r="C867" s="2" t="s">
         <v>7</v>
@@ -19619,10 +19619,10 @@
     </row>
     <row r="868" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A868" t="s">
-        <v>1710</v>
+        <v>1708</v>
       </c>
       <c r="B868" t="s">
-        <v>1711</v>
+        <v>1709</v>
       </c>
       <c r="C868" s="2" t="s">
         <v>7</v>
@@ -19633,10 +19633,10 @@
     </row>
     <row r="869" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A869" t="s">
-        <v>1712</v>
+        <v>1710</v>
       </c>
       <c r="B869" t="s">
-        <v>1713</v>
+        <v>1711</v>
       </c>
       <c r="C869" s="2" t="s">
         <v>7</v>
@@ -19647,10 +19647,10 @@
     </row>
     <row r="870" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A870" t="s">
-        <v>1714</v>
+        <v>1712</v>
       </c>
       <c r="B870" t="s">
-        <v>1715</v>
+        <v>1713</v>
       </c>
       <c r="C870" s="2" t="s">
         <v>7</v>
@@ -19661,10 +19661,10 @@
     </row>
     <row r="871" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A871" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
       <c r="B871" t="s">
-        <v>1717</v>
+        <v>1715</v>
       </c>
       <c r="C871" s="2" t="s">
         <v>7</v>
@@ -19675,10 +19675,10 @@
     </row>
     <row r="872" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A872" t="s">
-        <v>1718</v>
+        <v>1716</v>
       </c>
       <c r="B872" t="s">
-        <v>1719</v>
+        <v>1717</v>
       </c>
       <c r="C872" s="2" t="s">
         <v>7</v>
@@ -19689,10 +19689,10 @@
     </row>
     <row r="873" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A873" t="s">
-        <v>1720</v>
+        <v>1718</v>
       </c>
       <c r="B873" t="s">
-        <v>1721</v>
+        <v>1719</v>
       </c>
       <c r="C873" s="2" t="s">
         <v>7</v>
@@ -19703,10 +19703,10 @@
     </row>
     <row r="874" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A874" t="s">
-        <v>1722</v>
+        <v>1720</v>
       </c>
       <c r="B874" t="s">
-        <v>1723</v>
+        <v>1721</v>
       </c>
       <c r="C874" s="2" t="s">
         <v>7</v>
@@ -19717,10 +19717,10 @@
     </row>
     <row r="875" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A875" t="s">
-        <v>1724</v>
+        <v>1722</v>
       </c>
       <c r="B875" t="s">
-        <v>1725</v>
+        <v>1723</v>
       </c>
       <c r="C875" s="2" t="s">
         <v>7</v>
@@ -19731,10 +19731,10 @@
     </row>
     <row r="876" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A876" t="s">
-        <v>1726</v>
+        <v>1724</v>
       </c>
       <c r="B876" t="s">
-        <v>1727</v>
+        <v>1725</v>
       </c>
       <c r="C876" s="2" t="s">
         <v>7</v>
@@ -19745,10 +19745,10 @@
     </row>
     <row r="877" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A877" t="s">
-        <v>1728</v>
+        <v>1726</v>
       </c>
       <c r="B877" t="s">
-        <v>1729</v>
+        <v>1727</v>
       </c>
       <c r="C877" s="2" t="s">
         <v>7</v>
@@ -19759,10 +19759,10 @@
     </row>
     <row r="878" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A878" t="s">
-        <v>1730</v>
+        <v>1728</v>
       </c>
       <c r="B878" t="s">
-        <v>1731</v>
+        <v>1729</v>
       </c>
       <c r="C878" s="2" t="s">
         <v>7</v>
@@ -19773,10 +19773,10 @@
     </row>
     <row r="879" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A879" t="s">
-        <v>1732</v>
+        <v>1730</v>
       </c>
       <c r="B879" t="s">
-        <v>1733</v>
+        <v>1731</v>
       </c>
       <c r="C879" s="2" t="s">
         <v>7</v>
@@ -19787,10 +19787,10 @@
     </row>
     <row r="880" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A880" t="s">
-        <v>1734</v>
+        <v>1732</v>
       </c>
       <c r="B880" t="s">
-        <v>1735</v>
+        <v>1733</v>
       </c>
       <c r="C880" s="2" t="s">
         <v>7</v>
@@ -19801,10 +19801,10 @@
     </row>
     <row r="881" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A881" t="s">
-        <v>1736</v>
+        <v>1734</v>
       </c>
       <c r="B881" t="s">
-        <v>1737</v>
+        <v>1735</v>
       </c>
       <c r="C881" s="2" t="s">
         <v>7</v>
@@ -19815,10 +19815,10 @@
     </row>
     <row r="882" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A882" t="s">
-        <v>1738</v>
+        <v>1736</v>
       </c>
       <c r="B882" t="s">
-        <v>1739</v>
+        <v>1737</v>
       </c>
       <c r="C882" s="2" t="s">
         <v>7</v>
@@ -19829,10 +19829,10 @@
     </row>
     <row r="883" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A883" t="s">
-        <v>1740</v>
+        <v>1738</v>
       </c>
       <c r="B883" t="s">
-        <v>1741</v>
+        <v>1739</v>
       </c>
       <c r="C883" s="2" t="s">
         <v>7</v>
@@ -19843,10 +19843,10 @@
     </row>
     <row r="884" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A884" t="s">
-        <v>1742</v>
+        <v>1740</v>
       </c>
       <c r="B884" t="s">
-        <v>1743</v>
+        <v>1741</v>
       </c>
       <c r="C884" s="2" t="s">
         <v>7</v>
@@ -19857,10 +19857,10 @@
     </row>
     <row r="885" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A885" t="s">
-        <v>1744</v>
+        <v>1742</v>
       </c>
       <c r="B885" t="s">
-        <v>1745</v>
+        <v>1743</v>
       </c>
       <c r="C885" s="2" t="s">
         <v>7</v>
@@ -19871,10 +19871,10 @@
     </row>
     <row r="886" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A886" t="s">
-        <v>1746</v>
+        <v>1744</v>
       </c>
       <c r="B886" t="s">
-        <v>1747</v>
+        <v>1745</v>
       </c>
       <c r="C886" s="2" t="s">
         <v>7</v>
@@ -19885,10 +19885,10 @@
     </row>
     <row r="887" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A887" t="s">
-        <v>1748</v>
+        <v>1746</v>
       </c>
       <c r="B887" t="s">
-        <v>1749</v>
+        <v>1747</v>
       </c>
       <c r="C887" s="2" t="s">
         <v>7</v>
@@ -19899,10 +19899,10 @@
     </row>
     <row r="888" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A888" t="s">
-        <v>1750</v>
+        <v>1748</v>
       </c>
       <c r="B888" t="s">
-        <v>1751</v>
+        <v>1749</v>
       </c>
       <c r="C888" s="2" t="s">
         <v>7</v>
@@ -19913,10 +19913,10 @@
     </row>
     <row r="889" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A889" t="s">
-        <v>1752</v>
+        <v>1750</v>
       </c>
       <c r="B889" t="s">
-        <v>1753</v>
+        <v>1751</v>
       </c>
       <c r="C889" s="2" t="s">
         <v>7</v>
@@ -19927,10 +19927,10 @@
     </row>
     <row r="890" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A890" t="s">
-        <v>1754</v>
+        <v>1752</v>
       </c>
       <c r="B890" t="s">
-        <v>1755</v>
+        <v>1753</v>
       </c>
       <c r="C890" s="2" t="s">
         <v>7</v>
@@ -19941,10 +19941,10 @@
     </row>
     <row r="891" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A891" t="s">
-        <v>1756</v>
+        <v>1754</v>
       </c>
       <c r="B891" t="s">
-        <v>1757</v>
+        <v>1755</v>
       </c>
       <c r="C891" s="2" t="s">
         <v>7</v>
@@ -19955,10 +19955,10 @@
     </row>
     <row r="892" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A892" t="s">
-        <v>1758</v>
+        <v>1756</v>
       </c>
       <c r="B892" t="s">
-        <v>1759</v>
+        <v>1757</v>
       </c>
       <c r="C892" s="2" t="s">
         <v>7</v>
@@ -19969,10 +19969,10 @@
     </row>
     <row r="893" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A893" t="s">
-        <v>1760</v>
+        <v>1758</v>
       </c>
       <c r="B893" t="s">
-        <v>1761</v>
+        <v>1759</v>
       </c>
       <c r="C893" s="2" t="s">
         <v>7</v>
@@ -19983,10 +19983,10 @@
     </row>
     <row r="894" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A894" t="s">
-        <v>1762</v>
+        <v>1760</v>
       </c>
       <c r="B894" t="s">
-        <v>1763</v>
+        <v>1761</v>
       </c>
       <c r="C894" s="2" t="s">
         <v>7</v>
@@ -19997,10 +19997,10 @@
     </row>
     <row r="895" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A895" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="B895" t="s">
-        <v>1765</v>
+        <v>1763</v>
       </c>
       <c r="C895" s="2" t="s">
         <v>7</v>
@@ -20011,10 +20011,10 @@
     </row>
     <row r="896" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A896" t="s">
-        <v>1766</v>
+        <v>1764</v>
       </c>
       <c r="B896" t="s">
-        <v>1767</v>
+        <v>1765</v>
       </c>
       <c r="C896" s="2" t="s">
         <v>7</v>
@@ -20025,10 +20025,10 @@
     </row>
     <row r="897" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A897" t="s">
-        <v>1768</v>
+        <v>1766</v>
       </c>
       <c r="B897" t="s">
-        <v>1769</v>
+        <v>1767</v>
       </c>
       <c r="C897" s="2" t="s">
         <v>7</v>
@@ -20039,10 +20039,10 @@
     </row>
     <row r="898" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A898" t="s">
-        <v>1770</v>
+        <v>1768</v>
       </c>
       <c r="B898" t="s">
-        <v>1771</v>
+        <v>1769</v>
       </c>
       <c r="C898" s="2" t="s">
         <v>7</v>
@@ -20053,10 +20053,10 @@
     </row>
     <row r="899" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A899" t="s">
-        <v>1774</v>
+        <v>1770</v>
       </c>
       <c r="B899" t="s">
-        <v>1775</v>
+        <v>1771</v>
       </c>
       <c r="C899" s="2" t="s">
         <v>7</v>
@@ -20067,10 +20067,10 @@
     </row>
     <row r="900" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A900" t="s">
-        <v>1776</v>
+        <v>1774</v>
       </c>
       <c r="B900" t="s">
-        <v>1777</v>
+        <v>1775</v>
       </c>
       <c r="C900" s="2" t="s">
         <v>7</v>
@@ -20081,10 +20081,10 @@
     </row>
     <row r="901" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A901" t="s">
-        <v>1778</v>
+        <v>1776</v>
       </c>
       <c r="B901" t="s">
-        <v>1779</v>
+        <v>1777</v>
       </c>
       <c r="C901" s="2" t="s">
         <v>7</v>
@@ -20095,10 +20095,10 @@
     </row>
     <row r="902" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A902" t="s">
-        <v>1780</v>
+        <v>1778</v>
       </c>
       <c r="B902" t="s">
-        <v>1781</v>
+        <v>1779</v>
       </c>
       <c r="C902" s="2" t="s">
         <v>7</v>
@@ -20109,10 +20109,10 @@
     </row>
     <row r="903" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A903" t="s">
-        <v>1782</v>
+        <v>1780</v>
       </c>
       <c r="B903" t="s">
-        <v>1783</v>
+        <v>1781</v>
       </c>
       <c r="C903" s="2" t="s">
         <v>7</v>
@@ -20123,10 +20123,10 @@
     </row>
     <row r="904" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A904" t="s">
-        <v>1784</v>
+        <v>1782</v>
       </c>
       <c r="B904" t="s">
-        <v>1785</v>
+        <v>1783</v>
       </c>
       <c r="C904" s="2" t="s">
         <v>7</v>
@@ -20137,10 +20137,10 @@
     </row>
     <row r="905" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A905" t="s">
-        <v>1786</v>
+        <v>1784</v>
       </c>
       <c r="B905" t="s">
-        <v>1787</v>
+        <v>1785</v>
       </c>
       <c r="C905" s="2" t="s">
         <v>7</v>
@@ -20151,10 +20151,10 @@
     </row>
     <row r="906" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A906" t="s">
-        <v>1788</v>
+        <v>1786</v>
       </c>
       <c r="B906" t="s">
-        <v>1789</v>
+        <v>1787</v>
       </c>
       <c r="C906" s="2" t="s">
         <v>7</v>
@@ -20165,10 +20165,10 @@
     </row>
     <row r="907" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A907" t="s">
-        <v>1790</v>
+        <v>1788</v>
       </c>
       <c r="B907" t="s">
-        <v>1791</v>
+        <v>1789</v>
       </c>
       <c r="C907" s="2" t="s">
         <v>7</v>
@@ -20179,10 +20179,10 @@
     </row>
     <row r="908" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A908" t="s">
-        <v>1792</v>
+        <v>1790</v>
       </c>
       <c r="B908" t="s">
-        <v>1793</v>
+        <v>1791</v>
       </c>
       <c r="C908" s="2" t="s">
         <v>7</v>
@@ -20193,10 +20193,10 @@
     </row>
     <row r="909" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A909" t="s">
-        <v>1794</v>
+        <v>1792</v>
       </c>
       <c r="B909" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="C909" s="2" t="s">
         <v>7</v>
@@ -20207,10 +20207,10 @@
     </row>
     <row r="910" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A910" t="s">
-        <v>1796</v>
+        <v>1794</v>
       </c>
       <c r="B910" t="s">
-        <v>1797</v>
+        <v>1795</v>
       </c>
       <c r="C910" s="2" t="s">
         <v>7</v>
@@ -20221,10 +20221,10 @@
     </row>
     <row r="911" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A911" t="s">
-        <v>1798</v>
+        <v>1796</v>
       </c>
       <c r="B911" t="s">
-        <v>1799</v>
+        <v>1797</v>
       </c>
       <c r="C911" s="2" t="s">
         <v>7</v>
@@ -20235,10 +20235,10 @@
     </row>
     <row r="912" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A912" t="s">
-        <v>1800</v>
+        <v>1798</v>
       </c>
       <c r="B912" t="s">
-        <v>1801</v>
+        <v>1799</v>
       </c>
       <c r="C912" s="2" t="s">
         <v>7</v>
@@ -20249,10 +20249,10 @@
     </row>
     <row r="913" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A913" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="B913" t="s">
-        <v>1803</v>
+        <v>1801</v>
       </c>
       <c r="C913" s="2" t="s">
         <v>7</v>
@@ -20263,10 +20263,10 @@
     </row>
     <row r="914" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A914" t="s">
-        <v>1804</v>
+        <v>1802</v>
       </c>
       <c r="B914" t="s">
-        <v>1805</v>
+        <v>1803</v>
       </c>
       <c r="C914" s="2" t="s">
         <v>7</v>
@@ -20277,10 +20277,10 @@
     </row>
     <row r="915" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A915" t="s">
-        <v>1806</v>
+        <v>1804</v>
       </c>
       <c r="B915" t="s">
-        <v>1807</v>
+        <v>1805</v>
       </c>
       <c r="C915" s="2" t="s">
         <v>7</v>
@@ -20291,10 +20291,10 @@
     </row>
     <row r="916" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A916" t="s">
-        <v>1808</v>
+        <v>1806</v>
       </c>
       <c r="B916" t="s">
-        <v>1809</v>
+        <v>1807</v>
       </c>
       <c r="C916" s="2" t="s">
         <v>7</v>
@@ -20305,10 +20305,10 @@
     </row>
     <row r="917" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A917" t="s">
-        <v>1810</v>
+        <v>1808</v>
       </c>
       <c r="B917" t="s">
-        <v>1811</v>
+        <v>1809</v>
       </c>
       <c r="C917" s="2" t="s">
         <v>7</v>
@@ -20319,10 +20319,10 @@
     </row>
     <row r="918" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A918" t="s">
-        <v>1812</v>
+        <v>1810</v>
       </c>
       <c r="B918" t="s">
-        <v>1813</v>
+        <v>1811</v>
       </c>
       <c r="C918" s="2" t="s">
         <v>7</v>
@@ -20333,10 +20333,10 @@
     </row>
     <row r="919" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A919" t="s">
-        <v>1814</v>
+        <v>1812</v>
       </c>
       <c r="B919" t="s">
-        <v>1815</v>
+        <v>1813</v>
       </c>
       <c r="C919" s="2" t="s">
         <v>7</v>
@@ -20347,10 +20347,10 @@
     </row>
     <row r="920" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A920" t="s">
-        <v>1816</v>
+        <v>1814</v>
       </c>
       <c r="B920" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="C920" s="2" t="s">
         <v>7</v>
@@ -20361,10 +20361,10 @@
     </row>
     <row r="921" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A921" t="s">
-        <v>1818</v>
+        <v>1816</v>
       </c>
       <c r="B921" t="s">
-        <v>1819</v>
+        <v>1817</v>
       </c>
       <c r="C921" s="2" t="s">
         <v>7</v>
@@ -20375,10 +20375,10 @@
     </row>
     <row r="922" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A922" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="B922" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="C922" s="2" t="s">
         <v>7</v>
@@ -20389,10 +20389,10 @@
     </row>
     <row r="923" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A923" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="B923" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="C923" s="2" t="s">
         <v>7</v>
@@ -20403,10 +20403,10 @@
     </row>
     <row r="924" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A924" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="B924" t="s">
-        <v>1825</v>
+        <v>1823</v>
       </c>
       <c r="C924" s="2" t="s">
         <v>7</v>
@@ -20417,10 +20417,10 @@
     </row>
     <row r="925" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A925" t="s">
-        <v>1826</v>
+        <v>1824</v>
       </c>
       <c r="B925" t="s">
-        <v>1827</v>
+        <v>1825</v>
       </c>
       <c r="C925" s="2" t="s">
         <v>7</v>
@@ -20431,10 +20431,10 @@
     </row>
     <row r="926" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A926" t="s">
-        <v>1828</v>
+        <v>1826</v>
       </c>
       <c r="B926" t="s">
-        <v>1829</v>
+        <v>1827</v>
       </c>
       <c r="C926" s="2" t="s">
         <v>7</v>
@@ -20445,10 +20445,10 @@
     </row>
     <row r="927" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A927" t="s">
-        <v>1830</v>
+        <v>1828</v>
       </c>
       <c r="B927" t="s">
-        <v>1831</v>
+        <v>1829</v>
       </c>
       <c r="C927" s="2" t="s">
         <v>7</v>
@@ -20459,10 +20459,10 @@
     </row>
     <row r="928" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A928" t="s">
-        <v>1832</v>
+        <v>1830</v>
       </c>
       <c r="B928" t="s">
-        <v>1833</v>
+        <v>1831</v>
       </c>
       <c r="C928" s="2" t="s">
         <v>7</v>
@@ -20473,10 +20473,10 @@
     </row>
     <row r="929" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A929" t="s">
-        <v>1834</v>
+        <v>1832</v>
       </c>
       <c r="B929" t="s">
-        <v>1835</v>
+        <v>1833</v>
       </c>
       <c r="C929" s="2" t="s">
         <v>7</v>
@@ -20487,10 +20487,10 @@
     </row>
     <row r="930" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A930" t="s">
-        <v>1836</v>
+        <v>1834</v>
       </c>
       <c r="B930" t="s">
-        <v>1837</v>
+        <v>1835</v>
       </c>
       <c r="C930" s="2" t="s">
         <v>7</v>
@@ -20501,10 +20501,10 @@
     </row>
     <row r="931" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A931" t="s">
-        <v>1838</v>
+        <v>1836</v>
       </c>
       <c r="B931" t="s">
-        <v>1839</v>
+        <v>1837</v>
       </c>
       <c r="C931" s="2" t="s">
         <v>7</v>
@@ -20515,10 +20515,10 @@
     </row>
     <row r="932" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A932" t="s">
-        <v>1840</v>
+        <v>1838</v>
       </c>
       <c r="B932" t="s">
-        <v>1841</v>
+        <v>1839</v>
       </c>
       <c r="C932" s="2" t="s">
         <v>7</v>
@@ -20529,10 +20529,10 @@
     </row>
     <row r="933" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A933" t="s">
-        <v>1842</v>
+        <v>1840</v>
       </c>
       <c r="B933" t="s">
-        <v>1843</v>
+        <v>1841</v>
       </c>
       <c r="C933" s="2" t="s">
         <v>7</v>
@@ -20543,10 +20543,10 @@
     </row>
     <row r="934" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A934" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
       <c r="B934" t="s">
-        <v>1845</v>
+        <v>1843</v>
       </c>
       <c r="C934" s="2" t="s">
         <v>7</v>
@@ -20557,10 +20557,10 @@
     </row>
     <row r="935" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A935" t="s">
-        <v>1846</v>
+        <v>1844</v>
       </c>
       <c r="B935" t="s">
-        <v>1847</v>
+        <v>1845</v>
       </c>
       <c r="C935" s="2" t="s">
         <v>7</v>
@@ -20571,10 +20571,10 @@
     </row>
     <row r="936" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A936" t="s">
-        <v>1848</v>
+        <v>1846</v>
       </c>
       <c r="B936" t="s">
-        <v>1849</v>
+        <v>1847</v>
       </c>
       <c r="C936" s="2" t="s">
         <v>7</v>
@@ -20585,10 +20585,10 @@
     </row>
     <row r="937" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A937" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="B937" t="s">
-        <v>1851</v>
+        <v>1849</v>
       </c>
       <c r="C937" s="2" t="s">
         <v>7</v>
@@ -20599,10 +20599,10 @@
     </row>
     <row r="938" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A938" t="s">
-        <v>1852</v>
+        <v>1850</v>
       </c>
       <c r="B938" t="s">
-        <v>1853</v>
+        <v>1851</v>
       </c>
       <c r="C938" s="2" t="s">
         <v>7</v>
@@ -20613,10 +20613,10 @@
     </row>
     <row r="939" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A939" t="s">
-        <v>1854</v>
+        <v>1852</v>
       </c>
       <c r="B939" t="s">
-        <v>1855</v>
+        <v>1853</v>
       </c>
       <c r="C939" s="2" t="s">
         <v>7</v>
@@ -20627,10 +20627,10 @@
     </row>
     <row r="940" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A940" t="s">
-        <v>1856</v>
+        <v>1854</v>
       </c>
       <c r="B940" t="s">
-        <v>1857</v>
+        <v>1855</v>
       </c>
       <c r="C940" s="2" t="s">
         <v>7</v>
@@ -20641,10 +20641,10 @@
     </row>
     <row r="941" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A941" t="s">
-        <v>1858</v>
+        <v>1856</v>
       </c>
       <c r="B941" t="s">
-        <v>1859</v>
+        <v>1857</v>
       </c>
       <c r="C941" s="2" t="s">
         <v>7</v>
@@ -20655,10 +20655,10 @@
     </row>
     <row r="942" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A942" t="s">
-        <v>1862</v>
+        <v>1858</v>
       </c>
       <c r="B942" t="s">
-        <v>1863</v>
+        <v>1859</v>
       </c>
       <c r="C942" s="2" t="s">
         <v>7</v>
@@ -20669,10 +20669,10 @@
     </row>
     <row r="943" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A943" t="s">
-        <v>1864</v>
+        <v>1862</v>
       </c>
       <c r="B943" t="s">
-        <v>1865</v>
+        <v>1863</v>
       </c>
       <c r="C943" s="2" t="s">
         <v>7</v>
@@ -20683,10 +20683,10 @@
     </row>
     <row r="944" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A944" t="s">
-        <v>1866</v>
+        <v>1864</v>
       </c>
       <c r="B944" t="s">
-        <v>1867</v>
+        <v>1865</v>
       </c>
       <c r="C944" s="2" t="s">
         <v>7</v>
@@ -20697,10 +20697,10 @@
     </row>
     <row r="945" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A945" t="s">
-        <v>1868</v>
+        <v>1866</v>
       </c>
       <c r="B945" t="s">
-        <v>1869</v>
+        <v>1867</v>
       </c>
       <c r="C945" s="2" t="s">
         <v>7</v>
@@ -20711,10 +20711,10 @@
     </row>
     <row r="946" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A946" t="s">
-        <v>1870</v>
+        <v>1868</v>
       </c>
       <c r="B946" t="s">
-        <v>1871</v>
+        <v>1869</v>
       </c>
       <c r="C946" s="2" t="s">
         <v>7</v>
@@ -20725,10 +20725,10 @@
     </row>
     <row r="947" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A947" t="s">
-        <v>1874</v>
+        <v>1870</v>
       </c>
       <c r="B947" t="s">
-        <v>1875</v>
+        <v>1871</v>
       </c>
       <c r="C947" s="2" t="s">
         <v>7</v>
@@ -20739,10 +20739,10 @@
     </row>
     <row r="948" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A948" t="s">
-        <v>1876</v>
+        <v>1874</v>
       </c>
       <c r="B948" t="s">
-        <v>1877</v>
+        <v>1875</v>
       </c>
       <c r="C948" s="2" t="s">
         <v>7</v>
@@ -20753,10 +20753,10 @@
     </row>
     <row r="949" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A949" t="s">
-        <v>1878</v>
+        <v>1876</v>
       </c>
       <c r="B949" t="s">
-        <v>1879</v>
+        <v>1877</v>
       </c>
       <c r="C949" s="2" t="s">
         <v>7</v>
@@ -20767,10 +20767,10 @@
     </row>
     <row r="950" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A950" t="s">
-        <v>1880</v>
+        <v>1878</v>
       </c>
       <c r="B950" t="s">
-        <v>1881</v>
+        <v>1879</v>
       </c>
       <c r="C950" s="2" t="s">
         <v>7</v>
@@ -20781,10 +20781,10 @@
     </row>
     <row r="951" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A951" t="s">
-        <v>1882</v>
+        <v>1880</v>
       </c>
       <c r="B951" t="s">
-        <v>1883</v>
+        <v>1881</v>
       </c>
       <c r="C951" s="2" t="s">
         <v>7</v>
@@ -20795,10 +20795,10 @@
     </row>
     <row r="952" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A952" t="s">
-        <v>1884</v>
+        <v>1882</v>
       </c>
       <c r="B952" t="s">
-        <v>1885</v>
+        <v>1883</v>
       </c>
       <c r="C952" s="2" t="s">
         <v>7</v>
@@ -20809,10 +20809,10 @@
     </row>
     <row r="953" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A953" t="s">
-        <v>1886</v>
+        <v>1884</v>
       </c>
       <c r="B953" t="s">
-        <v>1887</v>
+        <v>1885</v>
       </c>
       <c r="C953" s="2" t="s">
         <v>7</v>
@@ -20823,10 +20823,10 @@
     </row>
     <row r="954" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A954" t="s">
-        <v>1888</v>
+        <v>1886</v>
       </c>
       <c r="B954" t="s">
-        <v>1889</v>
+        <v>1887</v>
       </c>
       <c r="C954" s="2" t="s">
         <v>7</v>
@@ -20837,10 +20837,10 @@
     </row>
     <row r="955" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A955" t="s">
-        <v>1890</v>
+        <v>1888</v>
       </c>
       <c r="B955" t="s">
-        <v>1891</v>
+        <v>1889</v>
       </c>
       <c r="C955" s="2" t="s">
         <v>7</v>
@@ -20851,10 +20851,10 @@
     </row>
     <row r="956" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A956" t="s">
-        <v>1892</v>
+        <v>1890</v>
       </c>
       <c r="B956" t="s">
-        <v>1893</v>
+        <v>1891</v>
       </c>
       <c r="C956" s="2" t="s">
         <v>7</v>
@@ -20865,10 +20865,10 @@
     </row>
     <row r="957" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A957" t="s">
-        <v>1894</v>
+        <v>1892</v>
       </c>
       <c r="B957" t="s">
-        <v>1895</v>
+        <v>1893</v>
       </c>
       <c r="C957" s="2" t="s">
         <v>7</v>
@@ -20879,10 +20879,10 @@
     </row>
     <row r="958" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A958" t="s">
-        <v>1896</v>
+        <v>1894</v>
       </c>
       <c r="B958" t="s">
-        <v>1897</v>
+        <v>1895</v>
       </c>
       <c r="C958" s="2" t="s">
         <v>7</v>
@@ -20893,10 +20893,10 @@
     </row>
     <row r="959" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A959" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="B959" t="s">
-        <v>1899</v>
+        <v>1897</v>
       </c>
       <c r="C959" s="2" t="s">
         <v>7</v>
@@ -20907,10 +20907,10 @@
     </row>
     <row r="960" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A960" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
       <c r="B960" t="s">
-        <v>1901</v>
+        <v>1899</v>
       </c>
       <c r="C960" s="2" t="s">
         <v>7</v>
@@ -20921,10 +20921,10 @@
     </row>
     <row r="961" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A961" t="s">
-        <v>1902</v>
+        <v>1900</v>
       </c>
       <c r="B961" t="s">
-        <v>1903</v>
+        <v>1901</v>
       </c>
       <c r="C961" s="2" t="s">
         <v>7</v>
@@ -20935,10 +20935,10 @@
     </row>
     <row r="962" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A962" t="s">
-        <v>1906</v>
+        <v>1902</v>
       </c>
       <c r="B962" t="s">
-        <v>1907</v>
+        <v>1903</v>
       </c>
       <c r="C962" s="2" t="s">
         <v>7</v>
@@ -20949,10 +20949,10 @@
     </row>
     <row r="963" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A963" t="s">
-        <v>1908</v>
+        <v>1906</v>
       </c>
       <c r="B963" t="s">
-        <v>1909</v>
+        <v>1907</v>
       </c>
       <c r="C963" s="2" t="s">
         <v>7</v>
@@ -20963,10 +20963,10 @@
     </row>
     <row r="964" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A964" t="s">
-        <v>1910</v>
+        <v>1908</v>
       </c>
       <c r="B964" t="s">
-        <v>1911</v>
+        <v>1909</v>
       </c>
       <c r="C964" s="2" t="s">
         <v>7</v>
@@ -20977,10 +20977,10 @@
     </row>
     <row r="965" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A965" t="s">
-        <v>1912</v>
+        <v>1910</v>
       </c>
       <c r="B965" t="s">
-        <v>1913</v>
+        <v>1911</v>
       </c>
       <c r="C965" s="2" t="s">
         <v>7</v>
@@ -20991,10 +20991,10 @@
     </row>
     <row r="966" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A966" t="s">
-        <v>1914</v>
+        <v>1912</v>
       </c>
       <c r="B966" t="s">
-        <v>1915</v>
+        <v>1913</v>
       </c>
       <c r="C966" s="2" t="s">
         <v>7</v>
@@ -21005,10 +21005,10 @@
     </row>
     <row r="967" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A967" t="s">
-        <v>1916</v>
+        <v>1914</v>
       </c>
       <c r="B967" t="s">
-        <v>1917</v>
+        <v>1915</v>
       </c>
       <c r="C967" s="2" t="s">
         <v>7</v>
@@ -21019,10 +21019,10 @@
     </row>
     <row r="968" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A968" t="s">
-        <v>1918</v>
+        <v>1916</v>
       </c>
       <c r="B968" t="s">
-        <v>1919</v>
+        <v>1917</v>
       </c>
       <c r="C968" s="2" t="s">
         <v>7</v>
@@ -21033,10 +21033,10 @@
     </row>
     <row r="969" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A969" t="s">
-        <v>1920</v>
+        <v>1918</v>
       </c>
       <c r="B969" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="C969" s="2" t="s">
         <v>7</v>
@@ -21047,10 +21047,10 @@
     </row>
     <row r="970" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A970" t="s">
-        <v>1922</v>
+        <v>1920</v>
       </c>
       <c r="B970" t="s">
-        <v>1923</v>
+        <v>1921</v>
       </c>
       <c r="C970" s="2" t="s">
         <v>7</v>
@@ -21061,10 +21061,10 @@
     </row>
     <row r="971" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A971" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
       <c r="B971" t="s">
-        <v>1925</v>
+        <v>1923</v>
       </c>
       <c r="C971" s="2" t="s">
         <v>7</v>
@@ -21075,10 +21075,10 @@
     </row>
     <row r="972" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A972" t="s">
-        <v>1926</v>
+        <v>1924</v>
       </c>
       <c r="B972" t="s">
-        <v>1927</v>
+        <v>1925</v>
       </c>
       <c r="C972" s="2" t="s">
         <v>7</v>
@@ -21089,10 +21089,10 @@
     </row>
     <row r="973" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A973" t="s">
-        <v>1928</v>
+        <v>1926</v>
       </c>
       <c r="B973" t="s">
-        <v>1929</v>
+        <v>1927</v>
       </c>
       <c r="C973" s="2" t="s">
         <v>7</v>
@@ -21103,10 +21103,10 @@
     </row>
     <row r="974" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A974" t="s">
-        <v>1930</v>
+        <v>1928</v>
       </c>
       <c r="B974" t="s">
-        <v>1931</v>
+        <v>1929</v>
       </c>
       <c r="C974" s="2" t="s">
         <v>7</v>
@@ -21117,10 +21117,10 @@
     </row>
     <row r="975" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A975" t="s">
-        <v>1932</v>
+        <v>1930</v>
       </c>
       <c r="B975" t="s">
-        <v>1933</v>
+        <v>1931</v>
       </c>
       <c r="C975" s="2" t="s">
         <v>7</v>
@@ -21131,10 +21131,10 @@
     </row>
     <row r="976" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A976" t="s">
-        <v>1934</v>
+        <v>1932</v>
       </c>
       <c r="B976" t="s">
-        <v>1935</v>
+        <v>1933</v>
       </c>
       <c r="C976" s="2" t="s">
         <v>7</v>
@@ -21145,10 +21145,10 @@
     </row>
     <row r="977" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A977" t="s">
-        <v>1936</v>
+        <v>1934</v>
       </c>
       <c r="B977" t="s">
-        <v>1937</v>
+        <v>1935</v>
       </c>
       <c r="C977" s="2" t="s">
         <v>7</v>
@@ -21159,10 +21159,10 @@
     </row>
     <row r="978" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A978" t="s">
-        <v>1938</v>
+        <v>1936</v>
       </c>
       <c r="B978" t="s">
-        <v>1939</v>
+        <v>1937</v>
       </c>
       <c r="C978" s="2" t="s">
         <v>7</v>
@@ -21173,10 +21173,10 @@
     </row>
     <row r="979" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A979" t="s">
-        <v>1940</v>
+        <v>1938</v>
       </c>
       <c r="B979" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="C979" s="2" t="s">
         <v>7</v>
@@ -21187,10 +21187,10 @@
     </row>
     <row r="980" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A980" t="s">
-        <v>1942</v>
+        <v>1940</v>
       </c>
       <c r="B980" t="s">
-        <v>1943</v>
+        <v>1941</v>
       </c>
       <c r="C980" s="2" t="s">
         <v>7</v>
@@ -21201,10 +21201,10 @@
     </row>
     <row r="981" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A981" t="s">
-        <v>1944</v>
+        <v>1942</v>
       </c>
       <c r="B981" t="s">
-        <v>1945</v>
+        <v>1943</v>
       </c>
       <c r="C981" s="2" t="s">
         <v>7</v>
@@ -21215,10 +21215,10 @@
     </row>
     <row r="982" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A982" t="s">
-        <v>1946</v>
+        <v>1944</v>
       </c>
       <c r="B982" t="s">
-        <v>1947</v>
+        <v>1945</v>
       </c>
       <c r="C982" s="2" t="s">
         <v>7</v>
@@ -21229,10 +21229,10 @@
     </row>
     <row r="983" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A983" t="s">
-        <v>1948</v>
+        <v>1946</v>
       </c>
       <c r="B983" t="s">
-        <v>1949</v>
+        <v>1947</v>
       </c>
       <c r="C983" s="2" t="s">
         <v>7</v>
@@ -21243,10 +21243,10 @@
     </row>
     <row r="984" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A984" t="s">
-        <v>1950</v>
+        <v>1948</v>
       </c>
       <c r="B984" t="s">
-        <v>1951</v>
+        <v>1949</v>
       </c>
       <c r="C984" s="2" t="s">
         <v>7</v>
@@ -21257,10 +21257,10 @@
     </row>
     <row r="985" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A985" t="s">
-        <v>1952</v>
+        <v>1950</v>
       </c>
       <c r="B985" t="s">
-        <v>1953</v>
+        <v>1951</v>
       </c>
       <c r="C985" s="2" t="s">
         <v>7</v>
@@ -21271,10 +21271,10 @@
     </row>
     <row r="986" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A986" t="s">
-        <v>1954</v>
+        <v>1952</v>
       </c>
       <c r="B986" t="s">
-        <v>1955</v>
+        <v>1953</v>
       </c>
       <c r="C986" s="2" t="s">
         <v>7</v>
@@ -21285,10 +21285,10 @@
     </row>
     <row r="987" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A987" t="s">
-        <v>1956</v>
+        <v>1954</v>
       </c>
       <c r="B987" t="s">
-        <v>1957</v>
+        <v>1955</v>
       </c>
       <c r="C987" s="2" t="s">
         <v>7</v>
@@ -21299,10 +21299,10 @@
     </row>
     <row r="988" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A988" t="s">
-        <v>1958</v>
+        <v>1956</v>
       </c>
       <c r="B988" t="s">
-        <v>1959</v>
+        <v>1957</v>
       </c>
       <c r="C988" s="2" t="s">
         <v>7</v>
@@ -21313,10 +21313,10 @@
     </row>
     <row r="989" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A989" t="s">
-        <v>1960</v>
+        <v>1958</v>
       </c>
       <c r="B989" t="s">
-        <v>1961</v>
+        <v>1959</v>
       </c>
       <c r="C989" s="2" t="s">
         <v>7</v>
@@ -21327,10 +21327,10 @@
     </row>
     <row r="990" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A990" t="s">
-        <v>1962</v>
+        <v>1960</v>
       </c>
       <c r="B990" t="s">
-        <v>1963</v>
+        <v>1961</v>
       </c>
       <c r="C990" s="2" t="s">
         <v>7</v>
@@ -21341,10 +21341,10 @@
     </row>
     <row r="991" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A991" t="s">
-        <v>1964</v>
+        <v>1962</v>
       </c>
       <c r="B991" t="s">
-        <v>1965</v>
+        <v>1963</v>
       </c>
       <c r="C991" s="2" t="s">
         <v>7</v>
@@ -21355,10 +21355,10 @@
     </row>
     <row r="992" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A992" t="s">
-        <v>1966</v>
+        <v>1964</v>
       </c>
       <c r="B992" t="s">
-        <v>1967</v>
+        <v>1965</v>
       </c>
       <c r="C992" s="2" t="s">
         <v>7</v>
@@ -21369,10 +21369,10 @@
     </row>
     <row r="993" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A993" t="s">
-        <v>1968</v>
+        <v>1966</v>
       </c>
       <c r="B993" t="s">
-        <v>1969</v>
+        <v>1967</v>
       </c>
       <c r="C993" s="2" t="s">
         <v>7</v>
@@ -21383,10 +21383,10 @@
     </row>
     <row r="994" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A994" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="B994" t="s">
-        <v>1971</v>
+        <v>1969</v>
       </c>
       <c r="C994" s="2" t="s">
         <v>7</v>
@@ -21397,10 +21397,10 @@
     </row>
     <row r="995" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A995" t="s">
-        <v>1972</v>
+        <v>1970</v>
       </c>
       <c r="B995" t="s">
-        <v>1973</v>
+        <v>1971</v>
       </c>
       <c r="C995" s="2" t="s">
         <v>7</v>
@@ -21411,10 +21411,10 @@
     </row>
     <row r="996" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A996" t="s">
-        <v>1974</v>
+        <v>1972</v>
       </c>
       <c r="B996" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="C996" s="2" t="s">
         <v>7</v>
@@ -21425,10 +21425,10 @@
     </row>
     <row r="997" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A997" t="s">
-        <v>1976</v>
+        <v>1974</v>
       </c>
       <c r="B997" t="s">
-        <v>1977</v>
+        <v>1975</v>
       </c>
       <c r="C997" s="2" t="s">
         <v>7</v>
@@ -21439,10 +21439,10 @@
     </row>
     <row r="998" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A998" t="s">
-        <v>1978</v>
+        <v>1976</v>
       </c>
       <c r="B998" t="s">
-        <v>1979</v>
+        <v>1977</v>
       </c>
       <c r="C998" s="2" t="s">
         <v>7</v>
@@ -21453,10 +21453,10 @@
     </row>
     <row r="999" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A999" t="s">
-        <v>1980</v>
+        <v>1978</v>
       </c>
       <c r="B999" t="s">
-        <v>1981</v>
+        <v>1979</v>
       </c>
       <c r="C999" s="2" t="s">
         <v>7</v>
@@ -21467,10 +21467,10 @@
     </row>
     <row r="1000" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1000" t="s">
-        <v>1982</v>
+        <v>1980</v>
       </c>
       <c r="B1000" t="s">
-        <v>1983</v>
+        <v>1981</v>
       </c>
       <c r="C1000" s="2" t="s">
         <v>7</v>
@@ -21481,10 +21481,10 @@
     </row>
     <row r="1001" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1001" t="s">
-        <v>1984</v>
+        <v>1982</v>
       </c>
       <c r="B1001" t="s">
-        <v>1985</v>
+        <v>1983</v>
       </c>
       <c r="C1001" s="2" t="s">
         <v>7</v>
@@ -21495,10 +21495,10 @@
     </row>
     <row r="1002" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1002" t="s">
-        <v>1988</v>
+        <v>1984</v>
       </c>
       <c r="B1002" t="s">
-        <v>1989</v>
+        <v>1985</v>
       </c>
       <c r="C1002" s="2" t="s">
         <v>7</v>
@@ -21509,10 +21509,10 @@
     </row>
     <row r="1003" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1003" t="s">
-        <v>1990</v>
+        <v>1986</v>
       </c>
       <c r="B1003" t="s">
-        <v>1991</v>
+        <v>1987</v>
       </c>
       <c r="C1003" s="2" t="s">
         <v>7</v>
@@ -21523,10 +21523,10 @@
     </row>
     <row r="1004" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1004" t="s">
-        <v>1992</v>
+        <v>1988</v>
       </c>
       <c r="B1004" t="s">
-        <v>1993</v>
+        <v>1989</v>
       </c>
       <c r="C1004" s="2" t="s">
         <v>7</v>
@@ -21537,10 +21537,10 @@
     </row>
     <row r="1005" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1005" t="s">
-        <v>1994</v>
+        <v>1990</v>
       </c>
       <c r="B1005" t="s">
-        <v>1995</v>
+        <v>1991</v>
       </c>
       <c r="C1005" s="2" t="s">
         <v>7</v>
@@ -21551,10 +21551,10 @@
     </row>
     <row r="1006" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1006" t="s">
-        <v>1996</v>
+        <v>1992</v>
       </c>
       <c r="B1006" t="s">
-        <v>1997</v>
+        <v>1993</v>
       </c>
       <c r="C1006" s="2" t="s">
         <v>7</v>
@@ -21565,10 +21565,10 @@
     </row>
     <row r="1007" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1007" t="s">
-        <v>1998</v>
+        <v>1994</v>
       </c>
       <c r="B1007" t="s">
-        <v>1999</v>
+        <v>1995</v>
       </c>
       <c r="C1007" s="2" t="s">
         <v>7</v>
@@ -21579,10 +21579,10 @@
     </row>
     <row r="1008" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1008" t="s">
-        <v>2000</v>
+        <v>1996</v>
       </c>
       <c r="B1008" t="s">
-        <v>2001</v>
+        <v>1997</v>
       </c>
       <c r="C1008" s="2" t="s">
         <v>7</v>
@@ -21593,10 +21593,10 @@
     </row>
     <row r="1009" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1009" t="s">
-        <v>2002</v>
+        <v>1998</v>
       </c>
       <c r="B1009" t="s">
-        <v>2003</v>
+        <v>1999</v>
       </c>
       <c r="C1009" s="2" t="s">
         <v>7</v>
@@ -21607,10 +21607,10 @@
     </row>
     <row r="1010" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1010" t="s">
-        <v>2004</v>
+        <v>2000</v>
       </c>
       <c r="B1010" t="s">
-        <v>2005</v>
+        <v>2001</v>
       </c>
       <c r="C1010" s="2" t="s">
         <v>7</v>
@@ -21621,10 +21621,10 @@
     </row>
     <row r="1011" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1011" t="s">
-        <v>2006</v>
+        <v>2002</v>
       </c>
       <c r="B1011" t="s">
-        <v>2007</v>
+        <v>2003</v>
       </c>
       <c r="C1011" s="2" t="s">
         <v>7</v>
@@ -21635,10 +21635,10 @@
     </row>
     <row r="1012" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1012" t="s">
-        <v>2008</v>
+        <v>2004</v>
       </c>
       <c r="B1012" t="s">
-        <v>2009</v>
+        <v>2005</v>
       </c>
       <c r="C1012" s="2" t="s">
         <v>7</v>
@@ -21649,10 +21649,10 @@
     </row>
     <row r="1013" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1013" t="s">
-        <v>2012</v>
+        <v>2006</v>
       </c>
       <c r="B1013" t="s">
-        <v>2013</v>
+        <v>2007</v>
       </c>
       <c r="C1013" s="2" t="s">
         <v>7</v>
@@ -21663,10 +21663,10 @@
     </row>
     <row r="1014" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1014" t="s">
-        <v>2014</v>
+        <v>2008</v>
       </c>
       <c r="B1014" t="s">
-        <v>2015</v>
+        <v>2009</v>
       </c>
       <c r="C1014" s="2" t="s">
         <v>7</v>
@@ -21677,10 +21677,10 @@
     </row>
     <row r="1015" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1015" t="s">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="B1015" t="s">
-        <v>2017</v>
+        <v>2013</v>
       </c>
       <c r="C1015" s="2" t="s">
         <v>7</v>
@@ -21691,10 +21691,10 @@
     </row>
     <row r="1016" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1016" t="s">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="B1016" t="s">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="C1016" s="2" t="s">
         <v>7</v>
@@ -21705,10 +21705,10 @@
     </row>
     <row r="1017" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1017" t="s">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="B1017" t="s">
-        <v>2021</v>
+        <v>2017</v>
       </c>
       <c r="C1017" s="2" t="s">
         <v>7</v>
@@ -21719,10 +21719,10 @@
     </row>
     <row r="1018" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1018" t="s">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="B1018" t="s">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="C1018" s="2" t="s">
         <v>7</v>
@@ -21733,10 +21733,10 @@
     </row>
     <row r="1019" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1019" t="s">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="B1019" t="s">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="C1019" s="2" t="s">
         <v>7</v>
@@ -21747,10 +21747,10 @@
     </row>
     <row r="1020" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1020" t="s">
-        <v>2026</v>
+        <v>2022</v>
       </c>
       <c r="B1020" t="s">
-        <v>2027</v>
+        <v>2023</v>
       </c>
       <c r="C1020" s="2" t="s">
         <v>7</v>
@@ -21761,10 +21761,10 @@
     </row>
     <row r="1021" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1021" t="s">
-        <v>2028</v>
+        <v>2024</v>
       </c>
       <c r="B1021" t="s">
-        <v>2029</v>
+        <v>2025</v>
       </c>
       <c r="C1021" s="2" t="s">
         <v>7</v>
@@ -21775,10 +21775,10 @@
     </row>
     <row r="1022" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1022" t="s">
-        <v>2030</v>
+        <v>2026</v>
       </c>
       <c r="B1022" t="s">
-        <v>2031</v>
+        <v>2027</v>
       </c>
       <c r="C1022" s="2" t="s">
         <v>7</v>
@@ -21789,10 +21789,10 @@
     </row>
     <row r="1023" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1023" t="s">
-        <v>2032</v>
+        <v>2028</v>
       </c>
       <c r="B1023" t="s">
-        <v>2033</v>
+        <v>2029</v>
       </c>
       <c r="C1023" s="2" t="s">
         <v>7</v>
@@ -21803,10 +21803,10 @@
     </row>
     <row r="1024" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1024" t="s">
-        <v>2034</v>
+        <v>2030</v>
       </c>
       <c r="B1024" t="s">
-        <v>2035</v>
+        <v>2031</v>
       </c>
       <c r="C1024" s="2" t="s">
         <v>7</v>
@@ -21817,10 +21817,10 @@
     </row>
     <row r="1025" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1025" t="s">
-        <v>2036</v>
+        <v>2032</v>
       </c>
       <c r="B1025" t="s">
-        <v>2037</v>
+        <v>2033</v>
       </c>
       <c r="C1025" s="2" t="s">
         <v>7</v>
@@ -21831,10 +21831,10 @@
     </row>
     <row r="1026" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1026" t="s">
-        <v>2038</v>
+        <v>2034</v>
       </c>
       <c r="B1026" t="s">
-        <v>2039</v>
+        <v>2035</v>
       </c>
       <c r="C1026" s="2" t="s">
         <v>7</v>
@@ -21845,10 +21845,10 @@
     </row>
     <row r="1027" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1027" t="s">
-        <v>2040</v>
+        <v>2036</v>
       </c>
       <c r="B1027" t="s">
-        <v>2041</v>
+        <v>2037</v>
       </c>
       <c r="C1027" s="2" t="s">
         <v>7</v>
@@ -21859,10 +21859,10 @@
     </row>
     <row r="1028" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1028" t="s">
-        <v>2042</v>
+        <v>2038</v>
       </c>
       <c r="B1028" t="s">
-        <v>2043</v>
+        <v>2039</v>
       </c>
       <c r="C1028" s="2" t="s">
         <v>7</v>
@@ -21873,10 +21873,10 @@
     </row>
     <row r="1029" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1029" t="s">
-        <v>2044</v>
+        <v>2040</v>
       </c>
       <c r="B1029" t="s">
-        <v>2045</v>
+        <v>2041</v>
       </c>
       <c r="C1029" s="2" t="s">
         <v>7</v>
@@ -21887,10 +21887,10 @@
     </row>
     <row r="1030" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1030" t="s">
-        <v>2046</v>
+        <v>2042</v>
       </c>
       <c r="B1030" t="s">
-        <v>2047</v>
+        <v>2043</v>
       </c>
       <c r="C1030" s="2" t="s">
         <v>7</v>
@@ -21901,10 +21901,10 @@
     </row>
     <row r="1031" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1031" t="s">
-        <v>2048</v>
+        <v>2044</v>
       </c>
       <c r="B1031" t="s">
-        <v>2049</v>
+        <v>2045</v>
       </c>
       <c r="C1031" s="2" t="s">
         <v>7</v>
@@ -21915,10 +21915,10 @@
     </row>
     <row r="1032" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1032" t="s">
-        <v>2050</v>
+        <v>2046</v>
       </c>
       <c r="B1032" t="s">
-        <v>2051</v>
+        <v>2047</v>
       </c>
       <c r="C1032" s="2" t="s">
         <v>7</v>
@@ -21929,10 +21929,10 @@
     </row>
     <row r="1033" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1033" t="s">
-        <v>2052</v>
+        <v>2048</v>
       </c>
       <c r="B1033" t="s">
-        <v>2053</v>
+        <v>2049</v>
       </c>
       <c r="C1033" s="2" t="s">
         <v>7</v>
@@ -21943,10 +21943,10 @@
     </row>
     <row r="1034" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1034" t="s">
-        <v>2054</v>
+        <v>2050</v>
       </c>
       <c r="B1034" t="s">
-        <v>2055</v>
+        <v>2051</v>
       </c>
       <c r="C1034" s="2" t="s">
         <v>7</v>
@@ -21957,10 +21957,10 @@
     </row>
     <row r="1035" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1035" t="s">
-        <v>2056</v>
+        <v>2052</v>
       </c>
       <c r="B1035" t="s">
-        <v>2057</v>
+        <v>2053</v>
       </c>
       <c r="C1035" s="2" t="s">
         <v>7</v>
@@ -21971,10 +21971,10 @@
     </row>
     <row r="1036" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1036" t="s">
-        <v>2058</v>
+        <v>2054</v>
       </c>
       <c r="B1036" t="s">
-        <v>2059</v>
+        <v>2055</v>
       </c>
       <c r="C1036" s="2" t="s">
         <v>7</v>
@@ -21985,10 +21985,10 @@
     </row>
     <row r="1037" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1037" t="s">
-        <v>2060</v>
+        <v>2056</v>
       </c>
       <c r="B1037" t="s">
-        <v>2061</v>
+        <v>2057</v>
       </c>
       <c r="C1037" s="2" t="s">
         <v>7</v>
@@ -21999,10 +21999,10 @@
     </row>
     <row r="1038" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1038" t="s">
-        <v>2062</v>
+        <v>2058</v>
       </c>
       <c r="B1038" t="s">
-        <v>2063</v>
+        <v>2059</v>
       </c>
       <c r="C1038" s="2" t="s">
         <v>7</v>
@@ -22013,10 +22013,10 @@
     </row>
     <row r="1039" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1039" t="s">
-        <v>2064</v>
+        <v>2060</v>
       </c>
       <c r="B1039" t="s">
-        <v>2065</v>
+        <v>2061</v>
       </c>
       <c r="C1039" s="2" t="s">
         <v>7</v>
@@ -22027,10 +22027,10 @@
     </row>
     <row r="1040" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1040" t="s">
-        <v>2066</v>
+        <v>2062</v>
       </c>
       <c r="B1040" t="s">
-        <v>2067</v>
+        <v>2063</v>
       </c>
       <c r="C1040" s="2" t="s">
         <v>7</v>
@@ -22041,10 +22041,10 @@
     </row>
     <row r="1041" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1041" t="s">
-        <v>2068</v>
+        <v>2064</v>
       </c>
       <c r="B1041" t="s">
-        <v>2069</v>
+        <v>2065</v>
       </c>
       <c r="C1041" s="2" t="s">
         <v>7</v>
@@ -22055,10 +22055,10 @@
     </row>
     <row r="1042" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1042" t="s">
-        <v>2070</v>
+        <v>2066</v>
       </c>
       <c r="B1042" t="s">
-        <v>2071</v>
+        <v>2067</v>
       </c>
       <c r="C1042" s="2" t="s">
         <v>7</v>
@@ -22069,10 +22069,10 @@
     </row>
     <row r="1043" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1043" t="s">
-        <v>2078</v>
+        <v>2068</v>
       </c>
       <c r="B1043" t="s">
-        <v>2079</v>
+        <v>2069</v>
       </c>
       <c r="C1043" s="2" t="s">
         <v>7</v>
@@ -22083,10 +22083,10 @@
     </row>
     <row r="1044" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1044" t="s">
-        <v>2080</v>
+        <v>2070</v>
       </c>
       <c r="B1044" t="s">
-        <v>2081</v>
+        <v>2071</v>
       </c>
       <c r="C1044" s="2" t="s">
         <v>7</v>
@@ -22097,10 +22097,10 @@
     </row>
     <row r="1045" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1045" t="s">
-        <v>2082</v>
+        <v>2078</v>
       </c>
       <c r="B1045" t="s">
-        <v>2083</v>
+        <v>2079</v>
       </c>
       <c r="C1045" s="2" t="s">
         <v>7</v>
@@ -22111,10 +22111,10 @@
     </row>
     <row r="1046" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1046" t="s">
-        <v>2084</v>
+        <v>2080</v>
       </c>
       <c r="B1046" t="s">
-        <v>2085</v>
+        <v>2081</v>
       </c>
       <c r="C1046" s="2" t="s">
         <v>7</v>
@@ -22125,10 +22125,10 @@
     </row>
     <row r="1047" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1047" t="s">
-        <v>2086</v>
+        <v>2082</v>
       </c>
       <c r="B1047" t="s">
-        <v>2087</v>
+        <v>2083</v>
       </c>
       <c r="C1047" s="2" t="s">
         <v>7</v>
@@ -22139,10 +22139,10 @@
     </row>
     <row r="1048" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1048" t="s">
-        <v>2088</v>
+        <v>2084</v>
       </c>
       <c r="B1048" t="s">
-        <v>2089</v>
+        <v>2085</v>
       </c>
       <c r="C1048" s="2" t="s">
         <v>7</v>
@@ -22153,10 +22153,10 @@
     </row>
     <row r="1049" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1049" t="s">
-        <v>2090</v>
+        <v>2086</v>
       </c>
       <c r="B1049" t="s">
-        <v>2091</v>
+        <v>2087</v>
       </c>
       <c r="C1049" s="2" t="s">
         <v>7</v>
@@ -22167,10 +22167,10 @@
     </row>
     <row r="1050" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1050" t="s">
-        <v>2092</v>
+        <v>2088</v>
       </c>
       <c r="B1050" t="s">
-        <v>2093</v>
+        <v>2089</v>
       </c>
       <c r="C1050" s="2" t="s">
         <v>7</v>
@@ -22181,10 +22181,10 @@
     </row>
     <row r="1051" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1051" t="s">
-        <v>2094</v>
+        <v>2090</v>
       </c>
       <c r="B1051" t="s">
-        <v>2095</v>
+        <v>2091</v>
       </c>
       <c r="C1051" s="2" t="s">
         <v>7</v>
@@ -22195,10 +22195,10 @@
     </row>
     <row r="1052" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1052" t="s">
-        <v>2096</v>
+        <v>2092</v>
       </c>
       <c r="B1052" t="s">
-        <v>2097</v>
+        <v>2093</v>
       </c>
       <c r="C1052" s="2" t="s">
         <v>7</v>
@@ -22209,10 +22209,10 @@
     </row>
     <row r="1053" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1053" t="s">
-        <v>2098</v>
+        <v>2094</v>
       </c>
       <c r="B1053" t="s">
-        <v>2099</v>
+        <v>2095</v>
       </c>
       <c r="C1053" s="2" t="s">
         <v>7</v>
@@ -22223,10 +22223,10 @@
     </row>
     <row r="1054" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1054" t="s">
-        <v>2100</v>
+        <v>2096</v>
       </c>
       <c r="B1054" t="s">
-        <v>2101</v>
+        <v>2097</v>
       </c>
       <c r="C1054" s="2" t="s">
         <v>7</v>
@@ -22237,10 +22237,10 @@
     </row>
     <row r="1055" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1055" t="s">
-        <v>2102</v>
+        <v>2098</v>
       </c>
       <c r="B1055" t="s">
-        <v>2103</v>
+        <v>2099</v>
       </c>
       <c r="C1055" s="2" t="s">
         <v>7</v>
@@ -22251,10 +22251,10 @@
     </row>
     <row r="1056" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1056" t="s">
-        <v>2104</v>
+        <v>2100</v>
       </c>
       <c r="B1056" t="s">
-        <v>2105</v>
+        <v>2101</v>
       </c>
       <c r="C1056" s="2" t="s">
         <v>7</v>
@@ -22265,10 +22265,10 @@
     </row>
     <row r="1057" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1057" t="s">
-        <v>2106</v>
+        <v>2102</v>
       </c>
       <c r="B1057" t="s">
-        <v>2107</v>
+        <v>2103</v>
       </c>
       <c r="C1057" s="2" t="s">
         <v>7</v>
@@ -22279,10 +22279,10 @@
     </row>
     <row r="1058" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1058" t="s">
-        <v>2108</v>
+        <v>2104</v>
       </c>
       <c r="B1058" t="s">
-        <v>2109</v>
+        <v>2105</v>
       </c>
       <c r="C1058" s="2" t="s">
         <v>7</v>
@@ -22293,10 +22293,10 @@
     </row>
     <row r="1059" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1059" t="s">
-        <v>2110</v>
+        <v>2106</v>
       </c>
       <c r="B1059" t="s">
-        <v>2111</v>
+        <v>2107</v>
       </c>
       <c r="C1059" s="2" t="s">
         <v>7</v>
@@ -22307,10 +22307,10 @@
     </row>
     <row r="1060" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1060" t="s">
-        <v>2112</v>
+        <v>2108</v>
       </c>
       <c r="B1060" t="s">
-        <v>2113</v>
+        <v>2109</v>
       </c>
       <c r="C1060" s="2" t="s">
         <v>7</v>
@@ -22321,10 +22321,10 @@
     </row>
     <row r="1061" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1061" t="s">
-        <v>2114</v>
+        <v>2110</v>
       </c>
       <c r="B1061" t="s">
-        <v>2115</v>
+        <v>2111</v>
       </c>
       <c r="C1061" s="2" t="s">
         <v>7</v>
@@ -22335,10 +22335,10 @@
     </row>
     <row r="1062" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1062" t="s">
-        <v>2116</v>
+        <v>2112</v>
       </c>
       <c r="B1062" t="s">
-        <v>2117</v>
+        <v>2113</v>
       </c>
       <c r="C1062" s="2" t="s">
         <v>7</v>
@@ -22349,10 +22349,10 @@
     </row>
     <row r="1063" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1063" t="s">
-        <v>2118</v>
+        <v>2114</v>
       </c>
       <c r="B1063" t="s">
-        <v>2119</v>
+        <v>2115</v>
       </c>
       <c r="C1063" s="2" t="s">
         <v>7</v>
@@ -22363,10 +22363,10 @@
     </row>
     <row r="1064" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1064" t="s">
-        <v>2120</v>
+        <v>2116</v>
       </c>
       <c r="B1064" t="s">
-        <v>2121</v>
+        <v>2117</v>
       </c>
       <c r="C1064" s="2" t="s">
         <v>7</v>
@@ -22377,10 +22377,10 @@
     </row>
     <row r="1065" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1065" t="s">
-        <v>2122</v>
+        <v>2118</v>
       </c>
       <c r="B1065" t="s">
-        <v>2123</v>
+        <v>2119</v>
       </c>
       <c r="C1065" s="2" t="s">
         <v>7</v>
@@ -22391,10 +22391,10 @@
     </row>
     <row r="1066" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1066" t="s">
-        <v>2124</v>
+        <v>2120</v>
       </c>
       <c r="B1066" t="s">
-        <v>2125</v>
+        <v>2121</v>
       </c>
       <c r="C1066" s="2" t="s">
         <v>7</v>
@@ -22405,10 +22405,10 @@
     </row>
     <row r="1067" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1067" t="s">
-        <v>2126</v>
+        <v>2122</v>
       </c>
       <c r="B1067" t="s">
-        <v>2127</v>
+        <v>2123</v>
       </c>
       <c r="C1067" s="2" t="s">
         <v>7</v>
@@ -22419,10 +22419,10 @@
     </row>
     <row r="1068" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1068" t="s">
-        <v>2128</v>
+        <v>2124</v>
       </c>
       <c r="B1068" t="s">
-        <v>2129</v>
+        <v>2125</v>
       </c>
       <c r="C1068" s="2" t="s">
         <v>7</v>
@@ -22433,10 +22433,10 @@
     </row>
     <row r="1069" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1069" t="s">
-        <v>2132</v>
+        <v>2126</v>
       </c>
       <c r="B1069" t="s">
-        <v>2133</v>
+        <v>2127</v>
       </c>
       <c r="C1069" s="2" t="s">
         <v>7</v>
@@ -22447,10 +22447,10 @@
     </row>
     <row r="1070" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1070" t="s">
-        <v>2134</v>
+        <v>2128</v>
       </c>
       <c r="B1070" t="s">
-        <v>2135</v>
+        <v>2129</v>
       </c>
       <c r="C1070" s="2" t="s">
         <v>7</v>
@@ -22461,10 +22461,10 @@
     </row>
     <row r="1071" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1071" t="s">
-        <v>2136</v>
+        <v>2132</v>
       </c>
       <c r="B1071" t="s">
-        <v>2137</v>
+        <v>2133</v>
       </c>
       <c r="C1071" s="2" t="s">
         <v>7</v>
@@ -22475,10 +22475,10 @@
     </row>
     <row r="1072" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1072" t="s">
-        <v>2138</v>
+        <v>2134</v>
       </c>
       <c r="B1072" t="s">
-        <v>2139</v>
+        <v>2135</v>
       </c>
       <c r="C1072" s="2" t="s">
         <v>7</v>
@@ -22489,10 +22489,10 @@
     </row>
     <row r="1073" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1073" t="s">
-        <v>2140</v>
+        <v>2136</v>
       </c>
       <c r="B1073" t="s">
-        <v>2141</v>
+        <v>2137</v>
       </c>
       <c r="C1073" s="2" t="s">
         <v>7</v>
@@ -22503,10 +22503,10 @@
     </row>
     <row r="1074" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1074" t="s">
-        <v>2142</v>
+        <v>2138</v>
       </c>
       <c r="B1074" t="s">
-        <v>2143</v>
+        <v>2139</v>
       </c>
       <c r="C1074" s="2" t="s">
         <v>7</v>
@@ -22517,10 +22517,10 @@
     </row>
     <row r="1075" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1075" t="s">
-        <v>2144</v>
+        <v>2140</v>
       </c>
       <c r="B1075" t="s">
-        <v>2145</v>
+        <v>2141</v>
       </c>
       <c r="C1075" s="2" t="s">
         <v>7</v>
@@ -22531,10 +22531,10 @@
     </row>
     <row r="1076" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1076" t="s">
-        <v>2146</v>
+        <v>2142</v>
       </c>
       <c r="B1076" t="s">
-        <v>2147</v>
+        <v>2143</v>
       </c>
       <c r="C1076" s="2" t="s">
         <v>7</v>
@@ -22545,10 +22545,10 @@
     </row>
     <row r="1077" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1077" t="s">
-        <v>2148</v>
+        <v>2144</v>
       </c>
       <c r="B1077" t="s">
-        <v>2149</v>
+        <v>2145</v>
       </c>
       <c r="C1077" s="2" t="s">
         <v>7</v>
@@ -22559,10 +22559,10 @@
     </row>
     <row r="1078" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1078" t="s">
-        <v>2150</v>
+        <v>2146</v>
       </c>
       <c r="B1078" t="s">
-        <v>2151</v>
+        <v>2147</v>
       </c>
       <c r="C1078" s="2" t="s">
         <v>7</v>
@@ -22573,10 +22573,10 @@
     </row>
     <row r="1079" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1079" t="s">
-        <v>2152</v>
+        <v>2148</v>
       </c>
       <c r="B1079" t="s">
-        <v>2153</v>
+        <v>2149</v>
       </c>
       <c r="C1079" s="2" t="s">
         <v>7</v>
@@ -22587,10 +22587,10 @@
     </row>
     <row r="1080" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1080" t="s">
-        <v>2154</v>
+        <v>2150</v>
       </c>
       <c r="B1080" t="s">
-        <v>2155</v>
+        <v>2151</v>
       </c>
       <c r="C1080" s="2" t="s">
         <v>7</v>
@@ -22601,10 +22601,10 @@
     </row>
     <row r="1081" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1081" t="s">
-        <v>2156</v>
+        <v>2152</v>
       </c>
       <c r="B1081" t="s">
-        <v>2157</v>
+        <v>2153</v>
       </c>
       <c r="C1081" s="2" t="s">
         <v>7</v>
@@ -22615,10 +22615,10 @@
     </row>
     <row r="1082" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1082" t="s">
-        <v>2158</v>
+        <v>2154</v>
       </c>
       <c r="B1082" t="s">
-        <v>2159</v>
+        <v>2155</v>
       </c>
       <c r="C1082" s="2" t="s">
         <v>7</v>
@@ -22629,10 +22629,10 @@
     </row>
     <row r="1083" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1083" t="s">
-        <v>2160</v>
+        <v>2156</v>
       </c>
       <c r="B1083" t="s">
-        <v>2161</v>
+        <v>2157</v>
       </c>
       <c r="C1083" s="2" t="s">
         <v>7</v>
@@ -22643,10 +22643,10 @@
     </row>
     <row r="1084" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1084" t="s">
-        <v>2162</v>
+        <v>2158</v>
       </c>
       <c r="B1084" t="s">
-        <v>2163</v>
+        <v>2159</v>
       </c>
       <c r="C1084" s="2" t="s">
         <v>7</v>
@@ -22657,10 +22657,10 @@
     </row>
     <row r="1085" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1085" t="s">
-        <v>2164</v>
+        <v>2160</v>
       </c>
       <c r="B1085" t="s">
-        <v>2165</v>
+        <v>2161</v>
       </c>
       <c r="C1085" s="2" t="s">
         <v>7</v>
@@ -22671,10 +22671,10 @@
     </row>
     <row r="1086" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1086" t="s">
-        <v>2166</v>
+        <v>2162</v>
       </c>
       <c r="B1086" t="s">
-        <v>2167</v>
+        <v>2163</v>
       </c>
       <c r="C1086" s="2" t="s">
         <v>7</v>
@@ -22685,10 +22685,10 @@
     </row>
     <row r="1087" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1087" t="s">
-        <v>2168</v>
+        <v>2164</v>
       </c>
       <c r="B1087" t="s">
-        <v>2169</v>
+        <v>2165</v>
       </c>
       <c r="C1087" s="2" t="s">
         <v>7</v>
@@ -22699,10 +22699,10 @@
     </row>
     <row r="1088" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1088" t="s">
-        <v>2170</v>
+        <v>2166</v>
       </c>
       <c r="B1088" t="s">
-        <v>2171</v>
+        <v>2167</v>
       </c>
       <c r="C1088" s="2" t="s">
         <v>7</v>
@@ -22713,10 +22713,10 @@
     </row>
     <row r="1089" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1089" t="s">
-        <v>2172</v>
+        <v>2168</v>
       </c>
       <c r="B1089" t="s">
-        <v>2173</v>
+        <v>2169</v>
       </c>
       <c r="C1089" s="2" t="s">
         <v>7</v>
@@ -22727,10 +22727,10 @@
     </row>
     <row r="1090" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1090" t="s">
-        <v>2174</v>
+        <v>2170</v>
       </c>
       <c r="B1090" t="s">
-        <v>2175</v>
+        <v>2171</v>
       </c>
       <c r="C1090" s="2" t="s">
         <v>7</v>
@@ -22741,10 +22741,10 @@
     </row>
     <row r="1091" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1091" t="s">
-        <v>2176</v>
+        <v>2172</v>
       </c>
       <c r="B1091" t="s">
-        <v>2177</v>
+        <v>2173</v>
       </c>
       <c r="C1091" s="2" t="s">
         <v>7</v>
@@ -22755,10 +22755,10 @@
     </row>
     <row r="1092" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1092" t="s">
-        <v>2178</v>
+        <v>2174</v>
       </c>
       <c r="B1092" t="s">
-        <v>2179</v>
+        <v>2175</v>
       </c>
       <c r="C1092" s="2" t="s">
         <v>7</v>
@@ -22769,10 +22769,10 @@
     </row>
     <row r="1093" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1093" t="s">
-        <v>2180</v>
+        <v>2176</v>
       </c>
       <c r="B1093" t="s">
-        <v>2181</v>
+        <v>2177</v>
       </c>
       <c r="C1093" s="2" t="s">
         <v>7</v>
@@ -22783,10 +22783,10 @@
     </row>
     <row r="1094" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1094" t="s">
-        <v>2182</v>
+        <v>2178</v>
       </c>
       <c r="B1094" t="s">
-        <v>2183</v>
+        <v>2179</v>
       </c>
       <c r="C1094" s="2" t="s">
         <v>7</v>
@@ -22797,10 +22797,10 @@
     </row>
     <row r="1095" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1095" t="s">
-        <v>2184</v>
+        <v>2180</v>
       </c>
       <c r="B1095" t="s">
-        <v>2185</v>
+        <v>2181</v>
       </c>
       <c r="C1095" s="2" t="s">
         <v>7</v>
@@ -22811,10 +22811,10 @@
     </row>
     <row r="1096" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1096" t="s">
-        <v>2186</v>
+        <v>2182</v>
       </c>
       <c r="B1096" t="s">
-        <v>2187</v>
+        <v>2183</v>
       </c>
       <c r="C1096" s="2" t="s">
         <v>7</v>
@@ -22825,10 +22825,10 @@
     </row>
     <row r="1097" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1097" t="s">
-        <v>2188</v>
+        <v>2184</v>
       </c>
       <c r="B1097" t="s">
-        <v>2189</v>
+        <v>2185</v>
       </c>
       <c r="C1097" s="2" t="s">
         <v>7</v>
@@ -22839,10 +22839,10 @@
     </row>
     <row r="1098" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1098" t="s">
-        <v>2190</v>
+        <v>2186</v>
       </c>
       <c r="B1098" t="s">
-        <v>2191</v>
+        <v>2187</v>
       </c>
       <c r="C1098" s="2" t="s">
         <v>7</v>
@@ -22853,10 +22853,10 @@
     </row>
     <row r="1099" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1099" t="s">
-        <v>2192</v>
+        <v>2188</v>
       </c>
       <c r="B1099" t="s">
-        <v>2193</v>
+        <v>2189</v>
       </c>
       <c r="C1099" s="2" t="s">
         <v>7</v>
@@ -22867,10 +22867,10 @@
     </row>
     <row r="1100" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1100" t="s">
-        <v>2194</v>
+        <v>2190</v>
       </c>
       <c r="B1100" t="s">
-        <v>2195</v>
+        <v>2191</v>
       </c>
       <c r="C1100" s="2" t="s">
         <v>7</v>
@@ -22881,10 +22881,10 @@
     </row>
     <row r="1101" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1101" t="s">
-        <v>2196</v>
+        <v>2192</v>
       </c>
       <c r="B1101" t="s">
-        <v>2197</v>
+        <v>2193</v>
       </c>
       <c r="C1101" s="2" t="s">
         <v>7</v>
@@ -22895,10 +22895,10 @@
     </row>
     <row r="1102" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1102" t="s">
-        <v>2198</v>
+        <v>2194</v>
       </c>
       <c r="B1102" t="s">
-        <v>2199</v>
+        <v>2195</v>
       </c>
       <c r="C1102" s="2" t="s">
         <v>7</v>
@@ -22909,10 +22909,10 @@
     </row>
     <row r="1103" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1103" t="s">
-        <v>2200</v>
+        <v>2196</v>
       </c>
       <c r="B1103" t="s">
-        <v>2201</v>
+        <v>2197</v>
       </c>
       <c r="C1103" s="2" t="s">
         <v>7</v>
@@ -22923,10 +22923,10 @@
     </row>
     <row r="1104" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1104" t="s">
-        <v>2202</v>
+        <v>2198</v>
       </c>
       <c r="B1104" t="s">
-        <v>2203</v>
+        <v>2199</v>
       </c>
       <c r="C1104" s="2" t="s">
         <v>7</v>
@@ -22937,10 +22937,10 @@
     </row>
     <row r="1105" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1105" t="s">
-        <v>2204</v>
+        <v>2200</v>
       </c>
       <c r="B1105" t="s">
-        <v>2205</v>
+        <v>2201</v>
       </c>
       <c r="C1105" s="2" t="s">
         <v>7</v>
@@ -22951,10 +22951,10 @@
     </row>
     <row r="1106" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1106" t="s">
-        <v>2206</v>
+        <v>2202</v>
       </c>
       <c r="B1106" t="s">
-        <v>2207</v>
+        <v>2203</v>
       </c>
       <c r="C1106" s="2" t="s">
         <v>7</v>
@@ -22965,10 +22965,10 @@
     </row>
     <row r="1107" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1107" t="s">
-        <v>2208</v>
+        <v>2204</v>
       </c>
       <c r="B1107" t="s">
-        <v>2209</v>
+        <v>2205</v>
       </c>
       <c r="C1107" s="2" t="s">
         <v>7</v>
@@ -22979,10 +22979,10 @@
     </row>
     <row r="1108" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1108" t="s">
-        <v>2210</v>
+        <v>2206</v>
       </c>
       <c r="B1108" t="s">
-        <v>2211</v>
+        <v>2207</v>
       </c>
       <c r="C1108" s="2" t="s">
         <v>7</v>
@@ -22993,10 +22993,10 @@
     </row>
     <row r="1109" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1109" t="s">
-        <v>2212</v>
+        <v>2208</v>
       </c>
       <c r="B1109" t="s">
-        <v>2213</v>
+        <v>2209</v>
       </c>
       <c r="C1109" s="2" t="s">
         <v>7</v>
@@ -23007,10 +23007,10 @@
     </row>
     <row r="1110" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1110" t="s">
-        <v>2214</v>
+        <v>2210</v>
       </c>
       <c r="B1110" t="s">
-        <v>2215</v>
+        <v>2211</v>
       </c>
       <c r="C1110" s="2" t="s">
         <v>7</v>
@@ -23021,10 +23021,10 @@
     </row>
     <row r="1111" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1111" t="s">
-        <v>2216</v>
+        <v>2212</v>
       </c>
       <c r="B1111" t="s">
-        <v>2217</v>
+        <v>2213</v>
       </c>
       <c r="C1111" s="2" t="s">
         <v>7</v>
@@ -23035,10 +23035,10 @@
     </row>
     <row r="1112" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1112" t="s">
-        <v>2218</v>
+        <v>2214</v>
       </c>
       <c r="B1112" t="s">
-        <v>2219</v>
+        <v>2215</v>
       </c>
       <c r="C1112" s="2" t="s">
         <v>7</v>
@@ -23049,10 +23049,10 @@
     </row>
     <row r="1113" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1113" t="s">
-        <v>2220</v>
+        <v>2216</v>
       </c>
       <c r="B1113" t="s">
-        <v>2221</v>
+        <v>2217</v>
       </c>
       <c r="C1113" s="2" t="s">
         <v>7</v>
@@ -23063,10 +23063,10 @@
     </row>
     <row r="1114" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1114" t="s">
-        <v>2222</v>
+        <v>2218</v>
       </c>
       <c r="B1114" t="s">
-        <v>2223</v>
+        <v>2219</v>
       </c>
       <c r="C1114" s="2" t="s">
         <v>7</v>
@@ -23077,10 +23077,10 @@
     </row>
     <row r="1115" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1115" t="s">
-        <v>2224</v>
+        <v>2220</v>
       </c>
       <c r="B1115" t="s">
-        <v>2225</v>
+        <v>2221</v>
       </c>
       <c r="C1115" s="2" t="s">
         <v>7</v>
@@ -23091,10 +23091,10 @@
     </row>
     <row r="1116" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1116" t="s">
-        <v>2226</v>
+        <v>2222</v>
       </c>
       <c r="B1116" t="s">
-        <v>2227</v>
+        <v>2223</v>
       </c>
       <c r="C1116" s="2" t="s">
         <v>7</v>
@@ -23105,10 +23105,10 @@
     </row>
     <row r="1117" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1117" t="s">
-        <v>2228</v>
+        <v>2224</v>
       </c>
       <c r="B1117" t="s">
-        <v>2229</v>
+        <v>2225</v>
       </c>
       <c r="C1117" s="2" t="s">
         <v>7</v>
@@ -23119,10 +23119,10 @@
     </row>
     <row r="1118" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1118" t="s">
-        <v>2230</v>
+        <v>2226</v>
       </c>
       <c r="B1118" t="s">
-        <v>2231</v>
+        <v>2227</v>
       </c>
       <c r="C1118" s="2" t="s">
         <v>7</v>
@@ -23133,10 +23133,10 @@
     </row>
     <row r="1119" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1119" t="s">
-        <v>2232</v>
+        <v>2228</v>
       </c>
       <c r="B1119" t="s">
-        <v>2233</v>
+        <v>2229</v>
       </c>
       <c r="C1119" s="2" t="s">
         <v>7</v>
@@ -23147,10 +23147,10 @@
     </row>
     <row r="1120" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1120" t="s">
-        <v>2234</v>
+        <v>2230</v>
       </c>
       <c r="B1120" t="s">
-        <v>2235</v>
+        <v>2231</v>
       </c>
       <c r="C1120" s="2" t="s">
         <v>7</v>
@@ -23161,10 +23161,10 @@
     </row>
     <row r="1121" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1121" t="s">
-        <v>2236</v>
+        <v>2232</v>
       </c>
       <c r="B1121" t="s">
-        <v>2237</v>
+        <v>2233</v>
       </c>
       <c r="C1121" s="2" t="s">
         <v>7</v>
@@ -23175,10 +23175,10 @@
     </row>
     <row r="1122" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1122" t="s">
-        <v>2238</v>
+        <v>2234</v>
       </c>
       <c r="B1122" t="s">
-        <v>2239</v>
+        <v>2235</v>
       </c>
       <c r="C1122" s="2" t="s">
         <v>7</v>
@@ -23189,10 +23189,10 @@
     </row>
     <row r="1123" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1123" t="s">
-        <v>2240</v>
+        <v>2236</v>
       </c>
       <c r="B1123" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="C1123" s="2" t="s">
         <v>7</v>
@@ -23203,10 +23203,10 @@
     </row>
     <row r="1124" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1124" t="s">
-        <v>2242</v>
+        <v>2238</v>
       </c>
       <c r="B1124" t="s">
-        <v>2243</v>
+        <v>2239</v>
       </c>
       <c r="C1124" s="2" t="s">
         <v>7</v>
@@ -23217,10 +23217,10 @@
     </row>
     <row r="1125" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1125" t="s">
-        <v>2246</v>
+        <v>2240</v>
       </c>
       <c r="B1125" t="s">
-        <v>2247</v>
+        <v>2241</v>
       </c>
       <c r="C1125" s="2" t="s">
         <v>7</v>
@@ -23231,10 +23231,10 @@
     </row>
     <row r="1126" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1126" t="s">
-        <v>2248</v>
+        <v>2242</v>
       </c>
       <c r="B1126" t="s">
-        <v>2249</v>
+        <v>2243</v>
       </c>
       <c r="C1126" s="2" t="s">
         <v>7</v>
@@ -23245,10 +23245,10 @@
     </row>
     <row r="1127" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1127" t="s">
-        <v>2250</v>
+        <v>2246</v>
       </c>
       <c r="B1127" t="s">
-        <v>2251</v>
+        <v>2247</v>
       </c>
       <c r="C1127" s="2" t="s">
         <v>7</v>
@@ -23259,10 +23259,10 @@
     </row>
     <row r="1128" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1128" t="s">
-        <v>2252</v>
+        <v>2248</v>
       </c>
       <c r="B1128" t="s">
-        <v>2253</v>
+        <v>2249</v>
       </c>
       <c r="C1128" s="2" t="s">
         <v>7</v>
@@ -23273,10 +23273,10 @@
     </row>
     <row r="1129" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1129" t="s">
-        <v>2254</v>
+        <v>2250</v>
       </c>
       <c r="B1129" t="s">
-        <v>2255</v>
+        <v>2251</v>
       </c>
       <c r="C1129" s="2" t="s">
         <v>7</v>
@@ -23287,10 +23287,10 @@
     </row>
     <row r="1130" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1130" t="s">
-        <v>2258</v>
+        <v>2252</v>
       </c>
       <c r="B1130" t="s">
-        <v>2259</v>
+        <v>2253</v>
       </c>
       <c r="C1130" s="2" t="s">
         <v>7</v>
@@ -23301,10 +23301,10 @@
     </row>
     <row r="1131" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1131" t="s">
-        <v>2260</v>
+        <v>2254</v>
       </c>
       <c r="B1131" t="s">
-        <v>2261</v>
+        <v>2255</v>
       </c>
       <c r="C1131" s="2" t="s">
         <v>7</v>
@@ -23315,10 +23315,10 @@
     </row>
     <row r="1132" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1132" t="s">
-        <v>2262</v>
+        <v>2258</v>
       </c>
       <c r="B1132" t="s">
-        <v>2263</v>
+        <v>2259</v>
       </c>
       <c r="C1132" s="2" t="s">
         <v>7</v>
@@ -23329,10 +23329,10 @@
     </row>
     <row r="1133" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1133" t="s">
-        <v>2264</v>
+        <v>2260</v>
       </c>
       <c r="B1133" t="s">
-        <v>2265</v>
+        <v>2261</v>
       </c>
       <c r="C1133" s="2" t="s">
         <v>7</v>
@@ -23343,10 +23343,10 @@
     </row>
     <row r="1134" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1134" t="s">
-        <v>2268</v>
+        <v>2262</v>
       </c>
       <c r="B1134" t="s">
-        <v>2269</v>
+        <v>2263</v>
       </c>
       <c r="C1134" s="2" t="s">
         <v>7</v>
@@ -23357,10 +23357,10 @@
     </row>
     <row r="1135" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1135" t="s">
-        <v>2270</v>
+        <v>2264</v>
       </c>
       <c r="B1135" t="s">
-        <v>2271</v>
+        <v>2265</v>
       </c>
       <c r="C1135" s="2" t="s">
         <v>7</v>
@@ -23371,10 +23371,10 @@
     </row>
     <row r="1136" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1136" t="s">
-        <v>2272</v>
+        <v>2268</v>
       </c>
       <c r="B1136" t="s">
-        <v>2273</v>
+        <v>2269</v>
       </c>
       <c r="C1136" s="2" t="s">
         <v>7</v>
@@ -23385,10 +23385,10 @@
     </row>
     <row r="1137" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1137" t="s">
-        <v>2274</v>
+        <v>2270</v>
       </c>
       <c r="B1137" t="s">
-        <v>2275</v>
+        <v>2271</v>
       </c>
       <c r="C1137" s="2" t="s">
         <v>7</v>
@@ -23399,10 +23399,10 @@
     </row>
     <row r="1138" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1138" t="s">
-        <v>2276</v>
+        <v>2272</v>
       </c>
       <c r="B1138" t="s">
-        <v>2277</v>
+        <v>2273</v>
       </c>
       <c r="C1138" s="2" t="s">
         <v>7</v>
@@ -23413,10 +23413,10 @@
     </row>
     <row r="1139" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1139" t="s">
-        <v>2278</v>
+        <v>2274</v>
       </c>
       <c r="B1139" t="s">
-        <v>2279</v>
+        <v>2275</v>
       </c>
       <c r="C1139" s="2" t="s">
         <v>7</v>
@@ -23427,10 +23427,10 @@
     </row>
     <row r="1140" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1140" t="s">
-        <v>2280</v>
+        <v>2276</v>
       </c>
       <c r="B1140" t="s">
-        <v>2281</v>
+        <v>2277</v>
       </c>
       <c r="C1140" s="2" t="s">
         <v>7</v>
@@ -23441,10 +23441,10 @@
     </row>
     <row r="1141" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1141" t="s">
-        <v>2282</v>
+        <v>2278</v>
       </c>
       <c r="B1141" t="s">
-        <v>2283</v>
+        <v>2279</v>
       </c>
       <c r="C1141" s="2" t="s">
         <v>7</v>
@@ -23455,10 +23455,10 @@
     </row>
     <row r="1142" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1142" t="s">
-        <v>2284</v>
+        <v>2280</v>
       </c>
       <c r="B1142" t="s">
-        <v>2285</v>
+        <v>2281</v>
       </c>
       <c r="C1142" s="2" t="s">
         <v>7</v>
@@ -23469,10 +23469,10 @@
     </row>
     <row r="1143" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1143" t="s">
-        <v>2286</v>
+        <v>2282</v>
       </c>
       <c r="B1143" t="s">
-        <v>2287</v>
+        <v>2283</v>
       </c>
       <c r="C1143" s="2" t="s">
         <v>7</v>
@@ -23483,10 +23483,10 @@
     </row>
     <row r="1144" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1144" t="s">
-        <v>2288</v>
+        <v>2284</v>
       </c>
       <c r="B1144" t="s">
-        <v>2289</v>
+        <v>2285</v>
       </c>
       <c r="C1144" s="2" t="s">
         <v>7</v>
@@ -23497,10 +23497,10 @@
     </row>
     <row r="1145" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1145" t="s">
-        <v>2290</v>
+        <v>2286</v>
       </c>
       <c r="B1145" t="s">
-        <v>2291</v>
+        <v>2287</v>
       </c>
       <c r="C1145" s="2" t="s">
         <v>7</v>
@@ -23511,10 +23511,10 @@
     </row>
     <row r="1146" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1146" t="s">
-        <v>2292</v>
+        <v>2288</v>
       </c>
       <c r="B1146" t="s">
-        <v>2293</v>
+        <v>2289</v>
       </c>
       <c r="C1146" s="2" t="s">
         <v>7</v>
@@ -23525,10 +23525,10 @@
     </row>
     <row r="1147" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1147" t="s">
-        <v>2294</v>
+        <v>2290</v>
       </c>
       <c r="B1147" t="s">
-        <v>2295</v>
+        <v>2291</v>
       </c>
       <c r="C1147" s="2" t="s">
         <v>7</v>
@@ -23539,10 +23539,10 @@
     </row>
     <row r="1148" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1148" t="s">
-        <v>2296</v>
+        <v>2292</v>
       </c>
       <c r="B1148" t="s">
-        <v>2297</v>
+        <v>2293</v>
       </c>
       <c r="C1148" s="2" t="s">
         <v>7</v>
@@ -23553,10 +23553,10 @@
     </row>
     <row r="1149" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1149" t="s">
-        <v>2298</v>
+        <v>2294</v>
       </c>
       <c r="B1149" t="s">
-        <v>2299</v>
+        <v>2295</v>
       </c>
       <c r="C1149" s="2" t="s">
         <v>7</v>
@@ -23567,10 +23567,10 @@
     </row>
     <row r="1150" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1150" t="s">
-        <v>2300</v>
+        <v>2296</v>
       </c>
       <c r="B1150" t="s">
-        <v>2301</v>
+        <v>2297</v>
       </c>
       <c r="C1150" s="2" t="s">
         <v>7</v>
@@ -23581,10 +23581,10 @@
     </row>
     <row r="1151" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1151" t="s">
-        <v>2302</v>
+        <v>2298</v>
       </c>
       <c r="B1151" t="s">
-        <v>2303</v>
+        <v>2299</v>
       </c>
       <c r="C1151" s="2" t="s">
         <v>7</v>
@@ -23595,10 +23595,10 @@
     </row>
     <row r="1152" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1152" t="s">
-        <v>2304</v>
+        <v>2300</v>
       </c>
       <c r="B1152" t="s">
-        <v>2305</v>
+        <v>2301</v>
       </c>
       <c r="C1152" s="2" t="s">
         <v>7</v>
@@ -23609,10 +23609,10 @@
     </row>
     <row r="1153" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1153" t="s">
-        <v>2308</v>
+        <v>2302</v>
       </c>
       <c r="B1153" t="s">
-        <v>2309</v>
+        <v>2303</v>
       </c>
       <c r="C1153" s="2" t="s">
         <v>7</v>
@@ -23623,10 +23623,10 @@
     </row>
     <row r="1154" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1154" t="s">
-        <v>2310</v>
+        <v>2304</v>
       </c>
       <c r="B1154" t="s">
-        <v>2311</v>
+        <v>2305</v>
       </c>
       <c r="C1154" s="2" t="s">
         <v>7</v>
@@ -23637,10 +23637,10 @@
     </row>
     <row r="1155" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1155" t="s">
-        <v>2312</v>
+        <v>2308</v>
       </c>
       <c r="B1155" t="s">
-        <v>2313</v>
+        <v>2309</v>
       </c>
       <c r="C1155" s="2" t="s">
         <v>7</v>
@@ -23651,10 +23651,10 @@
     </row>
     <row r="1156" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1156" t="s">
-        <v>2314</v>
+        <v>2310</v>
       </c>
       <c r="B1156" t="s">
-        <v>2315</v>
+        <v>2311</v>
       </c>
       <c r="C1156" s="2" t="s">
         <v>7</v>
@@ -23665,10 +23665,10 @@
     </row>
     <row r="1157" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1157" t="s">
-        <v>2316</v>
+        <v>2312</v>
       </c>
       <c r="B1157" t="s">
-        <v>2317</v>
+        <v>2313</v>
       </c>
       <c r="C1157" s="2" t="s">
         <v>7</v>
@@ -23679,10 +23679,10 @@
     </row>
     <row r="1158" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1158" t="s">
-        <v>2318</v>
+        <v>2314</v>
       </c>
       <c r="B1158" t="s">
-        <v>2319</v>
+        <v>2315</v>
       </c>
       <c r="C1158" s="2" t="s">
         <v>7</v>
@@ -23693,10 +23693,10 @@
     </row>
     <row r="1159" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1159" t="s">
-        <v>2320</v>
+        <v>2316</v>
       </c>
       <c r="B1159" t="s">
-        <v>2321</v>
+        <v>2317</v>
       </c>
       <c r="C1159" s="2" t="s">
         <v>7</v>
@@ -23707,10 +23707,10 @@
     </row>
     <row r="1160" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1160" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
       <c r="B1160" t="s">
-        <v>2323</v>
+        <v>2319</v>
       </c>
       <c r="C1160" s="2" t="s">
         <v>7</v>
@@ -23721,10 +23721,10 @@
     </row>
     <row r="1161" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1161" t="s">
-        <v>2324</v>
+        <v>2320</v>
       </c>
       <c r="B1161" t="s">
-        <v>2325</v>
+        <v>2321</v>
       </c>
       <c r="C1161" s="2" t="s">
         <v>7</v>
@@ -23735,10 +23735,10 @@
     </row>
     <row r="1162" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1162" t="s">
-        <v>2326</v>
+        <v>2322</v>
       </c>
       <c r="B1162" t="s">
-        <v>2327</v>
+        <v>2323</v>
       </c>
       <c r="C1162" s="2" t="s">
         <v>7</v>
@@ -23749,10 +23749,10 @@
     </row>
     <row r="1163" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1163" t="s">
-        <v>2328</v>
+        <v>2324</v>
       </c>
       <c r="B1163" t="s">
-        <v>2329</v>
+        <v>2325</v>
       </c>
       <c r="C1163" s="2" t="s">
         <v>7</v>
@@ -23763,10 +23763,10 @@
     </row>
     <row r="1164" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1164" t="s">
-        <v>2330</v>
+        <v>2326</v>
       </c>
       <c r="B1164" t="s">
-        <v>2331</v>
+        <v>2327</v>
       </c>
       <c r="C1164" s="2" t="s">
         <v>7</v>
@@ -23777,10 +23777,10 @@
     </row>
     <row r="1165" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1165" t="s">
-        <v>2332</v>
+        <v>2328</v>
       </c>
       <c r="B1165" t="s">
-        <v>2333</v>
+        <v>2329</v>
       </c>
       <c r="C1165" s="2" t="s">
         <v>7</v>
@@ -23791,10 +23791,10 @@
     </row>
     <row r="1166" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1166" t="s">
-        <v>2334</v>
+        <v>2330</v>
       </c>
       <c r="B1166" t="s">
-        <v>2335</v>
+        <v>2331</v>
       </c>
       <c r="C1166" s="2" t="s">
         <v>7</v>
@@ -23805,10 +23805,10 @@
     </row>
     <row r="1167" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1167" t="s">
-        <v>2336</v>
+        <v>2332</v>
       </c>
       <c r="B1167" t="s">
-        <v>2337</v>
+        <v>2333</v>
       </c>
       <c r="C1167" s="2" t="s">
         <v>7</v>
@@ -23819,10 +23819,10 @@
     </row>
     <row r="1168" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1168" t="s">
-        <v>2338</v>
+        <v>2334</v>
       </c>
       <c r="B1168" t="s">
-        <v>2339</v>
+        <v>2335</v>
       </c>
       <c r="C1168" s="2" t="s">
         <v>7</v>
@@ -23833,10 +23833,10 @@
     </row>
     <row r="1169" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1169" t="s">
-        <v>2340</v>
+        <v>2336</v>
       </c>
       <c r="B1169" t="s">
-        <v>2341</v>
+        <v>2337</v>
       </c>
       <c r="C1169" s="2" t="s">
         <v>7</v>
@@ -23847,10 +23847,10 @@
     </row>
     <row r="1170" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1170" t="s">
-        <v>2342</v>
+        <v>2338</v>
       </c>
       <c r="B1170" t="s">
-        <v>2343</v>
+        <v>2339</v>
       </c>
       <c r="C1170" s="2" t="s">
         <v>7</v>
@@ -23861,10 +23861,10 @@
     </row>
     <row r="1171" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1171" t="s">
-        <v>1628</v>
+        <v>2340</v>
       </c>
       <c r="B1171" t="s">
-        <v>1629</v>
+        <v>2341</v>
       </c>
       <c r="C1171" s="2" t="s">
         <v>7</v>
@@ -23875,10 +23875,10 @@
     </row>
     <row r="1172" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1172" t="s">
-        <v>1986</v>
+        <v>2342</v>
       </c>
       <c r="B1172" t="s">
-        <v>1987</v>
+        <v>2343</v>
       </c>
       <c r="C1172" s="2" t="s">
         <v>7</v>
@@ -24712,364 +24712,364 @@
     <hyperlink ref="C826" r:id="rId811" xr:uid="{00000000-0004-0000-0000-00002A030000}"/>
     <hyperlink ref="C827" r:id="rId812" xr:uid="{00000000-0004-0000-0000-00002B030000}"/>
     <hyperlink ref="C828" r:id="rId813" xr:uid="{00000000-0004-0000-0000-00002C030000}"/>
-    <hyperlink ref="C1171" r:id="rId814" xr:uid="{00000000-0004-0000-0000-00002D030000}"/>
-    <hyperlink ref="C829" r:id="rId815" xr:uid="{00000000-0004-0000-0000-00002E030000}"/>
-    <hyperlink ref="C830" r:id="rId816" xr:uid="{00000000-0004-0000-0000-00002F030000}"/>
-    <hyperlink ref="C831" r:id="rId817" xr:uid="{00000000-0004-0000-0000-000030030000}"/>
-    <hyperlink ref="C832" r:id="rId818" xr:uid="{00000000-0004-0000-0000-000031030000}"/>
-    <hyperlink ref="C833" r:id="rId819" xr:uid="{00000000-0004-0000-0000-000032030000}"/>
-    <hyperlink ref="C834" r:id="rId820" xr:uid="{00000000-0004-0000-0000-000033030000}"/>
-    <hyperlink ref="C835" r:id="rId821" xr:uid="{00000000-0004-0000-0000-000034030000}"/>
-    <hyperlink ref="C836" r:id="rId822" xr:uid="{00000000-0004-0000-0000-000035030000}"/>
-    <hyperlink ref="C837" r:id="rId823" xr:uid="{00000000-0004-0000-0000-000036030000}"/>
-    <hyperlink ref="C838" r:id="rId824" xr:uid="{00000000-0004-0000-0000-000037030000}"/>
-    <hyperlink ref="C839" r:id="rId825" xr:uid="{00000000-0004-0000-0000-000038030000}"/>
-    <hyperlink ref="C840" r:id="rId826" xr:uid="{00000000-0004-0000-0000-000039030000}"/>
-    <hyperlink ref="C841" r:id="rId827" xr:uid="{00000000-0004-0000-0000-00003A030000}"/>
-    <hyperlink ref="C842" r:id="rId828" xr:uid="{00000000-0004-0000-0000-00003B030000}"/>
-    <hyperlink ref="C843" r:id="rId829" xr:uid="{00000000-0004-0000-0000-00003C030000}"/>
-    <hyperlink ref="C844" r:id="rId830" xr:uid="{00000000-0004-0000-0000-00003D030000}"/>
-    <hyperlink ref="C845" r:id="rId831" xr:uid="{00000000-0004-0000-0000-00003E030000}"/>
-    <hyperlink ref="C846" r:id="rId832" xr:uid="{00000000-0004-0000-0000-00003F030000}"/>
-    <hyperlink ref="C847" r:id="rId833" xr:uid="{00000000-0004-0000-0000-000040030000}"/>
-    <hyperlink ref="C848" r:id="rId834" xr:uid="{00000000-0004-0000-0000-000041030000}"/>
-    <hyperlink ref="C849" r:id="rId835" xr:uid="{00000000-0004-0000-0000-000042030000}"/>
-    <hyperlink ref="C850" r:id="rId836" xr:uid="{00000000-0004-0000-0000-000043030000}"/>
-    <hyperlink ref="C851" r:id="rId837" xr:uid="{00000000-0004-0000-0000-000044030000}"/>
-    <hyperlink ref="C852" r:id="rId838" xr:uid="{00000000-0004-0000-0000-000045030000}"/>
-    <hyperlink ref="C853" r:id="rId839" xr:uid="{00000000-0004-0000-0000-000046030000}"/>
+    <hyperlink ref="C829" r:id="rId814" xr:uid="{00000000-0004-0000-0000-00002D030000}"/>
+    <hyperlink ref="C830" r:id="rId815" xr:uid="{00000000-0004-0000-0000-00002E030000}"/>
+    <hyperlink ref="C831" r:id="rId816" xr:uid="{00000000-0004-0000-0000-00002F030000}"/>
+    <hyperlink ref="C832" r:id="rId817" xr:uid="{00000000-0004-0000-0000-000030030000}"/>
+    <hyperlink ref="C833" r:id="rId818" xr:uid="{00000000-0004-0000-0000-000031030000}"/>
+    <hyperlink ref="C834" r:id="rId819" xr:uid="{00000000-0004-0000-0000-000032030000}"/>
+    <hyperlink ref="C835" r:id="rId820" xr:uid="{00000000-0004-0000-0000-000033030000}"/>
+    <hyperlink ref="C836" r:id="rId821" xr:uid="{00000000-0004-0000-0000-000034030000}"/>
+    <hyperlink ref="C837" r:id="rId822" xr:uid="{00000000-0004-0000-0000-000035030000}"/>
+    <hyperlink ref="C838" r:id="rId823" xr:uid="{00000000-0004-0000-0000-000036030000}"/>
+    <hyperlink ref="C839" r:id="rId824" xr:uid="{00000000-0004-0000-0000-000037030000}"/>
+    <hyperlink ref="C840" r:id="rId825" xr:uid="{00000000-0004-0000-0000-000038030000}"/>
+    <hyperlink ref="C841" r:id="rId826" xr:uid="{00000000-0004-0000-0000-000039030000}"/>
+    <hyperlink ref="C842" r:id="rId827" xr:uid="{00000000-0004-0000-0000-00003A030000}"/>
+    <hyperlink ref="C843" r:id="rId828" xr:uid="{00000000-0004-0000-0000-00003B030000}"/>
+    <hyperlink ref="C844" r:id="rId829" xr:uid="{00000000-0004-0000-0000-00003C030000}"/>
+    <hyperlink ref="C845" r:id="rId830" xr:uid="{00000000-0004-0000-0000-00003D030000}"/>
+    <hyperlink ref="C846" r:id="rId831" xr:uid="{00000000-0004-0000-0000-00003E030000}"/>
+    <hyperlink ref="C847" r:id="rId832" xr:uid="{00000000-0004-0000-0000-00003F030000}"/>
+    <hyperlink ref="C848" r:id="rId833" xr:uid="{00000000-0004-0000-0000-000040030000}"/>
+    <hyperlink ref="C849" r:id="rId834" xr:uid="{00000000-0004-0000-0000-000041030000}"/>
+    <hyperlink ref="C850" r:id="rId835" xr:uid="{00000000-0004-0000-0000-000042030000}"/>
+    <hyperlink ref="C851" r:id="rId836" xr:uid="{00000000-0004-0000-0000-000043030000}"/>
+    <hyperlink ref="C852" r:id="rId837" xr:uid="{00000000-0004-0000-0000-000044030000}"/>
+    <hyperlink ref="C853" r:id="rId838" xr:uid="{00000000-0004-0000-0000-000045030000}"/>
+    <hyperlink ref="C854" r:id="rId839" xr:uid="{00000000-0004-0000-0000-000046030000}"/>
     <hyperlink ref="C25" r:id="rId840" xr:uid="{00000000-0004-0000-0000-000047030000}"/>
-    <hyperlink ref="C854" r:id="rId841" xr:uid="{00000000-0004-0000-0000-000048030000}"/>
-    <hyperlink ref="C855" r:id="rId842" xr:uid="{00000000-0004-0000-0000-000049030000}"/>
-    <hyperlink ref="C856" r:id="rId843" xr:uid="{00000000-0004-0000-0000-00004A030000}"/>
-    <hyperlink ref="C857" r:id="rId844" xr:uid="{00000000-0004-0000-0000-00004B030000}"/>
-    <hyperlink ref="C858" r:id="rId845" xr:uid="{00000000-0004-0000-0000-00004C030000}"/>
-    <hyperlink ref="C859" r:id="rId846" xr:uid="{00000000-0004-0000-0000-00004D030000}"/>
-    <hyperlink ref="C860" r:id="rId847" xr:uid="{00000000-0004-0000-0000-00004E030000}"/>
-    <hyperlink ref="C861" r:id="rId848" xr:uid="{00000000-0004-0000-0000-00004F030000}"/>
-    <hyperlink ref="C862" r:id="rId849" xr:uid="{00000000-0004-0000-0000-000050030000}"/>
-    <hyperlink ref="C863" r:id="rId850" xr:uid="{00000000-0004-0000-0000-000051030000}"/>
-    <hyperlink ref="C864" r:id="rId851" xr:uid="{00000000-0004-0000-0000-000052030000}"/>
-    <hyperlink ref="C865" r:id="rId852" xr:uid="{00000000-0004-0000-0000-000053030000}"/>
-    <hyperlink ref="C866" r:id="rId853" xr:uid="{00000000-0004-0000-0000-000054030000}"/>
-    <hyperlink ref="C867" r:id="rId854" xr:uid="{00000000-0004-0000-0000-000055030000}"/>
-    <hyperlink ref="C868" r:id="rId855" xr:uid="{00000000-0004-0000-0000-000056030000}"/>
-    <hyperlink ref="C869" r:id="rId856" xr:uid="{00000000-0004-0000-0000-000057030000}"/>
-    <hyperlink ref="C870" r:id="rId857" xr:uid="{00000000-0004-0000-0000-000058030000}"/>
-    <hyperlink ref="C871" r:id="rId858" xr:uid="{00000000-0004-0000-0000-000059030000}"/>
-    <hyperlink ref="C872" r:id="rId859" xr:uid="{00000000-0004-0000-0000-00005A030000}"/>
-    <hyperlink ref="C873" r:id="rId860" xr:uid="{00000000-0004-0000-0000-00005B030000}"/>
-    <hyperlink ref="C874" r:id="rId861" xr:uid="{00000000-0004-0000-0000-00005C030000}"/>
-    <hyperlink ref="C875" r:id="rId862" xr:uid="{00000000-0004-0000-0000-00005D030000}"/>
-    <hyperlink ref="C876" r:id="rId863" xr:uid="{00000000-0004-0000-0000-00005E030000}"/>
-    <hyperlink ref="C877" r:id="rId864" xr:uid="{00000000-0004-0000-0000-00005F030000}"/>
-    <hyperlink ref="C878" r:id="rId865" xr:uid="{00000000-0004-0000-0000-000060030000}"/>
-    <hyperlink ref="C879" r:id="rId866" xr:uid="{00000000-0004-0000-0000-000061030000}"/>
-    <hyperlink ref="C880" r:id="rId867" xr:uid="{00000000-0004-0000-0000-000062030000}"/>
-    <hyperlink ref="C881" r:id="rId868" xr:uid="{00000000-0004-0000-0000-000063030000}"/>
-    <hyperlink ref="C882" r:id="rId869" xr:uid="{00000000-0004-0000-0000-000064030000}"/>
-    <hyperlink ref="C883" r:id="rId870" xr:uid="{00000000-0004-0000-0000-000065030000}"/>
-    <hyperlink ref="C884" r:id="rId871" xr:uid="{00000000-0004-0000-0000-000066030000}"/>
-    <hyperlink ref="C885" r:id="rId872" xr:uid="{00000000-0004-0000-0000-000067030000}"/>
-    <hyperlink ref="C886" r:id="rId873" xr:uid="{00000000-0004-0000-0000-000068030000}"/>
-    <hyperlink ref="C887" r:id="rId874" xr:uid="{00000000-0004-0000-0000-000069030000}"/>
-    <hyperlink ref="C888" r:id="rId875" xr:uid="{00000000-0004-0000-0000-00006A030000}"/>
-    <hyperlink ref="C889" r:id="rId876" xr:uid="{00000000-0004-0000-0000-00006B030000}"/>
-    <hyperlink ref="C890" r:id="rId877" xr:uid="{00000000-0004-0000-0000-00006C030000}"/>
-    <hyperlink ref="C891" r:id="rId878" xr:uid="{00000000-0004-0000-0000-00006D030000}"/>
-    <hyperlink ref="C892" r:id="rId879" xr:uid="{00000000-0004-0000-0000-00006E030000}"/>
-    <hyperlink ref="C893" r:id="rId880" xr:uid="{00000000-0004-0000-0000-00006F030000}"/>
-    <hyperlink ref="C894" r:id="rId881" xr:uid="{00000000-0004-0000-0000-000070030000}"/>
-    <hyperlink ref="C895" r:id="rId882" xr:uid="{00000000-0004-0000-0000-000071030000}"/>
-    <hyperlink ref="C896" r:id="rId883" xr:uid="{00000000-0004-0000-0000-000072030000}"/>
-    <hyperlink ref="C897" r:id="rId884" xr:uid="{00000000-0004-0000-0000-000073030000}"/>
-    <hyperlink ref="C898" r:id="rId885" xr:uid="{00000000-0004-0000-0000-000074030000}"/>
+    <hyperlink ref="C855" r:id="rId841" xr:uid="{00000000-0004-0000-0000-000048030000}"/>
+    <hyperlink ref="C856" r:id="rId842" xr:uid="{00000000-0004-0000-0000-000049030000}"/>
+    <hyperlink ref="C857" r:id="rId843" xr:uid="{00000000-0004-0000-0000-00004A030000}"/>
+    <hyperlink ref="C858" r:id="rId844" xr:uid="{00000000-0004-0000-0000-00004B030000}"/>
+    <hyperlink ref="C859" r:id="rId845" xr:uid="{00000000-0004-0000-0000-00004C030000}"/>
+    <hyperlink ref="C860" r:id="rId846" xr:uid="{00000000-0004-0000-0000-00004D030000}"/>
+    <hyperlink ref="C861" r:id="rId847" xr:uid="{00000000-0004-0000-0000-00004E030000}"/>
+    <hyperlink ref="C862" r:id="rId848" xr:uid="{00000000-0004-0000-0000-00004F030000}"/>
+    <hyperlink ref="C863" r:id="rId849" xr:uid="{00000000-0004-0000-0000-000050030000}"/>
+    <hyperlink ref="C864" r:id="rId850" xr:uid="{00000000-0004-0000-0000-000051030000}"/>
+    <hyperlink ref="C865" r:id="rId851" xr:uid="{00000000-0004-0000-0000-000052030000}"/>
+    <hyperlink ref="C866" r:id="rId852" xr:uid="{00000000-0004-0000-0000-000053030000}"/>
+    <hyperlink ref="C867" r:id="rId853" xr:uid="{00000000-0004-0000-0000-000054030000}"/>
+    <hyperlink ref="C868" r:id="rId854" xr:uid="{00000000-0004-0000-0000-000055030000}"/>
+    <hyperlink ref="C869" r:id="rId855" xr:uid="{00000000-0004-0000-0000-000056030000}"/>
+    <hyperlink ref="C870" r:id="rId856" xr:uid="{00000000-0004-0000-0000-000057030000}"/>
+    <hyperlink ref="C871" r:id="rId857" xr:uid="{00000000-0004-0000-0000-000058030000}"/>
+    <hyperlink ref="C872" r:id="rId858" xr:uid="{00000000-0004-0000-0000-000059030000}"/>
+    <hyperlink ref="C873" r:id="rId859" xr:uid="{00000000-0004-0000-0000-00005A030000}"/>
+    <hyperlink ref="C874" r:id="rId860" xr:uid="{00000000-0004-0000-0000-00005B030000}"/>
+    <hyperlink ref="C875" r:id="rId861" xr:uid="{00000000-0004-0000-0000-00005C030000}"/>
+    <hyperlink ref="C876" r:id="rId862" xr:uid="{00000000-0004-0000-0000-00005D030000}"/>
+    <hyperlink ref="C877" r:id="rId863" xr:uid="{00000000-0004-0000-0000-00005E030000}"/>
+    <hyperlink ref="C878" r:id="rId864" xr:uid="{00000000-0004-0000-0000-00005F030000}"/>
+    <hyperlink ref="C879" r:id="rId865" xr:uid="{00000000-0004-0000-0000-000060030000}"/>
+    <hyperlink ref="C880" r:id="rId866" xr:uid="{00000000-0004-0000-0000-000061030000}"/>
+    <hyperlink ref="C881" r:id="rId867" xr:uid="{00000000-0004-0000-0000-000062030000}"/>
+    <hyperlink ref="C882" r:id="rId868" xr:uid="{00000000-0004-0000-0000-000063030000}"/>
+    <hyperlink ref="C883" r:id="rId869" xr:uid="{00000000-0004-0000-0000-000064030000}"/>
+    <hyperlink ref="C884" r:id="rId870" xr:uid="{00000000-0004-0000-0000-000065030000}"/>
+    <hyperlink ref="C885" r:id="rId871" xr:uid="{00000000-0004-0000-0000-000066030000}"/>
+    <hyperlink ref="C886" r:id="rId872" xr:uid="{00000000-0004-0000-0000-000067030000}"/>
+    <hyperlink ref="C887" r:id="rId873" xr:uid="{00000000-0004-0000-0000-000068030000}"/>
+    <hyperlink ref="C888" r:id="rId874" xr:uid="{00000000-0004-0000-0000-000069030000}"/>
+    <hyperlink ref="C889" r:id="rId875" xr:uid="{00000000-0004-0000-0000-00006A030000}"/>
+    <hyperlink ref="C890" r:id="rId876" xr:uid="{00000000-0004-0000-0000-00006B030000}"/>
+    <hyperlink ref="C891" r:id="rId877" xr:uid="{00000000-0004-0000-0000-00006C030000}"/>
+    <hyperlink ref="C892" r:id="rId878" xr:uid="{00000000-0004-0000-0000-00006D030000}"/>
+    <hyperlink ref="C893" r:id="rId879" xr:uid="{00000000-0004-0000-0000-00006E030000}"/>
+    <hyperlink ref="C894" r:id="rId880" xr:uid="{00000000-0004-0000-0000-00006F030000}"/>
+    <hyperlink ref="C895" r:id="rId881" xr:uid="{00000000-0004-0000-0000-000070030000}"/>
+    <hyperlink ref="C896" r:id="rId882" xr:uid="{00000000-0004-0000-0000-000071030000}"/>
+    <hyperlink ref="C897" r:id="rId883" xr:uid="{00000000-0004-0000-0000-000072030000}"/>
+    <hyperlink ref="C898" r:id="rId884" xr:uid="{00000000-0004-0000-0000-000073030000}"/>
+    <hyperlink ref="C899" r:id="rId885" xr:uid="{00000000-0004-0000-0000-000074030000}"/>
     <hyperlink ref="C26" r:id="rId886" xr:uid="{00000000-0004-0000-0000-000075030000}"/>
-    <hyperlink ref="C899" r:id="rId887" xr:uid="{00000000-0004-0000-0000-000076030000}"/>
-    <hyperlink ref="C900" r:id="rId888" xr:uid="{00000000-0004-0000-0000-000077030000}"/>
-    <hyperlink ref="C901" r:id="rId889" xr:uid="{00000000-0004-0000-0000-000078030000}"/>
-    <hyperlink ref="C902" r:id="rId890" xr:uid="{00000000-0004-0000-0000-000079030000}"/>
-    <hyperlink ref="C903" r:id="rId891" xr:uid="{00000000-0004-0000-0000-00007A030000}"/>
-    <hyperlink ref="C904" r:id="rId892" xr:uid="{00000000-0004-0000-0000-00007B030000}"/>
-    <hyperlink ref="C905" r:id="rId893" xr:uid="{00000000-0004-0000-0000-00007C030000}"/>
-    <hyperlink ref="C906" r:id="rId894" xr:uid="{00000000-0004-0000-0000-00007D030000}"/>
-    <hyperlink ref="C907" r:id="rId895" xr:uid="{00000000-0004-0000-0000-00007E030000}"/>
-    <hyperlink ref="C908" r:id="rId896" xr:uid="{00000000-0004-0000-0000-00007F030000}"/>
-    <hyperlink ref="C909" r:id="rId897" xr:uid="{00000000-0004-0000-0000-000080030000}"/>
-    <hyperlink ref="C910" r:id="rId898" xr:uid="{00000000-0004-0000-0000-000081030000}"/>
-    <hyperlink ref="C911" r:id="rId899" xr:uid="{00000000-0004-0000-0000-000082030000}"/>
-    <hyperlink ref="C912" r:id="rId900" xr:uid="{00000000-0004-0000-0000-000083030000}"/>
-    <hyperlink ref="C913" r:id="rId901" xr:uid="{00000000-0004-0000-0000-000084030000}"/>
-    <hyperlink ref="C914" r:id="rId902" xr:uid="{00000000-0004-0000-0000-000085030000}"/>
-    <hyperlink ref="C915" r:id="rId903" xr:uid="{00000000-0004-0000-0000-000086030000}"/>
-    <hyperlink ref="C916" r:id="rId904" xr:uid="{00000000-0004-0000-0000-000087030000}"/>
-    <hyperlink ref="C917" r:id="rId905" xr:uid="{00000000-0004-0000-0000-000088030000}"/>
-    <hyperlink ref="C918" r:id="rId906" xr:uid="{00000000-0004-0000-0000-000089030000}"/>
-    <hyperlink ref="C919" r:id="rId907" xr:uid="{00000000-0004-0000-0000-00008A030000}"/>
-    <hyperlink ref="C920" r:id="rId908" xr:uid="{00000000-0004-0000-0000-00008B030000}"/>
-    <hyperlink ref="C921" r:id="rId909" xr:uid="{00000000-0004-0000-0000-00008C030000}"/>
-    <hyperlink ref="C922" r:id="rId910" xr:uid="{00000000-0004-0000-0000-00008D030000}"/>
-    <hyperlink ref="C923" r:id="rId911" xr:uid="{00000000-0004-0000-0000-00008E030000}"/>
-    <hyperlink ref="C924" r:id="rId912" xr:uid="{00000000-0004-0000-0000-00008F030000}"/>
-    <hyperlink ref="C925" r:id="rId913" xr:uid="{00000000-0004-0000-0000-000090030000}"/>
-    <hyperlink ref="C926" r:id="rId914" xr:uid="{00000000-0004-0000-0000-000091030000}"/>
-    <hyperlink ref="C927" r:id="rId915" xr:uid="{00000000-0004-0000-0000-000092030000}"/>
-    <hyperlink ref="C928" r:id="rId916" xr:uid="{00000000-0004-0000-0000-000093030000}"/>
-    <hyperlink ref="C929" r:id="rId917" xr:uid="{00000000-0004-0000-0000-000094030000}"/>
-    <hyperlink ref="C930" r:id="rId918" xr:uid="{00000000-0004-0000-0000-000095030000}"/>
-    <hyperlink ref="C931" r:id="rId919" xr:uid="{00000000-0004-0000-0000-000096030000}"/>
-    <hyperlink ref="C932" r:id="rId920" xr:uid="{00000000-0004-0000-0000-000097030000}"/>
-    <hyperlink ref="C933" r:id="rId921" xr:uid="{00000000-0004-0000-0000-000098030000}"/>
-    <hyperlink ref="C934" r:id="rId922" xr:uid="{00000000-0004-0000-0000-000099030000}"/>
-    <hyperlink ref="C935" r:id="rId923" xr:uid="{00000000-0004-0000-0000-00009A030000}"/>
-    <hyperlink ref="C936" r:id="rId924" xr:uid="{00000000-0004-0000-0000-00009B030000}"/>
-    <hyperlink ref="C937" r:id="rId925" xr:uid="{00000000-0004-0000-0000-00009C030000}"/>
-    <hyperlink ref="C938" r:id="rId926" xr:uid="{00000000-0004-0000-0000-00009D030000}"/>
-    <hyperlink ref="C939" r:id="rId927" xr:uid="{00000000-0004-0000-0000-00009E030000}"/>
-    <hyperlink ref="C940" r:id="rId928" xr:uid="{00000000-0004-0000-0000-00009F030000}"/>
-    <hyperlink ref="C941" r:id="rId929" xr:uid="{00000000-0004-0000-0000-0000A0030000}"/>
+    <hyperlink ref="C900" r:id="rId887" xr:uid="{00000000-0004-0000-0000-000076030000}"/>
+    <hyperlink ref="C901" r:id="rId888" xr:uid="{00000000-0004-0000-0000-000077030000}"/>
+    <hyperlink ref="C902" r:id="rId889" xr:uid="{00000000-0004-0000-0000-000078030000}"/>
+    <hyperlink ref="C903" r:id="rId890" xr:uid="{00000000-0004-0000-0000-000079030000}"/>
+    <hyperlink ref="C904" r:id="rId891" xr:uid="{00000000-0004-0000-0000-00007A030000}"/>
+    <hyperlink ref="C905" r:id="rId892" xr:uid="{00000000-0004-0000-0000-00007B030000}"/>
+    <hyperlink ref="C906" r:id="rId893" xr:uid="{00000000-0004-0000-0000-00007C030000}"/>
+    <hyperlink ref="C907" r:id="rId894" xr:uid="{00000000-0004-0000-0000-00007D030000}"/>
+    <hyperlink ref="C908" r:id="rId895" xr:uid="{00000000-0004-0000-0000-00007E030000}"/>
+    <hyperlink ref="C909" r:id="rId896" xr:uid="{00000000-0004-0000-0000-00007F030000}"/>
+    <hyperlink ref="C910" r:id="rId897" xr:uid="{00000000-0004-0000-0000-000080030000}"/>
+    <hyperlink ref="C911" r:id="rId898" xr:uid="{00000000-0004-0000-0000-000081030000}"/>
+    <hyperlink ref="C912" r:id="rId899" xr:uid="{00000000-0004-0000-0000-000082030000}"/>
+    <hyperlink ref="C913" r:id="rId900" xr:uid="{00000000-0004-0000-0000-000083030000}"/>
+    <hyperlink ref="C914" r:id="rId901" xr:uid="{00000000-0004-0000-0000-000084030000}"/>
+    <hyperlink ref="C915" r:id="rId902" xr:uid="{00000000-0004-0000-0000-000085030000}"/>
+    <hyperlink ref="C916" r:id="rId903" xr:uid="{00000000-0004-0000-0000-000086030000}"/>
+    <hyperlink ref="C917" r:id="rId904" xr:uid="{00000000-0004-0000-0000-000087030000}"/>
+    <hyperlink ref="C918" r:id="rId905" xr:uid="{00000000-0004-0000-0000-000088030000}"/>
+    <hyperlink ref="C919" r:id="rId906" xr:uid="{00000000-0004-0000-0000-000089030000}"/>
+    <hyperlink ref="C920" r:id="rId907" xr:uid="{00000000-0004-0000-0000-00008A030000}"/>
+    <hyperlink ref="C921" r:id="rId908" xr:uid="{00000000-0004-0000-0000-00008B030000}"/>
+    <hyperlink ref="C922" r:id="rId909" xr:uid="{00000000-0004-0000-0000-00008C030000}"/>
+    <hyperlink ref="C923" r:id="rId910" xr:uid="{00000000-0004-0000-0000-00008D030000}"/>
+    <hyperlink ref="C924" r:id="rId911" xr:uid="{00000000-0004-0000-0000-00008E030000}"/>
+    <hyperlink ref="C925" r:id="rId912" xr:uid="{00000000-0004-0000-0000-00008F030000}"/>
+    <hyperlink ref="C926" r:id="rId913" xr:uid="{00000000-0004-0000-0000-000090030000}"/>
+    <hyperlink ref="C927" r:id="rId914" xr:uid="{00000000-0004-0000-0000-000091030000}"/>
+    <hyperlink ref="C928" r:id="rId915" xr:uid="{00000000-0004-0000-0000-000092030000}"/>
+    <hyperlink ref="C929" r:id="rId916" xr:uid="{00000000-0004-0000-0000-000093030000}"/>
+    <hyperlink ref="C930" r:id="rId917" xr:uid="{00000000-0004-0000-0000-000094030000}"/>
+    <hyperlink ref="C931" r:id="rId918" xr:uid="{00000000-0004-0000-0000-000095030000}"/>
+    <hyperlink ref="C932" r:id="rId919" xr:uid="{00000000-0004-0000-0000-000096030000}"/>
+    <hyperlink ref="C933" r:id="rId920" xr:uid="{00000000-0004-0000-0000-000097030000}"/>
+    <hyperlink ref="C934" r:id="rId921" xr:uid="{00000000-0004-0000-0000-000098030000}"/>
+    <hyperlink ref="C935" r:id="rId922" xr:uid="{00000000-0004-0000-0000-000099030000}"/>
+    <hyperlink ref="C936" r:id="rId923" xr:uid="{00000000-0004-0000-0000-00009A030000}"/>
+    <hyperlink ref="C937" r:id="rId924" xr:uid="{00000000-0004-0000-0000-00009B030000}"/>
+    <hyperlink ref="C938" r:id="rId925" xr:uid="{00000000-0004-0000-0000-00009C030000}"/>
+    <hyperlink ref="C939" r:id="rId926" xr:uid="{00000000-0004-0000-0000-00009D030000}"/>
+    <hyperlink ref="C940" r:id="rId927" xr:uid="{00000000-0004-0000-0000-00009E030000}"/>
+    <hyperlink ref="C941" r:id="rId928" xr:uid="{00000000-0004-0000-0000-00009F030000}"/>
+    <hyperlink ref="C942" r:id="rId929" xr:uid="{00000000-0004-0000-0000-0000A0030000}"/>
     <hyperlink ref="C27" r:id="rId930" xr:uid="{00000000-0004-0000-0000-0000A1030000}"/>
-    <hyperlink ref="C942" r:id="rId931" xr:uid="{00000000-0004-0000-0000-0000A2030000}"/>
-    <hyperlink ref="C943" r:id="rId932" xr:uid="{00000000-0004-0000-0000-0000A3030000}"/>
-    <hyperlink ref="C944" r:id="rId933" xr:uid="{00000000-0004-0000-0000-0000A4030000}"/>
-    <hyperlink ref="C945" r:id="rId934" xr:uid="{00000000-0004-0000-0000-0000A5030000}"/>
-    <hyperlink ref="C946" r:id="rId935" xr:uid="{00000000-0004-0000-0000-0000A6030000}"/>
+    <hyperlink ref="C943" r:id="rId931" xr:uid="{00000000-0004-0000-0000-0000A2030000}"/>
+    <hyperlink ref="C944" r:id="rId932" xr:uid="{00000000-0004-0000-0000-0000A3030000}"/>
+    <hyperlink ref="C945" r:id="rId933" xr:uid="{00000000-0004-0000-0000-0000A4030000}"/>
+    <hyperlink ref="C946" r:id="rId934" xr:uid="{00000000-0004-0000-0000-0000A5030000}"/>
+    <hyperlink ref="C947" r:id="rId935" xr:uid="{00000000-0004-0000-0000-0000A6030000}"/>
     <hyperlink ref="C28" r:id="rId936" xr:uid="{00000000-0004-0000-0000-0000A7030000}"/>
-    <hyperlink ref="C947" r:id="rId937" xr:uid="{00000000-0004-0000-0000-0000A8030000}"/>
-    <hyperlink ref="C948" r:id="rId938" xr:uid="{00000000-0004-0000-0000-0000A9030000}"/>
-    <hyperlink ref="C949" r:id="rId939" xr:uid="{00000000-0004-0000-0000-0000AA030000}"/>
-    <hyperlink ref="C950" r:id="rId940" xr:uid="{00000000-0004-0000-0000-0000AB030000}"/>
-    <hyperlink ref="C951" r:id="rId941" xr:uid="{00000000-0004-0000-0000-0000AC030000}"/>
-    <hyperlink ref="C952" r:id="rId942" xr:uid="{00000000-0004-0000-0000-0000AD030000}"/>
-    <hyperlink ref="C953" r:id="rId943" xr:uid="{00000000-0004-0000-0000-0000AE030000}"/>
-    <hyperlink ref="C954" r:id="rId944" xr:uid="{00000000-0004-0000-0000-0000AF030000}"/>
-    <hyperlink ref="C955" r:id="rId945" xr:uid="{00000000-0004-0000-0000-0000B0030000}"/>
-    <hyperlink ref="C956" r:id="rId946" xr:uid="{00000000-0004-0000-0000-0000B1030000}"/>
-    <hyperlink ref="C957" r:id="rId947" xr:uid="{00000000-0004-0000-0000-0000B2030000}"/>
-    <hyperlink ref="C958" r:id="rId948" xr:uid="{00000000-0004-0000-0000-0000B3030000}"/>
-    <hyperlink ref="C959" r:id="rId949" xr:uid="{00000000-0004-0000-0000-0000B4030000}"/>
-    <hyperlink ref="C960" r:id="rId950" xr:uid="{00000000-0004-0000-0000-0000B5030000}"/>
-    <hyperlink ref="C961" r:id="rId951" xr:uid="{00000000-0004-0000-0000-0000B6030000}"/>
+    <hyperlink ref="C948" r:id="rId937" xr:uid="{00000000-0004-0000-0000-0000A8030000}"/>
+    <hyperlink ref="C949" r:id="rId938" xr:uid="{00000000-0004-0000-0000-0000A9030000}"/>
+    <hyperlink ref="C950" r:id="rId939" xr:uid="{00000000-0004-0000-0000-0000AA030000}"/>
+    <hyperlink ref="C951" r:id="rId940" xr:uid="{00000000-0004-0000-0000-0000AB030000}"/>
+    <hyperlink ref="C952" r:id="rId941" xr:uid="{00000000-0004-0000-0000-0000AC030000}"/>
+    <hyperlink ref="C953" r:id="rId942" xr:uid="{00000000-0004-0000-0000-0000AD030000}"/>
+    <hyperlink ref="C954" r:id="rId943" xr:uid="{00000000-0004-0000-0000-0000AE030000}"/>
+    <hyperlink ref="C955" r:id="rId944" xr:uid="{00000000-0004-0000-0000-0000AF030000}"/>
+    <hyperlink ref="C956" r:id="rId945" xr:uid="{00000000-0004-0000-0000-0000B0030000}"/>
+    <hyperlink ref="C957" r:id="rId946" xr:uid="{00000000-0004-0000-0000-0000B1030000}"/>
+    <hyperlink ref="C958" r:id="rId947" xr:uid="{00000000-0004-0000-0000-0000B2030000}"/>
+    <hyperlink ref="C959" r:id="rId948" xr:uid="{00000000-0004-0000-0000-0000B3030000}"/>
+    <hyperlink ref="C960" r:id="rId949" xr:uid="{00000000-0004-0000-0000-0000B4030000}"/>
+    <hyperlink ref="C961" r:id="rId950" xr:uid="{00000000-0004-0000-0000-0000B5030000}"/>
+    <hyperlink ref="C962" r:id="rId951" xr:uid="{00000000-0004-0000-0000-0000B6030000}"/>
     <hyperlink ref="C29" r:id="rId952" xr:uid="{00000000-0004-0000-0000-0000B7030000}"/>
-    <hyperlink ref="C962" r:id="rId953" xr:uid="{00000000-0004-0000-0000-0000B8030000}"/>
-    <hyperlink ref="C963" r:id="rId954" xr:uid="{00000000-0004-0000-0000-0000B9030000}"/>
-    <hyperlink ref="C964" r:id="rId955" xr:uid="{00000000-0004-0000-0000-0000BA030000}"/>
-    <hyperlink ref="C965" r:id="rId956" xr:uid="{00000000-0004-0000-0000-0000BB030000}"/>
-    <hyperlink ref="C966" r:id="rId957" xr:uid="{00000000-0004-0000-0000-0000BC030000}"/>
-    <hyperlink ref="C967" r:id="rId958" xr:uid="{00000000-0004-0000-0000-0000BD030000}"/>
-    <hyperlink ref="C968" r:id="rId959" xr:uid="{00000000-0004-0000-0000-0000BE030000}"/>
-    <hyperlink ref="C969" r:id="rId960" xr:uid="{00000000-0004-0000-0000-0000BF030000}"/>
-    <hyperlink ref="C970" r:id="rId961" xr:uid="{00000000-0004-0000-0000-0000C0030000}"/>
-    <hyperlink ref="C971" r:id="rId962" xr:uid="{00000000-0004-0000-0000-0000C1030000}"/>
-    <hyperlink ref="C972" r:id="rId963" xr:uid="{00000000-0004-0000-0000-0000C2030000}"/>
-    <hyperlink ref="C973" r:id="rId964" xr:uid="{00000000-0004-0000-0000-0000C3030000}"/>
-    <hyperlink ref="C974" r:id="rId965" xr:uid="{00000000-0004-0000-0000-0000C4030000}"/>
-    <hyperlink ref="C975" r:id="rId966" xr:uid="{00000000-0004-0000-0000-0000C5030000}"/>
-    <hyperlink ref="C976" r:id="rId967" xr:uid="{00000000-0004-0000-0000-0000C6030000}"/>
-    <hyperlink ref="C977" r:id="rId968" xr:uid="{00000000-0004-0000-0000-0000C7030000}"/>
-    <hyperlink ref="C978" r:id="rId969" xr:uid="{00000000-0004-0000-0000-0000C8030000}"/>
-    <hyperlink ref="C979" r:id="rId970" xr:uid="{00000000-0004-0000-0000-0000C9030000}"/>
-    <hyperlink ref="C980" r:id="rId971" xr:uid="{00000000-0004-0000-0000-0000CA030000}"/>
-    <hyperlink ref="C981" r:id="rId972" xr:uid="{00000000-0004-0000-0000-0000CB030000}"/>
-    <hyperlink ref="C982" r:id="rId973" xr:uid="{00000000-0004-0000-0000-0000CC030000}"/>
-    <hyperlink ref="C983" r:id="rId974" xr:uid="{00000000-0004-0000-0000-0000CD030000}"/>
-    <hyperlink ref="C984" r:id="rId975" xr:uid="{00000000-0004-0000-0000-0000CE030000}"/>
-    <hyperlink ref="C985" r:id="rId976" xr:uid="{00000000-0004-0000-0000-0000CF030000}"/>
-    <hyperlink ref="C986" r:id="rId977" xr:uid="{00000000-0004-0000-0000-0000D0030000}"/>
-    <hyperlink ref="C987" r:id="rId978" xr:uid="{00000000-0004-0000-0000-0000D1030000}"/>
-    <hyperlink ref="C988" r:id="rId979" xr:uid="{00000000-0004-0000-0000-0000D2030000}"/>
-    <hyperlink ref="C989" r:id="rId980" xr:uid="{00000000-0004-0000-0000-0000D3030000}"/>
-    <hyperlink ref="C990" r:id="rId981" xr:uid="{00000000-0004-0000-0000-0000D4030000}"/>
-    <hyperlink ref="C991" r:id="rId982" xr:uid="{00000000-0004-0000-0000-0000D5030000}"/>
-    <hyperlink ref="C992" r:id="rId983" xr:uid="{00000000-0004-0000-0000-0000D6030000}"/>
-    <hyperlink ref="C993" r:id="rId984" xr:uid="{00000000-0004-0000-0000-0000D7030000}"/>
-    <hyperlink ref="C994" r:id="rId985" xr:uid="{00000000-0004-0000-0000-0000D8030000}"/>
-    <hyperlink ref="C995" r:id="rId986" xr:uid="{00000000-0004-0000-0000-0000D9030000}"/>
-    <hyperlink ref="C996" r:id="rId987" xr:uid="{00000000-0004-0000-0000-0000DA030000}"/>
-    <hyperlink ref="C997" r:id="rId988" xr:uid="{00000000-0004-0000-0000-0000DB030000}"/>
-    <hyperlink ref="C998" r:id="rId989" xr:uid="{00000000-0004-0000-0000-0000DC030000}"/>
-    <hyperlink ref="C999" r:id="rId990" xr:uid="{00000000-0004-0000-0000-0000DD030000}"/>
-    <hyperlink ref="C1000" r:id="rId991" xr:uid="{00000000-0004-0000-0000-0000DE030000}"/>
-    <hyperlink ref="C1001" r:id="rId992" xr:uid="{00000000-0004-0000-0000-0000DF030000}"/>
-    <hyperlink ref="C1172" r:id="rId993" xr:uid="{00000000-0004-0000-0000-0000E0030000}"/>
-    <hyperlink ref="C1002" r:id="rId994" xr:uid="{00000000-0004-0000-0000-0000E1030000}"/>
-    <hyperlink ref="C1003" r:id="rId995" xr:uid="{00000000-0004-0000-0000-0000E2030000}"/>
-    <hyperlink ref="C1004" r:id="rId996" xr:uid="{00000000-0004-0000-0000-0000E3030000}"/>
-    <hyperlink ref="C1005" r:id="rId997" xr:uid="{00000000-0004-0000-0000-0000E4030000}"/>
-    <hyperlink ref="C1006" r:id="rId998" xr:uid="{00000000-0004-0000-0000-0000E5030000}"/>
-    <hyperlink ref="C1007" r:id="rId999" xr:uid="{00000000-0004-0000-0000-0000E6030000}"/>
-    <hyperlink ref="C1008" r:id="rId1000" xr:uid="{00000000-0004-0000-0000-0000E7030000}"/>
-    <hyperlink ref="C1009" r:id="rId1001" xr:uid="{00000000-0004-0000-0000-0000E8030000}"/>
-    <hyperlink ref="C1010" r:id="rId1002" xr:uid="{00000000-0004-0000-0000-0000E9030000}"/>
-    <hyperlink ref="C1011" r:id="rId1003" xr:uid="{00000000-0004-0000-0000-0000EA030000}"/>
-    <hyperlink ref="C1012" r:id="rId1004" xr:uid="{00000000-0004-0000-0000-0000EB030000}"/>
+    <hyperlink ref="C963" r:id="rId953" xr:uid="{00000000-0004-0000-0000-0000B8030000}"/>
+    <hyperlink ref="C964" r:id="rId954" xr:uid="{00000000-0004-0000-0000-0000B9030000}"/>
+    <hyperlink ref="C965" r:id="rId955" xr:uid="{00000000-0004-0000-0000-0000BA030000}"/>
+    <hyperlink ref="C966" r:id="rId956" xr:uid="{00000000-0004-0000-0000-0000BB030000}"/>
+    <hyperlink ref="C967" r:id="rId957" xr:uid="{00000000-0004-0000-0000-0000BC030000}"/>
+    <hyperlink ref="C968" r:id="rId958" xr:uid="{00000000-0004-0000-0000-0000BD030000}"/>
+    <hyperlink ref="C969" r:id="rId959" xr:uid="{00000000-0004-0000-0000-0000BE030000}"/>
+    <hyperlink ref="C970" r:id="rId960" xr:uid="{00000000-0004-0000-0000-0000BF030000}"/>
+    <hyperlink ref="C971" r:id="rId961" xr:uid="{00000000-0004-0000-0000-0000C0030000}"/>
+    <hyperlink ref="C972" r:id="rId962" xr:uid="{00000000-0004-0000-0000-0000C1030000}"/>
+    <hyperlink ref="C973" r:id="rId963" xr:uid="{00000000-0004-0000-0000-0000C2030000}"/>
+    <hyperlink ref="C974" r:id="rId964" xr:uid="{00000000-0004-0000-0000-0000C3030000}"/>
+    <hyperlink ref="C975" r:id="rId965" xr:uid="{00000000-0004-0000-0000-0000C4030000}"/>
+    <hyperlink ref="C976" r:id="rId966" xr:uid="{00000000-0004-0000-0000-0000C5030000}"/>
+    <hyperlink ref="C977" r:id="rId967" xr:uid="{00000000-0004-0000-0000-0000C6030000}"/>
+    <hyperlink ref="C978" r:id="rId968" xr:uid="{00000000-0004-0000-0000-0000C7030000}"/>
+    <hyperlink ref="C979" r:id="rId969" xr:uid="{00000000-0004-0000-0000-0000C8030000}"/>
+    <hyperlink ref="C980" r:id="rId970" xr:uid="{00000000-0004-0000-0000-0000C9030000}"/>
+    <hyperlink ref="C981" r:id="rId971" xr:uid="{00000000-0004-0000-0000-0000CA030000}"/>
+    <hyperlink ref="C982" r:id="rId972" xr:uid="{00000000-0004-0000-0000-0000CB030000}"/>
+    <hyperlink ref="C983" r:id="rId973" xr:uid="{00000000-0004-0000-0000-0000CC030000}"/>
+    <hyperlink ref="C984" r:id="rId974" xr:uid="{00000000-0004-0000-0000-0000CD030000}"/>
+    <hyperlink ref="C985" r:id="rId975" xr:uid="{00000000-0004-0000-0000-0000CE030000}"/>
+    <hyperlink ref="C986" r:id="rId976" xr:uid="{00000000-0004-0000-0000-0000CF030000}"/>
+    <hyperlink ref="C987" r:id="rId977" xr:uid="{00000000-0004-0000-0000-0000D0030000}"/>
+    <hyperlink ref="C988" r:id="rId978" xr:uid="{00000000-0004-0000-0000-0000D1030000}"/>
+    <hyperlink ref="C989" r:id="rId979" xr:uid="{00000000-0004-0000-0000-0000D2030000}"/>
+    <hyperlink ref="C990" r:id="rId980" xr:uid="{00000000-0004-0000-0000-0000D3030000}"/>
+    <hyperlink ref="C991" r:id="rId981" xr:uid="{00000000-0004-0000-0000-0000D4030000}"/>
+    <hyperlink ref="C992" r:id="rId982" xr:uid="{00000000-0004-0000-0000-0000D5030000}"/>
+    <hyperlink ref="C993" r:id="rId983" xr:uid="{00000000-0004-0000-0000-0000D6030000}"/>
+    <hyperlink ref="C994" r:id="rId984" xr:uid="{00000000-0004-0000-0000-0000D7030000}"/>
+    <hyperlink ref="C995" r:id="rId985" xr:uid="{00000000-0004-0000-0000-0000D8030000}"/>
+    <hyperlink ref="C996" r:id="rId986" xr:uid="{00000000-0004-0000-0000-0000D9030000}"/>
+    <hyperlink ref="C997" r:id="rId987" xr:uid="{00000000-0004-0000-0000-0000DA030000}"/>
+    <hyperlink ref="C998" r:id="rId988" xr:uid="{00000000-0004-0000-0000-0000DB030000}"/>
+    <hyperlink ref="C999" r:id="rId989" xr:uid="{00000000-0004-0000-0000-0000DC030000}"/>
+    <hyperlink ref="C1000" r:id="rId990" xr:uid="{00000000-0004-0000-0000-0000DD030000}"/>
+    <hyperlink ref="C1001" r:id="rId991" xr:uid="{00000000-0004-0000-0000-0000DE030000}"/>
+    <hyperlink ref="C1002" r:id="rId992" xr:uid="{00000000-0004-0000-0000-0000DF030000}"/>
+    <hyperlink ref="C1003" r:id="rId993" xr:uid="{00000000-0004-0000-0000-0000E0030000}"/>
+    <hyperlink ref="C1004" r:id="rId994" xr:uid="{00000000-0004-0000-0000-0000E1030000}"/>
+    <hyperlink ref="C1005" r:id="rId995" xr:uid="{00000000-0004-0000-0000-0000E2030000}"/>
+    <hyperlink ref="C1006" r:id="rId996" xr:uid="{00000000-0004-0000-0000-0000E3030000}"/>
+    <hyperlink ref="C1007" r:id="rId997" xr:uid="{00000000-0004-0000-0000-0000E4030000}"/>
+    <hyperlink ref="C1008" r:id="rId998" xr:uid="{00000000-0004-0000-0000-0000E5030000}"/>
+    <hyperlink ref="C1009" r:id="rId999" xr:uid="{00000000-0004-0000-0000-0000E6030000}"/>
+    <hyperlink ref="C1010" r:id="rId1000" xr:uid="{00000000-0004-0000-0000-0000E7030000}"/>
+    <hyperlink ref="C1011" r:id="rId1001" xr:uid="{00000000-0004-0000-0000-0000E8030000}"/>
+    <hyperlink ref="C1012" r:id="rId1002" xr:uid="{00000000-0004-0000-0000-0000E9030000}"/>
+    <hyperlink ref="C1013" r:id="rId1003" xr:uid="{00000000-0004-0000-0000-0000EA030000}"/>
+    <hyperlink ref="C1014" r:id="rId1004" xr:uid="{00000000-0004-0000-0000-0000EB030000}"/>
     <hyperlink ref="C30" r:id="rId1005" xr:uid="{00000000-0004-0000-0000-0000EC030000}"/>
-    <hyperlink ref="C1013" r:id="rId1006" xr:uid="{00000000-0004-0000-0000-0000ED030000}"/>
-    <hyperlink ref="C1014" r:id="rId1007" xr:uid="{00000000-0004-0000-0000-0000EE030000}"/>
-    <hyperlink ref="C1015" r:id="rId1008" xr:uid="{00000000-0004-0000-0000-0000EF030000}"/>
-    <hyperlink ref="C1016" r:id="rId1009" xr:uid="{00000000-0004-0000-0000-0000F0030000}"/>
-    <hyperlink ref="C1017" r:id="rId1010" xr:uid="{00000000-0004-0000-0000-0000F1030000}"/>
-    <hyperlink ref="C1018" r:id="rId1011" xr:uid="{00000000-0004-0000-0000-0000F2030000}"/>
-    <hyperlink ref="C1019" r:id="rId1012" xr:uid="{00000000-0004-0000-0000-0000F3030000}"/>
-    <hyperlink ref="C1020" r:id="rId1013" xr:uid="{00000000-0004-0000-0000-0000F4030000}"/>
-    <hyperlink ref="C1021" r:id="rId1014" xr:uid="{00000000-0004-0000-0000-0000F5030000}"/>
-    <hyperlink ref="C1022" r:id="rId1015" xr:uid="{00000000-0004-0000-0000-0000F6030000}"/>
-    <hyperlink ref="C1023" r:id="rId1016" xr:uid="{00000000-0004-0000-0000-0000F7030000}"/>
-    <hyperlink ref="C1024" r:id="rId1017" xr:uid="{00000000-0004-0000-0000-0000F8030000}"/>
-    <hyperlink ref="C1025" r:id="rId1018" xr:uid="{00000000-0004-0000-0000-0000F9030000}"/>
-    <hyperlink ref="C1026" r:id="rId1019" xr:uid="{00000000-0004-0000-0000-0000FA030000}"/>
-    <hyperlink ref="C1027" r:id="rId1020" xr:uid="{00000000-0004-0000-0000-0000FB030000}"/>
-    <hyperlink ref="C1028" r:id="rId1021" xr:uid="{00000000-0004-0000-0000-0000FC030000}"/>
-    <hyperlink ref="C1029" r:id="rId1022" xr:uid="{00000000-0004-0000-0000-0000FD030000}"/>
-    <hyperlink ref="C1030" r:id="rId1023" xr:uid="{00000000-0004-0000-0000-0000FE030000}"/>
-    <hyperlink ref="C1031" r:id="rId1024" xr:uid="{00000000-0004-0000-0000-0000FF030000}"/>
-    <hyperlink ref="C1032" r:id="rId1025" xr:uid="{00000000-0004-0000-0000-000000040000}"/>
-    <hyperlink ref="C1033" r:id="rId1026" xr:uid="{00000000-0004-0000-0000-000001040000}"/>
-    <hyperlink ref="C1034" r:id="rId1027" xr:uid="{00000000-0004-0000-0000-000002040000}"/>
-    <hyperlink ref="C1035" r:id="rId1028" xr:uid="{00000000-0004-0000-0000-000003040000}"/>
-    <hyperlink ref="C1036" r:id="rId1029" xr:uid="{00000000-0004-0000-0000-000004040000}"/>
-    <hyperlink ref="C1037" r:id="rId1030" xr:uid="{00000000-0004-0000-0000-000005040000}"/>
-    <hyperlink ref="C1038" r:id="rId1031" xr:uid="{00000000-0004-0000-0000-000006040000}"/>
-    <hyperlink ref="C1039" r:id="rId1032" xr:uid="{00000000-0004-0000-0000-000007040000}"/>
-    <hyperlink ref="C1040" r:id="rId1033" xr:uid="{00000000-0004-0000-0000-000008040000}"/>
-    <hyperlink ref="C1041" r:id="rId1034" xr:uid="{00000000-0004-0000-0000-000009040000}"/>
-    <hyperlink ref="C1042" r:id="rId1035" xr:uid="{00000000-0004-0000-0000-00000A040000}"/>
+    <hyperlink ref="C1015" r:id="rId1006" xr:uid="{00000000-0004-0000-0000-0000ED030000}"/>
+    <hyperlink ref="C1016" r:id="rId1007" xr:uid="{00000000-0004-0000-0000-0000EE030000}"/>
+    <hyperlink ref="C1017" r:id="rId1008" xr:uid="{00000000-0004-0000-0000-0000EF030000}"/>
+    <hyperlink ref="C1018" r:id="rId1009" xr:uid="{00000000-0004-0000-0000-0000F0030000}"/>
+    <hyperlink ref="C1019" r:id="rId1010" xr:uid="{00000000-0004-0000-0000-0000F1030000}"/>
+    <hyperlink ref="C1020" r:id="rId1011" xr:uid="{00000000-0004-0000-0000-0000F2030000}"/>
+    <hyperlink ref="C1021" r:id="rId1012" xr:uid="{00000000-0004-0000-0000-0000F3030000}"/>
+    <hyperlink ref="C1022" r:id="rId1013" xr:uid="{00000000-0004-0000-0000-0000F4030000}"/>
+    <hyperlink ref="C1023" r:id="rId1014" xr:uid="{00000000-0004-0000-0000-0000F5030000}"/>
+    <hyperlink ref="C1024" r:id="rId1015" xr:uid="{00000000-0004-0000-0000-0000F6030000}"/>
+    <hyperlink ref="C1025" r:id="rId1016" xr:uid="{00000000-0004-0000-0000-0000F7030000}"/>
+    <hyperlink ref="C1026" r:id="rId1017" xr:uid="{00000000-0004-0000-0000-0000F8030000}"/>
+    <hyperlink ref="C1027" r:id="rId1018" xr:uid="{00000000-0004-0000-0000-0000F9030000}"/>
+    <hyperlink ref="C1028" r:id="rId1019" xr:uid="{00000000-0004-0000-0000-0000FA030000}"/>
+    <hyperlink ref="C1029" r:id="rId1020" xr:uid="{00000000-0004-0000-0000-0000FB030000}"/>
+    <hyperlink ref="C1030" r:id="rId1021" xr:uid="{00000000-0004-0000-0000-0000FC030000}"/>
+    <hyperlink ref="C1031" r:id="rId1022" xr:uid="{00000000-0004-0000-0000-0000FD030000}"/>
+    <hyperlink ref="C1032" r:id="rId1023" xr:uid="{00000000-0004-0000-0000-0000FE030000}"/>
+    <hyperlink ref="C1033" r:id="rId1024" xr:uid="{00000000-0004-0000-0000-0000FF030000}"/>
+    <hyperlink ref="C1034" r:id="rId1025" xr:uid="{00000000-0004-0000-0000-000000040000}"/>
+    <hyperlink ref="C1035" r:id="rId1026" xr:uid="{00000000-0004-0000-0000-000001040000}"/>
+    <hyperlink ref="C1036" r:id="rId1027" xr:uid="{00000000-0004-0000-0000-000002040000}"/>
+    <hyperlink ref="C1037" r:id="rId1028" xr:uid="{00000000-0004-0000-0000-000003040000}"/>
+    <hyperlink ref="C1038" r:id="rId1029" xr:uid="{00000000-0004-0000-0000-000004040000}"/>
+    <hyperlink ref="C1039" r:id="rId1030" xr:uid="{00000000-0004-0000-0000-000005040000}"/>
+    <hyperlink ref="C1040" r:id="rId1031" xr:uid="{00000000-0004-0000-0000-000006040000}"/>
+    <hyperlink ref="C1041" r:id="rId1032" xr:uid="{00000000-0004-0000-0000-000007040000}"/>
+    <hyperlink ref="C1042" r:id="rId1033" xr:uid="{00000000-0004-0000-0000-000008040000}"/>
+    <hyperlink ref="C1043" r:id="rId1034" xr:uid="{00000000-0004-0000-0000-000009040000}"/>
+    <hyperlink ref="C1044" r:id="rId1035" xr:uid="{00000000-0004-0000-0000-00000A040000}"/>
     <hyperlink ref="C31" r:id="rId1036" xr:uid="{00000000-0004-0000-0000-00000B040000}"/>
     <hyperlink ref="C32" r:id="rId1037" xr:uid="{00000000-0004-0000-0000-00000C040000}"/>
     <hyperlink ref="C33" r:id="rId1038" xr:uid="{00000000-0004-0000-0000-00000D040000}"/>
-    <hyperlink ref="C1043" r:id="rId1039" xr:uid="{00000000-0004-0000-0000-00000E040000}"/>
-    <hyperlink ref="C1044" r:id="rId1040" xr:uid="{00000000-0004-0000-0000-00000F040000}"/>
-    <hyperlink ref="C1045" r:id="rId1041" xr:uid="{00000000-0004-0000-0000-000010040000}"/>
-    <hyperlink ref="C1046" r:id="rId1042" xr:uid="{00000000-0004-0000-0000-000011040000}"/>
-    <hyperlink ref="C1047" r:id="rId1043" xr:uid="{00000000-0004-0000-0000-000012040000}"/>
-    <hyperlink ref="C1048" r:id="rId1044" xr:uid="{00000000-0004-0000-0000-000013040000}"/>
-    <hyperlink ref="C1049" r:id="rId1045" xr:uid="{00000000-0004-0000-0000-000014040000}"/>
-    <hyperlink ref="C1050" r:id="rId1046" xr:uid="{00000000-0004-0000-0000-000015040000}"/>
-    <hyperlink ref="C1051" r:id="rId1047" xr:uid="{00000000-0004-0000-0000-000016040000}"/>
-    <hyperlink ref="C1052" r:id="rId1048" xr:uid="{00000000-0004-0000-0000-000017040000}"/>
-    <hyperlink ref="C1053" r:id="rId1049" xr:uid="{00000000-0004-0000-0000-000018040000}"/>
-    <hyperlink ref="C1054" r:id="rId1050" xr:uid="{00000000-0004-0000-0000-000019040000}"/>
-    <hyperlink ref="C1055" r:id="rId1051" xr:uid="{00000000-0004-0000-0000-00001A040000}"/>
-    <hyperlink ref="C1056" r:id="rId1052" xr:uid="{00000000-0004-0000-0000-00001B040000}"/>
-    <hyperlink ref="C1057" r:id="rId1053" xr:uid="{00000000-0004-0000-0000-00001C040000}"/>
-    <hyperlink ref="C1058" r:id="rId1054" xr:uid="{00000000-0004-0000-0000-00001D040000}"/>
-    <hyperlink ref="C1059" r:id="rId1055" xr:uid="{00000000-0004-0000-0000-00001E040000}"/>
-    <hyperlink ref="C1060" r:id="rId1056" xr:uid="{00000000-0004-0000-0000-00001F040000}"/>
-    <hyperlink ref="C1061" r:id="rId1057" xr:uid="{00000000-0004-0000-0000-000020040000}"/>
-    <hyperlink ref="C1062" r:id="rId1058" xr:uid="{00000000-0004-0000-0000-000021040000}"/>
-    <hyperlink ref="C1063" r:id="rId1059" xr:uid="{00000000-0004-0000-0000-000022040000}"/>
-    <hyperlink ref="C1064" r:id="rId1060" xr:uid="{00000000-0004-0000-0000-000023040000}"/>
-    <hyperlink ref="C1065" r:id="rId1061" xr:uid="{00000000-0004-0000-0000-000024040000}"/>
-    <hyperlink ref="C1066" r:id="rId1062" xr:uid="{00000000-0004-0000-0000-000025040000}"/>
-    <hyperlink ref="C1067" r:id="rId1063" xr:uid="{00000000-0004-0000-0000-000026040000}"/>
-    <hyperlink ref="C1068" r:id="rId1064" xr:uid="{00000000-0004-0000-0000-000027040000}"/>
+    <hyperlink ref="C1045" r:id="rId1039" xr:uid="{00000000-0004-0000-0000-00000E040000}"/>
+    <hyperlink ref="C1046" r:id="rId1040" xr:uid="{00000000-0004-0000-0000-00000F040000}"/>
+    <hyperlink ref="C1047" r:id="rId1041" xr:uid="{00000000-0004-0000-0000-000010040000}"/>
+    <hyperlink ref="C1048" r:id="rId1042" xr:uid="{00000000-0004-0000-0000-000011040000}"/>
+    <hyperlink ref="C1049" r:id="rId1043" xr:uid="{00000000-0004-0000-0000-000012040000}"/>
+    <hyperlink ref="C1050" r:id="rId1044" xr:uid="{00000000-0004-0000-0000-000013040000}"/>
+    <hyperlink ref="C1051" r:id="rId1045" xr:uid="{00000000-0004-0000-0000-000014040000}"/>
+    <hyperlink ref="C1052" r:id="rId1046" xr:uid="{00000000-0004-0000-0000-000015040000}"/>
+    <hyperlink ref="C1053" r:id="rId1047" xr:uid="{00000000-0004-0000-0000-000016040000}"/>
+    <hyperlink ref="C1054" r:id="rId1048" xr:uid="{00000000-0004-0000-0000-000017040000}"/>
+    <hyperlink ref="C1055" r:id="rId1049" xr:uid="{00000000-0004-0000-0000-000018040000}"/>
+    <hyperlink ref="C1056" r:id="rId1050" xr:uid="{00000000-0004-0000-0000-000019040000}"/>
+    <hyperlink ref="C1057" r:id="rId1051" xr:uid="{00000000-0004-0000-0000-00001A040000}"/>
+    <hyperlink ref="C1058" r:id="rId1052" xr:uid="{00000000-0004-0000-0000-00001B040000}"/>
+    <hyperlink ref="C1059" r:id="rId1053" xr:uid="{00000000-0004-0000-0000-00001C040000}"/>
+    <hyperlink ref="C1060" r:id="rId1054" xr:uid="{00000000-0004-0000-0000-00001D040000}"/>
+    <hyperlink ref="C1061" r:id="rId1055" xr:uid="{00000000-0004-0000-0000-00001E040000}"/>
+    <hyperlink ref="C1062" r:id="rId1056" xr:uid="{00000000-0004-0000-0000-00001F040000}"/>
+    <hyperlink ref="C1063" r:id="rId1057" xr:uid="{00000000-0004-0000-0000-000020040000}"/>
+    <hyperlink ref="C1064" r:id="rId1058" xr:uid="{00000000-0004-0000-0000-000021040000}"/>
+    <hyperlink ref="C1065" r:id="rId1059" xr:uid="{00000000-0004-0000-0000-000022040000}"/>
+    <hyperlink ref="C1066" r:id="rId1060" xr:uid="{00000000-0004-0000-0000-000023040000}"/>
+    <hyperlink ref="C1067" r:id="rId1061" xr:uid="{00000000-0004-0000-0000-000024040000}"/>
+    <hyperlink ref="C1068" r:id="rId1062" xr:uid="{00000000-0004-0000-0000-000025040000}"/>
+    <hyperlink ref="C1069" r:id="rId1063" xr:uid="{00000000-0004-0000-0000-000026040000}"/>
+    <hyperlink ref="C1070" r:id="rId1064" xr:uid="{00000000-0004-0000-0000-000027040000}"/>
     <hyperlink ref="C34" r:id="rId1065" xr:uid="{00000000-0004-0000-0000-000028040000}"/>
-    <hyperlink ref="C1069" r:id="rId1066" xr:uid="{00000000-0004-0000-0000-000029040000}"/>
-    <hyperlink ref="C1070" r:id="rId1067" xr:uid="{00000000-0004-0000-0000-00002A040000}"/>
-    <hyperlink ref="C1071" r:id="rId1068" xr:uid="{00000000-0004-0000-0000-00002B040000}"/>
-    <hyperlink ref="C1072" r:id="rId1069" xr:uid="{00000000-0004-0000-0000-00002C040000}"/>
-    <hyperlink ref="C1073" r:id="rId1070" xr:uid="{00000000-0004-0000-0000-00002D040000}"/>
-    <hyperlink ref="C1074" r:id="rId1071" xr:uid="{00000000-0004-0000-0000-00002E040000}"/>
-    <hyperlink ref="C1075" r:id="rId1072" xr:uid="{00000000-0004-0000-0000-00002F040000}"/>
-    <hyperlink ref="C1076" r:id="rId1073" xr:uid="{00000000-0004-0000-0000-000030040000}"/>
-    <hyperlink ref="C1077" r:id="rId1074" xr:uid="{00000000-0004-0000-0000-000031040000}"/>
-    <hyperlink ref="C1078" r:id="rId1075" xr:uid="{00000000-0004-0000-0000-000032040000}"/>
-    <hyperlink ref="C1079" r:id="rId1076" xr:uid="{00000000-0004-0000-0000-000033040000}"/>
-    <hyperlink ref="C1080" r:id="rId1077" xr:uid="{00000000-0004-0000-0000-000034040000}"/>
-    <hyperlink ref="C1081" r:id="rId1078" xr:uid="{00000000-0004-0000-0000-000035040000}"/>
-    <hyperlink ref="C1082" r:id="rId1079" xr:uid="{00000000-0004-0000-0000-000036040000}"/>
-    <hyperlink ref="C1083" r:id="rId1080" xr:uid="{00000000-0004-0000-0000-000037040000}"/>
-    <hyperlink ref="C1084" r:id="rId1081" xr:uid="{00000000-0004-0000-0000-000038040000}"/>
-    <hyperlink ref="C1085" r:id="rId1082" xr:uid="{00000000-0004-0000-0000-000039040000}"/>
-    <hyperlink ref="C1086" r:id="rId1083" xr:uid="{00000000-0004-0000-0000-00003A040000}"/>
-    <hyperlink ref="C1087" r:id="rId1084" xr:uid="{00000000-0004-0000-0000-00003B040000}"/>
-    <hyperlink ref="C1088" r:id="rId1085" xr:uid="{00000000-0004-0000-0000-00003C040000}"/>
-    <hyperlink ref="C1089" r:id="rId1086" xr:uid="{00000000-0004-0000-0000-00003D040000}"/>
-    <hyperlink ref="C1090" r:id="rId1087" xr:uid="{00000000-0004-0000-0000-00003E040000}"/>
-    <hyperlink ref="C1091" r:id="rId1088" xr:uid="{00000000-0004-0000-0000-00003F040000}"/>
-    <hyperlink ref="C1092" r:id="rId1089" xr:uid="{00000000-0004-0000-0000-000040040000}"/>
-    <hyperlink ref="C1093" r:id="rId1090" xr:uid="{00000000-0004-0000-0000-000041040000}"/>
-    <hyperlink ref="C1094" r:id="rId1091" xr:uid="{00000000-0004-0000-0000-000042040000}"/>
-    <hyperlink ref="C1095" r:id="rId1092" xr:uid="{00000000-0004-0000-0000-000043040000}"/>
-    <hyperlink ref="C1096" r:id="rId1093" xr:uid="{00000000-0004-0000-0000-000044040000}"/>
-    <hyperlink ref="C1097" r:id="rId1094" xr:uid="{00000000-0004-0000-0000-000045040000}"/>
-    <hyperlink ref="C1098" r:id="rId1095" xr:uid="{00000000-0004-0000-0000-000046040000}"/>
-    <hyperlink ref="C1099" r:id="rId1096" xr:uid="{00000000-0004-0000-0000-000047040000}"/>
-    <hyperlink ref="C1100" r:id="rId1097" xr:uid="{00000000-0004-0000-0000-000048040000}"/>
-    <hyperlink ref="C1101" r:id="rId1098" xr:uid="{00000000-0004-0000-0000-000049040000}"/>
-    <hyperlink ref="C1102" r:id="rId1099" xr:uid="{00000000-0004-0000-0000-00004A040000}"/>
-    <hyperlink ref="C1103" r:id="rId1100" xr:uid="{00000000-0004-0000-0000-00004B040000}"/>
-    <hyperlink ref="C1104" r:id="rId1101" xr:uid="{00000000-0004-0000-0000-00004C040000}"/>
-    <hyperlink ref="C1105" r:id="rId1102" xr:uid="{00000000-0004-0000-0000-00004D040000}"/>
-    <hyperlink ref="C1106" r:id="rId1103" xr:uid="{00000000-0004-0000-0000-00004E040000}"/>
-    <hyperlink ref="C1107" r:id="rId1104" xr:uid="{00000000-0004-0000-0000-00004F040000}"/>
-    <hyperlink ref="C1108" r:id="rId1105" xr:uid="{00000000-0004-0000-0000-000050040000}"/>
-    <hyperlink ref="C1109" r:id="rId1106" xr:uid="{00000000-0004-0000-0000-000051040000}"/>
-    <hyperlink ref="C1110" r:id="rId1107" xr:uid="{00000000-0004-0000-0000-000052040000}"/>
-    <hyperlink ref="C1111" r:id="rId1108" xr:uid="{00000000-0004-0000-0000-000053040000}"/>
-    <hyperlink ref="C1112" r:id="rId1109" xr:uid="{00000000-0004-0000-0000-000054040000}"/>
-    <hyperlink ref="C1113" r:id="rId1110" xr:uid="{00000000-0004-0000-0000-000055040000}"/>
-    <hyperlink ref="C1114" r:id="rId1111" xr:uid="{00000000-0004-0000-0000-000056040000}"/>
-    <hyperlink ref="C1115" r:id="rId1112" xr:uid="{00000000-0004-0000-0000-000057040000}"/>
-    <hyperlink ref="C1116" r:id="rId1113" xr:uid="{00000000-0004-0000-0000-000058040000}"/>
-    <hyperlink ref="C1117" r:id="rId1114" xr:uid="{00000000-0004-0000-0000-000059040000}"/>
-    <hyperlink ref="C1118" r:id="rId1115" xr:uid="{00000000-0004-0000-0000-00005A040000}"/>
-    <hyperlink ref="C1119" r:id="rId1116" xr:uid="{00000000-0004-0000-0000-00005B040000}"/>
-    <hyperlink ref="C1120" r:id="rId1117" xr:uid="{00000000-0004-0000-0000-00005C040000}"/>
-    <hyperlink ref="C1121" r:id="rId1118" xr:uid="{00000000-0004-0000-0000-00005D040000}"/>
-    <hyperlink ref="C1122" r:id="rId1119" xr:uid="{00000000-0004-0000-0000-00005E040000}"/>
-    <hyperlink ref="C1123" r:id="rId1120" xr:uid="{00000000-0004-0000-0000-00005F040000}"/>
-    <hyperlink ref="C1124" r:id="rId1121" xr:uid="{00000000-0004-0000-0000-000060040000}"/>
+    <hyperlink ref="C1071" r:id="rId1066" xr:uid="{00000000-0004-0000-0000-000029040000}"/>
+    <hyperlink ref="C1072" r:id="rId1067" xr:uid="{00000000-0004-0000-0000-00002A040000}"/>
+    <hyperlink ref="C1073" r:id="rId1068" xr:uid="{00000000-0004-0000-0000-00002B040000}"/>
+    <hyperlink ref="C1074" r:id="rId1069" xr:uid="{00000000-0004-0000-0000-00002C040000}"/>
+    <hyperlink ref="C1075" r:id="rId1070" xr:uid="{00000000-0004-0000-0000-00002D040000}"/>
+    <hyperlink ref="C1076" r:id="rId1071" xr:uid="{00000000-0004-0000-0000-00002E040000}"/>
+    <hyperlink ref="C1077" r:id="rId1072" xr:uid="{00000000-0004-0000-0000-00002F040000}"/>
+    <hyperlink ref="C1078" r:id="rId1073" xr:uid="{00000000-0004-0000-0000-000030040000}"/>
+    <hyperlink ref="C1079" r:id="rId1074" xr:uid="{00000000-0004-0000-0000-000031040000}"/>
+    <hyperlink ref="C1080" r:id="rId1075" xr:uid="{00000000-0004-0000-0000-000032040000}"/>
+    <hyperlink ref="C1081" r:id="rId1076" xr:uid="{00000000-0004-0000-0000-000033040000}"/>
+    <hyperlink ref="C1082" r:id="rId1077" xr:uid="{00000000-0004-0000-0000-000034040000}"/>
+    <hyperlink ref="C1083" r:id="rId1078" xr:uid="{00000000-0004-0000-0000-000035040000}"/>
+    <hyperlink ref="C1084" r:id="rId1079" xr:uid="{00000000-0004-0000-0000-000036040000}"/>
+    <hyperlink ref="C1085" r:id="rId1080" xr:uid="{00000000-0004-0000-0000-000037040000}"/>
+    <hyperlink ref="C1086" r:id="rId1081" xr:uid="{00000000-0004-0000-0000-000038040000}"/>
+    <hyperlink ref="C1087" r:id="rId1082" xr:uid="{00000000-0004-0000-0000-000039040000}"/>
+    <hyperlink ref="C1088" r:id="rId1083" xr:uid="{00000000-0004-0000-0000-00003A040000}"/>
+    <hyperlink ref="C1089" r:id="rId1084" xr:uid="{00000000-0004-0000-0000-00003B040000}"/>
+    <hyperlink ref="C1090" r:id="rId1085" xr:uid="{00000000-0004-0000-0000-00003C040000}"/>
+    <hyperlink ref="C1091" r:id="rId1086" xr:uid="{00000000-0004-0000-0000-00003D040000}"/>
+    <hyperlink ref="C1092" r:id="rId1087" xr:uid="{00000000-0004-0000-0000-00003E040000}"/>
+    <hyperlink ref="C1093" r:id="rId1088" xr:uid="{00000000-0004-0000-0000-00003F040000}"/>
+    <hyperlink ref="C1094" r:id="rId1089" xr:uid="{00000000-0004-0000-0000-000040040000}"/>
+    <hyperlink ref="C1095" r:id="rId1090" xr:uid="{00000000-0004-0000-0000-000041040000}"/>
+    <hyperlink ref="C1096" r:id="rId1091" xr:uid="{00000000-0004-0000-0000-000042040000}"/>
+    <hyperlink ref="C1097" r:id="rId1092" xr:uid="{00000000-0004-0000-0000-000043040000}"/>
+    <hyperlink ref="C1098" r:id="rId1093" xr:uid="{00000000-0004-0000-0000-000044040000}"/>
+    <hyperlink ref="C1099" r:id="rId1094" xr:uid="{00000000-0004-0000-0000-000045040000}"/>
+    <hyperlink ref="C1100" r:id="rId1095" xr:uid="{00000000-0004-0000-0000-000046040000}"/>
+    <hyperlink ref="C1101" r:id="rId1096" xr:uid="{00000000-0004-0000-0000-000047040000}"/>
+    <hyperlink ref="C1102" r:id="rId1097" xr:uid="{00000000-0004-0000-0000-000048040000}"/>
+    <hyperlink ref="C1103" r:id="rId1098" xr:uid="{00000000-0004-0000-0000-000049040000}"/>
+    <hyperlink ref="C1104" r:id="rId1099" xr:uid="{00000000-0004-0000-0000-00004A040000}"/>
+    <hyperlink ref="C1105" r:id="rId1100" xr:uid="{00000000-0004-0000-0000-00004B040000}"/>
+    <hyperlink ref="C1106" r:id="rId1101" xr:uid="{00000000-0004-0000-0000-00004C040000}"/>
+    <hyperlink ref="C1107" r:id="rId1102" xr:uid="{00000000-0004-0000-0000-00004D040000}"/>
+    <hyperlink ref="C1108" r:id="rId1103" xr:uid="{00000000-0004-0000-0000-00004E040000}"/>
+    <hyperlink ref="C1109" r:id="rId1104" xr:uid="{00000000-0004-0000-0000-00004F040000}"/>
+    <hyperlink ref="C1110" r:id="rId1105" xr:uid="{00000000-0004-0000-0000-000050040000}"/>
+    <hyperlink ref="C1111" r:id="rId1106" xr:uid="{00000000-0004-0000-0000-000051040000}"/>
+    <hyperlink ref="C1112" r:id="rId1107" xr:uid="{00000000-0004-0000-0000-000052040000}"/>
+    <hyperlink ref="C1113" r:id="rId1108" xr:uid="{00000000-0004-0000-0000-000053040000}"/>
+    <hyperlink ref="C1114" r:id="rId1109" xr:uid="{00000000-0004-0000-0000-000054040000}"/>
+    <hyperlink ref="C1115" r:id="rId1110" xr:uid="{00000000-0004-0000-0000-000055040000}"/>
+    <hyperlink ref="C1116" r:id="rId1111" xr:uid="{00000000-0004-0000-0000-000056040000}"/>
+    <hyperlink ref="C1117" r:id="rId1112" xr:uid="{00000000-0004-0000-0000-000057040000}"/>
+    <hyperlink ref="C1118" r:id="rId1113" xr:uid="{00000000-0004-0000-0000-000058040000}"/>
+    <hyperlink ref="C1119" r:id="rId1114" xr:uid="{00000000-0004-0000-0000-000059040000}"/>
+    <hyperlink ref="C1120" r:id="rId1115" xr:uid="{00000000-0004-0000-0000-00005A040000}"/>
+    <hyperlink ref="C1121" r:id="rId1116" xr:uid="{00000000-0004-0000-0000-00005B040000}"/>
+    <hyperlink ref="C1122" r:id="rId1117" xr:uid="{00000000-0004-0000-0000-00005C040000}"/>
+    <hyperlink ref="C1123" r:id="rId1118" xr:uid="{00000000-0004-0000-0000-00005D040000}"/>
+    <hyperlink ref="C1124" r:id="rId1119" xr:uid="{00000000-0004-0000-0000-00005E040000}"/>
+    <hyperlink ref="C1125" r:id="rId1120" xr:uid="{00000000-0004-0000-0000-00005F040000}"/>
+    <hyperlink ref="C1126" r:id="rId1121" xr:uid="{00000000-0004-0000-0000-000060040000}"/>
     <hyperlink ref="C35" r:id="rId1122" xr:uid="{00000000-0004-0000-0000-000061040000}"/>
-    <hyperlink ref="C1125" r:id="rId1123" xr:uid="{00000000-0004-0000-0000-000062040000}"/>
-    <hyperlink ref="C1126" r:id="rId1124" xr:uid="{00000000-0004-0000-0000-000063040000}"/>
-    <hyperlink ref="C1127" r:id="rId1125" xr:uid="{00000000-0004-0000-0000-000064040000}"/>
-    <hyperlink ref="C1128" r:id="rId1126" xr:uid="{00000000-0004-0000-0000-000065040000}"/>
-    <hyperlink ref="C1129" r:id="rId1127" xr:uid="{00000000-0004-0000-0000-000066040000}"/>
+    <hyperlink ref="C1127" r:id="rId1123" xr:uid="{00000000-0004-0000-0000-000062040000}"/>
+    <hyperlink ref="C1128" r:id="rId1124" xr:uid="{00000000-0004-0000-0000-000063040000}"/>
+    <hyperlink ref="C1129" r:id="rId1125" xr:uid="{00000000-0004-0000-0000-000064040000}"/>
+    <hyperlink ref="C1130" r:id="rId1126" xr:uid="{00000000-0004-0000-0000-000065040000}"/>
+    <hyperlink ref="C1131" r:id="rId1127" xr:uid="{00000000-0004-0000-0000-000066040000}"/>
     <hyperlink ref="C36" r:id="rId1128" xr:uid="{00000000-0004-0000-0000-000067040000}"/>
-    <hyperlink ref="C1130" r:id="rId1129" xr:uid="{00000000-0004-0000-0000-000068040000}"/>
-    <hyperlink ref="C1131" r:id="rId1130" xr:uid="{00000000-0004-0000-0000-000069040000}"/>
-    <hyperlink ref="C1132" r:id="rId1131" xr:uid="{00000000-0004-0000-0000-00006A040000}"/>
-    <hyperlink ref="C1133" r:id="rId1132" xr:uid="{00000000-0004-0000-0000-00006B040000}"/>
+    <hyperlink ref="C1132" r:id="rId1129" xr:uid="{00000000-0004-0000-0000-000068040000}"/>
+    <hyperlink ref="C1133" r:id="rId1130" xr:uid="{00000000-0004-0000-0000-000069040000}"/>
+    <hyperlink ref="C1134" r:id="rId1131" xr:uid="{00000000-0004-0000-0000-00006A040000}"/>
+    <hyperlink ref="C1135" r:id="rId1132" xr:uid="{00000000-0004-0000-0000-00006B040000}"/>
     <hyperlink ref="C37" r:id="rId1133" xr:uid="{00000000-0004-0000-0000-00006C040000}"/>
-    <hyperlink ref="C1134" r:id="rId1134" xr:uid="{00000000-0004-0000-0000-00006D040000}"/>
-    <hyperlink ref="C1135" r:id="rId1135" xr:uid="{00000000-0004-0000-0000-00006E040000}"/>
-    <hyperlink ref="C1136" r:id="rId1136" xr:uid="{00000000-0004-0000-0000-00006F040000}"/>
-    <hyperlink ref="C1137" r:id="rId1137" xr:uid="{00000000-0004-0000-0000-000070040000}"/>
-    <hyperlink ref="C1138" r:id="rId1138" xr:uid="{00000000-0004-0000-0000-000071040000}"/>
-    <hyperlink ref="C1139" r:id="rId1139" xr:uid="{00000000-0004-0000-0000-000072040000}"/>
-    <hyperlink ref="C1140" r:id="rId1140" xr:uid="{00000000-0004-0000-0000-000073040000}"/>
-    <hyperlink ref="C1141" r:id="rId1141" xr:uid="{00000000-0004-0000-0000-000074040000}"/>
-    <hyperlink ref="C1142" r:id="rId1142" xr:uid="{00000000-0004-0000-0000-000075040000}"/>
-    <hyperlink ref="C1143" r:id="rId1143" xr:uid="{00000000-0004-0000-0000-000076040000}"/>
-    <hyperlink ref="C1144" r:id="rId1144" xr:uid="{00000000-0004-0000-0000-000077040000}"/>
-    <hyperlink ref="C1145" r:id="rId1145" xr:uid="{00000000-0004-0000-0000-000078040000}"/>
-    <hyperlink ref="C1146" r:id="rId1146" xr:uid="{00000000-0004-0000-0000-000079040000}"/>
-    <hyperlink ref="C1147" r:id="rId1147" xr:uid="{00000000-0004-0000-0000-00007A040000}"/>
-    <hyperlink ref="C1148" r:id="rId1148" xr:uid="{00000000-0004-0000-0000-00007B040000}"/>
-    <hyperlink ref="C1149" r:id="rId1149" xr:uid="{00000000-0004-0000-0000-00007C040000}"/>
-    <hyperlink ref="C1150" r:id="rId1150" xr:uid="{00000000-0004-0000-0000-00007D040000}"/>
-    <hyperlink ref="C1151" r:id="rId1151" xr:uid="{00000000-0004-0000-0000-00007E040000}"/>
-    <hyperlink ref="C1152" r:id="rId1152" xr:uid="{00000000-0004-0000-0000-00007F040000}"/>
+    <hyperlink ref="C1136" r:id="rId1134" xr:uid="{00000000-0004-0000-0000-00006D040000}"/>
+    <hyperlink ref="C1137" r:id="rId1135" xr:uid="{00000000-0004-0000-0000-00006E040000}"/>
+    <hyperlink ref="C1138" r:id="rId1136" xr:uid="{00000000-0004-0000-0000-00006F040000}"/>
+    <hyperlink ref="C1139" r:id="rId1137" xr:uid="{00000000-0004-0000-0000-000070040000}"/>
+    <hyperlink ref="C1140" r:id="rId1138" xr:uid="{00000000-0004-0000-0000-000071040000}"/>
+    <hyperlink ref="C1141" r:id="rId1139" xr:uid="{00000000-0004-0000-0000-000072040000}"/>
+    <hyperlink ref="C1142" r:id="rId1140" xr:uid="{00000000-0004-0000-0000-000073040000}"/>
+    <hyperlink ref="C1143" r:id="rId1141" xr:uid="{00000000-0004-0000-0000-000074040000}"/>
+    <hyperlink ref="C1144" r:id="rId1142" xr:uid="{00000000-0004-0000-0000-000075040000}"/>
+    <hyperlink ref="C1145" r:id="rId1143" xr:uid="{00000000-0004-0000-0000-000076040000}"/>
+    <hyperlink ref="C1146" r:id="rId1144" xr:uid="{00000000-0004-0000-0000-000077040000}"/>
+    <hyperlink ref="C1147" r:id="rId1145" xr:uid="{00000000-0004-0000-0000-000078040000}"/>
+    <hyperlink ref="C1148" r:id="rId1146" xr:uid="{00000000-0004-0000-0000-000079040000}"/>
+    <hyperlink ref="C1149" r:id="rId1147" xr:uid="{00000000-0004-0000-0000-00007A040000}"/>
+    <hyperlink ref="C1150" r:id="rId1148" xr:uid="{00000000-0004-0000-0000-00007B040000}"/>
+    <hyperlink ref="C1151" r:id="rId1149" xr:uid="{00000000-0004-0000-0000-00007C040000}"/>
+    <hyperlink ref="C1152" r:id="rId1150" xr:uid="{00000000-0004-0000-0000-00007D040000}"/>
+    <hyperlink ref="C1153" r:id="rId1151" xr:uid="{00000000-0004-0000-0000-00007E040000}"/>
+    <hyperlink ref="C1154" r:id="rId1152" xr:uid="{00000000-0004-0000-0000-00007F040000}"/>
     <hyperlink ref="C38" r:id="rId1153" xr:uid="{00000000-0004-0000-0000-000080040000}"/>
-    <hyperlink ref="C1153" r:id="rId1154" xr:uid="{00000000-0004-0000-0000-000081040000}"/>
-    <hyperlink ref="C1154" r:id="rId1155" xr:uid="{00000000-0004-0000-0000-000082040000}"/>
-    <hyperlink ref="C1155" r:id="rId1156" xr:uid="{00000000-0004-0000-0000-000083040000}"/>
-    <hyperlink ref="C1156" r:id="rId1157" xr:uid="{00000000-0004-0000-0000-000084040000}"/>
-    <hyperlink ref="C1157" r:id="rId1158" xr:uid="{00000000-0004-0000-0000-000085040000}"/>
-    <hyperlink ref="C1158" r:id="rId1159" xr:uid="{00000000-0004-0000-0000-000086040000}"/>
-    <hyperlink ref="C1159" r:id="rId1160" xr:uid="{00000000-0004-0000-0000-000087040000}"/>
-    <hyperlink ref="C1160" r:id="rId1161" xr:uid="{00000000-0004-0000-0000-000088040000}"/>
-    <hyperlink ref="C1161" r:id="rId1162" xr:uid="{00000000-0004-0000-0000-000089040000}"/>
-    <hyperlink ref="C1162" r:id="rId1163" xr:uid="{00000000-0004-0000-0000-00008A040000}"/>
-    <hyperlink ref="C1163" r:id="rId1164" xr:uid="{00000000-0004-0000-0000-00008B040000}"/>
-    <hyperlink ref="C1164" r:id="rId1165" xr:uid="{00000000-0004-0000-0000-00008C040000}"/>
-    <hyperlink ref="C1165" r:id="rId1166" xr:uid="{00000000-0004-0000-0000-00008D040000}"/>
-    <hyperlink ref="C1166" r:id="rId1167" xr:uid="{00000000-0004-0000-0000-00008E040000}"/>
-    <hyperlink ref="C1167" r:id="rId1168" xr:uid="{00000000-0004-0000-0000-00008F040000}"/>
-    <hyperlink ref="C1168" r:id="rId1169" xr:uid="{00000000-0004-0000-0000-000090040000}"/>
-    <hyperlink ref="C1169" r:id="rId1170" xr:uid="{00000000-0004-0000-0000-000091040000}"/>
-    <hyperlink ref="C1170" r:id="rId1171" xr:uid="{00000000-0004-0000-0000-000092040000}"/>
+    <hyperlink ref="C1155" r:id="rId1154" xr:uid="{00000000-0004-0000-0000-000081040000}"/>
+    <hyperlink ref="C1156" r:id="rId1155" xr:uid="{00000000-0004-0000-0000-000082040000}"/>
+    <hyperlink ref="C1157" r:id="rId1156" xr:uid="{00000000-0004-0000-0000-000083040000}"/>
+    <hyperlink ref="C1158" r:id="rId1157" xr:uid="{00000000-0004-0000-0000-000084040000}"/>
+    <hyperlink ref="C1159" r:id="rId1158" xr:uid="{00000000-0004-0000-0000-000085040000}"/>
+    <hyperlink ref="C1160" r:id="rId1159" xr:uid="{00000000-0004-0000-0000-000086040000}"/>
+    <hyperlink ref="C1161" r:id="rId1160" xr:uid="{00000000-0004-0000-0000-000087040000}"/>
+    <hyperlink ref="C1162" r:id="rId1161" xr:uid="{00000000-0004-0000-0000-000088040000}"/>
+    <hyperlink ref="C1163" r:id="rId1162" xr:uid="{00000000-0004-0000-0000-000089040000}"/>
+    <hyperlink ref="C1164" r:id="rId1163" xr:uid="{00000000-0004-0000-0000-00008A040000}"/>
+    <hyperlink ref="C1165" r:id="rId1164" xr:uid="{00000000-0004-0000-0000-00008B040000}"/>
+    <hyperlink ref="C1166" r:id="rId1165" xr:uid="{00000000-0004-0000-0000-00008C040000}"/>
+    <hyperlink ref="C1167" r:id="rId1166" xr:uid="{00000000-0004-0000-0000-00008D040000}"/>
+    <hyperlink ref="C1168" r:id="rId1167" xr:uid="{00000000-0004-0000-0000-00008E040000}"/>
+    <hyperlink ref="C1169" r:id="rId1168" xr:uid="{00000000-0004-0000-0000-00008F040000}"/>
+    <hyperlink ref="C1170" r:id="rId1169" xr:uid="{00000000-0004-0000-0000-000090040000}"/>
+    <hyperlink ref="C1171" r:id="rId1170" xr:uid="{00000000-0004-0000-0000-000091040000}"/>
+    <hyperlink ref="C1172" r:id="rId1171" xr:uid="{00000000-0004-0000-0000-000092040000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/danish_artwork_review.xlsx
+++ b/data/danish_artwork_review.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EPGoal\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2257F572-88AF-4F5B-A5CF-1AB6D85636EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BA6FC9F-A7EA-4529-9C8B-F1ACD119A5B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="23520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Danske backdrops" sheetId="1" r:id="rId1"/>
